--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Como usar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$P$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$P$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +68,9 @@
     <font>
       <color rgb="00595959"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -109,7 +112,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -153,12 +156,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -188,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -196,22 +204,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -219,7 +233,10 @@
     <xf numFmtId="165" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,14 +245,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -247,6 +264,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -258,6 +276,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -270,7 +289,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -307,10 +326,13 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -996,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1007,6 +1029,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1019,7 +1042,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Acompanha o mês selecionado na aba Comparativo (célula B3). Desvio positivo = gastou acima do orçado.</t>
+          <t>Acompanha o mês selecionado na aba Comparativo (célula B3). Desvio positivo = gastou acima do orçado. ATENÇÃO: confira a coluna 'Linhas lançadas' — desvio negativo em linha não lançada é ausência de dado, não economia.</t>
         </is>
       </c>
     </row>
@@ -1080,6 +1103,11 @@
           <t>% Executado do ano</t>
         </is>
       </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Linhas lançadas</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -1093,15 +1121,15 @@
         </is>
       </c>
       <c r="C6" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"Jurídico",Planejado!$C$5:$C$25,"Equipe")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"Jurídico",Planejado!$C$5:$C$26,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="8">
@@ -1116,6 +1144,10 @@
         <f>IFERROR(E6/C6,"")</f>
         <v/>
       </c>
+      <c r="I6" s="10">
+        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Equipe")</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -1129,15 +1161,15 @@
         </is>
       </c>
       <c r="C7" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"Jurídico",Planejado!$C$5:$C$25,"Despesas")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"Jurídico",Planejado!$C$5:$C$26,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="8">
@@ -1152,40 +1184,48 @@
         <f>IFERROR(E7/C7,"")</f>
         <v/>
       </c>
+      <c r="I7" s="10">
+        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Despesas")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Equipe + Despesas</t>
         </is>
       </c>
-      <c r="C8" s="11">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D8" s="11">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="E8" s="11">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="F8" s="11">
+      <c r="C8" s="12">
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D8" s="12">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="E8" s="12">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="F8" s="12">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>IFERROR(F8/D8,"")</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <f>IFERROR(E8/C8,"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="14">
+        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"Jurídico")</f>
         <v/>
       </c>
     </row>
@@ -1201,15 +1241,15 @@
         </is>
       </c>
       <c r="C9" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"TI",Planejado!$C$5:$C$25,"Equipe")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"TI",Planejado!$C$5:$C$26,"Equipe")</f>
         <v/>
       </c>
       <c r="D9" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Equipe")</f>
         <v/>
       </c>
       <c r="E9" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Equipe")</f>
         <v/>
       </c>
       <c r="F9" s="8">
@@ -1224,6 +1264,10 @@
         <f>IFERROR(E9/C9,"")</f>
         <v/>
       </c>
+      <c r="I9" s="10">
+        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Equipe")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -1237,15 +1281,15 @@
         </is>
       </c>
       <c r="C10" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"TI",Planejado!$C$5:$C$25,"Despesas")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"TI",Planejado!$C$5:$C$26,"Despesas")</f>
         <v/>
       </c>
       <c r="D10" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Despesas")</f>
         <v/>
       </c>
       <c r="E10" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Despesas")</f>
         <v/>
       </c>
       <c r="F10" s="8">
@@ -1260,77 +1304,89 @@
         <f>IFERROR(E10/C10,"")</f>
         <v/>
       </c>
+      <c r="I10" s="10">
+        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Despesas")</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Equipe + Despesas</t>
         </is>
       </c>
-      <c r="C11" s="11">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="D11" s="11">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="F11" s="11">
+      <c r="C11" s="12">
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="D11" s="12">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E11" s="12">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F11" s="12">
         <f>E11-D11</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <f>IFERROR(F11/D11,"")</f>
         <v/>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <f>IFERROR(E11/C11,"")</f>
         <v/>
       </c>
+      <c r="I11" s="14">
+        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr"/>
-      <c r="C12" s="14">
-        <f>SUM(Planejado!$P$5:$P$25)</f>
-        <v/>
-      </c>
-      <c r="D12" s="14">
-        <f>SUM(Comparativo!$I$6:$I$26)</f>
-        <v/>
-      </c>
-      <c r="E12" s="14">
-        <f>SUM(Comparativo!$J$6:$J$26)</f>
-        <v/>
-      </c>
-      <c r="F12" s="14">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="16">
+        <f>SUM(Planejado!$P$5:$P$26)</f>
+        <v/>
+      </c>
+      <c r="D12" s="16">
+        <f>SUM(Comparativo!$I$6:$I$27)</f>
+        <v/>
+      </c>
+      <c r="E12" s="16">
+        <f>SUM(Comparativo!$J$6:$J$27)</f>
+        <v/>
+      </c>
+      <c r="F12" s="16">
         <f>E12-D12</f>
         <v/>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="17">
         <f>IFERROR(F12/D12,"")</f>
         <v/>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="17">
         <f>IFERROR(E12/C12,"")</f>
         <v/>
       </c>
+      <c r="I12" s="18">
+        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$27)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>MAIORES DESVIOS DO ACUMULADO (top 5 acima do orçado)</t>
         </is>
@@ -1375,155 +1431,155 @@
       <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="n">
+      <c r="A17" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C17" s="18">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="19">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="19">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="19">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="20">
+      <c r="B17" s="21">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A17),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="21">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A17),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="22">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A17),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="22">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A17),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="22">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A17),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="23">
         <f>IFERROR(F17/D17,"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="n">
+      <c r="A18" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="18">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C18" s="18">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="19">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="19">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="19">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="20">
+      <c r="B18" s="21">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A18),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C18" s="21">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A18),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="22">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A18),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="22">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A18),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="22">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A18),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="23">
         <f>IFERROR(F18/D18,"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n">
+      <c r="A19" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="18">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C19" s="18">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="19">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="19">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="19">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="20">
+      <c r="B19" s="21">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A19),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="21">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A19),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="22">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A19),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="22">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A19),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="22">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A19),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="23">
         <f>IFERROR(F19/D19,"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="n">
+      <c r="A20" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="18">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C20" s="18">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="19">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="19">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="19">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="20">
+      <c r="B20" s="21">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A20),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="21">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A20),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="22">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A20),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="22">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A20),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="22">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A20),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="23">
         <f>IFERROR(F20/D20,"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n">
+      <c r="A21" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="18">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C21" s="18">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="19">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="19">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="19">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="20">
+      <c r="B21" s="21">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A21),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="21">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A21),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="22">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A21),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="22">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A21),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="22">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A21),Comparativo!$O$6:$O$27,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="23">
         <f>IFERROR(F21/D21,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1535,7 +1591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1553,6 +1609,7 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="10" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1575,17 +1632,17 @@
           <t>Mês de referência:</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
-        <is>
-          <t>Ago/26</t>
-        </is>
-      </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Jul/26</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Mês nº:</t>
         </is>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="26">
         <f>MATCH($B$3,Planejado!$H$4:$O$4,0)</f>
         <v/>
       </c>
@@ -1661,1365 +1718,1520 @@
           <t>Situação</t>
         </is>
       </c>
-      <c r="O5" s="24" t="inlineStr">
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t>(aux ranking)</t>
         </is>
       </c>
+      <c r="P5" s="27" t="inlineStr">
+        <is>
+          <t>(aux meses lançados)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="25">
+      <c r="A6" s="28">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="28">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="28">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="29">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="28">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="30">
         <f>INDEX(Planejado!$H5:$O5,$D$3)</f>
         <v/>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="30">
         <f>INDEX(Realizado!$H5:$O5,$D$3)</f>
         <v/>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="30">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="30">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H5:$O5)</f>
         <v/>
       </c>
-      <c r="J6" s="27">
+      <c r="J6" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H5:$O5)</f>
         <v/>
       </c>
-      <c r="K6" s="27">
+      <c r="K6" s="30">
         <f>J6-I6</f>
         <v/>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="31">
         <f>IFERROR(K6/I6,"")</f>
         <v/>
       </c>
-      <c r="M6" s="28">
+      <c r="M6" s="31">
         <f>IFERROR(J6/I6,"")</f>
         <v/>
       </c>
-      <c r="N6" s="29">
-        <f>IF(AND(I6=0,J6=0),"—",IF(J6=0,"Sem lançamento",IF(I6=0,"Não orçado",IF(K6&gt;0.05*I6,"Acima do orçado",IF(K6&lt;-0.05*I6,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O6" s="24">
+      <c r="N6" s="32">
+        <f>IF(P6=0,"Sem lançamento",IF(AND(I6=0,J6=0),"—",IF(I6=0,"Não orçado",IF(K6&gt;0.05*I6,"Acima do orçado",IF(K6&lt;-0.05*I6,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O6" s="27">
         <f>IF(K6&gt;1,K6+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P6" s="33">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H5:$O5&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="25">
+      <c r="A7" s="28">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="28">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="28">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="29">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="28">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="30">
         <f>INDEX(Planejado!$H6:$O6,$D$3)</f>
         <v/>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="30">
         <f>INDEX(Realizado!$H6:$O6,$D$3)</f>
         <v/>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="30">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="30">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H6:$O6)</f>
         <v/>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H6:$O6)</f>
         <v/>
       </c>
-      <c r="K7" s="27">
+      <c r="K7" s="30">
         <f>J7-I7</f>
         <v/>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="31">
         <f>IFERROR(K7/I7,"")</f>
         <v/>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="31">
         <f>IFERROR(J7/I7,"")</f>
         <v/>
       </c>
-      <c r="N7" s="29">
-        <f>IF(AND(I7=0,J7=0),"—",IF(J7=0,"Sem lançamento",IF(I7=0,"Não orçado",IF(K7&gt;0.05*I7,"Acima do orçado",IF(K7&lt;-0.05*I7,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O7" s="24">
+      <c r="N7" s="32">
+        <f>IF(P7=0,"Sem lançamento",IF(AND(I7=0,J7=0),"—",IF(I7=0,"Não orçado",IF(K7&gt;0.05*I7,"Acima do orçado",IF(K7&lt;-0.05*I7,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O7" s="27">
         <f>IF(K7&gt;1,K7+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P7" s="33">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H6:$O6&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="25">
+      <c r="A8" s="28">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="28">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="28">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="29">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="28">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="30">
         <f>INDEX(Planejado!$H7:$O7,$D$3)</f>
         <v/>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="30">
         <f>INDEX(Realizado!$H7:$O7,$D$3)</f>
         <v/>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="30">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="30">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H7:$O7)</f>
         <v/>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H7:$O7)</f>
         <v/>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="30">
         <f>J8-I8</f>
         <v/>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="31">
         <f>IFERROR(K8/I8,"")</f>
         <v/>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="31">
         <f>IFERROR(J8/I8,"")</f>
         <v/>
       </c>
-      <c r="N8" s="29">
-        <f>IF(AND(I8=0,J8=0),"—",IF(J8=0,"Sem lançamento",IF(I8=0,"Não orçado",IF(K8&gt;0.05*I8,"Acima do orçado",IF(K8&lt;-0.05*I8,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O8" s="24">
+      <c r="N8" s="32">
+        <f>IF(P8=0,"Sem lançamento",IF(AND(I8=0,J8=0),"—",IF(I8=0,"Não orçado",IF(K8&gt;0.05*I8,"Acima do orçado",IF(K8&lt;-0.05*I8,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O8" s="27">
         <f>IF(K8&gt;1,K8+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P8" s="33">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H7:$O7&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="25">
+      <c r="A9" s="28">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="28">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="28">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="29">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="28">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="30">
         <f>INDEX(Planejado!$H8:$O8,$D$3)</f>
         <v/>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="30">
         <f>INDEX(Realizado!$H8:$O8,$D$3)</f>
         <v/>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="30">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="30">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H8:$O8)</f>
         <v/>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H8:$O8)</f>
         <v/>
       </c>
-      <c r="K9" s="27">
+      <c r="K9" s="30">
         <f>J9-I9</f>
         <v/>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="31">
         <f>IFERROR(K9/I9,"")</f>
         <v/>
       </c>
-      <c r="M9" s="28">
+      <c r="M9" s="31">
         <f>IFERROR(J9/I9,"")</f>
         <v/>
       </c>
-      <c r="N9" s="29">
-        <f>IF(AND(I9=0,J9=0),"—",IF(J9=0,"Sem lançamento",IF(I9=0,"Não orçado",IF(K9&gt;0.05*I9,"Acima do orçado",IF(K9&lt;-0.05*I9,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O9" s="24">
+      <c r="N9" s="32">
+        <f>IF(P9=0,"Sem lançamento",IF(AND(I9=0,J9=0),"—",IF(I9=0,"Não orçado",IF(K9&gt;0.05*I9,"Acima do orçado",IF(K9&lt;-0.05*I9,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O9" s="27">
         <f>IF(K9&gt;1,K9+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P9" s="33">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H8:$O8&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="25">
+      <c r="A10" s="28">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="28">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="28">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="29">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="28">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="30">
         <f>INDEX(Planejado!$H9:$O9,$D$3)</f>
         <v/>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="30">
         <f>INDEX(Realizado!$H9:$O9,$D$3)</f>
         <v/>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="30">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="30">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H9:$O9)</f>
         <v/>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H9:$O9)</f>
         <v/>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="30">
         <f>J10-I10</f>
         <v/>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="31">
         <f>IFERROR(K10/I10,"")</f>
         <v/>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="31">
         <f>IFERROR(J10/I10,"")</f>
         <v/>
       </c>
-      <c r="N10" s="29">
-        <f>IF(AND(I10=0,J10=0),"—",IF(J10=0,"Sem lançamento",IF(I10=0,"Não orçado",IF(K10&gt;0.05*I10,"Acima do orçado",IF(K10&lt;-0.05*I10,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O10" s="24">
+      <c r="N10" s="32">
+        <f>IF(P10=0,"Sem lançamento",IF(AND(I10=0,J10=0),"—",IF(I10=0,"Não orçado",IF(K10&gt;0.05*I10,"Acima do orçado",IF(K10&lt;-0.05*I10,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O10" s="27">
         <f>IF(K10&gt;1,K10+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P10" s="33">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H9:$O9&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="25">
+      <c r="A11" s="28">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="28">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="28">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="29">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="28">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="30">
         <f>INDEX(Planejado!$H10:$O10,$D$3)</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="30">
         <f>INDEX(Realizado!$H10:$O10,$D$3)</f>
         <v/>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="30">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="30">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H10:$O10)</f>
         <v/>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H10:$O10)</f>
         <v/>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="30">
         <f>J11-I11</f>
         <v/>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="31">
         <f>IFERROR(K11/I11,"")</f>
         <v/>
       </c>
-      <c r="M11" s="28">
+      <c r="M11" s="31">
         <f>IFERROR(J11/I11,"")</f>
         <v/>
       </c>
-      <c r="N11" s="29">
-        <f>IF(AND(I11=0,J11=0),"—",IF(J11=0,"Sem lançamento",IF(I11=0,"Não orçado",IF(K11&gt;0.05*I11,"Acima do orçado",IF(K11&lt;-0.05*I11,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O11" s="24">
+      <c r="N11" s="32">
+        <f>IF(P11=0,"Sem lançamento",IF(AND(I11=0,J11=0),"—",IF(I11=0,"Não orçado",IF(K11&gt;0.05*I11,"Acima do orçado",IF(K11&lt;-0.05*I11,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O11" s="27">
         <f>IF(K11&gt;1,K11+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P11" s="33">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H10:$O10&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="25">
+      <c r="A12" s="28">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="28">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="28">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="29">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="28">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="30">
         <f>INDEX(Planejado!$H11:$O11,$D$3)</f>
         <v/>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="30">
         <f>INDEX(Realizado!$H11:$O11,$D$3)</f>
         <v/>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="30">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="30">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H11:$O11)</f>
         <v/>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H11:$O11)</f>
         <v/>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="30">
         <f>J12-I12</f>
         <v/>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="31">
         <f>IFERROR(K12/I12,"")</f>
         <v/>
       </c>
-      <c r="M12" s="28">
+      <c r="M12" s="31">
         <f>IFERROR(J12/I12,"")</f>
         <v/>
       </c>
-      <c r="N12" s="29">
-        <f>IF(AND(I12=0,J12=0),"—",IF(J12=0,"Sem lançamento",IF(I12=0,"Não orçado",IF(K12&gt;0.05*I12,"Acima do orçado",IF(K12&lt;-0.05*I12,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O12" s="24">
+      <c r="N12" s="32">
+        <f>IF(P12=0,"Sem lançamento",IF(AND(I12=0,J12=0),"—",IF(I12=0,"Não orçado",IF(K12&gt;0.05*I12,"Acima do orçado",IF(K12&lt;-0.05*I12,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O12" s="27">
         <f>IF(K12&gt;1,K12+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P12" s="33">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H11:$O11&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="25">
+      <c r="A13" s="28">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="28">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="28">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="29">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="28">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="30">
         <f>INDEX(Planejado!$H12:$O12,$D$3)</f>
         <v/>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="30">
         <f>INDEX(Realizado!$H12:$O12,$D$3)</f>
         <v/>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="30">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="30">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H12:$O12)</f>
         <v/>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H12:$O12)</f>
         <v/>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="30">
         <f>J13-I13</f>
         <v/>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="31">
         <f>IFERROR(K13/I13,"")</f>
         <v/>
       </c>
-      <c r="M13" s="28">
+      <c r="M13" s="31">
         <f>IFERROR(J13/I13,"")</f>
         <v/>
       </c>
-      <c r="N13" s="29">
-        <f>IF(AND(I13=0,J13=0),"—",IF(J13=0,"Sem lançamento",IF(I13=0,"Não orçado",IF(K13&gt;0.05*I13,"Acima do orçado",IF(K13&lt;-0.05*I13,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O13" s="24">
+      <c r="N13" s="32">
+        <f>IF(P13=0,"Sem lançamento",IF(AND(I13=0,J13=0),"—",IF(I13=0,"Não orçado",IF(K13&gt;0.05*I13,"Acima do orçado",IF(K13&lt;-0.05*I13,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O13" s="27">
         <f>IF(K13&gt;1,K13+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P13" s="33">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H12:$O12&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="25">
+      <c r="A14" s="28">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="28">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="28">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="29">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="28">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="30">
         <f>INDEX(Planejado!$H13:$O13,$D$3)</f>
         <v/>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="30">
         <f>INDEX(Realizado!$H13:$O13,$D$3)</f>
         <v/>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="30">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="30">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H13:$O13)</f>
         <v/>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H13:$O13)</f>
         <v/>
       </c>
-      <c r="K14" s="27">
+      <c r="K14" s="30">
         <f>J14-I14</f>
         <v/>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="31">
         <f>IFERROR(K14/I14,"")</f>
         <v/>
       </c>
-      <c r="M14" s="28">
+      <c r="M14" s="31">
         <f>IFERROR(J14/I14,"")</f>
         <v/>
       </c>
-      <c r="N14" s="29">
-        <f>IF(AND(I14=0,J14=0),"—",IF(J14=0,"Sem lançamento",IF(I14=0,"Não orçado",IF(K14&gt;0.05*I14,"Acima do orçado",IF(K14&lt;-0.05*I14,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O14" s="24">
+      <c r="N14" s="32">
+        <f>IF(P14=0,"Sem lançamento",IF(AND(I14=0,J14=0),"—",IF(I14=0,"Não orçado",IF(K14&gt;0.05*I14,"Acima do orçado",IF(K14&lt;-0.05*I14,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O14" s="27">
         <f>IF(K14&gt;1,K14+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P14" s="33">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H13:$O13&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="30">
+      <c r="A15" s="28">
         <f>Planejado!A14</f>
         <v/>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="28">
         <f>Planejado!B14</f>
         <v/>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="28">
         <f>Planejado!C14</f>
         <v/>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="29">
         <f>Planejado!D14</f>
         <v/>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="28">
         <f>Planejado!G14</f>
         <v/>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="30">
         <f>INDEX(Planejado!$H14:$O14,$D$3)</f>
         <v/>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="30">
         <f>INDEX(Realizado!$H14:$O14,$D$3)</f>
         <v/>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="30">
         <f>G15-F15</f>
         <v/>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="30">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H14:$O14)</f>
         <v/>
       </c>
-      <c r="J15" s="32">
+      <c r="J15" s="30">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H14:$O14)</f>
         <v/>
       </c>
-      <c r="K15" s="32">
+      <c r="K15" s="30">
         <f>J15-I15</f>
         <v/>
       </c>
-      <c r="L15" s="33">
+      <c r="L15" s="31">
         <f>IFERROR(K15/I15,"")</f>
         <v/>
       </c>
-      <c r="M15" s="33">
+      <c r="M15" s="31">
         <f>IFERROR(J15/I15,"")</f>
         <v/>
       </c>
-      <c r="N15" s="34">
-        <f>IF(AND(I15=0,J15=0),"—",IF(J15=0,"Sem lançamento",IF(I15=0,"Não orçado",IF(K15&gt;0.05*I15,"Acima do orçado",IF(K15&lt;-0.05*I15,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O15" s="24">
+      <c r="N15" s="32">
+        <f>IF(P15=0,"Sem lançamento",IF(AND(I15=0,J15=0),"—",IF(I15=0,"Não orçado",IF(K15&gt;0.05*I15,"Acima do orçado",IF(K15&lt;-0.05*I15,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O15" s="27">
         <f>IF(K15&gt;1,K15+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P15" s="33">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H14:$O14&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="30">
+      <c r="A16" s="34">
         <f>Planejado!A15</f>
         <v/>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="34">
         <f>Planejado!B15</f>
         <v/>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="34">
         <f>Planejado!C15</f>
         <v/>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="35">
         <f>Planejado!D15</f>
         <v/>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="34">
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="36">
         <f>INDEX(Planejado!$H15:$O15,$D$3)</f>
         <v/>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="36">
         <f>INDEX(Realizado!$H15:$O15,$D$3)</f>
         <v/>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="36">
         <f>G16-F16</f>
         <v/>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H15:$O15)</f>
         <v/>
       </c>
-      <c r="J16" s="32">
+      <c r="J16" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H15:$O15)</f>
         <v/>
       </c>
-      <c r="K16" s="32">
+      <c r="K16" s="36">
         <f>J16-I16</f>
         <v/>
       </c>
-      <c r="L16" s="33">
+      <c r="L16" s="37">
         <f>IFERROR(K16/I16,"")</f>
         <v/>
       </c>
-      <c r="M16" s="33">
+      <c r="M16" s="37">
         <f>IFERROR(J16/I16,"")</f>
         <v/>
       </c>
-      <c r="N16" s="34">
-        <f>IF(AND(I16=0,J16=0),"—",IF(J16=0,"Sem lançamento",IF(I16=0,"Não orçado",IF(K16&gt;0.05*I16,"Acima do orçado",IF(K16&lt;-0.05*I16,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O16" s="24">
+      <c r="N16" s="38">
+        <f>IF(P16=0,"Sem lançamento",IF(AND(I16=0,J16=0),"—",IF(I16=0,"Não orçado",IF(K16&gt;0.05*I16,"Acima do orçado",IF(K16&lt;-0.05*I16,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O16" s="27">
         <f>IF(K16&gt;1,K16+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P16" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H15:$O15&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="30">
+      <c r="A17" s="34">
         <f>Planejado!A16</f>
         <v/>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="34">
         <f>Planejado!B16</f>
         <v/>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="34">
         <f>Planejado!C16</f>
         <v/>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="35">
         <f>Planejado!D16</f>
         <v/>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="34">
         <f>Planejado!G16</f>
         <v/>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="36">
         <f>INDEX(Planejado!$H16:$O16,$D$3)</f>
         <v/>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="36">
         <f>INDEX(Realizado!$H16:$O16,$D$3)</f>
         <v/>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="36">
         <f>G17-F17</f>
         <v/>
       </c>
-      <c r="I17" s="32">
+      <c r="I17" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H16:$O16)</f>
         <v/>
       </c>
-      <c r="J17" s="32">
+      <c r="J17" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H16:$O16)</f>
         <v/>
       </c>
-      <c r="K17" s="32">
+      <c r="K17" s="36">
         <f>J17-I17</f>
         <v/>
       </c>
-      <c r="L17" s="33">
+      <c r="L17" s="37">
         <f>IFERROR(K17/I17,"")</f>
         <v/>
       </c>
-      <c r="M17" s="33">
+      <c r="M17" s="37">
         <f>IFERROR(J17/I17,"")</f>
         <v/>
       </c>
-      <c r="N17" s="34">
-        <f>IF(AND(I17=0,J17=0),"—",IF(J17=0,"Sem lançamento",IF(I17=0,"Não orçado",IF(K17&gt;0.05*I17,"Acima do orçado",IF(K17&lt;-0.05*I17,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O17" s="24">
+      <c r="N17" s="38">
+        <f>IF(P17=0,"Sem lançamento",IF(AND(I17=0,J17=0),"—",IF(I17=0,"Não orçado",IF(K17&gt;0.05*I17,"Acima do orçado",IF(K17&lt;-0.05*I17,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O17" s="27">
         <f>IF(K17&gt;1,K17+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P17" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H16:$O16&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="30">
+      <c r="A18" s="34">
         <f>Planejado!A17</f>
         <v/>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="34">
         <f>Planejado!B17</f>
         <v/>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="34">
         <f>Planejado!C17</f>
         <v/>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="35">
         <f>Planejado!D17</f>
         <v/>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="34">
         <f>Planejado!G17</f>
         <v/>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="36">
         <f>INDEX(Planejado!$H17:$O17,$D$3)</f>
         <v/>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="36">
         <f>INDEX(Realizado!$H17:$O17,$D$3)</f>
         <v/>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="36">
         <f>G18-F18</f>
         <v/>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H17:$O17)</f>
         <v/>
       </c>
-      <c r="J18" s="32">
+      <c r="J18" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H17:$O17)</f>
         <v/>
       </c>
-      <c r="K18" s="32">
+      <c r="K18" s="36">
         <f>J18-I18</f>
         <v/>
       </c>
-      <c r="L18" s="33">
+      <c r="L18" s="37">
         <f>IFERROR(K18/I18,"")</f>
         <v/>
       </c>
-      <c r="M18" s="33">
+      <c r="M18" s="37">
         <f>IFERROR(J18/I18,"")</f>
         <v/>
       </c>
-      <c r="N18" s="34">
-        <f>IF(AND(I18=0,J18=0),"—",IF(J18=0,"Sem lançamento",IF(I18=0,"Não orçado",IF(K18&gt;0.05*I18,"Acima do orçado",IF(K18&lt;-0.05*I18,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O18" s="24">
+      <c r="N18" s="38">
+        <f>IF(P18=0,"Sem lançamento",IF(AND(I18=0,J18=0),"—",IF(I18=0,"Não orçado",IF(K18&gt;0.05*I18,"Acima do orçado",IF(K18&lt;-0.05*I18,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O18" s="27">
         <f>IF(K18&gt;1,K18+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P18" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H17:$O17&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="30">
+      <c r="A19" s="34">
         <f>Planejado!A18</f>
         <v/>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="34">
         <f>Planejado!B18</f>
         <v/>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="34">
         <f>Planejado!C18</f>
         <v/>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="35">
         <f>Planejado!D18</f>
         <v/>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="34">
         <f>Planejado!G18</f>
         <v/>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="36">
         <f>INDEX(Planejado!$H18:$O18,$D$3)</f>
         <v/>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="36">
         <f>INDEX(Realizado!$H18:$O18,$D$3)</f>
         <v/>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="36">
         <f>G19-F19</f>
         <v/>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H18:$O18)</f>
         <v/>
       </c>
-      <c r="J19" s="32">
+      <c r="J19" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H18:$O18)</f>
         <v/>
       </c>
-      <c r="K19" s="32">
+      <c r="K19" s="36">
         <f>J19-I19</f>
         <v/>
       </c>
-      <c r="L19" s="33">
+      <c r="L19" s="37">
         <f>IFERROR(K19/I19,"")</f>
         <v/>
       </c>
-      <c r="M19" s="33">
+      <c r="M19" s="37">
         <f>IFERROR(J19/I19,"")</f>
         <v/>
       </c>
-      <c r="N19" s="34">
-        <f>IF(AND(I19=0,J19=0),"—",IF(J19=0,"Sem lançamento",IF(I19=0,"Não orçado",IF(K19&gt;0.05*I19,"Acima do orçado",IF(K19&lt;-0.05*I19,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O19" s="24">
+      <c r="N19" s="38">
+        <f>IF(P19=0,"Sem lançamento",IF(AND(I19=0,J19=0),"—",IF(I19=0,"Não orçado",IF(K19&gt;0.05*I19,"Acima do orçado",IF(K19&lt;-0.05*I19,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O19" s="27">
         <f>IF(K19&gt;1,K19+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P19" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H18:$O18&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="30">
+      <c r="A20" s="34">
         <f>Planejado!A19</f>
         <v/>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="34">
         <f>Planejado!B19</f>
         <v/>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="34">
         <f>Planejado!C19</f>
         <v/>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="35">
         <f>Planejado!D19</f>
         <v/>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="34">
         <f>Planejado!G19</f>
         <v/>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="36">
         <f>INDEX(Planejado!$H19:$O19,$D$3)</f>
         <v/>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="36">
         <f>INDEX(Realizado!$H19:$O19,$D$3)</f>
         <v/>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="36">
         <f>G20-F20</f>
         <v/>
       </c>
-      <c r="I20" s="32">
+      <c r="I20" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H19:$O19)</f>
         <v/>
       </c>
-      <c r="J20" s="32">
+      <c r="J20" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H19:$O19)</f>
         <v/>
       </c>
-      <c r="K20" s="32">
+      <c r="K20" s="36">
         <f>J20-I20</f>
         <v/>
       </c>
-      <c r="L20" s="33">
+      <c r="L20" s="37">
         <f>IFERROR(K20/I20,"")</f>
         <v/>
       </c>
-      <c r="M20" s="33">
+      <c r="M20" s="37">
         <f>IFERROR(J20/I20,"")</f>
         <v/>
       </c>
-      <c r="N20" s="34">
-        <f>IF(AND(I20=0,J20=0),"—",IF(J20=0,"Sem lançamento",IF(I20=0,"Não orçado",IF(K20&gt;0.05*I20,"Acima do orçado",IF(K20&lt;-0.05*I20,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O20" s="24">
+      <c r="N20" s="38">
+        <f>IF(P20=0,"Sem lançamento",IF(AND(I20=0,J20=0),"—",IF(I20=0,"Não orçado",IF(K20&gt;0.05*I20,"Acima do orçado",IF(K20&lt;-0.05*I20,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O20" s="27">
         <f>IF(K20&gt;1,K20+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P20" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H19:$O19&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="30">
+      <c r="A21" s="34">
         <f>Planejado!A20</f>
         <v/>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="34">
         <f>Planejado!B20</f>
         <v/>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="34">
         <f>Planejado!C20</f>
         <v/>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="35">
         <f>Planejado!D20</f>
         <v/>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="34">
         <f>Planejado!G20</f>
         <v/>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="36">
         <f>INDEX(Planejado!$H20:$O20,$D$3)</f>
         <v/>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="36">
         <f>INDEX(Realizado!$H20:$O20,$D$3)</f>
         <v/>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="36">
         <f>G21-F21</f>
         <v/>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H20:$O20)</f>
         <v/>
       </c>
-      <c r="J21" s="32">
+      <c r="J21" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H20:$O20)</f>
         <v/>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="36">
         <f>J21-I21</f>
         <v/>
       </c>
-      <c r="L21" s="33">
+      <c r="L21" s="37">
         <f>IFERROR(K21/I21,"")</f>
         <v/>
       </c>
-      <c r="M21" s="33">
+      <c r="M21" s="37">
         <f>IFERROR(J21/I21,"")</f>
         <v/>
       </c>
-      <c r="N21" s="34">
-        <f>IF(AND(I21=0,J21=0),"—",IF(J21=0,"Sem lançamento",IF(I21=0,"Não orçado",IF(K21&gt;0.05*I21,"Acima do orçado",IF(K21&lt;-0.05*I21,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O21" s="24">
+      <c r="N21" s="38">
+        <f>IF(P21=0,"Sem lançamento",IF(AND(I21=0,J21=0),"—",IF(I21=0,"Não orçado",IF(K21&gt;0.05*I21,"Acima do orçado",IF(K21&lt;-0.05*I21,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O21" s="27">
         <f>IF(K21&gt;1,K21+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P21" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H20:$O20&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="30">
+      <c r="A22" s="34">
         <f>Planejado!A21</f>
         <v/>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="34">
         <f>Planejado!B21</f>
         <v/>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="34">
         <f>Planejado!C21</f>
         <v/>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="35">
         <f>Planejado!D21</f>
         <v/>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="34">
         <f>Planejado!G21</f>
         <v/>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="36">
         <f>INDEX(Planejado!$H21:$O21,$D$3)</f>
         <v/>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="36">
         <f>INDEX(Realizado!$H21:$O21,$D$3)</f>
         <v/>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="36">
         <f>G22-F22</f>
         <v/>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H21:$O21)</f>
         <v/>
       </c>
-      <c r="J22" s="32">
+      <c r="J22" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H21:$O21)</f>
         <v/>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="36">
         <f>J22-I22</f>
         <v/>
       </c>
-      <c r="L22" s="33">
+      <c r="L22" s="37">
         <f>IFERROR(K22/I22,"")</f>
         <v/>
       </c>
-      <c r="M22" s="33">
+      <c r="M22" s="37">
         <f>IFERROR(J22/I22,"")</f>
         <v/>
       </c>
-      <c r="N22" s="34">
-        <f>IF(AND(I22=0,J22=0),"—",IF(J22=0,"Sem lançamento",IF(I22=0,"Não orçado",IF(K22&gt;0.05*I22,"Acima do orçado",IF(K22&lt;-0.05*I22,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O22" s="24">
+      <c r="N22" s="38">
+        <f>IF(P22=0,"Sem lançamento",IF(AND(I22=0,J22=0),"—",IF(I22=0,"Não orçado",IF(K22&gt;0.05*I22,"Acima do orçado",IF(K22&lt;-0.05*I22,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O22" s="27">
         <f>IF(K22&gt;1,K22+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P22" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H21:$O21&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="30">
+      <c r="A23" s="34">
         <f>Planejado!A22</f>
         <v/>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="34">
         <f>Planejado!B22</f>
         <v/>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="34">
         <f>Planejado!C22</f>
         <v/>
       </c>
-      <c r="D23" s="31">
+      <c r="D23" s="35">
         <f>Planejado!D22</f>
         <v/>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="34">
         <f>Planejado!G22</f>
         <v/>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="36">
         <f>INDEX(Planejado!$H22:$O22,$D$3)</f>
         <v/>
       </c>
-      <c r="G23" s="32">
+      <c r="G23" s="36">
         <f>INDEX(Realizado!$H22:$O22,$D$3)</f>
         <v/>
       </c>
-      <c r="H23" s="32">
+      <c r="H23" s="36">
         <f>G23-F23</f>
         <v/>
       </c>
-      <c r="I23" s="32">
+      <c r="I23" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H22:$O22)</f>
         <v/>
       </c>
-      <c r="J23" s="32">
+      <c r="J23" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H22:$O22)</f>
         <v/>
       </c>
-      <c r="K23" s="32">
+      <c r="K23" s="36">
         <f>J23-I23</f>
         <v/>
       </c>
-      <c r="L23" s="33">
+      <c r="L23" s="37">
         <f>IFERROR(K23/I23,"")</f>
         <v/>
       </c>
-      <c r="M23" s="33">
+      <c r="M23" s="37">
         <f>IFERROR(J23/I23,"")</f>
         <v/>
       </c>
-      <c r="N23" s="34">
-        <f>IF(AND(I23=0,J23=0),"—",IF(J23=0,"Sem lançamento",IF(I23=0,"Não orçado",IF(K23&gt;0.05*I23,"Acima do orçado",IF(K23&lt;-0.05*I23,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O23" s="24">
+      <c r="N23" s="38">
+        <f>IF(P23=0,"Sem lançamento",IF(AND(I23=0,J23=0),"—",IF(I23=0,"Não orçado",IF(K23&gt;0.05*I23,"Acima do orçado",IF(K23&lt;-0.05*I23,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O23" s="27">
         <f>IF(K23&gt;1,K23+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P23" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H22:$O22&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="30">
+      <c r="A24" s="34">
         <f>Planejado!A23</f>
         <v/>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="34">
         <f>Planejado!B23</f>
         <v/>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="34">
         <f>Planejado!C23</f>
         <v/>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="35">
         <f>Planejado!D23</f>
         <v/>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="34">
         <f>Planejado!G23</f>
         <v/>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="36">
         <f>INDEX(Planejado!$H23:$O23,$D$3)</f>
         <v/>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="36">
         <f>INDEX(Realizado!$H23:$O23,$D$3)</f>
         <v/>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="36">
         <f>G24-F24</f>
         <v/>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H23:$O23)</f>
         <v/>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H23:$O23)</f>
         <v/>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="36">
         <f>J24-I24</f>
         <v/>
       </c>
-      <c r="L24" s="33">
+      <c r="L24" s="37">
         <f>IFERROR(K24/I24,"")</f>
         <v/>
       </c>
-      <c r="M24" s="33">
+      <c r="M24" s="37">
         <f>IFERROR(J24/I24,"")</f>
         <v/>
       </c>
-      <c r="N24" s="34">
-        <f>IF(AND(I24=0,J24=0),"—",IF(J24=0,"Sem lançamento",IF(I24=0,"Não orçado",IF(K24&gt;0.05*I24,"Acima do orçado",IF(K24&lt;-0.05*I24,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O24" s="24">
+      <c r="N24" s="38">
+        <f>IF(P24=0,"Sem lançamento",IF(AND(I24=0,J24=0),"—",IF(I24=0,"Não orçado",IF(K24&gt;0.05*I24,"Acima do orçado",IF(K24&lt;-0.05*I24,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O24" s="27">
         <f>IF(K24&gt;1,K24+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P24" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H23:$O23&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="30">
+      <c r="A25" s="34">
         <f>Planejado!A24</f>
         <v/>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="34">
         <f>Planejado!B24</f>
         <v/>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="34">
         <f>Planejado!C24</f>
         <v/>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="35">
         <f>Planejado!D24</f>
         <v/>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="34">
         <f>Planejado!G24</f>
         <v/>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="36">
         <f>INDEX(Planejado!$H24:$O24,$D$3)</f>
         <v/>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="36">
         <f>INDEX(Realizado!$H24:$O24,$D$3)</f>
         <v/>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="36">
         <f>G25-F25</f>
         <v/>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H24:$O24)</f>
         <v/>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H24:$O24)</f>
         <v/>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="36">
         <f>J25-I25</f>
         <v/>
       </c>
-      <c r="L25" s="33">
+      <c r="L25" s="37">
         <f>IFERROR(K25/I25,"")</f>
         <v/>
       </c>
-      <c r="M25" s="33">
+      <c r="M25" s="37">
         <f>IFERROR(J25/I25,"")</f>
         <v/>
       </c>
-      <c r="N25" s="34">
-        <f>IF(AND(I25=0,J25=0),"—",IF(J25=0,"Sem lançamento",IF(I25=0,"Não orçado",IF(K25&gt;0.05*I25,"Acima do orçado",IF(K25&lt;-0.05*I25,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O25" s="24">
+      <c r="N25" s="38">
+        <f>IF(P25=0,"Sem lançamento",IF(AND(I25=0,J25=0),"—",IF(I25=0,"Não orçado",IF(K25&gt;0.05*I25,"Acima do orçado",IF(K25&lt;-0.05*I25,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O25" s="27">
         <f>IF(K25&gt;1,K25+ROW()/1000000,"")</f>
         <v/>
       </c>
+      <c r="P25" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H24:$O24&lt;&gt;""))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="30">
+      <c r="A26" s="34">
         <f>Planejado!A25</f>
         <v/>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="34">
         <f>Planejado!B25</f>
         <v/>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="34">
         <f>Planejado!C25</f>
         <v/>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="35">
         <f>Planejado!D25</f>
         <v/>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="34">
         <f>Planejado!G25</f>
         <v/>
       </c>
-      <c r="F26" s="32">
+      <c r="F26" s="36">
         <f>INDEX(Planejado!$H25:$O25,$D$3)</f>
         <v/>
       </c>
-      <c r="G26" s="32">
+      <c r="G26" s="36">
         <f>INDEX(Realizado!$H25:$O25,$D$3)</f>
         <v/>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="36">
         <f>G26-F26</f>
         <v/>
       </c>
-      <c r="I26" s="32">
+      <c r="I26" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H25:$O25)</f>
         <v/>
       </c>
-      <c r="J26" s="32">
+      <c r="J26" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H25:$O25)</f>
         <v/>
       </c>
-      <c r="K26" s="32">
+      <c r="K26" s="36">
         <f>J26-I26</f>
         <v/>
       </c>
-      <c r="L26" s="33">
+      <c r="L26" s="37">
         <f>IFERROR(K26/I26,"")</f>
         <v/>
       </c>
-      <c r="M26" s="33">
+      <c r="M26" s="37">
         <f>IFERROR(J26/I26,"")</f>
         <v/>
       </c>
-      <c r="N26" s="34">
-        <f>IF(AND(I26=0,J26=0),"—",IF(J26=0,"Sem lançamento",IF(I26=0,"Não orçado",IF(K26&gt;0.05*I26,"Acima do orçado",IF(K26&lt;-0.05*I26,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O26" s="24">
+      <c r="N26" s="38">
+        <f>IF(P26=0,"Sem lançamento",IF(AND(I26=0,J26=0),"—",IF(I26=0,"Não orçado",IF(K26&gt;0.05*I26,"Acima do orçado",IF(K26&lt;-0.05*I26,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O26" s="27">
         <f>IF(K26&gt;1,K26+ROW()/1000000,"")</f>
         <v/>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="P26" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H25:$O25&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="34">
+        <f>Planejado!A26</f>
+        <v/>
+      </c>
+      <c r="B27" s="34">
+        <f>Planejado!B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="34">
+        <f>Planejado!C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="35">
+        <f>Planejado!D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="34">
+        <f>Planejado!G26</f>
+        <v/>
+      </c>
+      <c r="F27" s="36">
+        <f>INDEX(Planejado!$H26:$O26,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G27" s="36">
+        <f>INDEX(Realizado!$H26:$O26,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H27" s="36">
+        <f>G27-F27</f>
+        <v/>
+      </c>
+      <c r="I27" s="36">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H26:$O26)</f>
+        <v/>
+      </c>
+      <c r="J27" s="36">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H26:$O26)</f>
+        <v/>
+      </c>
+      <c r="K27" s="36">
+        <f>J27-I27</f>
+        <v/>
+      </c>
+      <c r="L27" s="37">
+        <f>IFERROR(K27/I27,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="37">
+        <f>IFERROR(J27/I27,"")</f>
+        <v/>
+      </c>
+      <c r="N27" s="38">
+        <f>IF(P27=0,"Sem lançamento",IF(AND(I27=0,J27=0),"—",IF(I27=0,"Não orçado",IF(K27&gt;0.05*I27,"Acima do orçado",IF(K27&lt;-0.05*I27,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O27" s="27">
+        <f>IF(K27&gt;1,K27+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P27" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H26:$O26&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="14">
-        <f>SUM(F6:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="14">
-        <f>SUM(G6:G26)</f>
-        <v/>
-      </c>
-      <c r="H27" s="14">
-        <f>SUM(H6:H26)</f>
-        <v/>
-      </c>
-      <c r="I27" s="14">
-        <f>SUM(I6:I26)</f>
-        <v/>
-      </c>
-      <c r="J27" s="14">
-        <f>SUM(J6:J26)</f>
-        <v/>
-      </c>
-      <c r="K27" s="14">
-        <f>SUM(K6:K26)</f>
-        <v/>
-      </c>
-      <c r="L27" s="35">
-        <f>IFERROR(K27/I27,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="35">
-        <f>IFERROR(J27/I27,"")</f>
-        <v/>
-      </c>
-      <c r="N27" s="13" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="16">
+        <f>SUM(F6:F27)</f>
+        <v/>
+      </c>
+      <c r="G28" s="16">
+        <f>SUM(G6:G27)</f>
+        <v/>
+      </c>
+      <c r="H28" s="16">
+        <f>SUM(H6:H27)</f>
+        <v/>
+      </c>
+      <c r="I28" s="16">
+        <f>SUM(I6:I27)</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>SUM(J6:J27)</f>
+        <v/>
+      </c>
+      <c r="K28" s="16">
+        <f>SUM(K6:K27)</f>
+        <v/>
+      </c>
+      <c r="L28" s="40">
+        <f>IFERROR(K28/I28,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="40">
+        <f>IFERROR(J28/I28,"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="15" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N26"/>
+  <autoFilter ref="A5:N27"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H26">
+  <conditionalFormatting sqref="H6:H27">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3027,7 +3239,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K26">
+  <conditionalFormatting sqref="K6:K27">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3050,7 +3262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3168,1341 +3380,1406 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>JUR-E01</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>Miguel Clepf</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>Advogado Júnior</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="H5" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="I5" s="27" t="n">
+      <c r="I5" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="J5" s="27" t="n">
+      <c r="J5" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="K5" s="27" t="n">
+      <c r="K5" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="L5" s="27" t="n">
+      <c r="L5" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="N5" s="27" t="n">
+      <c r="N5" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="O5" s="27" t="n">
+      <c r="O5" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="P5" s="36">
+      <c r="P5" s="41">
         <f>SUM(H5:O5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>JUR-E02</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
-        <is>
-          <t>Geovanna</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>Geovanna — salário bruto</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Analista Administrativo</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>CLT</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="H6" s="27" t="n">
-        <v>4825.515</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>4825.515</v>
-      </c>
-      <c r="J6" s="27" t="n">
-        <v>4825.515</v>
-      </c>
-      <c r="K6" s="27" t="n">
-        <v>4825.515</v>
-      </c>
-      <c r="L6" s="27" t="n">
-        <v>4825.515</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>4825.515</v>
-      </c>
-      <c r="N6" s="27" t="n">
-        <v>4825.515</v>
-      </c>
-      <c r="O6" s="27" t="n">
-        <v>4825.515</v>
-      </c>
-      <c r="P6" s="36">
+      <c r="H6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="I6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="J6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="K6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="L6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="M6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="N6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="O6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="P6" s="41">
         <f>SUM(H6:O6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>JUR-E02B</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Jurídico</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Geovanna — encargos e benefícios</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>INSS patronal, FGTS, provisões de 13º e férias, benefícios — PREENCHER</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>Encargos e Benefícios - CLT</t>
+        </is>
+      </c>
+      <c r="H7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="I7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="J7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="L7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="M7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="N7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="O7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="P7" s="41">
+        <f>SUM(H7:O7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>JUR-E03</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Thamar Victória</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
-        <is>
-          <t>Advogada</t>
-        </is>
-      </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>Advogada — reajuste permanente de R$ 5.000 para R$ 5.500 (revisado a partir de out/26)</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H8" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="I7" s="27" t="n">
+      <c r="I8" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="J7" s="27" t="n">
+      <c r="J8" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="K7" s="27" t="n">
+      <c r="K8" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="L7" s="27" t="n">
+      <c r="L8" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="M7" s="27" t="n">
-        <v>5000</v>
-      </c>
-      <c r="N7" s="27" t="n">
-        <v>5000</v>
-      </c>
-      <c r="O7" s="27" t="n">
-        <v>5000</v>
-      </c>
-      <c r="P7" s="36">
-        <f>SUM(H7:O7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="M8" s="30" t="n">
+        <v>5500</v>
+      </c>
+      <c r="N8" s="30" t="n">
+        <v>5500</v>
+      </c>
+      <c r="O8" s="30" t="n">
+        <v>5500</v>
+      </c>
+      <c r="P8" s="41">
+        <f>SUM(H8:O8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>JUR-D01</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>JUSFY</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Fase de teste com objetivo de eliminar o Astrea</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr"/>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr"/>
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H9" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I9" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="J8" s="27" t="n">
+      <c r="J9" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="K8" s="27" t="n">
+      <c r="K9" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="L8" s="27" t="n">
+      <c r="L9" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="M9" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="N8" s="27" t="n">
+      <c r="N9" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="O8" s="27" t="n">
+      <c r="O9" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="P8" s="36">
-        <f>SUM(H8:O8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="P9" s="41">
+        <f>SUM(H9:O9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>JUR-D02</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>JUSBRASIL</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr"/>
-      <c r="F9" s="25" t="inlineStr"/>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr"/>
+      <c r="F10" s="28" t="inlineStr"/>
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H10" s="30" t="n">
         <v>104.9</v>
       </c>
-      <c r="I9" s="27" t="n">
+      <c r="I10" s="30" t="n">
         <v>104.9</v>
       </c>
-      <c r="J9" s="27" t="n">
+      <c r="J10" s="30" t="n">
         <v>104.9</v>
       </c>
-      <c r="K9" s="27" t="n">
+      <c r="K10" s="30" t="n">
         <v>104.9</v>
       </c>
-      <c r="L9" s="27" t="n">
+      <c r="L10" s="30" t="n">
         <v>104.9</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M10" s="30" t="n">
         <v>104.9</v>
       </c>
-      <c r="N9" s="27" t="n">
+      <c r="N10" s="30" t="n">
         <v>104.9</v>
       </c>
-      <c r="O9" s="27" t="n">
+      <c r="O10" s="30" t="n">
         <v>104.9</v>
       </c>
-      <c r="P9" s="36">
-        <f>SUM(H9:O9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="P10" s="41">
+        <f>SUM(H10:O10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>JUR-D03</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>ASTREA</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Previsto sair quando o Jusfy for homologado — definir mês de corte</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr"/>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr"/>
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H11" s="30" t="n">
         <v>112.07</v>
       </c>
-      <c r="I10" s="27" t="n">
+      <c r="I11" s="30" t="n">
         <v>112.07</v>
       </c>
-      <c r="J10" s="27" t="n">
+      <c r="J11" s="30" t="n">
         <v>112.07</v>
       </c>
-      <c r="K10" s="27" t="n">
+      <c r="K11" s="30" t="n">
         <v>112.07</v>
       </c>
-      <c r="L10" s="27" t="n">
+      <c r="L11" s="30" t="n">
         <v>112.07</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M11" s="30" t="n">
         <v>112.07</v>
       </c>
-      <c r="N10" s="27" t="n">
+      <c r="N11" s="30" t="n">
         <v>112.07</v>
       </c>
-      <c r="O10" s="27" t="n">
+      <c r="O11" s="30" t="n">
         <v>112.07</v>
       </c>
-      <c r="P10" s="36">
-        <f>SUM(H10:O10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="P11" s="41">
+        <f>SUM(H11:O11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>JUR-D04</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>LEME</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr"/>
-      <c r="F11" s="25" t="inlineStr"/>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr"/>
+      <c r="F12" s="28" t="inlineStr"/>
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H12" s="30" t="n">
         <v>1030</v>
       </c>
-      <c r="I11" s="27" t="n">
+      <c r="I12" s="30" t="n">
         <v>1030</v>
       </c>
-      <c r="J11" s="27" t="n">
+      <c r="J12" s="30" t="n">
         <v>1030</v>
       </c>
-      <c r="K11" s="27" t="n">
+      <c r="K12" s="30" t="n">
         <v>1030</v>
       </c>
-      <c r="L11" s="27" t="n">
+      <c r="L12" s="30" t="n">
         <v>1030</v>
       </c>
-      <c r="M11" s="27" t="n">
+      <c r="M12" s="30" t="n">
         <v>1030</v>
       </c>
-      <c r="N11" s="27" t="n">
+      <c r="N12" s="30" t="n">
         <v>1030</v>
       </c>
-      <c r="O11" s="27" t="n">
+      <c r="O12" s="30" t="n">
         <v>1030</v>
       </c>
-      <c r="P11" s="36">
-        <f>SUM(H11:O11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="P12" s="41">
+        <f>SUM(H12:O12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>JUR-D05</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Cursos / Eventos / Network</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr"/>
-      <c r="F12" s="25" t="inlineStr"/>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr"/>
+      <c r="F13" s="28" t="inlineStr"/>
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="H12" s="27" t="n">
+      <c r="H13" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="I12" s="27" t="n">
+      <c r="I13" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="J12" s="27" t="n">
+      <c r="J13" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="K12" s="27" t="n">
+      <c r="K13" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="L12" s="27" t="n">
+      <c r="L13" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="M12" s="27" t="n">
+      <c r="M13" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="N12" s="27" t="n">
+      <c r="N13" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="O12" s="27" t="n">
+      <c r="O13" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="P12" s="36">
-        <f>SUM(H12:O12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="P13" s="41">
+        <f>SUM(H13:O13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>JUR-D06</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Bonificações trimestrais/semestrais do time</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Participação em projetos e atingimento de resultados</t>
         </is>
       </c>
-      <c r="F13" s="25" t="inlineStr"/>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr"/>
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H14" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="27" t="n">
+      <c r="I14" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="27" t="n">
+      <c r="J14" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="27" t="n">
+      <c r="K14" s="30" t="n">
         <v>10293.6</v>
       </c>
-      <c r="L13" s="27" t="n">
+      <c r="L14" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M14" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="27" t="n">
+      <c r="N14" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="27" t="n">
+      <c r="O14" s="30" t="n">
         <v>12867</v>
       </c>
-      <c r="P13" s="36">
-        <f>SUM(H13:O13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="P14" s="41">
+        <f>SUM(H14:O14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>TI-E01</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C14" s="30" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D14" s="31" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>Vinicius Di Franco</t>
         </is>
       </c>
-      <c r="E14" s="31" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>Analista Administrativo</t>
         </is>
       </c>
-      <c r="F14" s="30" t="inlineStr">
+      <c r="F15" s="34" t="inlineStr">
         <is>
           <t>CLT</t>
         </is>
       </c>
-      <c r="G14" s="30" t="inlineStr">
+      <c r="G15" s="34" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="H14" s="32" t="n">
+      <c r="H15" s="36" t="n">
         <v>5416.525</v>
       </c>
-      <c r="I14" s="32" t="n">
+      <c r="I15" s="36" t="n">
         <v>5416.525</v>
       </c>
-      <c r="J14" s="32" t="n">
+      <c r="J15" s="36" t="n">
         <v>5416.525</v>
       </c>
-      <c r="K14" s="32" t="n">
+      <c r="K15" s="36" t="n">
         <v>5416.525</v>
       </c>
-      <c r="L14" s="32" t="n">
+      <c r="L15" s="36" t="n">
         <v>5416.525</v>
       </c>
-      <c r="M14" s="32" t="n">
+      <c r="M15" s="36" t="n">
         <v>5416.525</v>
       </c>
-      <c r="N14" s="32" t="n">
+      <c r="N15" s="36" t="n">
         <v>5416.525</v>
       </c>
-      <c r="O14" s="32" t="n">
+      <c r="O15" s="36" t="n">
         <v>5416.525</v>
       </c>
-      <c r="P14" s="36">
-        <f>SUM(H14:O14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="P15" s="41">
+        <f>SUM(H15:O15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>TI-E02</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C15" s="30" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D15" s="31" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>Elias Benedito</t>
         </is>
       </c>
-      <c r="E15" s="31" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>Suporte Técnico Terceirizado</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F16" s="34" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G15" s="30" t="inlineStr">
+      <c r="G16" s="34" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H15" s="32" t="n">
+      <c r="H16" s="36" t="n">
         <v>1065</v>
       </c>
-      <c r="I15" s="32" t="n">
+      <c r="I16" s="36" t="n">
         <v>1065</v>
       </c>
-      <c r="J15" s="32" t="n">
+      <c r="J16" s="36" t="n">
         <v>1065</v>
       </c>
-      <c r="K15" s="32" t="n">
+      <c r="K16" s="36" t="n">
         <v>1065</v>
       </c>
-      <c r="L15" s="32" t="n">
+      <c r="L16" s="36" t="n">
         <v>1065</v>
       </c>
-      <c r="M15" s="32" t="n">
+      <c r="M16" s="36" t="n">
         <v>1065</v>
       </c>
-      <c r="N15" s="32" t="n">
+      <c r="N16" s="36" t="n">
         <v>1065</v>
       </c>
-      <c r="O15" s="32" t="n">
+      <c r="O16" s="36" t="n">
         <v>1065</v>
       </c>
-      <c r="P15" s="36">
-        <f>SUM(H15:O15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="P16" s="41">
+        <f>SUM(H16:O16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>TI-E03</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D16" s="31" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
         <is>
           <t>Jonathan</t>
         </is>
       </c>
-      <c r="E16" s="31" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>Consultor</t>
         </is>
       </c>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="F17" s="34" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G16" s="30" t="inlineStr">
+      <c r="G17" s="34" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H16" s="32" t="n">
+      <c r="H17" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="I16" s="32" t="n">
+      <c r="I17" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="J16" s="32" t="n">
+      <c r="J17" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="K16" s="32" t="n">
+      <c r="K17" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="L16" s="32" t="n">
+      <c r="L17" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="M16" s="32" t="n">
+      <c r="M17" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="N16" s="32" t="n">
+      <c r="N17" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="O16" s="32" t="n">
+      <c r="O17" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="P16" s="36">
-        <f>SUM(H16:O16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="P17" s="41">
+        <f>SUM(H17:O17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>TI-D01</t>
         </is>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C17" s="30" t="inlineStr">
+      <c r="C18" s="34" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D17" s="31" t="inlineStr">
+      <c r="D18" s="35" t="inlineStr">
         <is>
           <t>Peças de Manutenção</t>
         </is>
       </c>
-      <c r="E17" s="31" t="inlineStr">
+      <c r="E18" s="35" t="inlineStr">
         <is>
           <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr"/>
-      <c r="G17" s="30" t="inlineStr">
+      <c r="F18" s="34" t="inlineStr"/>
+      <c r="G18" s="34" t="inlineStr">
         <is>
           <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
-      <c r="H17" s="32" t="n">
+      <c r="H18" s="36" t="n">
         <v>810</v>
       </c>
-      <c r="I17" s="32" t="n">
+      <c r="I18" s="36" t="n">
         <v>810</v>
       </c>
-      <c r="J17" s="32" t="n">
+      <c r="J18" s="36" t="n">
         <v>810</v>
       </c>
-      <c r="K17" s="32" t="n">
+      <c r="K18" s="36" t="n">
         <v>810</v>
       </c>
-      <c r="L17" s="32" t="n">
+      <c r="L18" s="36" t="n">
         <v>810</v>
       </c>
-      <c r="M17" s="32" t="n">
+      <c r="M18" s="36" t="n">
         <v>810</v>
       </c>
-      <c r="N17" s="32" t="n">
+      <c r="N18" s="36" t="n">
         <v>810</v>
       </c>
-      <c r="O17" s="32" t="n">
+      <c r="O18" s="36" t="n">
         <v>810</v>
       </c>
-      <c r="P17" s="36">
-        <f>SUM(H17:O17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="P18" s="41">
+        <f>SUM(H18:O18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>TI-D02</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D18" s="31" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>Backup em Nuvem</t>
         </is>
       </c>
-      <c r="E18" s="31" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F18" s="30" t="inlineStr"/>
-      <c r="G18" s="30" t="inlineStr">
+      <c r="F19" s="34" t="inlineStr"/>
+      <c r="G19" s="34" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H18" s="32" t="n">
+      <c r="H19" s="36" t="n">
         <v>825</v>
       </c>
-      <c r="I18" s="32" t="n">
+      <c r="I19" s="36" t="n">
         <v>825</v>
       </c>
-      <c r="J18" s="32" t="n">
+      <c r="J19" s="36" t="n">
         <v>825</v>
       </c>
-      <c r="K18" s="32" t="n">
+      <c r="K19" s="36" t="n">
         <v>825</v>
       </c>
-      <c r="L18" s="32" t="n">
+      <c r="L19" s="36" t="n">
         <v>825</v>
       </c>
-      <c r="M18" s="32" t="n">
+      <c r="M19" s="36" t="n">
         <v>825</v>
       </c>
-      <c r="N18" s="32" t="n">
+      <c r="N19" s="36" t="n">
         <v>825</v>
       </c>
-      <c r="O18" s="32" t="n">
+      <c r="O19" s="36" t="n">
         <v>825</v>
       </c>
-      <c r="P18" s="36">
-        <f>SUM(H18:O18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="P19" s="41">
+        <f>SUM(H19:O19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>TI-D03</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C19" s="30" t="inlineStr">
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D19" s="31" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>Inteligência Artificial (Adapta)</t>
         </is>
       </c>
-      <c r="E19" s="31" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F19" s="30" t="inlineStr"/>
-      <c r="G19" s="30" t="inlineStr">
+      <c r="F20" s="34" t="inlineStr"/>
+      <c r="G20" s="34" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H19" s="32" t="n">
+      <c r="H20" s="36" t="n">
         <v>1300</v>
       </c>
-      <c r="I19" s="32" t="n">
+      <c r="I20" s="36" t="n">
         <v>1300</v>
       </c>
-      <c r="J19" s="32" t="n">
+      <c r="J20" s="36" t="n">
         <v>1600</v>
       </c>
-      <c r="K19" s="32" t="n">
+      <c r="K20" s="36" t="n">
         <v>1600</v>
       </c>
-      <c r="L19" s="32" t="n">
+      <c r="L20" s="36" t="n">
         <v>1600</v>
       </c>
-      <c r="M19" s="32" t="n">
+      <c r="M20" s="36" t="n">
         <v>1600</v>
       </c>
-      <c r="N19" s="32" t="n">
+      <c r="N20" s="36" t="n">
         <v>1600</v>
       </c>
-      <c r="O19" s="32" t="n">
+      <c r="O20" s="36" t="n">
         <v>1600</v>
       </c>
-      <c r="P19" s="36">
-        <f>SUM(H19:O19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="P20" s="41">
+        <f>SUM(H20:O20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>TI-D04</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C20" s="30" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D20" s="31" t="inlineStr">
+      <c r="D21" s="35" t="inlineStr">
         <is>
           <t>Antivírus</t>
         </is>
       </c>
-      <c r="E20" s="31" t="inlineStr">
+      <c r="E21" s="35" t="inlineStr">
         <is>
           <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F20" s="30" t="inlineStr"/>
-      <c r="G20" s="30" t="inlineStr">
+      <c r="F21" s="34" t="inlineStr"/>
+      <c r="G21" s="34" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H20" s="32" t="n">
+      <c r="H21" s="36" t="n">
         <v>240</v>
       </c>
-      <c r="I20" s="32" t="n">
+      <c r="I21" s="36" t="n">
         <v>240</v>
       </c>
-      <c r="J20" s="32" t="n">
+      <c r="J21" s="36" t="n">
         <v>240</v>
       </c>
-      <c r="K20" s="32" t="n">
+      <c r="K21" s="36" t="n">
         <v>240</v>
       </c>
-      <c r="L20" s="32" t="n">
+      <c r="L21" s="36" t="n">
         <v>240</v>
       </c>
-      <c r="M20" s="32" t="n">
+      <c r="M21" s="36" t="n">
         <v>240</v>
       </c>
-      <c r="N20" s="32" t="n">
+      <c r="N21" s="36" t="n">
         <v>240</v>
       </c>
-      <c r="O20" s="32" t="n">
+      <c r="O21" s="36" t="n">
         <v>240</v>
       </c>
-      <c r="P20" s="36">
-        <f>SUM(H20:O20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="P21" s="41">
+        <f>SUM(H21:O21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>TI-D05</t>
         </is>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C21" s="30" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D21" s="31" t="inlineStr">
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>Pacote Office 365</t>
         </is>
       </c>
-      <c r="E21" s="31" t="inlineStr">
+      <c r="E22" s="35" t="inlineStr">
         <is>
           <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F21" s="30" t="inlineStr"/>
-      <c r="G21" s="30" t="inlineStr">
+      <c r="F22" s="34" t="inlineStr"/>
+      <c r="G22" s="34" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H21" s="32" t="n">
+      <c r="H22" s="36" t="n">
         <v>375</v>
       </c>
-      <c r="I21" s="32" t="n">
+      <c r="I22" s="36" t="n">
         <v>375</v>
       </c>
-      <c r="J21" s="32" t="n">
+      <c r="J22" s="36" t="n">
         <v>375</v>
       </c>
-      <c r="K21" s="32" t="n">
+      <c r="K22" s="36" t="n">
         <v>375</v>
       </c>
-      <c r="L21" s="32" t="n">
+      <c r="L22" s="36" t="n">
         <v>375</v>
       </c>
-      <c r="M21" s="32" t="n">
+      <c r="M22" s="36" t="n">
         <v>375</v>
       </c>
-      <c r="N21" s="32" t="n">
+      <c r="N22" s="36" t="n">
         <v>375</v>
       </c>
-      <c r="O21" s="32" t="n">
+      <c r="O22" s="36" t="n">
         <v>375</v>
       </c>
-      <c r="P21" s="36">
-        <f>SUM(H21:O21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="P22" s="41">
+        <f>SUM(H22:O22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>TI-D06</t>
         </is>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C22" s="30" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D22" s="31" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
         </is>
       </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="E23" s="35" t="inlineStr">
         <is>
           <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
         </is>
       </c>
-      <c r="F22" s="30" t="inlineStr"/>
-      <c r="G22" s="30" t="inlineStr">
+      <c r="F23" s="34" t="inlineStr"/>
+      <c r="G23" s="34" t="inlineStr">
         <is>
           <t>Móveis e Utensílios</t>
         </is>
       </c>
-      <c r="H22" s="32" t="n">
+      <c r="H23" s="36" t="n">
         <v>2800</v>
       </c>
-      <c r="I22" s="32" t="n">
+      <c r="I23" s="36" t="n">
         <v>2800</v>
       </c>
-      <c r="J22" s="32" t="n">
+      <c r="J23" s="36" t="n">
         <v>2800</v>
       </c>
-      <c r="K22" s="32" t="n">
+      <c r="K23" s="36" t="n">
         <v>2800</v>
       </c>
-      <c r="L22" s="32" t="n">
+      <c r="L23" s="36" t="n">
         <v>2800</v>
       </c>
-      <c r="M22" s="32" t="n">
+      <c r="M23" s="36" t="n">
         <v>2800</v>
       </c>
-      <c r="N22" s="32" t="n">
+      <c r="N23" s="36" t="n">
         <v>2800</v>
       </c>
-      <c r="O22" s="32" t="n">
+      <c r="O23" s="36" t="n">
         <v>2800</v>
       </c>
-      <c r="P22" s="36">
-        <f>SUM(H22:O22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="P23" s="41">
+        <f>SUM(H23:O23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>TI-D07</t>
         </is>
       </c>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C23" s="30" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D23" s="31" t="inlineStr">
+      <c r="D24" s="35" t="inlineStr">
         <is>
           <t>Cursos e Treinamentos</t>
         </is>
       </c>
-      <c r="E23" s="31" t="inlineStr"/>
-      <c r="F23" s="30" t="inlineStr"/>
-      <c r="G23" s="30" t="inlineStr">
+      <c r="E24" s="35" t="inlineStr"/>
+      <c r="F24" s="34" t="inlineStr"/>
+      <c r="G24" s="34" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="H23" s="32" t="n">
+      <c r="H24" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="I23" s="32" t="n">
+      <c r="I24" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="J23" s="32" t="n">
+      <c r="J24" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="K23" s="32" t="n">
+      <c r="K24" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="L23" s="32" t="n">
+      <c r="L24" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="M23" s="32" t="n">
+      <c r="M24" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="N23" s="32" t="n">
+      <c r="N24" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="O23" s="32" t="n">
+      <c r="O24" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="P23" s="36">
-        <f>SUM(H23:O23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="P24" s="41">
+        <f>SUM(H24:O24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>TI-D08</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B25" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C24" s="30" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D24" s="31" t="inlineStr">
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>Aplicativo de Gravação de Reunião</t>
         </is>
       </c>
-      <c r="E24" s="31" t="inlineStr"/>
-      <c r="F24" s="30" t="inlineStr"/>
-      <c r="G24" s="30" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr"/>
+      <c r="F25" s="34" t="inlineStr"/>
+      <c r="G25" s="34" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H24" s="32" t="n">
+      <c r="H25" s="36" t="n">
         <v>220</v>
       </c>
-      <c r="I24" s="32" t="n">
+      <c r="I25" s="36" t="n">
         <v>220</v>
       </c>
-      <c r="J24" s="32" t="n">
+      <c r="J25" s="36" t="n">
         <v>220</v>
       </c>
-      <c r="K24" s="32" t="n">
+      <c r="K25" s="36" t="n">
         <v>220</v>
       </c>
-      <c r="L24" s="32" t="n">
+      <c r="L25" s="36" t="n">
         <v>220</v>
       </c>
-      <c r="M24" s="32" t="n">
+      <c r="M25" s="36" t="n">
         <v>220</v>
       </c>
-      <c r="N24" s="32" t="n">
+      <c r="N25" s="36" t="n">
         <v>220</v>
       </c>
-      <c r="O24" s="32" t="n">
+      <c r="O25" s="36" t="n">
         <v>220</v>
       </c>
-      <c r="P24" s="36">
-        <f>SUM(H24:O24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="P25" s="41">
+        <f>SUM(H25:O25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>TI-D09</t>
         </is>
       </c>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B26" s="34" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C25" s="30" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D25" s="31" t="inlineStr">
+      <c r="D26" s="35" t="inlineStr">
         <is>
           <t>Bonificação do time</t>
         </is>
       </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="E26" s="35" t="inlineStr">
         <is>
           <t>Cumprimento de prazos e participação em projetos</t>
         </is>
       </c>
-      <c r="F25" s="30" t="inlineStr"/>
-      <c r="G25" s="30" t="inlineStr">
+      <c r="F26" s="34" t="inlineStr"/>
+      <c r="G26" s="34" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="H25" s="32" t="n">
+      <c r="H26" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="32" t="n">
+      <c r="I26" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="32" t="n">
+      <c r="J26" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="32" t="n">
+      <c r="K26" s="36" t="n">
         <v>2400</v>
       </c>
-      <c r="L25" s="32" t="n">
+      <c r="L26" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="32" t="n">
+      <c r="M26" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="32" t="n">
+      <c r="N26" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="32" t="n">
+      <c r="O26" s="36" t="n">
         <v>3600</v>
       </c>
-      <c r="P25" s="36">
-        <f>SUM(H25:O25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="P26" s="41">
+        <f>SUM(H26:O26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="14">
-        <f>SUM(H5:H25)</f>
-        <v/>
-      </c>
-      <c r="I26" s="14">
-        <f>SUM(I5:I25)</f>
-        <v/>
-      </c>
-      <c r="J26" s="14">
-        <f>SUM(J5:J25)</f>
-        <v/>
-      </c>
-      <c r="K26" s="14">
-        <f>SUM(K5:K25)</f>
-        <v/>
-      </c>
-      <c r="L26" s="14">
-        <f>SUM(L5:L25)</f>
-        <v/>
-      </c>
-      <c r="M26" s="14">
-        <f>SUM(M5:M25)</f>
-        <v/>
-      </c>
-      <c r="N26" s="14">
-        <f>SUM(N5:N25)</f>
-        <v/>
-      </c>
-      <c r="O26" s="14">
-        <f>SUM(O5:O25)</f>
-        <v/>
-      </c>
-      <c r="P26" s="14">
-        <f>SUM(P5:P25)</f>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="16">
+        <f>SUM(H5:H26)</f>
+        <v/>
+      </c>
+      <c r="I27" s="16">
+        <f>SUM(I5:I26)</f>
+        <v/>
+      </c>
+      <c r="J27" s="16">
+        <f>SUM(J5:J26)</f>
+        <v/>
+      </c>
+      <c r="K27" s="16">
+        <f>SUM(K5:K26)</f>
+        <v/>
+      </c>
+      <c r="L27" s="16">
+        <f>SUM(L5:L26)</f>
+        <v/>
+      </c>
+      <c r="M27" s="16">
+        <f>SUM(M5:M26)</f>
+        <v/>
+      </c>
+      <c r="N27" s="16">
+        <f>SUM(N5:N26)</f>
+        <v/>
+      </c>
+      <c r="O27" s="16">
+        <f>SUM(O5:O26)</f>
+        <v/>
+      </c>
+      <c r="P27" s="16">
+        <f>SUM(P5:P26)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P25"/>
+  <autoFilter ref="A4:P26"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
@@ -4517,7 +4794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4555,1071 +4832,1231 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>Detalhe / Observação</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>Vínculo</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="42" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="42" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="J4" s="37" t="inlineStr">
+      <c r="J4" s="42" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="K4" s="37" t="inlineStr">
+      <c r="K4" s="42" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="L4" s="37" t="inlineStr">
+      <c r="L4" s="42" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="M4" s="37" t="inlineStr">
+      <c r="M4" s="42" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="N4" s="37" t="inlineStr">
+      <c r="N4" s="42" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="O4" s="37" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="P4" s="37" t="inlineStr">
+      <c r="P4" s="42" t="inlineStr">
         <is>
           <t>TOTAL REALIZADO</t>
         </is>
       </c>
-      <c r="Q4" s="37" t="inlineStr">
+      <c r="Q4" s="42" t="inlineStr">
         <is>
           <t>Fonte do dado</t>
         </is>
       </c>
-      <c r="R4" s="37" t="inlineStr">
+      <c r="R4" s="42" t="inlineStr">
         <is>
           <t>Observações do mês</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="38">
+      <c r="A5" s="43">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="43">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="43">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="44">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="44">
         <f>Planejado!E5</f>
         <v/>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="43">
         <f>Planejado!F5</f>
         <v/>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="43">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="H5" s="40" t="n"/>
-      <c r="I5" s="40" t="n"/>
-      <c r="J5" s="40" t="n"/>
-      <c r="K5" s="40" t="n"/>
-      <c r="L5" s="40" t="n"/>
-      <c r="M5" s="40" t="n"/>
-      <c r="N5" s="40" t="n"/>
-      <c r="O5" s="40" t="n"/>
-      <c r="P5" s="36">
+      <c r="H5" s="45" t="n">
+        <v>8818</v>
+      </c>
+      <c r="I5" s="45" t="n">
+        <v>8818</v>
+      </c>
+      <c r="J5" s="45" t="n">
+        <v>8818</v>
+      </c>
+      <c r="K5" s="45" t="n"/>
+      <c r="L5" s="45" t="n"/>
+      <c r="M5" s="45" t="n"/>
+      <c r="N5" s="45" t="n"/>
+      <c r="O5" s="45" t="n"/>
+      <c r="P5" s="41">
         <f>SUM(H5:O5)</f>
         <v/>
       </c>
-      <c r="Q5" s="41" t="n"/>
-      <c r="R5" s="41" t="n"/>
+      <c r="Q5" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="R5" s="46" t="inlineStr">
+        <is>
+          <t>Valor cheio da nota — R$ 1.182/mês abaixo do contratado</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="38">
+      <c r="A6" s="43">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="43">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="43">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="44">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="44">
         <f>Planejado!E6</f>
         <v/>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="43">
         <f>Planejado!F6</f>
         <v/>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="43">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="H6" s="40" t="n"/>
-      <c r="I6" s="40" t="n"/>
-      <c r="J6" s="40" t="n"/>
-      <c r="K6" s="40" t="n"/>
-      <c r="L6" s="40" t="n"/>
-      <c r="M6" s="40" t="n"/>
-      <c r="N6" s="40" t="n"/>
-      <c r="O6" s="40" t="n"/>
-      <c r="P6" s="36">
+      <c r="H6" s="45" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="I6" s="45" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="J6" s="45" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="K6" s="45" t="n"/>
+      <c r="L6" s="45" t="n"/>
+      <c r="M6" s="45" t="n"/>
+      <c r="N6" s="45" t="n"/>
+      <c r="O6" s="45" t="n"/>
+      <c r="P6" s="41">
         <f>SUM(H6:O6)</f>
         <v/>
       </c>
-      <c r="Q6" s="41" t="n"/>
-      <c r="R6" s="41" t="n"/>
+      <c r="Q6" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="R6" s="46" t="inlineStr">
+        <is>
+          <t>Salário bruto</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="38">
+      <c r="A7" s="43">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="43">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="43">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="44">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="44">
         <f>Planejado!E7</f>
         <v/>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="43">
         <f>Planejado!F7</f>
         <v/>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="43">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="H7" s="40" t="n"/>
-      <c r="I7" s="40" t="n"/>
-      <c r="J7" s="40" t="n"/>
-      <c r="K7" s="40" t="n"/>
-      <c r="L7" s="40" t="n"/>
-      <c r="M7" s="40" t="n"/>
-      <c r="N7" s="40" t="n"/>
-      <c r="O7" s="40" t="n"/>
-      <c r="P7" s="36">
+      <c r="H7" s="45" t="n"/>
+      <c r="I7" s="45" t="n"/>
+      <c r="J7" s="45" t="n"/>
+      <c r="K7" s="45" t="n"/>
+      <c r="L7" s="45" t="n"/>
+      <c r="M7" s="45" t="n"/>
+      <c r="N7" s="45" t="n"/>
+      <c r="O7" s="45" t="n"/>
+      <c r="P7" s="41">
         <f>SUM(H7:O7)</f>
         <v/>
       </c>
-      <c r="Q7" s="41" t="n"/>
-      <c r="R7" s="41" t="n"/>
+      <c r="Q7" s="46" t="n"/>
+      <c r="R7" s="46" t="inlineStr">
+        <is>
+          <t>PREENCHER — encargos e benefícios sobre o bruto</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="38">
+      <c r="A8" s="43">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="43">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="43">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="44">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="44">
         <f>Planejado!E8</f>
         <v/>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="43">
         <f>Planejado!F8</f>
         <v/>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="43">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="H8" s="40" t="n"/>
-      <c r="I8" s="40" t="n"/>
-      <c r="J8" s="40" t="n"/>
-      <c r="K8" s="40" t="n"/>
-      <c r="L8" s="40" t="n"/>
-      <c r="M8" s="40" t="n"/>
-      <c r="N8" s="40" t="n"/>
-      <c r="O8" s="40" t="n"/>
-      <c r="P8" s="36">
+      <c r="H8" s="45" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I8" s="45" t="n">
+        <v>5500</v>
+      </c>
+      <c r="J8" s="45" t="n">
+        <v>5500</v>
+      </c>
+      <c r="K8" s="45" t="n"/>
+      <c r="L8" s="45" t="n"/>
+      <c r="M8" s="45" t="n"/>
+      <c r="N8" s="45" t="n"/>
+      <c r="O8" s="45" t="n"/>
+      <c r="P8" s="41">
         <f>SUM(H8:O8)</f>
         <v/>
       </c>
-      <c r="Q8" s="41" t="n"/>
-      <c r="R8" s="41" t="n"/>
+      <c r="Q8" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="R8" s="46" t="inlineStr">
+        <is>
+          <t>Reajuste permanente aplicado desde mai/26</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="38">
+      <c r="A9" s="43">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="43">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="43">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="44">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="44">
         <f>Planejado!E9</f>
         <v/>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="43">
         <f>Planejado!F9</f>
         <v/>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="43">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="H9" s="40" t="n"/>
-      <c r="I9" s="40" t="n"/>
-      <c r="J9" s="40" t="n"/>
-      <c r="K9" s="40" t="n"/>
-      <c r="L9" s="40" t="n"/>
-      <c r="M9" s="40" t="n"/>
-      <c r="N9" s="40" t="n"/>
-      <c r="O9" s="40" t="n"/>
-      <c r="P9" s="36">
+      <c r="H9" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="45" t="n"/>
+      <c r="L9" s="45" t="n"/>
+      <c r="M9" s="45" t="n"/>
+      <c r="N9" s="45" t="n"/>
+      <c r="O9" s="45" t="n"/>
+      <c r="P9" s="41">
         <f>SUM(H9:O9)</f>
         <v/>
       </c>
-      <c r="Q9" s="41" t="n"/>
-      <c r="R9" s="41" t="n"/>
+      <c r="Q9" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="R9" s="46" t="inlineStr">
+        <is>
+          <t>Ainda não iniciado — sem cobrança</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="38">
+      <c r="A10" s="43">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="43">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="43">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="44">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E10" s="39">
+      <c r="E10" s="44">
         <f>Planejado!E10</f>
         <v/>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="43">
         <f>Planejado!F10</f>
         <v/>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="43">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="H10" s="40" t="n"/>
-      <c r="I10" s="40" t="n"/>
-      <c r="J10" s="40" t="n"/>
-      <c r="K10" s="40" t="n"/>
-      <c r="L10" s="40" t="n"/>
-      <c r="M10" s="40" t="n"/>
-      <c r="N10" s="40" t="n"/>
-      <c r="O10" s="40" t="n"/>
-      <c r="P10" s="36">
+      <c r="H10" s="45" t="n">
+        <v>136</v>
+      </c>
+      <c r="I10" s="45" t="n">
+        <v>136</v>
+      </c>
+      <c r="J10" s="45" t="n">
+        <v>136</v>
+      </c>
+      <c r="K10" s="45" t="n"/>
+      <c r="L10" s="45" t="n"/>
+      <c r="M10" s="45" t="n"/>
+      <c r="N10" s="45" t="n"/>
+      <c r="O10" s="45" t="n"/>
+      <c r="P10" s="41">
         <f>SUM(H10:O10)</f>
         <v/>
       </c>
-      <c r="Q10" s="41" t="n"/>
-      <c r="R10" s="41" t="n"/>
+      <c r="Q10" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="R10" s="46" t="inlineStr">
+        <is>
+          <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="38">
+      <c r="A11" s="43">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="43">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="43">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="44">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="44">
         <f>Planejado!E11</f>
         <v/>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="43">
         <f>Planejado!F11</f>
         <v/>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="43">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="H11" s="40" t="n"/>
-      <c r="I11" s="40" t="n"/>
-      <c r="J11" s="40" t="n"/>
-      <c r="K11" s="40" t="n"/>
-      <c r="L11" s="40" t="n"/>
-      <c r="M11" s="40" t="n"/>
-      <c r="N11" s="40" t="n"/>
-      <c r="O11" s="40" t="n"/>
-      <c r="P11" s="36">
+      <c r="H11" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="45" t="n"/>
+      <c r="L11" s="45" t="n"/>
+      <c r="M11" s="45" t="n"/>
+      <c r="N11" s="45" t="n"/>
+      <c r="O11" s="45" t="n"/>
+      <c r="P11" s="41">
         <f>SUM(H11:O11)</f>
         <v/>
       </c>
-      <c r="Q11" s="41" t="n"/>
-      <c r="R11" s="41" t="n"/>
+      <c r="Q11" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="R11" s="46" t="inlineStr">
+        <is>
+          <t>Cancelado — sem cobrança</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="38">
+      <c r="A12" s="43">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="43">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="43">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="44">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="44">
         <f>Planejado!E12</f>
         <v/>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="43">
         <f>Planejado!F12</f>
         <v/>
       </c>
-      <c r="G12" s="38">
+      <c r="G12" s="43">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="H12" s="40" t="n"/>
-      <c r="I12" s="40" t="n"/>
-      <c r="J12" s="40" t="n"/>
-      <c r="K12" s="40" t="n"/>
-      <c r="L12" s="40" t="n"/>
-      <c r="M12" s="40" t="n"/>
-      <c r="N12" s="40" t="n"/>
-      <c r="O12" s="40" t="n"/>
-      <c r="P12" s="36">
+      <c r="H12" s="45" t="n">
+        <v>970</v>
+      </c>
+      <c r="I12" s="45" t="n">
+        <v>970</v>
+      </c>
+      <c r="J12" s="45" t="n">
+        <v>970</v>
+      </c>
+      <c r="K12" s="45" t="n"/>
+      <c r="L12" s="45" t="n"/>
+      <c r="M12" s="45" t="n"/>
+      <c r="N12" s="45" t="n"/>
+      <c r="O12" s="45" t="n"/>
+      <c r="P12" s="41">
         <f>SUM(H12:O12)</f>
         <v/>
       </c>
-      <c r="Q12" s="41" t="n"/>
-      <c r="R12" s="41" t="n"/>
+      <c r="Q12" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="R12" s="46" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="38">
+      <c r="A13" s="43">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="43">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="43">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="44">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="44">
         <f>Planejado!E13</f>
         <v/>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="43">
         <f>Planejado!F13</f>
         <v/>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="43">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="H13" s="40" t="n"/>
-      <c r="I13" s="40" t="n"/>
-      <c r="J13" s="40" t="n"/>
-      <c r="K13" s="40" t="n"/>
-      <c r="L13" s="40" t="n"/>
-      <c r="M13" s="40" t="n"/>
-      <c r="N13" s="40" t="n"/>
-      <c r="O13" s="40" t="n"/>
-      <c r="P13" s="36">
+      <c r="H13" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="45" t="n"/>
+      <c r="L13" s="45" t="n"/>
+      <c r="M13" s="45" t="n"/>
+      <c r="N13" s="45" t="n"/>
+      <c r="O13" s="45" t="n"/>
+      <c r="P13" s="41">
         <f>SUM(H13:O13)</f>
         <v/>
       </c>
-      <c r="Q13" s="41" t="n"/>
-      <c r="R13" s="41" t="n"/>
+      <c r="Q13" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="R13" s="46" t="inlineStr">
+        <is>
+          <t>Sem gasto no período</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="38">
+      <c r="A14" s="43">
         <f>Planejado!A14</f>
         <v/>
       </c>
-      <c r="B14" s="38">
+      <c r="B14" s="43">
         <f>Planejado!B14</f>
         <v/>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="43">
         <f>Planejado!C14</f>
         <v/>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="44">
         <f>Planejado!D14</f>
         <v/>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="44">
         <f>Planejado!E14</f>
         <v/>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="43">
         <f>Planejado!F14</f>
         <v/>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="43">
         <f>Planejado!G14</f>
         <v/>
       </c>
-      <c r="H14" s="40" t="n"/>
-      <c r="I14" s="40" t="n"/>
-      <c r="J14" s="40" t="n"/>
-      <c r="K14" s="40" t="n"/>
-      <c r="L14" s="40" t="n"/>
-      <c r="M14" s="40" t="n"/>
-      <c r="N14" s="40" t="n"/>
-      <c r="O14" s="40" t="n"/>
-      <c r="P14" s="36">
+      <c r="H14" s="45" t="n"/>
+      <c r="I14" s="45" t="n"/>
+      <c r="J14" s="45" t="n"/>
+      <c r="K14" s="45" t="n"/>
+      <c r="L14" s="45" t="n"/>
+      <c r="M14" s="45" t="n"/>
+      <c r="N14" s="45" t="n"/>
+      <c r="O14" s="45" t="n"/>
+      <c r="P14" s="41">
         <f>SUM(H14:O14)</f>
         <v/>
       </c>
-      <c r="Q14" s="41" t="n"/>
-      <c r="R14" s="41" t="n"/>
+      <c r="Q14" s="46" t="n"/>
+      <c r="R14" s="46" t="inlineStr">
+        <is>
+          <t>Bonificação de ago/26 a confirmar</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="38">
+      <c r="A15" s="43">
         <f>Planejado!A15</f>
         <v/>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="43">
         <f>Planejado!B15</f>
         <v/>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="43">
         <f>Planejado!C15</f>
         <v/>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="44">
         <f>Planejado!D15</f>
         <v/>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="44">
         <f>Planejado!E15</f>
         <v/>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="43">
         <f>Planejado!F15</f>
         <v/>
       </c>
-      <c r="G15" s="38">
+      <c r="G15" s="43">
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="H15" s="40" t="n"/>
-      <c r="I15" s="40" t="n"/>
-      <c r="J15" s="40" t="n"/>
-      <c r="K15" s="40" t="n"/>
-      <c r="L15" s="40" t="n"/>
-      <c r="M15" s="40" t="n"/>
-      <c r="N15" s="40" t="n"/>
-      <c r="O15" s="40" t="n"/>
-      <c r="P15" s="36">
+      <c r="H15" s="45" t="n"/>
+      <c r="I15" s="45" t="n"/>
+      <c r="J15" s="45" t="n"/>
+      <c r="K15" s="45" t="n"/>
+      <c r="L15" s="45" t="n"/>
+      <c r="M15" s="45" t="n"/>
+      <c r="N15" s="45" t="n"/>
+      <c r="O15" s="45" t="n"/>
+      <c r="P15" s="41">
         <f>SUM(H15:O15)</f>
         <v/>
       </c>
-      <c r="Q15" s="41" t="n"/>
-      <c r="R15" s="41" t="n"/>
+      <c r="Q15" s="46" t="n"/>
+      <c r="R15" s="46" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="38">
+      <c r="A16" s="43">
         <f>Planejado!A16</f>
         <v/>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="43">
         <f>Planejado!B16</f>
         <v/>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="43">
         <f>Planejado!C16</f>
         <v/>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="44">
         <f>Planejado!D16</f>
         <v/>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="44">
         <f>Planejado!E16</f>
         <v/>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="43">
         <f>Planejado!F16</f>
         <v/>
       </c>
-      <c r="G16" s="38">
+      <c r="G16" s="43">
         <f>Planejado!G16</f>
         <v/>
       </c>
-      <c r="H16" s="40" t="n"/>
-      <c r="I16" s="40" t="n"/>
-      <c r="J16" s="40" t="n"/>
-      <c r="K16" s="40" t="n"/>
-      <c r="L16" s="40" t="n"/>
-      <c r="M16" s="40" t="n"/>
-      <c r="N16" s="40" t="n"/>
-      <c r="O16" s="40" t="n"/>
-      <c r="P16" s="36">
+      <c r="H16" s="45" t="n"/>
+      <c r="I16" s="45" t="n"/>
+      <c r="J16" s="45" t="n"/>
+      <c r="K16" s="45" t="n"/>
+      <c r="L16" s="45" t="n"/>
+      <c r="M16" s="45" t="n"/>
+      <c r="N16" s="45" t="n"/>
+      <c r="O16" s="45" t="n"/>
+      <c r="P16" s="41">
         <f>SUM(H16:O16)</f>
         <v/>
       </c>
-      <c r="Q16" s="41" t="n"/>
-      <c r="R16" s="41" t="n"/>
+      <c r="Q16" s="46" t="n"/>
+      <c r="R16" s="46" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="38">
+      <c r="A17" s="43">
         <f>Planejado!A17</f>
         <v/>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="43">
         <f>Planejado!B17</f>
         <v/>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="43">
         <f>Planejado!C17</f>
         <v/>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="44">
         <f>Planejado!D17</f>
         <v/>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="44">
         <f>Planejado!E17</f>
         <v/>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="43">
         <f>Planejado!F17</f>
         <v/>
       </c>
-      <c r="G17" s="38">
+      <c r="G17" s="43">
         <f>Planejado!G17</f>
         <v/>
       </c>
-      <c r="H17" s="40" t="n"/>
-      <c r="I17" s="40" t="n"/>
-      <c r="J17" s="40" t="n"/>
-      <c r="K17" s="40" t="n"/>
-      <c r="L17" s="40" t="n"/>
-      <c r="M17" s="40" t="n"/>
-      <c r="N17" s="40" t="n"/>
-      <c r="O17" s="40" t="n"/>
-      <c r="P17" s="36">
+      <c r="H17" s="45" t="n"/>
+      <c r="I17" s="45" t="n"/>
+      <c r="J17" s="45" t="n"/>
+      <c r="K17" s="45" t="n"/>
+      <c r="L17" s="45" t="n"/>
+      <c r="M17" s="45" t="n"/>
+      <c r="N17" s="45" t="n"/>
+      <c r="O17" s="45" t="n"/>
+      <c r="P17" s="41">
         <f>SUM(H17:O17)</f>
         <v/>
       </c>
-      <c r="Q17" s="41" t="n"/>
-      <c r="R17" s="41" t="n"/>
+      <c r="Q17" s="46" t="n"/>
+      <c r="R17" s="46" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="38">
+      <c r="A18" s="43">
         <f>Planejado!A18</f>
         <v/>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="43">
         <f>Planejado!B18</f>
         <v/>
       </c>
-      <c r="C18" s="38">
+      <c r="C18" s="43">
         <f>Planejado!C18</f>
         <v/>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="44">
         <f>Planejado!D18</f>
         <v/>
       </c>
-      <c r="E18" s="39">
+      <c r="E18" s="44">
         <f>Planejado!E18</f>
         <v/>
       </c>
-      <c r="F18" s="38">
+      <c r="F18" s="43">
         <f>Planejado!F18</f>
         <v/>
       </c>
-      <c r="G18" s="38">
+      <c r="G18" s="43">
         <f>Planejado!G18</f>
         <v/>
       </c>
-      <c r="H18" s="40" t="n"/>
-      <c r="I18" s="40" t="n"/>
-      <c r="J18" s="40" t="n"/>
-      <c r="K18" s="40" t="n"/>
-      <c r="L18" s="40" t="n"/>
-      <c r="M18" s="40" t="n"/>
-      <c r="N18" s="40" t="n"/>
-      <c r="O18" s="40" t="n"/>
-      <c r="P18" s="36">
+      <c r="H18" s="45" t="n"/>
+      <c r="I18" s="45" t="n"/>
+      <c r="J18" s="45" t="n"/>
+      <c r="K18" s="45" t="n"/>
+      <c r="L18" s="45" t="n"/>
+      <c r="M18" s="45" t="n"/>
+      <c r="N18" s="45" t="n"/>
+      <c r="O18" s="45" t="n"/>
+      <c r="P18" s="41">
         <f>SUM(H18:O18)</f>
         <v/>
       </c>
-      <c r="Q18" s="41" t="n"/>
-      <c r="R18" s="41" t="n"/>
+      <c r="Q18" s="46" t="n"/>
+      <c r="R18" s="46" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="38">
+      <c r="A19" s="43">
         <f>Planejado!A19</f>
         <v/>
       </c>
-      <c r="B19" s="38">
+      <c r="B19" s="43">
         <f>Planejado!B19</f>
         <v/>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="43">
         <f>Planejado!C19</f>
         <v/>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="44">
         <f>Planejado!D19</f>
         <v/>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="44">
         <f>Planejado!E19</f>
         <v/>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="43">
         <f>Planejado!F19</f>
         <v/>
       </c>
-      <c r="G19" s="38">
+      <c r="G19" s="43">
         <f>Planejado!G19</f>
         <v/>
       </c>
-      <c r="H19" s="40" t="n"/>
-      <c r="I19" s="40" t="n"/>
-      <c r="J19" s="40" t="n"/>
-      <c r="K19" s="40" t="n"/>
-      <c r="L19" s="40" t="n"/>
-      <c r="M19" s="40" t="n"/>
-      <c r="N19" s="40" t="n"/>
-      <c r="O19" s="40" t="n"/>
-      <c r="P19" s="36">
+      <c r="H19" s="45" t="n"/>
+      <c r="I19" s="45" t="n"/>
+      <c r="J19" s="45" t="n"/>
+      <c r="K19" s="45" t="n"/>
+      <c r="L19" s="45" t="n"/>
+      <c r="M19" s="45" t="n"/>
+      <c r="N19" s="45" t="n"/>
+      <c r="O19" s="45" t="n"/>
+      <c r="P19" s="41">
         <f>SUM(H19:O19)</f>
         <v/>
       </c>
-      <c r="Q19" s="41" t="n"/>
-      <c r="R19" s="41" t="n"/>
+      <c r="Q19" s="46" t="n"/>
+      <c r="R19" s="46" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="38">
+      <c r="A20" s="43">
         <f>Planejado!A20</f>
         <v/>
       </c>
-      <c r="B20" s="38">
+      <c r="B20" s="43">
         <f>Planejado!B20</f>
         <v/>
       </c>
-      <c r="C20" s="38">
+      <c r="C20" s="43">
         <f>Planejado!C20</f>
         <v/>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="44">
         <f>Planejado!D20</f>
         <v/>
       </c>
-      <c r="E20" s="39">
+      <c r="E20" s="44">
         <f>Planejado!E20</f>
         <v/>
       </c>
-      <c r="F20" s="38">
+      <c r="F20" s="43">
         <f>Planejado!F20</f>
         <v/>
       </c>
-      <c r="G20" s="38">
+      <c r="G20" s="43">
         <f>Planejado!G20</f>
         <v/>
       </c>
-      <c r="H20" s="40" t="n"/>
-      <c r="I20" s="40" t="n"/>
-      <c r="J20" s="40" t="n"/>
-      <c r="K20" s="40" t="n"/>
-      <c r="L20" s="40" t="n"/>
-      <c r="M20" s="40" t="n"/>
-      <c r="N20" s="40" t="n"/>
-      <c r="O20" s="40" t="n"/>
-      <c r="P20" s="36">
+      <c r="H20" s="45" t="n"/>
+      <c r="I20" s="45" t="n"/>
+      <c r="J20" s="45" t="n"/>
+      <c r="K20" s="45" t="n"/>
+      <c r="L20" s="45" t="n"/>
+      <c r="M20" s="45" t="n"/>
+      <c r="N20" s="45" t="n"/>
+      <c r="O20" s="45" t="n"/>
+      <c r="P20" s="41">
         <f>SUM(H20:O20)</f>
         <v/>
       </c>
-      <c r="Q20" s="41" t="n"/>
-      <c r="R20" s="41" t="n"/>
+      <c r="Q20" s="46" t="n"/>
+      <c r="R20" s="46" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="38">
+      <c r="A21" s="43">
         <f>Planejado!A21</f>
         <v/>
       </c>
-      <c r="B21" s="38">
+      <c r="B21" s="43">
         <f>Planejado!B21</f>
         <v/>
       </c>
-      <c r="C21" s="38">
+      <c r="C21" s="43">
         <f>Planejado!C21</f>
         <v/>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="44">
         <f>Planejado!D21</f>
         <v/>
       </c>
-      <c r="E21" s="39">
+      <c r="E21" s="44">
         <f>Planejado!E21</f>
         <v/>
       </c>
-      <c r="F21" s="38">
+      <c r="F21" s="43">
         <f>Planejado!F21</f>
         <v/>
       </c>
-      <c r="G21" s="38">
+      <c r="G21" s="43">
         <f>Planejado!G21</f>
         <v/>
       </c>
-      <c r="H21" s="40" t="n"/>
-      <c r="I21" s="40" t="n"/>
-      <c r="J21" s="40" t="n"/>
-      <c r="K21" s="40" t="n"/>
-      <c r="L21" s="40" t="n"/>
-      <c r="M21" s="40" t="n"/>
-      <c r="N21" s="40" t="n"/>
-      <c r="O21" s="40" t="n"/>
-      <c r="P21" s="36">
+      <c r="H21" s="45" t="n"/>
+      <c r="I21" s="45" t="n"/>
+      <c r="J21" s="45" t="n"/>
+      <c r="K21" s="45" t="n"/>
+      <c r="L21" s="45" t="n"/>
+      <c r="M21" s="45" t="n"/>
+      <c r="N21" s="45" t="n"/>
+      <c r="O21" s="45" t="n"/>
+      <c r="P21" s="41">
         <f>SUM(H21:O21)</f>
         <v/>
       </c>
-      <c r="Q21" s="41" t="n"/>
-      <c r="R21" s="41" t="n"/>
+      <c r="Q21" s="46" t="n"/>
+      <c r="R21" s="46" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="38">
+      <c r="A22" s="43">
         <f>Planejado!A22</f>
         <v/>
       </c>
-      <c r="B22" s="38">
+      <c r="B22" s="43">
         <f>Planejado!B22</f>
         <v/>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="43">
         <f>Planejado!C22</f>
         <v/>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="44">
         <f>Planejado!D22</f>
         <v/>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="44">
         <f>Planejado!E22</f>
         <v/>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="43">
         <f>Planejado!F22</f>
         <v/>
       </c>
-      <c r="G22" s="38">
+      <c r="G22" s="43">
         <f>Planejado!G22</f>
         <v/>
       </c>
-      <c r="H22" s="40" t="n"/>
-      <c r="I22" s="40" t="n"/>
-      <c r="J22" s="40" t="n"/>
-      <c r="K22" s="40" t="n"/>
-      <c r="L22" s="40" t="n"/>
-      <c r="M22" s="40" t="n"/>
-      <c r="N22" s="40" t="n"/>
-      <c r="O22" s="40" t="n"/>
-      <c r="P22" s="36">
+      <c r="H22" s="45" t="n"/>
+      <c r="I22" s="45" t="n"/>
+      <c r="J22" s="45" t="n"/>
+      <c r="K22" s="45" t="n"/>
+      <c r="L22" s="45" t="n"/>
+      <c r="M22" s="45" t="n"/>
+      <c r="N22" s="45" t="n"/>
+      <c r="O22" s="45" t="n"/>
+      <c r="P22" s="41">
         <f>SUM(H22:O22)</f>
         <v/>
       </c>
-      <c r="Q22" s="41" t="n"/>
-      <c r="R22" s="41" t="n"/>
+      <c r="Q22" s="46" t="n"/>
+      <c r="R22" s="46" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="38">
+      <c r="A23" s="43">
         <f>Planejado!A23</f>
         <v/>
       </c>
-      <c r="B23" s="38">
+      <c r="B23" s="43">
         <f>Planejado!B23</f>
         <v/>
       </c>
-      <c r="C23" s="38">
+      <c r="C23" s="43">
         <f>Planejado!C23</f>
         <v/>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="44">
         <f>Planejado!D23</f>
         <v/>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="44">
         <f>Planejado!E23</f>
         <v/>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="43">
         <f>Planejado!F23</f>
         <v/>
       </c>
-      <c r="G23" s="38">
+      <c r="G23" s="43">
         <f>Planejado!G23</f>
         <v/>
       </c>
-      <c r="H23" s="40" t="n"/>
-      <c r="I23" s="40" t="n"/>
-      <c r="J23" s="40" t="n"/>
-      <c r="K23" s="40" t="n"/>
-      <c r="L23" s="40" t="n"/>
-      <c r="M23" s="40" t="n"/>
-      <c r="N23" s="40" t="n"/>
-      <c r="O23" s="40" t="n"/>
-      <c r="P23" s="36">
+      <c r="H23" s="45" t="n"/>
+      <c r="I23" s="45" t="n"/>
+      <c r="J23" s="45" t="n"/>
+      <c r="K23" s="45" t="n"/>
+      <c r="L23" s="45" t="n"/>
+      <c r="M23" s="45" t="n"/>
+      <c r="N23" s="45" t="n"/>
+      <c r="O23" s="45" t="n"/>
+      <c r="P23" s="41">
         <f>SUM(H23:O23)</f>
         <v/>
       </c>
-      <c r="Q23" s="41" t="n"/>
-      <c r="R23" s="41" t="n"/>
+      <c r="Q23" s="46" t="n"/>
+      <c r="R23" s="46" t="n"/>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="38">
+      <c r="A24" s="43">
         <f>Planejado!A24</f>
         <v/>
       </c>
-      <c r="B24" s="38">
+      <c r="B24" s="43">
         <f>Planejado!B24</f>
         <v/>
       </c>
-      <c r="C24" s="38">
+      <c r="C24" s="43">
         <f>Planejado!C24</f>
         <v/>
       </c>
-      <c r="D24" s="39">
+      <c r="D24" s="44">
         <f>Planejado!D24</f>
         <v/>
       </c>
-      <c r="E24" s="39">
+      <c r="E24" s="44">
         <f>Planejado!E24</f>
         <v/>
       </c>
-      <c r="F24" s="38">
+      <c r="F24" s="43">
         <f>Planejado!F24</f>
         <v/>
       </c>
-      <c r="G24" s="38">
+      <c r="G24" s="43">
         <f>Planejado!G24</f>
         <v/>
       </c>
-      <c r="H24" s="40" t="n"/>
-      <c r="I24" s="40" t="n"/>
-      <c r="J24" s="40" t="n"/>
-      <c r="K24" s="40" t="n"/>
-      <c r="L24" s="40" t="n"/>
-      <c r="M24" s="40" t="n"/>
-      <c r="N24" s="40" t="n"/>
-      <c r="O24" s="40" t="n"/>
-      <c r="P24" s="36">
+      <c r="H24" s="45" t="n"/>
+      <c r="I24" s="45" t="n"/>
+      <c r="J24" s="45" t="n"/>
+      <c r="K24" s="45" t="n"/>
+      <c r="L24" s="45" t="n"/>
+      <c r="M24" s="45" t="n"/>
+      <c r="N24" s="45" t="n"/>
+      <c r="O24" s="45" t="n"/>
+      <c r="P24" s="41">
         <f>SUM(H24:O24)</f>
         <v/>
       </c>
-      <c r="Q24" s="41" t="n"/>
-      <c r="R24" s="41" t="n"/>
+      <c r="Q24" s="46" t="n"/>
+      <c r="R24" s="46" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="38">
+      <c r="A25" s="43">
         <f>Planejado!A25</f>
         <v/>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="43">
         <f>Planejado!B25</f>
         <v/>
       </c>
-      <c r="C25" s="38">
+      <c r="C25" s="43">
         <f>Planejado!C25</f>
         <v/>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="44">
         <f>Planejado!D25</f>
         <v/>
       </c>
-      <c r="E25" s="39">
+      <c r="E25" s="44">
         <f>Planejado!E25</f>
         <v/>
       </c>
-      <c r="F25" s="38">
+      <c r="F25" s="43">
         <f>Planejado!F25</f>
         <v/>
       </c>
-      <c r="G25" s="38">
+      <c r="G25" s="43">
         <f>Planejado!G25</f>
         <v/>
       </c>
-      <c r="H25" s="40" t="n"/>
-      <c r="I25" s="40" t="n"/>
-      <c r="J25" s="40" t="n"/>
-      <c r="K25" s="40" t="n"/>
-      <c r="L25" s="40" t="n"/>
-      <c r="M25" s="40" t="n"/>
-      <c r="N25" s="40" t="n"/>
-      <c r="O25" s="40" t="n"/>
-      <c r="P25" s="36">
+      <c r="H25" s="45" t="n"/>
+      <c r="I25" s="45" t="n"/>
+      <c r="J25" s="45" t="n"/>
+      <c r="K25" s="45" t="n"/>
+      <c r="L25" s="45" t="n"/>
+      <c r="M25" s="45" t="n"/>
+      <c r="N25" s="45" t="n"/>
+      <c r="O25" s="45" t="n"/>
+      <c r="P25" s="41">
         <f>SUM(H25:O25)</f>
         <v/>
       </c>
-      <c r="Q25" s="41" t="n"/>
-      <c r="R25" s="41" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="42" t="inlineStr">
+      <c r="Q25" s="46" t="n"/>
+      <c r="R25" s="46" t="n"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="43">
+        <f>Planejado!A26</f>
+        <v/>
+      </c>
+      <c r="B26" s="43">
+        <f>Planejado!B26</f>
+        <v/>
+      </c>
+      <c r="C26" s="43">
+        <f>Planejado!C26</f>
+        <v/>
+      </c>
+      <c r="D26" s="44">
+        <f>Planejado!D26</f>
+        <v/>
+      </c>
+      <c r="E26" s="44">
+        <f>Planejado!E26</f>
+        <v/>
+      </c>
+      <c r="F26" s="43">
+        <f>Planejado!F26</f>
+        <v/>
+      </c>
+      <c r="G26" s="43">
+        <f>Planejado!G26</f>
+        <v/>
+      </c>
+      <c r="H26" s="45" t="n"/>
+      <c r="I26" s="45" t="n"/>
+      <c r="J26" s="45" t="n"/>
+      <c r="K26" s="45" t="n"/>
+      <c r="L26" s="45" t="n"/>
+      <c r="M26" s="45" t="n"/>
+      <c r="N26" s="45" t="n"/>
+      <c r="O26" s="45" t="n"/>
+      <c r="P26" s="41">
+        <f>SUM(H26:O26)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="46" t="n"/>
+      <c r="R26" s="46" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="47" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B26" s="42" t="n"/>
-      <c r="C26" s="42" t="n"/>
-      <c r="D26" s="42" t="n"/>
-      <c r="E26" s="42" t="n"/>
-      <c r="F26" s="42" t="n"/>
-      <c r="G26" s="42" t="n"/>
-      <c r="H26" s="43">
-        <f>SUM(H5:H25)</f>
-        <v/>
-      </c>
-      <c r="I26" s="43">
-        <f>SUM(I5:I25)</f>
-        <v/>
-      </c>
-      <c r="J26" s="43">
-        <f>SUM(J5:J25)</f>
-        <v/>
-      </c>
-      <c r="K26" s="43">
-        <f>SUM(K5:K25)</f>
-        <v/>
-      </c>
-      <c r="L26" s="43">
-        <f>SUM(L5:L25)</f>
-        <v/>
-      </c>
-      <c r="M26" s="43">
-        <f>SUM(M5:M25)</f>
-        <v/>
-      </c>
-      <c r="N26" s="43">
-        <f>SUM(N5:N25)</f>
-        <v/>
-      </c>
-      <c r="O26" s="43">
-        <f>SUM(O5:O25)</f>
-        <v/>
-      </c>
-      <c r="P26" s="43">
-        <f>SUM(P5:P25)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="42" t="n"/>
-      <c r="R26" s="42" t="n"/>
+      <c r="B27" s="47" t="n"/>
+      <c r="C27" s="47" t="n"/>
+      <c r="D27" s="47" t="n"/>
+      <c r="E27" s="47" t="n"/>
+      <c r="F27" s="47" t="n"/>
+      <c r="G27" s="47" t="n"/>
+      <c r="H27" s="48">
+        <f>SUM(H5:H26)</f>
+        <v/>
+      </c>
+      <c r="I27" s="48">
+        <f>SUM(I5:I26)</f>
+        <v/>
+      </c>
+      <c r="J27" s="48">
+        <f>SUM(J5:J26)</f>
+        <v/>
+      </c>
+      <c r="K27" s="48">
+        <f>SUM(K5:K26)</f>
+        <v/>
+      </c>
+      <c r="L27" s="48">
+        <f>SUM(L5:L26)</f>
+        <v/>
+      </c>
+      <c r="M27" s="48">
+        <f>SUM(M5:M26)</f>
+        <v/>
+      </c>
+      <c r="N27" s="48">
+        <f>SUM(N5:N26)</f>
+        <v/>
+      </c>
+      <c r="O27" s="48">
+        <f>SUM(O5:O26)</f>
+        <v/>
+      </c>
+      <c r="P27" s="48">
+        <f>SUM(P5:P26)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="47" t="n"/>
+      <c r="R27" s="47" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5718,385 +6155,385 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="44" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B5" s="27">
-        <f>SUMIFS(Planejado!$H$5:$H$25,Planejado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C5" s="27">
-        <f>SUMIFS(Realizado!$H$5:$H$25,Realizado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D5" s="27">
-        <f>SUMIFS(Planejado!$H$5:$H$25,Planejado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="E5" s="27">
-        <f>SUMIFS(Realizado!$H$5:$H$25,Realizado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="F5" s="27">
+      <c r="B5" s="30">
+        <f>SUMIFS(Planejado!$H$5:$H$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C5" s="30">
+        <f>SUMIFS(Realizado!$H$5:$H$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D5" s="30">
+        <f>SUMIFS(Planejado!$H$5:$H$26,Planejado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="E5" s="30">
+        <f>SUMIFS(Realizado!$H$5:$H$26,Realizado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="F5" s="30">
         <f>B5+D5</f>
         <v/>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="30">
         <f>C5+E5</f>
         <v/>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="30">
         <f>G5-F5</f>
         <v/>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="30">
         <f>SUM($F$5:F5)</f>
         <v/>
       </c>
-      <c r="J5" s="27">
+      <c r="J5" s="30">
         <f>SUM($G$5:G5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B6" s="32">
-        <f>SUMIFS(Planejado!$I$5:$I$25,Planejado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C6" s="32">
-        <f>SUMIFS(Realizado!$I$5:$I$25,Realizado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>SUMIFS(Planejado!$I$5:$I$25,Planejado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="E6" s="32">
-        <f>SUMIFS(Realizado!$I$5:$I$25,Realizado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
+      <c r="B6" s="36">
+        <f>SUMIFS(Planejado!$I$5:$I$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C6" s="36">
+        <f>SUMIFS(Realizado!$I$5:$I$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D6" s="36">
+        <f>SUMIFS(Planejado!$I$5:$I$26,Planejado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="E6" s="36">
+        <f>SUMIFS(Realizado!$I$5:$I$26,Realizado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="F6" s="36">
         <f>B6+D6</f>
         <v/>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="36">
         <f>C6+E6</f>
         <v/>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="36">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="36">
         <f>SUM($F$5:F6)</f>
         <v/>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="36">
         <f>SUM($G$5:G6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B7" s="27">
-        <f>SUMIFS(Planejado!$J$5:$J$25,Planejado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C7" s="27">
-        <f>SUMIFS(Realizado!$J$5:$J$25,Realizado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D7" s="27">
-        <f>SUMIFS(Planejado!$J$5:$J$25,Planejado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="E7" s="27">
-        <f>SUMIFS(Realizado!$J$5:$J$25,Realizado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="F7" s="27">
+      <c r="B7" s="30">
+        <f>SUMIFS(Planejado!$J$5:$J$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C7" s="30">
+        <f>SUMIFS(Realizado!$J$5:$J$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D7" s="30">
+        <f>SUMIFS(Planejado!$J$5:$J$26,Planejado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="E7" s="30">
+        <f>SUMIFS(Realizado!$J$5:$J$26,Realizado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="F7" s="30">
         <f>B7+D7</f>
         <v/>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="30">
         <f>C7+E7</f>
         <v/>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="30">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="30">
         <f>SUM($F$5:F7)</f>
         <v/>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="30">
         <f>SUM($G$5:G7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="B8" s="32">
-        <f>SUMIFS(Planejado!$K$5:$K$25,Planejado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C8" s="32">
-        <f>SUMIFS(Realizado!$K$5:$K$25,Realizado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D8" s="32">
-        <f>SUMIFS(Planejado!$K$5:$K$25,Planejado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="E8" s="32">
-        <f>SUMIFS(Realizado!$K$5:$K$25,Realizado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="F8" s="32">
+      <c r="B8" s="36">
+        <f>SUMIFS(Planejado!$K$5:$K$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C8" s="36">
+        <f>SUMIFS(Realizado!$K$5:$K$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D8" s="36">
+        <f>SUMIFS(Planejado!$K$5:$K$26,Planejado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="E8" s="36">
+        <f>SUMIFS(Realizado!$K$5:$K$26,Realizado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="F8" s="36">
         <f>B8+D8</f>
         <v/>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="36">
         <f>C8+E8</f>
         <v/>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="36">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="36">
         <f>SUM($F$5:F8)</f>
         <v/>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="36">
         <f>SUM($G$5:G8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="44" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="B9" s="27">
-        <f>SUMIFS(Planejado!$L$5:$L$25,Planejado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C9" s="27">
-        <f>SUMIFS(Realizado!$L$5:$L$25,Realizado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D9" s="27">
-        <f>SUMIFS(Planejado!$L$5:$L$25,Planejado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="E9" s="27">
-        <f>SUMIFS(Realizado!$L$5:$L$25,Realizado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="F9" s="27">
+      <c r="B9" s="30">
+        <f>SUMIFS(Planejado!$L$5:$L$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C9" s="30">
+        <f>SUMIFS(Realizado!$L$5:$L$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>SUMIFS(Planejado!$L$5:$L$26,Planejado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="E9" s="30">
+        <f>SUMIFS(Realizado!$L$5:$L$26,Realizado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="F9" s="30">
         <f>B9+D9</f>
         <v/>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="30">
         <f>C9+E9</f>
         <v/>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="30">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="30">
         <f>SUM($F$5:F9)</f>
         <v/>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="30">
         <f>SUM($G$5:G9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="B10" s="32">
-        <f>SUMIFS(Planejado!$M$5:$M$25,Planejado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C10" s="32">
-        <f>SUMIFS(Realizado!$M$5:$M$25,Realizado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D10" s="32">
-        <f>SUMIFS(Planejado!$M$5:$M$25,Planejado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="E10" s="32">
-        <f>SUMIFS(Realizado!$M$5:$M$25,Realizado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="F10" s="32">
+      <c r="B10" s="36">
+        <f>SUMIFS(Planejado!$M$5:$M$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C10" s="36">
+        <f>SUMIFS(Realizado!$M$5:$M$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D10" s="36">
+        <f>SUMIFS(Planejado!$M$5:$M$26,Planejado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="E10" s="36">
+        <f>SUMIFS(Realizado!$M$5:$M$26,Realizado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="F10" s="36">
         <f>B10+D10</f>
         <v/>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="36">
         <f>C10+E10</f>
         <v/>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="36">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="36">
         <f>SUM($F$5:F10)</f>
         <v/>
       </c>
-      <c r="J10" s="32">
+      <c r="J10" s="36">
         <f>SUM($G$5:G10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="44" t="inlineStr">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="B11" s="27">
-        <f>SUMIFS(Planejado!$N$5:$N$25,Planejado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C11" s="27">
-        <f>SUMIFS(Realizado!$N$5:$N$25,Realizado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D11" s="27">
-        <f>SUMIFS(Planejado!$N$5:$N$25,Planejado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="E11" s="27">
-        <f>SUMIFS(Realizado!$N$5:$N$25,Realizado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="F11" s="27">
+      <c r="B11" s="30">
+        <f>SUMIFS(Planejado!$N$5:$N$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C11" s="30">
+        <f>SUMIFS(Realizado!$N$5:$N$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D11" s="30">
+        <f>SUMIFS(Planejado!$N$5:$N$26,Planejado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="E11" s="30">
+        <f>SUMIFS(Realizado!$N$5:$N$26,Realizado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
         <f>B11+D11</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="30">
         <f>C11+E11</f>
         <v/>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="30">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="30">
         <f>SUM($F$5:F11)</f>
         <v/>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="30">
         <f>SUM($G$5:G11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="B12" s="32">
-        <f>SUMIFS(Planejado!$O$5:$O$25,Planejado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C12" s="32">
-        <f>SUMIFS(Realizado!$O$5:$O$25,Realizado!$B$5:$B$25,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
-        <f>SUMIFS(Planejado!$O$5:$O$25,Planejado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="E12" s="32">
-        <f>SUMIFS(Realizado!$O$5:$O$25,Realizado!$B$5:$B$25,"TI")</f>
-        <v/>
-      </c>
-      <c r="F12" s="32">
+      <c r="B12" s="36">
+        <f>SUMIFS(Planejado!$O$5:$O$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C12" s="36">
+        <f>SUMIFS(Realizado!$O$5:$O$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D12" s="36">
+        <f>SUMIFS(Planejado!$O$5:$O$26,Planejado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="E12" s="36">
+        <f>SUMIFS(Realizado!$O$5:$O$26,Realizado!$B$5:$B$26,"TI")</f>
+        <v/>
+      </c>
+      <c r="F12" s="36">
         <f>B12+D12</f>
         <v/>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="36">
         <f>C12+E12</f>
         <v/>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="36">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="36">
         <f>SUM($F$5:F12)</f>
         <v/>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="36">
         <f>SUM($G$5:G12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="16">
         <f>SUM(B5:B12)</f>
         <v/>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="16">
         <f>SUM(C5:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="16">
         <f>SUM(D5:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="16">
         <f>SUM(E5:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="16">
         <f>SUM(F5:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="16">
         <f>SUM(G5:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="16">
         <f>SUM(H5:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="13" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6122,7 +6559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6204,346 +6641,389 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="B5" s="27">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C5" s="27">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D5" s="27">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="E5" s="27">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="F5" s="27">
+      <c r="B5" s="30">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A5,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C5" s="30">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A5,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D5" s="30">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A5,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E5" s="30">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A5,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F5" s="30">
         <f>B5+D5</f>
         <v/>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="30">
         <f>C5+E5</f>
         <v/>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="30">
         <f>G5-F5</f>
         <v/>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="52">
         <f>IFERROR(H5/F5,"")</f>
         <v/>
       </c>
-      <c r="J5" s="27">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$G$5:$G$25,$A5)</f>
+      <c r="J5" s="30">
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>Encargos e Benefícios - CLT</t>
+        </is>
+      </c>
+      <c r="B6" s="36">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A6,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C6" s="36">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A6,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D6" s="36">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A6,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E6" s="36">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A6,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F6" s="36">
+        <f>B6+D6</f>
+        <v/>
+      </c>
+      <c r="G6" s="36">
+        <f>C6+E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="36">
+        <f>G6-F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="54">
+        <f>IFERROR(H6/F6,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="36">
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="B6" s="32">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C6" s="32">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="E6" s="32">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>B6+D6</f>
-        <v/>
-      </c>
-      <c r="G6" s="32">
-        <f>C6+E6</f>
-        <v/>
-      </c>
-      <c r="H6" s="32">
-        <f>G6-F6</f>
-        <v/>
-      </c>
-      <c r="I6" s="49">
-        <f>IFERROR(H6/F6,"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="32">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$G$5:$G$25,$A6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="46" t="inlineStr">
+      <c r="B7" s="30">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A7,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C7" s="30">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A7,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D7" s="30">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A7,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E7" s="30">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A7,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F7" s="30">
+        <f>B7+D7</f>
+        <v/>
+      </c>
+      <c r="G7" s="30">
+        <f>C7+E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="30">
+        <f>G7-F7</f>
+        <v/>
+      </c>
+      <c r="I7" s="52">
+        <f>IFERROR(H7/F7,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="30">
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="B7" s="27">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C7" s="27">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D7" s="27">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="E7" s="27">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="F7" s="27">
-        <f>B7+D7</f>
-        <v/>
-      </c>
-      <c r="G7" s="27">
-        <f>C7+E7</f>
-        <v/>
-      </c>
-      <c r="H7" s="27">
-        <f>G7-F7</f>
-        <v/>
-      </c>
-      <c r="I7" s="47">
-        <f>IFERROR(H7/F7,"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="27">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$G$5:$G$25,$A7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="B8" s="36">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A8,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C8" s="36">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A8,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D8" s="36">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A8,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E8" s="36">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A8,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F8" s="36">
+        <f>B8+D8</f>
+        <v/>
+      </c>
+      <c r="G8" s="36">
+        <f>C8+E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="36">
+        <f>G8-F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="54">
+        <f>IFERROR(H8/F8,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="36">
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="B8" s="32">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C8" s="32">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D8" s="32">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="E8" s="32">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="F8" s="32">
-        <f>B8+D8</f>
-        <v/>
-      </c>
-      <c r="G8" s="32">
-        <f>C8+E8</f>
-        <v/>
-      </c>
-      <c r="H8" s="32">
-        <f>G8-F8</f>
-        <v/>
-      </c>
-      <c r="I8" s="49">
-        <f>IFERROR(H8/F8,"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="32">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$G$5:$G$25,$A8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="46" t="inlineStr">
+      <c r="B9" s="30">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A9,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C9" s="30">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A9,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D9" s="30">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A9,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E9" s="30">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A9,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F9" s="30">
+        <f>B9+D9</f>
+        <v/>
+      </c>
+      <c r="G9" s="30">
+        <f>C9+E9</f>
+        <v/>
+      </c>
+      <c r="H9" s="30">
+        <f>G9-F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="52">
+        <f>IFERROR(H9/F9,"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="30">
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="B9" s="27">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C9" s="27">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D9" s="27">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="E9" s="27">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="F9" s="27">
-        <f>B9+D9</f>
-        <v/>
-      </c>
-      <c r="G9" s="27">
-        <f>C9+E9</f>
-        <v/>
-      </c>
-      <c r="H9" s="27">
-        <f>G9-F9</f>
-        <v/>
-      </c>
-      <c r="I9" s="47">
-        <f>IFERROR(H9/F9,"")</f>
-        <v/>
-      </c>
-      <c r="J9" s="27">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$G$5:$G$25,$A9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="B10" s="36">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A10,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C10" s="36">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A10,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D10" s="36">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A10,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E10" s="36">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A10,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F10" s="36">
+        <f>B10+D10</f>
+        <v/>
+      </c>
+      <c r="G10" s="36">
+        <f>C10+E10</f>
+        <v/>
+      </c>
+      <c r="H10" s="36">
+        <f>G10-F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="54">
+        <f>IFERROR(H10/F10,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="36">
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
-      <c r="B10" s="32">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C10" s="32">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D10" s="32">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="E10" s="32">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="F10" s="32">
-        <f>B10+D10</f>
-        <v/>
-      </c>
-      <c r="G10" s="32">
-        <f>C10+E10</f>
-        <v/>
-      </c>
-      <c r="H10" s="32">
-        <f>G10-F10</f>
-        <v/>
-      </c>
-      <c r="I10" s="49">
-        <f>IFERROR(H10/F10,"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="32">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$G$5:$G$25,$A10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="B11" s="30">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A11,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C11" s="30">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A11,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D11" s="30">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A11,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E11" s="30">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A11,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F11" s="30">
+        <f>B11+D11</f>
+        <v/>
+      </c>
+      <c r="G11" s="30">
+        <f>C11+E11</f>
+        <v/>
+      </c>
+      <c r="H11" s="30">
+        <f>G11-F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="52">
+        <f>IFERROR(H11/F11,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="30">
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="53" t="inlineStr">
         <is>
           <t>Móveis e Utensílios</t>
         </is>
       </c>
-      <c r="B11" s="27">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C11" s="27">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D11" s="27">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="E11" s="27">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"TI")</f>
-        <v/>
-      </c>
-      <c r="F11" s="27">
-        <f>B11+D11</f>
-        <v/>
-      </c>
-      <c r="G11" s="27">
-        <f>C11+E11</f>
-        <v/>
-      </c>
-      <c r="H11" s="27">
-        <f>G11-F11</f>
-        <v/>
-      </c>
-      <c r="I11" s="47">
-        <f>IFERROR(H11/F11,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="27">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$G$5:$G$25,$A11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="B12" s="36">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A12,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C12" s="36">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A12,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D12" s="36">
+        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A12,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E12" s="36">
+        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A12,Comparativo!$B$6:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F12" s="36">
+        <f>B12+D12</f>
+        <v/>
+      </c>
+      <c r="G12" s="36">
+        <f>C12+E12</f>
+        <v/>
+      </c>
+      <c r="H12" s="36">
+        <f>G12-F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="54">
+        <f>IFERROR(H12/F12,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="36">
+        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="14">
-        <f>SUM(B5:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="14">
-        <f>SUM(C5:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="14">
-        <f>SUM(D5:D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="14">
-        <f>SUM(E5:E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="14">
-        <f>SUM(F5:F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="14">
-        <f>SUM(G5:G11)</f>
-        <v/>
-      </c>
-      <c r="H12" s="14">
-        <f>SUM(H5:H11)</f>
-        <v/>
-      </c>
-      <c r="I12" s="15">
-        <f>IFERROR(H12/F12,"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="14">
-        <f>SUM(J5:J11)</f>
+      <c r="B13" s="16">
+        <f>SUM(B5:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>SUM(C5:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="16">
+        <f>SUM(D5:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="16">
+        <f>SUM(E5:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="16">
+        <f>SUM(F5:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="16">
+        <f>SUM(G5:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="16">
+        <f>SUM(H5:H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>IFERROR(H13/F13,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="16">
+        <f>SUM(J5:J12)</f>
         <v/>
       </c>
     </row>
@@ -6552,7 +7032,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H11">
+  <conditionalFormatting sqref="H5:H12">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -6570,7 +7050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6628,224 +7108,384 @@
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>Encargos da Geovanna — CAMPO A PREENCHER</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>A linha JUR-E02B foi criada para receber os encargos e benefícios sobre o salário bruto (INSS patronal, FGTS, provisões de 13º e férias, VT/VR, plano de saúde). Hoje está em branco em mai, jun e jul.</t>
+        </is>
+      </c>
+      <c r="D5" s="56" t="inlineStr">
+        <is>
+          <t>Enquanto não for preenchida, a folha do Jurídico aparece R$ 1.938,61/mês abaixo do orçado — economia que não existe, é só encargo não lançado.</t>
+        </is>
+      </c>
+      <c r="E5" s="56" t="inlineStr">
+        <is>
+          <t>Cristiane + RH</t>
+        </is>
+      </c>
+      <c r="F5" s="57" t="inlineStr">
+        <is>
+          <t>PREENCHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="59" t="inlineStr">
+        <is>
+          <t>Vinicius Di Franco tem o mesmo problema</t>
+        </is>
+      </c>
+      <c r="C6" s="59" t="inlineStr">
+        <is>
+          <t>O orçamento dele (R$ 5.416,53/mês) também é custo total com encargos. Quando o realizado do TI for lançado, ou vem o custo total, ou a linha precisa ser dividida em bruto + encargos como foi feito com a Geovanna.</t>
+        </is>
+      </c>
+      <c r="D6" s="59" t="inlineStr">
+        <is>
+          <t>Se lançarem o bruto contra o orçado de custo total, o TI vai mostrar uma economia falsa da mesma natureza.</t>
+        </is>
+      </c>
+      <c r="E6" s="59" t="inlineStr">
+        <is>
+          <t>Cristiane + RH</t>
+        </is>
+      </c>
+      <c r="F6" s="60" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="56" t="inlineStr">
+        <is>
+          <t>Reajuste da Thamar — revisão orçamentária</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="inlineStr">
+        <is>
+          <t>Reajuste permanente de R$ 5.000 para R$ 5.500/mês, já em vigor desde mai/26. O planejado foi mantido em R$ 5.000 em mai–set (para o desvio ficar visível) e revisado para R$ 5.500 de out a dez.</t>
+        </is>
+      </c>
+      <c r="D7" s="56" t="inlineStr">
+        <is>
+          <t>Desvio já incorrido de R$ 500/mês. Impacto de +R$ 1.500 no orçamento do restante do ano; o orçamento total sobe para R$ 395.852,68.</t>
+        </is>
+      </c>
+      <c r="E7" s="56" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F7" s="61" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="58" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" s="59" t="inlineStr">
+        <is>
+          <t>Jusbrasil 30% acima do orçado</t>
+        </is>
+      </c>
+      <c r="C8" s="59" t="inlineStr">
+        <is>
+          <t>Orçado R$ 104,90/mês, realizado R$ 136,00/mês nos três meses.</t>
+        </is>
+      </c>
+      <c r="D8" s="59" t="inlineStr">
+        <is>
+          <t>Menor desvio em reais (R$ 31,10/mês), mas o maior em percentual. Vale conferir se houve reajuste contratual ou mudança de plano.</t>
+        </is>
+      </c>
+      <c r="E8" s="59" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F8" s="60" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
+          <t>Bonificação de ago/26 do Jurídico</t>
+        </is>
+      </c>
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t>Estão orçados R$ 10.293,60 em agosto e R$ 12.867,00 em dezembro. O realizado de agosto ainda não foi informado.</t>
+        </is>
+      </c>
+      <c r="D9" s="56" t="inlineStr">
+        <is>
+          <t>É a maior despesa isolada do Jurídico no segundo semestre. Sem confirmação, o acumulado de agosto fica distorcido.</t>
+        </is>
+      </c>
+      <c r="E9" s="56" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F9" s="60" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="51" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>Base de meses do time de TI</t>
         </is>
       </c>
-      <c r="C5" s="51" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>A ficha original trazia a coluna TOTAL do TI em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9), enquanto o grid mensal tem 8 (mai–dez). Definido: vale mai–dez para todos.</t>
         </is>
       </c>
-      <c r="D5" s="51" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>Orçamento de equipe do TI passou de R$ 167.778,30 para R$ 131.852,20 (−R$ 35.926,10). Total geral: R$ 394.352,68.</t>
         </is>
       </c>
-      <c r="E5" s="51" t="inlineStr">
+      <c r="E10" s="59" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F5" s="52" t="inlineStr">
+      <c r="F10" s="61" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="53" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="54" t="inlineStr">
+      <c r="B11" s="56" t="inlineStr">
         <is>
           <t>Origem do valor realizado</t>
         </is>
       </c>
-      <c r="C6" s="54" t="inlineStr">
+      <c r="C11" s="56" t="inlineStr">
         <is>
           <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto.</t>
         </is>
       </c>
-      <c r="D6" s="54" t="inlineStr">
+      <c r="D11" s="56" t="inlineStr">
         <is>
           <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
         </is>
       </c>
-      <c r="E6" s="54" t="inlineStr">
+      <c r="E11" s="56" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F6" s="55" t="inlineStr">
+      <c r="F11" s="60" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="50" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="51" t="inlineStr">
-        <is>
-          <t>Jusfy x Astrea rodando em paralelo</t>
-        </is>
-      </c>
-      <c r="C7" s="51" t="inlineStr">
-        <is>
-          <t>O Jusfy é teste para eliminar o Astrea, mas ambos estão orçados os 8 meses. Falta definir o mês de corte do Astrea.</t>
-        </is>
-      </c>
-      <c r="D7" s="51" t="inlineStr">
-        <is>
-          <t>Se o Astrea sair antes de dezembro, o planejado precisa ser ajustado; senão o Jurídico vai aparecer 'economizando' o que na verdade era duplicidade.</t>
-        </is>
-      </c>
-      <c r="E7" s="51" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
+        <is>
+          <t>Jusfy x Astrea</t>
+        </is>
+      </c>
+      <c r="C12" s="59" t="inlineStr">
+        <is>
+          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
+        </is>
+      </c>
+      <c r="D12" s="59" t="inlineStr">
+        <is>
+          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado de ago a dez.</t>
+        </is>
+      </c>
+      <c r="E12" s="59" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F7" s="55" t="inlineStr">
+      <c r="F12" s="61" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>Rateio dos softwares corporativos de TI</t>
+        </is>
+      </c>
+      <c r="C13" s="56" t="inlineStr">
+        <is>
+          <t>Backup (R$ 6.600), Adapta/IA (R$ 12.200), Antivírus (R$ 1.920) e Office 365 (R$ 3.000) estão marcados na ficha como 'não sei se seria administrativo'. Total: R$ 23.720.</t>
+        </is>
+      </c>
+      <c r="D13" s="56" t="inlineStr">
+        <is>
+          <t>Se são da empresa toda e ficam no centro de custo de TI, o TI carrega despesa que não é dele e aparece caro no comparativo.</t>
+        </is>
+      </c>
+      <c r="E13" s="56" t="inlineStr">
+        <is>
+          <t>Cristiane + Controladoria</t>
+        </is>
+      </c>
+      <c r="F13" s="60" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B8" s="54" t="inlineStr">
-        <is>
-          <t>Rateio dos softwares corporativos de TI</t>
-        </is>
-      </c>
-      <c r="C8" s="54" t="inlineStr">
-        <is>
-          <t>Backup (R$ 6.600), Adapta/IA (R$ 12.200), Antivírus (R$ 1.920) e Office 365 (R$ 3.000) estão marcados na ficha como 'não sei se seria administrativo'. Total: R$ 23.720.</t>
-        </is>
-      </c>
-      <c r="D8" s="54" t="inlineStr">
-        <is>
-          <t>Se são da empresa toda e ficam no centro de custo de TI, o TI carrega despesa que não é dele e aparece caro no comparativo.</t>
-        </is>
-      </c>
-      <c r="E8" s="54" t="inlineStr">
-        <is>
-          <t>Cristiane + Controladoria</t>
-        </is>
-      </c>
-      <c r="F8" s="55" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B14" s="59" t="inlineStr">
+        <is>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
+        </is>
+      </c>
+      <c r="C14" s="59" t="inlineStr">
+        <is>
+          <t>R$ 2.800/mês × 8 = R$ 22.400 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+        </is>
+      </c>
+      <c r="D14" s="59" t="inlineStr">
+        <is>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+        </is>
+      </c>
+      <c r="E14" s="59" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F14" s="60" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B9" s="51" t="inlineStr">
-        <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
-        </is>
-      </c>
-      <c r="C9" s="51" t="inlineStr">
-        <is>
-          <t>R$ 2.800/mês × 8 = R$ 22.400 diluídos linearmente, classificados em Móveis e Utensílios.</t>
-        </is>
-      </c>
-      <c r="D9" s="51" t="inlineStr">
-        <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
-        </is>
-      </c>
-      <c r="E9" s="51" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="56" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C15" s="56" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D15" s="56" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E15" s="56" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F9" s="55" t="inlineStr">
+      <c r="F15" s="60" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B10" s="54" t="inlineStr">
-        <is>
-          <t>Office 365 — nº de licenças</t>
-        </is>
-      </c>
-      <c r="C10" s="54" t="inlineStr">
-        <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
-        </is>
-      </c>
-      <c r="D10" s="54" t="inlineStr">
-        <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
-        </is>
-      </c>
-      <c r="E10" s="54" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F10" s="55" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="50" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="51" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>Critério de competência x caixa</t>
         </is>
       </c>
-      <c r="C11" s="51" t="inlineStr">
+      <c r="C16" s="59" t="inlineStr">
         <is>
           <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
         </is>
       </c>
-      <c r="D11" s="51" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
         </is>
       </c>
-      <c r="E11" s="51" t="inlineStr">
+      <c r="E16" s="59" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F11" s="55" t="inlineStr">
+      <c r="F16" s="60" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -6889,67 +7529,67 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>ROTINA MENSAL</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="57" t="inlineStr">
+      <c r="B5" s="63" t="inlineStr">
         <is>
           <t>Abra a aba REALIZADO e preencha apenas as células amarelas do mês que fechou. Se o item não teve gasto no mês, digite 0 — deixar em branco significa 'ainda não lancei'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="56" t="inlineStr">
+      <c r="A6" s="62" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="57" t="inlineStr">
+      <c r="B6" s="63" t="inlineStr">
         <is>
           <t>Preencha a coluna 'Fonte do dado' (ex.: relatório do financeiro, nota fiscal, extrato do cartão) para o número ser auditável depois.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="56" t="inlineStr">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="57" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="56" t="inlineStr">
+      <c r="A8" s="62" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="57" t="inlineStr">
+      <c r="B8" s="63" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="56" t="inlineStr">
+      <c r="A9" s="62" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="57" t="inlineStr">
+      <c r="B9" s="63" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -6957,67 +7597,67 @@
     </row>
     <row r="10" ht="8" customHeight="1"/>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>COMO LER OS NÚMEROS</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="56" t="inlineStr">
+      <c r="A12" s="62" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="57" t="inlineStr">
+      <c r="B12" s="63" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="56" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="57" t="inlineStr">
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="56" t="inlineStr">
+      <c r="A14" s="62" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="57" t="inlineStr">
+      <c r="B14" s="63" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="56" t="inlineStr">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="57" t="inlineStr">
+      <c r="B15" s="63" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="56" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="57" t="inlineStr">
+      <c r="B16" s="63" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -7025,43 +7665,43 @@
     </row>
     <row r="17" ht="8" customHeight="1"/>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>REGRAS DA PLANILHA</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="56" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="57" t="inlineStr">
+      <c r="B19" s="63" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="56" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="57" t="inlineStr">
+      <c r="B20" s="63" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="56" t="inlineStr">
+      <c r="A21" s="62" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="57" t="inlineStr">
+      <c r="B21" s="63" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Como usar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$P$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$P$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1121,15 +1121,15 @@
         </is>
       </c>
       <c r="C6" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"Jurídico",Planejado!$C$5:$C$26,"Equipe")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"Jurídico",Planejado!$C$5:$C$27,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="8">
@@ -1145,7 +1145,7 @@
         <v/>
       </c>
       <c r="I6" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1161,15 +1161,15 @@
         </is>
       </c>
       <c r="C7" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"Jurídico",Planejado!$C$5:$C$26,"Despesas")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"Jurídico",Planejado!$C$5:$C$27,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="8">
@@ -1185,7 +1185,7 @@
         <v/>
       </c>
       <c r="I7" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"Jurídico",Comparativo!$C$6:$C$27,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1201,15 +1201,15 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="F8" s="12">
@@ -1225,7 +1225,7 @@
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
     </row>
@@ -1241,15 +1241,15 @@
         </is>
       </c>
       <c r="C9" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"TI",Planejado!$C$5:$C$26,"Equipe")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"TI",Planejado!$C$5:$C$27,"Equipe")</f>
         <v/>
       </c>
       <c r="D9" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Equipe")</f>
         <v/>
       </c>
       <c r="E9" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Equipe")</f>
         <v/>
       </c>
       <c r="F9" s="8">
@@ -1265,7 +1265,7 @@
         <v/>
       </c>
       <c r="I9" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1281,15 +1281,15 @@
         </is>
       </c>
       <c r="C10" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"TI",Planejado!$C$5:$C$26,"Despesas")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"TI",Planejado!$C$5:$C$27,"Despesas")</f>
         <v/>
       </c>
       <c r="D10" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Despesas")</f>
         <v/>
       </c>
       <c r="E10" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Despesas")</f>
         <v/>
       </c>
       <c r="F10" s="8">
@@ -1305,7 +1305,7 @@
         <v/>
       </c>
       <c r="I10" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"TI",Comparativo!$C$6:$C$27,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1321,15 +1321,15 @@
         </is>
       </c>
       <c r="C11" s="12">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="12">
@@ -1345,7 +1345,7 @@
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0",Comparativo!$B$6:$B$27,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$27,"?*",Comparativo!$B$6:$B$27,"TI")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
     </row>
@@ -1357,15 +1357,15 @@
       </c>
       <c r="B12" s="15" t="inlineStr"/>
       <c r="C12" s="16">
-        <f>SUM(Planejado!$P$5:$P$26)</f>
+        <f>SUM(Planejado!$P$5:$P$27)</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>SUM(Comparativo!$I$6:$I$27)</f>
+        <f>SUM(Comparativo!$I$6:$I$28)</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>SUM(Comparativo!$J$6:$J$27)</f>
+        <f>SUM(Comparativo!$J$6:$J$28)</f>
         <v/>
       </c>
       <c r="F12" s="16">
@@ -1381,7 +1381,7 @@
         <v/>
       </c>
       <c r="I12" s="18">
-        <f>COUNTIFS(Comparativo!$P$6:$P$27,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$27)</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$28)</f>
         <v/>
       </c>
     </row>
@@ -1435,23 +1435,23 @@
         <v>1</v>
       </c>
       <c r="B17" s="21">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A17),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A17),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="C17" s="21">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A17),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A17),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="22">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A17),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A17),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="22">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A17),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A17),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="F17" s="22">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A17),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A17),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="G17" s="23">
@@ -1464,23 +1464,23 @@
         <v>2</v>
       </c>
       <c r="B18" s="21">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A18),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A18),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="C18" s="21">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A18),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A18),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="22">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A18),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A18),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="22">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A18),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A18),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="F18" s="22">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A18),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A18),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="G18" s="23">
@@ -1493,23 +1493,23 @@
         <v>3</v>
       </c>
       <c r="B19" s="21">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A19),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A19),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="C19" s="21">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A19),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A19),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="22">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A19),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A19),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="22">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A19),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A19),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="F19" s="22">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A19),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A19),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="G19" s="23">
@@ -1522,23 +1522,23 @@
         <v>4</v>
       </c>
       <c r="B20" s="21">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A20),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A20),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="C20" s="21">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A20),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A20),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="22">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A20),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A20),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="22">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A20),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A20),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="F20" s="22">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A20),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A20),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="G20" s="23">
@@ -1551,23 +1551,23 @@
         <v>5</v>
       </c>
       <c r="B21" s="21">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A21),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A21),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="C21" s="21">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A21),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A21),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="22">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A21),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A21),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="22">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A21),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A21),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="F21" s="22">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$27,MATCH(LARGE(Comparativo!$O$6:$O$27,A21),Comparativo!$O$6:$O$27,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A21),Comparativo!$O$6:$O$28,0)),"")</f>
         <v/>
       </c>
       <c r="G21" s="23">
@@ -1591,7 +1591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3181,57 +3181,123 @@
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="34">
+        <f>Planejado!A27</f>
+        <v/>
+      </c>
+      <c r="B28" s="34">
+        <f>Planejado!B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="34">
+        <f>Planejado!C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="35">
+        <f>Planejado!D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="34">
+        <f>Planejado!G27</f>
+        <v/>
+      </c>
+      <c r="F28" s="36">
+        <f>INDEX(Planejado!$H27:$O27,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G28" s="36">
+        <f>INDEX(Realizado!$H27:$O27,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H28" s="36">
+        <f>G28-F28</f>
+        <v/>
+      </c>
+      <c r="I28" s="36">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H27:$O27)</f>
+        <v/>
+      </c>
+      <c r="J28" s="36">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H27:$O27)</f>
+        <v/>
+      </c>
+      <c r="K28" s="36">
+        <f>J28-I28</f>
+        <v/>
+      </c>
+      <c r="L28" s="37">
+        <f>IFERROR(K28/I28,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="37">
+        <f>IFERROR(J28/I28,"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="38">
+        <f>IF(P28=0,"Sem lançamento",IF(AND(I28=0,J28=0),"—",IF(I28=0,"Não orçado",IF(K28&gt;0.05*I28,"Acima do orçado",IF(K28&lt;-0.05*I28,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O28" s="27">
+        <f>IF(K28&gt;1,K28+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="39">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H27:$O27&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="16">
-        <f>SUM(F6:F27)</f>
-        <v/>
-      </c>
-      <c r="G28" s="16">
-        <f>SUM(G6:G27)</f>
-        <v/>
-      </c>
-      <c r="H28" s="16">
-        <f>SUM(H6:H27)</f>
-        <v/>
-      </c>
-      <c r="I28" s="16">
-        <f>SUM(I6:I27)</f>
-        <v/>
-      </c>
-      <c r="J28" s="16">
-        <f>SUM(J6:J27)</f>
-        <v/>
-      </c>
-      <c r="K28" s="16">
-        <f>SUM(K6:K27)</f>
-        <v/>
-      </c>
-      <c r="L28" s="40">
-        <f>IFERROR(K28/I28,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="40">
-        <f>IFERROR(J28/I28,"")</f>
-        <v/>
-      </c>
-      <c r="N28" s="15" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="16">
+        <f>SUM(F6:F28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="16">
+        <f>SUM(G6:G28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="16">
+        <f>SUM(H6:H28)</f>
+        <v/>
+      </c>
+      <c r="I29" s="16">
+        <f>SUM(I6:I28)</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>SUM(J6:J28)</f>
+        <v/>
+      </c>
+      <c r="K29" s="16">
+        <f>SUM(K6:K28)</f>
+        <v/>
+      </c>
+      <c r="L29" s="40">
+        <f>IFERROR(K29/I29,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="40">
+        <f>IFERROR(J29/I29,"")</f>
+        <v/>
+      </c>
+      <c r="N29" s="15" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N27"/>
+  <autoFilter ref="A5:N28"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H27">
+  <conditionalFormatting sqref="H6:H28">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3239,7 +3305,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K27">
+  <conditionalFormatting sqref="K6:K28">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3262,7 +3328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4011,12 +4077,12 @@
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
-          <t>Vinicius Di Franco</t>
+          <t>Vinicius Di Franco — salário bruto</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Analista Administrativo</t>
+          <t>Analista Administrativo — aumento de R$ 2.570,52 para R$ 3.070,52 a partir de 05/08/26</t>
         </is>
       </c>
       <c r="F15" s="34" t="inlineStr">
@@ -4030,28 +4096,28 @@
         </is>
       </c>
       <c r="H15" s="36" t="n">
-        <v>5416.525</v>
+        <v>2570.52</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>5416.525</v>
+        <v>2570.52</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>5416.525</v>
+        <v>2570.52</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>5416.525</v>
+        <v>3070.52</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>5416.525</v>
+        <v>3070.52</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>5416.525</v>
+        <v>3070.52</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>5416.525</v>
+        <v>3070.52</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>5416.525</v>
+        <v>3070.52</v>
       </c>
       <c r="P15" s="41">
         <f>SUM(H15:O15)</f>
@@ -4061,7 +4127,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>TI-E02</t>
+          <t>TI-E01B</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
@@ -4076,47 +4142,47 @@
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
-          <t>Elias Benedito</t>
+          <t>Vinicius Di Franco — encargos e benefícios</t>
         </is>
       </c>
       <c r="E16" s="35" t="inlineStr">
         <is>
-          <t>Suporte Técnico Terceirizado</t>
+          <t>INSS patronal, FGTS, provisões de 13º e férias, benefícios — PREENCHER</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="G16" s="34" t="inlineStr">
         <is>
-          <t>Pessoal - PJ</t>
+          <t>Encargos e Benefícios - CLT</t>
         </is>
       </c>
       <c r="H16" s="36" t="n">
-        <v>1065</v>
+        <v>2846.005</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>1065</v>
+        <v>2846.005</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>1065</v>
+        <v>2846.005</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>1065</v>
+        <v>2846.005</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>1065</v>
+        <v>2846.005</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>1065</v>
+        <v>2846.005</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>1065</v>
+        <v>2846.005</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>1065</v>
+        <v>2846.005</v>
       </c>
       <c r="P16" s="41">
         <f>SUM(H16:O16)</f>
@@ -4126,7 +4192,7 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>TI-E03</t>
+          <t>TI-E02</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
@@ -4141,12 +4207,12 @@
       </c>
       <c r="D17" s="35" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Elias Benedito</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Consultor</t>
+          <t>Suporte Técnico Terceirizado</t>
         </is>
       </c>
       <c r="F17" s="34" t="inlineStr">
@@ -4160,28 +4226,28 @@
         </is>
       </c>
       <c r="H17" s="36" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="P17" s="41">
         <f>SUM(H17:O17)</f>
@@ -4191,7 +4257,7 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="34" t="inlineStr">
         <is>
-          <t>TI-D01</t>
+          <t>TI-E03</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
@@ -4201,48 +4267,52 @@
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="D18" s="35" t="inlineStr">
         <is>
-          <t>Peças de Manutenção</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="E18" s="35" t="inlineStr">
         <is>
-          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
-        </is>
-      </c>
-      <c r="F18" s="34" t="inlineStr"/>
+          <t>Consultor</t>
+        </is>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
       <c r="G18" s="34" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos Diversos</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="H18" s="36" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="P18" s="41">
         <f>SUM(H18:O18)</f>
@@ -4252,7 +4322,7 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="34" t="inlineStr">
         <is>
-          <t>TI-D02</t>
+          <t>TI-D01</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
@@ -4267,43 +4337,43 @@
       </c>
       <c r="D19" s="35" t="inlineStr">
         <is>
-          <t>Backup em Nuvem</t>
+          <t>Peças de Manutenção</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
+          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr"/>
       <c r="G19" s="34" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
       <c r="H19" s="36" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(H19:O19)</f>
@@ -4313,7 +4383,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="34" t="inlineStr">
         <is>
-          <t>TI-D03</t>
+          <t>TI-D02</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
@@ -4328,12 +4398,12 @@
       </c>
       <c r="D20" s="35" t="inlineStr">
         <is>
-          <t>Inteligência Artificial (Adapta)</t>
+          <t>Backup em Nuvem</t>
         </is>
       </c>
       <c r="E20" s="35" t="inlineStr">
         <is>
-          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
+          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F20" s="34" t="inlineStr"/>
@@ -4343,28 +4413,28 @@
         </is>
       </c>
       <c r="H20" s="36" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="P20" s="41">
         <f>SUM(H20:O20)</f>
@@ -4374,7 +4444,7 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="34" t="inlineStr">
         <is>
-          <t>TI-D04</t>
+          <t>TI-D03</t>
         </is>
       </c>
       <c r="B21" s="34" t="inlineStr">
@@ -4389,12 +4459,12 @@
       </c>
       <c r="D21" s="35" t="inlineStr">
         <is>
-          <t>Antivírus</t>
+          <t>Inteligência Artificial (Adapta)</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
+          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr"/>
@@ -4404,28 +4474,28 @@
         </is>
       </c>
       <c r="H21" s="36" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="O21" s="36" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="P21" s="41">
         <f>SUM(H21:O21)</f>
@@ -4435,7 +4505,7 @@
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="34" t="inlineStr">
         <is>
-          <t>TI-D05</t>
+          <t>TI-D04</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
@@ -4450,12 +4520,12 @@
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
-          <t>Pacote Office 365</t>
+          <t>Antivírus</t>
         </is>
       </c>
       <c r="E22" s="35" t="inlineStr">
         <is>
-          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
+          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F22" s="34" t="inlineStr"/>
@@ -4465,28 +4535,28 @@
         </is>
       </c>
       <c r="H22" s="36" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="O22" s="36" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="P22" s="41">
         <f>SUM(H22:O22)</f>
@@ -4496,7 +4566,7 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="34" t="inlineStr">
         <is>
-          <t>TI-D06</t>
+          <t>TI-D05</t>
         </is>
       </c>
       <c r="B23" s="34" t="inlineStr">
@@ -4511,43 +4581,43 @@
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
+          <t>Pacote Office 365</t>
         </is>
       </c>
       <c r="E23" s="35" t="inlineStr">
         <is>
-          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
+          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F23" s="34" t="inlineStr"/>
       <c r="G23" s="34" t="inlineStr">
         <is>
-          <t>Móveis e Utensílios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H23" s="36" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="O23" s="36" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="P23" s="41">
         <f>SUM(H23:O23)</f>
@@ -4557,7 +4627,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="34" t="inlineStr">
         <is>
-          <t>TI-D07</t>
+          <t>TI-D06</t>
         </is>
       </c>
       <c r="B24" s="34" t="inlineStr">
@@ -4572,39 +4642,43 @@
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>Cursos e Treinamentos</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="inlineStr"/>
+          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
+        </is>
+      </c>
       <c r="F24" s="34" t="inlineStr"/>
       <c r="G24" s="34" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Móveis e Utensílios</t>
         </is>
       </c>
       <c r="H24" s="36" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="I24" s="36" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="J24" s="36" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="K24" s="36" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="L24" s="36" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="M24" s="36" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="N24" s="36" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="O24" s="36" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="P24" s="41">
         <f>SUM(H24:O24)</f>
@@ -4614,7 +4688,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="34" t="inlineStr">
         <is>
-          <t>TI-D08</t>
+          <t>TI-D07</t>
         </is>
       </c>
       <c r="B25" s="34" t="inlineStr">
@@ -4629,39 +4703,39 @@
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>Aplicativo de Gravação de Reunião</t>
+          <t>Cursos e Treinamentos</t>
         </is>
       </c>
       <c r="E25" s="35" t="inlineStr"/>
       <c r="F25" s="34" t="inlineStr"/>
       <c r="G25" s="34" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="H25" s="36" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I25" s="36" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="J25" s="36" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="K25" s="36" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L25" s="36" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="M25" s="36" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="N25" s="36" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="O25" s="36" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="P25" s="41">
         <f>SUM(H25:O25)</f>
@@ -4671,7 +4745,7 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="34" t="inlineStr">
         <is>
-          <t>TI-D09</t>
+          <t>TI-D08</t>
         </is>
       </c>
       <c r="B26" s="34" t="inlineStr">
@@ -4686,100 +4760,157 @@
       </c>
       <c r="D26" s="35" t="inlineStr">
         <is>
-          <t>Bonificação do time</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="inlineStr">
-        <is>
-          <t>Cumprimento de prazos e participação em projetos</t>
-        </is>
-      </c>
+          <t>Aplicativo de Gravação de Reunião</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr"/>
       <c r="F26" s="34" t="inlineStr"/>
       <c r="G26" s="34" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H26" s="36" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="I26" s="36" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="J26" s="36" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="K26" s="36" t="n">
-        <v>2400</v>
+        <v>220</v>
       </c>
       <c r="L26" s="36" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="M26" s="36" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="N26" s="36" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="O26" s="36" t="n">
-        <v>3600</v>
+        <v>220</v>
       </c>
       <c r="P26" s="41">
         <f>SUM(H26:O26)</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>TI-D09</t>
+        </is>
+      </c>
+      <c r="B27" s="34" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr">
+        <is>
+          <t>Bonificação do time</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>Cumprimento de prazos e participação em projetos</t>
+        </is>
+      </c>
+      <c r="F27" s="34" t="inlineStr"/>
+      <c r="G27" s="34" t="inlineStr">
+        <is>
+          <t>Prêmios</t>
+        </is>
+      </c>
+      <c r="H27" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="36" t="n">
+        <v>2400</v>
+      </c>
+      <c r="L27" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="36" t="n">
+        <v>3600</v>
+      </c>
+      <c r="P27" s="41">
+        <f>SUM(H27:O27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="16">
-        <f>SUM(H5:H26)</f>
-        <v/>
-      </c>
-      <c r="I27" s="16">
-        <f>SUM(I5:I26)</f>
-        <v/>
-      </c>
-      <c r="J27" s="16">
-        <f>SUM(J5:J26)</f>
-        <v/>
-      </c>
-      <c r="K27" s="16">
-        <f>SUM(K5:K26)</f>
-        <v/>
-      </c>
-      <c r="L27" s="16">
-        <f>SUM(L5:L26)</f>
-        <v/>
-      </c>
-      <c r="M27" s="16">
-        <f>SUM(M5:M26)</f>
-        <v/>
-      </c>
-      <c r="N27" s="16">
-        <f>SUM(N5:N26)</f>
-        <v/>
-      </c>
-      <c r="O27" s="16">
-        <f>SUM(O5:O26)</f>
-        <v/>
-      </c>
-      <c r="P27" s="16">
-        <f>SUM(P5:P26)</f>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="16">
+        <f>SUM(H5:H27)</f>
+        <v/>
+      </c>
+      <c r="I28" s="16">
+        <f>SUM(I5:I27)</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>SUM(J5:J27)</f>
+        <v/>
+      </c>
+      <c r="K28" s="16">
+        <f>SUM(K5:K27)</f>
+        <v/>
+      </c>
+      <c r="L28" s="16">
+        <f>SUM(L5:L27)</f>
+        <v/>
+      </c>
+      <c r="M28" s="16">
+        <f>SUM(M5:M27)</f>
+        <v/>
+      </c>
+      <c r="N28" s="16">
+        <f>SUM(N5:N27)</f>
+        <v/>
+      </c>
+      <c r="O28" s="16">
+        <f>SUM(O5:O27)</f>
+        <v/>
+      </c>
+      <c r="P28" s="16">
+        <f>SUM(P5:P27)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P26"/>
+  <autoFilter ref="A4:P27"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
@@ -4794,7 +4925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5508,9 +5639,15 @@
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="H15" s="45" t="n"/>
-      <c r="I15" s="45" t="n"/>
-      <c r="J15" s="45" t="n"/>
+      <c r="H15" s="45" t="n">
+        <v>2570.52</v>
+      </c>
+      <c r="I15" s="45" t="n">
+        <v>2570.52</v>
+      </c>
+      <c r="J15" s="45" t="n">
+        <v>2570.52</v>
+      </c>
       <c r="K15" s="45" t="n"/>
       <c r="L15" s="45" t="n"/>
       <c r="M15" s="45" t="n"/>
@@ -5520,8 +5657,16 @@
         <f>SUM(H15:O15)</f>
         <v/>
       </c>
-      <c r="Q15" s="46" t="n"/>
-      <c r="R15" s="46" t="n"/>
+      <c r="Q15" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="R15" s="46" t="inlineStr">
+        <is>
+          <t>Salário bruto vigente até jul; sobe para R$ 3.070,52 em ago</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="43">
@@ -5565,7 +5710,11 @@
         <v/>
       </c>
       <c r="Q16" s="46" t="n"/>
-      <c r="R16" s="46" t="n"/>
+      <c r="R16" s="46" t="inlineStr">
+        <is>
+          <t>PREENCHER — encargos e benefícios sobre o bruto</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="43">
@@ -5596,9 +5745,15 @@
         <f>Planejado!G17</f>
         <v/>
       </c>
-      <c r="H17" s="45" t="n"/>
-      <c r="I17" s="45" t="n"/>
-      <c r="J17" s="45" t="n"/>
+      <c r="H17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="45" t="n">
+        <v>0</v>
+      </c>
       <c r="K17" s="45" t="n"/>
       <c r="L17" s="45" t="n"/>
       <c r="M17" s="45" t="n"/>
@@ -5608,8 +5763,16 @@
         <f>SUM(H17:O17)</f>
         <v/>
       </c>
-      <c r="Q17" s="46" t="n"/>
-      <c r="R17" s="46" t="n"/>
+      <c r="Q17" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="R17" s="46" t="inlineStr">
+        <is>
+          <t>Sem acionamento no período — confirmar se o contrato segue ativo</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="43">
@@ -5640,9 +5803,15 @@
         <f>Planejado!G18</f>
         <v/>
       </c>
-      <c r="H18" s="45" t="n"/>
-      <c r="I18" s="45" t="n"/>
-      <c r="J18" s="45" t="n"/>
+      <c r="H18" s="45" t="n">
+        <v>6300</v>
+      </c>
+      <c r="I18" s="45" t="n">
+        <v>6300</v>
+      </c>
+      <c r="J18" s="45" t="n">
+        <v>6300</v>
+      </c>
       <c r="K18" s="45" t="n"/>
       <c r="L18" s="45" t="n"/>
       <c r="M18" s="45" t="n"/>
@@ -5652,8 +5821,16 @@
         <f>SUM(H18:O18)</f>
         <v/>
       </c>
-      <c r="Q18" s="46" t="n"/>
-      <c r="R18" s="46" t="n"/>
+      <c r="Q18" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="R18" s="46" t="inlineStr">
+        <is>
+          <t>R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="43">
@@ -6007,56 +6184,100 @@
       <c r="Q26" s="46" t="n"/>
       <c r="R26" s="46" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="47" t="inlineStr">
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="43">
+        <f>Planejado!A27</f>
+        <v/>
+      </c>
+      <c r="B27" s="43">
+        <f>Planejado!B27</f>
+        <v/>
+      </c>
+      <c r="C27" s="43">
+        <f>Planejado!C27</f>
+        <v/>
+      </c>
+      <c r="D27" s="44">
+        <f>Planejado!D27</f>
+        <v/>
+      </c>
+      <c r="E27" s="44">
+        <f>Planejado!E27</f>
+        <v/>
+      </c>
+      <c r="F27" s="43">
+        <f>Planejado!F27</f>
+        <v/>
+      </c>
+      <c r="G27" s="43">
+        <f>Planejado!G27</f>
+        <v/>
+      </c>
+      <c r="H27" s="45" t="n"/>
+      <c r="I27" s="45" t="n"/>
+      <c r="J27" s="45" t="n"/>
+      <c r="K27" s="45" t="n"/>
+      <c r="L27" s="45" t="n"/>
+      <c r="M27" s="45" t="n"/>
+      <c r="N27" s="45" t="n"/>
+      <c r="O27" s="45" t="n"/>
+      <c r="P27" s="41">
+        <f>SUM(H27:O27)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="46" t="n"/>
+      <c r="R27" s="46" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="47" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B27" s="47" t="n"/>
-      <c r="C27" s="47" t="n"/>
-      <c r="D27" s="47" t="n"/>
-      <c r="E27" s="47" t="n"/>
-      <c r="F27" s="47" t="n"/>
-      <c r="G27" s="47" t="n"/>
-      <c r="H27" s="48">
-        <f>SUM(H5:H26)</f>
-        <v/>
-      </c>
-      <c r="I27" s="48">
-        <f>SUM(I5:I26)</f>
-        <v/>
-      </c>
-      <c r="J27" s="48">
-        <f>SUM(J5:J26)</f>
-        <v/>
-      </c>
-      <c r="K27" s="48">
-        <f>SUM(K5:K26)</f>
-        <v/>
-      </c>
-      <c r="L27" s="48">
-        <f>SUM(L5:L26)</f>
-        <v/>
-      </c>
-      <c r="M27" s="48">
-        <f>SUM(M5:M26)</f>
-        <v/>
-      </c>
-      <c r="N27" s="48">
-        <f>SUM(N5:N26)</f>
-        <v/>
-      </c>
-      <c r="O27" s="48">
-        <f>SUM(O5:O26)</f>
-        <v/>
-      </c>
-      <c r="P27" s="48">
-        <f>SUM(P5:P26)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="47" t="n"/>
-      <c r="R27" s="47" t="n"/>
+      <c r="B28" s="47" t="n"/>
+      <c r="C28" s="47" t="n"/>
+      <c r="D28" s="47" t="n"/>
+      <c r="E28" s="47" t="n"/>
+      <c r="F28" s="47" t="n"/>
+      <c r="G28" s="47" t="n"/>
+      <c r="H28" s="48">
+        <f>SUM(H5:H27)</f>
+        <v/>
+      </c>
+      <c r="I28" s="48">
+        <f>SUM(I5:I27)</f>
+        <v/>
+      </c>
+      <c r="J28" s="48">
+        <f>SUM(J5:J27)</f>
+        <v/>
+      </c>
+      <c r="K28" s="48">
+        <f>SUM(K5:K27)</f>
+        <v/>
+      </c>
+      <c r="L28" s="48">
+        <f>SUM(L5:L27)</f>
+        <v/>
+      </c>
+      <c r="M28" s="48">
+        <f>SUM(M5:M27)</f>
+        <v/>
+      </c>
+      <c r="N28" s="48">
+        <f>SUM(N5:N27)</f>
+        <v/>
+      </c>
+      <c r="O28" s="48">
+        <f>SUM(O5:O27)</f>
+        <v/>
+      </c>
+      <c r="P28" s="48">
+        <f>SUM(P5:P27)</f>
+        <v/>
+      </c>
+      <c r="Q28" s="47" t="n"/>
+      <c r="R28" s="47" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6161,19 +6382,19 @@
         </is>
       </c>
       <c r="B5" s="30">
-        <f>SUMIFS(Planejado!$H$5:$H$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$27,Planejado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="30">
-        <f>SUMIFS(Realizado!$H$5:$H$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$27,Realizado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="30">
-        <f>SUMIFS(Planejado!$H$5:$H$26,Planejado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$27,Planejado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="30">
-        <f>SUMIFS(Realizado!$H$5:$H$26,Realizado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$27,Realizado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="30">
@@ -6204,19 +6425,19 @@
         </is>
       </c>
       <c r="B6" s="36">
-        <f>SUMIFS(Planejado!$I$5:$I$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$27,Planejado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="36">
-        <f>SUMIFS(Realizado!$I$5:$I$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$27,Realizado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="36">
-        <f>SUMIFS(Planejado!$I$5:$I$26,Planejado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$27,Planejado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="36">
-        <f>SUMIFS(Realizado!$I$5:$I$26,Realizado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$27,Realizado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="36">
@@ -6247,19 +6468,19 @@
         </is>
       </c>
       <c r="B7" s="30">
-        <f>SUMIFS(Planejado!$J$5:$J$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$27,Planejado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="30">
-        <f>SUMIFS(Realizado!$J$5:$J$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$27,Realizado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="30">
-        <f>SUMIFS(Planejado!$J$5:$J$26,Planejado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$27,Planejado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="30">
-        <f>SUMIFS(Realizado!$J$5:$J$26,Realizado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$27,Realizado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="30">
@@ -6290,19 +6511,19 @@
         </is>
       </c>
       <c r="B8" s="36">
-        <f>SUMIFS(Planejado!$K$5:$K$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$27,Planejado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="36">
-        <f>SUMIFS(Realizado!$K$5:$K$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$27,Realizado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="36">
-        <f>SUMIFS(Planejado!$K$5:$K$26,Planejado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$27,Planejado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="36">
-        <f>SUMIFS(Realizado!$K$5:$K$26,Realizado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$27,Realizado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="36">
@@ -6333,19 +6554,19 @@
         </is>
       </c>
       <c r="B9" s="30">
-        <f>SUMIFS(Planejado!$L$5:$L$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$27,Planejado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="30">
-        <f>SUMIFS(Realizado!$L$5:$L$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$27,Realizado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="30">
-        <f>SUMIFS(Planejado!$L$5:$L$26,Planejado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$27,Planejado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="30">
-        <f>SUMIFS(Realizado!$L$5:$L$26,Realizado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$27,Realizado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="30">
@@ -6376,19 +6597,19 @@
         </is>
       </c>
       <c r="B10" s="36">
-        <f>SUMIFS(Planejado!$M$5:$M$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$27,Planejado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="36">
-        <f>SUMIFS(Realizado!$M$5:$M$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$27,Realizado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="36">
-        <f>SUMIFS(Planejado!$M$5:$M$26,Planejado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$27,Planejado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="36">
-        <f>SUMIFS(Realizado!$M$5:$M$26,Realizado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$27,Realizado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="36">
@@ -6419,19 +6640,19 @@
         </is>
       </c>
       <c r="B11" s="30">
-        <f>SUMIFS(Planejado!$N$5:$N$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$27,Planejado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="30">
-        <f>SUMIFS(Realizado!$N$5:$N$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$27,Realizado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="30">
-        <f>SUMIFS(Planejado!$N$5:$N$26,Planejado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$27,Planejado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="30">
-        <f>SUMIFS(Realizado!$N$5:$N$26,Realizado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$27,Realizado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="30">
@@ -6462,19 +6683,19 @@
         </is>
       </c>
       <c r="B12" s="36">
-        <f>SUMIFS(Planejado!$O$5:$O$26,Planejado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$27,Planejado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="C12" s="36">
-        <f>SUMIFS(Realizado!$O$5:$O$26,Realizado!$B$5:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$27,Realizado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="D12" s="36">
-        <f>SUMIFS(Planejado!$O$5:$O$26,Planejado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$27,Planejado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="E12" s="36">
-        <f>SUMIFS(Realizado!$O$5:$O$26,Realizado!$B$5:$B$26,"TI")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$27,Realizado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="F12" s="36">
@@ -6647,19 +6868,19 @@
         </is>
       </c>
       <c r="B5" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A5,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A5,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A5,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A5,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A5,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A5,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A5,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A5,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="30">
@@ -6679,7 +6900,7 @@
         <v/>
       </c>
       <c r="J5" s="30">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A5)</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A5)</f>
         <v/>
       </c>
     </row>
@@ -6690,19 +6911,19 @@
         </is>
       </c>
       <c r="B6" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A6,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A6,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A6,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A6,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A6,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A6,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A6,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A6,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="36">
@@ -6722,7 +6943,7 @@
         <v/>
       </c>
       <c r="J6" s="36">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A6)</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A6)</f>
         <v/>
       </c>
     </row>
@@ -6733,19 +6954,19 @@
         </is>
       </c>
       <c r="B7" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A7,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A7,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A7,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A7,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A7,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A7,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A7,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A7,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="30">
@@ -6765,7 +6986,7 @@
         <v/>
       </c>
       <c r="J7" s="30">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A7)</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A7)</f>
         <v/>
       </c>
     </row>
@@ -6776,19 +6997,19 @@
         </is>
       </c>
       <c r="B8" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A8,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A8,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A8,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A8,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A8,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A8,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A8,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A8,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="36">
@@ -6808,7 +7029,7 @@
         <v/>
       </c>
       <c r="J8" s="36">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A8)</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A8)</f>
         <v/>
       </c>
     </row>
@@ -6819,19 +7040,19 @@
         </is>
       </c>
       <c r="B9" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A9,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A9,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A9,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A9,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A9,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A9,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A9,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A9,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="30">
@@ -6851,7 +7072,7 @@
         <v/>
       </c>
       <c r="J9" s="30">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A9)</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A9)</f>
         <v/>
       </c>
     </row>
@@ -6862,19 +7083,19 @@
         </is>
       </c>
       <c r="B10" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A10,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A10,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A10,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A10,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A10,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A10,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A10,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A10,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="36">
@@ -6894,7 +7115,7 @@
         <v/>
       </c>
       <c r="J10" s="36">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A10)</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A10)</f>
         <v/>
       </c>
     </row>
@@ -6905,19 +7126,19 @@
         </is>
       </c>
       <c r="B11" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A11,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A11,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A11,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A11,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A11,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A11,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A11,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A11,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="30">
@@ -6937,7 +7158,7 @@
         <v/>
       </c>
       <c r="J11" s="30">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A11)</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A11)</f>
         <v/>
       </c>
     </row>
@@ -6948,19 +7169,19 @@
         </is>
       </c>
       <c r="B12" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A12,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A12,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="C12" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A12,Comparativo!$B$6:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A12,Comparativo!$B$6:$B$28,"Jurídico")</f>
         <v/>
       </c>
       <c r="D12" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$27,Comparativo!$E$6:$E$27,$A12,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A12,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="E12" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$27,Comparativo!$E$6:$E$27,$A12,Comparativo!$B$6:$B$27,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A12,Comparativo!$B$6:$B$28,"TI")</f>
         <v/>
       </c>
       <c r="F12" s="36">
@@ -6980,7 +7201,7 @@
         <v/>
       </c>
       <c r="J12" s="36">
-        <f>SUMIFS(Planejado!$P$5:$P$26,Planejado!$G$5:$G$26,$A12)</f>
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A12)</f>
         <v/>
       </c>
     </row>
@@ -7050,7 +7271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7147,17 +7368,17 @@
       </c>
       <c r="B6" s="59" t="inlineStr">
         <is>
-          <t>Vinicius Di Franco tem o mesmo problema</t>
+          <t>Encargos do Vinicius — CAMPO A PREENCHER</t>
         </is>
       </c>
       <c r="C6" s="59" t="inlineStr">
         <is>
-          <t>O orçamento dele (R$ 5.416,53/mês) também é custo total com encargos. Quando o realizado do TI for lançado, ou vem o custo total, ou a linha precisa ser dividida em bruto + encargos como foi feito com a Geovanna.</t>
+          <t>A linha TI-E01B foi criada para receber os encargos e benefícios sobre o salário bruto, mesmo tratamento dado à Geovanna. Hoje está em branco. Aumento permanente de R$ 500 registrado a partir de 05/08/26 (bruto de R$ 2.570,52 para R$ 3.070,52), o que eleva o orçamento em R$ 2.500 no restante do ano.</t>
         </is>
       </c>
       <c r="D6" s="59" t="inlineStr">
         <is>
-          <t>Se lançarem o bruto contra o orçado de custo total, o TI vai mostrar uma economia falsa da mesma natureza.</t>
+          <t>Enquanto não for preenchida, a folha do TI aparece R$ 2.846,01/mês abaixo do orçado — economia que não existe. Atenção: o orçado de custo total (R$ 5.416,53) implica encargos de 111% sobre o bruto de R$ 2.570,52, bem acima do usual (67% a 80%) — vale conferir se o orçamento dele está folgado.</t>
         </is>
       </c>
       <c r="E6" s="59" t="inlineStr">
@@ -7165,31 +7386,31 @@
           <t>Cristiane + RH</t>
         </is>
       </c>
-      <c r="F6" s="60" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F6" s="57" t="inlineStr">
+        <is>
+          <t>PREENCHER</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B7" s="56" t="inlineStr">
         <is>
-          <t>Reajuste da Thamar — revisão orçamentária</t>
+          <t>Jonathan R$ 3.700/mês abaixo do contratado</t>
         </is>
       </c>
       <c r="C7" s="56" t="inlineStr">
         <is>
-          <t>Reajuste permanente de R$ 5.000 para R$ 5.500/mês, já em vigor desde mai/26. O planejado foi mantido em R$ 5.000 em mai–set (para o desvio ficar visível) e revisado para R$ 5.500 de out a dez.</t>
+          <t>Orçado R$ 10.000/mês, realizado R$ 6.300/mês em mai, jun e jul.</t>
         </is>
       </c>
       <c r="D7" s="56" t="inlineStr">
         <is>
-          <t>Desvio já incorrido de R$ 500/mês. Impacto de +R$ 1.500 no orçamento do restante do ano; o orçamento total sobe para R$ 395.852,68.</t>
+          <t>Maior desvio em reais de todo o orçamento: R$ 11.100 em três meses. Se o valor menor for o novo padrão, o planejado de ago a dez deve ser revisado para baixo — sobrariam R$ 18.500 no orçamento do TI.</t>
         </is>
       </c>
       <c r="E7" s="56" t="inlineStr">
@@ -7197,31 +7418,31 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F7" s="61" t="inlineStr">
-        <is>
-          <t>APLICADO</t>
+      <c r="F7" s="60" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B8" s="59" t="inlineStr">
         <is>
-          <t>Jusbrasil 30% acima do orçado</t>
+          <t>Elias Benedito zerado nos três meses</t>
         </is>
       </c>
       <c r="C8" s="59" t="inlineStr">
         <is>
-          <t>Orçado R$ 104,90/mês, realizado R$ 136,00/mês nos três meses.</t>
+          <t>Orçado R$ 1.065/mês como suporte técnico terceirizado, realizado R$ 0 em mai, jun e jul.</t>
         </is>
       </c>
       <c r="D8" s="59" t="inlineStr">
         <is>
-          <t>Menor desvio em reais (R$ 31,10/mês), mas o maior em percentual. Vale conferir se houve reajuste contratual ou mudança de plano.</t>
+          <t>Confirmar se o contrato segue ativo (acionamento sob demanda) ou se foi encerrado. Se encerrado, são R$ 8.520 a liberar no orçamento do ano.</t>
         </is>
       </c>
       <c r="E8" s="59" t="inlineStr">
@@ -7238,22 +7459,22 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="55" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B9" s="56" t="inlineStr">
         <is>
-          <t>Bonificação de ago/26 do Jurídico</t>
+          <t>Reajuste da Thamar — revisão orçamentária</t>
         </is>
       </c>
       <c r="C9" s="56" t="inlineStr">
         <is>
-          <t>Estão orçados R$ 10.293,60 em agosto e R$ 12.867,00 em dezembro. O realizado de agosto ainda não foi informado.</t>
+          <t>Reajuste permanente de R$ 5.000 para R$ 5.500/mês, já em vigor desde mai/26. O planejado foi mantido em R$ 5.000 em mai–set (para o desvio ficar visível) e revisado para R$ 5.500 de out a dez.</t>
         </is>
       </c>
       <c r="D9" s="56" t="inlineStr">
         <is>
-          <t>É a maior despesa isolada do Jurídico no segundo semestre. Sem confirmação, o acumulado de agosto fica distorcido.</t>
+          <t>Desvio já incorrido de R$ 500/mês. Impacto de +R$ 1.500 no orçamento do restante do ano; o orçamento total sobe para R$ 395.852,68.</t>
         </is>
       </c>
       <c r="E9" s="56" t="inlineStr">
@@ -7261,31 +7482,31 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F9" s="60" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F9" s="61" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B10" s="59" t="inlineStr">
         <is>
-          <t>Base de meses do time de TI</t>
+          <t>Jusbrasil 30% acima do orçado</t>
         </is>
       </c>
       <c r="C10" s="59" t="inlineStr">
         <is>
-          <t>A ficha original trazia a coluna TOTAL do TI em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9), enquanto o grid mensal tem 8 (mai–dez). Definido: vale mai–dez para todos.</t>
+          <t>Orçado R$ 104,90/mês, realizado R$ 136,00/mês nos três meses.</t>
         </is>
       </c>
       <c r="D10" s="59" t="inlineStr">
         <is>
-          <t>Orçamento de equipe do TI passou de R$ 167.778,30 para R$ 131.852,20 (−R$ 35.926,10). Total geral: R$ 394.352,68.</t>
+          <t>Menor desvio em reais (R$ 31,10/mês), mas o maior em percentual. Vale conferir se houve reajuste contratual ou mudança de plano.</t>
         </is>
       </c>
       <c r="E10" s="59" t="inlineStr">
@@ -7293,36 +7514,36 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F10" s="61" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
+      <c r="F10" s="60" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B11" s="56" t="inlineStr">
         <is>
-          <t>Origem do valor realizado</t>
+          <t>Bonificação de ago/26 do Jurídico</t>
         </is>
       </c>
       <c r="C11" s="56" t="inlineStr">
         <is>
-          <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto.</t>
+          <t>Estão orçados R$ 10.293,60 em agosto e R$ 12.867,00 em dezembro. O realizado de agosto ainda não foi informado.</t>
         </is>
       </c>
       <c r="D11" s="56" t="inlineStr">
         <is>
-          <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
+          <t>É a maior despesa isolada do Jurídico no segundo semestre. Sem confirmação, o acumulado de agosto fica distorcido.</t>
         </is>
       </c>
       <c r="E11" s="56" t="inlineStr">
         <is>
-          <t>Cristiane + Financeiro</t>
+          <t>Cristiane</t>
         </is>
       </c>
       <c r="F11" s="60" t="inlineStr">
@@ -7334,22 +7555,22 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" s="59" t="inlineStr">
         <is>
-          <t>Jusfy x Astrea</t>
+          <t>Base de meses do time de TI</t>
         </is>
       </c>
       <c r="C12" s="59" t="inlineStr">
         <is>
-          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
+          <t>A ficha original trazia a coluna TOTAL do TI em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9), enquanto o grid mensal tem 8 (mai–dez). Definido: vale mai–dez para todos.</t>
         </is>
       </c>
       <c r="D12" s="59" t="inlineStr">
         <is>
-          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado de ago a dez.</t>
+          <t>Orçamento de equipe do TI passou de R$ 167.778,30 para R$ 131.852,20 (−R$ 35.926,10). Total geral: R$ 394.352,68.</t>
         </is>
       </c>
       <c r="E12" s="59" t="inlineStr">
@@ -7366,27 +7587,27 @@
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" s="56" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos de TI</t>
+          <t>Origem do valor realizado</t>
         </is>
       </c>
       <c r="C13" s="56" t="inlineStr">
         <is>
-          <t>Backup (R$ 6.600), Adapta/IA (R$ 12.200), Antivírus (R$ 1.920) e Office 365 (R$ 3.000) estão marcados na ficha como 'não sei se seria administrativo'. Total: R$ 23.720.</t>
+          <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto.</t>
         </is>
       </c>
       <c r="D13" s="56" t="inlineStr">
         <is>
-          <t>Se são da empresa toda e ficam no centro de custo de TI, o TI carrega despesa que não é dele e aparece caro no comparativo.</t>
+          <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
         </is>
       </c>
       <c r="E13" s="56" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
+          <t>Cristiane + Financeiro</t>
         </is>
       </c>
       <c r="F13" s="60" t="inlineStr">
@@ -7398,22 +7619,22 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" s="59" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Jusfy x Astrea</t>
         </is>
       </c>
       <c r="C14" s="59" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 8 = R$ 22.400 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
         </is>
       </c>
       <c r="D14" s="59" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado de ago a dez.</t>
         </is>
       </c>
       <c r="E14" s="59" t="inlineStr">
@@ -7421,36 +7642,36 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F14" s="60" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F14" s="61" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" s="56" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Rateio dos softwares corporativos de TI</t>
         </is>
       </c>
       <c r="C15" s="56" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Backup (R$ 6.600), Adapta/IA (R$ 12.200), Antivírus (R$ 1.920) e Office 365 (R$ 3.000) estão marcados na ficha como 'não sei se seria administrativo'. Total: R$ 23.720.</t>
         </is>
       </c>
       <c r="D15" s="56" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Se são da empresa toda e ficam no centro de custo de TI, o TI carrega despesa que não é dele e aparece caro no comparativo.</t>
         </is>
       </c>
       <c r="E15" s="56" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Controladoria</t>
         </is>
       </c>
       <c r="F15" s="60" t="inlineStr">
@@ -7462,30 +7683,94 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="58" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
+        </is>
+      </c>
+      <c r="C16" s="59" t="inlineStr">
+        <is>
+          <t>R$ 2.800/mês × 8 = R$ 22.400 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+        </is>
+      </c>
+      <c r="D16" s="59" t="inlineStr">
+        <is>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+        </is>
+      </c>
+      <c r="E16" s="59" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F16" s="60" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B17" s="56" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E17" s="56" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F17" s="60" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="58" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>Critério de competência x caixa</t>
         </is>
       </c>
-      <c r="C16" s="59" t="inlineStr">
+      <c r="C18" s="59" t="inlineStr">
         <is>
           <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr">
+      <c r="D18" s="59" t="inlineStr">
         <is>
           <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
         </is>
       </c>
-      <c r="E16" s="59" t="inlineStr">
+      <c r="E18" s="59" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F16" s="60" t="inlineStr">
+      <c r="F18" s="60" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -4147,7 +4147,7 @@
       </c>
       <c r="E16" s="35" t="inlineStr">
         <is>
-          <t>INSS patronal, FGTS, provisões de 13º e férias, benefícios — PREENCHER</t>
+          <t>INSS patronal, FGTS, provisões de 13º e férias, benefícios — PREENCHER. O orçado de custo total (R$ 5.416,53) foi dimensionado com folga para um aumento futuro ainda não concedido — a folga não é economia estrutural.</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="C6" s="59" t="inlineStr">
         <is>
-          <t>A linha TI-E01B foi criada para receber os encargos e benefícios sobre o salário bruto, mesmo tratamento dado à Geovanna. Hoje está em branco. Aumento permanente de R$ 500 registrado a partir de 05/08/26 (bruto de R$ 2.570,52 para R$ 3.070,52), o que eleva o orçamento em R$ 2.500 no restante do ano.</t>
+          <t>A linha TI-E01B recebe os encargos e benefícios sobre o salário bruto, mesmo tratamento dado à Geovanna. Hoje está em branco. Brutos confirmados pela gestora: R$ 2.570,52 até jul/26 e R$ 3.070,52 a partir de 05/08/26.</t>
         </is>
       </c>
       <c r="D6" s="59" t="inlineStr">
         <is>
-          <t>Enquanto não for preenchida, a folha do TI aparece R$ 2.846,01/mês abaixo do orçado — economia que não existe. Atenção: o orçado de custo total (R$ 5.416,53) implica encargos de 111% sobre o bruto de R$ 2.570,52, bem acima do usual (67% a 80%) — vale conferir se o orçamento dele está folgado.</t>
+          <t>A folga do orçado NÃO é economia estrutural: o custo total de R$ 5.416,53 foi dimensionado prevendo um aumento maior, ainda não concedido. Com o bruto de agosto, a folga praticamente se esgota — a encargos de 67% o custo vai a R$ 5.127,77 (sobram R$ 288,76/mês) e a 80% passa a estourar o orçado. Preencher os encargos reais é o que define se ainda há margem.</t>
         </is>
       </c>
       <c r="E6" s="59" t="inlineStr">

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -4082,7 +4082,7 @@
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Analista Administrativo — aumento de R$ 2.570,52 para R$ 3.070,52 a partir de 05/08/26</t>
+          <t>Analista Administrativo — aumento de R$ 2.570,52 para R$ 3.070,52 a partir de 05/08/26, absorvido pela folga do envelope orçado (custo total segue R$ 5.416,525/mês)</t>
         </is>
       </c>
       <c r="F15" s="34" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="E16" s="35" t="inlineStr">
         <is>
-          <t>INSS patronal, FGTS, provisões de 13º e férias, benefícios — PREENCHER. O orçado de custo total (R$ 5.416,53) foi dimensionado com folga para um aumento futuro ainda não concedido — a folga não é economia estrutural.</t>
+          <t>INSS patronal, FGTS, provisões de 13º e férias, benefícios — PREENCHER. Planejado = resíduo do envelope de R$ 5.416,525/mês, que já previa o aumento. A folga não é economia estrutural: com o bruto de agosto ela quase se esgota.</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
@@ -4170,19 +4170,19 @@
         <v>2846.005</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>2846.005</v>
+        <v>2346.005</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>2846.005</v>
+        <v>2346.005</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>2846.005</v>
+        <v>2346.005</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>2846.005</v>
+        <v>2346.005</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>2846.005</v>
+        <v>2346.005</v>
       </c>
       <c r="P16" s="41">
         <f>SUM(H16:O16)</f>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$P$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -112,7 +112,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -169,6 +169,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -196,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -327,6 +332,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -481,12 +489,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Mensal'!$A$5:$A$12</f>
+              <f>'Evolução Mensal'!$A$5:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Mensal'!$I$5:$I$12</f>
+              <f>'Evolução Mensal'!$I$5:$I$16</f>
             </numRef>
           </val>
         </ser>
@@ -513,12 +521,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Mensal'!$A$5:$A$12</f>
+              <f>'Evolução Mensal'!$A$5:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Mensal'!$J$5:$J$12</f>
+              <f>'Evolução Mensal'!$J$5:$J$16</f>
             </numRef>
           </val>
         </ser>
@@ -603,12 +611,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Mensal'!$A$5:$A$12</f>
+              <f>'Evolução Mensal'!$A$5:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Mensal'!$F$5:$F$12</f>
+              <f>'Evolução Mensal'!$F$5:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -635,12 +643,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Evolução Mensal'!$A$5:$A$12</f>
+              <f>'Evolução Mensal'!$A$5:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Evolução Mensal'!$G$5:$G$12</f>
+              <f>'Evolução Mensal'!$G$5:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -1075,7 +1083,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Orçado 8 meses</t>
+          <t>Orçado do ano</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1121,7 +1129,7 @@
         </is>
       </c>
       <c r="C6" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"Jurídico",Planejado!$C$5:$C$27,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"Jurídico",Planejado!$C$5:$C$27,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="8">
@@ -1161,7 +1169,7 @@
         </is>
       </c>
       <c r="C7" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"Jurídico",Planejado!$C$5:$C$27,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"Jurídico",Planejado!$C$5:$C$27,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="8">
@@ -1201,7 +1209,7 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="12">
@@ -1241,7 +1249,7 @@
         </is>
       </c>
       <c r="C9" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"TI",Planejado!$C$5:$C$27,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"TI",Planejado!$C$5:$C$27,"Equipe")</f>
         <v/>
       </c>
       <c r="D9" s="8">
@@ -1281,7 +1289,7 @@
         </is>
       </c>
       <c r="C10" s="8">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"TI",Planejado!$C$5:$C$27,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"TI",Planejado!$C$5:$C$27,"Despesas")</f>
         <v/>
       </c>
       <c r="D10" s="8">
@@ -1321,7 +1329,7 @@
         </is>
       </c>
       <c r="C11" s="12">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="12">
@@ -1357,7 +1365,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr"/>
       <c r="C12" s="16">
-        <f>SUM(Planejado!$P$5:$P$27)</f>
+        <f>SUM(Planejado!$T$5:$T$27)</f>
         <v/>
       </c>
       <c r="D12" s="16">
@@ -1643,7 +1651,7 @@
         </is>
       </c>
       <c r="D3" s="26">
-        <f>MATCH($B$3,Planejado!$H$4:$O$4,0)</f>
+        <f>MATCH($B$3,Planejado!$H$4:$S$4,0)</f>
         <v/>
       </c>
     </row>
@@ -1751,11 +1759,11 @@
         <v/>
       </c>
       <c r="F6" s="30">
-        <f>INDEX(Planejado!$H5:$O5,$D$3)</f>
+        <f>INDEX(Planejado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>INDEX(Realizado!$H5:$O5,$D$3)</f>
+        <f>INDEX(Realizado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
       <c r="H6" s="30">
@@ -1763,11 +1771,11 @@
         <v/>
       </c>
       <c r="I6" s="30">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H5:$O5)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H5:$S5)</f>
         <v/>
       </c>
       <c r="J6" s="30">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H5:$O5)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H5:$S5)</f>
         <v/>
       </c>
       <c r="K6" s="30">
@@ -1791,7 +1799,7 @@
         <v/>
       </c>
       <c r="P6" s="33">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H5:$O5&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H5:$S5&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -1817,11 +1825,11 @@
         <v/>
       </c>
       <c r="F7" s="30">
-        <f>INDEX(Planejado!$H6:$O6,$D$3)</f>
+        <f>INDEX(Planejado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>INDEX(Realizado!$H6:$O6,$D$3)</f>
+        <f>INDEX(Realizado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
       <c r="H7" s="30">
@@ -1829,11 +1837,11 @@
         <v/>
       </c>
       <c r="I7" s="30">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H6:$O6)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H6:$S6)</f>
         <v/>
       </c>
       <c r="J7" s="30">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H6:$O6)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H6:$S6)</f>
         <v/>
       </c>
       <c r="K7" s="30">
@@ -1857,7 +1865,7 @@
         <v/>
       </c>
       <c r="P7" s="33">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H6:$O6&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H6:$S6&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -1883,11 +1891,11 @@
         <v/>
       </c>
       <c r="F8" s="30">
-        <f>INDEX(Planejado!$H7:$O7,$D$3)</f>
+        <f>INDEX(Planejado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>INDEX(Realizado!$H7:$O7,$D$3)</f>
+        <f>INDEX(Realizado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
       <c r="H8" s="30">
@@ -1895,11 +1903,11 @@
         <v/>
       </c>
       <c r="I8" s="30">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H7:$O7)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H7:$S7)</f>
         <v/>
       </c>
       <c r="J8" s="30">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H7:$O7)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H7:$S7)</f>
         <v/>
       </c>
       <c r="K8" s="30">
@@ -1923,7 +1931,7 @@
         <v/>
       </c>
       <c r="P8" s="33">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H7:$O7&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H7:$S7&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -1949,11 +1957,11 @@
         <v/>
       </c>
       <c r="F9" s="30">
-        <f>INDEX(Planejado!$H8:$O8,$D$3)</f>
+        <f>INDEX(Planejado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>INDEX(Realizado!$H8:$O8,$D$3)</f>
+        <f>INDEX(Realizado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
       <c r="H9" s="30">
@@ -1961,11 +1969,11 @@
         <v/>
       </c>
       <c r="I9" s="30">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H8:$O8)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H8:$S8)</f>
         <v/>
       </c>
       <c r="J9" s="30">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H8:$O8)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H8:$S8)</f>
         <v/>
       </c>
       <c r="K9" s="30">
@@ -1989,7 +1997,7 @@
         <v/>
       </c>
       <c r="P9" s="33">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H8:$O8&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H8:$S8&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2015,11 +2023,11 @@
         <v/>
       </c>
       <c r="F10" s="30">
-        <f>INDEX(Planejado!$H9:$O9,$D$3)</f>
+        <f>INDEX(Planejado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>INDEX(Realizado!$H9:$O9,$D$3)</f>
+        <f>INDEX(Realizado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
       <c r="H10" s="30">
@@ -2027,11 +2035,11 @@
         <v/>
       </c>
       <c r="I10" s="30">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H9:$O9)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H9:$S9)</f>
         <v/>
       </c>
       <c r="J10" s="30">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H9:$O9)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H9:$S9)</f>
         <v/>
       </c>
       <c r="K10" s="30">
@@ -2055,7 +2063,7 @@
         <v/>
       </c>
       <c r="P10" s="33">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H9:$O9&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H9:$S9&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2081,11 +2089,11 @@
         <v/>
       </c>
       <c r="F11" s="30">
-        <f>INDEX(Planejado!$H10:$O10,$D$3)</f>
+        <f>INDEX(Planejado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>INDEX(Realizado!$H10:$O10,$D$3)</f>
+        <f>INDEX(Realizado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
       <c r="H11" s="30">
@@ -2093,11 +2101,11 @@
         <v/>
       </c>
       <c r="I11" s="30">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H10:$O10)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H10:$S10)</f>
         <v/>
       </c>
       <c r="J11" s="30">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H10:$O10)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H10:$S10)</f>
         <v/>
       </c>
       <c r="K11" s="30">
@@ -2121,7 +2129,7 @@
         <v/>
       </c>
       <c r="P11" s="33">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H10:$O10&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H10:$S10&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2147,11 +2155,11 @@
         <v/>
       </c>
       <c r="F12" s="30">
-        <f>INDEX(Planejado!$H11:$O11,$D$3)</f>
+        <f>INDEX(Planejado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>INDEX(Realizado!$H11:$O11,$D$3)</f>
+        <f>INDEX(Realizado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
       <c r="H12" s="30">
@@ -2159,11 +2167,11 @@
         <v/>
       </c>
       <c r="I12" s="30">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H11:$O11)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H11:$S11)</f>
         <v/>
       </c>
       <c r="J12" s="30">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H11:$O11)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H11:$S11)</f>
         <v/>
       </c>
       <c r="K12" s="30">
@@ -2187,7 +2195,7 @@
         <v/>
       </c>
       <c r="P12" s="33">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H11:$O11&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H11:$S11&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2213,11 +2221,11 @@
         <v/>
       </c>
       <c r="F13" s="30">
-        <f>INDEX(Planejado!$H12:$O12,$D$3)</f>
+        <f>INDEX(Planejado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>INDEX(Realizado!$H12:$O12,$D$3)</f>
+        <f>INDEX(Realizado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
       <c r="H13" s="30">
@@ -2225,11 +2233,11 @@
         <v/>
       </c>
       <c r="I13" s="30">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H12:$O12)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H12:$S12)</f>
         <v/>
       </c>
       <c r="J13" s="30">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H12:$O12)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H12:$S12)</f>
         <v/>
       </c>
       <c r="K13" s="30">
@@ -2253,7 +2261,7 @@
         <v/>
       </c>
       <c r="P13" s="33">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H12:$O12&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H12:$S12&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2279,11 +2287,11 @@
         <v/>
       </c>
       <c r="F14" s="30">
-        <f>INDEX(Planejado!$H13:$O13,$D$3)</f>
+        <f>INDEX(Planejado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>INDEX(Realizado!$H13:$O13,$D$3)</f>
+        <f>INDEX(Realizado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
       <c r="H14" s="30">
@@ -2291,11 +2299,11 @@
         <v/>
       </c>
       <c r="I14" s="30">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H13:$O13)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H13:$S13)</f>
         <v/>
       </c>
       <c r="J14" s="30">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H13:$O13)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H13:$S13)</f>
         <v/>
       </c>
       <c r="K14" s="30">
@@ -2319,7 +2327,7 @@
         <v/>
       </c>
       <c r="P14" s="33">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H13:$O13&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H13:$S13&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2345,11 +2353,11 @@
         <v/>
       </c>
       <c r="F15" s="30">
-        <f>INDEX(Planejado!$H14:$O14,$D$3)</f>
+        <f>INDEX(Planejado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>INDEX(Realizado!$H14:$O14,$D$3)</f>
+        <f>INDEX(Realizado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
       <c r="H15" s="30">
@@ -2357,11 +2365,11 @@
         <v/>
       </c>
       <c r="I15" s="30">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H14:$O14)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H14:$S14)</f>
         <v/>
       </c>
       <c r="J15" s="30">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H14:$O14)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H14:$S14)</f>
         <v/>
       </c>
       <c r="K15" s="30">
@@ -2385,7 +2393,7 @@
         <v/>
       </c>
       <c r="P15" s="33">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H14:$O14&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H14:$S14&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2411,11 +2419,11 @@
         <v/>
       </c>
       <c r="F16" s="36">
-        <f>INDEX(Planejado!$H15:$O15,$D$3)</f>
+        <f>INDEX(Planejado!$H15:$S15,$D$3)</f>
         <v/>
       </c>
       <c r="G16" s="36">
-        <f>INDEX(Realizado!$H15:$O15,$D$3)</f>
+        <f>INDEX(Realizado!$H15:$S15,$D$3)</f>
         <v/>
       </c>
       <c r="H16" s="36">
@@ -2423,11 +2431,11 @@
         <v/>
       </c>
       <c r="I16" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H15:$O15)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H15:$S15)</f>
         <v/>
       </c>
       <c r="J16" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H15:$O15)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H15:$S15)</f>
         <v/>
       </c>
       <c r="K16" s="36">
@@ -2451,7 +2459,7 @@
         <v/>
       </c>
       <c r="P16" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H15:$O15&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H15:$S15&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2477,11 +2485,11 @@
         <v/>
       </c>
       <c r="F17" s="36">
-        <f>INDEX(Planejado!$H16:$O16,$D$3)</f>
+        <f>INDEX(Planejado!$H16:$S16,$D$3)</f>
         <v/>
       </c>
       <c r="G17" s="36">
-        <f>INDEX(Realizado!$H16:$O16,$D$3)</f>
+        <f>INDEX(Realizado!$H16:$S16,$D$3)</f>
         <v/>
       </c>
       <c r="H17" s="36">
@@ -2489,11 +2497,11 @@
         <v/>
       </c>
       <c r="I17" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H16:$O16)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H16:$S16)</f>
         <v/>
       </c>
       <c r="J17" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H16:$O16)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H16:$S16)</f>
         <v/>
       </c>
       <c r="K17" s="36">
@@ -2517,7 +2525,7 @@
         <v/>
       </c>
       <c r="P17" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H16:$O16&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H16:$S16&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2543,11 +2551,11 @@
         <v/>
       </c>
       <c r="F18" s="36">
-        <f>INDEX(Planejado!$H17:$O17,$D$3)</f>
+        <f>INDEX(Planejado!$H17:$S17,$D$3)</f>
         <v/>
       </c>
       <c r="G18" s="36">
-        <f>INDEX(Realizado!$H17:$O17,$D$3)</f>
+        <f>INDEX(Realizado!$H17:$S17,$D$3)</f>
         <v/>
       </c>
       <c r="H18" s="36">
@@ -2555,11 +2563,11 @@
         <v/>
       </c>
       <c r="I18" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H17:$O17)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H17:$S17)</f>
         <v/>
       </c>
       <c r="J18" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H17:$O17)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H17:$S17)</f>
         <v/>
       </c>
       <c r="K18" s="36">
@@ -2583,7 +2591,7 @@
         <v/>
       </c>
       <c r="P18" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H17:$O17&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H17:$S17&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2609,11 +2617,11 @@
         <v/>
       </c>
       <c r="F19" s="36">
-        <f>INDEX(Planejado!$H18:$O18,$D$3)</f>
+        <f>INDEX(Planejado!$H18:$S18,$D$3)</f>
         <v/>
       </c>
       <c r="G19" s="36">
-        <f>INDEX(Realizado!$H18:$O18,$D$3)</f>
+        <f>INDEX(Realizado!$H18:$S18,$D$3)</f>
         <v/>
       </c>
       <c r="H19" s="36">
@@ -2621,11 +2629,11 @@
         <v/>
       </c>
       <c r="I19" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H18:$O18)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H18:$S18)</f>
         <v/>
       </c>
       <c r="J19" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H18:$O18)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H18:$S18)</f>
         <v/>
       </c>
       <c r="K19" s="36">
@@ -2649,7 +2657,7 @@
         <v/>
       </c>
       <c r="P19" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H18:$O18&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H18:$S18&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2675,11 +2683,11 @@
         <v/>
       </c>
       <c r="F20" s="36">
-        <f>INDEX(Planejado!$H19:$O19,$D$3)</f>
+        <f>INDEX(Planejado!$H19:$S19,$D$3)</f>
         <v/>
       </c>
       <c r="G20" s="36">
-        <f>INDEX(Realizado!$H19:$O19,$D$3)</f>
+        <f>INDEX(Realizado!$H19:$S19,$D$3)</f>
         <v/>
       </c>
       <c r="H20" s="36">
@@ -2687,11 +2695,11 @@
         <v/>
       </c>
       <c r="I20" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H19:$O19)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H19:$S19)</f>
         <v/>
       </c>
       <c r="J20" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H19:$O19)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H19:$S19)</f>
         <v/>
       </c>
       <c r="K20" s="36">
@@ -2715,7 +2723,7 @@
         <v/>
       </c>
       <c r="P20" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H19:$O19&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H19:$S19&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2741,11 +2749,11 @@
         <v/>
       </c>
       <c r="F21" s="36">
-        <f>INDEX(Planejado!$H20:$O20,$D$3)</f>
+        <f>INDEX(Planejado!$H20:$S20,$D$3)</f>
         <v/>
       </c>
       <c r="G21" s="36">
-        <f>INDEX(Realizado!$H20:$O20,$D$3)</f>
+        <f>INDEX(Realizado!$H20:$S20,$D$3)</f>
         <v/>
       </c>
       <c r="H21" s="36">
@@ -2753,11 +2761,11 @@
         <v/>
       </c>
       <c r="I21" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H20:$O20)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H20:$S20)</f>
         <v/>
       </c>
       <c r="J21" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H20:$O20)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H20:$S20)</f>
         <v/>
       </c>
       <c r="K21" s="36">
@@ -2781,7 +2789,7 @@
         <v/>
       </c>
       <c r="P21" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H20:$O20&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H20:$S20&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2807,11 +2815,11 @@
         <v/>
       </c>
       <c r="F22" s="36">
-        <f>INDEX(Planejado!$H21:$O21,$D$3)</f>
+        <f>INDEX(Planejado!$H21:$S21,$D$3)</f>
         <v/>
       </c>
       <c r="G22" s="36">
-        <f>INDEX(Realizado!$H21:$O21,$D$3)</f>
+        <f>INDEX(Realizado!$H21:$S21,$D$3)</f>
         <v/>
       </c>
       <c r="H22" s="36">
@@ -2819,11 +2827,11 @@
         <v/>
       </c>
       <c r="I22" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H21:$O21)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H21:$S21)</f>
         <v/>
       </c>
       <c r="J22" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H21:$O21)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H21:$S21)</f>
         <v/>
       </c>
       <c r="K22" s="36">
@@ -2847,7 +2855,7 @@
         <v/>
       </c>
       <c r="P22" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H21:$O21&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H21:$S21&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2873,11 +2881,11 @@
         <v/>
       </c>
       <c r="F23" s="36">
-        <f>INDEX(Planejado!$H22:$O22,$D$3)</f>
+        <f>INDEX(Planejado!$H22:$S22,$D$3)</f>
         <v/>
       </c>
       <c r="G23" s="36">
-        <f>INDEX(Realizado!$H22:$O22,$D$3)</f>
+        <f>INDEX(Realizado!$H22:$S22,$D$3)</f>
         <v/>
       </c>
       <c r="H23" s="36">
@@ -2885,11 +2893,11 @@
         <v/>
       </c>
       <c r="I23" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H22:$O22)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H22:$S22)</f>
         <v/>
       </c>
       <c r="J23" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H22:$O22)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H22:$S22)</f>
         <v/>
       </c>
       <c r="K23" s="36">
@@ -2913,7 +2921,7 @@
         <v/>
       </c>
       <c r="P23" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H22:$O22&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H22:$S22&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -2939,11 +2947,11 @@
         <v/>
       </c>
       <c r="F24" s="36">
-        <f>INDEX(Planejado!$H23:$O23,$D$3)</f>
+        <f>INDEX(Planejado!$H23:$S23,$D$3)</f>
         <v/>
       </c>
       <c r="G24" s="36">
-        <f>INDEX(Realizado!$H23:$O23,$D$3)</f>
+        <f>INDEX(Realizado!$H23:$S23,$D$3)</f>
         <v/>
       </c>
       <c r="H24" s="36">
@@ -2951,11 +2959,11 @@
         <v/>
       </c>
       <c r="I24" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H23:$O23)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H23:$S23)</f>
         <v/>
       </c>
       <c r="J24" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H23:$O23)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H23:$S23)</f>
         <v/>
       </c>
       <c r="K24" s="36">
@@ -2979,7 +2987,7 @@
         <v/>
       </c>
       <c r="P24" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H23:$O23&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H23:$S23&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -3005,11 +3013,11 @@
         <v/>
       </c>
       <c r="F25" s="36">
-        <f>INDEX(Planejado!$H24:$O24,$D$3)</f>
+        <f>INDEX(Planejado!$H24:$S24,$D$3)</f>
         <v/>
       </c>
       <c r="G25" s="36">
-        <f>INDEX(Realizado!$H24:$O24,$D$3)</f>
+        <f>INDEX(Realizado!$H24:$S24,$D$3)</f>
         <v/>
       </c>
       <c r="H25" s="36">
@@ -3017,11 +3025,11 @@
         <v/>
       </c>
       <c r="I25" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H24:$O24)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H24:$S24)</f>
         <v/>
       </c>
       <c r="J25" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H24:$O24)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H24:$S24)</f>
         <v/>
       </c>
       <c r="K25" s="36">
@@ -3045,7 +3053,7 @@
         <v/>
       </c>
       <c r="P25" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H24:$O24&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H24:$S24&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -3071,11 +3079,11 @@
         <v/>
       </c>
       <c r="F26" s="36">
-        <f>INDEX(Planejado!$H25:$O25,$D$3)</f>
+        <f>INDEX(Planejado!$H25:$S25,$D$3)</f>
         <v/>
       </c>
       <c r="G26" s="36">
-        <f>INDEX(Realizado!$H25:$O25,$D$3)</f>
+        <f>INDEX(Realizado!$H25:$S25,$D$3)</f>
         <v/>
       </c>
       <c r="H26" s="36">
@@ -3083,11 +3091,11 @@
         <v/>
       </c>
       <c r="I26" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H25:$O25)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H25:$S25)</f>
         <v/>
       </c>
       <c r="J26" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H25:$O25)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H25:$S25)</f>
         <v/>
       </c>
       <c r="K26" s="36">
@@ -3111,7 +3119,7 @@
         <v/>
       </c>
       <c r="P26" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H25:$O25&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H25:$S25&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -3137,11 +3145,11 @@
         <v/>
       </c>
       <c r="F27" s="36">
-        <f>INDEX(Planejado!$H26:$O26,$D$3)</f>
+        <f>INDEX(Planejado!$H26:$S26,$D$3)</f>
         <v/>
       </c>
       <c r="G27" s="36">
-        <f>INDEX(Realizado!$H26:$O26,$D$3)</f>
+        <f>INDEX(Realizado!$H26:$S26,$D$3)</f>
         <v/>
       </c>
       <c r="H27" s="36">
@@ -3149,11 +3157,11 @@
         <v/>
       </c>
       <c r="I27" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H26:$O26)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H26:$S26)</f>
         <v/>
       </c>
       <c r="J27" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H26:$O26)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H26:$S26)</f>
         <v/>
       </c>
       <c r="K27" s="36">
@@ -3177,7 +3185,7 @@
         <v/>
       </c>
       <c r="P27" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H26:$O26&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H26:$S26&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -3203,11 +3211,11 @@
         <v/>
       </c>
       <c r="F28" s="36">
-        <f>INDEX(Planejado!$H27:$O27,$D$3)</f>
+        <f>INDEX(Planejado!$H27:$S27,$D$3)</f>
         <v/>
       </c>
       <c r="G28" s="36">
-        <f>INDEX(Realizado!$H27:$O27,$D$3)</f>
+        <f>INDEX(Realizado!$H27:$S27,$D$3)</f>
         <v/>
       </c>
       <c r="H28" s="36">
@@ -3215,11 +3223,11 @@
         <v/>
       </c>
       <c r="I28" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$O$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H27:$O27)</f>
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H27:$S27)</f>
         <v/>
       </c>
       <c r="J28" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H27:$O27)</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H27:$S27)</f>
         <v/>
       </c>
       <c r="K28" s="36">
@@ -3243,7 +3251,7 @@
         <v/>
       </c>
       <c r="P28" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$O$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H27:$O27&lt;&gt;""))</f>
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H27:$S27&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
@@ -3315,7 +3323,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Mai/26,Jun/26,Jul/26,Ago/26,Set/26,Out/26,Nov/26,Dez/26"</formula1>
+      <formula1>"Jan/26,Fev/26,Mar/26,Abr/26,Mai/26,Jun/26,Jul/26,Ago/26,Set/26,Out/26,Nov/26,Dez/26"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3328,7 +3336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3338,15 +3346,19 @@
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3359,7 +3371,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Base: maio a dezembro/2026 (8 meses). CLT com encargos de folha + benefícios inclusos. Esta aba é a referência — altere aqui apenas se o orçamento for oficialmente revisado.</t>
+          <t>Base: janeiro a dezembro/2026 (12 meses). CLT com encargos de folha + benefícios inclusos. Esta aba é a referência — altere aqui apenas se o orçamento for oficialmente revisado.</t>
         </is>
       </c>
     </row>
@@ -3401,47 +3413,67 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="S4" s="6" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL 8 MESES</t>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL DO ANO</t>
         </is>
       </c>
     </row>
@@ -3505,8 +3537,20 @@
       <c r="O5" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="P5" s="41">
-        <f>SUM(H5:O5)</f>
+      <c r="P5" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q5" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R5" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="S5" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T5" s="41">
+        <f>SUM(H5:S5)</f>
         <v/>
       </c>
     </row>
@@ -3570,8 +3614,20 @@
       <c r="O6" s="30" t="n">
         <v>2886.91</v>
       </c>
-      <c r="P6" s="41">
-        <f>SUM(H6:O6)</f>
+      <c r="P6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="Q6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="R6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="S6" s="30" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="T6" s="41">
+        <f>SUM(H6:S6)</f>
         <v/>
       </c>
     </row>
@@ -3635,8 +3691,20 @@
       <c r="O7" s="30" t="n">
         <v>1938.605</v>
       </c>
-      <c r="P7" s="41">
-        <f>SUM(H7:O7)</f>
+      <c r="P7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="Q7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="R7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="S7" s="30" t="n">
+        <v>1938.605</v>
+      </c>
+      <c r="T7" s="41">
+        <f>SUM(H7:S7)</f>
         <v/>
       </c>
     </row>
@@ -3692,16 +3760,28 @@
         <v>5000</v>
       </c>
       <c r="M8" s="30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N8" s="30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="O8" s="30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P8" s="30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q8" s="30" t="n">
         <v>5500</v>
       </c>
-      <c r="N8" s="30" t="n">
+      <c r="R8" s="30" t="n">
         <v>5500</v>
       </c>
-      <c r="O8" s="30" t="n">
+      <c r="S8" s="30" t="n">
         <v>5500</v>
       </c>
-      <c r="P8" s="41">
-        <f>SUM(H8:O8)</f>
+      <c r="T8" s="41">
+        <f>SUM(H8:S8)</f>
         <v/>
       </c>
     </row>
@@ -3761,8 +3841,20 @@
       <c r="O9" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="P9" s="41">
-        <f>SUM(H9:O9)</f>
+      <c r="P9" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="S9" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" s="41">
+        <f>SUM(H9:S9)</f>
         <v/>
       </c>
     </row>
@@ -3818,8 +3910,20 @@
       <c r="O10" s="30" t="n">
         <v>104.9</v>
       </c>
-      <c r="P10" s="41">
-        <f>SUM(H10:O10)</f>
+      <c r="P10" s="30" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="Q10" s="30" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="R10" s="30" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="S10" s="30" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="T10" s="41">
+        <f>SUM(H10:S10)</f>
         <v/>
       </c>
     </row>
@@ -3846,7 +3950,7 @@
       </c>
       <c r="E11" s="29" t="inlineStr">
         <is>
-          <t>Previsto sair quando o Jusfy for homologado — definir mês de corte</t>
+          <t>Cancelado — realizado zerado desde mai/26</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr"/>
@@ -3879,8 +3983,20 @@
       <c r="O11" s="30" t="n">
         <v>112.07</v>
       </c>
-      <c r="P11" s="41">
-        <f>SUM(H11:O11)</f>
+      <c r="P11" s="30" t="n">
+        <v>112.07</v>
+      </c>
+      <c r="Q11" s="30" t="n">
+        <v>112.07</v>
+      </c>
+      <c r="R11" s="30" t="n">
+        <v>112.07</v>
+      </c>
+      <c r="S11" s="30" t="n">
+        <v>112.07</v>
+      </c>
+      <c r="T11" s="41">
+        <f>SUM(H11:S11)</f>
         <v/>
       </c>
     </row>
@@ -3936,8 +4052,20 @@
       <c r="O12" s="30" t="n">
         <v>1030</v>
       </c>
-      <c r="P12" s="41">
-        <f>SUM(H12:O12)</f>
+      <c r="P12" s="30" t="n">
+        <v>1030</v>
+      </c>
+      <c r="Q12" s="30" t="n">
+        <v>1030</v>
+      </c>
+      <c r="R12" s="30" t="n">
+        <v>1030</v>
+      </c>
+      <c r="S12" s="30" t="n">
+        <v>1030</v>
+      </c>
+      <c r="T12" s="41">
+        <f>SUM(H12:S12)</f>
         <v/>
       </c>
     </row>
@@ -3993,8 +4121,20 @@
       <c r="O13" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="P13" s="41">
-        <f>SUM(H13:O13)</f>
+      <c r="P13" s="30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q13" s="30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="R13" s="30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S13" s="30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T13" s="41">
+        <f>SUM(H13:S13)</f>
         <v/>
       </c>
     </row>
@@ -4021,7 +4161,7 @@
       </c>
       <c r="E14" s="29" t="inlineStr">
         <is>
-          <t>Participação em projetos e atingimento de resultados</t>
+          <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
         </is>
       </c>
       <c r="F14" s="28" t="inlineStr"/>
@@ -4040,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>10293.6</v>
+        <v>0</v>
       </c>
       <c r="L14" s="30" t="n">
         <v>0</v>
@@ -4052,10 +4192,22 @@
         <v>0</v>
       </c>
       <c r="O14" s="30" t="n">
+        <v>10293.6</v>
+      </c>
+      <c r="P14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="30" t="n">
         <v>12867</v>
       </c>
-      <c r="P14" s="41">
-        <f>SUM(H14:O14)</f>
+      <c r="T14" s="41">
+        <f>SUM(H14:S14)</f>
         <v/>
       </c>
     </row>
@@ -4105,22 +4257,34 @@
         <v>2570.52</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>3070.52</v>
+        <v>2570.52</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>3070.52</v>
+        <v>2570.52</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>3070.52</v>
+        <v>2570.52</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>3070.52</v>
+        <v>2570.52</v>
       </c>
       <c r="O15" s="36" t="n">
         <v>3070.52</v>
       </c>
-      <c r="P15" s="41">
-        <f>SUM(H15:O15)</f>
+      <c r="P15" s="36" t="n">
+        <v>3070.52</v>
+      </c>
+      <c r="Q15" s="36" t="n">
+        <v>3070.52</v>
+      </c>
+      <c r="R15" s="36" t="n">
+        <v>3070.52</v>
+      </c>
+      <c r="S15" s="36" t="n">
+        <v>3070.52</v>
+      </c>
+      <c r="T15" s="41">
+        <f>SUM(H15:S15)</f>
         <v/>
       </c>
     </row>
@@ -4170,22 +4334,34 @@
         <v>2846.005</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>2346.005</v>
+        <v>2846.005</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>2346.005</v>
+        <v>2846.005</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>2346.005</v>
+        <v>2846.005</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>2346.005</v>
+        <v>2846.005</v>
       </c>
       <c r="O16" s="36" t="n">
         <v>2346.005</v>
       </c>
-      <c r="P16" s="41">
-        <f>SUM(H16:O16)</f>
+      <c r="P16" s="36" t="n">
+        <v>2346.005</v>
+      </c>
+      <c r="Q16" s="36" t="n">
+        <v>2346.005</v>
+      </c>
+      <c r="R16" s="36" t="n">
+        <v>2346.005</v>
+      </c>
+      <c r="S16" s="36" t="n">
+        <v>2346.005</v>
+      </c>
+      <c r="T16" s="41">
+        <f>SUM(H16:S16)</f>
         <v/>
       </c>
     </row>
@@ -4249,8 +4425,20 @@
       <c r="O17" s="36" t="n">
         <v>1065</v>
       </c>
-      <c r="P17" s="41">
-        <f>SUM(H17:O17)</f>
+      <c r="P17" s="36" t="n">
+        <v>1065</v>
+      </c>
+      <c r="Q17" s="36" t="n">
+        <v>1065</v>
+      </c>
+      <c r="R17" s="36" t="n">
+        <v>1065</v>
+      </c>
+      <c r="S17" s="36" t="n">
+        <v>1065</v>
+      </c>
+      <c r="T17" s="41">
+        <f>SUM(H17:S17)</f>
         <v/>
       </c>
     </row>
@@ -4277,7 +4465,7 @@
       </c>
       <c r="E18" s="35" t="inlineStr">
         <is>
-          <t>Consultor</t>
+          <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
@@ -4291,13 +4479,13 @@
         </is>
       </c>
       <c r="H18" s="36" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="K18" s="36" t="n">
         <v>10000</v>
@@ -4314,8 +4502,20 @@
       <c r="O18" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="P18" s="41">
-        <f>SUM(H18:O18)</f>
+      <c r="P18" s="36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q18" s="36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R18" s="36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="S18" s="36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="T18" s="41">
+        <f>SUM(H18:S18)</f>
         <v/>
       </c>
     </row>
@@ -4375,8 +4575,20 @@
       <c r="O19" s="36" t="n">
         <v>810</v>
       </c>
-      <c r="P19" s="41">
-        <f>SUM(H19:O19)</f>
+      <c r="P19" s="36" t="n">
+        <v>810</v>
+      </c>
+      <c r="Q19" s="36" t="n">
+        <v>810</v>
+      </c>
+      <c r="R19" s="36" t="n">
+        <v>810</v>
+      </c>
+      <c r="S19" s="36" t="n">
+        <v>810</v>
+      </c>
+      <c r="T19" s="41">
+        <f>SUM(H19:S19)</f>
         <v/>
       </c>
     </row>
@@ -4436,8 +4648,20 @@
       <c r="O20" s="36" t="n">
         <v>825</v>
       </c>
-      <c r="P20" s="41">
-        <f>SUM(H20:O20)</f>
+      <c r="P20" s="36" t="n">
+        <v>825</v>
+      </c>
+      <c r="Q20" s="36" t="n">
+        <v>825</v>
+      </c>
+      <c r="R20" s="36" t="n">
+        <v>825</v>
+      </c>
+      <c r="S20" s="36" t="n">
+        <v>825</v>
+      </c>
+      <c r="T20" s="41">
+        <f>SUM(H20:S20)</f>
         <v/>
       </c>
     </row>
@@ -4480,16 +4704,16 @@
         <v>1300</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="N21" s="36" t="n">
         <v>1600</v>
@@ -4497,8 +4721,20 @@
       <c r="O21" s="36" t="n">
         <v>1600</v>
       </c>
-      <c r="P21" s="41">
-        <f>SUM(H21:O21)</f>
+      <c r="P21" s="36" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q21" s="36" t="n">
+        <v>1600</v>
+      </c>
+      <c r="R21" s="36" t="n">
+        <v>1600</v>
+      </c>
+      <c r="S21" s="36" t="n">
+        <v>1600</v>
+      </c>
+      <c r="T21" s="41">
+        <f>SUM(H21:S21)</f>
         <v/>
       </c>
     </row>
@@ -4558,8 +4794,20 @@
       <c r="O22" s="36" t="n">
         <v>240</v>
       </c>
-      <c r="P22" s="41">
-        <f>SUM(H22:O22)</f>
+      <c r="P22" s="36" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q22" s="36" t="n">
+        <v>240</v>
+      </c>
+      <c r="R22" s="36" t="n">
+        <v>240</v>
+      </c>
+      <c r="S22" s="36" t="n">
+        <v>240</v>
+      </c>
+      <c r="T22" s="41">
+        <f>SUM(H22:S22)</f>
         <v/>
       </c>
     </row>
@@ -4619,8 +4867,20 @@
       <c r="O23" s="36" t="n">
         <v>375</v>
       </c>
-      <c r="P23" s="41">
-        <f>SUM(H23:O23)</f>
+      <c r="P23" s="36" t="n">
+        <v>375</v>
+      </c>
+      <c r="Q23" s="36" t="n">
+        <v>375</v>
+      </c>
+      <c r="R23" s="36" t="n">
+        <v>375</v>
+      </c>
+      <c r="S23" s="36" t="n">
+        <v>375</v>
+      </c>
+      <c r="T23" s="41">
+        <f>SUM(H23:S23)</f>
         <v/>
       </c>
     </row>
@@ -4680,8 +4940,20 @@
       <c r="O24" s="36" t="n">
         <v>2800</v>
       </c>
-      <c r="P24" s="41">
-        <f>SUM(H24:O24)</f>
+      <c r="P24" s="36" t="n">
+        <v>2800</v>
+      </c>
+      <c r="Q24" s="36" t="n">
+        <v>2800</v>
+      </c>
+      <c r="R24" s="36" t="n">
+        <v>2800</v>
+      </c>
+      <c r="S24" s="36" t="n">
+        <v>2800</v>
+      </c>
+      <c r="T24" s="41">
+        <f>SUM(H24:S24)</f>
         <v/>
       </c>
     </row>
@@ -4737,8 +5009,20 @@
       <c r="O25" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="P25" s="41">
-        <f>SUM(H25:O25)</f>
+      <c r="P25" s="36" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q25" s="36" t="n">
+        <v>200</v>
+      </c>
+      <c r="R25" s="36" t="n">
+        <v>200</v>
+      </c>
+      <c r="S25" s="36" t="n">
+        <v>200</v>
+      </c>
+      <c r="T25" s="41">
+        <f>SUM(H25:S25)</f>
         <v/>
       </c>
     </row>
@@ -4794,8 +5078,20 @@
       <c r="O26" s="36" t="n">
         <v>220</v>
       </c>
-      <c r="P26" s="41">
-        <f>SUM(H26:O26)</f>
+      <c r="P26" s="36" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q26" s="36" t="n">
+        <v>220</v>
+      </c>
+      <c r="R26" s="36" t="n">
+        <v>220</v>
+      </c>
+      <c r="S26" s="36" t="n">
+        <v>220</v>
+      </c>
+      <c r="T26" s="41">
+        <f>SUM(H26:S26)</f>
         <v/>
       </c>
     </row>
@@ -4822,7 +5118,7 @@
       </c>
       <c r="E27" s="35" t="inlineStr">
         <is>
-          <t>Cumprimento de prazos e participação em projetos</t>
+          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
         </is>
       </c>
       <c r="F27" s="34" t="inlineStr"/>
@@ -4841,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="36" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="L27" s="36" t="n">
         <v>0</v>
@@ -4853,10 +5149,22 @@
         <v>0</v>
       </c>
       <c r="O27" s="36" t="n">
+        <v>2400</v>
+      </c>
+      <c r="P27" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="36" t="n">
         <v>3600</v>
       </c>
-      <c r="P27" s="41">
-        <f>SUM(H27:O27)</f>
+      <c r="T27" s="41">
+        <f>SUM(H27:S27)</f>
         <v/>
       </c>
     </row>
@@ -4908,12 +5216,28 @@
         <f>SUM(P5:P27)</f>
         <v/>
       </c>
+      <c r="Q28" s="16">
+        <f>SUM(Q5:Q27)</f>
+        <v/>
+      </c>
+      <c r="R28" s="16">
+        <f>SUM(R5:R27)</f>
+        <v/>
+      </c>
+      <c r="S28" s="16">
+        <f>SUM(S5:S27)</f>
+        <v/>
+      </c>
+      <c r="T28" s="16">
+        <f>SUM(T5:T27)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P27"/>
+  <autoFilter ref="A4:T27"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4925,7 +5249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4935,17 +5259,21 @@
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5000,55 +5328,75 @@
       </c>
       <c r="H4" s="42" t="inlineStr">
         <is>
+          <t>Jan/26</t>
+        </is>
+      </c>
+      <c r="I4" s="42" t="inlineStr">
+        <is>
+          <t>Fev/26</t>
+        </is>
+      </c>
+      <c r="J4" s="42" t="inlineStr">
+        <is>
+          <t>Mar/26</t>
+        </is>
+      </c>
+      <c r="K4" s="42" t="inlineStr">
+        <is>
+          <t>Abr/26</t>
+        </is>
+      </c>
+      <c r="L4" s="42" t="inlineStr">
+        <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="I4" s="42" t="inlineStr">
+      <c r="M4" s="42" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="J4" s="42" t="inlineStr">
+      <c r="N4" s="42" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="K4" s="42" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="L4" s="42" t="inlineStr">
+      <c r="P4" s="42" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="M4" s="42" t="inlineStr">
+      <c r="Q4" s="42" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="N4" s="42" t="inlineStr">
+      <c r="R4" s="42" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="O4" s="42" t="inlineStr">
+      <c r="S4" s="42" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="P4" s="42" t="inlineStr">
+      <c r="T4" s="42" t="inlineStr">
         <is>
           <t>TOTAL REALIZADO</t>
         </is>
       </c>
-      <c r="Q4" s="42" t="inlineStr">
+      <c r="U4" s="42" t="inlineStr">
         <is>
           <t>Fonte do dado</t>
         </is>
       </c>
-      <c r="R4" s="42" t="inlineStr">
+      <c r="V4" s="42" t="inlineStr">
         <is>
           <t>Observações do mês</t>
         </is>
@@ -5083,30 +5431,30 @@
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="H5" s="45" t="n">
+      <c r="H5" s="45" t="n"/>
+      <c r="I5" s="45" t="n"/>
+      <c r="J5" s="45" t="n"/>
+      <c r="K5" s="45" t="n"/>
+      <c r="L5" s="45" t="n">
         <v>8818</v>
       </c>
-      <c r="I5" s="45" t="n">
+      <c r="M5" s="45" t="n">
         <v>8818</v>
       </c>
-      <c r="J5" s="45" t="n">
+      <c r="N5" s="45" t="n">
         <v>8818</v>
       </c>
-      <c r="K5" s="45" t="n"/>
-      <c r="L5" s="45" t="n"/>
-      <c r="M5" s="45" t="n"/>
-      <c r="N5" s="45" t="n"/>
       <c r="O5" s="45" t="n"/>
-      <c r="P5" s="41">
-        <f>SUM(H5:O5)</f>
-        <v/>
-      </c>
-      <c r="Q5" s="46" t="inlineStr">
+      <c r="T5" s="41">
+        <f>SUM(H5:S5)</f>
+        <v/>
+      </c>
+      <c r="U5" s="46" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="R5" s="46" t="inlineStr">
+      <c r="V5" s="46" t="inlineStr">
         <is>
           <t>Valor cheio da nota — R$ 1.182/mês abaixo do contratado</t>
         </is>
@@ -5141,30 +5489,30 @@
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="H6" s="45" t="n">
+      <c r="H6" s="45" t="n"/>
+      <c r="I6" s="45" t="n"/>
+      <c r="J6" s="45" t="n"/>
+      <c r="K6" s="45" t="n"/>
+      <c r="L6" s="45" t="n">
         <v>2886.91</v>
       </c>
-      <c r="I6" s="45" t="n">
+      <c r="M6" s="45" t="n">
         <v>2886.91</v>
       </c>
-      <c r="J6" s="45" t="n">
+      <c r="N6" s="45" t="n">
         <v>2886.91</v>
       </c>
-      <c r="K6" s="45" t="n"/>
-      <c r="L6" s="45" t="n"/>
-      <c r="M6" s="45" t="n"/>
-      <c r="N6" s="45" t="n"/>
       <c r="O6" s="45" t="n"/>
-      <c r="P6" s="41">
-        <f>SUM(H6:O6)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="46" t="inlineStr">
+      <c r="T6" s="41">
+        <f>SUM(H6:S6)</f>
+        <v/>
+      </c>
+      <c r="U6" s="46" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="R6" s="46" t="inlineStr">
+      <c r="V6" s="46" t="inlineStr">
         <is>
           <t>Salário bruto</t>
         </is>
@@ -5207,12 +5555,12 @@
       <c r="M7" s="45" t="n"/>
       <c r="N7" s="45" t="n"/>
       <c r="O7" s="45" t="n"/>
-      <c r="P7" s="41">
-        <f>SUM(H7:O7)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="46" t="n"/>
-      <c r="R7" s="46" t="inlineStr">
+      <c r="T7" s="41">
+        <f>SUM(H7:S7)</f>
+        <v/>
+      </c>
+      <c r="U7" s="46" t="n"/>
+      <c r="V7" s="46" t="inlineStr">
         <is>
           <t>PREENCHER — encargos e benefícios sobre o bruto</t>
         </is>
@@ -5247,30 +5595,30 @@
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="45" t="n"/>
+      <c r="I8" s="45" t="n"/>
+      <c r="J8" s="45" t="n"/>
+      <c r="K8" s="45" t="n"/>
+      <c r="L8" s="45" t="n">
         <v>5500</v>
       </c>
-      <c r="I8" s="45" t="n">
+      <c r="M8" s="45" t="n">
         <v>5500</v>
       </c>
-      <c r="J8" s="45" t="n">
+      <c r="N8" s="45" t="n">
         <v>5500</v>
       </c>
-      <c r="K8" s="45" t="n"/>
-      <c r="L8" s="45" t="n"/>
-      <c r="M8" s="45" t="n"/>
-      <c r="N8" s="45" t="n"/>
       <c r="O8" s="45" t="n"/>
-      <c r="P8" s="41">
-        <f>SUM(H8:O8)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="46" t="inlineStr">
+      <c r="T8" s="41">
+        <f>SUM(H8:S8)</f>
+        <v/>
+      </c>
+      <c r="U8" s="46" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="R8" s="46" t="inlineStr">
+      <c r="V8" s="46" t="inlineStr">
         <is>
           <t>Reajuste permanente aplicado desde mai/26</t>
         </is>
@@ -5305,30 +5653,30 @@
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="H9" s="45" t="n">
+      <c r="H9" s="45" t="n"/>
+      <c r="I9" s="45" t="n"/>
+      <c r="J9" s="45" t="n"/>
+      <c r="K9" s="45" t="n"/>
+      <c r="L9" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="45" t="n">
+      <c r="M9" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="45" t="n">
+      <c r="N9" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="45" t="n"/>
-      <c r="L9" s="45" t="n"/>
-      <c r="M9" s="45" t="n"/>
-      <c r="N9" s="45" t="n"/>
       <c r="O9" s="45" t="n"/>
-      <c r="P9" s="41">
-        <f>SUM(H9:O9)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="46" t="inlineStr">
+      <c r="T9" s="41">
+        <f>SUM(H9:S9)</f>
+        <v/>
+      </c>
+      <c r="U9" s="46" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="R9" s="46" t="inlineStr">
+      <c r="V9" s="46" t="inlineStr">
         <is>
           <t>Ainda não iniciado — sem cobrança</t>
         </is>
@@ -5363,30 +5711,30 @@
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="H10" s="45" t="n">
+      <c r="H10" s="45" t="n"/>
+      <c r="I10" s="45" t="n"/>
+      <c r="J10" s="45" t="n"/>
+      <c r="K10" s="45" t="n"/>
+      <c r="L10" s="45" t="n">
         <v>136</v>
       </c>
-      <c r="I10" s="45" t="n">
+      <c r="M10" s="45" t="n">
         <v>136</v>
       </c>
-      <c r="J10" s="45" t="n">
+      <c r="N10" s="45" t="n">
         <v>136</v>
       </c>
-      <c r="K10" s="45" t="n"/>
-      <c r="L10" s="45" t="n"/>
-      <c r="M10" s="45" t="n"/>
-      <c r="N10" s="45" t="n"/>
       <c r="O10" s="45" t="n"/>
-      <c r="P10" s="41">
-        <f>SUM(H10:O10)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="46" t="inlineStr">
+      <c r="T10" s="41">
+        <f>SUM(H10:S10)</f>
+        <v/>
+      </c>
+      <c r="U10" s="46" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="R10" s="46" t="inlineStr">
+      <c r="V10" s="46" t="inlineStr">
         <is>
           <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
         </is>
@@ -5421,30 +5769,30 @@
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="H11" s="45" t="n">
+      <c r="H11" s="45" t="n"/>
+      <c r="I11" s="45" t="n"/>
+      <c r="J11" s="45" t="n"/>
+      <c r="K11" s="45" t="n"/>
+      <c r="L11" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="45" t="n">
+      <c r="M11" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="45" t="n">
+      <c r="N11" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="45" t="n"/>
-      <c r="L11" s="45" t="n"/>
-      <c r="M11" s="45" t="n"/>
-      <c r="N11" s="45" t="n"/>
       <c r="O11" s="45" t="n"/>
-      <c r="P11" s="41">
-        <f>SUM(H11:O11)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="46" t="inlineStr">
+      <c r="T11" s="41">
+        <f>SUM(H11:S11)</f>
+        <v/>
+      </c>
+      <c r="U11" s="46" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="R11" s="46" t="inlineStr">
+      <c r="V11" s="46" t="inlineStr">
         <is>
           <t>Cancelado — sem cobrança</t>
         </is>
@@ -5479,30 +5827,30 @@
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="45" t="n"/>
+      <c r="I12" s="45" t="n"/>
+      <c r="J12" s="45" t="n"/>
+      <c r="K12" s="45" t="n"/>
+      <c r="L12" s="45" t="n">
         <v>970</v>
       </c>
-      <c r="I12" s="45" t="n">
+      <c r="M12" s="45" t="n">
         <v>970</v>
       </c>
-      <c r="J12" s="45" t="n">
+      <c r="N12" s="45" t="n">
         <v>970</v>
       </c>
-      <c r="K12" s="45" t="n"/>
-      <c r="L12" s="45" t="n"/>
-      <c r="M12" s="45" t="n"/>
-      <c r="N12" s="45" t="n"/>
       <c r="O12" s="45" t="n"/>
-      <c r="P12" s="41">
-        <f>SUM(H12:O12)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="46" t="inlineStr">
+      <c r="T12" s="41">
+        <f>SUM(H12:S12)</f>
+        <v/>
+      </c>
+      <c r="U12" s="46" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="R12" s="46" t="n"/>
+      <c r="V12" s="46" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="43">
@@ -5533,30 +5881,30 @@
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="H13" s="45" t="n">
+      <c r="H13" s="45" t="n"/>
+      <c r="I13" s="45" t="n"/>
+      <c r="J13" s="45" t="n"/>
+      <c r="K13" s="45" t="n"/>
+      <c r="L13" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="45" t="n">
+      <c r="M13" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="45" t="n">
+      <c r="N13" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="45" t="n"/>
-      <c r="L13" s="45" t="n"/>
-      <c r="M13" s="45" t="n"/>
-      <c r="N13" s="45" t="n"/>
       <c r="O13" s="45" t="n"/>
-      <c r="P13" s="41">
-        <f>SUM(H13:O13)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="46" t="inlineStr">
+      <c r="T13" s="41">
+        <f>SUM(H13:S13)</f>
+        <v/>
+      </c>
+      <c r="U13" s="46" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="R13" s="46" t="inlineStr">
+      <c r="V13" s="46" t="inlineStr">
         <is>
           <t>Sem gasto no período</t>
         </is>
@@ -5599,12 +5947,12 @@
       <c r="M14" s="45" t="n"/>
       <c r="N14" s="45" t="n"/>
       <c r="O14" s="45" t="n"/>
-      <c r="P14" s="41">
-        <f>SUM(H14:O14)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="46" t="n"/>
-      <c r="R14" s="46" t="inlineStr">
+      <c r="T14" s="41">
+        <f>SUM(H14:S14)</f>
+        <v/>
+      </c>
+      <c r="U14" s="46" t="n"/>
+      <c r="V14" s="46" t="inlineStr">
         <is>
           <t>Bonificação de ago/26 a confirmar</t>
         </is>
@@ -5639,30 +5987,30 @@
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="H15" s="45" t="n">
+      <c r="H15" s="45" t="n"/>
+      <c r="I15" s="45" t="n"/>
+      <c r="J15" s="45" t="n"/>
+      <c r="K15" s="45" t="n"/>
+      <c r="L15" s="45" t="n">
         <v>2570.52</v>
       </c>
-      <c r="I15" s="45" t="n">
+      <c r="M15" s="45" t="n">
         <v>2570.52</v>
       </c>
-      <c r="J15" s="45" t="n">
+      <c r="N15" s="45" t="n">
         <v>2570.52</v>
       </c>
-      <c r="K15" s="45" t="n"/>
-      <c r="L15" s="45" t="n"/>
-      <c r="M15" s="45" t="n"/>
-      <c r="N15" s="45" t="n"/>
       <c r="O15" s="45" t="n"/>
-      <c r="P15" s="41">
-        <f>SUM(H15:O15)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="46" t="inlineStr">
+      <c r="T15" s="41">
+        <f>SUM(H15:S15)</f>
+        <v/>
+      </c>
+      <c r="U15" s="46" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="R15" s="46" t="inlineStr">
+      <c r="V15" s="46" t="inlineStr">
         <is>
           <t>Salário bruto vigente até jul; sobe para R$ 3.070,52 em ago</t>
         </is>
@@ -5705,12 +6053,12 @@
       <c r="M16" s="45" t="n"/>
       <c r="N16" s="45" t="n"/>
       <c r="O16" s="45" t="n"/>
-      <c r="P16" s="41">
-        <f>SUM(H16:O16)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="46" t="n"/>
-      <c r="R16" s="46" t="inlineStr">
+      <c r="T16" s="41">
+        <f>SUM(H16:S16)</f>
+        <v/>
+      </c>
+      <c r="U16" s="46" t="n"/>
+      <c r="V16" s="46" t="inlineStr">
         <is>
           <t>PREENCHER — encargos e benefícios sobre o bruto</t>
         </is>
@@ -5745,30 +6093,30 @@
         <f>Planejado!G17</f>
         <v/>
       </c>
-      <c r="H17" s="45" t="n">
+      <c r="H17" s="45" t="n"/>
+      <c r="I17" s="45" t="n"/>
+      <c r="J17" s="45" t="n"/>
+      <c r="K17" s="45" t="n"/>
+      <c r="L17" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="45" t="n">
+      <c r="M17" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="45" t="n">
+      <c r="N17" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="45" t="n"/>
-      <c r="L17" s="45" t="n"/>
-      <c r="M17" s="45" t="n"/>
-      <c r="N17" s="45" t="n"/>
       <c r="O17" s="45" t="n"/>
-      <c r="P17" s="41">
-        <f>SUM(H17:O17)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="46" t="inlineStr">
+      <c r="T17" s="41">
+        <f>SUM(H17:S17)</f>
+        <v/>
+      </c>
+      <c r="U17" s="46" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="R17" s="46" t="inlineStr">
+      <c r="V17" s="46" t="inlineStr">
         <is>
           <t>Sem acionamento no período — confirmar se o contrato segue ativo</t>
         </is>
@@ -5803,30 +6151,30 @@
         <f>Planejado!G18</f>
         <v/>
       </c>
-      <c r="H18" s="45" t="n">
+      <c r="H18" s="45" t="n"/>
+      <c r="I18" s="45" t="n"/>
+      <c r="J18" s="45" t="n"/>
+      <c r="K18" s="45" t="n"/>
+      <c r="L18" s="45" t="n">
         <v>6300</v>
       </c>
-      <c r="I18" s="45" t="n">
+      <c r="M18" s="45" t="n">
         <v>6300</v>
       </c>
-      <c r="J18" s="45" t="n">
+      <c r="N18" s="45" t="n">
         <v>6300</v>
       </c>
-      <c r="K18" s="45" t="n"/>
-      <c r="L18" s="45" t="n"/>
-      <c r="M18" s="45" t="n"/>
-      <c r="N18" s="45" t="n"/>
       <c r="O18" s="45" t="n"/>
-      <c r="P18" s="41">
-        <f>SUM(H18:O18)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="46" t="inlineStr">
+      <c r="T18" s="41">
+        <f>SUM(H18:S18)</f>
+        <v/>
+      </c>
+      <c r="U18" s="46" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="R18" s="46" t="inlineStr">
+      <c r="V18" s="46" t="inlineStr">
         <is>
           <t>R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
         </is>
@@ -5869,12 +6217,12 @@
       <c r="M19" s="45" t="n"/>
       <c r="N19" s="45" t="n"/>
       <c r="O19" s="45" t="n"/>
-      <c r="P19" s="41">
-        <f>SUM(H19:O19)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="46" t="n"/>
-      <c r="R19" s="46" t="n"/>
+      <c r="T19" s="41">
+        <f>SUM(H19:S19)</f>
+        <v/>
+      </c>
+      <c r="U19" s="46" t="n"/>
+      <c r="V19" s="46" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="43">
@@ -5913,12 +6261,12 @@
       <c r="M20" s="45" t="n"/>
       <c r="N20" s="45" t="n"/>
       <c r="O20" s="45" t="n"/>
-      <c r="P20" s="41">
-        <f>SUM(H20:O20)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="46" t="n"/>
-      <c r="R20" s="46" t="n"/>
+      <c r="T20" s="41">
+        <f>SUM(H20:S20)</f>
+        <v/>
+      </c>
+      <c r="U20" s="46" t="n"/>
+      <c r="V20" s="46" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="43">
@@ -5957,12 +6305,12 @@
       <c r="M21" s="45" t="n"/>
       <c r="N21" s="45" t="n"/>
       <c r="O21" s="45" t="n"/>
-      <c r="P21" s="41">
-        <f>SUM(H21:O21)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="46" t="n"/>
-      <c r="R21" s="46" t="n"/>
+      <c r="T21" s="41">
+        <f>SUM(H21:S21)</f>
+        <v/>
+      </c>
+      <c r="U21" s="46" t="n"/>
+      <c r="V21" s="46" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="43">
@@ -6001,12 +6349,12 @@
       <c r="M22" s="45" t="n"/>
       <c r="N22" s="45" t="n"/>
       <c r="O22" s="45" t="n"/>
-      <c r="P22" s="41">
-        <f>SUM(H22:O22)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="46" t="n"/>
-      <c r="R22" s="46" t="n"/>
+      <c r="T22" s="41">
+        <f>SUM(H22:S22)</f>
+        <v/>
+      </c>
+      <c r="U22" s="46" t="n"/>
+      <c r="V22" s="46" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="43">
@@ -6045,12 +6393,12 @@
       <c r="M23" s="45" t="n"/>
       <c r="N23" s="45" t="n"/>
       <c r="O23" s="45" t="n"/>
-      <c r="P23" s="41">
-        <f>SUM(H23:O23)</f>
-        <v/>
-      </c>
-      <c r="Q23" s="46" t="n"/>
-      <c r="R23" s="46" t="n"/>
+      <c r="T23" s="41">
+        <f>SUM(H23:S23)</f>
+        <v/>
+      </c>
+      <c r="U23" s="46" t="n"/>
+      <c r="V23" s="46" t="n"/>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="43">
@@ -6089,12 +6437,12 @@
       <c r="M24" s="45" t="n"/>
       <c r="N24" s="45" t="n"/>
       <c r="O24" s="45" t="n"/>
-      <c r="P24" s="41">
-        <f>SUM(H24:O24)</f>
-        <v/>
-      </c>
-      <c r="Q24" s="46" t="n"/>
-      <c r="R24" s="46" t="n"/>
+      <c r="T24" s="41">
+        <f>SUM(H24:S24)</f>
+        <v/>
+      </c>
+      <c r="U24" s="46" t="n"/>
+      <c r="V24" s="46" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="43">
@@ -6133,12 +6481,12 @@
       <c r="M25" s="45" t="n"/>
       <c r="N25" s="45" t="n"/>
       <c r="O25" s="45" t="n"/>
-      <c r="P25" s="41">
-        <f>SUM(H25:O25)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="46" t="n"/>
-      <c r="R25" s="46" t="n"/>
+      <c r="T25" s="41">
+        <f>SUM(H25:S25)</f>
+        <v/>
+      </c>
+      <c r="U25" s="46" t="n"/>
+      <c r="V25" s="46" t="n"/>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="43">
@@ -6177,12 +6525,12 @@
       <c r="M26" s="45" t="n"/>
       <c r="N26" s="45" t="n"/>
       <c r="O26" s="45" t="n"/>
-      <c r="P26" s="41">
-        <f>SUM(H26:O26)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="46" t="n"/>
-      <c r="R26" s="46" t="n"/>
+      <c r="T26" s="41">
+        <f>SUM(H26:S26)</f>
+        <v/>
+      </c>
+      <c r="U26" s="46" t="n"/>
+      <c r="V26" s="46" t="n"/>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="43">
@@ -6221,12 +6569,12 @@
       <c r="M27" s="45" t="n"/>
       <c r="N27" s="45" t="n"/>
       <c r="O27" s="45" t="n"/>
-      <c r="P27" s="41">
-        <f>SUM(H27:O27)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="46" t="n"/>
-      <c r="R27" s="46" t="n"/>
+      <c r="T27" s="41">
+        <f>SUM(H27:S27)</f>
+        <v/>
+      </c>
+      <c r="U27" s="46" t="n"/>
+      <c r="V27" s="46" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="47" t="inlineStr">
@@ -6276,13 +6624,29 @@
         <f>SUM(P5:P27)</f>
         <v/>
       </c>
-      <c r="Q28" s="47" t="n"/>
-      <c r="R28" s="47" t="n"/>
+      <c r="Q28" s="48">
+        <f>SUM(Q5:Q27)</f>
+        <v/>
+      </c>
+      <c r="R28" s="48">
+        <f>SUM(R5:R27)</f>
+        <v/>
+      </c>
+      <c r="S28" s="48">
+        <f>SUM(S5:S27)</f>
+        <v/>
+      </c>
+      <c r="T28" s="48">
+        <f>SUM(T5:T27)</f>
+        <v/>
+      </c>
+      <c r="U28" s="47" t="n"/>
+      <c r="V28" s="47" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6294,7 +6658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6378,7 +6742,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="49" t="inlineStr">
         <is>
-          <t>Mai/26</t>
+          <t>Jan/26</t>
         </is>
       </c>
       <c r="B5" s="30">
@@ -6421,7 +6785,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="50" t="inlineStr">
         <is>
-          <t>Jun/26</t>
+          <t>Fev/26</t>
         </is>
       </c>
       <c r="B6" s="36">
@@ -6464,7 +6828,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="49" t="inlineStr">
         <is>
-          <t>Jul/26</t>
+          <t>Mar/26</t>
         </is>
       </c>
       <c r="B7" s="30">
@@ -6507,7 +6871,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="50" t="inlineStr">
         <is>
-          <t>Ago/26</t>
+          <t>Abr/26</t>
         </is>
       </c>
       <c r="B8" s="36">
@@ -6550,7 +6914,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="49" t="inlineStr">
         <is>
-          <t>Set/26</t>
+          <t>Mai/26</t>
         </is>
       </c>
       <c r="B9" s="30">
@@ -6593,7 +6957,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="50" t="inlineStr">
         <is>
-          <t>Out/26</t>
+          <t>Jun/26</t>
         </is>
       </c>
       <c r="B10" s="36">
@@ -6636,7 +7000,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="49" t="inlineStr">
         <is>
-          <t>Nov/26</t>
+          <t>Jul/26</t>
         </is>
       </c>
       <c r="B11" s="30">
@@ -6679,7 +7043,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="50" t="inlineStr">
         <is>
-          <t>Dez/26</t>
+          <t>Ago/26</t>
         </is>
       </c>
       <c r="B12" s="36">
@@ -6719,49 +7083,221 @@
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>Set/26</t>
+        </is>
+      </c>
+      <c r="B13" s="30">
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C13" s="30">
+        <f>SUMIFS(Realizado!$P$5:$P$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D13" s="30">
+        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E13" s="30">
+        <f>SUMIFS(Realizado!$P$5:$P$27,Realizado!$B$5:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F13" s="30">
+        <f>B13+D13</f>
+        <v/>
+      </c>
+      <c r="G13" s="30">
+        <f>C13+E13</f>
+        <v/>
+      </c>
+      <c r="H13" s="30">
+        <f>G13-F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="30">
+        <f>SUM($F$5:F13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="30">
+        <f>SUM($G$5:G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="50" t="inlineStr">
+        <is>
+          <t>Out/26</t>
+        </is>
+      </c>
+      <c r="B14" s="36">
+        <f>SUMIFS(Planejado!$Q$5:$Q$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C14" s="36">
+        <f>SUMIFS(Realizado!$Q$5:$Q$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D14" s="36">
+        <f>SUMIFS(Planejado!$Q$5:$Q$27,Planejado!$B$5:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E14" s="36">
+        <f>SUMIFS(Realizado!$Q$5:$Q$27,Realizado!$B$5:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F14" s="36">
+        <f>B14+D14</f>
+        <v/>
+      </c>
+      <c r="G14" s="36">
+        <f>C14+E14</f>
+        <v/>
+      </c>
+      <c r="H14" s="36">
+        <f>G14-F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="36">
+        <f>SUM($F$5:F14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="36">
+        <f>SUM($G$5:G14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>Nov/26</t>
+        </is>
+      </c>
+      <c r="B15" s="30">
+        <f>SUMIFS(Planejado!$R$5:$R$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C15" s="30">
+        <f>SUMIFS(Realizado!$R$5:$R$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D15" s="30">
+        <f>SUMIFS(Planejado!$R$5:$R$27,Planejado!$B$5:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E15" s="30">
+        <f>SUMIFS(Realizado!$R$5:$R$27,Realizado!$B$5:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F15" s="30">
+        <f>B15+D15</f>
+        <v/>
+      </c>
+      <c r="G15" s="30">
+        <f>C15+E15</f>
+        <v/>
+      </c>
+      <c r="H15" s="30">
+        <f>G15-F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="30">
+        <f>SUM($F$5:F15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="30">
+        <f>SUM($G$5:G15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>Dez/26</t>
+        </is>
+      </c>
+      <c r="B16" s="36">
+        <f>SUMIFS(Planejado!$S$5:$S$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="C16" s="36">
+        <f>SUMIFS(Realizado!$S$5:$S$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <v/>
+      </c>
+      <c r="D16" s="36">
+        <f>SUMIFS(Planejado!$S$5:$S$27,Planejado!$B$5:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="E16" s="36">
+        <f>SUMIFS(Realizado!$S$5:$S$27,Realizado!$B$5:$B$27,"TI")</f>
+        <v/>
+      </c>
+      <c r="F16" s="36">
+        <f>B16+D16</f>
+        <v/>
+      </c>
+      <c r="G16" s="36">
+        <f>C16+E16</f>
+        <v/>
+      </c>
+      <c r="H16" s="36">
+        <f>G16-F16</f>
+        <v/>
+      </c>
+      <c r="I16" s="36">
+        <f>SUM($F$5:F16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="36">
+        <f>SUM($G$5:G16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="16">
-        <f>SUM(B5:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="16">
-        <f>SUM(C5:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="16">
-        <f>SUM(D5:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>SUM(E5:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>SUM(F5:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="16">
-        <f>SUM(G5:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="16">
-        <f>SUM(H5:H12)</f>
-        <v/>
-      </c>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
+      <c r="B17" s="16">
+        <f>SUM(B5:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="16">
+        <f>SUM(C5:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="16">
+        <f>SUM(D5:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="16">
+        <f>SUM(E5:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="16">
+        <f>SUM(F5:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="16">
+        <f>SUM(G5:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="16">
+        <f>SUM(H5:H16)</f>
+        <v/>
+      </c>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H12">
+  <conditionalFormatting sqref="H5:H16">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -6857,7 +7393,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Orçado 8 meses</t>
+          <t>Orçado do ano</t>
         </is>
       </c>
     </row>
@@ -6900,7 +7436,7 @@
         <v/>
       </c>
       <c r="J5" s="30">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A5)</f>
         <v/>
       </c>
     </row>
@@ -6943,7 +7479,7 @@
         <v/>
       </c>
       <c r="J6" s="36">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A6)</f>
         <v/>
       </c>
     </row>
@@ -6986,7 +7522,7 @@
         <v/>
       </c>
       <c r="J7" s="30">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A7)</f>
         <v/>
       </c>
     </row>
@@ -7029,7 +7565,7 @@
         <v/>
       </c>
       <c r="J8" s="36">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A8)</f>
         <v/>
       </c>
     </row>
@@ -7072,7 +7608,7 @@
         <v/>
       </c>
       <c r="J9" s="30">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A9)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A9)</f>
         <v/>
       </c>
     </row>
@@ -7115,7 +7651,7 @@
         <v/>
       </c>
       <c r="J10" s="36">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A10)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A10)</f>
         <v/>
       </c>
     </row>
@@ -7158,7 +7694,7 @@
         <v/>
       </c>
       <c r="J11" s="30">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A11)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A11)</f>
         <v/>
       </c>
     </row>
@@ -7201,7 +7737,7 @@
         <v/>
       </c>
       <c r="J12" s="36">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$G$5:$G$27,$A12)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A12)</f>
         <v/>
       </c>
     </row>
@@ -7271,7 +7807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7560,17 +8096,17 @@
       </c>
       <c r="B12" s="59" t="inlineStr">
         <is>
-          <t>Base de meses do time de TI</t>
+          <t>Base de meses — reconciliada com a ficha original</t>
         </is>
       </c>
       <c r="C12" s="59" t="inlineStr">
         <is>
-          <t>A ficha original trazia a coluna TOTAL do TI em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9), enquanto o grid mensal tem 8 (mai–dez). Definido: vale mai–dez para todos.</t>
+          <t>A ficha trazia a coluna TOTAL do TI digitada à mão em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9) enquanto o grid mensal tinha só 8 colunas. Com o período estendido para jan–dez, os três totais batem exatamente: R$ 64.998,30 + R$ 12.780,00 + R$ 90.000,00 = R$ 167.778,30, o valor original da ficha. Não era erro de digitação — era o grid que estava incompleto.</t>
         </is>
       </c>
       <c r="D12" s="59" t="inlineStr">
         <is>
-          <t>Orçamento de equipe do TI passou de R$ 167.778,30 para R$ 131.852,20 (−R$ 35.926,10). Total geral: R$ 394.352,68.</t>
+          <t>Equipe de TI volta ao valor original de R$ 167.778,30. Jonathan lançado com entrada em abr/26 (9 meses), que é o que explica os R$ 90.000 da ficha.</t>
         </is>
       </c>
       <c r="E12" s="59" t="inlineStr">
@@ -7587,54 +8123,54 @@
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B13" s="56" t="inlineStr">
         <is>
-          <t>Origem do valor realizado</t>
+          <t>Planejado de jan a abr — CONFERIR</t>
         </is>
       </c>
       <c r="C13" s="56" t="inlineStr">
         <is>
-          <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto.</t>
+          <t>O 1º quadrimestre foi preenchido replicando os valores mensais já conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
         </is>
       </c>
       <c r="D13" s="56" t="inlineStr">
         <is>
-          <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
+          <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
         </is>
       </c>
       <c r="E13" s="56" t="inlineStr">
         <is>
-          <t>Cristiane + Financeiro</t>
-        </is>
-      </c>
-      <c r="F13" s="60" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F13" s="62" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B14" s="59" t="inlineStr">
         <is>
-          <t>Jusfy x Astrea</t>
+          <t>Realizado de jan a abr — A LANÇAR</t>
         </is>
       </c>
       <c r="C14" s="59" t="inlineStr">
         <is>
-          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
+          <t>As colunas de jan a abr estão em branco na aba Realizado. Só mai, jun e jul foram informados.</t>
         </is>
       </c>
       <c r="D14" s="59" t="inlineStr">
         <is>
-          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado de ago a dez.</t>
+          <t>São 4 dos 7 meses já fechados do ano. Sem eles o acumulado e o Painel refletem menos da metade do período decorrido.</t>
         </is>
       </c>
       <c r="E14" s="59" t="inlineStr">
@@ -7642,36 +8178,36 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F14" s="61" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
+      <c r="F14" s="57" t="inlineStr">
+        <is>
+          <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B15" s="56" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos de TI</t>
+          <t>Origem do valor realizado</t>
         </is>
       </c>
       <c r="C15" s="56" t="inlineStr">
         <is>
-          <t>Backup (R$ 6.600), Adapta/IA (R$ 12.200), Antivírus (R$ 1.920) e Office 365 (R$ 3.000) estão marcados na ficha como 'não sei se seria administrativo'. Total: R$ 23.720.</t>
+          <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto.</t>
         </is>
       </c>
       <c r="D15" s="56" t="inlineStr">
         <is>
-          <t>Se são da empresa toda e ficam no centro de custo de TI, o TI carrega despesa que não é dele e aparece caro no comparativo.</t>
+          <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
         </is>
       </c>
       <c r="E15" s="56" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
+          <t>Cristiane + Financeiro</t>
         </is>
       </c>
       <c r="F15" s="60" t="inlineStr">
@@ -7683,22 +8219,22 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" s="59" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Jusfy x Astrea</t>
         </is>
       </c>
       <c r="C16" s="59" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 8 = R$ 22.400 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
         </is>
       </c>
       <c r="D16" s="59" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado de ago a dez.</t>
         </is>
       </c>
       <c r="E16" s="59" t="inlineStr">
@@ -7706,36 +8242,36 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F16" s="60" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F16" s="61" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" s="56" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Rateio dos softwares corporativos de TI</t>
         </is>
       </c>
       <c r="C17" s="56" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Backup (R$ 6.600), Adapta/IA (R$ 12.200), Antivírus (R$ 1.920) e Office 365 (R$ 3.000) estão marcados na ficha como 'não sei se seria administrativo'. Total: R$ 23.720.</t>
         </is>
       </c>
       <c r="D17" s="56" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Se são da empresa toda e ficam no centro de custo de TI, o TI carrega despesa que não é dele e aparece caro no comparativo.</t>
         </is>
       </c>
       <c r="E17" s="56" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Controladoria</t>
         </is>
       </c>
       <c r="F17" s="60" t="inlineStr">
@@ -7747,30 +8283,94 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="58" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B18" s="59" t="inlineStr">
+        <is>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
+        </is>
+      </c>
+      <c r="C18" s="59" t="inlineStr">
+        <is>
+          <t>R$ 2.800/mês × 8 = R$ 22.400 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+        </is>
+      </c>
+      <c r="D18" s="59" t="inlineStr">
+        <is>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+        </is>
+      </c>
+      <c r="E18" s="59" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F18" s="60" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="56" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C19" s="56" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D19" s="56" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E19" s="56" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F19" s="60" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="58" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>Critério de competência x caixa</t>
         </is>
       </c>
-      <c r="C18" s="59" t="inlineStr">
+      <c r="C20" s="59" t="inlineStr">
         <is>
           <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
         </is>
       </c>
-      <c r="D18" s="59" t="inlineStr">
+      <c r="D20" s="59" t="inlineStr">
         <is>
           <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
         </is>
       </c>
-      <c r="E18" s="59" t="inlineStr">
+      <c r="E20" s="59" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F18" s="60" t="inlineStr">
+      <c r="F20" s="60" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -7821,60 +8421,60 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="62" t="inlineStr">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="63" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>Abra a aba REALIZADO e preencha apenas as células amarelas do mês que fechou. Se o item não teve gasto no mês, digite 0 — deixar em branco significa 'ainda não lancei'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="62" t="inlineStr">
+      <c r="A6" s="63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="63" t="inlineStr">
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>Preencha a coluna 'Fonte do dado' (ex.: relatório do financeiro, nota fiscal, extrato do cartão) para o número ser auditável depois.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="62" t="inlineStr">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="62" t="inlineStr">
+      <c r="A8" s="63" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="63" t="inlineStr">
+      <c r="B8" s="64" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="62" t="inlineStr">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="63" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -7889,60 +8489,60 @@
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="62" t="inlineStr">
+      <c r="A12" s="63" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="63" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="62" t="inlineStr">
+      <c r="A13" s="63" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="63" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="62" t="inlineStr">
+      <c r="A14" s="63" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="63" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="62" t="inlineStr">
+      <c r="A15" s="63" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="63" t="inlineStr">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="62" t="inlineStr">
+      <c r="A16" s="63" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="63" t="inlineStr">
+      <c r="B16" s="64" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -7957,36 +8557,36 @@
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="62" t="inlineStr">
+      <c r="A19" s="63" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="63" t="inlineStr">
+      <c r="B19" s="64" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="62" t="inlineStr">
+      <c r="A20" s="63" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="63" t="inlineStr">
+      <c r="B20" s="64" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="62" t="inlineStr">
+      <c r="A21" s="63" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="63" t="inlineStr">
+      <c r="B21" s="64" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -161,12 +161,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1043,7 +1043,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PAINEL EXECUTIVO  —  Orçamento 2026 Jurídico e TI</t>
+          <t>PAINEL EXECUTIVO  —  Orçamento 2026  JURÍDICO E TI</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ORÇAMENTO PLANEJADO 2026  —  Jurídico e TI</t>
+          <t>ORÇAMENTO PLANEJADO 2026  —  JURÍDICO E TI</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REALIZADO 2026  —  Jurídico e TI</t>
+          <t>REALIZADO 2026  —  JURÍDICO E TI</t>
         </is>
       </c>
     </row>
@@ -6662,15 +6662,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -7320,15 +7320,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -7786,8 +7786,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H12">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
@@ -7807,7 +7807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="C5" s="56" t="inlineStr">
         <is>
-          <t>A linha JUR-E02B foi criada para receber os encargos e benefícios sobre o salário bruto (INSS patronal, FGTS, provisões de 13º e férias, VT/VR, plano de saúde). Hoje está em branco em mai, jun e jul.</t>
+          <t>A linha JUR-E02B recebe os encargos e benefícios sobre o salário bruto (INSS patronal, FGTS, provisões de 13º e férias, VT/VR, plano de saúde). Hoje está em branco.</t>
         </is>
       </c>
       <c r="D5" s="56" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="C6" s="59" t="inlineStr">
         <is>
-          <t>A linha TI-E01B recebe os encargos e benefícios sobre o salário bruto, mesmo tratamento dado à Geovanna. Hoje está em branco. Brutos confirmados pela gestora: R$ 2.570,52 até jul/26 e R$ 3.070,52 a partir de 05/08/26.</t>
+          <t>A linha TI-E01B recebe os encargos e benefícios sobre o salário bruto, mesmo tratamento dado à Geovanna. Hoje está em branco. Brutos confirmados pela gestora: R$ 2.570,52 até jul/26 e R$ 3.070,52 a partir de 05/08/26. O envelope orçado permanece em R$ 5.416,525/mês — o aumento foi absorvido pela folga, não somado ao orçamento.</t>
         </is>
       </c>
       <c r="D6" s="59" t="inlineStr">
         <is>
-          <t>A folga do orçado NÃO é economia estrutural: o custo total de R$ 5.416,53 foi dimensionado prevendo um aumento maior, ainda não concedido. Com o bruto de agosto, a folga praticamente se esgota — a encargos de 67% o custo vai a R$ 5.127,77 (sobram R$ 288,76/mês) e a 80% passa a estourar o orçado. Preencher os encargos reais é o que define se ainda há margem.</t>
+          <t>A folga do orçado NÃO é economia estrutural: o custo total foi dimensionado prevendo um aumento maior, ainda não concedido. Com o bruto de agosto, o orçado de encargos (R$ 2.346,01) equivale a 76% sobre o bruto — dentro da faixa normal (67% a 80%), então pode sobrar ou estourar.</t>
         </is>
       </c>
       <c r="E6" s="59" t="inlineStr">
@@ -7931,22 +7931,22 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="55" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B7" s="56" t="inlineStr">
         <is>
-          <t>Jonathan R$ 3.700/mês abaixo do contratado</t>
+          <t>Reajuste da Thamar — revisão orçamentária</t>
         </is>
       </c>
       <c r="C7" s="56" t="inlineStr">
         <is>
-          <t>Orçado R$ 10.000/mês, realizado R$ 6.300/mês em mai, jun e jul.</t>
+          <t>Reajuste permanente de R$ 5.000 para R$ 5.500/mês, em vigor desde mai/26. O planejado foi mantido em R$ 5.000 nos meses já realizados (para o desvio ficar visível) e revisado para R$ 5.500 de out a dez.</t>
         </is>
       </c>
       <c r="D7" s="56" t="inlineStr">
         <is>
-          <t>Maior desvio em reais de todo o orçamento: R$ 11.100 em três meses. Se o valor menor for o novo padrão, o planejado de ago a dez deve ser revisado para baixo — sobrariam R$ 18.500 no orçamento do TI.</t>
+          <t>Desvio já incorrido de R$ 500/mês. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
         </is>
       </c>
       <c r="E7" s="56" t="inlineStr">
@@ -7956,29 +7956,29 @@
       </c>
       <c r="F7" s="60" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="58" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B8" s="59" t="inlineStr">
         <is>
-          <t>Elias Benedito zerado nos três meses</t>
+          <t>Jusbrasil 30% acima do orçado</t>
         </is>
       </c>
       <c r="C8" s="59" t="inlineStr">
         <is>
-          <t>Orçado R$ 1.065/mês como suporte técnico terceirizado, realizado R$ 0 em mai, jun e jul.</t>
+          <t>Orçado R$ 104,90/mês, realizado R$ 136,00/mês em mai, jun e jul.</t>
         </is>
       </c>
       <c r="D8" s="59" t="inlineStr">
         <is>
-          <t>Confirmar se o contrato segue ativo (acionamento sob demanda) ou se foi encerrado. Se encerrado, são R$ 8.520 a liberar no orçamento do ano.</t>
+          <t>Menor desvio em reais (R$ 31,10/mês), mas o maior em percentual. Vale conferir se houve reajuste contratual ou mudança de plano.</t>
         </is>
       </c>
       <c r="E8" s="59" t="inlineStr">
@@ -7986,7 +7986,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F8" s="60" t="inlineStr">
+      <c r="F8" s="61" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -7995,22 +7995,22 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B9" s="56" t="inlineStr">
         <is>
-          <t>Reajuste da Thamar — revisão orçamentária</t>
+          <t>Bonificação de ago/26 do Jurídico</t>
         </is>
       </c>
       <c r="C9" s="56" t="inlineStr">
         <is>
-          <t>Reajuste permanente de R$ 5.000 para R$ 5.500/mês, já em vigor desde mai/26. O planejado foi mantido em R$ 5.000 em mai–set (para o desvio ficar visível) e revisado para R$ 5.500 de out a dez.</t>
+          <t>Estão orçados R$ 10.293,60 em agosto e R$ 12.867,00 em dezembro. O realizado de agosto ainda não foi informado.</t>
         </is>
       </c>
       <c r="D9" s="56" t="inlineStr">
         <is>
-          <t>Desvio já incorrido de R$ 500/mês. Impacto de +R$ 1.500 no orçamento do restante do ano; o orçamento total sobe para R$ 395.852,68.</t>
+          <t>É a maior despesa isolada do Jurídico no segundo semestre.</t>
         </is>
       </c>
       <c r="E9" s="56" t="inlineStr">
@@ -8020,29 +8020,29 @@
       </c>
       <c r="F9" s="61" t="inlineStr">
         <is>
-          <t>APLICADO</t>
+          <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B10" s="59" t="inlineStr">
         <is>
-          <t>Jusbrasil 30% acima do orçado</t>
+          <t>Jonathan R$ 3.700/mês abaixo do contratado</t>
         </is>
       </c>
       <c r="C10" s="59" t="inlineStr">
         <is>
-          <t>Orçado R$ 104,90/mês, realizado R$ 136,00/mês nos três meses.</t>
+          <t>Orçado R$ 10.000/mês, realizado R$ 6.300/mês em mai, jun e jul.</t>
         </is>
       </c>
       <c r="D10" s="59" t="inlineStr">
         <is>
-          <t>Menor desvio em reais (R$ 31,10/mês), mas o maior em percentual. Vale conferir se houve reajuste contratual ou mudança de plano.</t>
+          <t>Maior desvio em reais de todo o orçamento: R$ 11.100 em três meses. Se o valor menor for o novo padrão, o planejado de ago a dez deve ser revisado para baixo — sobrariam R$ 18.500 no orçamento do TI.</t>
         </is>
       </c>
       <c r="E10" s="59" t="inlineStr">
@@ -8050,7 +8050,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F10" s="60" t="inlineStr">
+      <c r="F10" s="61" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -8059,22 +8059,22 @@
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="55" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B11" s="56" t="inlineStr">
         <is>
-          <t>Bonificação de ago/26 do Jurídico</t>
+          <t>Elias Benedito zerado nos três meses</t>
         </is>
       </c>
       <c r="C11" s="56" t="inlineStr">
         <is>
-          <t>Estão orçados R$ 10.293,60 em agosto e R$ 12.867,00 em dezembro. O realizado de agosto ainda não foi informado.</t>
+          <t>Orçado R$ 1.065/mês como suporte técnico terceirizado, realizado R$ 0 em mai, jun e jul.</t>
         </is>
       </c>
       <c r="D11" s="56" t="inlineStr">
         <is>
-          <t>É a maior despesa isolada do Jurídico no segundo semestre. Sem confirmação, o acumulado de agosto fica distorcido.</t>
+          <t>Confirmar se o contrato segue ativo (acionamento sob demanda) ou se foi encerrado. Se encerrado, são R$ 12.780 a liberar no orçamento do ano.</t>
         </is>
       </c>
       <c r="E11" s="56" t="inlineStr">
@@ -8082,7 +8082,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F11" s="60" t="inlineStr">
+      <c r="F11" s="61" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -8091,22 +8091,22 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B12" s="59" t="inlineStr">
         <is>
-          <t>Base de meses — reconciliada com a ficha original</t>
+          <t>Planejado de jan a abr — CONFERIR</t>
         </is>
       </c>
       <c r="C12" s="59" t="inlineStr">
         <is>
-          <t>A ficha trazia a coluna TOTAL do TI digitada à mão em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9) enquanto o grid mensal tinha só 8 colunas. Com o período estendido para jan–dez, os três totais batem exatamente: R$ 64.998,30 + R$ 12.780,00 + R$ 90.000,00 = R$ 167.778,30, o valor original da ficha. Não era erro de digitação — era o grid que estava incompleto.</t>
+          <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
         </is>
       </c>
       <c r="D12" s="59" t="inlineStr">
         <is>
-          <t>Equipe de TI volta ao valor original de R$ 167.778,30. Jonathan lançado com entrada em abr/26 (9 meses), que é o que explica os R$ 90.000 da ficha.</t>
+          <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
         </is>
       </c>
       <c r="E12" s="59" t="inlineStr">
@@ -8114,31 +8114,31 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F12" s="61" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
+      <c r="F12" s="62" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="55" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B13" s="56" t="inlineStr">
         <is>
-          <t>Planejado de jan a abr — CONFERIR</t>
+          <t>Realizado de jan a abr — A LANÇAR</t>
         </is>
       </c>
       <c r="C13" s="56" t="inlineStr">
         <is>
-          <t>O 1º quadrimestre foi preenchido replicando os valores mensais já conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
+          <t>As colunas de jan a abr estão em branco na aba Realizado. Só mai, jun e jul foram informados.</t>
         </is>
       </c>
       <c r="D13" s="56" t="inlineStr">
         <is>
-          <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
+          <t>São 4 dos 7 meses já fechados do ano. Sem eles o acumulado e o Painel refletem menos da metade do período decorrido.</t>
         </is>
       </c>
       <c r="E13" s="56" t="inlineStr">
@@ -8146,31 +8146,31 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F13" s="62" t="inlineStr">
-        <is>
-          <t>CONFERIR</t>
+      <c r="F13" s="57" t="inlineStr">
+        <is>
+          <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="58" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B14" s="59" t="inlineStr">
         <is>
-          <t>Realizado de jan a abr — A LANÇAR</t>
+          <t>Despesas do TI — A LANÇAR</t>
         </is>
       </c>
       <c r="C14" s="59" t="inlineStr">
         <is>
-          <t>As colunas de jan a abr estão em branco na aba Realizado. Só mai, jun e jul foram informados.</t>
+          <t>As 9 linhas de despesas do TI (peças, backup, Adapta, antivírus, Office, sala de reunião, cursos, app de gravação e bonificação) não têm lançamento em nenhum mês.</t>
         </is>
       </c>
       <c r="D14" s="59" t="inlineStr">
         <is>
-          <t>São 4 dos 7 meses já fechados do ano. Sem eles o acumulado e o Painel refletem menos da metade do período decorrido.</t>
+          <t>São R$ 89.040 orçados no ano, 35% do orçamento do TI. Sem lançamento, o departamento aparece com desvio negativo que é ausência de dado.</t>
         </is>
       </c>
       <c r="E14" s="59" t="inlineStr">
@@ -8187,126 +8187,126 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" s="56" t="inlineStr">
         <is>
-          <t>Origem do valor realizado</t>
+          <t>Base de meses — reconciliada com a ficha original</t>
         </is>
       </c>
       <c r="C15" s="56" t="inlineStr">
         <is>
-          <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto.</t>
+          <t>A ficha trazia a coluna TOTAL do TI digitada à mão em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9) enquanto o grid mensal tinha só 8 colunas. Com o período em jan–dez os três totais batem exatamente: R$ 64.998,30 + R$ 12.780,00 + R$ 90.000,00 = R$ 167.778,30, o valor da ficha. Não era erro de digitação — era o grid que estava incompleto.</t>
         </is>
       </c>
       <c r="D15" s="56" t="inlineStr">
         <is>
-          <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
+          <t>Equipe de TI no valor original de R$ 167.778,30. Jonathan lançado com entrada em abr/26 (9 meses), que é o que explica os R$ 90.000.</t>
         </is>
       </c>
       <c r="E15" s="56" t="inlineStr">
         <is>
-          <t>Cristiane + Financeiro</t>
+          <t>Cristiane</t>
         </is>
       </c>
       <c r="F15" s="60" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" s="59" t="inlineStr">
         <is>
-          <t>Jusfy x Astrea</t>
+          <t>Origem do valor realizado</t>
         </is>
       </c>
       <c r="C16" s="59" t="inlineStr">
         <is>
-          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
+          <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto. Até aqui os números vieram informados pela gestora.</t>
         </is>
       </c>
       <c r="D16" s="59" t="inlineStr">
         <is>
-          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado de ago a dez.</t>
+          <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
         </is>
       </c>
       <c r="E16" s="59" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Financeiro</t>
         </is>
       </c>
       <c r="F16" s="61" t="inlineStr">
         <is>
-          <t>RESOLVIDO</t>
+          <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" s="56" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos de TI</t>
+          <t>Jusfy x Astrea</t>
         </is>
       </c>
       <c r="C17" s="56" t="inlineStr">
         <is>
-          <t>Backup (R$ 6.600), Adapta/IA (R$ 12.200), Antivírus (R$ 1.920) e Office 365 (R$ 3.000) estão marcados na ficha como 'não sei se seria administrativo'. Total: R$ 23.720.</t>
+          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
         </is>
       </c>
       <c r="D17" s="56" t="inlineStr">
         <is>
-          <t>Se são da empresa toda e ficam no centro de custo de TI, o TI carrega despesa que não é dele e aparece caro no comparativo.</t>
+          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado dos meses seguintes.</t>
         </is>
       </c>
       <c r="E17" s="56" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
+          <t>Cristiane</t>
         </is>
       </c>
       <c r="F17" s="60" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" s="59" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Rateio dos softwares corporativos de TI</t>
         </is>
       </c>
       <c r="C18" s="59" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 8 = R$ 22.400 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
         </is>
       </c>
       <c r="D18" s="59" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
         </is>
       </c>
       <c r="E18" s="59" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F18" s="60" t="inlineStr">
+          <t>Cristiane + Controladoria</t>
+        </is>
+      </c>
+      <c r="F18" s="61" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -8315,22 +8315,22 @@
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" s="56" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
         </is>
       </c>
       <c r="C19" s="56" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
         </is>
       </c>
       <c r="D19" s="56" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
         </is>
       </c>
       <c r="E19" s="56" t="inlineStr">
@@ -8338,7 +8338,7 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F19" s="60" t="inlineStr">
+      <c r="F19" s="61" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -8347,30 +8347,62 @@
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="58" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="59" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C20" s="59" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D20" s="59" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E20" s="59" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F20" s="61" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B20" s="59" t="inlineStr">
+      <c r="B21" s="56" t="inlineStr">
         <is>
           <t>Critério de competência x caixa</t>
         </is>
       </c>
-      <c r="C20" s="59" t="inlineStr">
+      <c r="C21" s="56" t="inlineStr">
         <is>
           <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
         </is>
       </c>
-      <c r="D20" s="59" t="inlineStr">
+      <c r="D21" s="56" t="inlineStr">
         <is>
           <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
         </is>
       </c>
-      <c r="E20" s="59" t="inlineStr">
+      <c r="E21" s="56" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F20" s="60" t="inlineStr">
+      <c r="F21" s="61" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Como usar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1129,15 +1129,15 @@
         </is>
       </c>
       <c r="C6" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"Jurídico",Planejado!$C$5:$C$27,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"Jurídico",Planejado!$C$5:$C$25,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="8">
@@ -1153,7 +1153,7 @@
         <v/>
       </c>
       <c r="I6" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1169,15 +1169,15 @@
         </is>
       </c>
       <c r="C7" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"Jurídico",Planejado!$C$5:$C$27,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"Jurídico",Planejado!$C$5:$C$25,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="8">
@@ -1193,7 +1193,7 @@
         <v/>
       </c>
       <c r="I7" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"Jurídico",Comparativo!$C$6:$C$28,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1209,15 +1209,15 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="F8" s="12">
@@ -1233,7 +1233,7 @@
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
     </row>
@@ -1249,15 +1249,15 @@
         </is>
       </c>
       <c r="C9" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"TI",Planejado!$C$5:$C$27,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"TI",Planejado!$C$5:$C$25,"Equipe")</f>
         <v/>
       </c>
       <c r="D9" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
       <c r="E9" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
       <c r="F9" s="8">
@@ -1273,7 +1273,7 @@
         <v/>
       </c>
       <c r="I9" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1289,15 +1289,15 @@
         </is>
       </c>
       <c r="C10" s="8">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"TI",Planejado!$C$5:$C$27,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"TI",Planejado!$C$5:$C$25,"Despesas")</f>
         <v/>
       </c>
       <c r="D10" s="8">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
       <c r="E10" s="8">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
       <c r="F10" s="8">
@@ -1313,7 +1313,7 @@
         <v/>
       </c>
       <c r="I10" s="10">
-        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"TI",Comparativo!$C$6:$C$28,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1329,15 +1329,15 @@
         </is>
       </c>
       <c r="C11" s="12">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="12">
@@ -1353,7 +1353,7 @@
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0",Comparativo!$B$6:$B$28,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$28,"?*",Comparativo!$B$6:$B$28,"TI")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
     </row>
@@ -1365,15 +1365,15 @@
       </c>
       <c r="B12" s="15" t="inlineStr"/>
       <c r="C12" s="16">
-        <f>SUM(Planejado!$T$5:$T$27)</f>
+        <f>SUM(Planejado!$T$5:$T$25)</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>SUM(Comparativo!$I$6:$I$28)</f>
+        <f>SUM(Comparativo!$I$6:$I$26)</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>SUM(Comparativo!$J$6:$J$28)</f>
+        <f>SUM(Comparativo!$J$6:$J$26)</f>
         <v/>
       </c>
       <c r="F12" s="16">
@@ -1389,7 +1389,7 @@
         <v/>
       </c>
       <c r="I12" s="18">
-        <f>COUNTIFS(Comparativo!$P$6:$P$28,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$28)</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$26)</f>
         <v/>
       </c>
     </row>
@@ -1443,23 +1443,23 @@
         <v>1</v>
       </c>
       <c r="B17" s="21">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A17),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="C17" s="21">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A17),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="22">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A17),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="22">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A17),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="F17" s="22">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A17),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="G17" s="23">
@@ -1472,23 +1472,23 @@
         <v>2</v>
       </c>
       <c r="B18" s="21">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A18),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="C18" s="21">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A18),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="22">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A18),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="22">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A18),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="F18" s="22">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A18),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="G18" s="23">
@@ -1501,23 +1501,23 @@
         <v>3</v>
       </c>
       <c r="B19" s="21">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A19),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="C19" s="21">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A19),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="22">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A19),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="22">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A19),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="F19" s="22">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A19),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="G19" s="23">
@@ -1530,23 +1530,23 @@
         <v>4</v>
       </c>
       <c r="B20" s="21">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A20),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="C20" s="21">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A20),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="22">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A20),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="22">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A20),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="F20" s="22">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A20),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="G20" s="23">
@@ -1559,23 +1559,23 @@
         <v>5</v>
       </c>
       <c r="B21" s="21">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A21),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="C21" s="21">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A21),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="22">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A21),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="22">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A21),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="F21" s="22">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$28,MATCH(LARGE(Comparativo!$O$6:$O$28,A21),Comparativo!$O$6:$O$28,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
       <c r="G21" s="23">
@@ -1599,7 +1599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2332,59 +2332,59 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="28">
+      <c r="A15" s="34">
         <f>Planejado!A14</f>
         <v/>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="34">
         <f>Planejado!B14</f>
         <v/>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="34">
         <f>Planejado!C14</f>
         <v/>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="35">
         <f>Planejado!D14</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="34">
         <f>Planejado!G14</f>
         <v/>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="36">
         <f>INDEX(Planejado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="36">
         <f>INDEX(Realizado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="36">
         <f>G15-F15</f>
         <v/>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="36">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H14:$S14)</f>
         <v/>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="36">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H14:$S14)</f>
         <v/>
       </c>
-      <c r="K15" s="30">
+      <c r="K15" s="36">
         <f>J15-I15</f>
         <v/>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="37">
         <f>IFERROR(K15/I15,"")</f>
         <v/>
       </c>
-      <c r="M15" s="31">
+      <c r="M15" s="37">
         <f>IFERROR(J15/I15,"")</f>
         <v/>
       </c>
-      <c r="N15" s="32">
+      <c r="N15" s="38">
         <f>IF(P15=0,"Sem lançamento",IF(AND(I15=0,J15=0),"—",IF(I15=0,"Não orçado",IF(K15&gt;0.05*I15,"Acima do orçado",IF(K15&lt;-0.05*I15,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
@@ -2392,7 +2392,7 @@
         <f>IF(K15&gt;1,K15+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P15" s="33">
+      <c r="P15" s="39">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H14:$S14&lt;&gt;""))</f>
         <v/>
       </c>
@@ -3123,189 +3123,57 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="34">
-        <f>Planejado!A26</f>
-        <v/>
-      </c>
-      <c r="B27" s="34">
-        <f>Planejado!B26</f>
-        <v/>
-      </c>
-      <c r="C27" s="34">
-        <f>Planejado!C26</f>
-        <v/>
-      </c>
-      <c r="D27" s="35">
-        <f>Planejado!D26</f>
-        <v/>
-      </c>
-      <c r="E27" s="34">
-        <f>Planejado!G26</f>
-        <v/>
-      </c>
-      <c r="F27" s="36">
-        <f>INDEX(Planejado!$H26:$S26,$D$3)</f>
-        <v/>
-      </c>
-      <c r="G27" s="36">
-        <f>INDEX(Realizado!$H26:$S26,$D$3)</f>
-        <v/>
-      </c>
-      <c r="H27" s="36">
-        <f>G27-F27</f>
-        <v/>
-      </c>
-      <c r="I27" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H26:$S26)</f>
-        <v/>
-      </c>
-      <c r="J27" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H26:$S26)</f>
-        <v/>
-      </c>
-      <c r="K27" s="36">
-        <f>J27-I27</f>
-        <v/>
-      </c>
-      <c r="L27" s="37">
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL GERAL</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="16">
+        <f>SUM(F6:F26)</f>
+        <v/>
+      </c>
+      <c r="G27" s="16">
+        <f>SUM(G6:G26)</f>
+        <v/>
+      </c>
+      <c r="H27" s="16">
+        <f>SUM(H6:H26)</f>
+        <v/>
+      </c>
+      <c r="I27" s="16">
+        <f>SUM(I6:I26)</f>
+        <v/>
+      </c>
+      <c r="J27" s="16">
+        <f>SUM(J6:J26)</f>
+        <v/>
+      </c>
+      <c r="K27" s="16">
+        <f>SUM(K6:K26)</f>
+        <v/>
+      </c>
+      <c r="L27" s="40">
         <f>IFERROR(K27/I27,"")</f>
         <v/>
       </c>
-      <c r="M27" s="37">
+      <c r="M27" s="40">
         <f>IFERROR(J27/I27,"")</f>
         <v/>
       </c>
-      <c r="N27" s="38">
-        <f>IF(P27=0,"Sem lançamento",IF(AND(I27=0,J27=0),"—",IF(I27=0,"Não orçado",IF(K27&gt;0.05*I27,"Acima do orçado",IF(K27&lt;-0.05*I27,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O27" s="27">
-        <f>IF(K27&gt;1,K27+ROW()/1000000,"")</f>
-        <v/>
-      </c>
-      <c r="P27" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H26:$S26&lt;&gt;""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="34">
-        <f>Planejado!A27</f>
-        <v/>
-      </c>
-      <c r="B28" s="34">
-        <f>Planejado!B27</f>
-        <v/>
-      </c>
-      <c r="C28" s="34">
-        <f>Planejado!C27</f>
-        <v/>
-      </c>
-      <c r="D28" s="35">
-        <f>Planejado!D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="34">
-        <f>Planejado!G27</f>
-        <v/>
-      </c>
-      <c r="F28" s="36">
-        <f>INDEX(Planejado!$H27:$S27,$D$3)</f>
-        <v/>
-      </c>
-      <c r="G28" s="36">
-        <f>INDEX(Realizado!$H27:$S27,$D$3)</f>
-        <v/>
-      </c>
-      <c r="H28" s="36">
-        <f>G28-F28</f>
-        <v/>
-      </c>
-      <c r="I28" s="36">
-        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H27:$S27)</f>
-        <v/>
-      </c>
-      <c r="J28" s="36">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H27:$S27)</f>
-        <v/>
-      </c>
-      <c r="K28" s="36">
-        <f>J28-I28</f>
-        <v/>
-      </c>
-      <c r="L28" s="37">
-        <f>IFERROR(K28/I28,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="37">
-        <f>IFERROR(J28/I28,"")</f>
-        <v/>
-      </c>
-      <c r="N28" s="38">
-        <f>IF(P28=0,"Sem lançamento",IF(AND(I28=0,J28=0),"—",IF(I28=0,"Não orçado",IF(K28&gt;0.05*I28,"Acima do orçado",IF(K28&lt;-0.05*I28,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O28" s="27">
-        <f>IF(K28&gt;1,K28+ROW()/1000000,"")</f>
-        <v/>
-      </c>
-      <c r="P28" s="39">
-        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H27:$S27&lt;&gt;""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL GERAL</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="15" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="16">
-        <f>SUM(F6:F28)</f>
-        <v/>
-      </c>
-      <c r="G29" s="16">
-        <f>SUM(G6:G28)</f>
-        <v/>
-      </c>
-      <c r="H29" s="16">
-        <f>SUM(H6:H28)</f>
-        <v/>
-      </c>
-      <c r="I29" s="16">
-        <f>SUM(I6:I28)</f>
-        <v/>
-      </c>
-      <c r="J29" s="16">
-        <f>SUM(J6:J28)</f>
-        <v/>
-      </c>
-      <c r="K29" s="16">
-        <f>SUM(K6:K28)</f>
-        <v/>
-      </c>
-      <c r="L29" s="40">
-        <f>IFERROR(K29/I29,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="40">
-        <f>IFERROR(J29/I29,"")</f>
-        <v/>
-      </c>
-      <c r="N29" s="15" t="n"/>
+      <c r="N27" s="15" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N28"/>
+  <autoFilter ref="A5:N26"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H28">
+  <conditionalFormatting sqref="H6:H26">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3313,7 +3181,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K28">
+  <conditionalFormatting sqref="K6:K26">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3336,7 +3204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3572,12 +3440,12 @@
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>Geovanna — salário bruto</t>
+          <t>Geovanna</t>
         </is>
       </c>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>Analista Administrativo</t>
+          <t>Analista Administrativo — orçada pelo custo total (encargos de folha + benefícios). Salário bruto informado: R$ 2.886,91/mês</t>
         </is>
       </c>
       <c r="F6" s="28" t="inlineStr">
@@ -3591,40 +3459,40 @@
         </is>
       </c>
       <c r="H6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="I6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="J6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="K6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="L6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="M6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="N6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="O6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="P6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="Q6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="R6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="S6" s="30" t="n">
-        <v>2886.91</v>
+        <v>4825.515</v>
       </c>
       <c r="T6" s="41">
         <f>SUM(H6:S6)</f>
@@ -3634,7 +3502,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="28" t="inlineStr">
         <is>
-          <t>JUR-E02B</t>
+          <t>JUR-E03</t>
         </is>
       </c>
       <c r="B7" s="28" t="inlineStr">
@@ -3649,59 +3517,59 @@
       </c>
       <c r="D7" s="29" t="inlineStr">
         <is>
-          <t>Geovanna — encargos e benefícios</t>
+          <t>Thamar Victória</t>
         </is>
       </c>
       <c r="E7" s="29" t="inlineStr">
         <is>
-          <t>INSS patronal, FGTS, provisões de 13º e férias, benefícios — PREENCHER</t>
+          <t>Advogada — reajuste permanente de R$ 5.000 para R$ 5.500 (revisado a partir de out/26)</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="G7" s="28" t="inlineStr">
         <is>
-          <t>Encargos e Benefícios - CLT</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="H7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="I7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="J7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="K7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="L7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="M7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="N7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="O7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="P7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5000</v>
       </c>
       <c r="Q7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5500</v>
       </c>
       <c r="R7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5500</v>
       </c>
       <c r="S7" s="30" t="n">
-        <v>1938.605</v>
+        <v>5500</v>
       </c>
       <c r="T7" s="41">
         <f>SUM(H7:S7)</f>
@@ -3711,7 +3579,7 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
-          <t>JUR-E03</t>
+          <t>JUR-D01</t>
         </is>
       </c>
       <c r="B8" s="28" t="inlineStr">
@@ -3721,64 +3589,60 @@
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>Thamar Victória</t>
+          <t>JUSFY</t>
         </is>
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>Advogada — reajuste permanente de R$ 5.000 para R$ 5.500 (revisado a partir de out/26)</t>
-        </is>
-      </c>
-      <c r="F8" s="28" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
+          <t>Fase de teste com objetivo de eliminar o Astrea</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr"/>
       <c r="G8" s="28" t="inlineStr">
         <is>
-          <t>Pessoal - PJ</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H8" s="30" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="I8" s="30" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="J8" s="30" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="K8" s="30" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="L8" s="30" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="M8" s="30" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="N8" s="30" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="O8" s="30" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="P8" s="30" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="30" t="n">
-        <v>5500</v>
+        <v>100</v>
       </c>
       <c r="R8" s="30" t="n">
-        <v>5500</v>
+        <v>100</v>
       </c>
       <c r="S8" s="30" t="n">
-        <v>5500</v>
+        <v>100</v>
       </c>
       <c r="T8" s="41">
         <f>SUM(H8:S8)</f>
@@ -3788,7 +3652,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="28" t="inlineStr">
         <is>
-          <t>JUR-D01</t>
+          <t>JUR-D02</t>
         </is>
       </c>
       <c r="B9" s="28" t="inlineStr">
@@ -3803,14 +3667,10 @@
       </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
-          <t>JUSFY</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="inlineStr">
-        <is>
-          <t>Fase de teste com objetivo de eliminar o Astrea</t>
-        </is>
-      </c>
+          <t>JUSBRASIL</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr"/>
       <c r="F9" s="28" t="inlineStr"/>
       <c r="G9" s="28" t="inlineStr">
         <is>
@@ -3818,40 +3678,40 @@
         </is>
       </c>
       <c r="H9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="I9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="J9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="K9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="L9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="M9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="N9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="O9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="P9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="Q9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="R9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="S9" s="30" t="n">
-        <v>100</v>
+        <v>104.9</v>
       </c>
       <c r="T9" s="41">
         <f>SUM(H9:S9)</f>
@@ -3861,7 +3721,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="28" t="inlineStr">
         <is>
-          <t>JUR-D02</t>
+          <t>JUR-D03</t>
         </is>
       </c>
       <c r="B10" s="28" t="inlineStr">
@@ -3876,10 +3736,14 @@
       </c>
       <c r="D10" s="29" t="inlineStr">
         <is>
-          <t>JUSBRASIL</t>
-        </is>
-      </c>
-      <c r="E10" s="29" t="inlineStr"/>
+          <t>ASTREA</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>Cancelado — realizado zerado desde mai/26</t>
+        </is>
+      </c>
       <c r="F10" s="28" t="inlineStr"/>
       <c r="G10" s="28" t="inlineStr">
         <is>
@@ -3887,40 +3751,40 @@
         </is>
       </c>
       <c r="H10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="L10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="M10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="N10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="O10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="P10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="Q10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="R10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="S10" s="30" t="n">
-        <v>104.9</v>
+        <v>112.07</v>
       </c>
       <c r="T10" s="41">
         <f>SUM(H10:S10)</f>
@@ -3930,7 +3794,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="28" t="inlineStr">
         <is>
-          <t>JUR-D03</t>
+          <t>JUR-D04</t>
         </is>
       </c>
       <c r="B11" s="28" t="inlineStr">
@@ -3945,14 +3809,10 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>ASTREA</t>
-        </is>
-      </c>
-      <c r="E11" s="29" t="inlineStr">
-        <is>
-          <t>Cancelado — realizado zerado desde mai/26</t>
-        </is>
-      </c>
+          <t>LEME</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr"/>
       <c r="F11" s="28" t="inlineStr"/>
       <c r="G11" s="28" t="inlineStr">
         <is>
@@ -3960,40 +3820,40 @@
         </is>
       </c>
       <c r="H11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="I11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="J11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="K11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="L11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="M11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="N11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="O11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="P11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="Q11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="R11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="S11" s="30" t="n">
-        <v>112.07</v>
+        <v>1030</v>
       </c>
       <c r="T11" s="41">
         <f>SUM(H11:S11)</f>
@@ -4003,7 +3863,7 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="28" t="inlineStr">
         <is>
-          <t>JUR-D04</t>
+          <t>JUR-D05</t>
         </is>
       </c>
       <c r="B12" s="28" t="inlineStr">
@@ -4018,51 +3878,51 @@
       </c>
       <c r="D12" s="29" t="inlineStr">
         <is>
-          <t>LEME</t>
+          <t>Cursos / Eventos / Network</t>
         </is>
       </c>
       <c r="E12" s="29" t="inlineStr"/>
       <c r="F12" s="28" t="inlineStr"/>
       <c r="G12" s="28" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="H12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="I12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="K12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="L12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="M12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="N12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="O12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="P12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="Q12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="R12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="S12" s="30" t="n">
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="T12" s="41">
         <f>SUM(H12:S12)</f>
@@ -4072,7 +3932,7 @@
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="28" t="inlineStr">
         <is>
-          <t>JUR-D05</t>
+          <t>JUR-D06</t>
         </is>
       </c>
       <c r="B13" s="28" t="inlineStr">
@@ -4087,51 +3947,55 @@
       </c>
       <c r="D13" s="29" t="inlineStr">
         <is>
-          <t>Cursos / Eventos / Network</t>
-        </is>
-      </c>
-      <c r="E13" s="29" t="inlineStr"/>
+          <t>Bonificações trimestrais/semestrais do time</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
       <c r="F13" s="28" t="inlineStr"/>
       <c r="G13" s="28" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Prêmios</t>
         </is>
       </c>
       <c r="H13" s="30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I13" s="30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J13" s="30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K13" s="30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L13" s="30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M13" s="30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N13" s="30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="O13" s="30" t="n">
-        <v>1000</v>
+        <v>10293.6</v>
       </c>
       <c r="P13" s="30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R13" s="30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="S13" s="30" t="n">
-        <v>1000</v>
+        <v>12867</v>
       </c>
       <c r="T13" s="41">
         <f>SUM(H13:S13)</f>
@@ -4139,72 +4003,76 @@
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>JUR-D06</t>
-        </is>
-      </c>
-      <c r="B14" s="28" t="inlineStr">
-        <is>
-          <t>Jurídico</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="inlineStr">
-        <is>
-          <t>Despesas</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="inlineStr">
-        <is>
-          <t>Bonificações trimestrais/semestrais do time</t>
-        </is>
-      </c>
-      <c r="E14" s="29" t="inlineStr">
-        <is>
-          <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
-        </is>
-      </c>
-      <c r="F14" s="28" t="inlineStr"/>
-      <c r="G14" s="28" t="inlineStr">
-        <is>
-          <t>Prêmios</t>
-        </is>
-      </c>
-      <c r="H14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="30" t="n">
-        <v>10293.6</v>
-      </c>
-      <c r="P14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="30" t="n">
-        <v>12867</v>
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>TI-E01</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>Equipe</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>Vinicius Di Franco</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="inlineStr">
+        <is>
+          <t>Analista Administrativo — orçado pelo custo total (encargos de folha + benefícios). Salário bruto: R$ 2.570,52/mês até jul/26 e R$ 3.070,52 a partir de 05/08/26, aumento absorvido pela folga do envelope</t>
+        </is>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>CLT</t>
+        </is>
+      </c>
+      <c r="G14" s="34" t="inlineStr">
+        <is>
+          <t>Pessoal - CLT</t>
+        </is>
+      </c>
+      <c r="H14" s="36" t="n">
+        <v>5416.525</v>
+      </c>
+      <c r="I14" s="36" t="n">
+        <v>5416.525</v>
+      </c>
+      <c r="J14" s="36" t="n">
+        <v>5416.525</v>
+      </c>
+      <c r="K14" s="36" t="n">
+        <v>5416.525</v>
+      </c>
+      <c r="L14" s="36" t="n">
+        <v>5416.525</v>
+      </c>
+      <c r="M14" s="36" t="n">
+        <v>5416.525</v>
+      </c>
+      <c r="N14" s="36" t="n">
+        <v>5416.525</v>
+      </c>
+      <c r="O14" s="36" t="n">
+        <v>5416.525</v>
+      </c>
+      <c r="P14" s="36" t="n">
+        <v>5416.525</v>
+      </c>
+      <c r="Q14" s="36" t="n">
+        <v>5416.525</v>
+      </c>
+      <c r="R14" s="36" t="n">
+        <v>5416.525</v>
+      </c>
+      <c r="S14" s="36" t="n">
+        <v>5416.525</v>
       </c>
       <c r="T14" s="41">
         <f>SUM(H14:S14)</f>
@@ -4214,7 +4082,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="34" t="inlineStr">
         <is>
-          <t>TI-E01</t>
+          <t>TI-E02</t>
         </is>
       </c>
       <c r="B15" s="34" t="inlineStr">
@@ -4229,59 +4097,59 @@
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
-          <t>Vinicius Di Franco — salário bruto</t>
+          <t>Elias Benedito</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Analista Administrativo — aumento de R$ 2.570,52 para R$ 3.070,52 a partir de 05/08/26, absorvido pela folga do envelope orçado (custo total segue R$ 5.416,525/mês)</t>
+          <t>Suporte Técnico Terceirizado</t>
         </is>
       </c>
       <c r="F15" s="34" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="G15" s="34" t="inlineStr">
         <is>
-          <t>Pessoal - CLT</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="H15" s="36" t="n">
-        <v>2570.52</v>
+        <v>1065</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>2570.52</v>
+        <v>1065</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>2570.52</v>
+        <v>1065</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>2570.52</v>
+        <v>1065</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>2570.52</v>
+        <v>1065</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>2570.52</v>
+        <v>1065</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>2570.52</v>
+        <v>1065</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>3070.52</v>
+        <v>1065</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>3070.52</v>
+        <v>1065</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>3070.52</v>
+        <v>1065</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>3070.52</v>
+        <v>1065</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>3070.52</v>
+        <v>1065</v>
       </c>
       <c r="T15" s="41">
         <f>SUM(H15:S15)</f>
@@ -4291,7 +4159,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>TI-E01B</t>
+          <t>TI-E03</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
@@ -4306,59 +4174,59 @@
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
-          <t>Vinicius Di Franco — encargos e benefícios</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="E16" s="35" t="inlineStr">
         <is>
-          <t>INSS patronal, FGTS, provisões de 13º e férias, benefícios — PREENCHER. Planejado = resíduo do envelope de R$ 5.416,525/mês, que já previa o aumento. A folga não é economia estrutural: com o bruto de agosto ela quase se esgota.</t>
+          <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
         <is>
-          <t>CLT</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="G16" s="34" t="inlineStr">
         <is>
-          <t>Encargos e Benefícios - CLT</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="H16" s="36" t="n">
-        <v>2846.005</v>
+        <v>0</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>2846.005</v>
+        <v>0</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>2846.005</v>
+        <v>0</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>2846.005</v>
+        <v>10000</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>2846.005</v>
+        <v>10000</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>2846.005</v>
+        <v>10000</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>2846.005</v>
+        <v>10000</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>2346.005</v>
+        <v>10000</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>2346.005</v>
+        <v>10000</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>2346.005</v>
+        <v>10000</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>2346.005</v>
+        <v>10000</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>2346.005</v>
+        <v>10000</v>
       </c>
       <c r="T16" s="41">
         <f>SUM(H16:S16)</f>
@@ -4368,7 +4236,7 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>TI-E02</t>
+          <t>TI-D01</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
@@ -4378,64 +4246,60 @@
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="D17" s="35" t="inlineStr">
         <is>
-          <t>Elias Benedito</t>
+          <t>Peças de Manutenção</t>
         </is>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>Suporte Técnico Terceirizado</t>
-        </is>
-      </c>
-      <c r="F17" s="34" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
+          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
+        </is>
+      </c>
+      <c r="F17" s="34" t="inlineStr"/>
       <c r="G17" s="34" t="inlineStr">
         <is>
-          <t>Pessoal - PJ</t>
+          <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
       <c r="H17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>1065</v>
+        <v>810</v>
       </c>
       <c r="T17" s="41">
         <f>SUM(H17:S17)</f>
@@ -4445,7 +4309,7 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="34" t="inlineStr">
         <is>
-          <t>TI-E03</t>
+          <t>TI-D02</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
@@ -4455,64 +4319,60 @@
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>Equipe</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="D18" s="35" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Backup em Nuvem</t>
         </is>
       </c>
       <c r="E18" s="35" t="inlineStr">
         <is>
-          <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
-        </is>
-      </c>
-      <c r="F18" s="34" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
+          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
+        </is>
+      </c>
+      <c r="F18" s="34" t="inlineStr"/>
       <c r="G18" s="34" t="inlineStr">
         <is>
-          <t>Pessoal - PJ</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H18" s="36" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>10000</v>
+        <v>825</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>10000</v>
+        <v>825</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>10000</v>
+        <v>825</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>10000</v>
+        <v>825</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>10000</v>
+        <v>825</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>10000</v>
+        <v>825</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>10000</v>
+        <v>825</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>10000</v>
+        <v>825</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>10000</v>
+        <v>825</v>
       </c>
       <c r="T18" s="41">
         <f>SUM(H18:S18)</f>
@@ -4522,7 +4382,7 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="34" t="inlineStr">
         <is>
-          <t>TI-D01</t>
+          <t>TI-D03</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
@@ -4537,55 +4397,55 @@
       </c>
       <c r="D19" s="35" t="inlineStr">
         <is>
-          <t>Peças de Manutenção</t>
+          <t>Inteligência Artificial (Adapta)</t>
         </is>
       </c>
       <c r="E19" s="35" t="inlineStr">
         <is>
-          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
+          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr"/>
       <c r="G19" s="34" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos Diversos</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H19" s="36" t="n">
-        <v>810</v>
+        <v>1300</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>810</v>
+        <v>1300</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>810</v>
+        <v>1300</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>810</v>
+        <v>1300</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>810</v>
+        <v>1300</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>810</v>
+        <v>1300</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>810</v>
+        <v>1600</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>810</v>
+        <v>1600</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>810</v>
+        <v>1600</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>810</v>
+        <v>1600</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>810</v>
+        <v>1600</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>810</v>
+        <v>1600</v>
       </c>
       <c r="T19" s="41">
         <f>SUM(H19:S19)</f>
@@ -4595,7 +4455,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="34" t="inlineStr">
         <is>
-          <t>TI-D02</t>
+          <t>TI-D04</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
@@ -4610,12 +4470,12 @@
       </c>
       <c r="D20" s="35" t="inlineStr">
         <is>
-          <t>Backup em Nuvem</t>
+          <t>Antivírus</t>
         </is>
       </c>
       <c r="E20" s="35" t="inlineStr">
         <is>
-          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
+          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F20" s="34" t="inlineStr"/>
@@ -4625,40 +4485,40 @@
         </is>
       </c>
       <c r="H20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>825</v>
+        <v>240</v>
       </c>
       <c r="T20" s="41">
         <f>SUM(H20:S20)</f>
@@ -4668,7 +4528,7 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="34" t="inlineStr">
         <is>
-          <t>TI-D03</t>
+          <t>TI-D05</t>
         </is>
       </c>
       <c r="B21" s="34" t="inlineStr">
@@ -4683,12 +4543,12 @@
       </c>
       <c r="D21" s="35" t="inlineStr">
         <is>
-          <t>Inteligência Artificial (Adapta)</t>
+          <t>Pacote Office 365</t>
         </is>
       </c>
       <c r="E21" s="35" t="inlineStr">
         <is>
-          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
+          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr"/>
@@ -4698,40 +4558,40 @@
         </is>
       </c>
       <c r="H21" s="36" t="n">
-        <v>1300</v>
+        <v>375</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>1300</v>
+        <v>375</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>1300</v>
+        <v>375</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>1300</v>
+        <v>375</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>1300</v>
+        <v>375</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>1300</v>
+        <v>375</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>1600</v>
+        <v>375</v>
       </c>
       <c r="O21" s="36" t="n">
-        <v>1600</v>
+        <v>375</v>
       </c>
       <c r="P21" s="36" t="n">
-        <v>1600</v>
+        <v>375</v>
       </c>
       <c r="Q21" s="36" t="n">
-        <v>1600</v>
+        <v>375</v>
       </c>
       <c r="R21" s="36" t="n">
-        <v>1600</v>
+        <v>375</v>
       </c>
       <c r="S21" s="36" t="n">
-        <v>1600</v>
+        <v>375</v>
       </c>
       <c r="T21" s="41">
         <f>SUM(H21:S21)</f>
@@ -4741,7 +4601,7 @@
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="34" t="inlineStr">
         <is>
-          <t>TI-D04</t>
+          <t>TI-D06</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
@@ -4756,55 +4616,55 @@
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
-          <t>Antivírus</t>
+          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
         </is>
       </c>
       <c r="E22" s="35" t="inlineStr">
         <is>
-          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
+          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
         </is>
       </c>
       <c r="F22" s="34" t="inlineStr"/>
       <c r="G22" s="34" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Móveis e Utensílios</t>
         </is>
       </c>
       <c r="H22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="O22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="Q22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="R22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="S22" s="36" t="n">
-        <v>240</v>
+        <v>2800</v>
       </c>
       <c r="T22" s="41">
         <f>SUM(H22:S22)</f>
@@ -4814,7 +4674,7 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="34" t="inlineStr">
         <is>
-          <t>TI-D05</t>
+          <t>TI-D07</t>
         </is>
       </c>
       <c r="B23" s="34" t="inlineStr">
@@ -4829,55 +4689,51 @@
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>Pacote Office 365</t>
-        </is>
-      </c>
-      <c r="E23" s="35" t="inlineStr">
-        <is>
-          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
-        </is>
-      </c>
+          <t>Cursos e Treinamentos</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr"/>
       <c r="F23" s="34" t="inlineStr"/>
       <c r="G23" s="34" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="H23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="O23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="Q23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="R23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="S23" s="36" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="T23" s="41">
         <f>SUM(H23:S23)</f>
@@ -4887,7 +4743,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="34" t="inlineStr">
         <is>
-          <t>TI-D06</t>
+          <t>TI-D08</t>
         </is>
       </c>
       <c r="B24" s="34" t="inlineStr">
@@ -4902,55 +4758,51 @@
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
-        </is>
-      </c>
-      <c r="E24" s="35" t="inlineStr">
-        <is>
-          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
-        </is>
-      </c>
+          <t>Aplicativo de Gravação de Reunião</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr"/>
       <c r="F24" s="34" t="inlineStr"/>
       <c r="G24" s="34" t="inlineStr">
         <is>
-          <t>Móveis e Utensílios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="I24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="J24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="K24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="L24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="M24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="N24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="O24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="P24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="Q24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="R24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="S24" s="36" t="n">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="T24" s="41">
         <f>SUM(H24:S24)</f>
@@ -4960,7 +4812,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="34" t="inlineStr">
         <is>
-          <t>TI-D07</t>
+          <t>TI-D09</t>
         </is>
       </c>
       <c r="B25" s="34" t="inlineStr">
@@ -4975,266 +4827,128 @@
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>Cursos e Treinamentos</t>
-        </is>
-      </c>
-      <c r="E25" s="35" t="inlineStr"/>
+          <t>Bonificação do time</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
       <c r="F25" s="34" t="inlineStr"/>
       <c r="G25" s="34" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Prêmios</t>
         </is>
       </c>
       <c r="H25" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I25" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J25" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K25" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L25" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M25" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N25" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O25" s="36" t="n">
-        <v>200</v>
+        <v>2400</v>
       </c>
       <c r="P25" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R25" s="36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S25" s="36" t="n">
-        <v>200</v>
+        <v>3600</v>
       </c>
       <c r="T25" s="41">
         <f>SUM(H25:S25)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="34" t="inlineStr">
-        <is>
-          <t>TI-D08</t>
-        </is>
-      </c>
-      <c r="B26" s="34" t="inlineStr">
-        <is>
-          <t>TI</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>Despesas</t>
-        </is>
-      </c>
-      <c r="D26" s="35" t="inlineStr">
-        <is>
-          <t>Aplicativo de Gravação de Reunião</t>
-        </is>
-      </c>
-      <c r="E26" s="35" t="inlineStr"/>
-      <c r="F26" s="34" t="inlineStr"/>
-      <c r="G26" s="34" t="inlineStr">
-        <is>
-          <t>Licenças de Softwares</t>
-        </is>
-      </c>
-      <c r="H26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="I26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="J26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="K26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="L26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="M26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="N26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="O26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="P26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="Q26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="R26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="S26" s="36" t="n">
-        <v>220</v>
-      </c>
-      <c r="T26" s="41">
-        <f>SUM(H26:S26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="34" t="inlineStr">
-        <is>
-          <t>TI-D09</t>
-        </is>
-      </c>
-      <c r="B27" s="34" t="inlineStr">
-        <is>
-          <t>TI</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>Despesas</t>
-        </is>
-      </c>
-      <c r="D27" s="35" t="inlineStr">
-        <is>
-          <t>Bonificação do time</t>
-        </is>
-      </c>
-      <c r="E27" s="35" t="inlineStr">
-        <is>
-          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
-        </is>
-      </c>
-      <c r="F27" s="34" t="inlineStr"/>
-      <c r="G27" s="34" t="inlineStr">
-        <is>
-          <t>Prêmios</t>
-        </is>
-      </c>
-      <c r="H27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="36" t="n">
-        <v>2400</v>
-      </c>
-      <c r="P27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="36" t="n">
-        <v>3600</v>
-      </c>
-      <c r="T27" s="41">
-        <f>SUM(H27:S27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="16">
-        <f>SUM(H5:H27)</f>
-        <v/>
-      </c>
-      <c r="I28" s="16">
-        <f>SUM(I5:I27)</f>
-        <v/>
-      </c>
-      <c r="J28" s="16">
-        <f>SUM(J5:J27)</f>
-        <v/>
-      </c>
-      <c r="K28" s="16">
-        <f>SUM(K5:K27)</f>
-        <v/>
-      </c>
-      <c r="L28" s="16">
-        <f>SUM(L5:L27)</f>
-        <v/>
-      </c>
-      <c r="M28" s="16">
-        <f>SUM(M5:M27)</f>
-        <v/>
-      </c>
-      <c r="N28" s="16">
-        <f>SUM(N5:N27)</f>
-        <v/>
-      </c>
-      <c r="O28" s="16">
-        <f>SUM(O5:O27)</f>
-        <v/>
-      </c>
-      <c r="P28" s="16">
-        <f>SUM(P5:P27)</f>
-        <v/>
-      </c>
-      <c r="Q28" s="16">
-        <f>SUM(Q5:Q27)</f>
-        <v/>
-      </c>
-      <c r="R28" s="16">
-        <f>SUM(R5:R27)</f>
-        <v/>
-      </c>
-      <c r="S28" s="16">
-        <f>SUM(S5:S27)</f>
-        <v/>
-      </c>
-      <c r="T28" s="16">
-        <f>SUM(T5:T27)</f>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="16">
+        <f>SUM(H5:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="16">
+        <f>SUM(I5:I25)</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>SUM(J5:J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="16">
+        <f>SUM(K5:K25)</f>
+        <v/>
+      </c>
+      <c r="L26" s="16">
+        <f>SUM(L5:L25)</f>
+        <v/>
+      </c>
+      <c r="M26" s="16">
+        <f>SUM(M5:M25)</f>
+        <v/>
+      </c>
+      <c r="N26" s="16">
+        <f>SUM(N5:N25)</f>
+        <v/>
+      </c>
+      <c r="O26" s="16">
+        <f>SUM(O5:O25)</f>
+        <v/>
+      </c>
+      <c r="P26" s="16">
+        <f>SUM(P5:P25)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="16">
+        <f>SUM(Q5:Q25)</f>
+        <v/>
+      </c>
+      <c r="R26" s="16">
+        <f>SUM(R5:R25)</f>
+        <v/>
+      </c>
+      <c r="S26" s="16">
+        <f>SUM(S5:S25)</f>
+        <v/>
+      </c>
+      <c r="T26" s="16">
+        <f>SUM(T5:T25)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T27"/>
+  <autoFilter ref="A4:T25"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
@@ -5249,7 +4963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5493,28 +5207,18 @@
       <c r="I6" s="45" t="n"/>
       <c r="J6" s="45" t="n"/>
       <c r="K6" s="45" t="n"/>
-      <c r="L6" s="45" t="n">
-        <v>2886.91</v>
-      </c>
-      <c r="M6" s="45" t="n">
-        <v>2886.91</v>
-      </c>
-      <c r="N6" s="45" t="n">
-        <v>2886.91</v>
-      </c>
+      <c r="L6" s="45" t="n"/>
+      <c r="M6" s="45" t="n"/>
+      <c r="N6" s="45" t="n"/>
       <c r="O6" s="45" t="n"/>
       <c r="T6" s="41">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
-      <c r="U6" s="46" t="inlineStr">
-        <is>
-          <t>Gestora, 05/08/26</t>
-        </is>
-      </c>
+      <c r="U6" s="46" t="n"/>
       <c r="V6" s="46" t="inlineStr">
         <is>
-          <t>Salário bruto</t>
+          <t>PREENCHER com o CUSTO TOTAL. Bruto informado: R$ 2.886,91/mês — faltam encargos e benefícios</t>
         </is>
       </c>
     </row>
@@ -5551,18 +5255,28 @@
       <c r="I7" s="45" t="n"/>
       <c r="J7" s="45" t="n"/>
       <c r="K7" s="45" t="n"/>
-      <c r="L7" s="45" t="n"/>
-      <c r="M7" s="45" t="n"/>
-      <c r="N7" s="45" t="n"/>
+      <c r="L7" s="45" t="n">
+        <v>5500</v>
+      </c>
+      <c r="M7" s="45" t="n">
+        <v>5500</v>
+      </c>
+      <c r="N7" s="45" t="n">
+        <v>5500</v>
+      </c>
       <c r="O7" s="45" t="n"/>
       <c r="T7" s="41">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
-      <c r="U7" s="46" t="n"/>
+      <c r="U7" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
       <c r="V7" s="46" t="inlineStr">
         <is>
-          <t>PREENCHER — encargos e benefícios sobre o bruto</t>
+          <t>Reajuste permanente aplicado desde mai/26</t>
         </is>
       </c>
     </row>
@@ -5600,13 +5314,13 @@
       <c r="J8" s="45" t="n"/>
       <c r="K8" s="45" t="n"/>
       <c r="L8" s="45" t="n">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="M8" s="45" t="n">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="N8" s="45" t="n">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="O8" s="45" t="n"/>
       <c r="T8" s="41">
@@ -5620,7 +5334,7 @@
       </c>
       <c r="V8" s="46" t="inlineStr">
         <is>
-          <t>Reajuste permanente aplicado desde mai/26</t>
+          <t>Ainda não iniciado — sem cobrança</t>
         </is>
       </c>
     </row>
@@ -5658,13 +5372,13 @@
       <c r="J9" s="45" t="n"/>
       <c r="K9" s="45" t="n"/>
       <c r="L9" s="45" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M9" s="45" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N9" s="45" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="O9" s="45" t="n"/>
       <c r="T9" s="41">
@@ -5678,7 +5392,7 @@
       </c>
       <c r="V9" s="46" t="inlineStr">
         <is>
-          <t>Ainda não iniciado — sem cobrança</t>
+          <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
         </is>
       </c>
     </row>
@@ -5716,13 +5430,13 @@
       <c r="J10" s="45" t="n"/>
       <c r="K10" s="45" t="n"/>
       <c r="L10" s="45" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M10" s="45" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N10" s="45" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="O10" s="45" t="n"/>
       <c r="T10" s="41">
@@ -5736,7 +5450,7 @@
       </c>
       <c r="V10" s="46" t="inlineStr">
         <is>
-          <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
+          <t>Cancelado — sem cobrança</t>
         </is>
       </c>
     </row>
@@ -5774,13 +5488,13 @@
       <c r="J11" s="45" t="n"/>
       <c r="K11" s="45" t="n"/>
       <c r="L11" s="45" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="M11" s="45" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="N11" s="45" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="O11" s="45" t="n"/>
       <c r="T11" s="41">
@@ -5792,11 +5506,7 @@
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V11" s="46" t="inlineStr">
-        <is>
-          <t>Cancelado — sem cobrança</t>
-        </is>
-      </c>
+      <c r="V11" s="46" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="43">
@@ -5832,13 +5542,13 @@
       <c r="J12" s="45" t="n"/>
       <c r="K12" s="45" t="n"/>
       <c r="L12" s="45" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="M12" s="45" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="N12" s="45" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="O12" s="45" t="n"/>
       <c r="T12" s="41">
@@ -5850,7 +5560,11 @@
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V12" s="46" t="n"/>
+      <c r="V12" s="46" t="inlineStr">
+        <is>
+          <t>Sem gasto no período</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="43">
@@ -5885,28 +5599,18 @@
       <c r="I13" s="45" t="n"/>
       <c r="J13" s="45" t="n"/>
       <c r="K13" s="45" t="n"/>
-      <c r="L13" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="45" t="n">
-        <v>0</v>
-      </c>
+      <c r="L13" s="45" t="n"/>
+      <c r="M13" s="45" t="n"/>
+      <c r="N13" s="45" t="n"/>
       <c r="O13" s="45" t="n"/>
       <c r="T13" s="41">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
-      <c r="U13" s="46" t="inlineStr">
-        <is>
-          <t>Gestora, 05/08/26</t>
-        </is>
-      </c>
+      <c r="U13" s="46" t="n"/>
       <c r="V13" s="46" t="inlineStr">
         <is>
-          <t>Sem gasto no período</t>
+          <t>Bonificação de ago/26 a confirmar</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5658,7 @@
       <c r="U14" s="46" t="n"/>
       <c r="V14" s="46" t="inlineStr">
         <is>
-          <t>Bonificação de ago/26 a confirmar</t>
+          <t>PREENCHER com o CUSTO TOTAL. Bruto: R$ 2.570,52/mês até jul e R$ 3.070,52 de ago — faltam encargos e benefícios</t>
         </is>
       </c>
     </row>
@@ -5992,13 +5696,13 @@
       <c r="J15" s="45" t="n"/>
       <c r="K15" s="45" t="n"/>
       <c r="L15" s="45" t="n">
-        <v>2570.52</v>
+        <v>0</v>
       </c>
       <c r="M15" s="45" t="n">
-        <v>2570.52</v>
+        <v>0</v>
       </c>
       <c r="N15" s="45" t="n">
-        <v>2570.52</v>
+        <v>0</v>
       </c>
       <c r="O15" s="45" t="n"/>
       <c r="T15" s="41">
@@ -6012,7 +5716,7 @@
       </c>
       <c r="V15" s="46" t="inlineStr">
         <is>
-          <t>Salário bruto vigente até jul; sobe para R$ 3.070,52 em ago</t>
+          <t>Sem acionamento no período — confirmar se o contrato segue ativo</t>
         </is>
       </c>
     </row>
@@ -6049,18 +5753,28 @@
       <c r="I16" s="45" t="n"/>
       <c r="J16" s="45" t="n"/>
       <c r="K16" s="45" t="n"/>
-      <c r="L16" s="45" t="n"/>
-      <c r="M16" s="45" t="n"/>
-      <c r="N16" s="45" t="n"/>
+      <c r="L16" s="45" t="n">
+        <v>6300</v>
+      </c>
+      <c r="M16" s="45" t="n">
+        <v>6300</v>
+      </c>
+      <c r="N16" s="45" t="n">
+        <v>6300</v>
+      </c>
       <c r="O16" s="45" t="n"/>
       <c r="T16" s="41">
         <f>SUM(H16:S16)</f>
         <v/>
       </c>
-      <c r="U16" s="46" t="n"/>
+      <c r="U16" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
       <c r="V16" s="46" t="inlineStr">
         <is>
-          <t>PREENCHER — encargos e benefícios sobre o bruto</t>
+          <t>R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
         </is>
       </c>
     </row>
@@ -6097,30 +5811,16 @@
       <c r="I17" s="45" t="n"/>
       <c r="J17" s="45" t="n"/>
       <c r="K17" s="45" t="n"/>
-      <c r="L17" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="45" t="n">
-        <v>0</v>
-      </c>
+      <c r="L17" s="45" t="n"/>
+      <c r="M17" s="45" t="n"/>
+      <c r="N17" s="45" t="n"/>
       <c r="O17" s="45" t="n"/>
       <c r="T17" s="41">
         <f>SUM(H17:S17)</f>
         <v/>
       </c>
-      <c r="U17" s="46" t="inlineStr">
-        <is>
-          <t>Gestora, 05/08/26</t>
-        </is>
-      </c>
-      <c r="V17" s="46" t="inlineStr">
-        <is>
-          <t>Sem acionamento no período — confirmar se o contrato segue ativo</t>
-        </is>
-      </c>
+      <c r="U17" s="46" t="n"/>
+      <c r="V17" s="46" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="43">
@@ -6155,30 +5855,16 @@
       <c r="I18" s="45" t="n"/>
       <c r="J18" s="45" t="n"/>
       <c r="K18" s="45" t="n"/>
-      <c r="L18" s="45" t="n">
-        <v>6300</v>
-      </c>
-      <c r="M18" s="45" t="n">
-        <v>6300</v>
-      </c>
-      <c r="N18" s="45" t="n">
-        <v>6300</v>
-      </c>
+      <c r="L18" s="45" t="n"/>
+      <c r="M18" s="45" t="n"/>
+      <c r="N18" s="45" t="n"/>
       <c r="O18" s="45" t="n"/>
       <c r="T18" s="41">
         <f>SUM(H18:S18)</f>
         <v/>
       </c>
-      <c r="U18" s="46" t="inlineStr">
-        <is>
-          <t>Gestora, 05/08/26</t>
-        </is>
-      </c>
-      <c r="V18" s="46" t="inlineStr">
-        <is>
-          <t>R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
-        </is>
-      </c>
+      <c r="U18" s="46" t="n"/>
+      <c r="V18" s="46" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="43">
@@ -6488,160 +6174,72 @@
       <c r="U25" s="46" t="n"/>
       <c r="V25" s="46" t="n"/>
     </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="43">
-        <f>Planejado!A26</f>
-        <v/>
-      </c>
-      <c r="B26" s="43">
-        <f>Planejado!B26</f>
-        <v/>
-      </c>
-      <c r="C26" s="43">
-        <f>Planejado!C26</f>
-        <v/>
-      </c>
-      <c r="D26" s="44">
-        <f>Planejado!D26</f>
-        <v/>
-      </c>
-      <c r="E26" s="44">
-        <f>Planejado!E26</f>
-        <v/>
-      </c>
-      <c r="F26" s="43">
-        <f>Planejado!F26</f>
-        <v/>
-      </c>
-      <c r="G26" s="43">
-        <f>Planejado!G26</f>
-        <v/>
-      </c>
-      <c r="H26" s="45" t="n"/>
-      <c r="I26" s="45" t="n"/>
-      <c r="J26" s="45" t="n"/>
-      <c r="K26" s="45" t="n"/>
-      <c r="L26" s="45" t="n"/>
-      <c r="M26" s="45" t="n"/>
-      <c r="N26" s="45" t="n"/>
-      <c r="O26" s="45" t="n"/>
-      <c r="T26" s="41">
-        <f>SUM(H26:S26)</f>
-        <v/>
-      </c>
-      <c r="U26" s="46" t="n"/>
-      <c r="V26" s="46" t="n"/>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="43">
-        <f>Planejado!A27</f>
-        <v/>
-      </c>
-      <c r="B27" s="43">
-        <f>Planejado!B27</f>
-        <v/>
-      </c>
-      <c r="C27" s="43">
-        <f>Planejado!C27</f>
-        <v/>
-      </c>
-      <c r="D27" s="44">
-        <f>Planejado!D27</f>
-        <v/>
-      </c>
-      <c r="E27" s="44">
-        <f>Planejado!E27</f>
-        <v/>
-      </c>
-      <c r="F27" s="43">
-        <f>Planejado!F27</f>
-        <v/>
-      </c>
-      <c r="G27" s="43">
-        <f>Planejado!G27</f>
-        <v/>
-      </c>
-      <c r="H27" s="45" t="n"/>
-      <c r="I27" s="45" t="n"/>
-      <c r="J27" s="45" t="n"/>
-      <c r="K27" s="45" t="n"/>
-      <c r="L27" s="45" t="n"/>
-      <c r="M27" s="45" t="n"/>
-      <c r="N27" s="45" t="n"/>
-      <c r="O27" s="45" t="n"/>
-      <c r="T27" s="41">
-        <f>SUM(H27:S27)</f>
-        <v/>
-      </c>
-      <c r="U27" s="46" t="n"/>
-      <c r="V27" s="46" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="47" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="47" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B28" s="47" t="n"/>
-      <c r="C28" s="47" t="n"/>
-      <c r="D28" s="47" t="n"/>
-      <c r="E28" s="47" t="n"/>
-      <c r="F28" s="47" t="n"/>
-      <c r="G28" s="47" t="n"/>
-      <c r="H28" s="48">
-        <f>SUM(H5:H27)</f>
-        <v/>
-      </c>
-      <c r="I28" s="48">
-        <f>SUM(I5:I27)</f>
-        <v/>
-      </c>
-      <c r="J28" s="48">
-        <f>SUM(J5:J27)</f>
-        <v/>
-      </c>
-      <c r="K28" s="48">
-        <f>SUM(K5:K27)</f>
-        <v/>
-      </c>
-      <c r="L28" s="48">
-        <f>SUM(L5:L27)</f>
-        <v/>
-      </c>
-      <c r="M28" s="48">
-        <f>SUM(M5:M27)</f>
-        <v/>
-      </c>
-      <c r="N28" s="48">
-        <f>SUM(N5:N27)</f>
-        <v/>
-      </c>
-      <c r="O28" s="48">
-        <f>SUM(O5:O27)</f>
-        <v/>
-      </c>
-      <c r="P28" s="48">
-        <f>SUM(P5:P27)</f>
-        <v/>
-      </c>
-      <c r="Q28" s="48">
-        <f>SUM(Q5:Q27)</f>
-        <v/>
-      </c>
-      <c r="R28" s="48">
-        <f>SUM(R5:R27)</f>
-        <v/>
-      </c>
-      <c r="S28" s="48">
-        <f>SUM(S5:S27)</f>
-        <v/>
-      </c>
-      <c r="T28" s="48">
-        <f>SUM(T5:T27)</f>
-        <v/>
-      </c>
-      <c r="U28" s="47" t="n"/>
-      <c r="V28" s="47" t="n"/>
+      <c r="B26" s="47" t="n"/>
+      <c r="C26" s="47" t="n"/>
+      <c r="D26" s="47" t="n"/>
+      <c r="E26" s="47" t="n"/>
+      <c r="F26" s="47" t="n"/>
+      <c r="G26" s="47" t="n"/>
+      <c r="H26" s="48">
+        <f>SUM(H5:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="48">
+        <f>SUM(I5:I25)</f>
+        <v/>
+      </c>
+      <c r="J26" s="48">
+        <f>SUM(J5:J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="48">
+        <f>SUM(K5:K25)</f>
+        <v/>
+      </c>
+      <c r="L26" s="48">
+        <f>SUM(L5:L25)</f>
+        <v/>
+      </c>
+      <c r="M26" s="48">
+        <f>SUM(M5:M25)</f>
+        <v/>
+      </c>
+      <c r="N26" s="48">
+        <f>SUM(N5:N25)</f>
+        <v/>
+      </c>
+      <c r="O26" s="48">
+        <f>SUM(O5:O25)</f>
+        <v/>
+      </c>
+      <c r="P26" s="48">
+        <f>SUM(P5:P25)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="48">
+        <f>SUM(Q5:Q25)</f>
+        <v/>
+      </c>
+      <c r="R26" s="48">
+        <f>SUM(R5:R25)</f>
+        <v/>
+      </c>
+      <c r="S26" s="48">
+        <f>SUM(S5:S25)</f>
+        <v/>
+      </c>
+      <c r="T26" s="48">
+        <f>SUM(T5:T25)</f>
+        <v/>
+      </c>
+      <c r="U26" s="47" t="n"/>
+      <c r="V26" s="47" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6746,19 +6344,19 @@
         </is>
       </c>
       <c r="B5" s="30">
-        <f>SUMIFS(Planejado!$H$5:$H$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="30">
-        <f>SUMIFS(Realizado!$H$5:$H$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="30">
-        <f>SUMIFS(Planejado!$H$5:$H$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="30">
-        <f>SUMIFS(Realizado!$H$5:$H$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="30">
@@ -6789,19 +6387,19 @@
         </is>
       </c>
       <c r="B6" s="36">
-        <f>SUMIFS(Planejado!$I$5:$I$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="36">
-        <f>SUMIFS(Realizado!$I$5:$I$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="36">
-        <f>SUMIFS(Planejado!$I$5:$I$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="36">
-        <f>SUMIFS(Realizado!$I$5:$I$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="36">
@@ -6832,19 +6430,19 @@
         </is>
       </c>
       <c r="B7" s="30">
-        <f>SUMIFS(Planejado!$J$5:$J$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="30">
-        <f>SUMIFS(Realizado!$J$5:$J$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="30">
-        <f>SUMIFS(Planejado!$J$5:$J$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="30">
-        <f>SUMIFS(Realizado!$J$5:$J$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="30">
@@ -6875,19 +6473,19 @@
         </is>
       </c>
       <c r="B8" s="36">
-        <f>SUMIFS(Planejado!$K$5:$K$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="36">
-        <f>SUMIFS(Realizado!$K$5:$K$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="36">
-        <f>SUMIFS(Planejado!$K$5:$K$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="36">
-        <f>SUMIFS(Realizado!$K$5:$K$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="36">
@@ -6918,19 +6516,19 @@
         </is>
       </c>
       <c r="B9" s="30">
-        <f>SUMIFS(Planejado!$L$5:$L$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="30">
-        <f>SUMIFS(Realizado!$L$5:$L$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="30">
-        <f>SUMIFS(Planejado!$L$5:$L$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="30">
-        <f>SUMIFS(Realizado!$L$5:$L$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="30">
@@ -6961,19 +6559,19 @@
         </is>
       </c>
       <c r="B10" s="36">
-        <f>SUMIFS(Planejado!$M$5:$M$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="36">
-        <f>SUMIFS(Realizado!$M$5:$M$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="36">
-        <f>SUMIFS(Planejado!$M$5:$M$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="36">
-        <f>SUMIFS(Realizado!$M$5:$M$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="36">
@@ -7004,19 +6602,19 @@
         </is>
       </c>
       <c r="B11" s="30">
-        <f>SUMIFS(Planejado!$N$5:$N$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="30">
-        <f>SUMIFS(Realizado!$N$5:$N$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="30">
-        <f>SUMIFS(Planejado!$N$5:$N$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="30">
-        <f>SUMIFS(Realizado!$N$5:$N$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="30">
@@ -7047,19 +6645,19 @@
         </is>
       </c>
       <c r="B12" s="36">
-        <f>SUMIFS(Planejado!$O$5:$O$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C12" s="36">
-        <f>SUMIFS(Realizado!$O$5:$O$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D12" s="36">
-        <f>SUMIFS(Planejado!$O$5:$O$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E12" s="36">
-        <f>SUMIFS(Realizado!$O$5:$O$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F12" s="36">
@@ -7090,19 +6688,19 @@
         </is>
       </c>
       <c r="B13" s="30">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C13" s="30">
-        <f>SUMIFS(Realizado!$P$5:$P$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D13" s="30">
-        <f>SUMIFS(Planejado!$P$5:$P$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E13" s="30">
-        <f>SUMIFS(Realizado!$P$5:$P$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F13" s="30">
@@ -7133,19 +6731,19 @@
         </is>
       </c>
       <c r="B14" s="36">
-        <f>SUMIFS(Planejado!$Q$5:$Q$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C14" s="36">
-        <f>SUMIFS(Realizado!$Q$5:$Q$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D14" s="36">
-        <f>SUMIFS(Planejado!$Q$5:$Q$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E14" s="36">
-        <f>SUMIFS(Realizado!$Q$5:$Q$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F14" s="36">
@@ -7176,19 +6774,19 @@
         </is>
       </c>
       <c r="B15" s="30">
-        <f>SUMIFS(Planejado!$R$5:$R$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C15" s="30">
-        <f>SUMIFS(Realizado!$R$5:$R$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D15" s="30">
-        <f>SUMIFS(Planejado!$R$5:$R$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E15" s="30">
-        <f>SUMIFS(Realizado!$R$5:$R$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F15" s="30">
@@ -7219,19 +6817,19 @@
         </is>
       </c>
       <c r="B16" s="36">
-        <f>SUMIFS(Planejado!$S$5:$S$27,Planejado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="C16" s="36">
-        <f>SUMIFS(Realizado!$S$5:$S$27,Realizado!$B$5:$B$27,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
       <c r="D16" s="36">
-        <f>SUMIFS(Planejado!$S$5:$S$27,Planejado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="E16" s="36">
-        <f>SUMIFS(Realizado!$S$5:$S$27,Realizado!$B$5:$B$27,"TI")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
       <c r="F16" s="36">
@@ -7316,7 +6914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7404,19 +7002,19 @@
         </is>
       </c>
       <c r="B5" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A5,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A5,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A5,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A5,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="30">
@@ -7436,30 +7034,30 @@
         <v/>
       </c>
       <c r="J5" s="30">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="53" t="inlineStr">
         <is>
-          <t>Encargos e Benefícios - CLT</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="B6" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A6,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A6,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A6,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A6,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="36">
@@ -7479,30 +7077,30 @@
         <v/>
       </c>
       <c r="J6" s="36">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="51" t="inlineStr">
         <is>
-          <t>Pessoal - PJ</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="B7" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A7,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A7,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A7,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A7,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="30">
@@ -7522,30 +7120,30 @@
         <v/>
       </c>
       <c r="J7" s="30">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="53" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="B8" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A8,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A8,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A8,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A8,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="36">
@@ -7565,30 +7163,30 @@
         <v/>
       </c>
       <c r="J8" s="36">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="51" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Prêmios</t>
         </is>
       </c>
       <c r="B9" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A9,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A9,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A9,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A9,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="30">
@@ -7608,30 +7206,30 @@
         <v/>
       </c>
       <c r="J9" s="30">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A9)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="53" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
       <c r="B10" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A10,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A10,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A10,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A10,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="36">
@@ -7651,30 +7249,30 @@
         <v/>
       </c>
       <c r="J10" s="36">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A10)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="51" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos Diversos</t>
+          <t>Móveis e Utensílios</t>
         </is>
       </c>
       <c r="B11" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A11,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A11,Comparativo!$B$6:$B$28,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="30">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A11,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="30">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A11,Comparativo!$B$6:$B$28,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="30">
@@ -7694,93 +7292,50 @@
         <v/>
       </c>
       <c r="J11" s="30">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="53" t="inlineStr">
-        <is>
-          <t>Móveis e Utensílios</t>
-        </is>
-      </c>
-      <c r="B12" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A12,Comparativo!$B$6:$B$28,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="C12" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A12,Comparativo!$B$6:$B$28,"Jurídico")</f>
-        <v/>
-      </c>
-      <c r="D12" s="36">
-        <f>SUMIFS(Comparativo!$I$6:$I$28,Comparativo!$E$6:$E$28,$A12,Comparativo!$B$6:$B$28,"TI")</f>
-        <v/>
-      </c>
-      <c r="E12" s="36">
-        <f>SUMIFS(Comparativo!$J$6:$J$28,Comparativo!$E$6:$E$28,$A12,Comparativo!$B$6:$B$28,"TI")</f>
-        <v/>
-      </c>
-      <c r="F12" s="36">
-        <f>B12+D12</f>
-        <v/>
-      </c>
-      <c r="G12" s="36">
-        <f>C12+E12</f>
-        <v/>
-      </c>
-      <c r="H12" s="36">
-        <f>G12-F12</f>
-        <v/>
-      </c>
-      <c r="I12" s="54">
+        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B12" s="16">
+        <f>SUM(B5:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="16">
+        <f>SUM(C5:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="16">
+        <f>SUM(D5:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="16">
+        <f>SUM(E5:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="16">
+        <f>SUM(F5:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="16">
+        <f>SUM(G5:G11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="16">
+        <f>SUM(H5:H11)</f>
+        <v/>
+      </c>
+      <c r="I12" s="17">
         <f>IFERROR(H12/F12,"")</f>
         <v/>
       </c>
-      <c r="J12" s="36">
-        <f>SUMIFS(Planejado!$T$5:$T$27,Planejado!$G$5:$G$27,$A12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" s="16">
-        <f>SUM(B5:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="16">
-        <f>SUM(C5:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="16">
-        <f>SUM(D5:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>SUM(E5:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>SUM(F5:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="16">
-        <f>SUM(G5:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="16">
-        <f>SUM(H5:H12)</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>IFERROR(H13/F13,"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="16">
-        <f>SUM(J5:J12)</f>
+      <c r="J12" s="16">
+        <f>SUM(J5:J11)</f>
         <v/>
       </c>
     </row>
@@ -7789,7 +7344,7 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H12">
+  <conditionalFormatting sqref="H5:H11">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -7872,17 +7427,17 @@
       </c>
       <c r="B5" s="56" t="inlineStr">
         <is>
-          <t>Encargos da Geovanna — CAMPO A PREENCHER</t>
+          <t>Custo total da Geovanna — A LANÇAR</t>
         </is>
       </c>
       <c r="C5" s="56" t="inlineStr">
         <is>
-          <t>A linha JUR-E02B recebe os encargos e benefícios sobre o salário bruto (INSS patronal, FGTS, provisões de 13º e férias, VT/VR, plano de saúde). Hoje está em branco.</t>
+          <t>O planejado dela é R$ 4.825,52/mês, que é o custo total orçado na ficha (salário + encargos de folha + benefícios). O dado disponível hoje é só o salário bruto, R$ 2.886,91/mês. O realizado está em branco.</t>
         </is>
       </c>
       <c r="D5" s="56" t="inlineStr">
         <is>
-          <t>Enquanto não for preenchida, a folha do Jurídico aparece R$ 1.938,61/mês abaixo do orçado — economia que não existe, é só encargo não lançado.</t>
+          <t>Lançar só o bruto contra um orçado de custo total mostraria economia de R$ 1.938,61/mês que não existe. Peça ao RH o custo total mensal dela, ou o bruto mais os encargos para somar antes de lançar.</t>
         </is>
       </c>
       <c r="E5" s="56" t="inlineStr">
@@ -7892,7 +7447,7 @@
       </c>
       <c r="F5" s="57" t="inlineStr">
         <is>
-          <t>PREENCHER</t>
+          <t>A LANÇAR</t>
         </is>
       </c>
     </row>
@@ -7904,17 +7459,17 @@
       </c>
       <c r="B6" s="59" t="inlineStr">
         <is>
-          <t>Encargos do Vinicius — CAMPO A PREENCHER</t>
+          <t>Custo total do Vinicius — A LANÇAR</t>
         </is>
       </c>
       <c r="C6" s="59" t="inlineStr">
         <is>
-          <t>A linha TI-E01B recebe os encargos e benefícios sobre o salário bruto, mesmo tratamento dado à Geovanna. Hoje está em branco. Brutos confirmados pela gestora: R$ 2.570,52 até jul/26 e R$ 3.070,52 a partir de 05/08/26. O envelope orçado permanece em R$ 5.416,525/mês — o aumento foi absorvido pela folga, não somado ao orçamento.</t>
+          <t>Mesmo caso da Geovanna. O planejado é R$ 5.416,525/mês (custo total). Brutos confirmados: R$ 2.570,52 até jul/26 e R$ 3.070,52 a partir de 05/08/26 — o aumento é absorvido pela folga do envelope, que já previa reajuste, então o orçado não muda. O realizado está em branco.</t>
         </is>
       </c>
       <c r="D6" s="59" t="inlineStr">
         <is>
-          <t>A folga do orçado NÃO é economia estrutural: o custo total foi dimensionado prevendo um aumento maior, ainda não concedido. Com o bruto de agosto, o orçado de encargos (R$ 2.346,01) equivale a 76% sobre o bruto — dentro da faixa normal (67% a 80%), então pode sobrar ou estourar.</t>
+          <t>A folga do orçado NÃO é economia estrutural. Com o bruto de agosto, sobram R$ 2.346,01 para encargos, o que equivale a 76% sobre o bruto — dentro da faixa normal (67% a 80%), então pode sobrar ou estourar. Só o custo total real vai dizer.</t>
         </is>
       </c>
       <c r="E6" s="59" t="inlineStr">
@@ -7924,7 +7479,7 @@
       </c>
       <c r="F6" s="57" t="inlineStr">
         <is>
-          <t>PREENCHER</t>
+          <t>A LANÇAR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -5145,10 +5145,18 @@
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="H5" s="45" t="n"/>
-      <c r="I5" s="45" t="n"/>
-      <c r="J5" s="45" t="n"/>
-      <c r="K5" s="45" t="n"/>
+      <c r="H5" s="45" t="n">
+        <v>8818</v>
+      </c>
+      <c r="I5" s="45" t="n">
+        <v>8818</v>
+      </c>
+      <c r="J5" s="45" t="n">
+        <v>8818</v>
+      </c>
+      <c r="K5" s="45" t="n">
+        <v>8818</v>
+      </c>
       <c r="L5" s="45" t="n">
         <v>8818</v>
       </c>
@@ -5251,10 +5259,18 @@
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="H7" s="45" t="n"/>
-      <c r="I7" s="45" t="n"/>
-      <c r="J7" s="45" t="n"/>
-      <c r="K7" s="45" t="n"/>
+      <c r="H7" s="45" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I7" s="45" t="n">
+        <v>5500</v>
+      </c>
+      <c r="J7" s="45" t="n">
+        <v>5500</v>
+      </c>
+      <c r="K7" s="45" t="n">
+        <v>5500</v>
+      </c>
       <c r="L7" s="45" t="n">
         <v>5500</v>
       </c>
@@ -5309,10 +5325,18 @@
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="H8" s="45" t="n"/>
-      <c r="I8" s="45" t="n"/>
-      <c r="J8" s="45" t="n"/>
-      <c r="K8" s="45" t="n"/>
+      <c r="H8" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="45" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="45" t="n">
         <v>0</v>
       </c>
@@ -5367,10 +5391,18 @@
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="H9" s="45" t="n"/>
-      <c r="I9" s="45" t="n"/>
-      <c r="J9" s="45" t="n"/>
-      <c r="K9" s="45" t="n"/>
+      <c r="H9" s="45" t="n">
+        <v>136</v>
+      </c>
+      <c r="I9" s="45" t="n">
+        <v>136</v>
+      </c>
+      <c r="J9" s="45" t="n">
+        <v>136</v>
+      </c>
+      <c r="K9" s="45" t="n">
+        <v>136</v>
+      </c>
       <c r="L9" s="45" t="n">
         <v>136</v>
       </c>
@@ -5425,10 +5457,18 @@
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="H10" s="45" t="n"/>
-      <c r="I10" s="45" t="n"/>
-      <c r="J10" s="45" t="n"/>
-      <c r="K10" s="45" t="n"/>
+      <c r="H10" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="45" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="45" t="n">
         <v>0</v>
       </c>
@@ -5483,10 +5523,18 @@
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="H11" s="45" t="n"/>
-      <c r="I11" s="45" t="n"/>
-      <c r="J11" s="45" t="n"/>
-      <c r="K11" s="45" t="n"/>
+      <c r="H11" s="45" t="n">
+        <v>970</v>
+      </c>
+      <c r="I11" s="45" t="n">
+        <v>970</v>
+      </c>
+      <c r="J11" s="45" t="n">
+        <v>970</v>
+      </c>
+      <c r="K11" s="45" t="n">
+        <v>970</v>
+      </c>
       <c r="L11" s="45" t="n">
         <v>970</v>
       </c>
@@ -5537,10 +5585,18 @@
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="H12" s="45" t="n"/>
-      <c r="I12" s="45" t="n"/>
-      <c r="J12" s="45" t="n"/>
-      <c r="K12" s="45" t="n"/>
+      <c r="H12" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="45" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="45" t="n">
         <v>0</v>
       </c>
@@ -5595,22 +5651,40 @@
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="H13" s="45" t="n"/>
-      <c r="I13" s="45" t="n"/>
-      <c r="J13" s="45" t="n"/>
-      <c r="K13" s="45" t="n"/>
-      <c r="L13" s="45" t="n"/>
-      <c r="M13" s="45" t="n"/>
-      <c r="N13" s="45" t="n"/>
+      <c r="H13" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="45" t="n">
+        <v>0</v>
+      </c>
       <c r="O13" s="45" t="n"/>
       <c r="T13" s="41">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
-      <c r="U13" s="46" t="n"/>
+      <c r="U13" s="46" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
       <c r="V13" s="46" t="inlineStr">
         <is>
-          <t>Bonificação de ago/26 a confirmar</t>
+          <t>Sem parcela no 1º semestre; bonificação de ago/26 a confirmar</t>
         </is>
       </c>
     </row>
@@ -5691,10 +5765,18 @@
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="H15" s="45" t="n"/>
-      <c r="I15" s="45" t="n"/>
-      <c r="J15" s="45" t="n"/>
-      <c r="K15" s="45" t="n"/>
+      <c r="H15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="45" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="45" t="n">
         <v>0</v>
       </c>
@@ -5749,10 +5831,18 @@
         <f>Planejado!G16</f>
         <v/>
       </c>
-      <c r="H16" s="45" t="n"/>
-      <c r="I16" s="45" t="n"/>
-      <c r="J16" s="45" t="n"/>
-      <c r="K16" s="45" t="n"/>
+      <c r="H16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="45" t="n">
+        <v>6300</v>
+      </c>
       <c r="L16" s="45" t="n">
         <v>6300</v>
       </c>
@@ -5774,7 +5864,7 @@
       </c>
       <c r="V16" s="46" t="inlineStr">
         <is>
-          <t>R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
+          <t>Entrada em abr/26. R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -3522,7 +3522,7 @@
       </c>
       <c r="E7" s="29" t="inlineStr">
         <is>
-          <t>Advogada — reajuste permanente de R$ 5.000 para R$ 5.500 (revisado a partir de out/26)</t>
+          <t>Advogada — recebe R$ 5.500/mês desde jan/26 contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -3557,10 +3557,10 @@
         <v>5000</v>
       </c>
       <c r="O7" s="30" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="P7" s="30" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="Q7" s="30" t="n">
         <v>5500</v>
@@ -7581,17 +7581,17 @@
       </c>
       <c r="B7" s="56" t="inlineStr">
         <is>
-          <t>Reajuste da Thamar — revisão orçamentária</t>
+          <t>Thamar acima do orçado desde janeiro</t>
         </is>
       </c>
       <c r="C7" s="56" t="inlineStr">
         <is>
-          <t>Reajuste permanente de R$ 5.000 para R$ 5.500/mês, em vigor desde mai/26. O planejado foi mantido em R$ 5.000 nos meses já realizados (para o desvio ficar visível) e revisado para R$ 5.500 de out a dez.</t>
+          <t>Recebe R$ 5.500/mês desde jan/26 contra R$ 5.000 orçados. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
         </is>
       </c>
       <c r="D7" s="56" t="inlineStr">
         <is>
-          <t>Desvio já incorrido de R$ 500/mês. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
+          <t>R$ 3.500 já gastos acima do orçado em jan–jul, e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela. Orçamento do Jurídico sobe para R$ 291.730,42.</t>
         </is>
       </c>
       <c r="E7" s="56" t="inlineStr">

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -3522,7 +3522,7 @@
       </c>
       <c r="E7" s="29" t="inlineStr">
         <is>
-          <t>Advogada — recebe R$ 5.500/mês desde jan/26 contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
+          <t>Advogada — recebia R$ 4.500/mês em jan–fev e passou a R$ 5.500 em mar/26 (aumento de R$ 1.000), contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -5260,10 +5260,10 @@
         <v/>
       </c>
       <c r="H7" s="45" t="n">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="I7" s="45" t="n">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="J7" s="45" t="n">
         <v>5500</v>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="V7" s="46" t="inlineStr">
         <is>
-          <t>Reajuste permanente aplicado desde mai/26</t>
+          <t>R$ 4.500/mês em jan–fev; aumento de R$ 1.000 a partir de mar/26</t>
         </is>
       </c>
     </row>
@@ -7581,17 +7581,17 @@
       </c>
       <c r="B7" s="56" t="inlineStr">
         <is>
-          <t>Thamar acima do orçado desde janeiro</t>
+          <t>Aumento da Thamar em mar/26</t>
         </is>
       </c>
       <c r="C7" s="56" t="inlineStr">
         <is>
-          <t>Recebe R$ 5.500/mês desde jan/26 contra R$ 5.000 orçados. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
+          <t>Recebia R$ 4.500/mês em jan e fev, abaixo dos R$ 5.000 orçados. Em mar/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
         </is>
       </c>
       <c r="D7" s="56" t="inlineStr">
         <is>
-          <t>R$ 3.500 já gastos acima do orçado em jan–jul, e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela. Orçamento do Jurídico sobe para R$ 291.730,42.</t>
+          <t>No acumulado jan–jul o efeito líquido é de R$ 1.500 acima do orçado (−R$ 1.000 em jan–fev, +R$ 2.500 em mar–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
         </is>
       </c>
       <c r="E7" s="56" t="inlineStr">

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -3522,7 +3522,7 @@
       </c>
       <c r="E7" s="29" t="inlineStr">
         <is>
-          <t>Advogada — recebia R$ 4.500/mês em jan–fev e passou a R$ 5.500 em mar/26 (aumento de R$ 1.000), contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
+          <t>Advogada — recebia R$ 4.500/mês em jan–mar e passou a R$ 5.500 em abr/26 (aumento de R$ 1.000), contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -5266,7 +5266,7 @@
         <v>4500</v>
       </c>
       <c r="J7" s="45" t="n">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="K7" s="45" t="n">
         <v>5500</v>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="V7" s="46" t="inlineStr">
         <is>
-          <t>R$ 4.500/mês em jan–fev; aumento de R$ 1.000 a partir de mar/26</t>
+          <t>R$ 4.500/mês em jan–mar; aumento de R$ 1.000 a partir de abr/26</t>
         </is>
       </c>
     </row>
@@ -7581,17 +7581,17 @@
       </c>
       <c r="B7" s="56" t="inlineStr">
         <is>
-          <t>Aumento da Thamar em mar/26</t>
+          <t>Aumento da Thamar em abr/26</t>
         </is>
       </c>
       <c r="C7" s="56" t="inlineStr">
         <is>
-          <t>Recebia R$ 4.500/mês em jan e fev, abaixo dos R$ 5.000 orçados. Em mar/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
+          <t>Recebia R$ 4.500/mês de jan a mar, abaixo dos R$ 5.000 orçados. Em abr/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
         </is>
       </c>
       <c r="D7" s="56" t="inlineStr">
         <is>
-          <t>No acumulado jan–jul o efeito líquido é de R$ 1.500 acima do orçado (−R$ 1.000 em jan–fev, +R$ 2.500 em mar–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
+          <t>No acumulado jan–jul o efeito líquido é de apenas R$ 500 acima do orçado (−R$ 1.500 em jan–mar, +R$ 2.000 em abr–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
         </is>
       </c>
       <c r="E7" s="56" t="inlineStr">

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,6 +95,11 @@
       <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
@@ -112,7 +117,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -152,6 +157,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF7DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -214,23 +224,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -241,7 +254,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -319,7 +332,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -328,19 +341,19 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1070,522 +1083,530 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>⚠ Geovanna: realizado em salário bruto; orçado em custo total — o desvio desta linha não é economia.</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Orçado do ano</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Realizado acum.</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Desvio (R$)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Desvio (%)</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>% Executado do ano</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Linhas lançadas</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="9">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"Jurídico",Planejado!$C$5:$C$25,"Equipe")</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <f>E6-D6</f>
         <v/>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="10">
         <f>IFERROR(F6/D6,"")</f>
         <v/>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <f>IFERROR(E6/C6,"")</f>
         <v/>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="11">
         <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"Jurídico",Planejado!$C$5:$C$25,"Despesas")</f>
         <v/>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="9">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="9">
         <f>E7-D7</f>
         <v/>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="10">
         <f>IFERROR(F7/D7,"")</f>
         <v/>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="10">
         <f>IFERROR(E7/C7,"")</f>
         <v/>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="11">
         <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Equipe + Despesas</t>
         </is>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>E8-D8</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <f>IFERROR(F8/D8,"")</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <f>IFERROR(E8/C8,"")</f>
         <v/>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="15">
         <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="9">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"TI",Planejado!$C$5:$C$25,"Equipe")</f>
         <v/>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="9">
         <f>E9-D9</f>
         <v/>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="10">
         <f>IFERROR(F9/D9,"")</f>
         <v/>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="10">
         <f>IFERROR(E9/C9,"")</f>
         <v/>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="11">
         <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="9">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"TI",Planejado!$C$5:$C$25,"Despesas")</f>
         <v/>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="9">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="9">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="9">
         <f>E10-D10</f>
         <v/>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="10">
         <f>IFERROR(F10/D10,"")</f>
         <v/>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="10">
         <f>IFERROR(E10/C10,"")</f>
         <v/>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="11">
         <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Equipe + Despesas</t>
         </is>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>E11-D11</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="14">
         <f>IFERROR(F11/D11,"")</f>
         <v/>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <f>IFERROR(E11/C11,"")</f>
         <v/>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="15">
         <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr"/>
-      <c r="C12" s="16">
+      <c r="B12" s="16" t="inlineStr"/>
+      <c r="C12" s="17">
         <f>SUM(Planejado!$T$5:$T$25)</f>
         <v/>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="17">
         <f>SUM(Comparativo!$I$6:$I$26)</f>
         <v/>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="17">
         <f>SUM(Comparativo!$J$6:$J$26)</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="17">
         <f>E12-D12</f>
         <v/>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="18">
         <f>IFERROR(F12/D12,"")</f>
         <v/>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="18">
         <f>IFERROR(E12/C12,"")</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="19">
         <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$26)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>MAIORES DESVIOS DO ACUMULADO (top 5 acima do orçado)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Realizado acum.</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Desvio (R$)</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Desvio (%)</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="22">
         <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="22">
         <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="23">
         <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="23">
         <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="23">
         <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="24">
         <f>IFERROR(F17/D17,"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="22">
         <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="22">
         <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="23">
         <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="23">
         <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="23">
         <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="24">
         <f>IFERROR(F18/D18,"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="n">
+      <c r="A19" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="22">
         <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="22">
         <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="23">
         <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="23">
         <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="23">
         <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="24">
         <f>IFERROR(F19/D19,"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="22">
         <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="22">
         <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="23">
         <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="23">
         <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="23">
         <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="24">
         <f>IFERROR(F20/D20,"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="n">
+      <c r="A21" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="22">
         <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="22">
         <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="23">
         <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="23">
         <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="23">
         <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
         <v/>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="24">
         <f>IFERROR(F21/D21,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A15:H15"/>
   </mergeCells>
@@ -1640,1532 +1661,1533 @@
           <t>Mês de referência:</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>Mês nº:</t>
         </is>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="27">
         <f>MATCH($B$3,Planejado!$H$4:$S$4,0)</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Planejado no mês</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Realizado no mês</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Desvio no mês (R$)</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Realizado acum.</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Desvio acum. (R$)</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>Desvio acum. (%)</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Situação</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="28" t="inlineStr">
         <is>
           <t>(aux ranking)</t>
         </is>
       </c>
-      <c r="P5" s="27" t="inlineStr">
+      <c r="P5" s="28" t="inlineStr">
         <is>
           <t>(aux meses lançados)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="28">
+      <c r="A6" s="29">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="29">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="29">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="29">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>INDEX(Planejado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="31">
         <f>INDEX(Realizado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="31">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="31">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H5:$S5)</f>
         <v/>
       </c>
-      <c r="J6" s="30">
+      <c r="J6" s="31">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H5:$S5)</f>
         <v/>
       </c>
-      <c r="K6" s="30">
+      <c r="K6" s="31">
         <f>J6-I6</f>
         <v/>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="32">
         <f>IFERROR(K6/I6,"")</f>
         <v/>
       </c>
-      <c r="M6" s="31">
+      <c r="M6" s="32">
         <f>IFERROR(J6/I6,"")</f>
         <v/>
       </c>
-      <c r="N6" s="32">
+      <c r="N6" s="33">
         <f>IF(P6=0,"Sem lançamento",IF(AND(I6=0,J6=0),"—",IF(I6=0,"Não orçado",IF(K6&gt;0.05*I6,"Acima do orçado",IF(K6&lt;-0.05*I6,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O6" s="27">
+      <c r="O6" s="28">
         <f>IF(K6&gt;1,K6+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P6" s="33">
+      <c r="P6" s="34">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H5:$S5&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="28">
+      <c r="A7" s="29">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="29">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="29">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>INDEX(Planejado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <f>INDEX(Realizado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H6:$S6)</f>
         <v/>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="31">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H6:$S6)</f>
         <v/>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="31">
         <f>J7-I7</f>
         <v/>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="32">
         <f>IFERROR(K7/I7,"")</f>
         <v/>
       </c>
-      <c r="M7" s="31">
+      <c r="M7" s="32">
         <f>IFERROR(J7/I7,"")</f>
         <v/>
       </c>
-      <c r="N7" s="32">
-        <f>IF(P7=0,"Sem lançamento",IF(AND(I7=0,J7=0),"—",IF(I7=0,"Não orçado",IF(K7&gt;0.05*I7,"Acima do orçado",IF(K7&lt;-0.05*I7,"Abaixo do orçado","Dentro do orçado")))))</f>
-        <v/>
-      </c>
-      <c r="O7" s="27">
+      <c r="N7" s="33" t="inlineStr">
+        <is>
+          <t>⚠ Base diferente</t>
+        </is>
+      </c>
+      <c r="O7" s="28">
         <f>IF(K7&gt;1,K7+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P7" s="33">
+      <c r="P7" s="34">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H6:$S6&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="28">
+      <c r="A8" s="29">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="29">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>INDEX(Planejado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <f>INDEX(Realizado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="31">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H7:$S7)</f>
         <v/>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="31">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H7:$S7)</f>
         <v/>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="31">
         <f>J8-I8</f>
         <v/>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="32">
         <f>IFERROR(K8/I8,"")</f>
         <v/>
       </c>
-      <c r="M8" s="31">
+      <c r="M8" s="32">
         <f>IFERROR(J8/I8,"")</f>
         <v/>
       </c>
-      <c r="N8" s="32">
+      <c r="N8" s="33">
         <f>IF(P8=0,"Sem lançamento",IF(AND(I8=0,J8=0),"—",IF(I8=0,"Não orçado",IF(K8&gt;0.05*I8,"Acima do orçado",IF(K8&lt;-0.05*I8,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="28">
         <f>IF(K8&gt;1,K8+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P8" s="33">
+      <c r="P8" s="34">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H7:$S7&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="28">
+      <c r="A9" s="29">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="29">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>INDEX(Planejado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <f>INDEX(Realizado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H8:$S8)</f>
         <v/>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="31">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H8:$S8)</f>
         <v/>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="31">
         <f>J9-I9</f>
         <v/>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="32">
         <f>IFERROR(K9/I9,"")</f>
         <v/>
       </c>
-      <c r="M9" s="31">
+      <c r="M9" s="32">
         <f>IFERROR(J9/I9,"")</f>
         <v/>
       </c>
-      <c r="N9" s="32">
+      <c r="N9" s="33">
         <f>IF(P9=0,"Sem lançamento",IF(AND(I9=0,J9=0),"—",IF(I9=0,"Não orçado",IF(K9&gt;0.05*I9,"Acima do orçado",IF(K9&lt;-0.05*I9,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O9" s="27">
+      <c r="O9" s="28">
         <f>IF(K9&gt;1,K9+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P9" s="33">
+      <c r="P9" s="34">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H8:$S8&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="28">
+      <c r="A10" s="29">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>INDEX(Planejado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <f>INDEX(Realizado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="31">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="31">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H9:$S9)</f>
         <v/>
       </c>
-      <c r="J10" s="30">
+      <c r="J10" s="31">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H9:$S9)</f>
         <v/>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="31">
         <f>J10-I10</f>
         <v/>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="32">
         <f>IFERROR(K10/I10,"")</f>
         <v/>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="32">
         <f>IFERROR(J10/I10,"")</f>
         <v/>
       </c>
-      <c r="N10" s="32">
+      <c r="N10" s="33">
         <f>IF(P10=0,"Sem lançamento",IF(AND(I10=0,J10=0),"—",IF(I10=0,"Não orçado",IF(K10&gt;0.05*I10,"Acima do orçado",IF(K10&lt;-0.05*I10,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O10" s="27">
+      <c r="O10" s="28">
         <f>IF(K10&gt;1,K10+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P10" s="33">
+      <c r="P10" s="34">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H9:$S9&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="28">
+      <c r="A11" s="29">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="29">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="29">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>INDEX(Planejado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <f>INDEX(Realizado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="31">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H10:$S10)</f>
         <v/>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="31">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H10:$S10)</f>
         <v/>
       </c>
-      <c r="K11" s="30">
+      <c r="K11" s="31">
         <f>J11-I11</f>
         <v/>
       </c>
-      <c r="L11" s="31">
+      <c r="L11" s="32">
         <f>IFERROR(K11/I11,"")</f>
         <v/>
       </c>
-      <c r="M11" s="31">
+      <c r="M11" s="32">
         <f>IFERROR(J11/I11,"")</f>
         <v/>
       </c>
-      <c r="N11" s="32">
+      <c r="N11" s="33">
         <f>IF(P11=0,"Sem lançamento",IF(AND(I11=0,J11=0),"—",IF(I11=0,"Não orçado",IF(K11&gt;0.05*I11,"Acima do orçado",IF(K11&lt;-0.05*I11,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O11" s="27">
+      <c r="O11" s="28">
         <f>IF(K11&gt;1,K11+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P11" s="33">
+      <c r="P11" s="34">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H10:$S10&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="28">
+      <c r="A12" s="29">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="29">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>INDEX(Planejado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="31">
         <f>INDEX(Realizado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="31">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="31">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H11:$S11)</f>
         <v/>
       </c>
-      <c r="J12" s="30">
+      <c r="J12" s="31">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H11:$S11)</f>
         <v/>
       </c>
-      <c r="K12" s="30">
+      <c r="K12" s="31">
         <f>J12-I12</f>
         <v/>
       </c>
-      <c r="L12" s="31">
+      <c r="L12" s="32">
         <f>IFERROR(K12/I12,"")</f>
         <v/>
       </c>
-      <c r="M12" s="31">
+      <c r="M12" s="32">
         <f>IFERROR(J12/I12,"")</f>
         <v/>
       </c>
-      <c r="N12" s="32">
+      <c r="N12" s="33">
         <f>IF(P12=0,"Sem lançamento",IF(AND(I12=0,J12=0),"—",IF(I12=0,"Não orçado",IF(K12&gt;0.05*I12,"Acima do orçado",IF(K12&lt;-0.05*I12,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O12" s="27">
+      <c r="O12" s="28">
         <f>IF(K12&gt;1,K12+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P12" s="33">
+      <c r="P12" s="34">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H11:$S11&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="28">
+      <c r="A13" s="29">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="29">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>INDEX(Planejado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <f>INDEX(Realizado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="31">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H12:$S12)</f>
         <v/>
       </c>
-      <c r="J13" s="30">
+      <c r="J13" s="31">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H12:$S12)</f>
         <v/>
       </c>
-      <c r="K13" s="30">
+      <c r="K13" s="31">
         <f>J13-I13</f>
         <v/>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="32">
         <f>IFERROR(K13/I13,"")</f>
         <v/>
       </c>
-      <c r="M13" s="31">
+      <c r="M13" s="32">
         <f>IFERROR(J13/I13,"")</f>
         <v/>
       </c>
-      <c r="N13" s="32">
+      <c r="N13" s="33">
         <f>IF(P13=0,"Sem lançamento",IF(AND(I13=0,J13=0),"—",IF(I13=0,"Não orçado",IF(K13&gt;0.05*I13,"Acima do orçado",IF(K13&lt;-0.05*I13,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O13" s="27">
+      <c r="O13" s="28">
         <f>IF(K13&gt;1,K13+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P13" s="33">
+      <c r="P13" s="34">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H12:$S12&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="28">
+      <c r="A14" s="29">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="29">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="29">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="29">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>INDEX(Planejado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <f>INDEX(Realizado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="31">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H13:$S13)</f>
         <v/>
       </c>
-      <c r="J14" s="30">
+      <c r="J14" s="31">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H13:$S13)</f>
         <v/>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="31">
         <f>J14-I14</f>
         <v/>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="32">
         <f>IFERROR(K14/I14,"")</f>
         <v/>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="32">
         <f>IFERROR(J14/I14,"")</f>
         <v/>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="33">
         <f>IF(P14=0,"Sem lançamento",IF(AND(I14=0,J14=0),"—",IF(I14=0,"Não orçado",IF(K14&gt;0.05*I14,"Acima do orçado",IF(K14&lt;-0.05*I14,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O14" s="27">
+      <c r="O14" s="28">
         <f>IF(K14&gt;1,K14+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P14" s="33">
+      <c r="P14" s="34">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H13:$S13&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="34">
+      <c r="A15" s="35">
         <f>Planejado!A14</f>
         <v/>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <f>Planejado!B14</f>
         <v/>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>Planejado!C14</f>
         <v/>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <f>Planejado!D14</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>Planejado!G14</f>
         <v/>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="37">
         <f>INDEX(Planejado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="37">
         <f>INDEX(Realizado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="37">
         <f>G15-F15</f>
         <v/>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H14:$S14)</f>
         <v/>
       </c>
-      <c r="J15" s="36">
+      <c r="J15" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H14:$S14)</f>
         <v/>
       </c>
-      <c r="K15" s="36">
+      <c r="K15" s="37">
         <f>J15-I15</f>
         <v/>
       </c>
-      <c r="L15" s="37">
+      <c r="L15" s="38">
         <f>IFERROR(K15/I15,"")</f>
         <v/>
       </c>
-      <c r="M15" s="37">
+      <c r="M15" s="38">
         <f>IFERROR(J15/I15,"")</f>
         <v/>
       </c>
-      <c r="N15" s="38">
+      <c r="N15" s="39">
         <f>IF(P15=0,"Sem lançamento",IF(AND(I15=0,J15=0),"—",IF(I15=0,"Não orçado",IF(K15&gt;0.05*I15,"Acima do orçado",IF(K15&lt;-0.05*I15,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O15" s="27">
+      <c r="O15" s="28">
         <f>IF(K15&gt;1,K15+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P15" s="39">
+      <c r="P15" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H14:$S14&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="34">
+      <c r="A16" s="35">
         <f>Planejado!A15</f>
         <v/>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="35">
         <f>Planejado!B15</f>
         <v/>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="35">
         <f>Planejado!C15</f>
         <v/>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="36">
         <f>Planejado!D15</f>
         <v/>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="35">
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="37">
         <f>INDEX(Planejado!$H15:$S15,$D$3)</f>
         <v/>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="37">
         <f>INDEX(Realizado!$H15:$S15,$D$3)</f>
         <v/>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="37">
         <f>G16-F16</f>
         <v/>
       </c>
-      <c r="I16" s="36">
+      <c r="I16" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H15:$S15)</f>
         <v/>
       </c>
-      <c r="J16" s="36">
+      <c r="J16" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H15:$S15)</f>
         <v/>
       </c>
-      <c r="K16" s="36">
+      <c r="K16" s="37">
         <f>J16-I16</f>
         <v/>
       </c>
-      <c r="L16" s="37">
+      <c r="L16" s="38">
         <f>IFERROR(K16/I16,"")</f>
         <v/>
       </c>
-      <c r="M16" s="37">
+      <c r="M16" s="38">
         <f>IFERROR(J16/I16,"")</f>
         <v/>
       </c>
-      <c r="N16" s="38">
+      <c r="N16" s="39">
         <f>IF(P16=0,"Sem lançamento",IF(AND(I16=0,J16=0),"—",IF(I16=0,"Não orçado",IF(K16&gt;0.05*I16,"Acima do orçado",IF(K16&lt;-0.05*I16,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O16" s="27">
+      <c r="O16" s="28">
         <f>IF(K16&gt;1,K16+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P16" s="39">
+      <c r="P16" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H15:$S15&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="34">
+      <c r="A17" s="35">
         <f>Planejado!A16</f>
         <v/>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="35">
         <f>Planejado!B16</f>
         <v/>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="35">
         <f>Planejado!C16</f>
         <v/>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="36">
         <f>Planejado!D16</f>
         <v/>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="35">
         <f>Planejado!G16</f>
         <v/>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="37">
         <f>INDEX(Planejado!$H16:$S16,$D$3)</f>
         <v/>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="37">
         <f>INDEX(Realizado!$H16:$S16,$D$3)</f>
         <v/>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="37">
         <f>G17-F17</f>
         <v/>
       </c>
-      <c r="I17" s="36">
+      <c r="I17" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H16:$S16)</f>
         <v/>
       </c>
-      <c r="J17" s="36">
+      <c r="J17" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H16:$S16)</f>
         <v/>
       </c>
-      <c r="K17" s="36">
+      <c r="K17" s="37">
         <f>J17-I17</f>
         <v/>
       </c>
-      <c r="L17" s="37">
+      <c r="L17" s="38">
         <f>IFERROR(K17/I17,"")</f>
         <v/>
       </c>
-      <c r="M17" s="37">
+      <c r="M17" s="38">
         <f>IFERROR(J17/I17,"")</f>
         <v/>
       </c>
-      <c r="N17" s="38">
+      <c r="N17" s="39">
         <f>IF(P17=0,"Sem lançamento",IF(AND(I17=0,J17=0),"—",IF(I17=0,"Não orçado",IF(K17&gt;0.05*I17,"Acima do orçado",IF(K17&lt;-0.05*I17,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O17" s="27">
+      <c r="O17" s="28">
         <f>IF(K17&gt;1,K17+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P17" s="39">
+      <c r="P17" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H16:$S16&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="34">
+      <c r="A18" s="35">
         <f>Planejado!A17</f>
         <v/>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="35">
         <f>Planejado!B17</f>
         <v/>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="35">
         <f>Planejado!C17</f>
         <v/>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="36">
         <f>Planejado!D17</f>
         <v/>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="35">
         <f>Planejado!G17</f>
         <v/>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="37">
         <f>INDEX(Planejado!$H17:$S17,$D$3)</f>
         <v/>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="37">
         <f>INDEX(Realizado!$H17:$S17,$D$3)</f>
         <v/>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="37">
         <f>G18-F18</f>
         <v/>
       </c>
-      <c r="I18" s="36">
+      <c r="I18" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H17:$S17)</f>
         <v/>
       </c>
-      <c r="J18" s="36">
+      <c r="J18" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H17:$S17)</f>
         <v/>
       </c>
-      <c r="K18" s="36">
+      <c r="K18" s="37">
         <f>J18-I18</f>
         <v/>
       </c>
-      <c r="L18" s="37">
+      <c r="L18" s="38">
         <f>IFERROR(K18/I18,"")</f>
         <v/>
       </c>
-      <c r="M18" s="37">
+      <c r="M18" s="38">
         <f>IFERROR(J18/I18,"")</f>
         <v/>
       </c>
-      <c r="N18" s="38">
+      <c r="N18" s="39">
         <f>IF(P18=0,"Sem lançamento",IF(AND(I18=0,J18=0),"—",IF(I18=0,"Não orçado",IF(K18&gt;0.05*I18,"Acima do orçado",IF(K18&lt;-0.05*I18,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O18" s="27">
+      <c r="O18" s="28">
         <f>IF(K18&gt;1,K18+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P18" s="39">
+      <c r="P18" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H17:$S17&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="34">
+      <c r="A19" s="35">
         <f>Planejado!A18</f>
         <v/>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="35">
         <f>Planejado!B18</f>
         <v/>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="35">
         <f>Planejado!C18</f>
         <v/>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="36">
         <f>Planejado!D18</f>
         <v/>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="35">
         <f>Planejado!G18</f>
         <v/>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="37">
         <f>INDEX(Planejado!$H18:$S18,$D$3)</f>
         <v/>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="37">
         <f>INDEX(Realizado!$H18:$S18,$D$3)</f>
         <v/>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="37">
         <f>G19-F19</f>
         <v/>
       </c>
-      <c r="I19" s="36">
+      <c r="I19" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H18:$S18)</f>
         <v/>
       </c>
-      <c r="J19" s="36">
+      <c r="J19" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H18:$S18)</f>
         <v/>
       </c>
-      <c r="K19" s="36">
+      <c r="K19" s="37">
         <f>J19-I19</f>
         <v/>
       </c>
-      <c r="L19" s="37">
+      <c r="L19" s="38">
         <f>IFERROR(K19/I19,"")</f>
         <v/>
       </c>
-      <c r="M19" s="37">
+      <c r="M19" s="38">
         <f>IFERROR(J19/I19,"")</f>
         <v/>
       </c>
-      <c r="N19" s="38">
+      <c r="N19" s="39">
         <f>IF(P19=0,"Sem lançamento",IF(AND(I19=0,J19=0),"—",IF(I19=0,"Não orçado",IF(K19&gt;0.05*I19,"Acima do orçado",IF(K19&lt;-0.05*I19,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O19" s="27">
+      <c r="O19" s="28">
         <f>IF(K19&gt;1,K19+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P19" s="39">
+      <c r="P19" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H18:$S18&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="34">
+      <c r="A20" s="35">
         <f>Planejado!A19</f>
         <v/>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="35">
         <f>Planejado!B19</f>
         <v/>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="35">
         <f>Planejado!C19</f>
         <v/>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="36">
         <f>Planejado!D19</f>
         <v/>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="35">
         <f>Planejado!G19</f>
         <v/>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="37">
         <f>INDEX(Planejado!$H19:$S19,$D$3)</f>
         <v/>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="37">
         <f>INDEX(Realizado!$H19:$S19,$D$3)</f>
         <v/>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="37">
         <f>G20-F20</f>
         <v/>
       </c>
-      <c r="I20" s="36">
+      <c r="I20" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H19:$S19)</f>
         <v/>
       </c>
-      <c r="J20" s="36">
+      <c r="J20" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H19:$S19)</f>
         <v/>
       </c>
-      <c r="K20" s="36">
+      <c r="K20" s="37">
         <f>J20-I20</f>
         <v/>
       </c>
-      <c r="L20" s="37">
+      <c r="L20" s="38">
         <f>IFERROR(K20/I20,"")</f>
         <v/>
       </c>
-      <c r="M20" s="37">
+      <c r="M20" s="38">
         <f>IFERROR(J20/I20,"")</f>
         <v/>
       </c>
-      <c r="N20" s="38">
+      <c r="N20" s="39">
         <f>IF(P20=0,"Sem lançamento",IF(AND(I20=0,J20=0),"—",IF(I20=0,"Não orçado",IF(K20&gt;0.05*I20,"Acima do orçado",IF(K20&lt;-0.05*I20,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O20" s="27">
+      <c r="O20" s="28">
         <f>IF(K20&gt;1,K20+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P20" s="39">
+      <c r="P20" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H19:$S19&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="34">
+      <c r="A21" s="35">
         <f>Planejado!A20</f>
         <v/>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>Planejado!B20</f>
         <v/>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>Planejado!C20</f>
         <v/>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="36">
         <f>Planejado!D20</f>
         <v/>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="35">
         <f>Planejado!G20</f>
         <v/>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="37">
         <f>INDEX(Planejado!$H20:$S20,$D$3)</f>
         <v/>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="37">
         <f>INDEX(Realizado!$H20:$S20,$D$3)</f>
         <v/>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="37">
         <f>G21-F21</f>
         <v/>
       </c>
-      <c r="I21" s="36">
+      <c r="I21" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H20:$S20)</f>
         <v/>
       </c>
-      <c r="J21" s="36">
+      <c r="J21" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H20:$S20)</f>
         <v/>
       </c>
-      <c r="K21" s="36">
+      <c r="K21" s="37">
         <f>J21-I21</f>
         <v/>
       </c>
-      <c r="L21" s="37">
+      <c r="L21" s="38">
         <f>IFERROR(K21/I21,"")</f>
         <v/>
       </c>
-      <c r="M21" s="37">
+      <c r="M21" s="38">
         <f>IFERROR(J21/I21,"")</f>
         <v/>
       </c>
-      <c r="N21" s="38">
+      <c r="N21" s="39">
         <f>IF(P21=0,"Sem lançamento",IF(AND(I21=0,J21=0),"—",IF(I21=0,"Não orçado",IF(K21&gt;0.05*I21,"Acima do orçado",IF(K21&lt;-0.05*I21,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O21" s="27">
+      <c r="O21" s="28">
         <f>IF(K21&gt;1,K21+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P21" s="39">
+      <c r="P21" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H20:$S20&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="34">
+      <c r="A22" s="35">
         <f>Planejado!A21</f>
         <v/>
       </c>
-      <c r="B22" s="34">
+      <c r="B22" s="35">
         <f>Planejado!B21</f>
         <v/>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="35">
         <f>Planejado!C21</f>
         <v/>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="36">
         <f>Planejado!D21</f>
         <v/>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="35">
         <f>Planejado!G21</f>
         <v/>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="37">
         <f>INDEX(Planejado!$H21:$S21,$D$3)</f>
         <v/>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="37">
         <f>INDEX(Realizado!$H21:$S21,$D$3)</f>
         <v/>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="37">
         <f>G22-F22</f>
         <v/>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H21:$S21)</f>
         <v/>
       </c>
-      <c r="J22" s="36">
+      <c r="J22" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H21:$S21)</f>
         <v/>
       </c>
-      <c r="K22" s="36">
+      <c r="K22" s="37">
         <f>J22-I22</f>
         <v/>
       </c>
-      <c r="L22" s="37">
+      <c r="L22" s="38">
         <f>IFERROR(K22/I22,"")</f>
         <v/>
       </c>
-      <c r="M22" s="37">
+      <c r="M22" s="38">
         <f>IFERROR(J22/I22,"")</f>
         <v/>
       </c>
-      <c r="N22" s="38">
+      <c r="N22" s="39">
         <f>IF(P22=0,"Sem lançamento",IF(AND(I22=0,J22=0),"—",IF(I22=0,"Não orçado",IF(K22&gt;0.05*I22,"Acima do orçado",IF(K22&lt;-0.05*I22,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O22" s="27">
+      <c r="O22" s="28">
         <f>IF(K22&gt;1,K22+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P22" s="39">
+      <c r="P22" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H21:$S21&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="34">
+      <c r="A23" s="35">
         <f>Planejado!A22</f>
         <v/>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>Planejado!B22</f>
         <v/>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>Planejado!C22</f>
         <v/>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="36">
         <f>Planejado!D22</f>
         <v/>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="35">
         <f>Planejado!G22</f>
         <v/>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="37">
         <f>INDEX(Planejado!$H22:$S22,$D$3)</f>
         <v/>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="37">
         <f>INDEX(Realizado!$H22:$S22,$D$3)</f>
         <v/>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="37">
         <f>G23-F23</f>
         <v/>
       </c>
-      <c r="I23" s="36">
+      <c r="I23" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H22:$S22)</f>
         <v/>
       </c>
-      <c r="J23" s="36">
+      <c r="J23" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H22:$S22)</f>
         <v/>
       </c>
-      <c r="K23" s="36">
+      <c r="K23" s="37">
         <f>J23-I23</f>
         <v/>
       </c>
-      <c r="L23" s="37">
+      <c r="L23" s="38">
         <f>IFERROR(K23/I23,"")</f>
         <v/>
       </c>
-      <c r="M23" s="37">
+      <c r="M23" s="38">
         <f>IFERROR(J23/I23,"")</f>
         <v/>
       </c>
-      <c r="N23" s="38">
+      <c r="N23" s="39">
         <f>IF(P23=0,"Sem lançamento",IF(AND(I23=0,J23=0),"—",IF(I23=0,"Não orçado",IF(K23&gt;0.05*I23,"Acima do orçado",IF(K23&lt;-0.05*I23,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O23" s="27">
+      <c r="O23" s="28">
         <f>IF(K23&gt;1,K23+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P23" s="39">
+      <c r="P23" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H22:$S22&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="34">
+      <c r="A24" s="35">
         <f>Planejado!A23</f>
         <v/>
       </c>
-      <c r="B24" s="34">
+      <c r="B24" s="35">
         <f>Planejado!B23</f>
         <v/>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="35">
         <f>Planejado!C23</f>
         <v/>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="36">
         <f>Planejado!D23</f>
         <v/>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="35">
         <f>Planejado!G23</f>
         <v/>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="37">
         <f>INDEX(Planejado!$H23:$S23,$D$3)</f>
         <v/>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="37">
         <f>INDEX(Realizado!$H23:$S23,$D$3)</f>
         <v/>
       </c>
-      <c r="H24" s="36">
+      <c r="H24" s="37">
         <f>G24-F24</f>
         <v/>
       </c>
-      <c r="I24" s="36">
+      <c r="I24" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H23:$S23)</f>
         <v/>
       </c>
-      <c r="J24" s="36">
+      <c r="J24" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H23:$S23)</f>
         <v/>
       </c>
-      <c r="K24" s="36">
+      <c r="K24" s="37">
         <f>J24-I24</f>
         <v/>
       </c>
-      <c r="L24" s="37">
+      <c r="L24" s="38">
         <f>IFERROR(K24/I24,"")</f>
         <v/>
       </c>
-      <c r="M24" s="37">
+      <c r="M24" s="38">
         <f>IFERROR(J24/I24,"")</f>
         <v/>
       </c>
-      <c r="N24" s="38">
+      <c r="N24" s="39">
         <f>IF(P24=0,"Sem lançamento",IF(AND(I24=0,J24=0),"—",IF(I24=0,"Não orçado",IF(K24&gt;0.05*I24,"Acima do orçado",IF(K24&lt;-0.05*I24,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O24" s="27">
+      <c r="O24" s="28">
         <f>IF(K24&gt;1,K24+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P24" s="39">
+      <c r="P24" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H23:$S23&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="34">
+      <c r="A25" s="35">
         <f>Planejado!A24</f>
         <v/>
       </c>
-      <c r="B25" s="34">
+      <c r="B25" s="35">
         <f>Planejado!B24</f>
         <v/>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="35">
         <f>Planejado!C24</f>
         <v/>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="36">
         <f>Planejado!D24</f>
         <v/>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="35">
         <f>Planejado!G24</f>
         <v/>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="37">
         <f>INDEX(Planejado!$H24:$S24,$D$3)</f>
         <v/>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="37">
         <f>INDEX(Realizado!$H24:$S24,$D$3)</f>
         <v/>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="37">
         <f>G25-F25</f>
         <v/>
       </c>
-      <c r="I25" s="36">
+      <c r="I25" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H24:$S24)</f>
         <v/>
       </c>
-      <c r="J25" s="36">
+      <c r="J25" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H24:$S24)</f>
         <v/>
       </c>
-      <c r="K25" s="36">
+      <c r="K25" s="37">
         <f>J25-I25</f>
         <v/>
       </c>
-      <c r="L25" s="37">
+      <c r="L25" s="38">
         <f>IFERROR(K25/I25,"")</f>
         <v/>
       </c>
-      <c r="M25" s="37">
+      <c r="M25" s="38">
         <f>IFERROR(J25/I25,"")</f>
         <v/>
       </c>
-      <c r="N25" s="38">
+      <c r="N25" s="39">
         <f>IF(P25=0,"Sem lançamento",IF(AND(I25=0,J25=0),"—",IF(I25=0,"Não orçado",IF(K25&gt;0.05*I25,"Acima do orçado",IF(K25&lt;-0.05*I25,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O25" s="27">
+      <c r="O25" s="28">
         <f>IF(K25&gt;1,K25+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P25" s="39">
+      <c r="P25" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H24:$S24&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="34">
+      <c r="A26" s="35">
         <f>Planejado!A25</f>
         <v/>
       </c>
-      <c r="B26" s="34">
+      <c r="B26" s="35">
         <f>Planejado!B25</f>
         <v/>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="35">
         <f>Planejado!C25</f>
         <v/>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="36">
         <f>Planejado!D25</f>
         <v/>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="35">
         <f>Planejado!G25</f>
         <v/>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="37">
         <f>INDEX(Planejado!$H25:$S25,$D$3)</f>
         <v/>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="37">
         <f>INDEX(Realizado!$H25:$S25,$D$3)</f>
         <v/>
       </c>
-      <c r="H26" s="36">
+      <c r="H26" s="37">
         <f>G26-F26</f>
         <v/>
       </c>
-      <c r="I26" s="36">
+      <c r="I26" s="37">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H25:$S25)</f>
         <v/>
       </c>
-      <c r="J26" s="36">
+      <c r="J26" s="37">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H25:$S25)</f>
         <v/>
       </c>
-      <c r="K26" s="36">
+      <c r="K26" s="37">
         <f>J26-I26</f>
         <v/>
       </c>
-      <c r="L26" s="37">
+      <c r="L26" s="38">
         <f>IFERROR(K26/I26,"")</f>
         <v/>
       </c>
-      <c r="M26" s="37">
+      <c r="M26" s="38">
         <f>IFERROR(J26/I26,"")</f>
         <v/>
       </c>
-      <c r="N26" s="38">
+      <c r="N26" s="39">
         <f>IF(P26=0,"Sem lançamento",IF(AND(I26=0,J26=0),"—",IF(I26=0,"Não orçado",IF(K26&gt;0.05*I26,"Acima do orçado",IF(K26&lt;-0.05*I26,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O26" s="27">
+      <c r="O26" s="28">
         <f>IF(K26&gt;1,K26+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P26" s="39">
+      <c r="P26" s="40">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H25:$S25&lt;&gt;""))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="16">
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="17">
         <f>SUM(F6:F26)</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="17">
         <f>SUM(G6:G26)</f>
         <v/>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="17">
         <f>SUM(H6:H26)</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="17">
         <f>SUM(I6:I26)</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="17">
         <f>SUM(J6:J26)</f>
         <v/>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="17">
         <f>SUM(K6:K26)</f>
         <v/>
       </c>
-      <c r="L27" s="40">
+      <c r="L27" s="41">
         <f>IFERROR(K27/I27,"")</f>
         <v/>
       </c>
-      <c r="M27" s="40">
+      <c r="M27" s="41">
         <f>IFERROR(J27/I27,"")</f>
         <v/>
       </c>
-      <c r="N27" s="15" t="n"/>
+      <c r="N27" s="16" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:N26"/>
@@ -3244,1705 +3266,1705 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Detalhe / Observação</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Vínculo</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="S4" s="6" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>TOTAL DO ANO</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>JUR-E01</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>Miguel Clepf</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>Advogado Júnior</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H5" s="30" t="n">
+      <c r="H5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="I5" s="30" t="n">
+      <c r="I5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="J5" s="30" t="n">
+      <c r="J5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="K5" s="30" t="n">
+      <c r="K5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="L5" s="30" t="n">
+      <c r="L5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="M5" s="30" t="n">
+      <c r="M5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="N5" s="30" t="n">
+      <c r="N5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="O5" s="30" t="n">
+      <c r="O5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="P5" s="30" t="n">
+      <c r="P5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="Q5" s="30" t="n">
+      <c r="Q5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="R5" s="30" t="n">
+      <c r="R5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="S5" s="30" t="n">
+      <c r="S5" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="T5" s="41">
+      <c r="T5" s="42">
         <f>SUM(H5:S5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>JUR-E02</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>Geovanna</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>Analista Administrativo — orçada pelo custo total (encargos de folha + benefícios). Salário bruto informado: R$ 2.886,91/mês</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>CLT</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="H6" s="30" t="n">
+      <c r="H6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="I6" s="30" t="n">
+      <c r="I6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="J6" s="30" t="n">
+      <c r="J6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="K6" s="30" t="n">
+      <c r="K6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="L6" s="30" t="n">
+      <c r="L6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="M6" s="30" t="n">
+      <c r="M6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="N6" s="30" t="n">
+      <c r="N6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="O6" s="30" t="n">
+      <c r="O6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="P6" s="30" t="n">
+      <c r="P6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="Q6" s="30" t="n">
+      <c r="Q6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="R6" s="30" t="n">
+      <c r="R6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="S6" s="30" t="n">
+      <c r="S6" s="31" t="n">
         <v>4825.515</v>
       </c>
-      <c r="T6" s="41">
+      <c r="T6" s="42">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>JUR-E03</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>Thamar Victória</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>Advogada — recebia R$ 4.500/mês em jan–mar e passou a R$ 5.500 em abr/26 (aumento de R$ 1.000), contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
         </is>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G7" s="28" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H7" s="30" t="n">
+      <c r="H7" s="31" t="n">
         <v>5000</v>
       </c>
-      <c r="I7" s="30" t="n">
+      <c r="I7" s="31" t="n">
         <v>5000</v>
       </c>
-      <c r="J7" s="30" t="n">
+      <c r="J7" s="31" t="n">
         <v>5000</v>
       </c>
-      <c r="K7" s="30" t="n">
+      <c r="K7" s="31" t="n">
         <v>5000</v>
       </c>
-      <c r="L7" s="30" t="n">
+      <c r="L7" s="31" t="n">
         <v>5000</v>
       </c>
-      <c r="M7" s="30" t="n">
+      <c r="M7" s="31" t="n">
         <v>5000</v>
       </c>
-      <c r="N7" s="30" t="n">
+      <c r="N7" s="31" t="n">
         <v>5000</v>
       </c>
-      <c r="O7" s="30" t="n">
+      <c r="O7" s="31" t="n">
         <v>5500</v>
       </c>
-      <c r="P7" s="30" t="n">
+      <c r="P7" s="31" t="n">
         <v>5500</v>
       </c>
-      <c r="Q7" s="30" t="n">
+      <c r="Q7" s="31" t="n">
         <v>5500</v>
       </c>
-      <c r="R7" s="30" t="n">
+      <c r="R7" s="31" t="n">
         <v>5500</v>
       </c>
-      <c r="S7" s="30" t="n">
+      <c r="S7" s="31" t="n">
         <v>5500</v>
       </c>
-      <c r="T7" s="41">
+      <c r="T7" s="42">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>JUR-D01</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>JUSFY</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>Fase de teste com objetivo de eliminar o Astrea</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr"/>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr"/>
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H8" s="30" t="n">
+      <c r="H8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="I8" s="30" t="n">
+      <c r="I8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="J8" s="30" t="n">
+      <c r="J8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="K8" s="30" t="n">
+      <c r="K8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="L8" s="30" t="n">
+      <c r="L8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="M8" s="30" t="n">
+      <c r="M8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="N8" s="30" t="n">
+      <c r="N8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="O8" s="30" t="n">
+      <c r="O8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="P8" s="30" t="n">
+      <c r="P8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="Q8" s="30" t="n">
+      <c r="Q8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="R8" s="30" t="n">
+      <c r="R8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="S8" s="30" t="n">
+      <c r="S8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="T8" s="41">
+      <c r="T8" s="42">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>JUR-D02</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>JUSBRASIL</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr"/>
-      <c r="F9" s="28" t="inlineStr"/>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr"/>
+      <c r="F9" s="29" t="inlineStr"/>
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H9" s="30" t="n">
+      <c r="H9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="I9" s="30" t="n">
+      <c r="I9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="J9" s="30" t="n">
+      <c r="J9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="K9" s="30" t="n">
+      <c r="K9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="L9" s="30" t="n">
+      <c r="L9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="M9" s="30" t="n">
+      <c r="M9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="N9" s="30" t="n">
+      <c r="N9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="O9" s="30" t="n">
+      <c r="O9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="P9" s="30" t="n">
+      <c r="P9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="Q9" s="30" t="n">
+      <c r="Q9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="R9" s="30" t="n">
+      <c r="R9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="S9" s="30" t="n">
+      <c r="S9" s="31" t="n">
         <v>104.9</v>
       </c>
-      <c r="T9" s="41">
+      <c r="T9" s="42">
         <f>SUM(H9:S9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>JUR-D03</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>ASTREA</t>
         </is>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>Cancelado — realizado zerado desde mai/26</t>
         </is>
       </c>
-      <c r="F10" s="28" t="inlineStr"/>
-      <c r="G10" s="28" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr"/>
+      <c r="G10" s="29" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H10" s="30" t="n">
+      <c r="H10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="I10" s="30" t="n">
+      <c r="I10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="J10" s="30" t="n">
+      <c r="J10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="K10" s="30" t="n">
+      <c r="K10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="L10" s="30" t="n">
+      <c r="L10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="M10" s="30" t="n">
+      <c r="M10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="N10" s="30" t="n">
+      <c r="N10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="O10" s="30" t="n">
+      <c r="O10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="P10" s="30" t="n">
+      <c r="P10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="Q10" s="30" t="n">
+      <c r="Q10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="R10" s="30" t="n">
+      <c r="R10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="S10" s="30" t="n">
+      <c r="S10" s="31" t="n">
         <v>112.07</v>
       </c>
-      <c r="T10" s="41">
+      <c r="T10" s="42">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>JUR-D04</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>LEME</t>
         </is>
       </c>
-      <c r="E11" s="29" t="inlineStr"/>
-      <c r="F11" s="28" t="inlineStr"/>
-      <c r="G11" s="28" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr"/>
+      <c r="F11" s="29" t="inlineStr"/>
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H11" s="30" t="n">
+      <c r="H11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="I11" s="30" t="n">
+      <c r="I11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="J11" s="30" t="n">
+      <c r="J11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="K11" s="30" t="n">
+      <c r="K11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="L11" s="30" t="n">
+      <c r="L11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="M11" s="30" t="n">
+      <c r="M11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="N11" s="30" t="n">
+      <c r="N11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="O11" s="30" t="n">
+      <c r="O11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="P11" s="30" t="n">
+      <c r="P11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="Q11" s="30" t="n">
+      <c r="Q11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="R11" s="30" t="n">
+      <c r="R11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="S11" s="30" t="n">
+      <c r="S11" s="31" t="n">
         <v>1030</v>
       </c>
-      <c r="T11" s="41">
+      <c r="T11" s="42">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>JUR-D05</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>Cursos / Eventos / Network</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr"/>
-      <c r="F12" s="28" t="inlineStr"/>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr"/>
+      <c r="F12" s="29" t="inlineStr"/>
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="H12" s="30" t="n">
+      <c r="H12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="I12" s="30" t="n">
+      <c r="I12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="J12" s="30" t="n">
+      <c r="J12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="K12" s="30" t="n">
+      <c r="K12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="L12" s="30" t="n">
+      <c r="L12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="M12" s="30" t="n">
+      <c r="M12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="N12" s="30" t="n">
+      <c r="N12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="O12" s="30" t="n">
+      <c r="O12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="P12" s="30" t="n">
+      <c r="P12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="Q12" s="30" t="n">
+      <c r="Q12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="R12" s="30" t="n">
+      <c r="R12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="S12" s="30" t="n">
+      <c r="S12" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="T12" s="41">
+      <c r="T12" s="42">
         <f>SUM(H12:S12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>JUR-D06</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Bonificações trimestrais/semestrais do time</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
         </is>
       </c>
-      <c r="F13" s="28" t="inlineStr"/>
-      <c r="G13" s="28" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr"/>
+      <c r="G13" s="29" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="H13" s="30" t="n">
+      <c r="H13" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="30" t="n">
+      <c r="I13" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="30" t="n">
+      <c r="J13" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="30" t="n">
+      <c r="K13" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="30" t="n">
+      <c r="L13" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="30" t="n">
+      <c r="M13" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="30" t="n">
+      <c r="N13" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="30" t="n">
+      <c r="O13" s="31" t="n">
         <v>10293.6</v>
       </c>
-      <c r="P13" s="30" t="n">
+      <c r="P13" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="30" t="n">
+      <c r="Q13" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="30" t="n">
+      <c r="R13" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="30" t="n">
+      <c r="S13" s="31" t="n">
         <v>12867</v>
       </c>
-      <c r="T13" s="41">
+      <c r="T13" s="42">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>TI-E01</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>Vinicius Di Franco</t>
         </is>
       </c>
-      <c r="E14" s="35" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>Analista Administrativo — orçado pelo custo total (encargos de folha + benefícios). Salário bruto: R$ 2.570,52/mês até jul/26 e R$ 3.070,52 a partir de 05/08/26, aumento absorvido pela folga do envelope</t>
         </is>
       </c>
-      <c r="F14" s="34" t="inlineStr">
+      <c r="F14" s="35" t="inlineStr">
         <is>
           <t>CLT</t>
         </is>
       </c>
-      <c r="G14" s="34" t="inlineStr">
+      <c r="G14" s="35" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="H14" s="36" t="n">
+      <c r="H14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="I14" s="36" t="n">
+      <c r="I14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="J14" s="36" t="n">
+      <c r="J14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="K14" s="36" t="n">
+      <c r="K14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="L14" s="36" t="n">
+      <c r="L14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="M14" s="36" t="n">
+      <c r="M14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="N14" s="36" t="n">
+      <c r="N14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="O14" s="36" t="n">
+      <c r="O14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="P14" s="36" t="n">
+      <c r="P14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="Q14" s="36" t="n">
+      <c r="Q14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="R14" s="36" t="n">
+      <c r="R14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="S14" s="36" t="n">
+      <c r="S14" s="37" t="n">
         <v>5416.525</v>
       </c>
-      <c r="T14" s="41">
+      <c r="T14" s="42">
         <f>SUM(H14:S14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>TI-E02</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>Elias Benedito</t>
         </is>
       </c>
-      <c r="E15" s="35" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>Suporte Técnico Terceirizado</t>
         </is>
       </c>
-      <c r="F15" s="34" t="inlineStr">
+      <c r="F15" s="35" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G15" s="34" t="inlineStr">
+      <c r="G15" s="35" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H15" s="36" t="n">
+      <c r="H15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="I15" s="36" t="n">
+      <c r="I15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="J15" s="36" t="n">
+      <c r="J15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="K15" s="36" t="n">
+      <c r="K15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="L15" s="36" t="n">
+      <c r="L15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="M15" s="36" t="n">
+      <c r="M15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="N15" s="36" t="n">
+      <c r="N15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="O15" s="36" t="n">
+      <c r="O15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="P15" s="36" t="n">
+      <c r="P15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="Q15" s="36" t="n">
+      <c r="Q15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="R15" s="36" t="n">
+      <c r="R15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="S15" s="36" t="n">
+      <c r="S15" s="37" t="n">
         <v>1065</v>
       </c>
-      <c r="T15" s="41">
+      <c r="T15" s="42">
         <f>SUM(H15:S15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>TI-E03</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D16" s="35" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>Jonathan</t>
         </is>
       </c>
-      <c r="E16" s="35" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
         </is>
       </c>
-      <c r="F16" s="34" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G16" s="34" t="inlineStr">
+      <c r="G16" s="35" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H16" s="36" t="n">
+      <c r="H16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="36" t="n">
+      <c r="I16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="36" t="n">
+      <c r="J16" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="36" t="n">
+      <c r="K16" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="L16" s="36" t="n">
+      <c r="L16" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="M16" s="36" t="n">
+      <c r="M16" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="N16" s="36" t="n">
+      <c r="N16" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="O16" s="36" t="n">
+      <c r="O16" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="P16" s="36" t="n">
+      <c r="P16" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="Q16" s="36" t="n">
+      <c r="Q16" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="R16" s="36" t="n">
+      <c r="R16" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="S16" s="36" t="n">
+      <c r="S16" s="37" t="n">
         <v>10000</v>
       </c>
-      <c r="T16" s="41">
+      <c r="T16" s="42">
         <f>SUM(H16:S16)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>TI-D01</t>
         </is>
       </c>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>Peças de Manutenção</t>
         </is>
       </c>
-      <c r="E17" s="35" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
         </is>
       </c>
-      <c r="F17" s="34" t="inlineStr"/>
-      <c r="G17" s="34" t="inlineStr">
+      <c r="F17" s="35" t="inlineStr"/>
+      <c r="G17" s="35" t="inlineStr">
         <is>
           <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
-      <c r="H17" s="36" t="n">
+      <c r="H17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="I17" s="36" t="n">
+      <c r="I17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="J17" s="36" t="n">
+      <c r="J17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="K17" s="36" t="n">
+      <c r="K17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="L17" s="36" t="n">
+      <c r="L17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="M17" s="36" t="n">
+      <c r="M17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="N17" s="36" t="n">
+      <c r="N17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="O17" s="36" t="n">
+      <c r="O17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="P17" s="36" t="n">
+      <c r="P17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="Q17" s="36" t="n">
+      <c r="Q17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="R17" s="36" t="n">
+      <c r="R17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="S17" s="36" t="n">
+      <c r="S17" s="37" t="n">
         <v>810</v>
       </c>
-      <c r="T17" s="41">
+      <c r="T17" s="42">
         <f>SUM(H17:S17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>TI-D02</t>
         </is>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D18" s="35" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>Backup em Nuvem</t>
         </is>
       </c>
-      <c r="E18" s="35" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F18" s="34" t="inlineStr"/>
-      <c r="G18" s="34" t="inlineStr">
+      <c r="F18" s="35" t="inlineStr"/>
+      <c r="G18" s="35" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H18" s="36" t="n">
+      <c r="H18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="I18" s="36" t="n">
+      <c r="I18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="J18" s="36" t="n">
+      <c r="J18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="K18" s="36" t="n">
+      <c r="K18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="L18" s="36" t="n">
+      <c r="L18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="M18" s="36" t="n">
+      <c r="M18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="N18" s="36" t="n">
+      <c r="N18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="O18" s="36" t="n">
+      <c r="O18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="P18" s="36" t="n">
+      <c r="P18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="Q18" s="36" t="n">
+      <c r="Q18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="R18" s="36" t="n">
+      <c r="R18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="S18" s="36" t="n">
+      <c r="S18" s="37" t="n">
         <v>825</v>
       </c>
-      <c r="T18" s="41">
+      <c r="T18" s="42">
         <f>SUM(H18:S18)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>TI-D03</t>
         </is>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>Inteligência Artificial (Adapta)</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F19" s="34" t="inlineStr"/>
-      <c r="G19" s="34" t="inlineStr">
+      <c r="F19" s="35" t="inlineStr"/>
+      <c r="G19" s="35" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H19" s="36" t="n">
+      <c r="H19" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="I19" s="36" t="n">
+      <c r="I19" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="J19" s="36" t="n">
+      <c r="J19" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="K19" s="36" t="n">
+      <c r="K19" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="L19" s="36" t="n">
+      <c r="L19" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="M19" s="36" t="n">
+      <c r="M19" s="37" t="n">
         <v>1300</v>
       </c>
-      <c r="N19" s="36" t="n">
+      <c r="N19" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="O19" s="36" t="n">
+      <c r="O19" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="P19" s="36" t="n">
+      <c r="P19" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="Q19" s="36" t="n">
+      <c r="Q19" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="R19" s="36" t="n">
+      <c r="R19" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="S19" s="36" t="n">
+      <c r="S19" s="37" t="n">
         <v>1600</v>
       </c>
-      <c r="T19" s="41">
+      <c r="T19" s="42">
         <f>SUM(H19:S19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>TI-D04</t>
         </is>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D20" s="35" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Antivírus</t>
         </is>
       </c>
-      <c r="E20" s="35" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F20" s="34" t="inlineStr"/>
-      <c r="G20" s="34" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr"/>
+      <c r="G20" s="35" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H20" s="36" t="n">
+      <c r="H20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="I20" s="36" t="n">
+      <c r="I20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="J20" s="36" t="n">
+      <c r="J20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="K20" s="36" t="n">
+      <c r="K20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="L20" s="36" t="n">
+      <c r="L20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="M20" s="36" t="n">
+      <c r="M20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="N20" s="36" t="n">
+      <c r="N20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="O20" s="36" t="n">
+      <c r="O20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="P20" s="36" t="n">
+      <c r="P20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="Q20" s="36" t="n">
+      <c r="Q20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="R20" s="36" t="n">
+      <c r="R20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="S20" s="36" t="n">
+      <c r="S20" s="37" t="n">
         <v>240</v>
       </c>
-      <c r="T20" s="41">
+      <c r="T20" s="42">
         <f>SUM(H20:S20)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>TI-D05</t>
         </is>
       </c>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D21" s="35" t="inlineStr">
+      <c r="D21" s="36" t="inlineStr">
         <is>
           <t>Pacote Office 365</t>
         </is>
       </c>
-      <c r="E21" s="35" t="inlineStr">
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F21" s="34" t="inlineStr"/>
-      <c r="G21" s="34" t="inlineStr">
+      <c r="F21" s="35" t="inlineStr"/>
+      <c r="G21" s="35" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H21" s="36" t="n">
+      <c r="H21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="I21" s="36" t="n">
+      <c r="I21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="J21" s="36" t="n">
+      <c r="J21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="K21" s="36" t="n">
+      <c r="K21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="L21" s="36" t="n">
+      <c r="L21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="M21" s="36" t="n">
+      <c r="M21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="N21" s="36" t="n">
+      <c r="N21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="O21" s="36" t="n">
+      <c r="O21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="P21" s="36" t="n">
+      <c r="P21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="Q21" s="36" t="n">
+      <c r="Q21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="R21" s="36" t="n">
+      <c r="R21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="S21" s="36" t="n">
+      <c r="S21" s="37" t="n">
         <v>375</v>
       </c>
-      <c r="T21" s="41">
+      <c r="T21" s="42">
         <f>SUM(H21:S21)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>TI-D06</t>
         </is>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D22" s="35" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
         </is>
       </c>
-      <c r="E22" s="35" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
         </is>
       </c>
-      <c r="F22" s="34" t="inlineStr"/>
-      <c r="G22" s="34" t="inlineStr">
+      <c r="F22" s="35" t="inlineStr"/>
+      <c r="G22" s="35" t="inlineStr">
         <is>
           <t>Móveis e Utensílios</t>
         </is>
       </c>
-      <c r="H22" s="36" t="n">
+      <c r="H22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="I22" s="36" t="n">
+      <c r="I22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="J22" s="36" t="n">
+      <c r="J22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="K22" s="36" t="n">
+      <c r="K22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="L22" s="36" t="n">
+      <c r="L22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="M22" s="36" t="n">
+      <c r="M22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="N22" s="36" t="n">
+      <c r="N22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="O22" s="36" t="n">
+      <c r="O22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="P22" s="36" t="n">
+      <c r="P22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="Q22" s="36" t="n">
+      <c r="Q22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="R22" s="36" t="n">
+      <c r="R22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="S22" s="36" t="n">
+      <c r="S22" s="37" t="n">
         <v>2800</v>
       </c>
-      <c r="T22" s="41">
+      <c r="T22" s="42">
         <f>SUM(H22:S22)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>TI-D07</t>
         </is>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D23" s="35" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>Cursos e Treinamentos</t>
         </is>
       </c>
-      <c r="E23" s="35" t="inlineStr"/>
-      <c r="F23" s="34" t="inlineStr"/>
-      <c r="G23" s="34" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr"/>
+      <c r="F23" s="35" t="inlineStr"/>
+      <c r="G23" s="35" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="H23" s="36" t="n">
+      <c r="H23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="I23" s="36" t="n">
+      <c r="I23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="J23" s="36" t="n">
+      <c r="J23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="K23" s="36" t="n">
+      <c r="K23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="L23" s="36" t="n">
+      <c r="L23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="M23" s="36" t="n">
+      <c r="M23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="N23" s="36" t="n">
+      <c r="N23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="O23" s="36" t="n">
+      <c r="O23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="P23" s="36" t="n">
+      <c r="P23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="Q23" s="36" t="n">
+      <c r="Q23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="R23" s="36" t="n">
+      <c r="R23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="S23" s="36" t="n">
+      <c r="S23" s="37" t="n">
         <v>200</v>
       </c>
-      <c r="T23" s="41">
+      <c r="T23" s="42">
         <f>SUM(H23:S23)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>TI-D08</t>
         </is>
       </c>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>Aplicativo de Gravação de Reunião</t>
         </is>
       </c>
-      <c r="E24" s="35" t="inlineStr"/>
-      <c r="F24" s="34" t="inlineStr"/>
-      <c r="G24" s="34" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr"/>
+      <c r="F24" s="35" t="inlineStr"/>
+      <c r="G24" s="35" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H24" s="36" t="n">
+      <c r="H24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="I24" s="36" t="n">
+      <c r="I24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="J24" s="36" t="n">
+      <c r="J24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="K24" s="36" t="n">
+      <c r="K24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="L24" s="36" t="n">
+      <c r="L24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="M24" s="36" t="n">
+      <c r="M24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="N24" s="36" t="n">
+      <c r="N24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="O24" s="36" t="n">
+      <c r="O24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="P24" s="36" t="n">
+      <c r="P24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="Q24" s="36" t="n">
+      <c r="Q24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="R24" s="36" t="n">
+      <c r="R24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="S24" s="36" t="n">
+      <c r="S24" s="37" t="n">
         <v>220</v>
       </c>
-      <c r="T24" s="41">
+      <c r="T24" s="42">
         <f>SUM(H24:S24)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>TI-D09</t>
         </is>
       </c>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D25" s="35" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>Bonificação do time</t>
         </is>
       </c>
-      <c r="E25" s="35" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
         </is>
       </c>
-      <c r="F25" s="34" t="inlineStr"/>
-      <c r="G25" s="34" t="inlineStr">
+      <c r="F25" s="35" t="inlineStr"/>
+      <c r="G25" s="35" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="H25" s="36" t="n">
+      <c r="H25" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="36" t="n">
+      <c r="I25" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="36" t="n">
+      <c r="J25" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="36" t="n">
+      <c r="K25" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="36" t="n">
+      <c r="L25" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="36" t="n">
+      <c r="M25" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="36" t="n">
+      <c r="N25" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="36" t="n">
+      <c r="O25" s="37" t="n">
         <v>2400</v>
       </c>
-      <c r="P25" s="36" t="n">
+      <c r="P25" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="36" t="n">
+      <c r="Q25" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="R25" s="36" t="n">
+      <c r="R25" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="36" t="n">
+      <c r="S25" s="37" t="n">
         <v>3600</v>
       </c>
-      <c r="T25" s="41">
+      <c r="T25" s="42">
         <f>SUM(H25:S25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="16">
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="16" t="n"/>
+      <c r="H26" s="17">
         <f>SUM(H5:H25)</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="17">
         <f>SUM(I5:I25)</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="17">
         <f>SUM(J5:J25)</f>
         <v/>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="17">
         <f>SUM(K5:K25)</f>
         <v/>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="17">
         <f>SUM(L5:L25)</f>
         <v/>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="17">
         <f>SUM(M5:M25)</f>
         <v/>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="17">
         <f>SUM(N5:N25)</f>
         <v/>
       </c>
-      <c r="O26" s="16">
+      <c r="O26" s="17">
         <f>SUM(O5:O25)</f>
         <v/>
       </c>
-      <c r="P26" s="16">
+      <c r="P26" s="17">
         <f>SUM(P5:P25)</f>
         <v/>
       </c>
-      <c r="Q26" s="16">
+      <c r="Q26" s="17">
         <f>SUM(Q5:Q25)</f>
         <v/>
       </c>
-      <c r="R26" s="16">
+      <c r="R26" s="17">
         <f>SUM(R5:R25)</f>
         <v/>
       </c>
-      <c r="S26" s="16">
+      <c r="S26" s="17">
         <f>SUM(S5:S25)</f>
         <v/>
       </c>
-      <c r="T26" s="16">
+      <c r="T26" s="17">
         <f>SUM(T5:T25)</f>
         <v/>
       </c>
@@ -5005,1331 +5027,1349 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
         <is>
           <t>Detalhe / Observação</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="43" t="inlineStr">
         <is>
           <t>Vínculo</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="G4" s="43" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="H4" s="42" t="inlineStr">
+      <c r="H4" s="43" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="I4" s="42" t="inlineStr">
+      <c r="I4" s="43" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="J4" s="42" t="inlineStr">
+      <c r="J4" s="43" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="K4" s="42" t="inlineStr">
+      <c r="K4" s="43" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="L4" s="42" t="inlineStr">
+      <c r="L4" s="43" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="M4" s="42" t="inlineStr">
+      <c r="M4" s="43" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="N4" s="42" t="inlineStr">
+      <c r="N4" s="43" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="O4" s="42" t="inlineStr">
+      <c r="O4" s="43" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="P4" s="42" t="inlineStr">
+      <c r="P4" s="43" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="Q4" s="42" t="inlineStr">
+      <c r="Q4" s="43" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="R4" s="42" t="inlineStr">
+      <c r="R4" s="43" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="S4" s="42" t="inlineStr">
+      <c r="S4" s="43" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="T4" s="42" t="inlineStr">
+      <c r="T4" s="43" t="inlineStr">
         <is>
           <t>TOTAL REALIZADO</t>
         </is>
       </c>
-      <c r="U4" s="42" t="inlineStr">
+      <c r="U4" s="43" t="inlineStr">
         <is>
           <t>Fonte do dado</t>
         </is>
       </c>
-      <c r="V4" s="42" t="inlineStr">
+      <c r="V4" s="43" t="inlineStr">
         <is>
           <t>Observações do mês</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="43">
+      <c r="A5" s="44">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="44">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="44">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="45">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="45">
         <f>Planejado!E5</f>
         <v/>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="44">
         <f>Planejado!F5</f>
         <v/>
       </c>
-      <c r="G5" s="43">
+      <c r="G5" s="44">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="H5" s="45" t="n">
+      <c r="H5" s="46" t="n">
         <v>8818</v>
       </c>
-      <c r="I5" s="45" t="n">
+      <c r="I5" s="46" t="n">
         <v>8818</v>
       </c>
-      <c r="J5" s="45" t="n">
+      <c r="J5" s="46" t="n">
         <v>8818</v>
       </c>
-      <c r="K5" s="45" t="n">
+      <c r="K5" s="46" t="n">
         <v>8818</v>
       </c>
-      <c r="L5" s="45" t="n">
+      <c r="L5" s="46" t="n">
         <v>8818</v>
       </c>
-      <c r="M5" s="45" t="n">
+      <c r="M5" s="46" t="n">
         <v>8818</v>
       </c>
-      <c r="N5" s="45" t="n">
+      <c r="N5" s="46" t="n">
         <v>8818</v>
       </c>
-      <c r="O5" s="45" t="n"/>
-      <c r="T5" s="41">
+      <c r="O5" s="46" t="n"/>
+      <c r="T5" s="42">
         <f>SUM(H5:S5)</f>
         <v/>
       </c>
-      <c r="U5" s="46" t="inlineStr">
+      <c r="U5" s="47" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V5" s="46" t="inlineStr">
+      <c r="V5" s="47" t="inlineStr">
         <is>
           <t>Valor cheio da nota — R$ 1.182/mês abaixo do contratado</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="43">
+      <c r="A6" s="44">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="44">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="44">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="45">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="45">
         <f>Planejado!E6</f>
         <v/>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="44">
         <f>Planejado!F6</f>
         <v/>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="44">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="H6" s="45" t="n"/>
-      <c r="I6" s="45" t="n"/>
-      <c r="J6" s="45" t="n"/>
-      <c r="K6" s="45" t="n"/>
-      <c r="L6" s="45" t="n"/>
-      <c r="M6" s="45" t="n"/>
-      <c r="N6" s="45" t="n"/>
-      <c r="O6" s="45" t="n"/>
-      <c r="T6" s="41">
+      <c r="H6" s="46" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="I6" s="46" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="J6" s="46" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="K6" s="46" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="L6" s="46" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="M6" s="46" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="N6" s="46" t="n">
+        <v>2886.91</v>
+      </c>
+      <c r="O6" s="46" t="n"/>
+      <c r="T6" s="42">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
-      <c r="U6" s="46" t="n"/>
-      <c r="V6" s="46" t="inlineStr">
-        <is>
-          <t>PREENCHER com o CUSTO TOTAL. Bruto informado: R$ 2.886,91/mês — faltam encargos e benefícios</t>
+      <c r="U6" s="47" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="V6" s="47" t="inlineStr">
+        <is>
+          <t>SALÁRIO BRUTO, sem alteração no ano. O orçado é custo total, então o desvio desta linha NÃO é economia: faltam encargos e benefícios (~R$ 1.938,61/mês)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="43">
+      <c r="A7" s="44">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B7" s="43">
+      <c r="B7" s="44">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="44">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="45">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="45">
         <f>Planejado!E7</f>
         <v/>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="44">
         <f>Planejado!F7</f>
         <v/>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="44">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="46" t="n">
         <v>4500</v>
       </c>
-      <c r="I7" s="45" t="n">
+      <c r="I7" s="46" t="n">
         <v>4500</v>
       </c>
-      <c r="J7" s="45" t="n">
+      <c r="J7" s="46" t="n">
         <v>4500</v>
       </c>
-      <c r="K7" s="45" t="n">
+      <c r="K7" s="46" t="n">
         <v>5500</v>
       </c>
-      <c r="L7" s="45" t="n">
+      <c r="L7" s="46" t="n">
         <v>5500</v>
       </c>
-      <c r="M7" s="45" t="n">
+      <c r="M7" s="46" t="n">
         <v>5500</v>
       </c>
-      <c r="N7" s="45" t="n">
+      <c r="N7" s="46" t="n">
         <v>5500</v>
       </c>
-      <c r="O7" s="45" t="n"/>
-      <c r="T7" s="41">
+      <c r="O7" s="46" t="n"/>
+      <c r="T7" s="42">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
-      <c r="U7" s="46" t="inlineStr">
+      <c r="U7" s="47" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V7" s="46" t="inlineStr">
+      <c r="V7" s="47" t="inlineStr">
         <is>
           <t>R$ 4.500/mês em jan–mar; aumento de R$ 1.000 a partir de abr/26</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="43">
+      <c r="A8" s="44">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B8" s="43">
+      <c r="B8" s="44">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="44">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="45">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="45">
         <f>Planejado!E8</f>
         <v/>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="44">
         <f>Planejado!F8</f>
         <v/>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="44">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="45" t="n">
+      <c r="I8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="45" t="n">
+      <c r="J8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="45" t="n">
+      <c r="K8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="45" t="n">
+      <c r="L8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="45" t="n">
+      <c r="M8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="45" t="n">
+      <c r="N8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="45" t="n"/>
-      <c r="T8" s="41">
+      <c r="O8" s="46" t="n"/>
+      <c r="T8" s="42">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
-      <c r="U8" s="46" t="inlineStr">
+      <c r="U8" s="47" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V8" s="46" t="inlineStr">
+      <c r="V8" s="47" t="inlineStr">
         <is>
           <t>Ainda não iniciado — sem cobrança</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="43">
+      <c r="A9" s="44">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B9" s="43">
+      <c r="B9" s="44">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="44">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="45">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="45">
         <f>Planejado!E9</f>
         <v/>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="44">
         <f>Planejado!F9</f>
         <v/>
       </c>
-      <c r="G9" s="43">
+      <c r="G9" s="44">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="H9" s="45" t="n">
+      <c r="H9" s="46" t="n">
         <v>136</v>
       </c>
-      <c r="I9" s="45" t="n">
+      <c r="I9" s="46" t="n">
         <v>136</v>
       </c>
-      <c r="J9" s="45" t="n">
+      <c r="J9" s="46" t="n">
         <v>136</v>
       </c>
-      <c r="K9" s="45" t="n">
+      <c r="K9" s="46" t="n">
         <v>136</v>
       </c>
-      <c r="L9" s="45" t="n">
+      <c r="L9" s="46" t="n">
         <v>136</v>
       </c>
-      <c r="M9" s="45" t="n">
+      <c r="M9" s="46" t="n">
         <v>136</v>
       </c>
-      <c r="N9" s="45" t="n">
+      <c r="N9" s="46" t="n">
         <v>136</v>
       </c>
-      <c r="O9" s="45" t="n"/>
-      <c r="T9" s="41">
+      <c r="O9" s="46" t="n"/>
+      <c r="T9" s="42">
         <f>SUM(H9:S9)</f>
         <v/>
       </c>
-      <c r="U9" s="46" t="inlineStr">
+      <c r="U9" s="47" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V9" s="46" t="inlineStr">
+      <c r="V9" s="47" t="inlineStr">
         <is>
           <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="43">
+      <c r="A10" s="44">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="44">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="44">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="45">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="45">
         <f>Planejado!E10</f>
         <v/>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="44">
         <f>Planejado!F10</f>
         <v/>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="44">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="H10" s="45" t="n">
+      <c r="H10" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="45" t="n">
+      <c r="I10" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="45" t="n">
+      <c r="J10" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="45" t="n">
+      <c r="K10" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="45" t="n">
+      <c r="L10" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="45" t="n">
+      <c r="M10" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="45" t="n">
+      <c r="N10" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="45" t="n"/>
-      <c r="T10" s="41">
+      <c r="O10" s="46" t="n"/>
+      <c r="T10" s="42">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
-      <c r="U10" s="46" t="inlineStr">
+      <c r="U10" s="47" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V10" s="46" t="inlineStr">
+      <c r="V10" s="47" t="inlineStr">
         <is>
           <t>Cancelado — sem cobrança</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="43">
+      <c r="A11" s="44">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B11" s="43">
+      <c r="B11" s="44">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="44">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D11" s="44">
+      <c r="D11" s="45">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="45">
         <f>Planejado!E11</f>
         <v/>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="44">
         <f>Planejado!F11</f>
         <v/>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="44">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="H11" s="45" t="n">
+      <c r="H11" s="46" t="n">
         <v>970</v>
       </c>
-      <c r="I11" s="45" t="n">
+      <c r="I11" s="46" t="n">
         <v>970</v>
       </c>
-      <c r="J11" s="45" t="n">
+      <c r="J11" s="46" t="n">
         <v>970</v>
       </c>
-      <c r="K11" s="45" t="n">
+      <c r="K11" s="46" t="n">
         <v>970</v>
       </c>
-      <c r="L11" s="45" t="n">
+      <c r="L11" s="46" t="n">
         <v>970</v>
       </c>
-      <c r="M11" s="45" t="n">
+      <c r="M11" s="46" t="n">
         <v>970</v>
       </c>
-      <c r="N11" s="45" t="n">
+      <c r="N11" s="46" t="n">
         <v>970</v>
       </c>
-      <c r="O11" s="45" t="n"/>
-      <c r="T11" s="41">
+      <c r="O11" s="46" t="n"/>
+      <c r="T11" s="42">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
-      <c r="U11" s="46" t="inlineStr">
+      <c r="U11" s="47" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V11" s="46" t="n"/>
+      <c r="V11" s="47" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="43">
+      <c r="A12" s="44">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="44">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="44">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="45">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="45">
         <f>Planejado!E12</f>
         <v/>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="44">
         <f>Planejado!F12</f>
         <v/>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="44">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="45" t="n">
+      <c r="I12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="45" t="n">
+      <c r="J12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="45" t="n">
+      <c r="K12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="45" t="n">
+      <c r="L12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="45" t="n">
+      <c r="M12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="45" t="n">
+      <c r="N12" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="45" t="n"/>
-      <c r="T12" s="41">
+      <c r="O12" s="46" t="n"/>
+      <c r="T12" s="42">
         <f>SUM(H12:S12)</f>
         <v/>
       </c>
-      <c r="U12" s="46" t="inlineStr">
+      <c r="U12" s="47" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V12" s="46" t="inlineStr">
+      <c r="V12" s="47" t="inlineStr">
         <is>
           <t>Sem gasto no período</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="43">
+      <c r="A13" s="44">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B13" s="43">
+      <c r="B13" s="44">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="44">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D13" s="44">
+      <c r="D13" s="45">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E13" s="44">
+      <c r="E13" s="45">
         <f>Planejado!E13</f>
         <v/>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="44">
         <f>Planejado!F13</f>
         <v/>
       </c>
-      <c r="G13" s="43">
+      <c r="G13" s="44">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="H13" s="45" t="n">
+      <c r="H13" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="45" t="n">
+      <c r="I13" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="45" t="n">
+      <c r="J13" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="45" t="n">
+      <c r="K13" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="45" t="n">
+      <c r="L13" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="45" t="n">
+      <c r="M13" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="45" t="n">
+      <c r="N13" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="45" t="n"/>
-      <c r="T13" s="41">
+      <c r="O13" s="46" t="n"/>
+      <c r="T13" s="42">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
-      <c r="U13" s="46" t="inlineStr">
+      <c r="U13" s="47" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V13" s="46" t="inlineStr">
+      <c r="V13" s="47" t="inlineStr">
         <is>
           <t>Sem parcela no 1º semestre; bonificação de ago/26 a confirmar</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="43">
+      <c r="A14" s="44">
         <f>Planejado!A14</f>
         <v/>
       </c>
-      <c r="B14" s="43">
+      <c r="B14" s="44">
         <f>Planejado!B14</f>
         <v/>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="44">
         <f>Planejado!C14</f>
         <v/>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="45">
         <f>Planejado!D14</f>
         <v/>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="45">
         <f>Planejado!E14</f>
         <v/>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="44">
         <f>Planejado!F14</f>
         <v/>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="44">
         <f>Planejado!G14</f>
         <v/>
       </c>
-      <c r="H14" s="45" t="n"/>
-      <c r="I14" s="45" t="n"/>
-      <c r="J14" s="45" t="n"/>
-      <c r="K14" s="45" t="n"/>
-      <c r="L14" s="45" t="n"/>
-      <c r="M14" s="45" t="n"/>
-      <c r="N14" s="45" t="n"/>
-      <c r="O14" s="45" t="n"/>
-      <c r="T14" s="41">
+      <c r="H14" s="46" t="n"/>
+      <c r="I14" s="46" t="n"/>
+      <c r="J14" s="46" t="n"/>
+      <c r="K14" s="46" t="n"/>
+      <c r="L14" s="46" t="n"/>
+      <c r="M14" s="46" t="n"/>
+      <c r="N14" s="46" t="n"/>
+      <c r="O14" s="46" t="n"/>
+      <c r="T14" s="42">
         <f>SUM(H14:S14)</f>
         <v/>
       </c>
-      <c r="U14" s="46" t="n"/>
-      <c r="V14" s="46" t="inlineStr">
+      <c r="U14" s="47" t="n"/>
+      <c r="V14" s="47" t="inlineStr">
         <is>
           <t>PREENCHER com o CUSTO TOTAL. Bruto: R$ 2.570,52/mês até jul e R$ 3.070,52 de ago — faltam encargos e benefícios</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="43">
+      <c r="A15" s="44">
         <f>Planejado!A15</f>
         <v/>
       </c>
-      <c r="B15" s="43">
+      <c r="B15" s="44">
         <f>Planejado!B15</f>
         <v/>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="44">
         <f>Planejado!C15</f>
         <v/>
       </c>
-      <c r="D15" s="44">
+      <c r="D15" s="45">
         <f>Planejado!D15</f>
         <v/>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="45">
         <f>Planejado!E15</f>
         <v/>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="44">
         <f>Planejado!F15</f>
         <v/>
       </c>
-      <c r="G15" s="43">
+      <c r="G15" s="44">
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="H15" s="45" t="n">
+      <c r="H15" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="45" t="n">
+      <c r="I15" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="45" t="n">
+      <c r="J15" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="45" t="n">
+      <c r="K15" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="45" t="n">
+      <c r="L15" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="45" t="n">
+      <c r="M15" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="45" t="n">
+      <c r="N15" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="45" t="n"/>
-      <c r="T15" s="41">
+      <c r="O15" s="46" t="n"/>
+      <c r="T15" s="42">
         <f>SUM(H15:S15)</f>
         <v/>
       </c>
-      <c r="U15" s="46" t="inlineStr">
+      <c r="U15" s="47" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V15" s="46" t="inlineStr">
+      <c r="V15" s="47" t="inlineStr">
         <is>
           <t>Sem acionamento no período — confirmar se o contrato segue ativo</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="43">
+      <c r="A16" s="44">
         <f>Planejado!A16</f>
         <v/>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="44">
         <f>Planejado!B16</f>
         <v/>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="44">
         <f>Planejado!C16</f>
         <v/>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="45">
         <f>Planejado!D16</f>
         <v/>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="45">
         <f>Planejado!E16</f>
         <v/>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="44">
         <f>Planejado!F16</f>
         <v/>
       </c>
-      <c r="G16" s="43">
+      <c r="G16" s="44">
         <f>Planejado!G16</f>
         <v/>
       </c>
-      <c r="H16" s="45" t="n">
+      <c r="H16" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="45" t="n">
+      <c r="I16" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="45" t="n">
+      <c r="J16" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="45" t="n">
+      <c r="K16" s="46" t="n">
         <v>6300</v>
       </c>
-      <c r="L16" s="45" t="n">
+      <c r="L16" s="46" t="n">
         <v>6300</v>
       </c>
-      <c r="M16" s="45" t="n">
+      <c r="M16" s="46" t="n">
         <v>6300</v>
       </c>
-      <c r="N16" s="45" t="n">
+      <c r="N16" s="46" t="n">
         <v>6300</v>
       </c>
-      <c r="O16" s="45" t="n"/>
-      <c r="T16" s="41">
+      <c r="O16" s="46" t="n"/>
+      <c r="T16" s="42">
         <f>SUM(H16:S16)</f>
         <v/>
       </c>
-      <c r="U16" s="46" t="inlineStr">
+      <c r="U16" s="47" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V16" s="46" t="inlineStr">
+      <c r="V16" s="47" t="inlineStr">
         <is>
           <t>Entrada em abr/26. R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="43">
+      <c r="A17" s="44">
         <f>Planejado!A17</f>
         <v/>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="44">
         <f>Planejado!B17</f>
         <v/>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="44">
         <f>Planejado!C17</f>
         <v/>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="45">
         <f>Planejado!D17</f>
         <v/>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="45">
         <f>Planejado!E17</f>
         <v/>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="44">
         <f>Planejado!F17</f>
         <v/>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="44">
         <f>Planejado!G17</f>
         <v/>
       </c>
-      <c r="H17" s="45" t="n"/>
-      <c r="I17" s="45" t="n"/>
-      <c r="J17" s="45" t="n"/>
-      <c r="K17" s="45" t="n"/>
-      <c r="L17" s="45" t="n"/>
-      <c r="M17" s="45" t="n"/>
-      <c r="N17" s="45" t="n"/>
-      <c r="O17" s="45" t="n"/>
-      <c r="T17" s="41">
+      <c r="H17" s="46" t="n"/>
+      <c r="I17" s="46" t="n"/>
+      <c r="J17" s="46" t="n"/>
+      <c r="K17" s="46" t="n"/>
+      <c r="L17" s="46" t="n"/>
+      <c r="M17" s="46" t="n"/>
+      <c r="N17" s="46" t="n"/>
+      <c r="O17" s="46" t="n"/>
+      <c r="T17" s="42">
         <f>SUM(H17:S17)</f>
         <v/>
       </c>
-      <c r="U17" s="46" t="n"/>
-      <c r="V17" s="46" t="n"/>
+      <c r="U17" s="47" t="n"/>
+      <c r="V17" s="47" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="43">
+      <c r="A18" s="44">
         <f>Planejado!A18</f>
         <v/>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="44">
         <f>Planejado!B18</f>
         <v/>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="44">
         <f>Planejado!C18</f>
         <v/>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="45">
         <f>Planejado!D18</f>
         <v/>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="45">
         <f>Planejado!E18</f>
         <v/>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="44">
         <f>Planejado!F18</f>
         <v/>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="44">
         <f>Planejado!G18</f>
         <v/>
       </c>
-      <c r="H18" s="45" t="n"/>
-      <c r="I18" s="45" t="n"/>
-      <c r="J18" s="45" t="n"/>
-      <c r="K18" s="45" t="n"/>
-      <c r="L18" s="45" t="n"/>
-      <c r="M18" s="45" t="n"/>
-      <c r="N18" s="45" t="n"/>
-      <c r="O18" s="45" t="n"/>
-      <c r="T18" s="41">
+      <c r="H18" s="46" t="n"/>
+      <c r="I18" s="46" t="n"/>
+      <c r="J18" s="46" t="n"/>
+      <c r="K18" s="46" t="n"/>
+      <c r="L18" s="46" t="n"/>
+      <c r="M18" s="46" t="n"/>
+      <c r="N18" s="46" t="n"/>
+      <c r="O18" s="46" t="n"/>
+      <c r="T18" s="42">
         <f>SUM(H18:S18)</f>
         <v/>
       </c>
-      <c r="U18" s="46" t="n"/>
-      <c r="V18" s="46" t="n"/>
+      <c r="U18" s="47" t="n"/>
+      <c r="V18" s="47" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="43">
+      <c r="A19" s="44">
         <f>Planejado!A19</f>
         <v/>
       </c>
-      <c r="B19" s="43">
+      <c r="B19" s="44">
         <f>Planejado!B19</f>
         <v/>
       </c>
-      <c r="C19" s="43">
+      <c r="C19" s="44">
         <f>Planejado!C19</f>
         <v/>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="45">
         <f>Planejado!D19</f>
         <v/>
       </c>
-      <c r="E19" s="44">
+      <c r="E19" s="45">
         <f>Planejado!E19</f>
         <v/>
       </c>
-      <c r="F19" s="43">
+      <c r="F19" s="44">
         <f>Planejado!F19</f>
         <v/>
       </c>
-      <c r="G19" s="43">
+      <c r="G19" s="44">
         <f>Planejado!G19</f>
         <v/>
       </c>
-      <c r="H19" s="45" t="n"/>
-      <c r="I19" s="45" t="n"/>
-      <c r="J19" s="45" t="n"/>
-      <c r="K19" s="45" t="n"/>
-      <c r="L19" s="45" t="n"/>
-      <c r="M19" s="45" t="n"/>
-      <c r="N19" s="45" t="n"/>
-      <c r="O19" s="45" t="n"/>
-      <c r="T19" s="41">
+      <c r="H19" s="46" t="n"/>
+      <c r="I19" s="46" t="n"/>
+      <c r="J19" s="46" t="n"/>
+      <c r="K19" s="46" t="n"/>
+      <c r="L19" s="46" t="n"/>
+      <c r="M19" s="46" t="n"/>
+      <c r="N19" s="46" t="n"/>
+      <c r="O19" s="46" t="n"/>
+      <c r="T19" s="42">
         <f>SUM(H19:S19)</f>
         <v/>
       </c>
-      <c r="U19" s="46" t="n"/>
-      <c r="V19" s="46" t="n"/>
+      <c r="U19" s="47" t="n"/>
+      <c r="V19" s="47" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="43">
+      <c r="A20" s="44">
         <f>Planejado!A20</f>
         <v/>
       </c>
-      <c r="B20" s="43">
+      <c r="B20" s="44">
         <f>Planejado!B20</f>
         <v/>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="44">
         <f>Planejado!C20</f>
         <v/>
       </c>
-      <c r="D20" s="44">
+      <c r="D20" s="45">
         <f>Planejado!D20</f>
         <v/>
       </c>
-      <c r="E20" s="44">
+      <c r="E20" s="45">
         <f>Planejado!E20</f>
         <v/>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="44">
         <f>Planejado!F20</f>
         <v/>
       </c>
-      <c r="G20" s="43">
+      <c r="G20" s="44">
         <f>Planejado!G20</f>
         <v/>
       </c>
-      <c r="H20" s="45" t="n"/>
-      <c r="I20" s="45" t="n"/>
-      <c r="J20" s="45" t="n"/>
-      <c r="K20" s="45" t="n"/>
-      <c r="L20" s="45" t="n"/>
-      <c r="M20" s="45" t="n"/>
-      <c r="N20" s="45" t="n"/>
-      <c r="O20" s="45" t="n"/>
-      <c r="T20" s="41">
+      <c r="H20" s="46" t="n"/>
+      <c r="I20" s="46" t="n"/>
+      <c r="J20" s="46" t="n"/>
+      <c r="K20" s="46" t="n"/>
+      <c r="L20" s="46" t="n"/>
+      <c r="M20" s="46" t="n"/>
+      <c r="N20" s="46" t="n"/>
+      <c r="O20" s="46" t="n"/>
+      <c r="T20" s="42">
         <f>SUM(H20:S20)</f>
         <v/>
       </c>
-      <c r="U20" s="46" t="n"/>
-      <c r="V20" s="46" t="n"/>
+      <c r="U20" s="47" t="n"/>
+      <c r="V20" s="47" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="43">
+      <c r="A21" s="44">
         <f>Planejado!A21</f>
         <v/>
       </c>
-      <c r="B21" s="43">
+      <c r="B21" s="44">
         <f>Planejado!B21</f>
         <v/>
       </c>
-      <c r="C21" s="43">
+      <c r="C21" s="44">
         <f>Planejado!C21</f>
         <v/>
       </c>
-      <c r="D21" s="44">
+      <c r="D21" s="45">
         <f>Planejado!D21</f>
         <v/>
       </c>
-      <c r="E21" s="44">
+      <c r="E21" s="45">
         <f>Planejado!E21</f>
         <v/>
       </c>
-      <c r="F21" s="43">
+      <c r="F21" s="44">
         <f>Planejado!F21</f>
         <v/>
       </c>
-      <c r="G21" s="43">
+      <c r="G21" s="44">
         <f>Planejado!G21</f>
         <v/>
       </c>
-      <c r="H21" s="45" t="n"/>
-      <c r="I21" s="45" t="n"/>
-      <c r="J21" s="45" t="n"/>
-      <c r="K21" s="45" t="n"/>
-      <c r="L21" s="45" t="n"/>
-      <c r="M21" s="45" t="n"/>
-      <c r="N21" s="45" t="n"/>
-      <c r="O21" s="45" t="n"/>
-      <c r="T21" s="41">
+      <c r="H21" s="46" t="n"/>
+      <c r="I21" s="46" t="n"/>
+      <c r="J21" s="46" t="n"/>
+      <c r="K21" s="46" t="n"/>
+      <c r="L21" s="46" t="n"/>
+      <c r="M21" s="46" t="n"/>
+      <c r="N21" s="46" t="n"/>
+      <c r="O21" s="46" t="n"/>
+      <c r="T21" s="42">
         <f>SUM(H21:S21)</f>
         <v/>
       </c>
-      <c r="U21" s="46" t="n"/>
-      <c r="V21" s="46" t="n"/>
+      <c r="U21" s="47" t="n"/>
+      <c r="V21" s="47" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="43">
+      <c r="A22" s="44">
         <f>Planejado!A22</f>
         <v/>
       </c>
-      <c r="B22" s="43">
+      <c r="B22" s="44">
         <f>Planejado!B22</f>
         <v/>
       </c>
-      <c r="C22" s="43">
+      <c r="C22" s="44">
         <f>Planejado!C22</f>
         <v/>
       </c>
-      <c r="D22" s="44">
+      <c r="D22" s="45">
         <f>Planejado!D22</f>
         <v/>
       </c>
-      <c r="E22" s="44">
+      <c r="E22" s="45">
         <f>Planejado!E22</f>
         <v/>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="44">
         <f>Planejado!F22</f>
         <v/>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="44">
         <f>Planejado!G22</f>
         <v/>
       </c>
-      <c r="H22" s="45" t="n"/>
-      <c r="I22" s="45" t="n"/>
-      <c r="J22" s="45" t="n"/>
-      <c r="K22" s="45" t="n"/>
-      <c r="L22" s="45" t="n"/>
-      <c r="M22" s="45" t="n"/>
-      <c r="N22" s="45" t="n"/>
-      <c r="O22" s="45" t="n"/>
-      <c r="T22" s="41">
+      <c r="H22" s="46" t="n"/>
+      <c r="I22" s="46" t="n"/>
+      <c r="J22" s="46" t="n"/>
+      <c r="K22" s="46" t="n"/>
+      <c r="L22" s="46" t="n"/>
+      <c r="M22" s="46" t="n"/>
+      <c r="N22" s="46" t="n"/>
+      <c r="O22" s="46" t="n"/>
+      <c r="T22" s="42">
         <f>SUM(H22:S22)</f>
         <v/>
       </c>
-      <c r="U22" s="46" t="n"/>
-      <c r="V22" s="46" t="n"/>
+      <c r="U22" s="47" t="n"/>
+      <c r="V22" s="47" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="43">
+      <c r="A23" s="44">
         <f>Planejado!A23</f>
         <v/>
       </c>
-      <c r="B23" s="43">
+      <c r="B23" s="44">
         <f>Planejado!B23</f>
         <v/>
       </c>
-      <c r="C23" s="43">
+      <c r="C23" s="44">
         <f>Planejado!C23</f>
         <v/>
       </c>
-      <c r="D23" s="44">
+      <c r="D23" s="45">
         <f>Planejado!D23</f>
         <v/>
       </c>
-      <c r="E23" s="44">
+      <c r="E23" s="45">
         <f>Planejado!E23</f>
         <v/>
       </c>
-      <c r="F23" s="43">
+      <c r="F23" s="44">
         <f>Planejado!F23</f>
         <v/>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="44">
         <f>Planejado!G23</f>
         <v/>
       </c>
-      <c r="H23" s="45" t="n"/>
-      <c r="I23" s="45" t="n"/>
-      <c r="J23" s="45" t="n"/>
-      <c r="K23" s="45" t="n"/>
-      <c r="L23" s="45" t="n"/>
-      <c r="M23" s="45" t="n"/>
-      <c r="N23" s="45" t="n"/>
-      <c r="O23" s="45" t="n"/>
-      <c r="T23" s="41">
+      <c r="H23" s="46" t="n"/>
+      <c r="I23" s="46" t="n"/>
+      <c r="J23" s="46" t="n"/>
+      <c r="K23" s="46" t="n"/>
+      <c r="L23" s="46" t="n"/>
+      <c r="M23" s="46" t="n"/>
+      <c r="N23" s="46" t="n"/>
+      <c r="O23" s="46" t="n"/>
+      <c r="T23" s="42">
         <f>SUM(H23:S23)</f>
         <v/>
       </c>
-      <c r="U23" s="46" t="n"/>
-      <c r="V23" s="46" t="n"/>
+      <c r="U23" s="47" t="n"/>
+      <c r="V23" s="47" t="n"/>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="43">
+      <c r="A24" s="44">
         <f>Planejado!A24</f>
         <v/>
       </c>
-      <c r="B24" s="43">
+      <c r="B24" s="44">
         <f>Planejado!B24</f>
         <v/>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="44">
         <f>Planejado!C24</f>
         <v/>
       </c>
-      <c r="D24" s="44">
+      <c r="D24" s="45">
         <f>Planejado!D24</f>
         <v/>
       </c>
-      <c r="E24" s="44">
+      <c r="E24" s="45">
         <f>Planejado!E24</f>
         <v/>
       </c>
-      <c r="F24" s="43">
+      <c r="F24" s="44">
         <f>Planejado!F24</f>
         <v/>
       </c>
-      <c r="G24" s="43">
+      <c r="G24" s="44">
         <f>Planejado!G24</f>
         <v/>
       </c>
-      <c r="H24" s="45" t="n"/>
-      <c r="I24" s="45" t="n"/>
-      <c r="J24" s="45" t="n"/>
-      <c r="K24" s="45" t="n"/>
-      <c r="L24" s="45" t="n"/>
-      <c r="M24" s="45" t="n"/>
-      <c r="N24" s="45" t="n"/>
-      <c r="O24" s="45" t="n"/>
-      <c r="T24" s="41">
+      <c r="H24" s="46" t="n"/>
+      <c r="I24" s="46" t="n"/>
+      <c r="J24" s="46" t="n"/>
+      <c r="K24" s="46" t="n"/>
+      <c r="L24" s="46" t="n"/>
+      <c r="M24" s="46" t="n"/>
+      <c r="N24" s="46" t="n"/>
+      <c r="O24" s="46" t="n"/>
+      <c r="T24" s="42">
         <f>SUM(H24:S24)</f>
         <v/>
       </c>
-      <c r="U24" s="46" t="n"/>
-      <c r="V24" s="46" t="n"/>
+      <c r="U24" s="47" t="n"/>
+      <c r="V24" s="47" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="43">
+      <c r="A25" s="44">
         <f>Planejado!A25</f>
         <v/>
       </c>
-      <c r="B25" s="43">
+      <c r="B25" s="44">
         <f>Planejado!B25</f>
         <v/>
       </c>
-      <c r="C25" s="43">
+      <c r="C25" s="44">
         <f>Planejado!C25</f>
         <v/>
       </c>
-      <c r="D25" s="44">
+      <c r="D25" s="45">
         <f>Planejado!D25</f>
         <v/>
       </c>
-      <c r="E25" s="44">
+      <c r="E25" s="45">
         <f>Planejado!E25</f>
         <v/>
       </c>
-      <c r="F25" s="43">
+      <c r="F25" s="44">
         <f>Planejado!F25</f>
         <v/>
       </c>
-      <c r="G25" s="43">
+      <c r="G25" s="44">
         <f>Planejado!G25</f>
         <v/>
       </c>
-      <c r="H25" s="45" t="n"/>
-      <c r="I25" s="45" t="n"/>
-      <c r="J25" s="45" t="n"/>
-      <c r="K25" s="45" t="n"/>
-      <c r="L25" s="45" t="n"/>
-      <c r="M25" s="45" t="n"/>
-      <c r="N25" s="45" t="n"/>
-      <c r="O25" s="45" t="n"/>
-      <c r="T25" s="41">
+      <c r="H25" s="46" t="n"/>
+      <c r="I25" s="46" t="n"/>
+      <c r="J25" s="46" t="n"/>
+      <c r="K25" s="46" t="n"/>
+      <c r="L25" s="46" t="n"/>
+      <c r="M25" s="46" t="n"/>
+      <c r="N25" s="46" t="n"/>
+      <c r="O25" s="46" t="n"/>
+      <c r="T25" s="42">
         <f>SUM(H25:S25)</f>
         <v/>
       </c>
-      <c r="U25" s="46" t="n"/>
-      <c r="V25" s="46" t="n"/>
+      <c r="U25" s="47" t="n"/>
+      <c r="V25" s="47" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="47" t="inlineStr">
+      <c r="A26" s="48" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B26" s="47" t="n"/>
-      <c r="C26" s="47" t="n"/>
-      <c r="D26" s="47" t="n"/>
-      <c r="E26" s="47" t="n"/>
-      <c r="F26" s="47" t="n"/>
-      <c r="G26" s="47" t="n"/>
-      <c r="H26" s="48">
+      <c r="B26" s="48" t="n"/>
+      <c r="C26" s="48" t="n"/>
+      <c r="D26" s="48" t="n"/>
+      <c r="E26" s="48" t="n"/>
+      <c r="F26" s="48" t="n"/>
+      <c r="G26" s="48" t="n"/>
+      <c r="H26" s="49">
         <f>SUM(H5:H25)</f>
         <v/>
       </c>
-      <c r="I26" s="48">
+      <c r="I26" s="49">
         <f>SUM(I5:I25)</f>
         <v/>
       </c>
-      <c r="J26" s="48">
+      <c r="J26" s="49">
         <f>SUM(J5:J25)</f>
         <v/>
       </c>
-      <c r="K26" s="48">
+      <c r="K26" s="49">
         <f>SUM(K5:K25)</f>
         <v/>
       </c>
-      <c r="L26" s="48">
+      <c r="L26" s="49">
         <f>SUM(L5:L25)</f>
         <v/>
       </c>
-      <c r="M26" s="48">
+      <c r="M26" s="49">
         <f>SUM(M5:M25)</f>
         <v/>
       </c>
-      <c r="N26" s="48">
+      <c r="N26" s="49">
         <f>SUM(N5:N25)</f>
         <v/>
       </c>
-      <c r="O26" s="48">
+      <c r="O26" s="49">
         <f>SUM(O5:O25)</f>
         <v/>
       </c>
-      <c r="P26" s="48">
+      <c r="P26" s="49">
         <f>SUM(P5:P25)</f>
         <v/>
       </c>
-      <c r="Q26" s="48">
+      <c r="Q26" s="49">
         <f>SUM(Q5:Q25)</f>
         <v/>
       </c>
-      <c r="R26" s="48">
+      <c r="R26" s="49">
         <f>SUM(R5:R25)</f>
         <v/>
       </c>
-      <c r="S26" s="48">
+      <c r="S26" s="49">
         <f>SUM(S5:S25)</f>
         <v/>
       </c>
-      <c r="T26" s="48">
+      <c r="T26" s="49">
         <f>SUM(T5:T25)</f>
         <v/>
       </c>
-      <c r="U26" s="47" t="n"/>
-      <c r="V26" s="47" t="n"/>
+      <c r="U26" s="48" t="n"/>
+      <c r="V26" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6376,609 +6416,609 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Mês</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Jurídico Plan.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Jurídico Real.</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>TI Plan.</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>TI Real.</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Total Plan.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Total Real.</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Desvio do mês (R$)</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Realizado acum.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>SUMIFS(Planejado!$H$5:$H$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>SUMIFS(Realizado!$H$5:$H$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>SUMIFS(Planejado!$H$5:$H$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>SUMIFS(Realizado!$H$5:$H$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>B5+D5</f>
         <v/>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="31">
         <f>C5+E5</f>
         <v/>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="31">
         <f>G5-F5</f>
         <v/>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="31">
         <f>SUM($F$5:F5)</f>
         <v/>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="31">
         <f>SUM($G$5:G5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="37">
         <f>SUMIFS(Planejado!$I$5:$I$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="37">
         <f>SUMIFS(Realizado!$I$5:$I$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="37">
         <f>SUMIFS(Planejado!$I$5:$I$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="37">
         <f>SUMIFS(Realizado!$I$5:$I$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="37">
         <f>B6+D6</f>
         <v/>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="37">
         <f>C6+E6</f>
         <v/>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="37">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="37">
         <f>SUM($F$5:F6)</f>
         <v/>
       </c>
-      <c r="J6" s="36">
+      <c r="J6" s="37">
         <f>SUM($G$5:G6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <f>SUMIFS(Planejado!$J$5:$J$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>SUMIFS(Realizado!$J$5:$J$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>SUMIFS(Planejado!$J$5:$J$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>SUMIFS(Realizado!$J$5:$J$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>B7+D7</f>
         <v/>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <f>C7+E7</f>
         <v/>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <f>SUM($F$5:F7)</f>
         <v/>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="31">
         <f>SUM($G$5:G7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="37">
         <f>SUMIFS(Planejado!$K$5:$K$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="37">
         <f>SUMIFS(Realizado!$K$5:$K$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="37">
         <f>SUMIFS(Planejado!$K$5:$K$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="37">
         <f>SUMIFS(Realizado!$K$5:$K$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="37">
         <f>B8+D8</f>
         <v/>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="37">
         <f>C8+E8</f>
         <v/>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="37">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="37">
         <f>SUM($F$5:F8)</f>
         <v/>
       </c>
-      <c r="J8" s="36">
+      <c r="J8" s="37">
         <f>SUM($G$5:G8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <f>SUMIFS(Planejado!$L$5:$L$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>SUMIFS(Realizado!$L$5:$L$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>SUMIFS(Planejado!$L$5:$L$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>SUMIFS(Realizado!$L$5:$L$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>B9+D9</f>
         <v/>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <f>C9+E9</f>
         <v/>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <f>SUM($F$5:F9)</f>
         <v/>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="31">
         <f>SUM($G$5:G9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="37">
         <f>SUMIFS(Planejado!$M$5:$M$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="37">
         <f>SUMIFS(Realizado!$M$5:$M$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="37">
         <f>SUMIFS(Planejado!$M$5:$M$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="37">
         <f>SUMIFS(Realizado!$M$5:$M$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="37">
         <f>B10+D10</f>
         <v/>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="37">
         <f>C10+E10</f>
         <v/>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="37">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="37">
         <f>SUM($F$5:F10)</f>
         <v/>
       </c>
-      <c r="J10" s="36">
+      <c r="J10" s="37">
         <f>SUM($G$5:G10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>SUMIFS(Planejado!$N$5:$N$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>SUMIFS(Realizado!$N$5:$N$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>SUMIFS(Planejado!$N$5:$N$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>SUMIFS(Realizado!$N$5:$N$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>B11+D11</f>
         <v/>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <f>C11+E11</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="31">
         <f>SUM($F$5:F11)</f>
         <v/>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="31">
         <f>SUM($G$5:G11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="37">
         <f>SUMIFS(Planejado!$O$5:$O$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="37">
         <f>SUMIFS(Realizado!$O$5:$O$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="37">
         <f>SUMIFS(Planejado!$O$5:$O$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="37">
         <f>SUMIFS(Realizado!$O$5:$O$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="37">
         <f>B12+D12</f>
         <v/>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="37">
         <f>C12+E12</f>
         <v/>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="37">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="37">
         <f>SUM($F$5:F12)</f>
         <v/>
       </c>
-      <c r="J12" s="36">
+      <c r="J12" s="37">
         <f>SUM($G$5:G12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>SUMIFS(Realizado!$P$5:$P$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>SUMIFS(Realizado!$P$5:$P$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>B13+D13</f>
         <v/>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <f>C13+E13</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="31">
         <f>SUM($F$5:F13)</f>
         <v/>
       </c>
-      <c r="J13" s="30">
+      <c r="J13" s="31">
         <f>SUM($G$5:G13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="37">
         <f>SUMIFS(Planejado!$Q$5:$Q$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>SUMIFS(Realizado!$Q$5:$Q$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="37">
         <f>SUMIFS(Planejado!$Q$5:$Q$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="37">
         <f>SUMIFS(Realizado!$Q$5:$Q$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="37">
         <f>B14+D14</f>
         <v/>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="37">
         <f>C14+E14</f>
         <v/>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="37">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="37">
         <f>SUM($F$5:F14)</f>
         <v/>
       </c>
-      <c r="J14" s="36">
+      <c r="J14" s="37">
         <f>SUM($G$5:G14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="49" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <f>SUMIFS(Planejado!$R$5:$R$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>SUMIFS(Realizado!$R$5:$R$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <f>SUMIFS(Planejado!$R$5:$R$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <f>SUMIFS(Realizado!$R$5:$R$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <f>B15+D15</f>
         <v/>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <f>C15+E15</f>
         <v/>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <f>G15-F15</f>
         <v/>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="31">
         <f>SUM($F$5:F15)</f>
         <v/>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="31">
         <f>SUM($G$5:G15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="50" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="37">
         <f>SUMIFS(Planejado!$S$5:$S$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="37">
         <f>SUMIFS(Realizado!$S$5:$S$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="37">
         <f>SUMIFS(Planejado!$S$5:$S$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="37">
         <f>SUMIFS(Realizado!$S$5:$S$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="37">
         <f>B16+D16</f>
         <v/>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="37">
         <f>C16+E16</f>
         <v/>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="37">
         <f>G16-F16</f>
         <v/>
       </c>
-      <c r="I16" s="36">
+      <c r="I16" s="37">
         <f>SUM($F$5:F16)</f>
         <v/>
       </c>
-      <c r="J16" s="36">
+      <c r="J16" s="37">
         <f>SUM($G$5:G16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="17">
         <f>SUM(B5:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="17">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="17">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="17">
         <f>SUM(E5:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="17">
         <f>SUM(F5:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="17">
         <f>SUM(G5:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="17">
         <f>SUM(H5:H16)</f>
         <v/>
       </c>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7034,397 +7074,397 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Jurídico — Plan.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Jurídico — Real.</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>TI — Plan.</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>TI — Real.</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Total Planejado acum.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Total Realizado acum.</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Desvio (R$)</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Desvio (%)</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Orçado do ano</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>B5+D5</f>
         <v/>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="31">
         <f>C5+E5</f>
         <v/>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="31">
         <f>G5-F5</f>
         <v/>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="53">
         <f>IFERROR(H5/F5,"")</f>
         <v/>
       </c>
-      <c r="J5" s="30">
+      <c r="J5" s="31">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="53" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="37">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="37">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="37">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="37">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="37">
         <f>B6+D6</f>
         <v/>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="37">
         <f>C6+E6</f>
         <v/>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="37">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="55">
         <f>IFERROR(H6/F6,"")</f>
         <v/>
       </c>
-      <c r="J6" s="36">
+      <c r="J6" s="37">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="51" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>B7+D7</f>
         <v/>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <f>C7+E7</f>
         <v/>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="53">
         <f>IFERROR(H7/F7,"")</f>
         <v/>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="31">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="53" t="inlineStr">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="37">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="37">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="37">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="37">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="37">
         <f>B8+D8</f>
         <v/>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="37">
         <f>C8+E8</f>
         <v/>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="37">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="54">
+      <c r="I8" s="55">
         <f>IFERROR(H8/F8,"")</f>
         <v/>
       </c>
-      <c r="J8" s="36">
+      <c r="J8" s="37">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="51" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>B9+D9</f>
         <v/>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <f>C9+E9</f>
         <v/>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="53">
         <f>IFERROR(H9/F9,"")</f>
         <v/>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="31">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="53" t="inlineStr">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="37">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="37">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="37">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="37">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="37">
         <f>B10+D10</f>
         <v/>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="37">
         <f>C10+E10</f>
         <v/>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="37">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="54">
+      <c r="I10" s="55">
         <f>IFERROR(H10/F10,"")</f>
         <v/>
       </c>
-      <c r="J10" s="36">
+      <c r="J10" s="37">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="51" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>Móveis e Utensílios</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>B11+D11</f>
         <v/>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <f>C11+E11</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="52">
+      <c r="I11" s="53">
         <f>IFERROR(H11/F11,"")</f>
         <v/>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="31">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="17">
         <f>SUM(B5:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="17">
         <f>SUM(C5:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="17">
         <f>SUM(D5:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="17">
         <f>SUM(E5:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="17">
         <f>SUM(F5:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="17">
         <f>SUM(G5:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="17">
         <f>SUM(H5:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="18">
         <f>IFERROR(H12/F12,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="17">
         <f>SUM(J5:J11)</f>
         <v/>
       </c>
@@ -7478,576 +7518,576 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Tema</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>O que está em aberto</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Impacto no comparativo</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Responsável</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="55" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="56" t="inlineStr">
-        <is>
-          <t>Custo total da Geovanna — A LANÇAR</t>
-        </is>
-      </c>
-      <c r="C5" s="56" t="inlineStr">
-        <is>
-          <t>O planejado dela é R$ 4.825,52/mês, que é o custo total orçado na ficha (salário + encargos de folha + benefícios). O dado disponível hoje é só o salário bruto, R$ 2.886,91/mês. O realizado está em branco.</t>
-        </is>
-      </c>
-      <c r="D5" s="56" t="inlineStr">
-        <is>
-          <t>Lançar só o bruto contra um orçado de custo total mostraria economia de R$ 1.938,61/mês que não existe. Peça ao RH o custo total mensal dela, ou o bruto mais os encargos para somar antes de lançar.</t>
-        </is>
-      </c>
-      <c r="E5" s="56" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
+        <is>
+          <t>Geovanna — realizado em base diferente do orçado</t>
+        </is>
+      </c>
+      <c r="C5" s="57" t="inlineStr">
+        <is>
+          <t>O planejado dela é R$ 4.825,52/mês, que é o CUSTO TOTAL orçado na ficha (salário + encargos de folha + benefícios). O realizado lançado é o SALÁRIO BRUTO, R$ 2.886,91/mês, confirmado sem alteração no ano. São bases diferentes.</t>
+        </is>
+      </c>
+      <c r="D5" s="57" t="inlineStr">
+        <is>
+          <t>O desvio desta linha (−R$ 1.938,61/mês, −R$ 13.570,24 no acumulado jan–jul) NÃO é economia: é o encargo que falta do lado do realizado. Para fechar, peça ao RH o custo total mensal dela — ou o percentual de encargos da empresa, que dá para calcular a partir do bruto.</t>
+        </is>
+      </c>
+      <c r="E5" s="57" t="inlineStr">
         <is>
           <t>Cristiane + RH</t>
         </is>
       </c>
-      <c r="F5" s="57" t="inlineStr">
+      <c r="F5" s="58" t="inlineStr">
+        <is>
+          <t>BASE DIFERENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>Vinicius — custo total A LANÇAR</t>
+        </is>
+      </c>
+      <c r="C6" s="60" t="inlineStr">
+        <is>
+          <t>Mesmo caso da Geovanna. O planejado é R$ 5.416,525/mês (custo total). Brutos confirmados: R$ 2.570,52 até jul/26 e R$ 3.070,52 a partir de 05/08/26 — o aumento é absorvido pela folga do envelope, que já previa reajuste, então o orçado não muda. O realizado está em branco.</t>
+        </is>
+      </c>
+      <c r="D6" s="60" t="inlineStr">
+        <is>
+          <t>A folga do orçado NÃO é economia estrutural. Com o bruto de agosto, sobram R$ 2.346,01 para encargos, o que equivale a 76% sobre o bruto — dentro da faixa normal (67% a 80%), então pode sobrar ou estourar. Só o custo total real vai dizer.</t>
+        </is>
+      </c>
+      <c r="E6" s="60" t="inlineStr">
+        <is>
+          <t>Cristiane + RH</t>
+        </is>
+      </c>
+      <c r="F6" s="58" t="inlineStr">
         <is>
           <t>A LANÇAR</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="58" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="59" t="inlineStr">
-        <is>
-          <t>Custo total do Vinicius — A LANÇAR</t>
-        </is>
-      </c>
-      <c r="C6" s="59" t="inlineStr">
-        <is>
-          <t>Mesmo caso da Geovanna. O planejado é R$ 5.416,525/mês (custo total). Brutos confirmados: R$ 2.570,52 até jul/26 e R$ 3.070,52 a partir de 05/08/26 — o aumento é absorvido pela folga do envelope, que já previa reajuste, então o orçado não muda. O realizado está em branco.</t>
-        </is>
-      </c>
-      <c r="D6" s="59" t="inlineStr">
-        <is>
-          <t>A folga do orçado NÃO é economia estrutural. Com o bruto de agosto, sobram R$ 2.346,01 para encargos, o que equivale a 76% sobre o bruto — dentro da faixa normal (67% a 80%), então pode sobrar ou estourar. Só o custo total real vai dizer.</t>
-        </is>
-      </c>
-      <c r="E6" s="59" t="inlineStr">
-        <is>
-          <t>Cristiane + RH</t>
-        </is>
-      </c>
-      <c r="F6" s="57" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="inlineStr">
+        <is>
+          <t>Aumento da Thamar em abr/26</t>
+        </is>
+      </c>
+      <c r="C7" s="57" t="inlineStr">
+        <is>
+          <t>Recebia R$ 4.500/mês de jan a mar, abaixo dos R$ 5.000 orçados. Em abr/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
+        </is>
+      </c>
+      <c r="D7" s="57" t="inlineStr">
+        <is>
+          <t>No acumulado jan–jul o efeito líquido é de apenas R$ 500 acima do orçado (−R$ 1.500 em jan–mar, +R$ 2.000 em abr–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
+        </is>
+      </c>
+      <c r="E7" s="57" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F7" s="61" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="59" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>Jusbrasil 30% acima do orçado</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="inlineStr">
+        <is>
+          <t>Orçado R$ 104,90/mês, realizado R$ 136,00/mês em mai, jun e jul.</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="inlineStr">
+        <is>
+          <t>Menor desvio em reais (R$ 31,10/mês), mas o maior em percentual. Vale conferir se houve reajuste contratual ou mudança de plano.</t>
+        </is>
+      </c>
+      <c r="E8" s="60" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F8" s="62" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="56" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B9" s="57" t="inlineStr">
+        <is>
+          <t>Bonificação de ago/26 do Jurídico</t>
+        </is>
+      </c>
+      <c r="C9" s="57" t="inlineStr">
+        <is>
+          <t>Estão orçados R$ 10.293,60 em agosto e R$ 12.867,00 em dezembro. O realizado de agosto ainda não foi informado.</t>
+        </is>
+      </c>
+      <c r="D9" s="57" t="inlineStr">
+        <is>
+          <t>É a maior despesa isolada do Jurídico no segundo semestre.</t>
+        </is>
+      </c>
+      <c r="E9" s="57" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F9" s="62" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>Jonathan R$ 3.700/mês abaixo do contratado</t>
+        </is>
+      </c>
+      <c r="C10" s="60" t="inlineStr">
+        <is>
+          <t>Orçado R$ 10.000/mês, realizado R$ 6.300/mês em mai, jun e jul.</t>
+        </is>
+      </c>
+      <c r="D10" s="60" t="inlineStr">
+        <is>
+          <t>Maior desvio em reais de todo o orçamento: R$ 11.100 em três meses. Se o valor menor for o novo padrão, o planejado de ago a dez deve ser revisado para baixo — sobrariam R$ 18.500 no orçamento do TI.</t>
+        </is>
+      </c>
+      <c r="E10" s="60" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F10" s="62" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="56" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B11" s="57" t="inlineStr">
+        <is>
+          <t>Elias Benedito zerado nos três meses</t>
+        </is>
+      </c>
+      <c r="C11" s="57" t="inlineStr">
+        <is>
+          <t>Orçado R$ 1.065/mês como suporte técnico terceirizado, realizado R$ 0 em mai, jun e jul.</t>
+        </is>
+      </c>
+      <c r="D11" s="57" t="inlineStr">
+        <is>
+          <t>Confirmar se o contrato segue ativo (acionamento sob demanda) ou se foi encerrado. Se encerrado, são R$ 12.780 a liberar no orçamento do ano.</t>
+        </is>
+      </c>
+      <c r="E11" s="57" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F11" s="62" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="59" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>Planejado de jan a abr — CONFERIR</t>
+        </is>
+      </c>
+      <c r="C12" s="60" t="inlineStr">
+        <is>
+          <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
+        </is>
+      </c>
+      <c r="E12" s="60" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F12" s="63" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="56" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B13" s="57" t="inlineStr">
+        <is>
+          <t>Realizado de jan a abr — A LANÇAR</t>
+        </is>
+      </c>
+      <c r="C13" s="57" t="inlineStr">
+        <is>
+          <t>As colunas de jan a abr estão em branco na aba Realizado. Só mai, jun e jul foram informados.</t>
+        </is>
+      </c>
+      <c r="D13" s="57" t="inlineStr">
+        <is>
+          <t>São 4 dos 7 meses já fechados do ano. Sem eles o acumulado e o Painel refletem menos da metade do período decorrido.</t>
+        </is>
+      </c>
+      <c r="E13" s="57" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F13" s="58" t="inlineStr">
         <is>
           <t>A LANÇAR</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="55" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B7" s="56" t="inlineStr">
-        <is>
-          <t>Aumento da Thamar em abr/26</t>
-        </is>
-      </c>
-      <c r="C7" s="56" t="inlineStr">
-        <is>
-          <t>Recebia R$ 4.500/mês de jan a mar, abaixo dos R$ 5.000 orçados. Em abr/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
-        </is>
-      </c>
-      <c r="D7" s="56" t="inlineStr">
-        <is>
-          <t>No acumulado jan–jul o efeito líquido é de apenas R$ 500 acima do orçado (−R$ 1.500 em jan–mar, +R$ 2.000 em abr–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
-        </is>
-      </c>
-      <c r="E7" s="56" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="59" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>Despesas do TI — A LANÇAR</t>
+        </is>
+      </c>
+      <c r="C14" s="60" t="inlineStr">
+        <is>
+          <t>As 9 linhas de despesas do TI (peças, backup, Adapta, antivírus, Office, sala de reunião, cursos, app de gravação e bonificação) não têm lançamento em nenhum mês.</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="inlineStr">
+        <is>
+          <t>São R$ 89.040 orçados no ano, 35% do orçamento do TI. Sem lançamento, o departamento aparece com desvio negativo que é ausência de dado.</t>
+        </is>
+      </c>
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F7" s="60" t="inlineStr">
-        <is>
-          <t>APLICADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="58" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B8" s="59" t="inlineStr">
-        <is>
-          <t>Jusbrasil 30% acima do orçado</t>
-        </is>
-      </c>
-      <c r="C8" s="59" t="inlineStr">
-        <is>
-          <t>Orçado R$ 104,90/mês, realizado R$ 136,00/mês em mai, jun e jul.</t>
-        </is>
-      </c>
-      <c r="D8" s="59" t="inlineStr">
-        <is>
-          <t>Menor desvio em reais (R$ 31,10/mês), mas o maior em percentual. Vale conferir se houve reajuste contratual ou mudança de plano.</t>
-        </is>
-      </c>
-      <c r="E8" s="59" t="inlineStr">
+      <c r="F14" s="58" t="inlineStr">
+        <is>
+          <t>A LANÇAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="57" t="inlineStr">
+        <is>
+          <t>Base de meses — reconciliada com a ficha original</t>
+        </is>
+      </c>
+      <c r="C15" s="57" t="inlineStr">
+        <is>
+          <t>A ficha trazia a coluna TOTAL do TI digitada à mão em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9) enquanto o grid mensal tinha só 8 colunas. Com o período em jan–dez os três totais batem exatamente: R$ 64.998,30 + R$ 12.780,00 + R$ 90.000,00 = R$ 167.778,30, o valor da ficha. Não era erro de digitação — era o grid que estava incompleto.</t>
+        </is>
+      </c>
+      <c r="D15" s="57" t="inlineStr">
+        <is>
+          <t>Equipe de TI no valor original de R$ 167.778,30. Jonathan lançado com entrada em abr/26 (9 meses), que é o que explica os R$ 90.000.</t>
+        </is>
+      </c>
+      <c r="E15" s="57" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F8" s="61" t="inlineStr">
+      <c r="F15" s="61" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" s="60" t="inlineStr">
+        <is>
+          <t>Origem do valor realizado</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto. Até aqui os números vieram informados pela gestora.</t>
+        </is>
+      </c>
+      <c r="D16" s="60" t="inlineStr">
+        <is>
+          <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
+        </is>
+      </c>
+      <c r="E16" s="60" t="inlineStr">
+        <is>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F16" s="62" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="55" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B9" s="56" t="inlineStr">
-        <is>
-          <t>Bonificação de ago/26 do Jurídico</t>
-        </is>
-      </c>
-      <c r="C9" s="56" t="inlineStr">
-        <is>
-          <t>Estão orçados R$ 10.293,60 em agosto e R$ 12.867,00 em dezembro. O realizado de agosto ainda não foi informado.</t>
-        </is>
-      </c>
-      <c r="D9" s="56" t="inlineStr">
-        <is>
-          <t>É a maior despesa isolada do Jurídico no segundo semestre.</t>
-        </is>
-      </c>
-      <c r="E9" s="56" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B17" s="57" t="inlineStr">
+        <is>
+          <t>Jusfy x Astrea</t>
+        </is>
+      </c>
+      <c r="C17" s="57" t="inlineStr">
+        <is>
+          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
+        </is>
+      </c>
+      <c r="D17" s="57" t="inlineStr">
+        <is>
+          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado dos meses seguintes.</t>
+        </is>
+      </c>
+      <c r="E17" s="57" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F9" s="61" t="inlineStr">
+      <c r="F17" s="61" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B18" s="60" t="inlineStr">
+        <is>
+          <t>Rateio dos softwares corporativos de TI</t>
+        </is>
+      </c>
+      <c r="C18" s="60" t="inlineStr">
+        <is>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="inlineStr">
+        <is>
+          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
+        </is>
+      </c>
+      <c r="E18" s="60" t="inlineStr">
+        <is>
+          <t>Cristiane + Controladoria</t>
+        </is>
+      </c>
+      <c r="F18" s="62" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="58" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B10" s="59" t="inlineStr">
-        <is>
-          <t>Jonathan R$ 3.700/mês abaixo do contratado</t>
-        </is>
-      </c>
-      <c r="C10" s="59" t="inlineStr">
-        <is>
-          <t>Orçado R$ 10.000/mês, realizado R$ 6.300/mês em mai, jun e jul.</t>
-        </is>
-      </c>
-      <c r="D10" s="59" t="inlineStr">
-        <is>
-          <t>Maior desvio em reais de todo o orçamento: R$ 11.100 em três meses. Se o valor menor for o novo padrão, o planejado de ago a dez deve ser revisado para baixo — sobrariam R$ 18.500 no orçamento do TI.</t>
-        </is>
-      </c>
-      <c r="E10" s="59" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="57" t="inlineStr">
+        <is>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
+        </is>
+      </c>
+      <c r="C19" s="57" t="inlineStr">
+        <is>
+          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+        </is>
+      </c>
+      <c r="D19" s="57" t="inlineStr">
+        <is>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+        </is>
+      </c>
+      <c r="E19" s="57" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F10" s="61" t="inlineStr">
+      <c r="F19" s="62" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="55" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B11" s="56" t="inlineStr">
-        <is>
-          <t>Elias Benedito zerado nos três meses</t>
-        </is>
-      </c>
-      <c r="C11" s="56" t="inlineStr">
-        <is>
-          <t>Orçado R$ 1.065/mês como suporte técnico terceirizado, realizado R$ 0 em mai, jun e jul.</t>
-        </is>
-      </c>
-      <c r="D11" s="56" t="inlineStr">
-        <is>
-          <t>Confirmar se o contrato segue ativo (acionamento sob demanda) ou se foi encerrado. Se encerrado, são R$ 12.780 a liberar no orçamento do ano.</t>
-        </is>
-      </c>
-      <c r="E11" s="56" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="60" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C20" s="60" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E20" s="60" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F11" s="61" t="inlineStr">
+      <c r="F20" s="62" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="58" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B12" s="59" t="inlineStr">
-        <is>
-          <t>Planejado de jan a abr — CONFERIR</t>
-        </is>
-      </c>
-      <c r="C12" s="59" t="inlineStr">
-        <is>
-          <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
-        </is>
-      </c>
-      <c r="D12" s="59" t="inlineStr">
-        <is>
-          <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
-        </is>
-      </c>
-      <c r="E12" s="59" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F12" s="62" t="inlineStr">
-        <is>
-          <t>CONFERIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="55" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="B13" s="56" t="inlineStr">
-        <is>
-          <t>Realizado de jan a abr — A LANÇAR</t>
-        </is>
-      </c>
-      <c r="C13" s="56" t="inlineStr">
-        <is>
-          <t>As colunas de jan a abr estão em branco na aba Realizado. Só mai, jun e jul foram informados.</t>
-        </is>
-      </c>
-      <c r="D13" s="56" t="inlineStr">
-        <is>
-          <t>São 4 dos 7 meses já fechados do ano. Sem eles o acumulado e o Painel refletem menos da metade do período decorrido.</t>
-        </is>
-      </c>
-      <c r="E13" s="56" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F13" s="57" t="inlineStr">
-        <is>
-          <t>A LANÇAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="58" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="B14" s="59" t="inlineStr">
-        <is>
-          <t>Despesas do TI — A LANÇAR</t>
-        </is>
-      </c>
-      <c r="C14" s="59" t="inlineStr">
-        <is>
-          <t>As 9 linhas de despesas do TI (peças, backup, Adapta, antivírus, Office, sala de reunião, cursos, app de gravação e bonificação) não têm lançamento em nenhum mês.</t>
-        </is>
-      </c>
-      <c r="D14" s="59" t="inlineStr">
-        <is>
-          <t>São R$ 89.040 orçados no ano, 35% do orçamento do TI. Sem lançamento, o departamento aparece com desvio negativo que é ausência de dado.</t>
-        </is>
-      </c>
-      <c r="E14" s="59" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F14" s="57" t="inlineStr">
-        <is>
-          <t>A LANÇAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B15" s="56" t="inlineStr">
-        <is>
-          <t>Base de meses — reconciliada com a ficha original</t>
-        </is>
-      </c>
-      <c r="C15" s="56" t="inlineStr">
-        <is>
-          <t>A ficha trazia a coluna TOTAL do TI digitada à mão em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9) enquanto o grid mensal tinha só 8 colunas. Com o período em jan–dez os três totais batem exatamente: R$ 64.998,30 + R$ 12.780,00 + R$ 90.000,00 = R$ 167.778,30, o valor da ficha. Não era erro de digitação — era o grid que estava incompleto.</t>
-        </is>
-      </c>
-      <c r="D15" s="56" t="inlineStr">
-        <is>
-          <t>Equipe de TI no valor original de R$ 167.778,30. Jonathan lançado com entrada em abr/26 (9 meses), que é o que explica os R$ 90.000.</t>
-        </is>
-      </c>
-      <c r="E15" s="56" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F15" s="60" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B16" s="59" t="inlineStr">
-        <is>
-          <t>Origem do valor realizado</t>
-        </is>
-      </c>
-      <c r="C16" s="59" t="inlineStr">
-        <is>
-          <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto. Até aqui os números vieram informados pela gestora.</t>
-        </is>
-      </c>
-      <c r="D16" s="59" t="inlineStr">
-        <is>
-          <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
-        </is>
-      </c>
-      <c r="E16" s="59" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="57" t="inlineStr">
+        <is>
+          <t>Critério de competência x caixa</t>
+        </is>
+      </c>
+      <c r="C21" s="57" t="inlineStr">
+        <is>
+          <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
+        </is>
+      </c>
+      <c r="D21" s="57" t="inlineStr">
+        <is>
+          <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
+        </is>
+      </c>
+      <c r="E21" s="57" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F16" s="61" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B17" s="56" t="inlineStr">
-        <is>
-          <t>Jusfy x Astrea</t>
-        </is>
-      </c>
-      <c r="C17" s="56" t="inlineStr">
-        <is>
-          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
-        </is>
-      </c>
-      <c r="D17" s="56" t="inlineStr">
-        <is>
-          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado dos meses seguintes.</t>
-        </is>
-      </c>
-      <c r="E17" s="56" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F17" s="60" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B18" s="59" t="inlineStr">
-        <is>
-          <t>Rateio dos softwares corporativos de TI</t>
-        </is>
-      </c>
-      <c r="C18" s="59" t="inlineStr">
-        <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
-        </is>
-      </c>
-      <c r="D18" s="59" t="inlineStr">
-        <is>
-          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
-        </is>
-      </c>
-      <c r="E18" s="59" t="inlineStr">
-        <is>
-          <t>Cristiane + Controladoria</t>
-        </is>
-      </c>
-      <c r="F18" s="61" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B19" s="56" t="inlineStr">
-        <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
-        </is>
-      </c>
-      <c r="C19" s="56" t="inlineStr">
-        <is>
-          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
-        </is>
-      </c>
-      <c r="D19" s="56" t="inlineStr">
-        <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
-        </is>
-      </c>
-      <c r="E19" s="56" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F19" s="61" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B20" s="59" t="inlineStr">
-        <is>
-          <t>Office 365 — nº de licenças</t>
-        </is>
-      </c>
-      <c r="C20" s="59" t="inlineStr">
-        <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
-        </is>
-      </c>
-      <c r="D20" s="59" t="inlineStr">
-        <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
-        </is>
-      </c>
-      <c r="E20" s="59" t="inlineStr">
-        <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F20" s="61" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="55" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B21" s="56" t="inlineStr">
-        <is>
-          <t>Critério de competência x caixa</t>
-        </is>
-      </c>
-      <c r="C21" s="56" t="inlineStr">
-        <is>
-          <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
-        </is>
-      </c>
-      <c r="D21" s="56" t="inlineStr">
-        <is>
-          <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
-        </is>
-      </c>
-      <c r="E21" s="56" t="inlineStr">
-        <is>
-          <t>Cristiane + Financeiro</t>
-        </is>
-      </c>
-      <c r="F21" s="61" t="inlineStr">
+      <c r="F21" s="62" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -8091,67 +8131,67 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>ROTINA MENSAL</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="63" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="64" t="inlineStr">
+      <c r="B5" s="65" t="inlineStr">
         <is>
           <t>Abra a aba REALIZADO e preencha apenas as células amarelas do mês que fechou. Se o item não teve gasto no mês, digite 0 — deixar em branco significa 'ainda não lancei'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="63" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="64" t="inlineStr">
+      <c r="B6" s="65" t="inlineStr">
         <is>
           <t>Preencha a coluna 'Fonte do dado' (ex.: relatório do financeiro, nota fiscal, extrato do cartão) para o número ser auditável depois.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="63" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="63" t="inlineStr">
+      <c r="A8" s="64" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="64" t="inlineStr">
+      <c r="B8" s="65" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="64" t="inlineStr">
+      <c r="B9" s="65" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -8159,67 +8199,67 @@
     </row>
     <row r="10" ht="8" customHeight="1"/>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>COMO LER OS NÚMEROS</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="63" t="inlineStr">
+      <c r="A12" s="64" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="64" t="inlineStr">
+      <c r="B12" s="65" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="63" t="inlineStr">
+      <c r="A13" s="64" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="64" t="inlineStr">
+      <c r="B13" s="65" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="63" t="inlineStr">
+      <c r="A14" s="64" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="64" t="inlineStr">
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="63" t="inlineStr">
+      <c r="A15" s="64" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="64" t="inlineStr">
+      <c r="B15" s="65" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="63" t="inlineStr">
+      <c r="A16" s="64" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="64" t="inlineStr">
+      <c r="B16" s="65" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -8227,43 +8267,43 @@
     </row>
     <row r="17" ht="8" customHeight="1"/>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>REGRAS DA PLANILHA</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="63" t="inlineStr">
+      <c r="A19" s="64" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="64" t="inlineStr">
+      <c r="B19" s="65" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="63" t="inlineStr">
+      <c r="A20" s="64" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="64" t="inlineStr">
+      <c r="B20" s="65" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="63" t="inlineStr">
+      <c r="A21" s="64" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="64" t="inlineStr">
+      <c r="B21" s="65" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,13 +111,42 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E6B3A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E6B3A"/>
+      <sz val="9"/>
     </font>
     <font>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -166,12 +195,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="001E6B3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -211,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -254,7 +288,30 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="20" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -262,7 +319,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -283,6 +344,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -332,7 +394,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -344,16 +406,16 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1039,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1413,202 +1475,529 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
         <is>
+          <t>ECONOMIA GERADA — acumulado de janeiro até o mês de referência</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Economia bruta</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="22">
+        <f>-SUMIF(Comparativo!$Q$6:$Q$26,"&lt;0")</f>
+        <v/>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>Soma de tudo que ficou abaixo do orçado</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="n"/>
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="n"/>
+      <c r="I16" s="23" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>(−) Gastos acima do orçado</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="22">
+        <f>-SUMIF(Comparativo!$Q$6:$Q$26,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>Estouros que consomem parte da economia</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="23" t="n"/>
+      <c r="I17" s="23" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="24">
+        <f> ECONOMIA LÍQUIDA</f>
+        <v/>
+      </c>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="25">
+        <f>-SUM(Comparativo!$Q$6:$Q$26)</f>
+        <v/>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>O número defensável: só linhas comparáveis</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="26" t="n"/>
+      <c r="G18" s="26" t="n"/>
+      <c r="H18" s="26" t="n"/>
+      <c r="I18" s="26" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Projeção para o ano</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="n"/>
+      <c r="C19" s="22">
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$26)/Comparativo!$D$3*12,"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Extrapolação linear, se o padrão dos meses fechados se mantiver</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="23" t="n"/>
+      <c r="I19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>% sobre o orçado do período</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="27">
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$26)/SUM(Comparativo!$S$6:$S$26),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>Economia líquida ÷ planejado das linhas que entram na conta</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="23" t="n"/>
+      <c r="I20" s="23" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>Fora desta conta: linhas sem nenhum lançamento; Geovanna (base diferente). Só entra o que foi efetivamente lançado e é comparável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>DE ONDE VEIO A ECONOMIA (top 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Departamento</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Planejado acum.</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Realizado acum.</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Economia (R$)</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>% da linha</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="31">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A25),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="31">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A25),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="32">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A25),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="32">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A25),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="33">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A25),Comparativo!$R$6:$R$26,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IFERROR(F25/D25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="31">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A26),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="31">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A26),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="32">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A26),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="32">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A26),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="33">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A26),Comparativo!$R$6:$R$26,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IFERROR(F26/D26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="31">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A27),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="31">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A27),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="32">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A27),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="32">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A27),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="33">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A27),Comparativo!$R$6:$R$26,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IFERROR(F27/D27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="31">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A28),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="31">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A28),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="32">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A28),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="32">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A28),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="33">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A28),Comparativo!$R$6:$R$26,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IFERROR(F28/D28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="31">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A29),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="31">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A29),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="32">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A29),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="32">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A29),Comparativo!$R$6:$R$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="33">
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A29),Comparativo!$R$6:$R$26,0)),""),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IFERROR(F29/D29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="35" t="inlineStr">
+        <is>
           <t>MAIORES DESVIOS DO ACUMULADO (top 5 acima do orçado)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Realizado acum.</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>Desvio (R$)</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>Desvio (%)</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="H33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="22">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C17" s="22">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="23">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="23">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="23">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A17),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="24">
-        <f>IFERROR(F17/D17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
+      <c r="B34" s="31">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A34),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="31">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A34),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="32">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A34),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="32">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A34),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="32">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A34),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="34">
+        <f>IFERROR(F34/D34,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="22">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C18" s="22">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="23">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="23">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="23">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A18),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="24">
-        <f>IFERROR(F18/D18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="B35" s="31">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A35),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="31">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A35),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="32">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A35),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="32">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A35),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="32">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A35),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="34">
+        <f>IFERROR(F35/D35,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="22">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C19" s="22">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="23">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="23">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="23">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A19),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="24">
-        <f>IFERROR(F19/D19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="B36" s="31">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A36),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="31">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A36),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="32">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A36),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="32">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A36),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="32">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A36),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="34">
+        <f>IFERROR(F36/D36,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="22">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C20" s="22">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="23">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="23">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="23">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A20),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="24">
-        <f>IFERROR(F20/D20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="B37" s="31">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A37),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="31">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A37),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="32">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A37),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="32">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A37),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="32">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A37),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="34">
+        <f>IFERROR(F37/D37,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="22">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C21" s="22">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="23">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="23">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="23">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A21),Comparativo!$O$6:$O$26,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="24">
-        <f>IFERROR(F21/D21,"")</f>
+      <c r="B38" s="31">
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A38),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="31">
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A38),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="32">
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A38),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="32">
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A38),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="32">
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A38),Comparativo!$O$6:$O$26,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="34">
+        <f>IFERROR(F38/D38,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="17">
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D18:I18"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D16:I16"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1620,7 +2009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1639,6 +2028,9 @@
     <col width="17" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="10" customWidth="1" min="15" max="15"/>
     <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="13" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1661,17 +2053,17 @@
           <t>Mês de referência:</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="36" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="37" t="inlineStr">
         <is>
           <t>Mês nº:</t>
         </is>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="38">
         <f>MATCH($B$3,Planejado!$H$4:$S$4,0)</f>
         <v/>
       </c>
@@ -1747,1401 +2139,1665 @@
           <t>Situação</t>
         </is>
       </c>
-      <c r="O5" s="28" t="inlineStr">
+      <c r="O5" s="39" t="inlineStr">
         <is>
           <t>(aux ranking)</t>
         </is>
       </c>
-      <c r="P5" s="28" t="inlineStr">
+      <c r="P5" s="39" t="inlineStr">
         <is>
           <t>(aux meses lançados)</t>
         </is>
       </c>
+      <c r="Q5" s="39" t="inlineStr">
+        <is>
+          <t>(aux desvio comparável)</t>
+        </is>
+      </c>
+      <c r="R5" s="39" t="inlineStr">
+        <is>
+          <t>(aux ranking economia)</t>
+        </is>
+      </c>
+      <c r="S5" s="39" t="inlineStr">
+        <is>
+          <t>(aux planejado comparável)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="29">
+      <c r="A6" s="40">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="40">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="40">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="41">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="40">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="42">
         <f>INDEX(Planejado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="42">
         <f>INDEX(Realizado!$H5:$S5,$D$3)</f>
         <v/>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="42">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="42">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H5:$S5)</f>
         <v/>
       </c>
-      <c r="J6" s="31">
+      <c r="J6" s="42">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H5:$S5)</f>
         <v/>
       </c>
-      <c r="K6" s="31">
+      <c r="K6" s="42">
         <f>J6-I6</f>
         <v/>
       </c>
-      <c r="L6" s="32">
+      <c r="L6" s="43">
         <f>IFERROR(K6/I6,"")</f>
         <v/>
       </c>
-      <c r="M6" s="32">
+      <c r="M6" s="43">
         <f>IFERROR(J6/I6,"")</f>
         <v/>
       </c>
-      <c r="N6" s="33">
+      <c r="N6" s="44">
         <f>IF(P6=0,"Sem lançamento",IF(AND(I6=0,J6=0),"—",IF(I6=0,"Não orçado",IF(K6&gt;0.05*I6,"Acima do orçado",IF(K6&lt;-0.05*I6,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O6" s="28">
+      <c r="O6" s="39">
         <f>IF(K6&gt;1,K6+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P6" s="34">
+      <c r="P6" s="45">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H5:$S5&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q6" s="46">
+        <f>IF(P6=0,"",K6)</f>
+        <v/>
+      </c>
+      <c r="R6" s="46">
+        <f>IF(AND(Q6&lt;&gt;"",Q6&lt;-1),-Q6+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S6" s="46">
+        <f>IF(Q6="","",I6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="29">
+      <c r="A7" s="40">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="40">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="40">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="41">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="40">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="42">
         <f>INDEX(Planejado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="42">
         <f>INDEX(Realizado!$H6:$S6,$D$3)</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="42">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="42">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H6:$S6)</f>
         <v/>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="42">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H6:$S6)</f>
         <v/>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="42">
         <f>J7-I7</f>
         <v/>
       </c>
-      <c r="L7" s="32">
+      <c r="L7" s="43">
         <f>IFERROR(K7/I7,"")</f>
         <v/>
       </c>
-      <c r="M7" s="32">
+      <c r="M7" s="43">
         <f>IFERROR(J7/I7,"")</f>
         <v/>
       </c>
-      <c r="N7" s="33" t="inlineStr">
+      <c r="N7" s="44" t="inlineStr">
         <is>
           <t>⚠ Base diferente</t>
         </is>
       </c>
-      <c r="O7" s="28">
+      <c r="O7" s="39">
         <f>IF(K7&gt;1,K7+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P7" s="34">
+      <c r="P7" s="45">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H6:$S6&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q7" s="46" t="n"/>
+      <c r="R7" s="46">
+        <f>IF(AND(Q7&lt;&gt;"",Q7&lt;-1),-Q7+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S7" s="46">
+        <f>IF(Q7="","",I7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="29">
+      <c r="A8" s="40">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="40">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="40">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="41">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="40">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="42">
         <f>INDEX(Planejado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="42">
         <f>INDEX(Realizado!$H7:$S7,$D$3)</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="42">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="42">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H7:$S7)</f>
         <v/>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="42">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H7:$S7)</f>
         <v/>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="42">
         <f>J8-I8</f>
         <v/>
       </c>
-      <c r="L8" s="32">
+      <c r="L8" s="43">
         <f>IFERROR(K8/I8,"")</f>
         <v/>
       </c>
-      <c r="M8" s="32">
+      <c r="M8" s="43">
         <f>IFERROR(J8/I8,"")</f>
         <v/>
       </c>
-      <c r="N8" s="33">
+      <c r="N8" s="44">
         <f>IF(P8=0,"Sem lançamento",IF(AND(I8=0,J8=0),"—",IF(I8=0,"Não orçado",IF(K8&gt;0.05*I8,"Acima do orçado",IF(K8&lt;-0.05*I8,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="39">
         <f>IF(K8&gt;1,K8+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P8" s="34">
+      <c r="P8" s="45">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H7:$S7&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q8" s="46">
+        <f>IF(P8=0,"",K8)</f>
+        <v/>
+      </c>
+      <c r="R8" s="46">
+        <f>IF(AND(Q8&lt;&gt;"",Q8&lt;-1),-Q8+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S8" s="46">
+        <f>IF(Q8="","",I8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="29">
+      <c r="A9" s="40">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="40">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="40">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="41">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="40">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="42">
         <f>INDEX(Planejado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="42">
         <f>INDEX(Realizado!$H8:$S8,$D$3)</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="42">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="42">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H8:$S8)</f>
         <v/>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="42">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H8:$S8)</f>
         <v/>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="42">
         <f>J9-I9</f>
         <v/>
       </c>
-      <c r="L9" s="32">
+      <c r="L9" s="43">
         <f>IFERROR(K9/I9,"")</f>
         <v/>
       </c>
-      <c r="M9" s="32">
+      <c r="M9" s="43">
         <f>IFERROR(J9/I9,"")</f>
         <v/>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="44">
         <f>IF(P9=0,"Sem lançamento",IF(AND(I9=0,J9=0),"—",IF(I9=0,"Não orçado",IF(K9&gt;0.05*I9,"Acima do orçado",IF(K9&lt;-0.05*I9,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O9" s="28">
+      <c r="O9" s="39">
         <f>IF(K9&gt;1,K9+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P9" s="34">
+      <c r="P9" s="45">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H8:$S8&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q9" s="46">
+        <f>IF(P9=0,"",K9)</f>
+        <v/>
+      </c>
+      <c r="R9" s="46">
+        <f>IF(AND(Q9&lt;&gt;"",Q9&lt;-1),-Q9+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S9" s="46">
+        <f>IF(Q9="","",I9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="29">
+      <c r="A10" s="40">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="40">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="40">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="41">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="40">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="42">
         <f>INDEX(Planejado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="42">
         <f>INDEX(Realizado!$H9:$S9,$D$3)</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="42">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="42">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H9:$S9)</f>
         <v/>
       </c>
-      <c r="J10" s="31">
+      <c r="J10" s="42">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H9:$S9)</f>
         <v/>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="42">
         <f>J10-I10</f>
         <v/>
       </c>
-      <c r="L10" s="32">
+      <c r="L10" s="43">
         <f>IFERROR(K10/I10,"")</f>
         <v/>
       </c>
-      <c r="M10" s="32">
+      <c r="M10" s="43">
         <f>IFERROR(J10/I10,"")</f>
         <v/>
       </c>
-      <c r="N10" s="33">
+      <c r="N10" s="44">
         <f>IF(P10=0,"Sem lançamento",IF(AND(I10=0,J10=0),"—",IF(I10=0,"Não orçado",IF(K10&gt;0.05*I10,"Acima do orçado",IF(K10&lt;-0.05*I10,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O10" s="28">
+      <c r="O10" s="39">
         <f>IF(K10&gt;1,K10+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P10" s="34">
+      <c r="P10" s="45">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H9:$S9&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q10" s="46">
+        <f>IF(P10=0,"",K10)</f>
+        <v/>
+      </c>
+      <c r="R10" s="46">
+        <f>IF(AND(Q10&lt;&gt;"",Q10&lt;-1),-Q10+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S10" s="46">
+        <f>IF(Q10="","",I10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="29">
+      <c r="A11" s="40">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="40">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="40">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="41">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="40">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="42">
         <f>INDEX(Planejado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="42">
         <f>INDEX(Realizado!$H10:$S10,$D$3)</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="42">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="42">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H10:$S10)</f>
         <v/>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="42">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H10:$S10)</f>
         <v/>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="42">
         <f>J11-I11</f>
         <v/>
       </c>
-      <c r="L11" s="32">
+      <c r="L11" s="43">
         <f>IFERROR(K11/I11,"")</f>
         <v/>
       </c>
-      <c r="M11" s="32">
+      <c r="M11" s="43">
         <f>IFERROR(J11/I11,"")</f>
         <v/>
       </c>
-      <c r="N11" s="33">
+      <c r="N11" s="44">
         <f>IF(P11=0,"Sem lançamento",IF(AND(I11=0,J11=0),"—",IF(I11=0,"Não orçado",IF(K11&gt;0.05*I11,"Acima do orçado",IF(K11&lt;-0.05*I11,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O11" s="28">
+      <c r="O11" s="39">
         <f>IF(K11&gt;1,K11+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P11" s="34">
+      <c r="P11" s="45">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H10:$S10&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q11" s="46">
+        <f>IF(P11=0,"",K11)</f>
+        <v/>
+      </c>
+      <c r="R11" s="46">
+        <f>IF(AND(Q11&lt;&gt;"",Q11&lt;-1),-Q11+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S11" s="46">
+        <f>IF(Q11="","",I11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="29">
+      <c r="A12" s="40">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="40">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="40">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="41">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="40">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="42">
         <f>INDEX(Planejado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="42">
         <f>INDEX(Realizado!$H11:$S11,$D$3)</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="42">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="42">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H11:$S11)</f>
         <v/>
       </c>
-      <c r="J12" s="31">
+      <c r="J12" s="42">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H11:$S11)</f>
         <v/>
       </c>
-      <c r="K12" s="31">
+      <c r="K12" s="42">
         <f>J12-I12</f>
         <v/>
       </c>
-      <c r="L12" s="32">
+      <c r="L12" s="43">
         <f>IFERROR(K12/I12,"")</f>
         <v/>
       </c>
-      <c r="M12" s="32">
+      <c r="M12" s="43">
         <f>IFERROR(J12/I12,"")</f>
         <v/>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="44">
         <f>IF(P12=0,"Sem lançamento",IF(AND(I12=0,J12=0),"—",IF(I12=0,"Não orçado",IF(K12&gt;0.05*I12,"Acima do orçado",IF(K12&lt;-0.05*I12,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O12" s="28">
+      <c r="O12" s="39">
         <f>IF(K12&gt;1,K12+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P12" s="34">
+      <c r="P12" s="45">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H11:$S11&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q12" s="46">
+        <f>IF(P12=0,"",K12)</f>
+        <v/>
+      </c>
+      <c r="R12" s="46">
+        <f>IF(AND(Q12&lt;&gt;"",Q12&lt;-1),-Q12+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S12" s="46">
+        <f>IF(Q12="","",I12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="29">
+      <c r="A13" s="40">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="40">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="40">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="41">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="40">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="42">
         <f>INDEX(Planejado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="42">
         <f>INDEX(Realizado!$H12:$S12,$D$3)</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="42">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="42">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H12:$S12)</f>
         <v/>
       </c>
-      <c r="J13" s="31">
+      <c r="J13" s="42">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H12:$S12)</f>
         <v/>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="42">
         <f>J13-I13</f>
         <v/>
       </c>
-      <c r="L13" s="32">
+      <c r="L13" s="43">
         <f>IFERROR(K13/I13,"")</f>
         <v/>
       </c>
-      <c r="M13" s="32">
+      <c r="M13" s="43">
         <f>IFERROR(J13/I13,"")</f>
         <v/>
       </c>
-      <c r="N13" s="33">
+      <c r="N13" s="44">
         <f>IF(P13=0,"Sem lançamento",IF(AND(I13=0,J13=0),"—",IF(I13=0,"Não orçado",IF(K13&gt;0.05*I13,"Acima do orçado",IF(K13&lt;-0.05*I13,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O13" s="28">
+      <c r="O13" s="39">
         <f>IF(K13&gt;1,K13+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P13" s="34">
+      <c r="P13" s="45">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H12:$S12&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q13" s="46">
+        <f>IF(P13=0,"",K13)</f>
+        <v/>
+      </c>
+      <c r="R13" s="46">
+        <f>IF(AND(Q13&lt;&gt;"",Q13&lt;-1),-Q13+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S13" s="46">
+        <f>IF(Q13="","",I13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="29">
+      <c r="A14" s="40">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="40">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="40">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="41">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="40">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="42">
         <f>INDEX(Planejado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="42">
         <f>INDEX(Realizado!$H13:$S13,$D$3)</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="42">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="42">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H13:$S13)</f>
         <v/>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="42">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H13:$S13)</f>
         <v/>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="42">
         <f>J14-I14</f>
         <v/>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="43">
         <f>IFERROR(K14/I14,"")</f>
         <v/>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="43">
         <f>IFERROR(J14/I14,"")</f>
         <v/>
       </c>
-      <c r="N14" s="33">
+      <c r="N14" s="44">
         <f>IF(P14=0,"Sem lançamento",IF(AND(I14=0,J14=0),"—",IF(I14=0,"Não orçado",IF(K14&gt;0.05*I14,"Acima do orçado",IF(K14&lt;-0.05*I14,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O14" s="28">
+      <c r="O14" s="39">
         <f>IF(K14&gt;1,K14+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P14" s="34">
+      <c r="P14" s="45">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H13:$S13&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q14" s="46">
+        <f>IF(P14=0,"",K14)</f>
+        <v/>
+      </c>
+      <c r="R14" s="46">
+        <f>IF(AND(Q14&lt;&gt;"",Q14&lt;-1),-Q14+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S14" s="46">
+        <f>IF(Q14="","",I14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="35">
+      <c r="A15" s="47">
         <f>Planejado!A14</f>
         <v/>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="47">
         <f>Planejado!B14</f>
         <v/>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="47">
         <f>Planejado!C14</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="48">
         <f>Planejado!D14</f>
         <v/>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="47">
         <f>Planejado!G14</f>
         <v/>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="49">
         <f>INDEX(Planejado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="49">
         <f>INDEX(Realizado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="49">
         <f>G15-F15</f>
         <v/>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H14:$S14)</f>
         <v/>
       </c>
-      <c r="J15" s="37">
+      <c r="J15" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H14:$S14)</f>
         <v/>
       </c>
-      <c r="K15" s="37">
+      <c r="K15" s="49">
         <f>J15-I15</f>
         <v/>
       </c>
-      <c r="L15" s="38">
+      <c r="L15" s="50">
         <f>IFERROR(K15/I15,"")</f>
         <v/>
       </c>
-      <c r="M15" s="38">
+      <c r="M15" s="50">
         <f>IFERROR(J15/I15,"")</f>
         <v/>
       </c>
-      <c r="N15" s="39">
+      <c r="N15" s="51">
         <f>IF(P15=0,"Sem lançamento",IF(AND(I15=0,J15=0),"—",IF(I15=0,"Não orçado",IF(K15&gt;0.05*I15,"Acima do orçado",IF(K15&lt;-0.05*I15,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O15" s="28">
+      <c r="O15" s="39">
         <f>IF(K15&gt;1,K15+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P15" s="40">
+      <c r="P15" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H14:$S14&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q15" s="46">
+        <f>IF(P15=0,"",K15)</f>
+        <v/>
+      </c>
+      <c r="R15" s="46">
+        <f>IF(AND(Q15&lt;&gt;"",Q15&lt;-1),-Q15+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S15" s="46">
+        <f>IF(Q15="","",I15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="35">
+      <c r="A16" s="47">
         <f>Planejado!A15</f>
         <v/>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="47">
         <f>Planejado!B15</f>
         <v/>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="47">
         <f>Planejado!C15</f>
         <v/>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="48">
         <f>Planejado!D15</f>
         <v/>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="47">
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="49">
         <f>INDEX(Planejado!$H15:$S15,$D$3)</f>
         <v/>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="49">
         <f>INDEX(Realizado!$H15:$S15,$D$3)</f>
         <v/>
       </c>
-      <c r="H16" s="37">
+      <c r="H16" s="49">
         <f>G16-F16</f>
         <v/>
       </c>
-      <c r="I16" s="37">
+      <c r="I16" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H15:$S15)</f>
         <v/>
       </c>
-      <c r="J16" s="37">
+      <c r="J16" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H15:$S15)</f>
         <v/>
       </c>
-      <c r="K16" s="37">
+      <c r="K16" s="49">
         <f>J16-I16</f>
         <v/>
       </c>
-      <c r="L16" s="38">
+      <c r="L16" s="50">
         <f>IFERROR(K16/I16,"")</f>
         <v/>
       </c>
-      <c r="M16" s="38">
+      <c r="M16" s="50">
         <f>IFERROR(J16/I16,"")</f>
         <v/>
       </c>
-      <c r="N16" s="39">
+      <c r="N16" s="51">
         <f>IF(P16=0,"Sem lançamento",IF(AND(I16=0,J16=0),"—",IF(I16=0,"Não orçado",IF(K16&gt;0.05*I16,"Acima do orçado",IF(K16&lt;-0.05*I16,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O16" s="28">
+      <c r="O16" s="39">
         <f>IF(K16&gt;1,K16+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P16" s="40">
+      <c r="P16" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H15:$S15&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q16" s="46">
+        <f>IF(P16=0,"",K16)</f>
+        <v/>
+      </c>
+      <c r="R16" s="46">
+        <f>IF(AND(Q16&lt;&gt;"",Q16&lt;-1),-Q16+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S16" s="46">
+        <f>IF(Q16="","",I16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="35">
+      <c r="A17" s="47">
         <f>Planejado!A16</f>
         <v/>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="47">
         <f>Planejado!B16</f>
         <v/>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="47">
         <f>Planejado!C16</f>
         <v/>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="48">
         <f>Planejado!D16</f>
         <v/>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="47">
         <f>Planejado!G16</f>
         <v/>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="49">
         <f>INDEX(Planejado!$H16:$S16,$D$3)</f>
         <v/>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="49">
         <f>INDEX(Realizado!$H16:$S16,$D$3)</f>
         <v/>
       </c>
-      <c r="H17" s="37">
+      <c r="H17" s="49">
         <f>G17-F17</f>
         <v/>
       </c>
-      <c r="I17" s="37">
+      <c r="I17" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H16:$S16)</f>
         <v/>
       </c>
-      <c r="J17" s="37">
+      <c r="J17" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H16:$S16)</f>
         <v/>
       </c>
-      <c r="K17" s="37">
+      <c r="K17" s="49">
         <f>J17-I17</f>
         <v/>
       </c>
-      <c r="L17" s="38">
+      <c r="L17" s="50">
         <f>IFERROR(K17/I17,"")</f>
         <v/>
       </c>
-      <c r="M17" s="38">
+      <c r="M17" s="50">
         <f>IFERROR(J17/I17,"")</f>
         <v/>
       </c>
-      <c r="N17" s="39">
+      <c r="N17" s="51">
         <f>IF(P17=0,"Sem lançamento",IF(AND(I17=0,J17=0),"—",IF(I17=0,"Não orçado",IF(K17&gt;0.05*I17,"Acima do orçado",IF(K17&lt;-0.05*I17,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O17" s="28">
+      <c r="O17" s="39">
         <f>IF(K17&gt;1,K17+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P17" s="40">
+      <c r="P17" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H16:$S16&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q17" s="46">
+        <f>IF(P17=0,"",K17)</f>
+        <v/>
+      </c>
+      <c r="R17" s="46">
+        <f>IF(AND(Q17&lt;&gt;"",Q17&lt;-1),-Q17+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S17" s="46">
+        <f>IF(Q17="","",I17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="35">
+      <c r="A18" s="47">
         <f>Planejado!A17</f>
         <v/>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="47">
         <f>Planejado!B17</f>
         <v/>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="47">
         <f>Planejado!C17</f>
         <v/>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="48">
         <f>Planejado!D17</f>
         <v/>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="47">
         <f>Planejado!G17</f>
         <v/>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="49">
         <f>INDEX(Planejado!$H17:$S17,$D$3)</f>
         <v/>
       </c>
-      <c r="G18" s="37">
+      <c r="G18" s="49">
         <f>INDEX(Realizado!$H17:$S17,$D$3)</f>
         <v/>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="49">
         <f>G18-F18</f>
         <v/>
       </c>
-      <c r="I18" s="37">
+      <c r="I18" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H17:$S17)</f>
         <v/>
       </c>
-      <c r="J18" s="37">
+      <c r="J18" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H17:$S17)</f>
         <v/>
       </c>
-      <c r="K18" s="37">
+      <c r="K18" s="49">
         <f>J18-I18</f>
         <v/>
       </c>
-      <c r="L18" s="38">
+      <c r="L18" s="50">
         <f>IFERROR(K18/I18,"")</f>
         <v/>
       </c>
-      <c r="M18" s="38">
+      <c r="M18" s="50">
         <f>IFERROR(J18/I18,"")</f>
         <v/>
       </c>
-      <c r="N18" s="39">
+      <c r="N18" s="51">
         <f>IF(P18=0,"Sem lançamento",IF(AND(I18=0,J18=0),"—",IF(I18=0,"Não orçado",IF(K18&gt;0.05*I18,"Acima do orçado",IF(K18&lt;-0.05*I18,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O18" s="28">
+      <c r="O18" s="39">
         <f>IF(K18&gt;1,K18+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P18" s="40">
+      <c r="P18" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H17:$S17&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q18" s="46">
+        <f>IF(P18=0,"",K18)</f>
+        <v/>
+      </c>
+      <c r="R18" s="46">
+        <f>IF(AND(Q18&lt;&gt;"",Q18&lt;-1),-Q18+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S18" s="46">
+        <f>IF(Q18="","",I18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="35">
+      <c r="A19" s="47">
         <f>Planejado!A18</f>
         <v/>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="47">
         <f>Planejado!B18</f>
         <v/>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="47">
         <f>Planejado!C18</f>
         <v/>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="48">
         <f>Planejado!D18</f>
         <v/>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="47">
         <f>Planejado!G18</f>
         <v/>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="49">
         <f>INDEX(Planejado!$H18:$S18,$D$3)</f>
         <v/>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="49">
         <f>INDEX(Realizado!$H18:$S18,$D$3)</f>
         <v/>
       </c>
-      <c r="H19" s="37">
+      <c r="H19" s="49">
         <f>G19-F19</f>
         <v/>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H18:$S18)</f>
         <v/>
       </c>
-      <c r="J19" s="37">
+      <c r="J19" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H18:$S18)</f>
         <v/>
       </c>
-      <c r="K19" s="37">
+      <c r="K19" s="49">
         <f>J19-I19</f>
         <v/>
       </c>
-      <c r="L19" s="38">
+      <c r="L19" s="50">
         <f>IFERROR(K19/I19,"")</f>
         <v/>
       </c>
-      <c r="M19" s="38">
+      <c r="M19" s="50">
         <f>IFERROR(J19/I19,"")</f>
         <v/>
       </c>
-      <c r="N19" s="39">
+      <c r="N19" s="51">
         <f>IF(P19=0,"Sem lançamento",IF(AND(I19=0,J19=0),"—",IF(I19=0,"Não orçado",IF(K19&gt;0.05*I19,"Acima do orçado",IF(K19&lt;-0.05*I19,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O19" s="28">
+      <c r="O19" s="39">
         <f>IF(K19&gt;1,K19+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P19" s="40">
+      <c r="P19" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H18:$S18&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q19" s="46">
+        <f>IF(P19=0,"",K19)</f>
+        <v/>
+      </c>
+      <c r="R19" s="46">
+        <f>IF(AND(Q19&lt;&gt;"",Q19&lt;-1),-Q19+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S19" s="46">
+        <f>IF(Q19="","",I19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="35">
+      <c r="A20" s="47">
         <f>Planejado!A19</f>
         <v/>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="47">
         <f>Planejado!B19</f>
         <v/>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="47">
         <f>Planejado!C19</f>
         <v/>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="48">
         <f>Planejado!D19</f>
         <v/>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="47">
         <f>Planejado!G19</f>
         <v/>
       </c>
-      <c r="F20" s="37">
+      <c r="F20" s="49">
         <f>INDEX(Planejado!$H19:$S19,$D$3)</f>
         <v/>
       </c>
-      <c r="G20" s="37">
+      <c r="G20" s="49">
         <f>INDEX(Realizado!$H19:$S19,$D$3)</f>
         <v/>
       </c>
-      <c r="H20" s="37">
+      <c r="H20" s="49">
         <f>G20-F20</f>
         <v/>
       </c>
-      <c r="I20" s="37">
+      <c r="I20" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H19:$S19)</f>
         <v/>
       </c>
-      <c r="J20" s="37">
+      <c r="J20" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H19:$S19)</f>
         <v/>
       </c>
-      <c r="K20" s="37">
+      <c r="K20" s="49">
         <f>J20-I20</f>
         <v/>
       </c>
-      <c r="L20" s="38">
+      <c r="L20" s="50">
         <f>IFERROR(K20/I20,"")</f>
         <v/>
       </c>
-      <c r="M20" s="38">
+      <c r="M20" s="50">
         <f>IFERROR(J20/I20,"")</f>
         <v/>
       </c>
-      <c r="N20" s="39">
+      <c r="N20" s="51">
         <f>IF(P20=0,"Sem lançamento",IF(AND(I20=0,J20=0),"—",IF(I20=0,"Não orçado",IF(K20&gt;0.05*I20,"Acima do orçado",IF(K20&lt;-0.05*I20,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O20" s="28">
+      <c r="O20" s="39">
         <f>IF(K20&gt;1,K20+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P20" s="40">
+      <c r="P20" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H19:$S19&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q20" s="46">
+        <f>IF(P20=0,"",K20)</f>
+        <v/>
+      </c>
+      <c r="R20" s="46">
+        <f>IF(AND(Q20&lt;&gt;"",Q20&lt;-1),-Q20+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S20" s="46">
+        <f>IF(Q20="","",I20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="35">
+      <c r="A21" s="47">
         <f>Planejado!A20</f>
         <v/>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="47">
         <f>Planejado!B20</f>
         <v/>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="47">
         <f>Planejado!C20</f>
         <v/>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="48">
         <f>Planejado!D20</f>
         <v/>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="47">
         <f>Planejado!G20</f>
         <v/>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="49">
         <f>INDEX(Planejado!$H20:$S20,$D$3)</f>
         <v/>
       </c>
-      <c r="G21" s="37">
+      <c r="G21" s="49">
         <f>INDEX(Realizado!$H20:$S20,$D$3)</f>
         <v/>
       </c>
-      <c r="H21" s="37">
+      <c r="H21" s="49">
         <f>G21-F21</f>
         <v/>
       </c>
-      <c r="I21" s="37">
+      <c r="I21" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H20:$S20)</f>
         <v/>
       </c>
-      <c r="J21" s="37">
+      <c r="J21" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H20:$S20)</f>
         <v/>
       </c>
-      <c r="K21" s="37">
+      <c r="K21" s="49">
         <f>J21-I21</f>
         <v/>
       </c>
-      <c r="L21" s="38">
+      <c r="L21" s="50">
         <f>IFERROR(K21/I21,"")</f>
         <v/>
       </c>
-      <c r="M21" s="38">
+      <c r="M21" s="50">
         <f>IFERROR(J21/I21,"")</f>
         <v/>
       </c>
-      <c r="N21" s="39">
+      <c r="N21" s="51">
         <f>IF(P21=0,"Sem lançamento",IF(AND(I21=0,J21=0),"—",IF(I21=0,"Não orçado",IF(K21&gt;0.05*I21,"Acima do orçado",IF(K21&lt;-0.05*I21,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O21" s="28">
+      <c r="O21" s="39">
         <f>IF(K21&gt;1,K21+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P21" s="40">
+      <c r="P21" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H20:$S20&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q21" s="46">
+        <f>IF(P21=0,"",K21)</f>
+        <v/>
+      </c>
+      <c r="R21" s="46">
+        <f>IF(AND(Q21&lt;&gt;"",Q21&lt;-1),-Q21+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S21" s="46">
+        <f>IF(Q21="","",I21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="35">
+      <c r="A22" s="47">
         <f>Planejado!A21</f>
         <v/>
       </c>
-      <c r="B22" s="35">
+      <c r="B22" s="47">
         <f>Planejado!B21</f>
         <v/>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="47">
         <f>Planejado!C21</f>
         <v/>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="48">
         <f>Planejado!D21</f>
         <v/>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="47">
         <f>Planejado!G21</f>
         <v/>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="49">
         <f>INDEX(Planejado!$H21:$S21,$D$3)</f>
         <v/>
       </c>
-      <c r="G22" s="37">
+      <c r="G22" s="49">
         <f>INDEX(Realizado!$H21:$S21,$D$3)</f>
         <v/>
       </c>
-      <c r="H22" s="37">
+      <c r="H22" s="49">
         <f>G22-F22</f>
         <v/>
       </c>
-      <c r="I22" s="37">
+      <c r="I22" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H21:$S21)</f>
         <v/>
       </c>
-      <c r="J22" s="37">
+      <c r="J22" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H21:$S21)</f>
         <v/>
       </c>
-      <c r="K22" s="37">
+      <c r="K22" s="49">
         <f>J22-I22</f>
         <v/>
       </c>
-      <c r="L22" s="38">
+      <c r="L22" s="50">
         <f>IFERROR(K22/I22,"")</f>
         <v/>
       </c>
-      <c r="M22" s="38">
+      <c r="M22" s="50">
         <f>IFERROR(J22/I22,"")</f>
         <v/>
       </c>
-      <c r="N22" s="39">
+      <c r="N22" s="51">
         <f>IF(P22=0,"Sem lançamento",IF(AND(I22=0,J22=0),"—",IF(I22=0,"Não orçado",IF(K22&gt;0.05*I22,"Acima do orçado",IF(K22&lt;-0.05*I22,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O22" s="28">
+      <c r="O22" s="39">
         <f>IF(K22&gt;1,K22+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P22" s="40">
+      <c r="P22" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H21:$S21&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q22" s="46">
+        <f>IF(P22=0,"",K22)</f>
+        <v/>
+      </c>
+      <c r="R22" s="46">
+        <f>IF(AND(Q22&lt;&gt;"",Q22&lt;-1),-Q22+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S22" s="46">
+        <f>IF(Q22="","",I22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="35">
+      <c r="A23" s="47">
         <f>Planejado!A22</f>
         <v/>
       </c>
-      <c r="B23" s="35">
+      <c r="B23" s="47">
         <f>Planejado!B22</f>
         <v/>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="47">
         <f>Planejado!C22</f>
         <v/>
       </c>
-      <c r="D23" s="36">
+      <c r="D23" s="48">
         <f>Planejado!D22</f>
         <v/>
       </c>
-      <c r="E23" s="35">
+      <c r="E23" s="47">
         <f>Planejado!G22</f>
         <v/>
       </c>
-      <c r="F23" s="37">
+      <c r="F23" s="49">
         <f>INDEX(Planejado!$H22:$S22,$D$3)</f>
         <v/>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="49">
         <f>INDEX(Realizado!$H22:$S22,$D$3)</f>
         <v/>
       </c>
-      <c r="H23" s="37">
+      <c r="H23" s="49">
         <f>G23-F23</f>
         <v/>
       </c>
-      <c r="I23" s="37">
+      <c r="I23" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H22:$S22)</f>
         <v/>
       </c>
-      <c r="J23" s="37">
+      <c r="J23" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H22:$S22)</f>
         <v/>
       </c>
-      <c r="K23" s="37">
+      <c r="K23" s="49">
         <f>J23-I23</f>
         <v/>
       </c>
-      <c r="L23" s="38">
+      <c r="L23" s="50">
         <f>IFERROR(K23/I23,"")</f>
         <v/>
       </c>
-      <c r="M23" s="38">
+      <c r="M23" s="50">
         <f>IFERROR(J23/I23,"")</f>
         <v/>
       </c>
-      <c r="N23" s="39">
+      <c r="N23" s="51">
         <f>IF(P23=0,"Sem lançamento",IF(AND(I23=0,J23=0),"—",IF(I23=0,"Não orçado",IF(K23&gt;0.05*I23,"Acima do orçado",IF(K23&lt;-0.05*I23,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O23" s="28">
+      <c r="O23" s="39">
         <f>IF(K23&gt;1,K23+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P23" s="40">
+      <c r="P23" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H22:$S22&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q23" s="46">
+        <f>IF(P23=0,"",K23)</f>
+        <v/>
+      </c>
+      <c r="R23" s="46">
+        <f>IF(AND(Q23&lt;&gt;"",Q23&lt;-1),-Q23+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S23" s="46">
+        <f>IF(Q23="","",I23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="35">
+      <c r="A24" s="47">
         <f>Planejado!A23</f>
         <v/>
       </c>
-      <c r="B24" s="35">
+      <c r="B24" s="47">
         <f>Planejado!B23</f>
         <v/>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="47">
         <f>Planejado!C23</f>
         <v/>
       </c>
-      <c r="D24" s="36">
+      <c r="D24" s="48">
         <f>Planejado!D23</f>
         <v/>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="47">
         <f>Planejado!G23</f>
         <v/>
       </c>
-      <c r="F24" s="37">
+      <c r="F24" s="49">
         <f>INDEX(Planejado!$H23:$S23,$D$3)</f>
         <v/>
       </c>
-      <c r="G24" s="37">
+      <c r="G24" s="49">
         <f>INDEX(Realizado!$H23:$S23,$D$3)</f>
         <v/>
       </c>
-      <c r="H24" s="37">
+      <c r="H24" s="49">
         <f>G24-F24</f>
         <v/>
       </c>
-      <c r="I24" s="37">
+      <c r="I24" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H23:$S23)</f>
         <v/>
       </c>
-      <c r="J24" s="37">
+      <c r="J24" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H23:$S23)</f>
         <v/>
       </c>
-      <c r="K24" s="37">
+      <c r="K24" s="49">
         <f>J24-I24</f>
         <v/>
       </c>
-      <c r="L24" s="38">
+      <c r="L24" s="50">
         <f>IFERROR(K24/I24,"")</f>
         <v/>
       </c>
-      <c r="M24" s="38">
+      <c r="M24" s="50">
         <f>IFERROR(J24/I24,"")</f>
         <v/>
       </c>
-      <c r="N24" s="39">
+      <c r="N24" s="51">
         <f>IF(P24=0,"Sem lançamento",IF(AND(I24=0,J24=0),"—",IF(I24=0,"Não orçado",IF(K24&gt;0.05*I24,"Acima do orçado",IF(K24&lt;-0.05*I24,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O24" s="28">
+      <c r="O24" s="39">
         <f>IF(K24&gt;1,K24+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P24" s="40">
+      <c r="P24" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H23:$S23&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q24" s="46">
+        <f>IF(P24=0,"",K24)</f>
+        <v/>
+      </c>
+      <c r="R24" s="46">
+        <f>IF(AND(Q24&lt;&gt;"",Q24&lt;-1),-Q24+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S24" s="46">
+        <f>IF(Q24="","",I24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="35">
+      <c r="A25" s="47">
         <f>Planejado!A24</f>
         <v/>
       </c>
-      <c r="B25" s="35">
+      <c r="B25" s="47">
         <f>Planejado!B24</f>
         <v/>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="47">
         <f>Planejado!C24</f>
         <v/>
       </c>
-      <c r="D25" s="36">
+      <c r="D25" s="48">
         <f>Planejado!D24</f>
         <v/>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="47">
         <f>Planejado!G24</f>
         <v/>
       </c>
-      <c r="F25" s="37">
+      <c r="F25" s="49">
         <f>INDEX(Planejado!$H24:$S24,$D$3)</f>
         <v/>
       </c>
-      <c r="G25" s="37">
+      <c r="G25" s="49">
         <f>INDEX(Realizado!$H24:$S24,$D$3)</f>
         <v/>
       </c>
-      <c r="H25" s="37">
+      <c r="H25" s="49">
         <f>G25-F25</f>
         <v/>
       </c>
-      <c r="I25" s="37">
+      <c r="I25" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H24:$S24)</f>
         <v/>
       </c>
-      <c r="J25" s="37">
+      <c r="J25" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H24:$S24)</f>
         <v/>
       </c>
-      <c r="K25" s="37">
+      <c r="K25" s="49">
         <f>J25-I25</f>
         <v/>
       </c>
-      <c r="L25" s="38">
+      <c r="L25" s="50">
         <f>IFERROR(K25/I25,"")</f>
         <v/>
       </c>
-      <c r="M25" s="38">
+      <c r="M25" s="50">
         <f>IFERROR(J25/I25,"")</f>
         <v/>
       </c>
-      <c r="N25" s="39">
+      <c r="N25" s="51">
         <f>IF(P25=0,"Sem lançamento",IF(AND(I25=0,J25=0),"—",IF(I25=0,"Não orçado",IF(K25&gt;0.05*I25,"Acima do orçado",IF(K25&lt;-0.05*I25,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O25" s="28">
+      <c r="O25" s="39">
         <f>IF(K25&gt;1,K25+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P25" s="40">
+      <c r="P25" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H24:$S24&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="Q25" s="46">
+        <f>IF(P25=0,"",K25)</f>
+        <v/>
+      </c>
+      <c r="R25" s="46">
+        <f>IF(AND(Q25&lt;&gt;"",Q25&lt;-1),-Q25+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S25" s="46">
+        <f>IF(Q25="","",I25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="35">
+      <c r="A26" s="47">
         <f>Planejado!A25</f>
         <v/>
       </c>
-      <c r="B26" s="35">
+      <c r="B26" s="47">
         <f>Planejado!B25</f>
         <v/>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="47">
         <f>Planejado!C25</f>
         <v/>
       </c>
-      <c r="D26" s="36">
+      <c r="D26" s="48">
         <f>Planejado!D25</f>
         <v/>
       </c>
-      <c r="E26" s="35">
+      <c r="E26" s="47">
         <f>Planejado!G25</f>
         <v/>
       </c>
-      <c r="F26" s="37">
+      <c r="F26" s="49">
         <f>INDEX(Planejado!$H25:$S25,$D$3)</f>
         <v/>
       </c>
-      <c r="G26" s="37">
+      <c r="G26" s="49">
         <f>INDEX(Realizado!$H25:$S25,$D$3)</f>
         <v/>
       </c>
-      <c r="H26" s="37">
+      <c r="H26" s="49">
         <f>G26-F26</f>
         <v/>
       </c>
-      <c r="I26" s="37">
+      <c r="I26" s="49">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H25:$S25)</f>
         <v/>
       </c>
-      <c r="J26" s="37">
+      <c r="J26" s="49">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H25:$S25)</f>
         <v/>
       </c>
-      <c r="K26" s="37">
+      <c r="K26" s="49">
         <f>J26-I26</f>
         <v/>
       </c>
-      <c r="L26" s="38">
+      <c r="L26" s="50">
         <f>IFERROR(K26/I26,"")</f>
         <v/>
       </c>
-      <c r="M26" s="38">
+      <c r="M26" s="50">
         <f>IFERROR(J26/I26,"")</f>
         <v/>
       </c>
-      <c r="N26" s="39">
+      <c r="N26" s="51">
         <f>IF(P26=0,"Sem lançamento",IF(AND(I26=0,J26=0),"—",IF(I26=0,"Não orçado",IF(K26&gt;0.05*I26,"Acima do orçado",IF(K26&lt;-0.05*I26,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
-      <c r="O26" s="28">
+      <c r="O26" s="39">
         <f>IF(K26&gt;1,K26+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P26" s="40">
+      <c r="P26" s="52">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H25:$S25&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q26" s="46">
+        <f>IF(P26=0,"",K26)</f>
+        <v/>
+      </c>
+      <c r="R26" s="46">
+        <f>IF(AND(Q26&lt;&gt;"",Q26&lt;-1),-Q26+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S26" s="46">
+        <f>IF(Q26="","",I26)</f>
         <v/>
       </c>
     </row>
@@ -3179,11 +3835,11 @@
         <f>SUM(K6:K26)</f>
         <v/>
       </c>
-      <c r="L27" s="41">
+      <c r="L27" s="53">
         <f>IFERROR(K27/I27,"")</f>
         <v/>
       </c>
-      <c r="M27" s="41">
+      <c r="M27" s="53">
         <f>IFERROR(J27/I27,"")</f>
         <v/>
       </c>
@@ -3368,1538 +4024,1538 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>JUR-E01</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>Miguel Clepf</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="E5" s="41" t="inlineStr">
         <is>
           <t>Advogado Júnior</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="40" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="40" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H5" s="31" t="n">
+      <c r="H5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="I5" s="31" t="n">
+      <c r="I5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="K5" s="31" t="n">
+      <c r="K5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="L5" s="31" t="n">
+      <c r="L5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="M5" s="31" t="n">
+      <c r="M5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="N5" s="31" t="n">
+      <c r="N5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="O5" s="31" t="n">
+      <c r="O5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="P5" s="31" t="n">
+      <c r="P5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="Q5" s="31" t="n">
+      <c r="Q5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="R5" s="31" t="n">
+      <c r="R5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="S5" s="31" t="n">
+      <c r="S5" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="T5" s="42">
+      <c r="T5" s="54">
         <f>SUM(H5:S5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>JUR-E02</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>Geovanna</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="41" t="inlineStr">
         <is>
           <t>Analista Administrativo — orçada pelo custo total (encargos de folha + benefícios). Salário bruto informado: R$ 2.886,91/mês</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr">
+      <c r="F6" s="40" t="inlineStr">
         <is>
           <t>CLT</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="40" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="H6" s="31" t="n">
+      <c r="H6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="I6" s="31" t="n">
+      <c r="I6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="J6" s="31" t="n">
+      <c r="J6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="K6" s="31" t="n">
+      <c r="K6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="L6" s="31" t="n">
+      <c r="L6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="M6" s="31" t="n">
+      <c r="M6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="N6" s="31" t="n">
+      <c r="N6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="O6" s="31" t="n">
+      <c r="O6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="P6" s="31" t="n">
+      <c r="P6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="Q6" s="31" t="n">
+      <c r="Q6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="R6" s="31" t="n">
+      <c r="R6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="S6" s="31" t="n">
+      <c r="S6" s="42" t="n">
         <v>4825.515</v>
       </c>
-      <c r="T6" s="42">
+      <c r="T6" s="54">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>JUR-E03</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D7" s="30" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>Thamar Victória</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="41" t="inlineStr">
         <is>
           <t>Advogada — recebia R$ 4.500/mês em jan–mar e passou a R$ 5.500 em abr/26 (aumento de R$ 1.000), contra R$ 5.000 orçados. Planejado revisado para R$ 5.500 a partir de ago/26</t>
         </is>
       </c>
-      <c r="F7" s="29" t="inlineStr">
+      <c r="F7" s="40" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="40" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H7" s="31" t="n">
+      <c r="H7" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="I7" s="31" t="n">
+      <c r="I7" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="J7" s="31" t="n">
+      <c r="J7" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="K7" s="31" t="n">
+      <c r="K7" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="L7" s="31" t="n">
+      <c r="L7" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="M7" s="31" t="n">
+      <c r="M7" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="N7" s="31" t="n">
+      <c r="N7" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="O7" s="31" t="n">
+      <c r="O7" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="P7" s="31" t="n">
+      <c r="P7" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="Q7" s="31" t="n">
+      <c r="Q7" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="R7" s="31" t="n">
+      <c r="R7" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="S7" s="31" t="n">
+      <c r="S7" s="42" t="n">
         <v>5500</v>
       </c>
-      <c r="T7" s="42">
+      <c r="T7" s="54">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>JUR-D01</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>JUSFY</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>Fase de teste com objetivo de eliminar o Astrea</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr"/>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="F8" s="40" t="inlineStr"/>
+      <c r="G8" s="40" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H8" s="31" t="n">
+      <c r="H8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="I8" s="31" t="n">
+      <c r="I8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="K8" s="31" t="n">
+      <c r="K8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="L8" s="31" t="n">
+      <c r="L8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="M8" s="31" t="n">
+      <c r="M8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="N8" s="31" t="n">
+      <c r="N8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="O8" s="31" t="n">
+      <c r="O8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="P8" s="31" t="n">
+      <c r="P8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="Q8" s="31" t="n">
+      <c r="Q8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="R8" s="31" t="n">
+      <c r="R8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="S8" s="31" t="n">
+      <c r="S8" s="42" t="n">
         <v>100</v>
       </c>
-      <c r="T8" s="42">
+      <c r="T8" s="54">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>JUR-D02</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr">
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>JUSBRASIL</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr"/>
-      <c r="F9" s="29" t="inlineStr"/>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="E9" s="41" t="inlineStr"/>
+      <c r="F9" s="40" t="inlineStr"/>
+      <c r="G9" s="40" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H9" s="31" t="n">
+      <c r="H9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="I9" s="31" t="n">
+      <c r="I9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="J9" s="31" t="n">
+      <c r="J9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="K9" s="31" t="n">
+      <c r="K9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="L9" s="31" t="n">
+      <c r="L9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="M9" s="31" t="n">
+      <c r="M9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="N9" s="31" t="n">
+      <c r="N9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="O9" s="31" t="n">
+      <c r="O9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="P9" s="31" t="n">
+      <c r="P9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="Q9" s="31" t="n">
+      <c r="Q9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="R9" s="31" t="n">
+      <c r="R9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="S9" s="31" t="n">
+      <c r="S9" s="42" t="n">
         <v>104.9</v>
       </c>
-      <c r="T9" s="42">
+      <c r="T9" s="54">
         <f>SUM(H9:S9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>JUR-D03</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="40" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D10" s="30" t="inlineStr">
+      <c r="D10" s="41" t="inlineStr">
         <is>
           <t>ASTREA</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="41" t="inlineStr">
         <is>
           <t>Cancelado — realizado zerado desde mai/26</t>
         </is>
       </c>
-      <c r="F10" s="29" t="inlineStr"/>
-      <c r="G10" s="29" t="inlineStr">
+      <c r="F10" s="40" t="inlineStr"/>
+      <c r="G10" s="40" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H10" s="31" t="n">
+      <c r="H10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="I10" s="31" t="n">
+      <c r="I10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="J10" s="31" t="n">
+      <c r="J10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="K10" s="31" t="n">
+      <c r="K10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="L10" s="31" t="n">
+      <c r="L10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="M10" s="31" t="n">
+      <c r="M10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="N10" s="31" t="n">
+      <c r="N10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="O10" s="31" t="n">
+      <c r="O10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="P10" s="31" t="n">
+      <c r="P10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="Q10" s="31" t="n">
+      <c r="Q10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="R10" s="31" t="n">
+      <c r="R10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="S10" s="31" t="n">
+      <c r="S10" s="42" t="n">
         <v>112.07</v>
       </c>
-      <c r="T10" s="42">
+      <c r="T10" s="54">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>JUR-D04</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="40" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="D11" s="41" t="inlineStr">
         <is>
           <t>LEME</t>
         </is>
       </c>
-      <c r="E11" s="30" t="inlineStr"/>
-      <c r="F11" s="29" t="inlineStr"/>
-      <c r="G11" s="29" t="inlineStr">
+      <c r="E11" s="41" t="inlineStr"/>
+      <c r="F11" s="40" t="inlineStr"/>
+      <c r="G11" s="40" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H11" s="31" t="n">
+      <c r="H11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="I11" s="31" t="n">
+      <c r="I11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="J11" s="31" t="n">
+      <c r="J11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="K11" s="31" t="n">
+      <c r="K11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="L11" s="31" t="n">
+      <c r="L11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="M11" s="31" t="n">
+      <c r="M11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="N11" s="31" t="n">
+      <c r="N11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="O11" s="31" t="n">
+      <c r="O11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="P11" s="31" t="n">
+      <c r="P11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="Q11" s="31" t="n">
+      <c r="Q11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="R11" s="31" t="n">
+      <c r="R11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="S11" s="31" t="n">
+      <c r="S11" s="42" t="n">
         <v>1030</v>
       </c>
-      <c r="T11" s="42">
+      <c r="T11" s="54">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>JUR-D05</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="40" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D12" s="30" t="inlineStr">
+      <c r="D12" s="41" t="inlineStr">
         <is>
           <t>Cursos / Eventos / Network</t>
         </is>
       </c>
-      <c r="E12" s="30" t="inlineStr"/>
-      <c r="F12" s="29" t="inlineStr"/>
-      <c r="G12" s="29" t="inlineStr">
+      <c r="E12" s="41" t="inlineStr"/>
+      <c r="F12" s="40" t="inlineStr"/>
+      <c r="G12" s="40" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="H12" s="31" t="n">
+      <c r="H12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="I12" s="31" t="n">
+      <c r="I12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="J12" s="31" t="n">
+      <c r="J12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="K12" s="31" t="n">
+      <c r="K12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="L12" s="31" t="n">
+      <c r="L12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="M12" s="31" t="n">
+      <c r="M12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="N12" s="31" t="n">
+      <c r="N12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="O12" s="31" t="n">
+      <c r="O12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="P12" s="31" t="n">
+      <c r="P12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="Q12" s="31" t="n">
+      <c r="Q12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="R12" s="31" t="n">
+      <c r="R12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="S12" s="31" t="n">
+      <c r="S12" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="T12" s="42">
+      <c r="T12" s="54">
         <f>SUM(H12:S12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>JUR-D06</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
+      <c r="D13" s="41" t="inlineStr">
         <is>
           <t>Bonificações trimestrais/semestrais do time</t>
         </is>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="41" t="inlineStr">
         <is>
           <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
         </is>
       </c>
-      <c r="F13" s="29" t="inlineStr"/>
-      <c r="G13" s="29" t="inlineStr">
+      <c r="F13" s="40" t="inlineStr"/>
+      <c r="G13" s="40" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="H13" s="31" t="n">
+      <c r="H13" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="31" t="n">
+      <c r="I13" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="31" t="n">
+      <c r="J13" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="31" t="n">
+      <c r="K13" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="31" t="n">
+      <c r="L13" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="31" t="n">
+      <c r="M13" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="31" t="n">
+      <c r="N13" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="31" t="n">
+      <c r="O13" s="42" t="n">
         <v>10293.6</v>
       </c>
-      <c r="P13" s="31" t="n">
+      <c r="P13" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="31" t="n">
+      <c r="Q13" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="31" t="n">
+      <c r="R13" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="31" t="n">
+      <c r="S13" s="42" t="n">
         <v>12867</v>
       </c>
-      <c r="T13" s="42">
+      <c r="T13" s="54">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>TI-E01</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="47" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="48" t="inlineStr">
         <is>
           <t>Vinicius Di Franco</t>
         </is>
       </c>
-      <c r="E14" s="36" t="inlineStr">
+      <c r="E14" s="48" t="inlineStr">
         <is>
           <t>Analista Administrativo — orçado pelo custo total (encargos de folha + benefícios). Salário bruto: R$ 2.570,52/mês até jul/26 e R$ 3.070,52 a partir de 05/08/26, aumento absorvido pela folga do envelope</t>
         </is>
       </c>
-      <c r="F14" s="35" t="inlineStr">
+      <c r="F14" s="47" t="inlineStr">
         <is>
           <t>CLT</t>
         </is>
       </c>
-      <c r="G14" s="35" t="inlineStr">
+      <c r="G14" s="47" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="H14" s="37" t="n">
+      <c r="H14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="I14" s="37" t="n">
+      <c r="I14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="J14" s="37" t="n">
+      <c r="J14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="K14" s="37" t="n">
+      <c r="K14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="L14" s="37" t="n">
+      <c r="L14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="M14" s="37" t="n">
+      <c r="M14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="N14" s="37" t="n">
+      <c r="N14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="O14" s="37" t="n">
+      <c r="O14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="P14" s="37" t="n">
+      <c r="P14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="Q14" s="37" t="n">
+      <c r="Q14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="R14" s="37" t="n">
+      <c r="R14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="S14" s="37" t="n">
+      <c r="S14" s="49" t="n">
         <v>5416.525</v>
       </c>
-      <c r="T14" s="42">
+      <c r="T14" s="54">
         <f>SUM(H14:S14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>TI-E02</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>Elias Benedito</t>
         </is>
       </c>
-      <c r="E15" s="36" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>Suporte Técnico Terceirizado</t>
         </is>
       </c>
-      <c r="F15" s="35" t="inlineStr">
+      <c r="F15" s="47" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G15" s="35" t="inlineStr">
+      <c r="G15" s="47" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H15" s="37" t="n">
+      <c r="H15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="I15" s="37" t="n">
+      <c r="I15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="J15" s="37" t="n">
+      <c r="J15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="K15" s="37" t="n">
+      <c r="K15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="L15" s="37" t="n">
+      <c r="L15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="M15" s="37" t="n">
+      <c r="M15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="N15" s="37" t="n">
+      <c r="N15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="O15" s="37" t="n">
+      <c r="O15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="P15" s="37" t="n">
+      <c r="P15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="Q15" s="37" t="n">
+      <c r="Q15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="R15" s="37" t="n">
+      <c r="R15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="S15" s="37" t="n">
+      <c r="S15" s="49" t="n">
         <v>1065</v>
       </c>
-      <c r="T15" s="42">
+      <c r="T15" s="54">
         <f>SUM(H15:S15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>TI-E03</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>Jonathan</t>
         </is>
       </c>
-      <c r="E16" s="36" t="inlineStr">
+      <c r="E16" s="48" t="inlineStr">
         <is>
           <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
         </is>
       </c>
-      <c r="F16" s="35" t="inlineStr">
+      <c r="F16" s="47" t="inlineStr">
         <is>
           <t>PJ</t>
         </is>
       </c>
-      <c r="G16" s="35" t="inlineStr">
+      <c r="G16" s="47" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="H16" s="37" t="n">
+      <c r="H16" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="37" t="n">
+      <c r="I16" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="37" t="n">
+      <c r="J16" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="37" t="n">
+      <c r="K16" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="L16" s="37" t="n">
+      <c r="L16" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="M16" s="37" t="n">
+      <c r="M16" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="N16" s="37" t="n">
+      <c r="N16" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="O16" s="37" t="n">
+      <c r="O16" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="P16" s="37" t="n">
+      <c r="P16" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="Q16" s="37" t="n">
+      <c r="Q16" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="R16" s="37" t="n">
+      <c r="R16" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="S16" s="37" t="n">
+      <c r="S16" s="49" t="n">
         <v>10000</v>
       </c>
-      <c r="T16" s="42">
+      <c r="T16" s="54">
         <f>SUM(H16:S16)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="47" t="inlineStr">
         <is>
           <t>TI-D01</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D17" s="36" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>Peças de Manutenção</t>
         </is>
       </c>
-      <c r="E17" s="36" t="inlineStr">
+      <c r="E17" s="48" t="inlineStr">
         <is>
           <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
         </is>
       </c>
-      <c r="F17" s="35" t="inlineStr"/>
-      <c r="G17" s="35" t="inlineStr">
+      <c r="F17" s="47" t="inlineStr"/>
+      <c r="G17" s="47" t="inlineStr">
         <is>
           <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
-      <c r="H17" s="37" t="n">
+      <c r="H17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="I17" s="37" t="n">
+      <c r="I17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="J17" s="37" t="n">
+      <c r="J17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="K17" s="37" t="n">
+      <c r="K17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="L17" s="37" t="n">
+      <c r="L17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="M17" s="37" t="n">
+      <c r="M17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="N17" s="37" t="n">
+      <c r="N17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="O17" s="37" t="n">
+      <c r="O17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="P17" s="37" t="n">
+      <c r="P17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="Q17" s="37" t="n">
+      <c r="Q17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="R17" s="37" t="n">
+      <c r="R17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="S17" s="37" t="n">
+      <c r="S17" s="49" t="n">
         <v>810</v>
       </c>
-      <c r="T17" s="42">
+      <c r="T17" s="54">
         <f>SUM(H17:S17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="47" t="inlineStr">
         <is>
           <t>TI-D02</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C18" s="47" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D18" s="36" t="inlineStr">
+      <c r="D18" s="48" t="inlineStr">
         <is>
           <t>Backup em Nuvem</t>
         </is>
       </c>
-      <c r="E18" s="36" t="inlineStr">
+      <c r="E18" s="48" t="inlineStr">
         <is>
           <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F18" s="35" t="inlineStr"/>
-      <c r="G18" s="35" t="inlineStr">
+      <c r="F18" s="47" t="inlineStr"/>
+      <c r="G18" s="47" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H18" s="37" t="n">
+      <c r="H18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="I18" s="37" t="n">
+      <c r="I18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="J18" s="37" t="n">
+      <c r="J18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="K18" s="37" t="n">
+      <c r="K18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="L18" s="37" t="n">
+      <c r="L18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="M18" s="37" t="n">
+      <c r="M18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="N18" s="37" t="n">
+      <c r="N18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="O18" s="37" t="n">
+      <c r="O18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="P18" s="37" t="n">
+      <c r="P18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="Q18" s="37" t="n">
+      <c r="Q18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="R18" s="37" t="n">
+      <c r="R18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="S18" s="37" t="n">
+      <c r="S18" s="49" t="n">
         <v>825</v>
       </c>
-      <c r="T18" s="42">
+      <c r="T18" s="54">
         <f>SUM(H18:S18)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>TI-D03</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="47" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D19" s="36" t="inlineStr">
+      <c r="D19" s="48" t="inlineStr">
         <is>
           <t>Inteligência Artificial (Adapta)</t>
         </is>
       </c>
-      <c r="E19" s="36" t="inlineStr">
+      <c r="E19" s="48" t="inlineStr">
         <is>
           <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F19" s="35" t="inlineStr"/>
-      <c r="G19" s="35" t="inlineStr">
+      <c r="F19" s="47" t="inlineStr"/>
+      <c r="G19" s="47" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H19" s="37" t="n">
+      <c r="H19" s="49" t="n">
         <v>1300</v>
       </c>
-      <c r="I19" s="37" t="n">
+      <c r="I19" s="49" t="n">
         <v>1300</v>
       </c>
-      <c r="J19" s="37" t="n">
+      <c r="J19" s="49" t="n">
         <v>1300</v>
       </c>
-      <c r="K19" s="37" t="n">
+      <c r="K19" s="49" t="n">
         <v>1300</v>
       </c>
-      <c r="L19" s="37" t="n">
+      <c r="L19" s="49" t="n">
         <v>1300</v>
       </c>
-      <c r="M19" s="37" t="n">
+      <c r="M19" s="49" t="n">
         <v>1300</v>
       </c>
-      <c r="N19" s="37" t="n">
+      <c r="N19" s="49" t="n">
         <v>1600</v>
       </c>
-      <c r="O19" s="37" t="n">
+      <c r="O19" s="49" t="n">
         <v>1600</v>
       </c>
-      <c r="P19" s="37" t="n">
+      <c r="P19" s="49" t="n">
         <v>1600</v>
       </c>
-      <c r="Q19" s="37" t="n">
+      <c r="Q19" s="49" t="n">
         <v>1600</v>
       </c>
-      <c r="R19" s="37" t="n">
+      <c r="R19" s="49" t="n">
         <v>1600</v>
       </c>
-      <c r="S19" s="37" t="n">
+      <c r="S19" s="49" t="n">
         <v>1600</v>
       </c>
-      <c r="T19" s="42">
+      <c r="T19" s="54">
         <f>SUM(H19:S19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>TI-D04</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="47" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D20" s="36" t="inlineStr">
+      <c r="D20" s="48" t="inlineStr">
         <is>
           <t>Antivírus</t>
         </is>
       </c>
-      <c r="E20" s="36" t="inlineStr">
+      <c r="E20" s="48" t="inlineStr">
         <is>
           <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F20" s="35" t="inlineStr"/>
-      <c r="G20" s="35" t="inlineStr">
+      <c r="F20" s="47" t="inlineStr"/>
+      <c r="G20" s="47" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H20" s="37" t="n">
+      <c r="H20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="I20" s="37" t="n">
+      <c r="I20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="J20" s="37" t="n">
+      <c r="J20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="K20" s="37" t="n">
+      <c r="K20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="L20" s="37" t="n">
+      <c r="L20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="M20" s="37" t="n">
+      <c r="M20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="N20" s="37" t="n">
+      <c r="N20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="O20" s="37" t="n">
+      <c r="O20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="P20" s="37" t="n">
+      <c r="P20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="Q20" s="37" t="n">
+      <c r="Q20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="R20" s="37" t="n">
+      <c r="R20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="S20" s="37" t="n">
+      <c r="S20" s="49" t="n">
         <v>240</v>
       </c>
-      <c r="T20" s="42">
+      <c r="T20" s="54">
         <f>SUM(H20:S20)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="47" t="inlineStr">
         <is>
           <t>TI-D05</t>
         </is>
       </c>
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="47" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D21" s="36" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>Pacote Office 365</t>
         </is>
       </c>
-      <c r="E21" s="36" t="inlineStr">
+      <c r="E21" s="48" t="inlineStr">
         <is>
           <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
         </is>
       </c>
-      <c r="F21" s="35" t="inlineStr"/>
-      <c r="G21" s="35" t="inlineStr">
+      <c r="F21" s="47" t="inlineStr"/>
+      <c r="G21" s="47" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H21" s="37" t="n">
+      <c r="H21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="I21" s="37" t="n">
+      <c r="I21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="J21" s="37" t="n">
+      <c r="J21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="K21" s="37" t="n">
+      <c r="K21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="L21" s="37" t="n">
+      <c r="L21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="M21" s="37" t="n">
+      <c r="M21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="N21" s="37" t="n">
+      <c r="N21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="O21" s="37" t="n">
+      <c r="O21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="P21" s="37" t="n">
+      <c r="P21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="Q21" s="37" t="n">
+      <c r="Q21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="R21" s="37" t="n">
+      <c r="R21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="S21" s="37" t="n">
+      <c r="S21" s="49" t="n">
         <v>375</v>
       </c>
-      <c r="T21" s="42">
+      <c r="T21" s="54">
         <f>SUM(H21:S21)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="47" t="inlineStr">
         <is>
           <t>TI-D06</t>
         </is>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="47" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D22" s="36" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
         </is>
       </c>
-      <c r="E22" s="36" t="inlineStr">
+      <c r="E22" s="48" t="inlineStr">
         <is>
           <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
         </is>
       </c>
-      <c r="F22" s="35" t="inlineStr"/>
-      <c r="G22" s="35" t="inlineStr">
+      <c r="F22" s="47" t="inlineStr"/>
+      <c r="G22" s="47" t="inlineStr">
         <is>
           <t>Móveis e Utensílios</t>
         </is>
       </c>
-      <c r="H22" s="37" t="n">
+      <c r="H22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="I22" s="37" t="n">
+      <c r="I22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="J22" s="37" t="n">
+      <c r="J22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="K22" s="37" t="n">
+      <c r="K22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="L22" s="37" t="n">
+      <c r="L22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="M22" s="37" t="n">
+      <c r="M22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="N22" s="37" t="n">
+      <c r="N22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="O22" s="37" t="n">
+      <c r="O22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="P22" s="37" t="n">
+      <c r="P22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="Q22" s="37" t="n">
+      <c r="Q22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="R22" s="37" t="n">
+      <c r="R22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="S22" s="37" t="n">
+      <c r="S22" s="49" t="n">
         <v>2800</v>
       </c>
-      <c r="T22" s="42">
+      <c r="T22" s="54">
         <f>SUM(H22:S22)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="47" t="inlineStr">
         <is>
           <t>TI-D07</t>
         </is>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="47" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D23" s="36" t="inlineStr">
+      <c r="D23" s="48" t="inlineStr">
         <is>
           <t>Cursos e Treinamentos</t>
         </is>
       </c>
-      <c r="E23" s="36" t="inlineStr"/>
-      <c r="F23" s="35" t="inlineStr"/>
-      <c r="G23" s="35" t="inlineStr">
+      <c r="E23" s="48" t="inlineStr"/>
+      <c r="F23" s="47" t="inlineStr"/>
+      <c r="G23" s="47" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="H23" s="37" t="n">
+      <c r="H23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="I23" s="37" t="n">
+      <c r="I23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="J23" s="37" t="n">
+      <c r="J23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="K23" s="37" t="n">
+      <c r="K23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="L23" s="37" t="n">
+      <c r="L23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="M23" s="37" t="n">
+      <c r="M23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="N23" s="37" t="n">
+      <c r="N23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="O23" s="37" t="n">
+      <c r="O23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="P23" s="37" t="n">
+      <c r="P23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="Q23" s="37" t="n">
+      <c r="Q23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="R23" s="37" t="n">
+      <c r="R23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="S23" s="37" t="n">
+      <c r="S23" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="T23" s="42">
+      <c r="T23" s="54">
         <f>SUM(H23:S23)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="47" t="inlineStr">
         <is>
           <t>TI-D08</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="47" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="D24" s="48" t="inlineStr">
         <is>
           <t>Aplicativo de Gravação de Reunião</t>
         </is>
       </c>
-      <c r="E24" s="36" t="inlineStr"/>
-      <c r="F24" s="35" t="inlineStr"/>
-      <c r="G24" s="35" t="inlineStr">
+      <c r="E24" s="48" t="inlineStr"/>
+      <c r="F24" s="47" t="inlineStr"/>
+      <c r="G24" s="47" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="H24" s="37" t="n">
+      <c r="H24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="I24" s="37" t="n">
+      <c r="I24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="J24" s="37" t="n">
+      <c r="J24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="K24" s="37" t="n">
+      <c r="K24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="L24" s="37" t="n">
+      <c r="L24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="M24" s="37" t="n">
+      <c r="M24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="N24" s="37" t="n">
+      <c r="N24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="O24" s="37" t="n">
+      <c r="O24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="P24" s="37" t="n">
+      <c r="P24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="Q24" s="37" t="n">
+      <c r="Q24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="R24" s="37" t="n">
+      <c r="R24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="S24" s="37" t="n">
+      <c r="S24" s="49" t="n">
         <v>220</v>
       </c>
-      <c r="T24" s="42">
+      <c r="T24" s="54">
         <f>SUM(H24:S24)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="47" t="inlineStr">
         <is>
           <t>TI-D09</t>
         </is>
       </c>
-      <c r="B25" s="35" t="inlineStr">
+      <c r="B25" s="47" t="inlineStr">
         <is>
           <t>TI</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="47" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="D25" s="36" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>Bonificação do time</t>
         </is>
       </c>
-      <c r="E25" s="36" t="inlineStr">
+      <c r="E25" s="48" t="inlineStr">
         <is>
           <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
         </is>
       </c>
-      <c r="F25" s="35" t="inlineStr"/>
-      <c r="G25" s="35" t="inlineStr">
+      <c r="F25" s="47" t="inlineStr"/>
+      <c r="G25" s="47" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="H25" s="37" t="n">
+      <c r="H25" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="37" t="n">
+      <c r="I25" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="37" t="n">
+      <c r="J25" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="37" t="n">
+      <c r="K25" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="37" t="n">
+      <c r="L25" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="37" t="n">
+      <c r="M25" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="37" t="n">
+      <c r="N25" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="37" t="n">
+      <c r="O25" s="49" t="n">
         <v>2400</v>
       </c>
-      <c r="P25" s="37" t="n">
+      <c r="P25" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="37" t="n">
+      <c r="Q25" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="R25" s="37" t="n">
+      <c r="R25" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="37" t="n">
+      <c r="S25" s="49" t="n">
         <v>3600</v>
       </c>
-      <c r="T25" s="42">
+      <c r="T25" s="54">
         <f>SUM(H25:S25)</f>
         <v/>
       </c>
@@ -5027,1349 +5683,1349 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="C4" s="43" t="inlineStr">
+      <c r="C4" s="55" t="inlineStr">
         <is>
           <t>Bloco</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="55" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="55" t="inlineStr">
         <is>
           <t>Detalhe / Observação</t>
         </is>
       </c>
-      <c r="F4" s="43" t="inlineStr">
+      <c r="F4" s="55" t="inlineStr">
         <is>
           <t>Vínculo</t>
         </is>
       </c>
-      <c r="G4" s="43" t="inlineStr">
+      <c r="G4" s="55" t="inlineStr">
         <is>
           <t>Plano de Contas</t>
         </is>
       </c>
-      <c r="H4" s="43" t="inlineStr">
+      <c r="H4" s="55" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="I4" s="43" t="inlineStr">
+      <c r="I4" s="55" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
+      <c r="J4" s="55" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="K4" s="43" t="inlineStr">
+      <c r="K4" s="55" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="L4" s="43" t="inlineStr">
+      <c r="L4" s="55" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="M4" s="43" t="inlineStr">
+      <c r="M4" s="55" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="N4" s="43" t="inlineStr">
+      <c r="N4" s="55" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="O4" s="43" t="inlineStr">
+      <c r="O4" s="55" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="P4" s="43" t="inlineStr">
+      <c r="P4" s="55" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="Q4" s="43" t="inlineStr">
+      <c r="Q4" s="55" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="R4" s="43" t="inlineStr">
+      <c r="R4" s="55" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="S4" s="43" t="inlineStr">
+      <c r="S4" s="55" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="T4" s="43" t="inlineStr">
+      <c r="T4" s="55" t="inlineStr">
         <is>
           <t>TOTAL REALIZADO</t>
         </is>
       </c>
-      <c r="U4" s="43" t="inlineStr">
+      <c r="U4" s="55" t="inlineStr">
         <is>
           <t>Fonte do dado</t>
         </is>
       </c>
-      <c r="V4" s="43" t="inlineStr">
+      <c r="V4" s="55" t="inlineStr">
         <is>
           <t>Observações do mês</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="44">
+      <c r="A5" s="56">
         <f>Planejado!A5</f>
         <v/>
       </c>
-      <c r="B5" s="44">
+      <c r="B5" s="56">
         <f>Planejado!B5</f>
         <v/>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="56">
         <f>Planejado!C5</f>
         <v/>
       </c>
-      <c r="D5" s="45">
+      <c r="D5" s="57">
         <f>Planejado!D5</f>
         <v/>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="57">
         <f>Planejado!E5</f>
         <v/>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="56">
         <f>Planejado!F5</f>
         <v/>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="56">
         <f>Planejado!G5</f>
         <v/>
       </c>
-      <c r="H5" s="46" t="n">
+      <c r="H5" s="58" t="n">
         <v>8818</v>
       </c>
-      <c r="I5" s="46" t="n">
+      <c r="I5" s="58" t="n">
         <v>8818</v>
       </c>
-      <c r="J5" s="46" t="n">
+      <c r="J5" s="58" t="n">
         <v>8818</v>
       </c>
-      <c r="K5" s="46" t="n">
+      <c r="K5" s="58" t="n">
         <v>8818</v>
       </c>
-      <c r="L5" s="46" t="n">
+      <c r="L5" s="58" t="n">
         <v>8818</v>
       </c>
-      <c r="M5" s="46" t="n">
+      <c r="M5" s="58" t="n">
         <v>8818</v>
       </c>
-      <c r="N5" s="46" t="n">
+      <c r="N5" s="58" t="n">
         <v>8818</v>
       </c>
-      <c r="O5" s="46" t="n"/>
-      <c r="T5" s="42">
+      <c r="O5" s="58" t="n"/>
+      <c r="T5" s="54">
         <f>SUM(H5:S5)</f>
         <v/>
       </c>
-      <c r="U5" s="47" t="inlineStr">
+      <c r="U5" s="59" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V5" s="47" t="inlineStr">
+      <c r="V5" s="59" t="inlineStr">
         <is>
           <t>Valor cheio da nota — R$ 1.182/mês abaixo do contratado</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="44">
+      <c r="A6" s="56">
         <f>Planejado!A6</f>
         <v/>
       </c>
-      <c r="B6" s="44">
+      <c r="B6" s="56">
         <f>Planejado!B6</f>
         <v/>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="56">
         <f>Planejado!C6</f>
         <v/>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="57">
         <f>Planejado!D6</f>
         <v/>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="57">
         <f>Planejado!E6</f>
         <v/>
       </c>
-      <c r="F6" s="44">
+      <c r="F6" s="56">
         <f>Planejado!F6</f>
         <v/>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="56">
         <f>Planejado!G6</f>
         <v/>
       </c>
-      <c r="H6" s="46" t="n">
+      <c r="H6" s="58" t="n">
         <v>2886.91</v>
       </c>
-      <c r="I6" s="46" t="n">
+      <c r="I6" s="58" t="n">
         <v>2886.91</v>
       </c>
-      <c r="J6" s="46" t="n">
+      <c r="J6" s="58" t="n">
         <v>2886.91</v>
       </c>
-      <c r="K6" s="46" t="n">
+      <c r="K6" s="58" t="n">
         <v>2886.91</v>
       </c>
-      <c r="L6" s="46" t="n">
+      <c r="L6" s="58" t="n">
         <v>2886.91</v>
       </c>
-      <c r="M6" s="46" t="n">
+      <c r="M6" s="58" t="n">
         <v>2886.91</v>
       </c>
-      <c r="N6" s="46" t="n">
+      <c r="N6" s="58" t="n">
         <v>2886.91</v>
       </c>
-      <c r="O6" s="46" t="n"/>
-      <c r="T6" s="42">
+      <c r="O6" s="58" t="n"/>
+      <c r="T6" s="54">
         <f>SUM(H6:S6)</f>
         <v/>
       </c>
-      <c r="U6" s="47" t="inlineStr">
+      <c r="U6" s="59" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V6" s="47" t="inlineStr">
+      <c r="V6" s="59" t="inlineStr">
         <is>
           <t>SALÁRIO BRUTO, sem alteração no ano. O orçado é custo total, então o desvio desta linha NÃO é economia: faltam encargos e benefícios (~R$ 1.938,61/mês)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="44">
+      <c r="A7" s="56">
         <f>Planejado!A7</f>
         <v/>
       </c>
-      <c r="B7" s="44">
+      <c r="B7" s="56">
         <f>Planejado!B7</f>
         <v/>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="56">
         <f>Planejado!C7</f>
         <v/>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="57">
         <f>Planejado!D7</f>
         <v/>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="57">
         <f>Planejado!E7</f>
         <v/>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="56">
         <f>Planejado!F7</f>
         <v/>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="56">
         <f>Planejado!G7</f>
         <v/>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="58" t="n">
         <v>4500</v>
       </c>
-      <c r="I7" s="46" t="n">
+      <c r="I7" s="58" t="n">
         <v>4500</v>
       </c>
-      <c r="J7" s="46" t="n">
+      <c r="J7" s="58" t="n">
         <v>4500</v>
       </c>
-      <c r="K7" s="46" t="n">
+      <c r="K7" s="58" t="n">
         <v>5500</v>
       </c>
-      <c r="L7" s="46" t="n">
+      <c r="L7" s="58" t="n">
         <v>5500</v>
       </c>
-      <c r="M7" s="46" t="n">
+      <c r="M7" s="58" t="n">
         <v>5500</v>
       </c>
-      <c r="N7" s="46" t="n">
+      <c r="N7" s="58" t="n">
         <v>5500</v>
       </c>
-      <c r="O7" s="46" t="n"/>
-      <c r="T7" s="42">
+      <c r="O7" s="58" t="n"/>
+      <c r="T7" s="54">
         <f>SUM(H7:S7)</f>
         <v/>
       </c>
-      <c r="U7" s="47" t="inlineStr">
+      <c r="U7" s="59" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V7" s="47" t="inlineStr">
+      <c r="V7" s="59" t="inlineStr">
         <is>
           <t>R$ 4.500/mês em jan–mar; aumento de R$ 1.000 a partir de abr/26</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="44">
+      <c r="A8" s="56">
         <f>Planejado!A8</f>
         <v/>
       </c>
-      <c r="B8" s="44">
+      <c r="B8" s="56">
         <f>Planejado!B8</f>
         <v/>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="56">
         <f>Planejado!C8</f>
         <v/>
       </c>
-      <c r="D8" s="45">
+      <c r="D8" s="57">
         <f>Planejado!D8</f>
         <v/>
       </c>
-      <c r="E8" s="45">
+      <c r="E8" s="57">
         <f>Planejado!E8</f>
         <v/>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="56">
         <f>Planejado!F8</f>
         <v/>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="56">
         <f>Planejado!G8</f>
         <v/>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="46" t="n">
+      <c r="I8" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="46" t="n">
+      <c r="J8" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="46" t="n">
+      <c r="K8" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="46" t="n">
+      <c r="L8" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="46" t="n">
+      <c r="M8" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="46" t="n">
+      <c r="N8" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="46" t="n"/>
-      <c r="T8" s="42">
+      <c r="O8" s="58" t="n"/>
+      <c r="T8" s="54">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
-      <c r="U8" s="47" t="inlineStr">
+      <c r="U8" s="59" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V8" s="47" t="inlineStr">
+      <c r="V8" s="59" t="inlineStr">
         <is>
           <t>Ainda não iniciado — sem cobrança</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="44">
+      <c r="A9" s="56">
         <f>Planejado!A9</f>
         <v/>
       </c>
-      <c r="B9" s="44">
+      <c r="B9" s="56">
         <f>Planejado!B9</f>
         <v/>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="56">
         <f>Planejado!C9</f>
         <v/>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="57">
         <f>Planejado!D9</f>
         <v/>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="57">
         <f>Planejado!E9</f>
         <v/>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="56">
         <f>Planejado!F9</f>
         <v/>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="56">
         <f>Planejado!G9</f>
         <v/>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="58" t="n">
         <v>136</v>
       </c>
-      <c r="I9" s="46" t="n">
+      <c r="I9" s="58" t="n">
         <v>136</v>
       </c>
-      <c r="J9" s="46" t="n">
+      <c r="J9" s="58" t="n">
         <v>136</v>
       </c>
-      <c r="K9" s="46" t="n">
+      <c r="K9" s="58" t="n">
         <v>136</v>
       </c>
-      <c r="L9" s="46" t="n">
+      <c r="L9" s="58" t="n">
         <v>136</v>
       </c>
-      <c r="M9" s="46" t="n">
+      <c r="M9" s="58" t="n">
         <v>136</v>
       </c>
-      <c r="N9" s="46" t="n">
+      <c r="N9" s="58" t="n">
         <v>136</v>
       </c>
-      <c r="O9" s="46" t="n"/>
-      <c r="T9" s="42">
+      <c r="O9" s="58" t="n"/>
+      <c r="T9" s="54">
         <f>SUM(H9:S9)</f>
         <v/>
       </c>
-      <c r="U9" s="47" t="inlineStr">
+      <c r="U9" s="59" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V9" s="47" t="inlineStr">
+      <c r="V9" s="59" t="inlineStr">
         <is>
           <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="44">
+      <c r="A10" s="56">
         <f>Planejado!A10</f>
         <v/>
       </c>
-      <c r="B10" s="44">
+      <c r="B10" s="56">
         <f>Planejado!B10</f>
         <v/>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="56">
         <f>Planejado!C10</f>
         <v/>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="57">
         <f>Planejado!D10</f>
         <v/>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="57">
         <f>Planejado!E10</f>
         <v/>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="56">
         <f>Planejado!F10</f>
         <v/>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="56">
         <f>Planejado!G10</f>
         <v/>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="H10" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="46" t="n">
+      <c r="I10" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="46" t="n">
+      <c r="J10" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="46" t="n">
+      <c r="K10" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="46" t="n">
+      <c r="L10" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="46" t="n">
+      <c r="M10" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N10" s="46" t="n">
+      <c r="N10" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="46" t="n"/>
-      <c r="T10" s="42">
+      <c r="O10" s="58" t="n"/>
+      <c r="T10" s="54">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
-      <c r="U10" s="47" t="inlineStr">
+      <c r="U10" s="59" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V10" s="47" t="inlineStr">
+      <c r="V10" s="59" t="inlineStr">
         <is>
           <t>Cancelado — sem cobrança</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="44">
+      <c r="A11" s="56">
         <f>Planejado!A11</f>
         <v/>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="56">
         <f>Planejado!B11</f>
         <v/>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="56">
         <f>Planejado!C11</f>
         <v/>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="57">
         <f>Planejado!D11</f>
         <v/>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="57">
         <f>Planejado!E11</f>
         <v/>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="56">
         <f>Planejado!F11</f>
         <v/>
       </c>
-      <c r="G11" s="44">
+      <c r="G11" s="56">
         <f>Planejado!G11</f>
         <v/>
       </c>
-      <c r="H11" s="46" t="n">
+      <c r="H11" s="58" t="n">
         <v>970</v>
       </c>
-      <c r="I11" s="46" t="n">
+      <c r="I11" s="58" t="n">
         <v>970</v>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="J11" s="58" t="n">
         <v>970</v>
       </c>
-      <c r="K11" s="46" t="n">
+      <c r="K11" s="58" t="n">
         <v>970</v>
       </c>
-      <c r="L11" s="46" t="n">
+      <c r="L11" s="58" t="n">
         <v>970</v>
       </c>
-      <c r="M11" s="46" t="n">
+      <c r="M11" s="58" t="n">
         <v>970</v>
       </c>
-      <c r="N11" s="46" t="n">
+      <c r="N11" s="58" t="n">
         <v>970</v>
       </c>
-      <c r="O11" s="46" t="n"/>
-      <c r="T11" s="42">
+      <c r="O11" s="58" t="n"/>
+      <c r="T11" s="54">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
-      <c r="U11" s="47" t="inlineStr">
+      <c r="U11" s="59" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V11" s="47" t="n"/>
+      <c r="V11" s="59" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="44">
+      <c r="A12" s="56">
         <f>Planejado!A12</f>
         <v/>
       </c>
-      <c r="B12" s="44">
+      <c r="B12" s="56">
         <f>Planejado!B12</f>
         <v/>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="56">
         <f>Planejado!C12</f>
         <v/>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="57">
         <f>Planejado!D12</f>
         <v/>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="57">
         <f>Planejado!E12</f>
         <v/>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="56">
         <f>Planejado!F12</f>
         <v/>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="56">
         <f>Planejado!G12</f>
         <v/>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="H12" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="46" t="n">
+      <c r="I12" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="46" t="n">
+      <c r="K12" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="46" t="n">
+      <c r="L12" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="46" t="n">
+      <c r="M12" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N12" s="46" t="n">
+      <c r="N12" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="46" t="n"/>
-      <c r="T12" s="42">
+      <c r="O12" s="58" t="n"/>
+      <c r="T12" s="54">
         <f>SUM(H12:S12)</f>
         <v/>
       </c>
-      <c r="U12" s="47" t="inlineStr">
+      <c r="U12" s="59" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V12" s="47" t="inlineStr">
+      <c r="V12" s="59" t="inlineStr">
         <is>
           <t>Sem gasto no período</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="44">
+      <c r="A13" s="56">
         <f>Planejado!A13</f>
         <v/>
       </c>
-      <c r="B13" s="44">
+      <c r="B13" s="56">
         <f>Planejado!B13</f>
         <v/>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="56">
         <f>Planejado!C13</f>
         <v/>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="57">
         <f>Planejado!D13</f>
         <v/>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="57">
         <f>Planejado!E13</f>
         <v/>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="56">
         <f>Planejado!F13</f>
         <v/>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="56">
         <f>Planejado!G13</f>
         <v/>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="H13" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="46" t="n">
+      <c r="I13" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="46" t="n">
+      <c r="K13" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="46" t="n">
+      <c r="L13" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="46" t="n">
+      <c r="M13" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="46" t="n">
+      <c r="N13" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="46" t="n"/>
-      <c r="T13" s="42">
+      <c r="O13" s="58" t="n"/>
+      <c r="T13" s="54">
         <f>SUM(H13:S13)</f>
         <v/>
       </c>
-      <c r="U13" s="47" t="inlineStr">
+      <c r="U13" s="59" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V13" s="47" t="inlineStr">
+      <c r="V13" s="59" t="inlineStr">
         <is>
           <t>Sem parcela no 1º semestre; bonificação de ago/26 a confirmar</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="44">
+      <c r="A14" s="56">
         <f>Planejado!A14</f>
         <v/>
       </c>
-      <c r="B14" s="44">
+      <c r="B14" s="56">
         <f>Planejado!B14</f>
         <v/>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="56">
         <f>Planejado!C14</f>
         <v/>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="57">
         <f>Planejado!D14</f>
         <v/>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="57">
         <f>Planejado!E14</f>
         <v/>
       </c>
-      <c r="F14" s="44">
+      <c r="F14" s="56">
         <f>Planejado!F14</f>
         <v/>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="56">
         <f>Planejado!G14</f>
         <v/>
       </c>
-      <c r="H14" s="46" t="n"/>
-      <c r="I14" s="46" t="n"/>
-      <c r="J14" s="46" t="n"/>
-      <c r="K14" s="46" t="n"/>
-      <c r="L14" s="46" t="n"/>
-      <c r="M14" s="46" t="n"/>
-      <c r="N14" s="46" t="n"/>
-      <c r="O14" s="46" t="n"/>
-      <c r="T14" s="42">
+      <c r="H14" s="58" t="n"/>
+      <c r="I14" s="58" t="n"/>
+      <c r="J14" s="58" t="n"/>
+      <c r="K14" s="58" t="n"/>
+      <c r="L14" s="58" t="n"/>
+      <c r="M14" s="58" t="n"/>
+      <c r="N14" s="58" t="n"/>
+      <c r="O14" s="58" t="n"/>
+      <c r="T14" s="54">
         <f>SUM(H14:S14)</f>
         <v/>
       </c>
-      <c r="U14" s="47" t="n"/>
-      <c r="V14" s="47" t="inlineStr">
+      <c r="U14" s="59" t="n"/>
+      <c r="V14" s="59" t="inlineStr">
         <is>
           <t>PREENCHER com o CUSTO TOTAL. Bruto: R$ 2.570,52/mês até jul e R$ 3.070,52 de ago — faltam encargos e benefícios</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="44">
+      <c r="A15" s="56">
         <f>Planejado!A15</f>
         <v/>
       </c>
-      <c r="B15" s="44">
+      <c r="B15" s="56">
         <f>Planejado!B15</f>
         <v/>
       </c>
-      <c r="C15" s="44">
+      <c r="C15" s="56">
         <f>Planejado!C15</f>
         <v/>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="57">
         <f>Planejado!D15</f>
         <v/>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="57">
         <f>Planejado!E15</f>
         <v/>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="56">
         <f>Planejado!F15</f>
         <v/>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="56">
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="H15" s="46" t="n">
+      <c r="H15" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="46" t="n">
+      <c r="I15" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="46" t="n">
+      <c r="J15" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="46" t="n">
+      <c r="K15" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="46" t="n">
+      <c r="L15" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="46" t="n">
+      <c r="M15" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="46" t="n">
+      <c r="N15" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="46" t="n"/>
-      <c r="T15" s="42">
+      <c r="O15" s="58" t="n"/>
+      <c r="T15" s="54">
         <f>SUM(H15:S15)</f>
         <v/>
       </c>
-      <c r="U15" s="47" t="inlineStr">
+      <c r="U15" s="59" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V15" s="47" t="inlineStr">
+      <c r="V15" s="59" t="inlineStr">
         <is>
           <t>Sem acionamento no período — confirmar se o contrato segue ativo</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="44">
+      <c r="A16" s="56">
         <f>Planejado!A16</f>
         <v/>
       </c>
-      <c r="B16" s="44">
+      <c r="B16" s="56">
         <f>Planejado!B16</f>
         <v/>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="56">
         <f>Planejado!C16</f>
         <v/>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="57">
         <f>Planejado!D16</f>
         <v/>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="57">
         <f>Planejado!E16</f>
         <v/>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="56">
         <f>Planejado!F16</f>
         <v/>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="56">
         <f>Planejado!G16</f>
         <v/>
       </c>
-      <c r="H16" s="46" t="n">
+      <c r="H16" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="46" t="n">
+      <c r="I16" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="46" t="n">
+      <c r="J16" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="46" t="n">
+      <c r="K16" s="58" t="n">
         <v>6300</v>
       </c>
-      <c r="L16" s="46" t="n">
+      <c r="L16" s="58" t="n">
         <v>6300</v>
       </c>
-      <c r="M16" s="46" t="n">
+      <c r="M16" s="58" t="n">
         <v>6300</v>
       </c>
-      <c r="N16" s="46" t="n">
+      <c r="N16" s="58" t="n">
         <v>6300</v>
       </c>
-      <c r="O16" s="46" t="n"/>
-      <c r="T16" s="42">
+      <c r="O16" s="58" t="n"/>
+      <c r="T16" s="54">
         <f>SUM(H16:S16)</f>
         <v/>
       </c>
-      <c r="U16" s="47" t="inlineStr">
+      <c r="U16" s="59" t="inlineStr">
         <is>
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V16" s="47" t="inlineStr">
+      <c r="V16" s="59" t="inlineStr">
         <is>
           <t>Entrada em abr/26. R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="44">
+      <c r="A17" s="56">
         <f>Planejado!A17</f>
         <v/>
       </c>
-      <c r="B17" s="44">
+      <c r="B17" s="56">
         <f>Planejado!B17</f>
         <v/>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="56">
         <f>Planejado!C17</f>
         <v/>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="57">
         <f>Planejado!D17</f>
         <v/>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="57">
         <f>Planejado!E17</f>
         <v/>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="56">
         <f>Planejado!F17</f>
         <v/>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="56">
         <f>Planejado!G17</f>
         <v/>
       </c>
-      <c r="H17" s="46" t="n"/>
-      <c r="I17" s="46" t="n"/>
-      <c r="J17" s="46" t="n"/>
-      <c r="K17" s="46" t="n"/>
-      <c r="L17" s="46" t="n"/>
-      <c r="M17" s="46" t="n"/>
-      <c r="N17" s="46" t="n"/>
-      <c r="O17" s="46" t="n"/>
-      <c r="T17" s="42">
+      <c r="H17" s="58" t="n"/>
+      <c r="I17" s="58" t="n"/>
+      <c r="J17" s="58" t="n"/>
+      <c r="K17" s="58" t="n"/>
+      <c r="L17" s="58" t="n"/>
+      <c r="M17" s="58" t="n"/>
+      <c r="N17" s="58" t="n"/>
+      <c r="O17" s="58" t="n"/>
+      <c r="T17" s="54">
         <f>SUM(H17:S17)</f>
         <v/>
       </c>
-      <c r="U17" s="47" t="n"/>
-      <c r="V17" s="47" t="n"/>
+      <c r="U17" s="59" t="n"/>
+      <c r="V17" s="59" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="44">
+      <c r="A18" s="56">
         <f>Planejado!A18</f>
         <v/>
       </c>
-      <c r="B18" s="44">
+      <c r="B18" s="56">
         <f>Planejado!B18</f>
         <v/>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="56">
         <f>Planejado!C18</f>
         <v/>
       </c>
-      <c r="D18" s="45">
+      <c r="D18" s="57">
         <f>Planejado!D18</f>
         <v/>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="57">
         <f>Planejado!E18</f>
         <v/>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="56">
         <f>Planejado!F18</f>
         <v/>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="56">
         <f>Planejado!G18</f>
         <v/>
       </c>
-      <c r="H18" s="46" t="n"/>
-      <c r="I18" s="46" t="n"/>
-      <c r="J18" s="46" t="n"/>
-      <c r="K18" s="46" t="n"/>
-      <c r="L18" s="46" t="n"/>
-      <c r="M18" s="46" t="n"/>
-      <c r="N18" s="46" t="n"/>
-      <c r="O18" s="46" t="n"/>
-      <c r="T18" s="42">
+      <c r="H18" s="58" t="n"/>
+      <c r="I18" s="58" t="n"/>
+      <c r="J18" s="58" t="n"/>
+      <c r="K18" s="58" t="n"/>
+      <c r="L18" s="58" t="n"/>
+      <c r="M18" s="58" t="n"/>
+      <c r="N18" s="58" t="n"/>
+      <c r="O18" s="58" t="n"/>
+      <c r="T18" s="54">
         <f>SUM(H18:S18)</f>
         <v/>
       </c>
-      <c r="U18" s="47" t="n"/>
-      <c r="V18" s="47" t="n"/>
+      <c r="U18" s="59" t="n"/>
+      <c r="V18" s="59" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="44">
+      <c r="A19" s="56">
         <f>Planejado!A19</f>
         <v/>
       </c>
-      <c r="B19" s="44">
+      <c r="B19" s="56">
         <f>Planejado!B19</f>
         <v/>
       </c>
-      <c r="C19" s="44">
+      <c r="C19" s="56">
         <f>Planejado!C19</f>
         <v/>
       </c>
-      <c r="D19" s="45">
+      <c r="D19" s="57">
         <f>Planejado!D19</f>
         <v/>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="57">
         <f>Planejado!E19</f>
         <v/>
       </c>
-      <c r="F19" s="44">
+      <c r="F19" s="56">
         <f>Planejado!F19</f>
         <v/>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="56">
         <f>Planejado!G19</f>
         <v/>
       </c>
-      <c r="H19" s="46" t="n"/>
-      <c r="I19" s="46" t="n"/>
-      <c r="J19" s="46" t="n"/>
-      <c r="K19" s="46" t="n"/>
-      <c r="L19" s="46" t="n"/>
-      <c r="M19" s="46" t="n"/>
-      <c r="N19" s="46" t="n"/>
-      <c r="O19" s="46" t="n"/>
-      <c r="T19" s="42">
+      <c r="H19" s="58" t="n"/>
+      <c r="I19" s="58" t="n"/>
+      <c r="J19" s="58" t="n"/>
+      <c r="K19" s="58" t="n"/>
+      <c r="L19" s="58" t="n"/>
+      <c r="M19" s="58" t="n"/>
+      <c r="N19" s="58" t="n"/>
+      <c r="O19" s="58" t="n"/>
+      <c r="T19" s="54">
         <f>SUM(H19:S19)</f>
         <v/>
       </c>
-      <c r="U19" s="47" t="n"/>
-      <c r="V19" s="47" t="n"/>
+      <c r="U19" s="59" t="n"/>
+      <c r="V19" s="59" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="44">
+      <c r="A20" s="56">
         <f>Planejado!A20</f>
         <v/>
       </c>
-      <c r="B20" s="44">
+      <c r="B20" s="56">
         <f>Planejado!B20</f>
         <v/>
       </c>
-      <c r="C20" s="44">
+      <c r="C20" s="56">
         <f>Planejado!C20</f>
         <v/>
       </c>
-      <c r="D20" s="45">
+      <c r="D20" s="57">
         <f>Planejado!D20</f>
         <v/>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="57">
         <f>Planejado!E20</f>
         <v/>
       </c>
-      <c r="F20" s="44">
+      <c r="F20" s="56">
         <f>Planejado!F20</f>
         <v/>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="56">
         <f>Planejado!G20</f>
         <v/>
       </c>
-      <c r="H20" s="46" t="n"/>
-      <c r="I20" s="46" t="n"/>
-      <c r="J20" s="46" t="n"/>
-      <c r="K20" s="46" t="n"/>
-      <c r="L20" s="46" t="n"/>
-      <c r="M20" s="46" t="n"/>
-      <c r="N20" s="46" t="n"/>
-      <c r="O20" s="46" t="n"/>
-      <c r="T20" s="42">
+      <c r="H20" s="58" t="n"/>
+      <c r="I20" s="58" t="n"/>
+      <c r="J20" s="58" t="n"/>
+      <c r="K20" s="58" t="n"/>
+      <c r="L20" s="58" t="n"/>
+      <c r="M20" s="58" t="n"/>
+      <c r="N20" s="58" t="n"/>
+      <c r="O20" s="58" t="n"/>
+      <c r="T20" s="54">
         <f>SUM(H20:S20)</f>
         <v/>
       </c>
-      <c r="U20" s="47" t="n"/>
-      <c r="V20" s="47" t="n"/>
+      <c r="U20" s="59" t="n"/>
+      <c r="V20" s="59" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="44">
+      <c r="A21" s="56">
         <f>Planejado!A21</f>
         <v/>
       </c>
-      <c r="B21" s="44">
+      <c r="B21" s="56">
         <f>Planejado!B21</f>
         <v/>
       </c>
-      <c r="C21" s="44">
+      <c r="C21" s="56">
         <f>Planejado!C21</f>
         <v/>
       </c>
-      <c r="D21" s="45">
+      <c r="D21" s="57">
         <f>Planejado!D21</f>
         <v/>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="57">
         <f>Planejado!E21</f>
         <v/>
       </c>
-      <c r="F21" s="44">
+      <c r="F21" s="56">
         <f>Planejado!F21</f>
         <v/>
       </c>
-      <c r="G21" s="44">
+      <c r="G21" s="56">
         <f>Planejado!G21</f>
         <v/>
       </c>
-      <c r="H21" s="46" t="n"/>
-      <c r="I21" s="46" t="n"/>
-      <c r="J21" s="46" t="n"/>
-      <c r="K21" s="46" t="n"/>
-      <c r="L21" s="46" t="n"/>
-      <c r="M21" s="46" t="n"/>
-      <c r="N21" s="46" t="n"/>
-      <c r="O21" s="46" t="n"/>
-      <c r="T21" s="42">
+      <c r="H21" s="58" t="n"/>
+      <c r="I21" s="58" t="n"/>
+      <c r="J21" s="58" t="n"/>
+      <c r="K21" s="58" t="n"/>
+      <c r="L21" s="58" t="n"/>
+      <c r="M21" s="58" t="n"/>
+      <c r="N21" s="58" t="n"/>
+      <c r="O21" s="58" t="n"/>
+      <c r="T21" s="54">
         <f>SUM(H21:S21)</f>
         <v/>
       </c>
-      <c r="U21" s="47" t="n"/>
-      <c r="V21" s="47" t="n"/>
+      <c r="U21" s="59" t="n"/>
+      <c r="V21" s="59" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="44">
+      <c r="A22" s="56">
         <f>Planejado!A22</f>
         <v/>
       </c>
-      <c r="B22" s="44">
+      <c r="B22" s="56">
         <f>Planejado!B22</f>
         <v/>
       </c>
-      <c r="C22" s="44">
+      <c r="C22" s="56">
         <f>Planejado!C22</f>
         <v/>
       </c>
-      <c r="D22" s="45">
+      <c r="D22" s="57">
         <f>Planejado!D22</f>
         <v/>
       </c>
-      <c r="E22" s="45">
+      <c r="E22" s="57">
         <f>Planejado!E22</f>
         <v/>
       </c>
-      <c r="F22" s="44">
+      <c r="F22" s="56">
         <f>Planejado!F22</f>
         <v/>
       </c>
-      <c r="G22" s="44">
+      <c r="G22" s="56">
         <f>Planejado!G22</f>
         <v/>
       </c>
-      <c r="H22" s="46" t="n"/>
-      <c r="I22" s="46" t="n"/>
-      <c r="J22" s="46" t="n"/>
-      <c r="K22" s="46" t="n"/>
-      <c r="L22" s="46" t="n"/>
-      <c r="M22" s="46" t="n"/>
-      <c r="N22" s="46" t="n"/>
-      <c r="O22" s="46" t="n"/>
-      <c r="T22" s="42">
+      <c r="H22" s="58" t="n"/>
+      <c r="I22" s="58" t="n"/>
+      <c r="J22" s="58" t="n"/>
+      <c r="K22" s="58" t="n"/>
+      <c r="L22" s="58" t="n"/>
+      <c r="M22" s="58" t="n"/>
+      <c r="N22" s="58" t="n"/>
+      <c r="O22" s="58" t="n"/>
+      <c r="T22" s="54">
         <f>SUM(H22:S22)</f>
         <v/>
       </c>
-      <c r="U22" s="47" t="n"/>
-      <c r="V22" s="47" t="n"/>
+      <c r="U22" s="59" t="n"/>
+      <c r="V22" s="59" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="44">
+      <c r="A23" s="56">
         <f>Planejado!A23</f>
         <v/>
       </c>
-      <c r="B23" s="44">
+      <c r="B23" s="56">
         <f>Planejado!B23</f>
         <v/>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="56">
         <f>Planejado!C23</f>
         <v/>
       </c>
-      <c r="D23" s="45">
+      <c r="D23" s="57">
         <f>Planejado!D23</f>
         <v/>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="57">
         <f>Planejado!E23</f>
         <v/>
       </c>
-      <c r="F23" s="44">
+      <c r="F23" s="56">
         <f>Planejado!F23</f>
         <v/>
       </c>
-      <c r="G23" s="44">
+      <c r="G23" s="56">
         <f>Planejado!G23</f>
         <v/>
       </c>
-      <c r="H23" s="46" t="n"/>
-      <c r="I23" s="46" t="n"/>
-      <c r="J23" s="46" t="n"/>
-      <c r="K23" s="46" t="n"/>
-      <c r="L23" s="46" t="n"/>
-      <c r="M23" s="46" t="n"/>
-      <c r="N23" s="46" t="n"/>
-      <c r="O23" s="46" t="n"/>
-      <c r="T23" s="42">
+      <c r="H23" s="58" t="n"/>
+      <c r="I23" s="58" t="n"/>
+      <c r="J23" s="58" t="n"/>
+      <c r="K23" s="58" t="n"/>
+      <c r="L23" s="58" t="n"/>
+      <c r="M23" s="58" t="n"/>
+      <c r="N23" s="58" t="n"/>
+      <c r="O23" s="58" t="n"/>
+      <c r="T23" s="54">
         <f>SUM(H23:S23)</f>
         <v/>
       </c>
-      <c r="U23" s="47" t="n"/>
-      <c r="V23" s="47" t="n"/>
+      <c r="U23" s="59" t="n"/>
+      <c r="V23" s="59" t="n"/>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="44">
+      <c r="A24" s="56">
         <f>Planejado!A24</f>
         <v/>
       </c>
-      <c r="B24" s="44">
+      <c r="B24" s="56">
         <f>Planejado!B24</f>
         <v/>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="56">
         <f>Planejado!C24</f>
         <v/>
       </c>
-      <c r="D24" s="45">
+      <c r="D24" s="57">
         <f>Planejado!D24</f>
         <v/>
       </c>
-      <c r="E24" s="45">
+      <c r="E24" s="57">
         <f>Planejado!E24</f>
         <v/>
       </c>
-      <c r="F24" s="44">
+      <c r="F24" s="56">
         <f>Planejado!F24</f>
         <v/>
       </c>
-      <c r="G24" s="44">
+      <c r="G24" s="56">
         <f>Planejado!G24</f>
         <v/>
       </c>
-      <c r="H24" s="46" t="n"/>
-      <c r="I24" s="46" t="n"/>
-      <c r="J24" s="46" t="n"/>
-      <c r="K24" s="46" t="n"/>
-      <c r="L24" s="46" t="n"/>
-      <c r="M24" s="46" t="n"/>
-      <c r="N24" s="46" t="n"/>
-      <c r="O24" s="46" t="n"/>
-      <c r="T24" s="42">
+      <c r="H24" s="58" t="n"/>
+      <c r="I24" s="58" t="n"/>
+      <c r="J24" s="58" t="n"/>
+      <c r="K24" s="58" t="n"/>
+      <c r="L24" s="58" t="n"/>
+      <c r="M24" s="58" t="n"/>
+      <c r="N24" s="58" t="n"/>
+      <c r="O24" s="58" t="n"/>
+      <c r="T24" s="54">
         <f>SUM(H24:S24)</f>
         <v/>
       </c>
-      <c r="U24" s="47" t="n"/>
-      <c r="V24" s="47" t="n"/>
+      <c r="U24" s="59" t="n"/>
+      <c r="V24" s="59" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="44">
+      <c r="A25" s="56">
         <f>Planejado!A25</f>
         <v/>
       </c>
-      <c r="B25" s="44">
+      <c r="B25" s="56">
         <f>Planejado!B25</f>
         <v/>
       </c>
-      <c r="C25" s="44">
+      <c r="C25" s="56">
         <f>Planejado!C25</f>
         <v/>
       </c>
-      <c r="D25" s="45">
+      <c r="D25" s="57">
         <f>Planejado!D25</f>
         <v/>
       </c>
-      <c r="E25" s="45">
+      <c r="E25" s="57">
         <f>Planejado!E25</f>
         <v/>
       </c>
-      <c r="F25" s="44">
+      <c r="F25" s="56">
         <f>Planejado!F25</f>
         <v/>
       </c>
-      <c r="G25" s="44">
+      <c r="G25" s="56">
         <f>Planejado!G25</f>
         <v/>
       </c>
-      <c r="H25" s="46" t="n"/>
-      <c r="I25" s="46" t="n"/>
-      <c r="J25" s="46" t="n"/>
-      <c r="K25" s="46" t="n"/>
-      <c r="L25" s="46" t="n"/>
-      <c r="M25" s="46" t="n"/>
-      <c r="N25" s="46" t="n"/>
-      <c r="O25" s="46" t="n"/>
-      <c r="T25" s="42">
+      <c r="H25" s="58" t="n"/>
+      <c r="I25" s="58" t="n"/>
+      <c r="J25" s="58" t="n"/>
+      <c r="K25" s="58" t="n"/>
+      <c r="L25" s="58" t="n"/>
+      <c r="M25" s="58" t="n"/>
+      <c r="N25" s="58" t="n"/>
+      <c r="O25" s="58" t="n"/>
+      <c r="T25" s="54">
         <f>SUM(H25:S25)</f>
         <v/>
       </c>
-      <c r="U25" s="47" t="n"/>
-      <c r="V25" s="47" t="n"/>
+      <c r="U25" s="59" t="n"/>
+      <c r="V25" s="59" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="48" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B26" s="48" t="n"/>
-      <c r="C26" s="48" t="n"/>
-      <c r="D26" s="48" t="n"/>
-      <c r="E26" s="48" t="n"/>
-      <c r="F26" s="48" t="n"/>
-      <c r="G26" s="48" t="n"/>
-      <c r="H26" s="49">
+      <c r="B26" s="60" t="n"/>
+      <c r="C26" s="60" t="n"/>
+      <c r="D26" s="60" t="n"/>
+      <c r="E26" s="60" t="n"/>
+      <c r="F26" s="60" t="n"/>
+      <c r="G26" s="60" t="n"/>
+      <c r="H26" s="61">
         <f>SUM(H5:H25)</f>
         <v/>
       </c>
-      <c r="I26" s="49">
+      <c r="I26" s="61">
         <f>SUM(I5:I25)</f>
         <v/>
       </c>
-      <c r="J26" s="49">
+      <c r="J26" s="61">
         <f>SUM(J5:J25)</f>
         <v/>
       </c>
-      <c r="K26" s="49">
+      <c r="K26" s="61">
         <f>SUM(K5:K25)</f>
         <v/>
       </c>
-      <c r="L26" s="49">
+      <c r="L26" s="61">
         <f>SUM(L5:L25)</f>
         <v/>
       </c>
-      <c r="M26" s="49">
+      <c r="M26" s="61">
         <f>SUM(M5:M25)</f>
         <v/>
       </c>
-      <c r="N26" s="49">
+      <c r="N26" s="61">
         <f>SUM(N5:N25)</f>
         <v/>
       </c>
-      <c r="O26" s="49">
+      <c r="O26" s="61">
         <f>SUM(O5:O25)</f>
         <v/>
       </c>
-      <c r="P26" s="49">
+      <c r="P26" s="61">
         <f>SUM(P5:P25)</f>
         <v/>
       </c>
-      <c r="Q26" s="49">
+      <c r="Q26" s="61">
         <f>SUM(Q5:Q25)</f>
         <v/>
       </c>
-      <c r="R26" s="49">
+      <c r="R26" s="61">
         <f>SUM(R5:R25)</f>
         <v/>
       </c>
-      <c r="S26" s="49">
+      <c r="S26" s="61">
         <f>SUM(S5:S25)</f>
         <v/>
       </c>
-      <c r="T26" s="49">
+      <c r="T26" s="61">
         <f>SUM(T5:T25)</f>
         <v/>
       </c>
-      <c r="U26" s="48" t="n"/>
-      <c r="V26" s="48" t="n"/>
+      <c r="U26" s="60" t="n"/>
+      <c r="V26" s="60" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6468,517 +7124,517 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>Jan/26</t>
         </is>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="42">
         <f>SUMIFS(Planejado!$H$5:$H$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="42">
         <f>SUMIFS(Realizado!$H$5:$H$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="42">
         <f>SUMIFS(Planejado!$H$5:$H$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="42">
         <f>SUMIFS(Realizado!$H$5:$H$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="42">
         <f>B5+D5</f>
         <v/>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="42">
         <f>C5+E5</f>
         <v/>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="42">
         <f>G5-F5</f>
         <v/>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="42">
         <f>SUM($F$5:F5)</f>
         <v/>
       </c>
-      <c r="J5" s="31">
+      <c r="J5" s="42">
         <f>SUM($G$5:G5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="63" t="inlineStr">
         <is>
           <t>Fev/26</t>
         </is>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="49">
         <f>SUMIFS(Planejado!$I$5:$I$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="49">
         <f>SUMIFS(Realizado!$I$5:$I$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="49">
         <f>SUMIFS(Planejado!$I$5:$I$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="49">
         <f>SUMIFS(Realizado!$I$5:$I$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="49">
         <f>B6+D6</f>
         <v/>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="49">
         <f>C6+E6</f>
         <v/>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="49">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="37">
+      <c r="I6" s="49">
         <f>SUM($F$5:F6)</f>
         <v/>
       </c>
-      <c r="J6" s="37">
+      <c r="J6" s="49">
         <f>SUM($G$5:G6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="50" t="inlineStr">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>Mar/26</t>
         </is>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="42">
         <f>SUMIFS(Planejado!$J$5:$J$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="42">
         <f>SUMIFS(Realizado!$J$5:$J$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="42">
         <f>SUMIFS(Planejado!$J$5:$J$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="42">
         <f>SUMIFS(Realizado!$J$5:$J$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="42">
         <f>B7+D7</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="42">
         <f>C7+E7</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="42">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="42">
         <f>SUM($F$5:F7)</f>
         <v/>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="42">
         <f>SUM($G$5:G7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="51" t="inlineStr">
+      <c r="A8" s="63" t="inlineStr">
         <is>
           <t>Abr/26</t>
         </is>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="49">
         <f>SUMIFS(Planejado!$K$5:$K$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="49">
         <f>SUMIFS(Realizado!$K$5:$K$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="49">
         <f>SUMIFS(Planejado!$K$5:$K$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="49">
         <f>SUMIFS(Realizado!$K$5:$K$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="49">
         <f>B8+D8</f>
         <v/>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="49">
         <f>C8+E8</f>
         <v/>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="49">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="49">
         <f>SUM($F$5:F8)</f>
         <v/>
       </c>
-      <c r="J8" s="37">
+      <c r="J8" s="49">
         <f>SUM($G$5:G8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="62" t="inlineStr">
         <is>
           <t>Mai/26</t>
         </is>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="42">
         <f>SUMIFS(Planejado!$L$5:$L$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="42">
         <f>SUMIFS(Realizado!$L$5:$L$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="42">
         <f>SUMIFS(Planejado!$L$5:$L$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="42">
         <f>SUMIFS(Realizado!$L$5:$L$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="42">
         <f>B9+D9</f>
         <v/>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="42">
         <f>C9+E9</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="42">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="42">
         <f>SUM($F$5:F9)</f>
         <v/>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="42">
         <f>SUM($G$5:G9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="63" t="inlineStr">
         <is>
           <t>Jun/26</t>
         </is>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="49">
         <f>SUMIFS(Planejado!$M$5:$M$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="49">
         <f>SUMIFS(Realizado!$M$5:$M$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="49">
         <f>SUMIFS(Planejado!$M$5:$M$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="49">
         <f>SUMIFS(Realizado!$M$5:$M$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="49">
         <f>B10+D10</f>
         <v/>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="49">
         <f>C10+E10</f>
         <v/>
       </c>
-      <c r="H10" s="37">
+      <c r="H10" s="49">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="37">
+      <c r="I10" s="49">
         <f>SUM($F$5:F10)</f>
         <v/>
       </c>
-      <c r="J10" s="37">
+      <c r="J10" s="49">
         <f>SUM($G$5:G10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="50" t="inlineStr">
+      <c r="A11" s="62" t="inlineStr">
         <is>
           <t>Jul/26</t>
         </is>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="42">
         <f>SUMIFS(Planejado!$N$5:$N$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="42">
         <f>SUMIFS(Realizado!$N$5:$N$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="42">
         <f>SUMIFS(Planejado!$N$5:$N$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="42">
         <f>SUMIFS(Realizado!$N$5:$N$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="42">
         <f>B11+D11</f>
         <v/>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="42">
         <f>C11+E11</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="42">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="42">
         <f>SUM($F$5:F11)</f>
         <v/>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="42">
         <f>SUM($G$5:G11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="51" t="inlineStr">
+      <c r="A12" s="63" t="inlineStr">
         <is>
           <t>Ago/26</t>
         </is>
       </c>
-      <c r="B12" s="37">
+      <c r="B12" s="49">
         <f>SUMIFS(Planejado!$O$5:$O$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="49">
         <f>SUMIFS(Realizado!$O$5:$O$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D12" s="37">
+      <c r="D12" s="49">
         <f>SUMIFS(Planejado!$O$5:$O$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E12" s="37">
+      <c r="E12" s="49">
         <f>SUMIFS(Realizado!$O$5:$O$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="49">
         <f>B12+D12</f>
         <v/>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="49">
         <f>C12+E12</f>
         <v/>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="49">
         <f>G12-F12</f>
         <v/>
       </c>
-      <c r="I12" s="37">
+      <c r="I12" s="49">
         <f>SUM($F$5:F12)</f>
         <v/>
       </c>
-      <c r="J12" s="37">
+      <c r="J12" s="49">
         <f>SUM($G$5:G12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr">
         <is>
           <t>Set/26</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="42">
         <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="42">
         <f>SUMIFS(Realizado!$P$5:$P$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="42">
         <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="42">
         <f>SUMIFS(Realizado!$P$5:$P$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="42">
         <f>B13+D13</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="42">
         <f>C13+E13</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="42">
         <f>G13-F13</f>
         <v/>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="42">
         <f>SUM($F$5:F13)</f>
         <v/>
       </c>
-      <c r="J13" s="31">
+      <c r="J13" s="42">
         <f>SUM($G$5:G13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="63" t="inlineStr">
         <is>
           <t>Out/26</t>
         </is>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="49">
         <f>SUMIFS(Planejado!$Q$5:$Q$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="49">
         <f>SUMIFS(Realizado!$Q$5:$Q$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="49">
         <f>SUMIFS(Planejado!$Q$5:$Q$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="49">
         <f>SUMIFS(Realizado!$Q$5:$Q$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="49">
         <f>B14+D14</f>
         <v/>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="49">
         <f>C14+E14</f>
         <v/>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="49">
         <f>G14-F14</f>
         <v/>
       </c>
-      <c r="I14" s="37">
+      <c r="I14" s="49">
         <f>SUM($F$5:F14)</f>
         <v/>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="49">
         <f>SUM($G$5:G14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="50" t="inlineStr">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t>Nov/26</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="42">
         <f>SUMIFS(Planejado!$R$5:$R$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="42">
         <f>SUMIFS(Realizado!$R$5:$R$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="42">
         <f>SUMIFS(Planejado!$R$5:$R$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="42">
         <f>SUMIFS(Realizado!$R$5:$R$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="42">
         <f>B15+D15</f>
         <v/>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="42">
         <f>C15+E15</f>
         <v/>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="42">
         <f>G15-F15</f>
         <v/>
       </c>
-      <c r="I15" s="31">
+      <c r="I15" s="42">
         <f>SUM($F$5:F15)</f>
         <v/>
       </c>
-      <c r="J15" s="31">
+      <c r="J15" s="42">
         <f>SUM($G$5:G15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="63" t="inlineStr">
         <is>
           <t>Dez/26</t>
         </is>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="49">
         <f>SUMIFS(Planejado!$S$5:$S$25,Planejado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="49">
         <f>SUMIFS(Realizado!$S$5:$S$25,Realizado!$B$5:$B$25,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="49">
         <f>SUMIFS(Planejado!$S$5:$S$25,Planejado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="49">
         <f>SUMIFS(Realizado!$S$5:$S$25,Realizado!$B$5:$B$25,"TI")</f>
         <v/>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="49">
         <f>B16+D16</f>
         <v/>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="49">
         <f>C16+E16</f>
         <v/>
       </c>
-      <c r="H16" s="37">
+      <c r="H16" s="49">
         <f>G16-F16</f>
         <v/>
       </c>
-      <c r="I16" s="37">
+      <c r="I16" s="49">
         <f>SUM($F$5:F16)</f>
         <v/>
       </c>
-      <c r="J16" s="37">
+      <c r="J16" s="49">
         <f>SUM($G$5:G16)</f>
         <v/>
       </c>
@@ -7126,302 +7782,302 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>Pessoal - CLT</t>
         </is>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="42">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="42">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="42">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="42">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="42">
         <f>B5+D5</f>
         <v/>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="42">
         <f>C5+E5</f>
         <v/>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="42">
         <f>G5-F5</f>
         <v/>
       </c>
-      <c r="I5" s="53">
+      <c r="I5" s="65">
         <f>IFERROR(H5/F5,"")</f>
         <v/>
       </c>
-      <c r="J5" s="31">
+      <c r="J5" s="42">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>Pessoal - PJ</t>
         </is>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="49">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="49">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="49">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="49">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="49">
         <f>B6+D6</f>
         <v/>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="49">
         <f>C6+E6</f>
         <v/>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="49">
         <f>G6-F6</f>
         <v/>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="67">
         <f>IFERROR(H6/F6,"")</f>
         <v/>
       </c>
-      <c r="J6" s="37">
+      <c r="J6" s="49">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>Licenças de Softwares</t>
         </is>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="42">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="42">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="42">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="42">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="42">
         <f>B7+D7</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="42">
         <f>C7+E7</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="42">
         <f>G7-F7</f>
         <v/>
       </c>
-      <c r="I7" s="53">
+      <c r="I7" s="65">
         <f>IFERROR(H7/F7,"")</f>
         <v/>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="42">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="54" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>Custeio de Treinamento</t>
         </is>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="49">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="49">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="49">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="49">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="49">
         <f>B8+D8</f>
         <v/>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="49">
         <f>C8+E8</f>
         <v/>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="49">
         <f>G8-F8</f>
         <v/>
       </c>
-      <c r="I8" s="55">
+      <c r="I8" s="67">
         <f>IFERROR(H8/F8,"")</f>
         <v/>
       </c>
-      <c r="J8" s="37">
+      <c r="J8" s="49">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="52" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>Prêmios</t>
         </is>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="42">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="42">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="42">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="42">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="42">
         <f>B9+D9</f>
         <v/>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="42">
         <f>C9+E9</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="42">
         <f>G9-F9</f>
         <v/>
       </c>
-      <c r="I9" s="53">
+      <c r="I9" s="65">
         <f>IFERROR(H9/F9,"")</f>
         <v/>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="42">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
-      <c r="B10" s="37">
+      <c r="B10" s="49">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="49">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="49">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="49">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="49">
         <f>B10+D10</f>
         <v/>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="49">
         <f>C10+E10</f>
         <v/>
       </c>
-      <c r="H10" s="37">
+      <c r="H10" s="49">
         <f>G10-F10</f>
         <v/>
       </c>
-      <c r="I10" s="55">
+      <c r="I10" s="67">
         <f>IFERROR(H10/F10,"")</f>
         <v/>
       </c>
-      <c r="J10" s="37">
+      <c r="J10" s="49">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="52" t="inlineStr">
+      <c r="A11" s="64" t="inlineStr">
         <is>
           <t>Móveis e Utensílios</t>
         </is>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="42">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="42">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"Jurídico")</f>
         <v/>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="42">
         <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="42">
         <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"TI")</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="42">
         <f>B11+D11</f>
         <v/>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="42">
         <f>C11+E11</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="42">
         <f>G11-F11</f>
         <v/>
       </c>
-      <c r="I11" s="53">
+      <c r="I11" s="65">
         <f>IFERROR(H11/F11,"")</f>
         <v/>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="42">
         <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A11)</f>
         <v/>
       </c>
@@ -7550,544 +8206,544 @@
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="56" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="57" t="inlineStr">
+      <c r="B5" s="69" t="inlineStr">
         <is>
           <t>Geovanna — realizado em base diferente do orçado</t>
         </is>
       </c>
-      <c r="C5" s="57" t="inlineStr">
+      <c r="C5" s="69" t="inlineStr">
         <is>
           <t>O planejado dela é R$ 4.825,52/mês, que é o CUSTO TOTAL orçado na ficha (salário + encargos de folha + benefícios). O realizado lançado é o SALÁRIO BRUTO, R$ 2.886,91/mês, confirmado sem alteração no ano. São bases diferentes.</t>
         </is>
       </c>
-      <c r="D5" s="57" t="inlineStr">
+      <c r="D5" s="69" t="inlineStr">
         <is>
           <t>O desvio desta linha (−R$ 1.938,61/mês, −R$ 13.570,24 no acumulado jan–jul) NÃO é economia: é o encargo que falta do lado do realizado. Para fechar, peça ao RH o custo total mensal dela — ou o percentual de encargos da empresa, que dá para calcular a partir do bruto.</t>
         </is>
       </c>
-      <c r="E5" s="57" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>Cristiane + RH</t>
         </is>
       </c>
-      <c r="F5" s="58" t="inlineStr">
+      <c r="F5" s="70" t="inlineStr">
         <is>
           <t>BASE DIFERENTE</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>Vinicius — custo total A LANÇAR</t>
         </is>
       </c>
-      <c r="C6" s="60" t="inlineStr">
+      <c r="C6" s="72" t="inlineStr">
         <is>
           <t>Mesmo caso da Geovanna. O planejado é R$ 5.416,525/mês (custo total). Brutos confirmados: R$ 2.570,52 até jul/26 e R$ 3.070,52 a partir de 05/08/26 — o aumento é absorvido pela folga do envelope, que já previa reajuste, então o orçado não muda. O realizado está em branco.</t>
         </is>
       </c>
-      <c r="D6" s="60" t="inlineStr">
+      <c r="D6" s="72" t="inlineStr">
         <is>
           <t>A folga do orçado NÃO é economia estrutural. Com o bruto de agosto, sobram R$ 2.346,01 para encargos, o que equivale a 76% sobre o bruto — dentro da faixa normal (67% a 80%), então pode sobrar ou estourar. Só o custo total real vai dizer.</t>
         </is>
       </c>
-      <c r="E6" s="60" t="inlineStr">
+      <c r="E6" s="72" t="inlineStr">
         <is>
           <t>Cristiane + RH</t>
         </is>
       </c>
-      <c r="F6" s="58" t="inlineStr">
+      <c r="F6" s="70" t="inlineStr">
         <is>
           <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="56" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B7" s="57" t="inlineStr">
+      <c r="B7" s="69" t="inlineStr">
         <is>
           <t>Aumento da Thamar em abr/26</t>
         </is>
       </c>
-      <c r="C7" s="57" t="inlineStr">
+      <c r="C7" s="69" t="inlineStr">
         <is>
           <t>Recebia R$ 4.500/mês de jan a mar, abaixo dos R$ 5.000 orçados. Em abr/26 teve aumento de R$ 1.000 e passou a R$ 5.500, acima do orçado. O planejado foi mantido em R$ 5.000 nos sete meses fechados (para o desvio ficar visível) e revisado para R$ 5.500 de ago a dez.</t>
         </is>
       </c>
-      <c r="D7" s="57" t="inlineStr">
+      <c r="D7" s="69" t="inlineStr">
         <is>
           <t>No acumulado jan–jul o efeito líquido é de apenas R$ 500 acima do orçado (−R$ 1.500 em jan–mar, +R$ 2.000 em abr–jul), e mais R$ 2.500 previstos até dezembro. Ao contrário do aumento do Vinicius, este estourou o orçado: não havia folga na linha dela.</t>
         </is>
       </c>
-      <c r="E7" s="57" t="inlineStr">
+      <c r="E7" s="69" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F7" s="61" t="inlineStr">
+      <c r="F7" s="73" t="inlineStr">
         <is>
           <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>Jusbrasil 30% acima do orçado</t>
         </is>
       </c>
-      <c r="C8" s="60" t="inlineStr">
+      <c r="C8" s="72" t="inlineStr">
         <is>
           <t>Orçado R$ 104,90/mês, realizado R$ 136,00/mês em mai, jun e jul.</t>
         </is>
       </c>
-      <c r="D8" s="60" t="inlineStr">
+      <c r="D8" s="72" t="inlineStr">
         <is>
           <t>Menor desvio em reais (R$ 31,10/mês), mas o maior em percentual. Vale conferir se houve reajuste contratual ou mudança de plano.</t>
         </is>
       </c>
-      <c r="E8" s="60" t="inlineStr">
+      <c r="E8" s="72" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F8" s="62" t="inlineStr">
+      <c r="F8" s="74" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="56" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B9" s="57" t="inlineStr">
+      <c r="B9" s="69" t="inlineStr">
         <is>
           <t>Bonificação de ago/26 do Jurídico</t>
         </is>
       </c>
-      <c r="C9" s="57" t="inlineStr">
+      <c r="C9" s="69" t="inlineStr">
         <is>
           <t>Estão orçados R$ 10.293,60 em agosto e R$ 12.867,00 em dezembro. O realizado de agosto ainda não foi informado.</t>
         </is>
       </c>
-      <c r="D9" s="57" t="inlineStr">
+      <c r="D9" s="69" t="inlineStr">
         <is>
           <t>É a maior despesa isolada do Jurídico no segundo semestre.</t>
         </is>
       </c>
-      <c r="E9" s="57" t="inlineStr">
+      <c r="E9" s="69" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F9" s="62" t="inlineStr">
+      <c r="F9" s="74" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="71" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="72" t="inlineStr">
         <is>
           <t>Jonathan R$ 3.700/mês abaixo do contratado</t>
         </is>
       </c>
-      <c r="C10" s="60" t="inlineStr">
+      <c r="C10" s="72" t="inlineStr">
         <is>
           <t>Orçado R$ 10.000/mês, realizado R$ 6.300/mês em mai, jun e jul.</t>
         </is>
       </c>
-      <c r="D10" s="60" t="inlineStr">
+      <c r="D10" s="72" t="inlineStr">
         <is>
           <t>Maior desvio em reais de todo o orçamento: R$ 11.100 em três meses. Se o valor menor for o novo padrão, o planejado de ago a dez deve ser revisado para baixo — sobrariam R$ 18.500 no orçamento do TI.</t>
         </is>
       </c>
-      <c r="E10" s="60" t="inlineStr">
+      <c r="E10" s="72" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F10" s="62" t="inlineStr">
+      <c r="F10" s="74" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="56" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B11" s="57" t="inlineStr">
+      <c r="B11" s="69" t="inlineStr">
         <is>
           <t>Elias Benedito zerado nos três meses</t>
         </is>
       </c>
-      <c r="C11" s="57" t="inlineStr">
+      <c r="C11" s="69" t="inlineStr">
         <is>
           <t>Orçado R$ 1.065/mês como suporte técnico terceirizado, realizado R$ 0 em mai, jun e jul.</t>
         </is>
       </c>
-      <c r="D11" s="57" t="inlineStr">
+      <c r="D11" s="69" t="inlineStr">
         <is>
           <t>Confirmar se o contrato segue ativo (acionamento sob demanda) ou se foi encerrado. Se encerrado, são R$ 12.780 a liberar no orçamento do ano.</t>
         </is>
       </c>
-      <c r="E11" s="57" t="inlineStr">
+      <c r="E11" s="69" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F11" s="62" t="inlineStr">
+      <c r="F11" s="74" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>Planejado de jan a abr — CONFERIR</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="72" t="inlineStr">
         <is>
           <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
         </is>
       </c>
-      <c r="D12" s="60" t="inlineStr">
+      <c r="D12" s="72" t="inlineStr">
         <is>
           <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
         </is>
       </c>
-      <c r="E12" s="60" t="inlineStr">
+      <c r="E12" s="72" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F12" s="63" t="inlineStr">
+      <c r="F12" s="75" t="inlineStr">
         <is>
           <t>CONFERIR</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="56" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B13" s="57" t="inlineStr">
+      <c r="B13" s="69" t="inlineStr">
         <is>
           <t>Realizado de jan a abr — A LANÇAR</t>
         </is>
       </c>
-      <c r="C13" s="57" t="inlineStr">
+      <c r="C13" s="69" t="inlineStr">
         <is>
           <t>As colunas de jan a abr estão em branco na aba Realizado. Só mai, jun e jul foram informados.</t>
         </is>
       </c>
-      <c r="D13" s="57" t="inlineStr">
+      <c r="D13" s="69" t="inlineStr">
         <is>
           <t>São 4 dos 7 meses já fechados do ano. Sem eles o acumulado e o Painel refletem menos da metade do período decorrido.</t>
         </is>
       </c>
-      <c r="E13" s="57" t="inlineStr">
+      <c r="E13" s="69" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F13" s="58" t="inlineStr">
+      <c r="F13" s="70" t="inlineStr">
         <is>
           <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="59" t="inlineStr">
+      <c r="A14" s="71" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="72" t="inlineStr">
         <is>
           <t>Despesas do TI — A LANÇAR</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="72" t="inlineStr">
         <is>
           <t>As 9 linhas de despesas do TI (peças, backup, Adapta, antivírus, Office, sala de reunião, cursos, app de gravação e bonificação) não têm lançamento em nenhum mês.</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr">
+      <c r="D14" s="72" t="inlineStr">
         <is>
           <t>São R$ 89.040 orçados no ano, 35% do orçamento do TI. Sem lançamento, o departamento aparece com desvio negativo que é ausência de dado.</t>
         </is>
       </c>
-      <c r="E14" s="60" t="inlineStr">
+      <c r="E14" s="72" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F14" s="58" t="inlineStr">
+      <c r="F14" s="70" t="inlineStr">
         <is>
           <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="56" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B15" s="57" t="inlineStr">
+      <c r="B15" s="69" t="inlineStr">
         <is>
           <t>Base de meses — reconciliada com a ficha original</t>
         </is>
       </c>
-      <c r="C15" s="57" t="inlineStr">
+      <c r="C15" s="69" t="inlineStr">
         <is>
           <t>A ficha trazia a coluna TOTAL do TI digitada à mão em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9) enquanto o grid mensal tinha só 8 colunas. Com o período em jan–dez os três totais batem exatamente: R$ 64.998,30 + R$ 12.780,00 + R$ 90.000,00 = R$ 167.778,30, o valor da ficha. Não era erro de digitação — era o grid que estava incompleto.</t>
         </is>
       </c>
-      <c r="D15" s="57" t="inlineStr">
+      <c r="D15" s="69" t="inlineStr">
         <is>
           <t>Equipe de TI no valor original de R$ 167.778,30. Jonathan lançado com entrada em abr/26 (9 meses), que é o que explica os R$ 90.000.</t>
         </is>
       </c>
-      <c r="E15" s="57" t="inlineStr">
+      <c r="E15" s="69" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F15" s="61" t="inlineStr">
+      <c r="F15" s="73" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="71" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="B16" s="72" t="inlineStr">
         <is>
           <t>Origem do valor realizado</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C16" s="72" t="inlineStr">
         <is>
           <t>Ainda não definido se o realizado virá de lançamento manual, de relatório do financeiro/ERP por centro de custo, ou misto. Até aqui os números vieram informados pela gestora.</t>
         </is>
       </c>
-      <c r="D16" s="60" t="inlineStr">
+      <c r="D16" s="72" t="inlineStr">
         <is>
           <t>Sem fonte definida o realizado pode divergir da contabilidade e o comparativo perde valor na apresentação à diretoria.</t>
         </is>
       </c>
-      <c r="E16" s="60" t="inlineStr">
+      <c r="E16" s="72" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F16" s="62" t="inlineStr">
+      <c r="F16" s="74" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="56" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B17" s="57" t="inlineStr">
+      <c r="B17" s="69" t="inlineStr">
         <is>
           <t>Jusfy x Astrea</t>
         </is>
       </c>
-      <c r="C17" s="57" t="inlineStr">
+      <c r="C17" s="69" t="inlineStr">
         <is>
           <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
         </is>
       </c>
-      <c r="D17" s="57" t="inlineStr">
+      <c r="D17" s="69" t="inlineStr">
         <is>
           <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado dos meses seguintes.</t>
         </is>
       </c>
-      <c r="E17" s="57" t="inlineStr">
+      <c r="E17" s="69" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F17" s="61" t="inlineStr">
+      <c r="F17" s="73" t="inlineStr">
         <is>
           <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="59" t="inlineStr">
+      <c r="A18" s="71" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="72" t="inlineStr">
         <is>
           <t>Rateio dos softwares corporativos de TI</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
+      <c r="C18" s="72" t="inlineStr">
         <is>
           <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
         </is>
       </c>
-      <c r="D18" s="60" t="inlineStr">
+      <c r="D18" s="72" t="inlineStr">
         <is>
           <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
         </is>
       </c>
-      <c r="E18" s="60" t="inlineStr">
+      <c r="E18" s="72" t="inlineStr">
         <is>
           <t>Cristiane + Controladoria</t>
         </is>
       </c>
-      <c r="F18" s="62" t="inlineStr">
+      <c r="F18" s="74" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="56" t="inlineStr">
+      <c r="A19" s="68" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B19" s="57" t="inlineStr">
+      <c r="B19" s="69" t="inlineStr">
         <is>
           <t>Sala de Reunião — recorrente ou pontual?</t>
         </is>
       </c>
-      <c r="C19" s="57" t="inlineStr">
+      <c r="C19" s="69" t="inlineStr">
         <is>
           <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
         </is>
       </c>
-      <c r="D19" s="57" t="inlineStr">
+      <c r="D19" s="69" t="inlineStr">
         <is>
           <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
         </is>
       </c>
-      <c r="E19" s="57" t="inlineStr">
+      <c r="E19" s="69" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F19" s="62" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="71" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="B20" s="72" t="inlineStr">
         <is>
           <t>Office 365 — nº de licenças</t>
         </is>
       </c>
-      <c r="C20" s="60" t="inlineStr">
+      <c r="C20" s="72" t="inlineStr">
         <is>
           <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
         </is>
       </c>
-      <c r="D20" s="60" t="inlineStr">
+      <c r="D20" s="72" t="inlineStr">
         <is>
           <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
         </is>
       </c>
-      <c r="E20" s="60" t="inlineStr">
+      <c r="E20" s="72" t="inlineStr">
         <is>
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F20" s="62" t="inlineStr">
+      <c r="F20" s="74" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="56" t="inlineStr">
+      <c r="A21" s="68" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B21" s="57" t="inlineStr">
+      <c r="B21" s="69" t="inlineStr">
         <is>
           <t>Critério de competência x caixa</t>
         </is>
       </c>
-      <c r="C21" s="57" t="inlineStr">
+      <c r="C21" s="69" t="inlineStr">
         <is>
           <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
         </is>
       </c>
-      <c r="D21" s="57" t="inlineStr">
+      <c r="D21" s="69" t="inlineStr">
         <is>
           <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
         </is>
       </c>
-      <c r="E21" s="57" t="inlineStr">
+      <c r="E21" s="69" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F21" s="62" t="inlineStr">
+      <c r="F21" s="74" t="inlineStr">
         <is>
           <t>EM ABERTO</t>
         </is>
@@ -8131,67 +8787,67 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>ROTINA MENSAL</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="64" t="inlineStr">
+      <c r="A5" s="76" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="65" t="inlineStr">
+      <c r="B5" s="77" t="inlineStr">
         <is>
           <t>Abra a aba REALIZADO e preencha apenas as células amarelas do mês que fechou. Se o item não teve gasto no mês, digite 0 — deixar em branco significa 'ainda não lancei'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="64" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="65" t="inlineStr">
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>Preencha a coluna 'Fonte do dado' (ex.: relatório do financeiro, nota fiscal, extrato do cartão) para o número ser auditável depois.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="76" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="77" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="64" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="65" t="inlineStr">
+      <c r="B8" s="77" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="64" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="65" t="inlineStr">
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -8199,67 +8855,67 @@
     </row>
     <row r="10" ht="8" customHeight="1"/>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>COMO LER OS NÚMEROS</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="64" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="65" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="64" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="65" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="64" t="inlineStr">
+      <c r="A14" s="76" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="65" t="inlineStr">
+      <c r="B14" s="77" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="64" t="inlineStr">
+      <c r="A15" s="76" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="65" t="inlineStr">
+      <c r="B15" s="77" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="64" t="inlineStr">
+      <c r="A16" s="76" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="65" t="inlineStr">
+      <c r="B16" s="77" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -8267,43 +8923,43 @@
     </row>
     <row r="17" ht="8" customHeight="1"/>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>REGRAS DA PLANILHA</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="64" t="inlineStr">
+      <c r="A19" s="76" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="65" t="inlineStr">
+      <c r="B19" s="77" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="64" t="inlineStr">
+      <c r="A20" s="76" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="65" t="inlineStr">
+      <c r="B20" s="77" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="64" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="65" t="inlineStr">
+      <c r="B21" s="77" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -5824,27 +5824,29 @@
         <v/>
       </c>
       <c r="H5" s="58" t="n">
+        <v>6750</v>
+      </c>
+      <c r="I5" s="58" t="n">
+        <v>6750</v>
+      </c>
+      <c r="J5" s="58" t="n">
+        <v>6750</v>
+      </c>
+      <c r="K5" s="58" t="n">
+        <v>6750</v>
+      </c>
+      <c r="L5" s="58" t="n">
+        <v>6750</v>
+      </c>
+      <c r="M5" s="58" t="n">
+        <v>6750</v>
+      </c>
+      <c r="N5" s="58" t="n">
+        <v>6750</v>
+      </c>
+      <c r="O5" s="58" t="n">
         <v>8818</v>
       </c>
-      <c r="I5" s="58" t="n">
-        <v>8818</v>
-      </c>
-      <c r="J5" s="58" t="n">
-        <v>8818</v>
-      </c>
-      <c r="K5" s="58" t="n">
-        <v>8818</v>
-      </c>
-      <c r="L5" s="58" t="n">
-        <v>8818</v>
-      </c>
-      <c r="M5" s="58" t="n">
-        <v>8818</v>
-      </c>
-      <c r="N5" s="58" t="n">
-        <v>8818</v>
-      </c>
-      <c r="O5" s="58" t="n"/>
       <c r="T5" s="54">
         <f>SUM(H5:S5)</f>
         <v/>
@@ -5856,7 +5858,7 @@
       </c>
       <c r="V5" s="59" t="inlineStr">
         <is>
-          <t>Valor cheio da nota — R$ 1.182/mês abaixo do contratado</t>
+          <t>R$ 6.750/mês de jan a jul; R$ 8.818 pagos em 01/08 (ref. julho). Lançado por caixa</t>
         </is>
       </c>
     </row>
@@ -8725,17 +8727,17 @@
       </c>
       <c r="B21" s="69" t="inlineStr">
         <is>
-          <t>Critério de competência x caixa</t>
+          <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
         </is>
       </c>
       <c r="C21" s="69" t="inlineStr">
         <is>
-          <t>Definir se o realizado será lançado pela data de pagamento (caixa) ou pelo mês de referência da despesa (competência).</t>
+          <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
         </is>
       </c>
       <c r="D21" s="69" t="inlineStr">
         <is>
-          <t>Misturar os dois critérios gera desvio artificial em meses de virada, principalmente em folha e prêmios.</t>
+          <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Vale conferir quais contratos pagam no mês seguinte e decidir se o comparativo passa para competência.</t>
         </is>
       </c>
       <c r="E21" s="69" t="inlineStr">
@@ -8743,9 +8745,9 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F21" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F21" s="75" t="inlineStr">
+        <is>
+          <t>DECIDIR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Como usar" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -146,7 +146,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -218,6 +218,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -245,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -410,6 +415,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1211,15 +1219,15 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"Jurídico",Planejado!$C$5:$C$25,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"Jurídico",Planejado!$C$5:$C$29,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -1235,7 +1243,7 @@
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1251,15 +1259,15 @@
         </is>
       </c>
       <c r="C7" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"Jurídico",Planejado!$C$5:$C$25,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"Jurídico",Planejado!$C$5:$C$29,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="9">
@@ -1275,7 +1283,7 @@
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"Jurídico",Comparativo!$C$6:$C$26,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1291,15 +1299,15 @@
         </is>
       </c>
       <c r="C8" s="13">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="F8" s="13">
@@ -1315,7 +1323,7 @@
         <v/>
       </c>
       <c r="I8" s="15">
-        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
     </row>
@@ -1331,15 +1339,15 @@
         </is>
       </c>
       <c r="C9" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"TI",Planejado!$C$5:$C$25,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"TI",Planejado!$C$5:$C$29,"Equipe")</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Equipe")</f>
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Equipe")</f>
         <v/>
       </c>
       <c r="F9" s="9">
@@ -1355,7 +1363,7 @@
         <v/>
       </c>
       <c r="I9" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1371,15 +1379,15 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"TI",Planejado!$C$5:$C$25,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"TI",Planejado!$C$5:$C$29,"Despesas")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Despesas")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Despesas")</f>
         <v/>
       </c>
       <c r="F10" s="9">
@@ -1395,7 +1403,7 @@
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"TI",Comparativo!$C$6:$C$26,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1411,15 +1419,15 @@
         </is>
       </c>
       <c r="C11" s="13">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="13">
@@ -1435,7 +1443,7 @@
         <v/>
       </c>
       <c r="I11" s="15">
-        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0",Comparativo!$B$6:$B$26,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$26,"?*",Comparativo!$B$6:$B$26,"TI")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
     </row>
@@ -1447,15 +1455,15 @@
       </c>
       <c r="B12" s="16" t="inlineStr"/>
       <c r="C12" s="17">
-        <f>SUM(Planejado!$T$5:$T$25)</f>
+        <f>SUM(Planejado!$T$5:$T$29)</f>
         <v/>
       </c>
       <c r="D12" s="17">
-        <f>SUM(Comparativo!$I$6:$I$26)</f>
+        <f>SUM(Comparativo!$I$6:$I$30)</f>
         <v/>
       </c>
       <c r="E12" s="17">
-        <f>SUM(Comparativo!$J$6:$J$26)</f>
+        <f>SUM(Comparativo!$J$6:$J$30)</f>
         <v/>
       </c>
       <c r="F12" s="17">
@@ -1471,7 +1479,7 @@
         <v/>
       </c>
       <c r="I12" s="19">
-        <f>COUNTIFS(Comparativo!$P$6:$P$26,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$26)</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$30)</f>
         <v/>
       </c>
     </row>
@@ -1490,7 +1498,7 @@
       </c>
       <c r="B16" s="21" t="n"/>
       <c r="C16" s="22">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$26,"&lt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$30,"&lt;0")</f>
         <v/>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -1512,7 +1520,7 @@
       </c>
       <c r="B17" s="21" t="n"/>
       <c r="C17" s="22">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$26,"&gt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$30,"&gt;0")</f>
         <v/>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -1533,7 +1541,7 @@
       </c>
       <c r="B18" s="24" t="n"/>
       <c r="C18" s="25">
-        <f>-SUM(Comparativo!$Q$6:$Q$26)</f>
+        <f>-SUM(Comparativo!$Q$6:$Q$30)</f>
         <v/>
       </c>
       <c r="D18" s="26" t="inlineStr">
@@ -1555,7 +1563,7 @@
       </c>
       <c r="B19" s="21" t="n"/>
       <c r="C19" s="22">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$26)/Comparativo!$D$3*12,"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$30)/Comparativo!$D$3*12,"")</f>
         <v/>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -1577,7 +1585,7 @@
       </c>
       <c r="B20" s="21" t="n"/>
       <c r="C20" s="27">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$26)/SUM(Comparativo!$S$6:$S$26),"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$30)/SUM(Comparativo!$S$6:$S$30),"")</f>
         <v/>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -1649,23 +1657,23 @@
         <v>1</v>
       </c>
       <c r="B25" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A25),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A25),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="C25" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A25),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A25),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A25),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A25),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A25),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A25),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A25),Comparativo!$R$6:$R$26,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A25),Comparativo!$R$6:$R$30,0)),""),"")</f>
         <v/>
       </c>
       <c r="G25" s="34">
@@ -1678,23 +1686,23 @@
         <v>2</v>
       </c>
       <c r="B26" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A26),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A26),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="C26" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A26),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A26),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A26),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A26),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A26),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A26),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="F26" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A26),Comparativo!$R$6:$R$26,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A26),Comparativo!$R$6:$R$30,0)),""),"")</f>
         <v/>
       </c>
       <c r="G26" s="34">
@@ -1707,23 +1715,23 @@
         <v>3</v>
       </c>
       <c r="B27" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A27),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A27),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="C27" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A27),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A27),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A27),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A27),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A27),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A27),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="F27" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A27),Comparativo!$R$6:$R$26,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A27),Comparativo!$R$6:$R$30,0)),""),"")</f>
         <v/>
       </c>
       <c r="G27" s="34">
@@ -1736,23 +1744,23 @@
         <v>4</v>
       </c>
       <c r="B28" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A28),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A28),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="C28" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A28),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A28),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A28),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A28),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A28),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A28),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="F28" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A28),Comparativo!$R$6:$R$26,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A28),Comparativo!$R$6:$R$30,0)),""),"")</f>
         <v/>
       </c>
       <c r="G28" s="34">
@@ -1765,23 +1773,23 @@
         <v>5</v>
       </c>
       <c r="B29" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A29),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A29),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="C29" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A29),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A29),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A29),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A29),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A29),Comparativo!$R$6:$R$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A29),Comparativo!$R$6:$R$30,0)),"")</f>
         <v/>
       </c>
       <c r="F29" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$R$6:$R$26,A29),Comparativo!$R$6:$R$26,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A29),Comparativo!$R$6:$R$30,0)),""),"")</f>
         <v/>
       </c>
       <c r="G29" s="34">
@@ -1839,23 +1847,23 @@
         <v>1</v>
       </c>
       <c r="B34" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A34),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A34),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="C34" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A34),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A34),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A34),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A34),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A34),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A34),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="F34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A34),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A34),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="G34" s="34">
@@ -1868,23 +1876,23 @@
         <v>2</v>
       </c>
       <c r="B35" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A35),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A35),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="C35" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A35),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A35),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A35),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A35),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A35),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A35),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="F35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A35),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A35),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="G35" s="34">
@@ -1897,23 +1905,23 @@
         <v>3</v>
       </c>
       <c r="B36" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A36),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A36),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="C36" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A36),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A36),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A36),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A36),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A36),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A36),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="F36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A36),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A36),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="G36" s="34">
@@ -1926,23 +1934,23 @@
         <v>4</v>
       </c>
       <c r="B37" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A37),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A37),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="C37" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A37),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A37),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A37),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A37),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A37),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A37),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="F37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A37),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A37),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="G37" s="34">
@@ -1955,23 +1963,23 @@
         <v>5</v>
       </c>
       <c r="B38" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A38),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A38),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="C38" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A38),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A38),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A38),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A38),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A38),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A38),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="F38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$26,MATCH(LARGE(Comparativo!$O$6:$O$26,A38),Comparativo!$O$6:$O$26,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A38),Comparativo!$O$6:$O$30,0)),"")</f>
         <v/>
       </c>
       <c r="G38" s="34">
@@ -2009,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3801,57 +3809,369 @@
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="47">
+        <f>Planejado!A26</f>
+        <v/>
+      </c>
+      <c r="B27" s="47">
+        <f>Planejado!B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="47">
+        <f>Planejado!C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="48">
+        <f>Planejado!D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="47">
+        <f>Planejado!G26</f>
+        <v/>
+      </c>
+      <c r="F27" s="49">
+        <f>INDEX(Planejado!$H26:$S26,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G27" s="49">
+        <f>INDEX(Realizado!$H26:$S26,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H27" s="49">
+        <f>G27-F27</f>
+        <v/>
+      </c>
+      <c r="I27" s="49">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H26:$S26)</f>
+        <v/>
+      </c>
+      <c r="J27" s="49">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H26:$S26)</f>
+        <v/>
+      </c>
+      <c r="K27" s="49">
+        <f>J27-I27</f>
+        <v/>
+      </c>
+      <c r="L27" s="50">
+        <f>IFERROR(K27/I27,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="50">
+        <f>IFERROR(J27/I27,"")</f>
+        <v/>
+      </c>
+      <c r="N27" s="51">
+        <f>IF(P27=0,"Sem lançamento",IF(AND(I27=0,J27=0),"—",IF(I27=0,"Não orçado",IF(K27&gt;0.05*I27,"Acima do orçado",IF(K27&lt;-0.05*I27,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O27" s="39">
+        <f>IF(K27&gt;1,K27+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P27" s="52">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H26:$S26&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q27" s="46">
+        <f>IF(P27=0,"",K27)</f>
+        <v/>
+      </c>
+      <c r="R27" s="46">
+        <f>IF(AND(Q27&lt;&gt;"",Q27&lt;-1),-Q27+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S27" s="46">
+        <f>IF(Q27="","",I27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="47">
+        <f>Planejado!A27</f>
+        <v/>
+      </c>
+      <c r="B28" s="47">
+        <f>Planejado!B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="47">
+        <f>Planejado!C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="48">
+        <f>Planejado!D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="47">
+        <f>Planejado!G27</f>
+        <v/>
+      </c>
+      <c r="F28" s="49">
+        <f>INDEX(Planejado!$H27:$S27,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G28" s="49">
+        <f>INDEX(Realizado!$H27:$S27,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H28" s="49">
+        <f>G28-F28</f>
+        <v/>
+      </c>
+      <c r="I28" s="49">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H27:$S27)</f>
+        <v/>
+      </c>
+      <c r="J28" s="49">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H27:$S27)</f>
+        <v/>
+      </c>
+      <c r="K28" s="49">
+        <f>J28-I28</f>
+        <v/>
+      </c>
+      <c r="L28" s="50">
+        <f>IFERROR(K28/I28,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="50">
+        <f>IFERROR(J28/I28,"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="51">
+        <f>IF(P28=0,"Sem lançamento",IF(AND(I28=0,J28=0),"—",IF(I28=0,"Não orçado",IF(K28&gt;0.05*I28,"Acima do orçado",IF(K28&lt;-0.05*I28,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O28" s="39">
+        <f>IF(K28&gt;1,K28+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P28" s="52">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H27:$S27&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q28" s="46">
+        <f>IF(P28=0,"",K28)</f>
+        <v/>
+      </c>
+      <c r="R28" s="46">
+        <f>IF(AND(Q28&lt;&gt;"",Q28&lt;-1),-Q28+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S28" s="46">
+        <f>IF(Q28="","",I28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="47">
+        <f>Planejado!A28</f>
+        <v/>
+      </c>
+      <c r="B29" s="47">
+        <f>Planejado!B28</f>
+        <v/>
+      </c>
+      <c r="C29" s="47">
+        <f>Planejado!C28</f>
+        <v/>
+      </c>
+      <c r="D29" s="48">
+        <f>Planejado!D28</f>
+        <v/>
+      </c>
+      <c r="E29" s="47">
+        <f>Planejado!G28</f>
+        <v/>
+      </c>
+      <c r="F29" s="49">
+        <f>INDEX(Planejado!$H28:$S28,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G29" s="49">
+        <f>INDEX(Realizado!$H28:$S28,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H29" s="49">
+        <f>G29-F29</f>
+        <v/>
+      </c>
+      <c r="I29" s="49">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H28:$S28)</f>
+        <v/>
+      </c>
+      <c r="J29" s="49">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H28:$S28)</f>
+        <v/>
+      </c>
+      <c r="K29" s="49">
+        <f>J29-I29</f>
+        <v/>
+      </c>
+      <c r="L29" s="50">
+        <f>IFERROR(K29/I29,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="50">
+        <f>IFERROR(J29/I29,"")</f>
+        <v/>
+      </c>
+      <c r="N29" s="51">
+        <f>IF(P29=0,"Sem lançamento",IF(AND(I29=0,J29=0),"—",IF(I29=0,"Não orçado",IF(K29&gt;0.05*I29,"Acima do orçado",IF(K29&lt;-0.05*I29,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O29" s="39">
+        <f>IF(K29&gt;1,K29+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P29" s="52">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H28:$S28&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q29" s="46">
+        <f>IF(P29=0,"",K29)</f>
+        <v/>
+      </c>
+      <c r="R29" s="46">
+        <f>IF(AND(Q29&lt;&gt;"",Q29&lt;-1),-Q29+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S29" s="46">
+        <f>IF(Q29="","",I29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="47">
+        <f>Planejado!A29</f>
+        <v/>
+      </c>
+      <c r="B30" s="47">
+        <f>Planejado!B29</f>
+        <v/>
+      </c>
+      <c r="C30" s="47">
+        <f>Planejado!C29</f>
+        <v/>
+      </c>
+      <c r="D30" s="48">
+        <f>Planejado!D29</f>
+        <v/>
+      </c>
+      <c r="E30" s="47">
+        <f>Planejado!G29</f>
+        <v/>
+      </c>
+      <c r="F30" s="49">
+        <f>INDEX(Planejado!$H29:$S29,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G30" s="49">
+        <f>INDEX(Realizado!$H29:$S29,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H30" s="49">
+        <f>G30-F30</f>
+        <v/>
+      </c>
+      <c r="I30" s="49">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H29:$S29)</f>
+        <v/>
+      </c>
+      <c r="J30" s="49">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H29:$S29)</f>
+        <v/>
+      </c>
+      <c r="K30" s="49">
+        <f>J30-I30</f>
+        <v/>
+      </c>
+      <c r="L30" s="50">
+        <f>IFERROR(K30/I30,"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="50">
+        <f>IFERROR(J30/I30,"")</f>
+        <v/>
+      </c>
+      <c r="N30" s="51">
+        <f>IF(P30=0,"Sem lançamento",IF(AND(I30=0,J30=0),"—",IF(I30=0,"Não orçado",IF(K30&gt;0.05*I30,"Acima do orçado",IF(K30&lt;-0.05*I30,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O30" s="39">
+        <f>IF(K30&gt;1,K30+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P30" s="52">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H29:$S29&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q30" s="46">
+        <f>IF(P30=0,"",K30)</f>
+        <v/>
+      </c>
+      <c r="R30" s="46">
+        <f>IF(AND(Q30&lt;&gt;"",Q30&lt;-1),-Q30+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S30" s="46">
+        <f>IF(Q30="","",I30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="17">
-        <f>SUM(F6:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="17">
-        <f>SUM(G6:G26)</f>
-        <v/>
-      </c>
-      <c r="H27" s="17">
-        <f>SUM(H6:H26)</f>
-        <v/>
-      </c>
-      <c r="I27" s="17">
-        <f>SUM(I6:I26)</f>
-        <v/>
-      </c>
-      <c r="J27" s="17">
-        <f>SUM(J6:J26)</f>
-        <v/>
-      </c>
-      <c r="K27" s="17">
-        <f>SUM(K6:K26)</f>
-        <v/>
-      </c>
-      <c r="L27" s="53">
-        <f>IFERROR(K27/I27,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="53">
-        <f>IFERROR(J27/I27,"")</f>
-        <v/>
-      </c>
-      <c r="N27" s="16" t="n"/>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="17">
+        <f>SUM(F6:F30)</f>
+        <v/>
+      </c>
+      <c r="G31" s="17">
+        <f>SUM(G6:G30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="17">
+        <f>SUM(H6:H30)</f>
+        <v/>
+      </c>
+      <c r="I31" s="17">
+        <f>SUM(I6:I30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="17">
+        <f>SUM(J6:J30)</f>
+        <v/>
+      </c>
+      <c r="K31" s="17">
+        <f>SUM(K6:K30)</f>
+        <v/>
+      </c>
+      <c r="L31" s="53">
+        <f>IFERROR(K31/I31,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="53">
+        <f>IFERROR(J31/I31,"")</f>
+        <v/>
+      </c>
+      <c r="N31" s="16" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N26"/>
+  <autoFilter ref="A5:N30"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H26">
+  <conditionalFormatting sqref="H6:H30">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3859,7 +4179,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K26">
+  <conditionalFormatting sqref="K6:K30">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3882,7 +4202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4348,7 +4668,11 @@
           <t>JUSBRASIL</t>
         </is>
       </c>
-      <c r="E9" s="41" t="inlineStr"/>
+      <c r="E9" s="41" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 104,90/mês, custo real R$ 136,00/mês. Corrigir na revisão orçamentária</t>
+        </is>
+      </c>
       <c r="F9" s="40" t="inlineStr"/>
       <c r="G9" s="40" t="inlineStr">
         <is>
@@ -4419,7 +4743,7 @@
       </c>
       <c r="E10" s="41" t="inlineStr">
         <is>
-          <t>Cancelado — realizado zerado desde mai/26</t>
+          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 112,07/mês, custo real R$ 346,00/mês. Corrigir na revisão orçamentária</t>
         </is>
       </c>
       <c r="F10" s="40" t="inlineStr"/>
@@ -5490,7 +5814,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="47" t="inlineStr">
         <is>
-          <t>TI-D09</t>
+          <t>TI-D10</t>
         </is>
       </c>
       <c r="B25" s="47" t="inlineStr">
@@ -5505,18 +5829,18 @@
       </c>
       <c r="D25" s="48" t="inlineStr">
         <is>
-          <t>Bonificação do time</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="E25" s="48" t="inlineStr">
         <is>
-          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria</t>
         </is>
       </c>
       <c r="F25" s="47" t="inlineStr"/>
       <c r="G25" s="47" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H25" s="49" t="n">
@@ -5541,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="49" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="P25" s="49" t="n">
         <v>0</v>
@@ -5553,80 +5877,372 @@
         <v>0</v>
       </c>
       <c r="S25" s="49" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="T25" s="54">
         <f>SUM(H25:S25)</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="47" t="inlineStr">
+        <is>
+          <t>TI-D11</t>
+        </is>
+      </c>
+      <c r="B26" s="47" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C26" s="47" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D26" s="48" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="E26" s="48" t="inlineStr">
+        <is>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria</t>
+        </is>
+      </c>
+      <c r="F26" s="47" t="inlineStr"/>
+      <c r="G26" s="47" t="inlineStr">
+        <is>
+          <t>Licenças de Softwares</t>
+        </is>
+      </c>
+      <c r="H26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="54">
+        <f>SUM(H26:S26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="47" t="inlineStr">
+        <is>
+          <t>TI-D12</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D27" s="48" t="inlineStr">
+        <is>
+          <t>Adapta One</t>
+        </is>
+      </c>
+      <c r="E27" s="48" t="inlineStr">
+        <is>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
+        </is>
+      </c>
+      <c r="F27" s="47" t="inlineStr"/>
+      <c r="G27" s="47" t="inlineStr">
+        <is>
+          <t>Licenças de Softwares</t>
+        </is>
+      </c>
+      <c r="H27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="54">
+        <f>SUM(H27:S27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="47" t="inlineStr">
+        <is>
+          <t>TI-D13</t>
+        </is>
+      </c>
+      <c r="B28" s="47" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C28" s="47" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D28" s="48" t="inlineStr">
+        <is>
+          <t>Adapta Skip</t>
+        </is>
+      </c>
+      <c r="E28" s="48" t="inlineStr">
+        <is>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
+        </is>
+      </c>
+      <c r="F28" s="47" t="inlineStr"/>
+      <c r="G28" s="47" t="inlineStr">
+        <is>
+          <t>Licenças de Softwares</t>
+        </is>
+      </c>
+      <c r="H28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="54">
+        <f>SUM(H28:S28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="47" t="inlineStr">
+        <is>
+          <t>TI-D09</t>
+        </is>
+      </c>
+      <c r="B29" s="47" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D29" s="48" t="inlineStr">
+        <is>
+          <t>Bonificação do time</t>
+        </is>
+      </c>
+      <c r="E29" s="48" t="inlineStr">
+        <is>
+          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
+      <c r="F29" s="47" t="inlineStr"/>
+      <c r="G29" s="47" t="inlineStr">
+        <is>
+          <t>Prêmios</t>
+        </is>
+      </c>
+      <c r="H29" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="49" t="n">
+        <v>2400</v>
+      </c>
+      <c r="P29" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="49" t="n">
+        <v>3600</v>
+      </c>
+      <c r="T29" s="54">
+        <f>SUM(H29:S29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="17">
-        <f>SUM(H5:H25)</f>
-        <v/>
-      </c>
-      <c r="I26" s="17">
-        <f>SUM(I5:I25)</f>
-        <v/>
-      </c>
-      <c r="J26" s="17">
-        <f>SUM(J5:J25)</f>
-        <v/>
-      </c>
-      <c r="K26" s="17">
-        <f>SUM(K5:K25)</f>
-        <v/>
-      </c>
-      <c r="L26" s="17">
-        <f>SUM(L5:L25)</f>
-        <v/>
-      </c>
-      <c r="M26" s="17">
-        <f>SUM(M5:M25)</f>
-        <v/>
-      </c>
-      <c r="N26" s="17">
-        <f>SUM(N5:N25)</f>
-        <v/>
-      </c>
-      <c r="O26" s="17">
-        <f>SUM(O5:O25)</f>
-        <v/>
-      </c>
-      <c r="P26" s="17">
-        <f>SUM(P5:P25)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="17">
-        <f>SUM(Q5:Q25)</f>
-        <v/>
-      </c>
-      <c r="R26" s="17">
-        <f>SUM(R5:R25)</f>
-        <v/>
-      </c>
-      <c r="S26" s="17">
-        <f>SUM(S5:S25)</f>
-        <v/>
-      </c>
-      <c r="T26" s="17">
-        <f>SUM(T5:T25)</f>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="17">
+        <f>SUM(H5:H29)</f>
+        <v/>
+      </c>
+      <c r="I30" s="17">
+        <f>SUM(I5:I29)</f>
+        <v/>
+      </c>
+      <c r="J30" s="17">
+        <f>SUM(J5:J29)</f>
+        <v/>
+      </c>
+      <c r="K30" s="17">
+        <f>SUM(K5:K29)</f>
+        <v/>
+      </c>
+      <c r="L30" s="17">
+        <f>SUM(L5:L29)</f>
+        <v/>
+      </c>
+      <c r="M30" s="17">
+        <f>SUM(M5:M29)</f>
+        <v/>
+      </c>
+      <c r="N30" s="17">
+        <f>SUM(N5:N29)</f>
+        <v/>
+      </c>
+      <c r="O30" s="17">
+        <f>SUM(O5:O29)</f>
+        <v/>
+      </c>
+      <c r="P30" s="17">
+        <f>SUM(P5:P29)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="17">
+        <f>SUM(Q5:Q29)</f>
+        <v/>
+      </c>
+      <c r="R30" s="17">
+        <f>SUM(R5:R29)</f>
+        <v/>
+      </c>
+      <c r="S30" s="17">
+        <f>SUM(S5:S29)</f>
+        <v/>
+      </c>
+      <c r="T30" s="17">
+        <f>SUM(T5:T29)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T25"/>
+  <autoFilter ref="A4:T29"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
@@ -5641,7 +6257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6122,7 +6738,7 @@
       </c>
       <c r="V9" s="59" t="inlineStr">
         <is>
-          <t>Acima do orçado (R$ 104,90) — conferir contrato</t>
+          <t>R$ 136,00/mês contra R$ 104,90 orçados. Erro no orçamento original</t>
         </is>
       </c>
     </row>
@@ -6156,25 +6772,25 @@
         <v/>
       </c>
       <c r="H10" s="58" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="I10" s="58" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="J10" s="58" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="K10" s="58" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="L10" s="58" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="M10" s="58" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="N10" s="58" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="O10" s="58" t="n"/>
       <c r="T10" s="54">
@@ -6188,7 +6804,7 @@
       </c>
       <c r="V10" s="59" t="inlineStr">
         <is>
-          <t>Cancelado — sem cobrança</t>
+          <t>R$ 346,00/mês — 3x o orçado (R$ 112,07). Erro no orçamento original</t>
         </is>
       </c>
     </row>
@@ -6962,72 +7578,248 @@
       <c r="U25" s="59" t="n"/>
       <c r="V25" s="59" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="60" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="56">
+        <f>Planejado!A26</f>
+        <v/>
+      </c>
+      <c r="B26" s="56">
+        <f>Planejado!B26</f>
+        <v/>
+      </c>
+      <c r="C26" s="56">
+        <f>Planejado!C26</f>
+        <v/>
+      </c>
+      <c r="D26" s="57">
+        <f>Planejado!D26</f>
+        <v/>
+      </c>
+      <c r="E26" s="57">
+        <f>Planejado!E26</f>
+        <v/>
+      </c>
+      <c r="F26" s="56">
+        <f>Planejado!F26</f>
+        <v/>
+      </c>
+      <c r="G26" s="56">
+        <f>Planejado!G26</f>
+        <v/>
+      </c>
+      <c r="H26" s="58" t="n"/>
+      <c r="I26" s="58" t="n"/>
+      <c r="J26" s="58" t="n"/>
+      <c r="K26" s="58" t="n"/>
+      <c r="L26" s="58" t="n"/>
+      <c r="M26" s="58" t="n"/>
+      <c r="N26" s="58" t="n"/>
+      <c r="O26" s="58" t="n"/>
+      <c r="T26" s="54">
+        <f>SUM(H26:S26)</f>
+        <v/>
+      </c>
+      <c r="U26" s="59" t="n"/>
+      <c r="V26" s="59" t="n"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="56">
+        <f>Planejado!A27</f>
+        <v/>
+      </c>
+      <c r="B27" s="56">
+        <f>Planejado!B27</f>
+        <v/>
+      </c>
+      <c r="C27" s="56">
+        <f>Planejado!C27</f>
+        <v/>
+      </c>
+      <c r="D27" s="57">
+        <f>Planejado!D27</f>
+        <v/>
+      </c>
+      <c r="E27" s="57">
+        <f>Planejado!E27</f>
+        <v/>
+      </c>
+      <c r="F27" s="56">
+        <f>Planejado!F27</f>
+        <v/>
+      </c>
+      <c r="G27" s="56">
+        <f>Planejado!G27</f>
+        <v/>
+      </c>
+      <c r="H27" s="58" t="n"/>
+      <c r="I27" s="58" t="n"/>
+      <c r="J27" s="58" t="n"/>
+      <c r="K27" s="58" t="n"/>
+      <c r="L27" s="58" t="n"/>
+      <c r="M27" s="58" t="n"/>
+      <c r="N27" s="58" t="n"/>
+      <c r="O27" s="58" t="n"/>
+      <c r="T27" s="54">
+        <f>SUM(H27:S27)</f>
+        <v/>
+      </c>
+      <c r="U27" s="59" t="n"/>
+      <c r="V27" s="59" t="n"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="56">
+        <f>Planejado!A28</f>
+        <v/>
+      </c>
+      <c r="B28" s="56">
+        <f>Planejado!B28</f>
+        <v/>
+      </c>
+      <c r="C28" s="56">
+        <f>Planejado!C28</f>
+        <v/>
+      </c>
+      <c r="D28" s="57">
+        <f>Planejado!D28</f>
+        <v/>
+      </c>
+      <c r="E28" s="57">
+        <f>Planejado!E28</f>
+        <v/>
+      </c>
+      <c r="F28" s="56">
+        <f>Planejado!F28</f>
+        <v/>
+      </c>
+      <c r="G28" s="56">
+        <f>Planejado!G28</f>
+        <v/>
+      </c>
+      <c r="H28" s="58" t="n"/>
+      <c r="I28" s="58" t="n"/>
+      <c r="J28" s="58" t="n"/>
+      <c r="K28" s="58" t="n"/>
+      <c r="L28" s="58" t="n"/>
+      <c r="M28" s="58" t="n"/>
+      <c r="N28" s="58" t="n"/>
+      <c r="O28" s="58" t="n"/>
+      <c r="T28" s="54">
+        <f>SUM(H28:S28)</f>
+        <v/>
+      </c>
+      <c r="U28" s="59" t="n"/>
+      <c r="V28" s="59" t="n"/>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="56">
+        <f>Planejado!A29</f>
+        <v/>
+      </c>
+      <c r="B29" s="56">
+        <f>Planejado!B29</f>
+        <v/>
+      </c>
+      <c r="C29" s="56">
+        <f>Planejado!C29</f>
+        <v/>
+      </c>
+      <c r="D29" s="57">
+        <f>Planejado!D29</f>
+        <v/>
+      </c>
+      <c r="E29" s="57">
+        <f>Planejado!E29</f>
+        <v/>
+      </c>
+      <c r="F29" s="56">
+        <f>Planejado!F29</f>
+        <v/>
+      </c>
+      <c r="G29" s="56">
+        <f>Planejado!G29</f>
+        <v/>
+      </c>
+      <c r="H29" s="58" t="n"/>
+      <c r="I29" s="58" t="n"/>
+      <c r="J29" s="58" t="n"/>
+      <c r="K29" s="58" t="n"/>
+      <c r="L29" s="58" t="n"/>
+      <c r="M29" s="58" t="n"/>
+      <c r="N29" s="58" t="n"/>
+      <c r="O29" s="58" t="n"/>
+      <c r="T29" s="54">
+        <f>SUM(H29:S29)</f>
+        <v/>
+      </c>
+      <c r="U29" s="59" t="n"/>
+      <c r="V29" s="59" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="60" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B26" s="60" t="n"/>
-      <c r="C26" s="60" t="n"/>
-      <c r="D26" s="60" t="n"/>
-      <c r="E26" s="60" t="n"/>
-      <c r="F26" s="60" t="n"/>
-      <c r="G26" s="60" t="n"/>
-      <c r="H26" s="61">
-        <f>SUM(H5:H25)</f>
-        <v/>
-      </c>
-      <c r="I26" s="61">
-        <f>SUM(I5:I25)</f>
-        <v/>
-      </c>
-      <c r="J26" s="61">
-        <f>SUM(J5:J25)</f>
-        <v/>
-      </c>
-      <c r="K26" s="61">
-        <f>SUM(K5:K25)</f>
-        <v/>
-      </c>
-      <c r="L26" s="61">
-        <f>SUM(L5:L25)</f>
-        <v/>
-      </c>
-      <c r="M26" s="61">
-        <f>SUM(M5:M25)</f>
-        <v/>
-      </c>
-      <c r="N26" s="61">
-        <f>SUM(N5:N25)</f>
-        <v/>
-      </c>
-      <c r="O26" s="61">
-        <f>SUM(O5:O25)</f>
-        <v/>
-      </c>
-      <c r="P26" s="61">
-        <f>SUM(P5:P25)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="61">
-        <f>SUM(Q5:Q25)</f>
-        <v/>
-      </c>
-      <c r="R26" s="61">
-        <f>SUM(R5:R25)</f>
-        <v/>
-      </c>
-      <c r="S26" s="61">
-        <f>SUM(S5:S25)</f>
-        <v/>
-      </c>
-      <c r="T26" s="61">
-        <f>SUM(T5:T25)</f>
-        <v/>
-      </c>
-      <c r="U26" s="60" t="n"/>
-      <c r="V26" s="60" t="n"/>
+      <c r="B30" s="60" t="n"/>
+      <c r="C30" s="60" t="n"/>
+      <c r="D30" s="60" t="n"/>
+      <c r="E30" s="60" t="n"/>
+      <c r="F30" s="60" t="n"/>
+      <c r="G30" s="60" t="n"/>
+      <c r="H30" s="61">
+        <f>SUM(H5:H29)</f>
+        <v/>
+      </c>
+      <c r="I30" s="61">
+        <f>SUM(I5:I29)</f>
+        <v/>
+      </c>
+      <c r="J30" s="61">
+        <f>SUM(J5:J29)</f>
+        <v/>
+      </c>
+      <c r="K30" s="61">
+        <f>SUM(K5:K29)</f>
+        <v/>
+      </c>
+      <c r="L30" s="61">
+        <f>SUM(L5:L29)</f>
+        <v/>
+      </c>
+      <c r="M30" s="61">
+        <f>SUM(M5:M29)</f>
+        <v/>
+      </c>
+      <c r="N30" s="61">
+        <f>SUM(N5:N29)</f>
+        <v/>
+      </c>
+      <c r="O30" s="61">
+        <f>SUM(O5:O29)</f>
+        <v/>
+      </c>
+      <c r="P30" s="61">
+        <f>SUM(P5:P29)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="61">
+        <f>SUM(Q5:Q29)</f>
+        <v/>
+      </c>
+      <c r="R30" s="61">
+        <f>SUM(R5:R29)</f>
+        <v/>
+      </c>
+      <c r="S30" s="61">
+        <f>SUM(S5:S29)</f>
+        <v/>
+      </c>
+      <c r="T30" s="61">
+        <f>SUM(T5:T29)</f>
+        <v/>
+      </c>
+      <c r="U30" s="60" t="n"/>
+      <c r="V30" s="60" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7132,19 +7924,19 @@
         </is>
       </c>
       <c r="B5" s="42">
-        <f>SUMIFS(Planejado!$H$5:$H$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="42">
-        <f>SUMIFS(Realizado!$H$5:$H$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="42">
-        <f>SUMIFS(Planejado!$H$5:$H$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="42">
-        <f>SUMIFS(Realizado!$H$5:$H$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="42">
@@ -7175,19 +7967,19 @@
         </is>
       </c>
       <c r="B6" s="49">
-        <f>SUMIFS(Planejado!$I$5:$I$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="49">
-        <f>SUMIFS(Realizado!$I$5:$I$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="49">
-        <f>SUMIFS(Planejado!$I$5:$I$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="49">
-        <f>SUMIFS(Realizado!$I$5:$I$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="49">
@@ -7218,19 +8010,19 @@
         </is>
       </c>
       <c r="B7" s="42">
-        <f>SUMIFS(Planejado!$J$5:$J$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="42">
-        <f>SUMIFS(Realizado!$J$5:$J$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="42">
-        <f>SUMIFS(Planejado!$J$5:$J$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="42">
-        <f>SUMIFS(Realizado!$J$5:$J$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="42">
@@ -7261,19 +8053,19 @@
         </is>
       </c>
       <c r="B8" s="49">
-        <f>SUMIFS(Planejado!$K$5:$K$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="49">
-        <f>SUMIFS(Realizado!$K$5:$K$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="49">
-        <f>SUMIFS(Planejado!$K$5:$K$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="49">
-        <f>SUMIFS(Realizado!$K$5:$K$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="49">
@@ -7304,19 +8096,19 @@
         </is>
       </c>
       <c r="B9" s="42">
-        <f>SUMIFS(Planejado!$L$5:$L$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="42">
-        <f>SUMIFS(Realizado!$L$5:$L$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="42">
-        <f>SUMIFS(Planejado!$L$5:$L$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="42">
-        <f>SUMIFS(Realizado!$L$5:$L$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="42">
@@ -7347,19 +8139,19 @@
         </is>
       </c>
       <c r="B10" s="49">
-        <f>SUMIFS(Planejado!$M$5:$M$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="49">
-        <f>SUMIFS(Realizado!$M$5:$M$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="49">
-        <f>SUMIFS(Planejado!$M$5:$M$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="49">
-        <f>SUMIFS(Realizado!$M$5:$M$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="49">
@@ -7390,19 +8182,19 @@
         </is>
       </c>
       <c r="B11" s="42">
-        <f>SUMIFS(Planejado!$N$5:$N$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="42">
-        <f>SUMIFS(Realizado!$N$5:$N$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="42">
-        <f>SUMIFS(Planejado!$N$5:$N$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="42">
-        <f>SUMIFS(Realizado!$N$5:$N$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="42">
@@ -7433,19 +8225,19 @@
         </is>
       </c>
       <c r="B12" s="49">
-        <f>SUMIFS(Planejado!$O$5:$O$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C12" s="49">
-        <f>SUMIFS(Realizado!$O$5:$O$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D12" s="49">
-        <f>SUMIFS(Planejado!$O$5:$O$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E12" s="49">
-        <f>SUMIFS(Realizado!$O$5:$O$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F12" s="49">
@@ -7476,19 +8268,19 @@
         </is>
       </c>
       <c r="B13" s="42">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C13" s="42">
-        <f>SUMIFS(Realizado!$P$5:$P$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D13" s="42">
-        <f>SUMIFS(Planejado!$P$5:$P$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E13" s="42">
-        <f>SUMIFS(Realizado!$P$5:$P$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F13" s="42">
@@ -7519,19 +8311,19 @@
         </is>
       </c>
       <c r="B14" s="49">
-        <f>SUMIFS(Planejado!$Q$5:$Q$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C14" s="49">
-        <f>SUMIFS(Realizado!$Q$5:$Q$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D14" s="49">
-        <f>SUMIFS(Planejado!$Q$5:$Q$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E14" s="49">
-        <f>SUMIFS(Realizado!$Q$5:$Q$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F14" s="49">
@@ -7562,19 +8354,19 @@
         </is>
       </c>
       <c r="B15" s="42">
-        <f>SUMIFS(Planejado!$R$5:$R$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C15" s="42">
-        <f>SUMIFS(Realizado!$R$5:$R$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D15" s="42">
-        <f>SUMIFS(Planejado!$R$5:$R$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E15" s="42">
-        <f>SUMIFS(Realizado!$R$5:$R$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F15" s="42">
@@ -7605,19 +8397,19 @@
         </is>
       </c>
       <c r="B16" s="49">
-        <f>SUMIFS(Planejado!$S$5:$S$25,Planejado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$29,Planejado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="C16" s="49">
-        <f>SUMIFS(Realizado!$S$5:$S$25,Realizado!$B$5:$B$25,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$29,Realizado!$B$5:$B$29,"Jurídico")</f>
         <v/>
       </c>
       <c r="D16" s="49">
-        <f>SUMIFS(Planejado!$S$5:$S$25,Planejado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$29,Planejado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="E16" s="49">
-        <f>SUMIFS(Realizado!$S$5:$S$25,Realizado!$B$5:$B$25,"TI")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$29,Realizado!$B$5:$B$29,"TI")</f>
         <v/>
       </c>
       <c r="F16" s="49">
@@ -7790,19 +8582,19 @@
         </is>
       </c>
       <c r="B5" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A5,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A5,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A5,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A5,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A5,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="42">
@@ -7822,7 +8614,7 @@
         <v/>
       </c>
       <c r="J5" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A5)</f>
         <v/>
       </c>
     </row>
@@ -7833,19 +8625,19 @@
         </is>
       </c>
       <c r="B6" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A6,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A6,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A6,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A6,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A6,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="49">
@@ -7865,7 +8657,7 @@
         <v/>
       </c>
       <c r="J6" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A6)</f>
         <v/>
       </c>
     </row>
@@ -7876,19 +8668,19 @@
         </is>
       </c>
       <c r="B7" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A7,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A7,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A7,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A7,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A7,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="42">
@@ -7908,7 +8700,7 @@
         <v/>
       </c>
       <c r="J7" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A7)</f>
         <v/>
       </c>
     </row>
@@ -7919,19 +8711,19 @@
         </is>
       </c>
       <c r="B8" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A8,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A8,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A8,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A8,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A8,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="49">
@@ -7951,7 +8743,7 @@
         <v/>
       </c>
       <c r="J8" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A8)</f>
         <v/>
       </c>
     </row>
@@ -7962,19 +8754,19 @@
         </is>
       </c>
       <c r="B9" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A9,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A9,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A9,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A9,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A9,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="42">
@@ -7994,7 +8786,7 @@
         <v/>
       </c>
       <c r="J9" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A9)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A9)</f>
         <v/>
       </c>
     </row>
@@ -8005,19 +8797,19 @@
         </is>
       </c>
       <c r="B10" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A10,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A10,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A10,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A10,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A10,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="49">
@@ -8037,7 +8829,7 @@
         <v/>
       </c>
       <c r="J10" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A10)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A10)</f>
         <v/>
       </c>
     </row>
@@ -8048,19 +8840,19 @@
         </is>
       </c>
       <c r="B11" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A11,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A11,Comparativo!$B$6:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A11,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$26,Comparativo!$E$6:$E$26,$A11,Comparativo!$B$6:$B$26,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A11,Comparativo!$B$6:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="42">
@@ -8080,7 +8872,7 @@
         <v/>
       </c>
       <c r="J11" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$25,Planejado!$G$5:$G$25,$A11)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A11)</f>
         <v/>
       </c>
     </row>
@@ -8150,7 +8942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8604,12 +9396,12 @@
       </c>
       <c r="C17" s="69" t="inlineStr">
         <is>
-          <t>O risco era pagar os dois em paralelo. O realizado de mai–jul mostra Astrea em R$ 0 (cancelado) e Jusfy em R$ 0 (ainda não iniciado) — no momento não há custo de nenhum dos dois.</t>
+          <t>O Astrea NÃO foi cancelado: custa R$ 346,00/mês e segue ativo. O Jusfy está em R$ 0 — ainda não iniciado. A informação anterior de que o Astrea estava zerado foi corrigida pela gestora.</t>
         </is>
       </c>
       <c r="D17" s="69" t="inlineStr">
         <is>
-          <t>Economia de R$ 212,07/mês enquanto durar. Falta decidir se o Jusfy entra e quando, para ajustar o planejado dos meses seguintes.</t>
+          <t>O Astrea sozinho consome R$ 4.152/ano. Se o Jusfy entrar e o objetivo era substituí-lo, essa é a economia em jogo — e ela é maior do que parecia, porque o custo real do Astrea é 3x o que estava orçado.</t>
         </is>
       </c>
       <c r="E17" s="69" t="inlineStr">
@@ -8617,100 +9409,100 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F17" s="73" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
+      <c r="F17" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B18" s="72" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos de TI</t>
+          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
         </is>
       </c>
       <c r="C18" s="72" t="inlineStr">
         <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
+          <t>Os dois valores já chegaram errados na ficha de orçamento que a gestora recebeu. Astrea: orçado R$ 112,07/mês, custo real R$ 346,00 (3,1x). Jusbrasil: orçado R$ 104,90/mês, custo real R$ 136,00 (1,3x). PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
         </is>
       </c>
       <c r="D18" s="72" t="inlineStr">
         <is>
-          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
+          <t>O planejado dessas duas linhas foi mantido como está na ficha, para o erro ficar visível no comparativo. Subdimensionamento de R$ 3.180,36 no ano (R$ 2.807,16 do Astrea + R$ 373,20 do Jusbrasil). Não é estouro de gestão: é erro na origem do orçamento, e precisa de correção formal.</t>
         </is>
       </c>
       <c r="E18" s="72" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
-        </is>
-      </c>
-      <c r="F18" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F18" s="76" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B19" s="69" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Ferramentas de IA sem orçamento — DEFINIR META</t>
         </is>
       </c>
       <c r="C19" s="69" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>Claude, GPT, Adapta One e Adapta Skip são gastos que existem hoje e não constavam na ficha. Foram criadas quatro linhas separadas, com planejado zerado, para a meta ser definida junto com a diretoria.</t>
         </is>
       </c>
       <c r="D19" s="69" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>Enquanto o planejado for zero, qualquer lançamento nessas linhas aparece como 'Não orçado'. Conferir também se há sobreposição com a linha 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano — pode ser que ela já cubra o Adapta One e o Adapta Skip. E confirmar o nome exato do 'Adapta Skip'.</t>
         </is>
       </c>
       <c r="E19" s="69" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F19" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F19" s="76" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B20" s="72" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Rateio dos softwares corporativos de TI</t>
         </is>
       </c>
       <c r="C20" s="72" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
         </is>
       </c>
       <c r="D20" s="72" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
         </is>
       </c>
       <c r="E20" s="72" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Controladoria</t>
         </is>
       </c>
       <c r="F20" s="74" t="inlineStr">
@@ -8722,30 +9514,94 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="68" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="69" t="inlineStr">
+        <is>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
+        </is>
+      </c>
+      <c r="C21" s="69" t="inlineStr">
+        <is>
+          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+        </is>
+      </c>
+      <c r="D21" s="69" t="inlineStr">
+        <is>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+        </is>
+      </c>
+      <c r="E21" s="69" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F21" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="72" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C22" s="72" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D22" s="72" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E22" s="72" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F22" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="68" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B21" s="69" t="inlineStr">
+      <c r="B23" s="69" t="inlineStr">
         <is>
           <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
         </is>
       </c>
-      <c r="C21" s="69" t="inlineStr">
+      <c r="C23" s="69" t="inlineStr">
         <is>
           <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
         </is>
       </c>
-      <c r="D21" s="69" t="inlineStr">
+      <c r="D23" s="69" t="inlineStr">
         <is>
           <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Vale conferir quais contratos pagam no mês seguinte e decidir se o comparativo passa para competência.</t>
         </is>
       </c>
-      <c r="E21" s="69" t="inlineStr">
+      <c r="E23" s="69" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F21" s="75" t="inlineStr">
+      <c r="F23" s="75" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>
@@ -8796,60 +9652,60 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="76" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="77" t="inlineStr">
+      <c r="B5" s="78" t="inlineStr">
         <is>
           <t>Abra a aba REALIZADO e preencha apenas as células amarelas do mês que fechou. Se o item não teve gasto no mês, digite 0 — deixar em branco significa 'ainda não lancei'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="76" t="inlineStr">
+      <c r="A6" s="77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="77" t="inlineStr">
+      <c r="B6" s="78" t="inlineStr">
         <is>
           <t>Preencha a coluna 'Fonte do dado' (ex.: relatório do financeiro, nota fiscal, extrato do cartão) para o número ser auditável depois.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="76" t="inlineStr">
+      <c r="A7" s="77" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="77" t="inlineStr">
+      <c r="B7" s="78" t="inlineStr">
         <is>
           <t>Vá na aba COMPARATIVO e selecione o mês em B3. Todas as demais abas acompanham essa escolha.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="76" t="inlineStr">
+      <c r="A8" s="77" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="77" t="inlineStr">
+      <c r="B8" s="78" t="inlineStr">
         <is>
           <t>Confira o PAINEL: ele mostra o desvio por departamento e os 5 maiores estouros do acumulado. É a tela para levar à diretoria.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="76" t="inlineStr">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="77" t="inlineStr">
+      <c r="B9" s="78" t="inlineStr">
         <is>
           <t>Atualize a aba PENDÊNCIAS conforme as decisões forem sendo tomadas.</t>
         </is>
@@ -8864,60 +9720,60 @@
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="76" t="inlineStr">
+      <c r="A12" s="77" t="inlineStr">
         <is>
           <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
-      <c r="B12" s="77" t="inlineStr">
+      <c r="B12" s="78" t="inlineStr">
         <is>
           <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="76" t="inlineStr">
+      <c r="A13" s="77" t="inlineStr">
         <is>
           <t>Desvio negativo (verde)</t>
         </is>
       </c>
-      <c r="B13" s="77" t="inlineStr">
+      <c r="B13" s="78" t="inlineStr">
         <is>
           <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="76" t="inlineStr">
+      <c r="A14" s="77" t="inlineStr">
         <is>
           <t>Planejado acum.</t>
         </is>
       </c>
-      <c r="B14" s="77" t="inlineStr">
+      <c r="B14" s="78" t="inlineStr">
         <is>
           <t>Soma de maio até o mês selecionado.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="76" t="inlineStr">
+      <c r="A15" s="77" t="inlineStr">
         <is>
           <t>% Executado</t>
         </is>
       </c>
-      <c r="B15" s="77" t="inlineStr">
+      <c r="B15" s="78" t="inlineStr">
         <is>
           <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="76" t="inlineStr">
+      <c r="A16" s="77" t="inlineStr">
         <is>
           <t>Sem lançamento</t>
         </is>
       </c>
-      <c r="B16" s="77" t="inlineStr">
+      <c r="B16" s="78" t="inlineStr">
         <is>
           <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
         </is>
@@ -8932,36 +9788,36 @@
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="76" t="inlineStr">
+      <c r="A19" s="77" t="inlineStr">
         <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="77" t="inlineStr">
+      <c r="B19" s="78" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="76" t="inlineStr">
+      <c r="A20" s="77" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="77" t="inlineStr">
+      <c r="B20" s="78" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="77" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="77" t="inlineStr">
+      <c r="B21" s="78" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -224,7 +224,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
     <fill>
@@ -234,7 +234,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -23619,25 +23619,25 @@
         <v/>
       </c>
       <c r="H10" s="58" t="n">
-        <v>346</v>
+        <v>1346.28</v>
       </c>
       <c r="I10" s="58" t="n">
-        <v>346</v>
+        <v>5385.12</v>
       </c>
       <c r="J10" s="58" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="K10" s="58" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="L10" s="58" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="M10" s="58" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="N10" s="58" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="O10" s="58" t="n"/>
       <c r="T10" s="54">
@@ -23646,12 +23646,12 @@
       </c>
       <c r="U10" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Extrato do financeiro</t>
         </is>
       </c>
       <c r="V10" s="59" t="inlineStr">
         <is>
-          <t>R$ 346,00/mês — 3x o orçado (R$ 112,07). Erro no orçamento original</t>
+          <t>Anuidade 2026 = R$ 6.731,40 em 5x de R$ 1.346,28, quitada em fev (competência até abr). Sem cobrança de mar em diante</t>
         </is>
       </c>
     </row>
@@ -25789,7 +25789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -26078,7 +26078,7 @@
       </c>
       <c r="B12" s="72" t="inlineStr">
         <is>
-          <t>Planejado de jan a abr — CONFERIR</t>
+          <t>Planejado de jan a abr — conferido</t>
         </is>
       </c>
       <c r="C12" s="72" t="inlineStr">
@@ -26088,7 +26088,7 @@
       </c>
       <c r="D12" s="72" t="inlineStr">
         <is>
-          <t>Se algum contrato tinha valor diferente no 1º quadrimestre, ou se houve bonificação nesse período, o planejado de jan a abr precisa ser corrigido antes de comparar com o realizado.</t>
+          <t>Conferido e validado pela gestora: os valores replicados estão corretos, nenhum ajuste necessário.</t>
         </is>
       </c>
       <c r="E12" s="72" t="inlineStr">
@@ -26096,9 +26096,9 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
-        <is>
-          <t>CONFERIR</t>
+      <c r="F12" s="73" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
@@ -26128,9 +26128,9 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F13" s="76" t="inlineStr">
-        <is>
-          <t>EM ANDAMENTO</t>
+      <c r="F13" s="73" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
@@ -26160,7 +26160,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F14" s="77" t="inlineStr">
+      <c r="F14" s="75" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -26270,17 +26270,17 @@
       </c>
       <c r="B18" s="72" t="inlineStr">
         <is>
-          <t>Jusfy x Astrea</t>
+          <t>Jusfy — nunca iniciado</t>
         </is>
       </c>
       <c r="C18" s="72" t="inlineStr">
         <is>
-          <t>O Astrea NÃO foi cancelado: custa R$ 346,00/mês e segue ativo. O Jusfy está em R$ 0 — ainda não iniciado. A informação anterior de que o Astrea estava zerado foi corrigida pela gestora.</t>
+          <t>O Jusfy entrou na ficha porque o orçamento foi montado em nov/dez de 2025, durante a fase de experimento. Em janeiro a decisão foi cancelar, e o serviço nunca chegou a ser iniciado. Custo zero o ano todo.</t>
         </is>
       </c>
       <c r="D18" s="72" t="inlineStr">
         <is>
-          <t>O Astrea sozinho consome R$ 4.152/ano. Se o Jusfy entrar e o objetivo era substituí-lo, essa é a economia em jogo — e ela é maior do que parecia, porque o custo real do Astrea é 3x o que estava orçado.</t>
+          <t>Os R$ 1.200 orçados no ano nunca serão usados. Não é economia de gestão: é item que já nasceu fora do escopo e deve sair na revisão do orçamento.</t>
         </is>
       </c>
       <c r="E18" s="72" t="inlineStr">
@@ -26288,63 +26288,63 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F18" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F18" s="73" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="68" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B19" s="69" t="inlineStr">
         <is>
-          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
+          <t>Astrea — anuidade quitada e cancelamento em curso</t>
         </is>
       </c>
       <c r="C19" s="69" t="inlineStr">
         <is>
-          <t>Os dois valores já chegaram errados na ficha de orçamento que a gestora recebeu. Astrea: orçado R$ 112,07/mês, custo real R$ 346,00 (3,1x). Jusbrasil: orçado R$ 104,90/mês, custo real R$ 136,00 (1,3x). PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
+          <t>A anuidade 2026 custou R$ 6.731,40, parcelada em 5x de R$ 1.346,28. Pelo extrato, uma parcela foi paga em jan e as outras quatro em fev (incluindo R$ 4.038,84 de antecipação); por competência as parcelas vão até abr/26. Não há e não haverá cobrança de mar em diante. O cancelamento formal foi solicitado em ago/26 e aguarda confirmação por e-mail do fornecedor.</t>
         </is>
       </c>
       <c r="D19" s="69" t="inlineStr">
         <is>
-          <t>O planejado dessas duas linhas foi mantido como está na ficha, para o erro ficar visível no comparativo. Subdimensionamento de R$ 3.180,36 no ano (R$ 2.807,16 do Astrea + R$ 373,20 do Jusbrasil). Não é estouro de gestão: é erro na origem do orçamento, e precisa de correção formal.</t>
+          <t>O realizado das linhas de mar a dez é zero de fato, não falta de lançamento. Guardar a confirmação por e-mail do cancelamento para não haver renovação automática da anuidade 2027.</t>
         </is>
       </c>
       <c r="E19" s="69" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F19" s="77" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F19" s="76" t="inlineStr">
+        <is>
+          <t>EM ANDAMENTO</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="71" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B20" s="72" t="inlineStr">
         <is>
-          <t>Ferramentas de IA sem orçamento — DEFINIR META</t>
+          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
         </is>
       </c>
       <c r="C20" s="72" t="inlineStr">
         <is>
-          <t>Claude, GPT, Adapta One e Adapta Skip são gastos que existem hoje e não constavam na ficha. Foram criadas quatro linhas separadas, com planejado zerado, para a meta ser definida junto com a diretoria.</t>
+          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
         </is>
       </c>
       <c r="D20" s="72" t="inlineStr">
         <is>
-          <t>Enquanto o planejado for zero, qualquer lançamento nessas linhas aparece como 'Não orçado'. Conferir também se há sobreposição com a linha 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano — pode ser que ela já cubra o Adapta One e o Adapta Skip. E confirmar o nome exato do 'Adapta Skip'.</t>
+          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
         </is>
       </c>
       <c r="E20" s="72" t="inlineStr">
@@ -26352,7 +26352,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F20" s="77" t="inlineStr">
+      <c r="F20" s="75" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -26361,59 +26361,59 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B21" s="69" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos de TI</t>
+          <t>Ferramentas de IA sem orçamento — DEFINIR META</t>
         </is>
       </c>
       <c r="C21" s="69" t="inlineStr">
         <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
+          <t>Claude, GPT, Adapta One e Adapta Skip são gastos que existem hoje e não constavam na ficha. Foram criadas quatro linhas separadas, com planejado zerado, para a meta ser definida junto com a diretoria.</t>
         </is>
       </c>
       <c r="D21" s="69" t="inlineStr">
         <is>
-          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
+          <t>Enquanto o planejado for zero, qualquer lançamento nessas linhas aparece como 'Não orçado'. Conferir também se há sobreposição com a linha 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano — pode ser que ela já cubra o Adapta One e o Adapta Skip. E confirmar o nome exato do 'Adapta Skip'.</t>
         </is>
       </c>
       <c r="E21" s="69" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
-        </is>
-      </c>
-      <c r="F21" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F21" s="75" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B22" s="72" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Rateio dos softwares corporativos de TI</t>
         </is>
       </c>
       <c r="C22" s="72" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
         </is>
       </c>
       <c r="D22" s="72" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
         </is>
       </c>
       <c r="E22" s="72" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Controladoria</t>
         </is>
       </c>
       <c r="F22" s="74" t="inlineStr">
@@ -26425,22 +26425,22 @@
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B23" s="69" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
         </is>
       </c>
       <c r="C23" s="69" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
         </is>
       </c>
       <c r="D23" s="69" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
         </is>
       </c>
       <c r="E23" s="69" t="inlineStr">
@@ -26457,30 +26457,62 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="71" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="72" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C24" s="72" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D24" s="72" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E24" s="72" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F24" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="68" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B24" s="72" t="inlineStr">
+      <c r="B25" s="69" t="inlineStr">
         <is>
           <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
         </is>
       </c>
-      <c r="C24" s="72" t="inlineStr">
+      <c r="C25" s="69" t="inlineStr">
         <is>
           <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
         </is>
       </c>
-      <c r="D24" s="72" t="inlineStr">
+      <c r="D25" s="69" t="inlineStr">
         <is>
           <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Com a extração vindo do SIENGE, basta escolher o regime na hora de gerar o relatório: definir isso UMA vez e manter, para o histórico não misturar critérios.</t>
         </is>
       </c>
-      <c r="E24" s="72" t="inlineStr">
+      <c r="E25" s="69" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F25" s="77" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -19,8 +19,8 @@
     <sheet name="Contas Pagas (detalhe)" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$423</definedName>
   </definedNames>
@@ -1250,15 +1250,15 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"Jurídico",Planejado!$C$5:$C$29,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"Jurídico",Planejado!$C$5:$C$30,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -1274,7 +1274,7 @@
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1290,15 +1290,15 @@
         </is>
       </c>
       <c r="C7" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"Jurídico",Planejado!$C$5:$C$29,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"Jurídico",Planejado!$C$5:$C$30,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="9">
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"Jurídico",Comparativo!$C$6:$C$30,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1330,15 +1330,15 @@
         </is>
       </c>
       <c r="C8" s="13">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="F8" s="13">
@@ -1354,7 +1354,7 @@
         <v/>
       </c>
       <c r="I8" s="15">
-        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
     </row>
@@ -1370,15 +1370,15 @@
         </is>
       </c>
       <c r="C9" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"TI",Planejado!$C$5:$C$29,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"TI",Planejado!$C$5:$C$30,"Equipe")</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Equipe")</f>
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Equipe")</f>
         <v/>
       </c>
       <c r="F9" s="9">
@@ -1394,7 +1394,7 @@
         <v/>
       </c>
       <c r="I9" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1410,15 +1410,15 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"TI",Planejado!$C$5:$C$29,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"TI",Planejado!$C$5:$C$30,"Despesas")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Despesas")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Despesas")</f>
         <v/>
       </c>
       <c r="F10" s="9">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"TI",Comparativo!$C$6:$C$30,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1450,15 +1450,15 @@
         </is>
       </c>
       <c r="C11" s="13">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="13">
@@ -1474,7 +1474,7 @@
         <v/>
       </c>
       <c r="I11" s="15">
-        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0",Comparativo!$B$6:$B$30,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$30,"?*",Comparativo!$B$6:$B$30,"TI")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
     </row>
@@ -1486,15 +1486,15 @@
       </c>
       <c r="B12" s="16" t="inlineStr"/>
       <c r="C12" s="17">
-        <f>SUM(Planejado!$T$5:$T$29)</f>
+        <f>SUM(Planejado!$T$5:$T$30)</f>
         <v/>
       </c>
       <c r="D12" s="17">
-        <f>SUM(Comparativo!$I$6:$I$30)</f>
+        <f>SUM(Comparativo!$I$6:$I$31)</f>
         <v/>
       </c>
       <c r="E12" s="17">
-        <f>SUM(Comparativo!$J$6:$J$30)</f>
+        <f>SUM(Comparativo!$J$6:$J$31)</f>
         <v/>
       </c>
       <c r="F12" s="17">
@@ -1510,7 +1510,7 @@
         <v/>
       </c>
       <c r="I12" s="19">
-        <f>COUNTIFS(Comparativo!$P$6:$P$30,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$30)</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$31)</f>
         <v/>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B16" s="21" t="n"/>
       <c r="C16" s="22">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$30,"&lt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$31,"&lt;0")</f>
         <v/>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B17" s="21" t="n"/>
       <c r="C17" s="22">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$30,"&gt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$31,"&gt;0")</f>
         <v/>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B18" s="24" t="n"/>
       <c r="C18" s="25">
-        <f>-SUM(Comparativo!$Q$6:$Q$30)</f>
+        <f>-SUM(Comparativo!$Q$6:$Q$31)</f>
         <v/>
       </c>
       <c r="D18" s="26" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B19" s="21" t="n"/>
       <c r="C19" s="22">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$30)/Comparativo!$D$3*12,"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$31)/Comparativo!$D$3*12,"")</f>
         <v/>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B20" s="21" t="n"/>
       <c r="C20" s="27">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$30)/SUM(Comparativo!$S$6:$S$30),"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$31)/SUM(Comparativo!$S$6:$S$31),"")</f>
         <v/>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -1688,23 +1688,23 @@
         <v>1</v>
       </c>
       <c r="B25" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A25),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A25),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="C25" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A25),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A25),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A25),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A25),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A25),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A25),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A25),Comparativo!$R$6:$R$30,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A25),Comparativo!$R$6:$R$31,0)),""),"")</f>
         <v/>
       </c>
       <c r="G25" s="34">
@@ -1717,23 +1717,23 @@
         <v>2</v>
       </c>
       <c r="B26" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A26),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A26),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="C26" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A26),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A26),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A26),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A26),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A26),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A26),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="F26" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A26),Comparativo!$R$6:$R$30,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A26),Comparativo!$R$6:$R$31,0)),""),"")</f>
         <v/>
       </c>
       <c r="G26" s="34">
@@ -1746,23 +1746,23 @@
         <v>3</v>
       </c>
       <c r="B27" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A27),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A27),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="C27" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A27),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A27),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A27),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A27),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A27),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A27),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="F27" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A27),Comparativo!$R$6:$R$30,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A27),Comparativo!$R$6:$R$31,0)),""),"")</f>
         <v/>
       </c>
       <c r="G27" s="34">
@@ -1775,23 +1775,23 @@
         <v>4</v>
       </c>
       <c r="B28" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A28),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A28),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="C28" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A28),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A28),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A28),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A28),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A28),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A28),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="F28" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A28),Comparativo!$R$6:$R$30,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A28),Comparativo!$R$6:$R$31,0)),""),"")</f>
         <v/>
       </c>
       <c r="G28" s="34">
@@ -1804,23 +1804,23 @@
         <v>5</v>
       </c>
       <c r="B29" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A29),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A29),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="C29" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A29),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A29),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A29),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A29),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A29),Comparativo!$R$6:$R$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A29),Comparativo!$R$6:$R$31,0)),"")</f>
         <v/>
       </c>
       <c r="F29" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$R$6:$R$30,A29),Comparativo!$R$6:$R$30,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A29),Comparativo!$R$6:$R$31,0)),""),"")</f>
         <v/>
       </c>
       <c r="G29" s="34">
@@ -1878,23 +1878,23 @@
         <v>1</v>
       </c>
       <c r="B34" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A34),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A34),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="C34" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A34),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A34),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A34),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A34),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A34),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A34),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="F34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A34),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A34),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="G34" s="34">
@@ -1907,23 +1907,23 @@
         <v>2</v>
       </c>
       <c r="B35" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A35),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A35),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="C35" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A35),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A35),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A35),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A35),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A35),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A35),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="F35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A35),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A35),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="G35" s="34">
@@ -1936,23 +1936,23 @@
         <v>3</v>
       </c>
       <c r="B36" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A36),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A36),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="C36" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A36),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A36),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A36),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A36),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A36),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A36),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="F36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A36),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A36),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="G36" s="34">
@@ -1965,23 +1965,23 @@
         <v>4</v>
       </c>
       <c r="B37" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A37),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A37),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="C37" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A37),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A37),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A37),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A37),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A37),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A37),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="F37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A37),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A37),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="G37" s="34">
@@ -1994,23 +1994,23 @@
         <v>5</v>
       </c>
       <c r="B38" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A38),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A38),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="C38" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A38),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A38),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A38),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A38),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A38),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A38),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="F38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$30,MATCH(LARGE(Comparativo!$O$6:$O$30,A38),Comparativo!$O$6:$O$30,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A38),Comparativo!$O$6:$O$31,0)),"")</f>
         <v/>
       </c>
       <c r="G38" s="34">
@@ -18856,7 +18856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19713,59 +19713,59 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="47">
+      <c r="A15" s="40">
         <f>Planejado!A14</f>
         <v/>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="40">
         <f>Planejado!B14</f>
         <v/>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="40">
         <f>Planejado!C14</f>
         <v/>
       </c>
-      <c r="D15" s="48">
+      <c r="D15" s="41">
         <f>Planejado!D14</f>
         <v/>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="40">
         <f>Planejado!G14</f>
         <v/>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="42">
         <f>INDEX(Planejado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="42">
         <f>INDEX(Realizado!$H14:$S14,$D$3)</f>
         <v/>
       </c>
-      <c r="H15" s="49">
+      <c r="H15" s="42">
         <f>G15-F15</f>
         <v/>
       </c>
-      <c r="I15" s="49">
+      <c r="I15" s="42">
         <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H14:$S14)</f>
         <v/>
       </c>
-      <c r="J15" s="49">
+      <c r="J15" s="42">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H14:$S14)</f>
         <v/>
       </c>
-      <c r="K15" s="49">
+      <c r="K15" s="42">
         <f>J15-I15</f>
         <v/>
       </c>
-      <c r="L15" s="50">
+      <c r="L15" s="43">
         <f>IFERROR(K15/I15,"")</f>
         <v/>
       </c>
-      <c r="M15" s="50">
+      <c r="M15" s="43">
         <f>IFERROR(J15/I15,"")</f>
         <v/>
       </c>
-      <c r="N15" s="51">
+      <c r="N15" s="44">
         <f>IF(P15=0,"Sem lançamento",IF(AND(I15=0,J15=0),"—",IF(I15=0,"Não orçado",IF(K15&gt;0.05*I15,"Acima do orçado",IF(K15&lt;-0.05*I15,"Abaixo do orçado","Dentro do orçado")))))</f>
         <v/>
       </c>
@@ -19773,7 +19773,7 @@
         <f>IF(K15&gt;1,K15+ROW()/1000000,"")</f>
         <v/>
       </c>
-      <c r="P15" s="52">
+      <c r="P15" s="45">
         <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H14:$S14&lt;&gt;""))</f>
         <v/>
       </c>
@@ -20960,57 +20960,135 @@
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="47">
+        <f>Planejado!A30</f>
+        <v/>
+      </c>
+      <c r="B31" s="47">
+        <f>Planejado!B30</f>
+        <v/>
+      </c>
+      <c r="C31" s="47">
+        <f>Planejado!C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="48">
+        <f>Planejado!D30</f>
+        <v/>
+      </c>
+      <c r="E31" s="47">
+        <f>Planejado!G30</f>
+        <v/>
+      </c>
+      <c r="F31" s="49">
+        <f>INDEX(Planejado!$H30:$S30,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G31" s="49">
+        <f>INDEX(Realizado!$H30:$S30,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H31" s="49">
+        <f>G31-F31</f>
+        <v/>
+      </c>
+      <c r="I31" s="49">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H30:$S30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="49">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H30:$S30)</f>
+        <v/>
+      </c>
+      <c r="K31" s="49">
+        <f>J31-I31</f>
+        <v/>
+      </c>
+      <c r="L31" s="50">
+        <f>IFERROR(K31/I31,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="50">
+        <f>IFERROR(J31/I31,"")</f>
+        <v/>
+      </c>
+      <c r="N31" s="51">
+        <f>IF(P31=0,"Sem lançamento",IF(AND(I31=0,J31=0),"—",IF(I31=0,"Não orçado",IF(K31&gt;0.05*I31,"Acima do orçado",IF(K31&lt;-0.05*I31,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O31" s="39">
+        <f>IF(K31&gt;1,K31+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P31" s="52">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H30:$S30&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q31" s="46">
+        <f>IF(P31=0,"",K31)</f>
+        <v/>
+      </c>
+      <c r="R31" s="46">
+        <f>IF(AND(Q31&lt;&gt;"",Q31&lt;-1),-Q31+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S31" s="46">
+        <f>IF(Q31="","",I31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="17">
-        <f>SUM(F6:F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="17">
-        <f>SUM(G6:G30)</f>
-        <v/>
-      </c>
-      <c r="H31" s="17">
-        <f>SUM(H6:H30)</f>
-        <v/>
-      </c>
-      <c r="I31" s="17">
-        <f>SUM(I6:I30)</f>
-        <v/>
-      </c>
-      <c r="J31" s="17">
-        <f>SUM(J6:J30)</f>
-        <v/>
-      </c>
-      <c r="K31" s="17">
-        <f>SUM(K6:K30)</f>
-        <v/>
-      </c>
-      <c r="L31" s="53">
-        <f>IFERROR(K31/I31,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="53">
-        <f>IFERROR(J31/I31,"")</f>
-        <v/>
-      </c>
-      <c r="N31" s="16" t="n"/>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="17">
+        <f>SUM(F6:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="17">
+        <f>SUM(G6:G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="17">
+        <f>SUM(H6:H31)</f>
+        <v/>
+      </c>
+      <c r="I32" s="17">
+        <f>SUM(I6:I31)</f>
+        <v/>
+      </c>
+      <c r="J32" s="17">
+        <f>SUM(J6:J31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="17">
+        <f>SUM(K6:K31)</f>
+        <v/>
+      </c>
+      <c r="L32" s="53">
+        <f>IFERROR(K32/I32,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="53">
+        <f>IFERROR(J32/I32,"")</f>
+        <v/>
+      </c>
+      <c r="N32" s="16" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N30"/>
+  <autoFilter ref="A5:N31"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H30">
+  <conditionalFormatting sqref="H6:H31">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -21018,7 +21096,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K30">
+  <conditionalFormatting sqref="K6:K31">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -21041,7 +21119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21416,7 +21494,7 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="40" t="inlineStr">
         <is>
-          <t>JUR-D01</t>
+          <t>JUR-E04</t>
         </is>
       </c>
       <c r="B8" s="40" t="inlineStr">
@@ -21426,60 +21504,64 @@
       </c>
       <c r="C8" s="40" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="D8" s="41" t="inlineStr">
         <is>
-          <t>JUSFY</t>
+          <t>Dra. Michele de Oliveira Silva</t>
         </is>
       </c>
       <c r="E8" s="41" t="inlineStr">
         <is>
-          <t>Fase de teste com objetivo de eliminar o Astrea</t>
-        </is>
-      </c>
-      <c r="F8" s="40" t="inlineStr"/>
+          <t>Advogada — NÃO CONSTAVA NA FICHA. R$ 2.750/mês fixos desde jul/26. Planejado a definir com a diretoria</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
       <c r="G8" s="40" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="H8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S8" s="42" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T8" s="54">
         <f>SUM(H8:S8)</f>
@@ -21489,7 +21571,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>JUR-D02</t>
+          <t>JUR-D01</t>
         </is>
       </c>
       <c r="B9" s="40" t="inlineStr">
@@ -21504,12 +21586,12 @@
       </c>
       <c r="D9" s="41" t="inlineStr">
         <is>
-          <t>JUSBRASIL</t>
+          <t>JUSFY</t>
         </is>
       </c>
       <c r="E9" s="41" t="inlineStr">
         <is>
-          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 104,90/mês, custo real R$ 136,00/mês. Corrigir na revisão orçamentária</t>
+          <t>Fase de teste com objetivo de eliminar o Astrea</t>
         </is>
       </c>
       <c r="F9" s="40" t="inlineStr"/>
@@ -21519,40 +21601,40 @@
         </is>
       </c>
       <c r="H9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="I9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="J9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="K9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="L9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="M9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="N9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="O9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="P9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="R9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="S9" s="42" t="n">
-        <v>104.9</v>
+        <v>100</v>
       </c>
       <c r="T9" s="54">
         <f>SUM(H9:S9)</f>
@@ -21562,7 +21644,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="40" t="inlineStr">
         <is>
-          <t>JUR-D03</t>
+          <t>JUR-D02</t>
         </is>
       </c>
       <c r="B10" s="40" t="inlineStr">
@@ -21577,12 +21659,12 @@
       </c>
       <c r="D10" s="41" t="inlineStr">
         <is>
-          <t>ASTREA</t>
+          <t>JUSBRASIL</t>
         </is>
       </c>
       <c r="E10" s="41" t="inlineStr">
         <is>
-          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 112,07/mês, custo real R$ 346,00/mês. Corrigir na revisão orçamentária</t>
+          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 104,90/mês, custo real R$ 136,00/mês. Corrigir na revisão orçamentária</t>
         </is>
       </c>
       <c r="F10" s="40" t="inlineStr"/>
@@ -21592,40 +21674,40 @@
         </is>
       </c>
       <c r="H10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="I10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="J10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="K10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="L10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="M10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="N10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="O10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="P10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="Q10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="R10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="S10" s="42" t="n">
-        <v>112.07</v>
+        <v>104.9</v>
       </c>
       <c r="T10" s="54">
         <f>SUM(H10:S10)</f>
@@ -21635,7 +21717,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="40" t="inlineStr">
         <is>
-          <t>JUR-D04</t>
+          <t>JUR-D03</t>
         </is>
       </c>
       <c r="B11" s="40" t="inlineStr">
@@ -21650,10 +21732,14 @@
       </c>
       <c r="D11" s="41" t="inlineStr">
         <is>
-          <t>LEME</t>
-        </is>
-      </c>
-      <c r="E11" s="41" t="inlineStr"/>
+          <t>ASTREA</t>
+        </is>
+      </c>
+      <c r="E11" s="41" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO VEIO ERRADO: orçado R$ 112,07/mês, custo real R$ 346,00/mês. Corrigir na revisão orçamentária</t>
+        </is>
+      </c>
       <c r="F11" s="40" t="inlineStr"/>
       <c r="G11" s="40" t="inlineStr">
         <is>
@@ -21661,40 +21747,40 @@
         </is>
       </c>
       <c r="H11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="I11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="J11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="K11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="L11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="M11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="N11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="O11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="P11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="Q11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="R11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="S11" s="42" t="n">
-        <v>1030</v>
+        <v>112.07</v>
       </c>
       <c r="T11" s="54">
         <f>SUM(H11:S11)</f>
@@ -21704,7 +21790,7 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="40" t="inlineStr">
         <is>
-          <t>JUR-D05</t>
+          <t>JUR-D04</t>
         </is>
       </c>
       <c r="B12" s="40" t="inlineStr">
@@ -21719,51 +21805,51 @@
       </c>
       <c r="D12" s="41" t="inlineStr">
         <is>
-          <t>Cursos / Eventos / Network</t>
+          <t>LEME</t>
         </is>
       </c>
       <c r="E12" s="41" t="inlineStr"/>
       <c r="F12" s="40" t="inlineStr"/>
       <c r="G12" s="40" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="I12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="J12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="K12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="L12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="M12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="N12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="O12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="P12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="Q12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="R12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="S12" s="42" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="T12" s="54">
         <f>SUM(H12:S12)</f>
@@ -21773,7 +21859,7 @@
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="40" t="inlineStr">
         <is>
-          <t>JUR-D06</t>
+          <t>JUR-D05</t>
         </is>
       </c>
       <c r="B13" s="40" t="inlineStr">
@@ -21788,55 +21874,51 @@
       </c>
       <c r="D13" s="41" t="inlineStr">
         <is>
-          <t>Bonificações trimestrais/semestrais do time</t>
-        </is>
-      </c>
-      <c r="E13" s="41" t="inlineStr">
-        <is>
-          <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
-        </is>
-      </c>
+          <t>Cursos / Eventos / Network</t>
+        </is>
+      </c>
+      <c r="E13" s="41" t="inlineStr"/>
       <c r="F13" s="40" t="inlineStr"/>
       <c r="G13" s="40" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="H13" s="42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I13" s="42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J13" s="42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K13" s="42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L13" s="42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M13" s="42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N13" s="42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="O13" s="42" t="n">
-        <v>10293.6</v>
+        <v>1000</v>
       </c>
       <c r="P13" s="42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q13" s="42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R13" s="42" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S13" s="42" t="n">
-        <v>12867</v>
+        <v>1000</v>
       </c>
       <c r="T13" s="54">
         <f>SUM(H13:S13)</f>
@@ -21844,76 +21926,72 @@
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="47" t="inlineStr">
-        <is>
-          <t>TI-E01</t>
-        </is>
-      </c>
-      <c r="B14" s="47" t="inlineStr">
-        <is>
-          <t>TI</t>
-        </is>
-      </c>
-      <c r="C14" s="47" t="inlineStr">
-        <is>
-          <t>Equipe</t>
-        </is>
-      </c>
-      <c r="D14" s="48" t="inlineStr">
-        <is>
-          <t>Vinicius Di Franco</t>
-        </is>
-      </c>
-      <c r="E14" s="48" t="inlineStr">
-        <is>
-          <t>Analista Administrativo — orçado pelo custo total (encargos de folha + benefícios). Salário bruto: R$ 2.570,52/mês até jul/26 e R$ 3.070,52 a partir de 05/08/26, aumento absorvido pela folga do envelope</t>
-        </is>
-      </c>
-      <c r="F14" s="47" t="inlineStr">
-        <is>
-          <t>CLT</t>
-        </is>
-      </c>
-      <c r="G14" s="47" t="inlineStr">
-        <is>
-          <t>Pessoal - CLT</t>
-        </is>
-      </c>
-      <c r="H14" s="49" t="n">
-        <v>5416.525</v>
-      </c>
-      <c r="I14" s="49" t="n">
-        <v>5416.525</v>
-      </c>
-      <c r="J14" s="49" t="n">
-        <v>5416.525</v>
-      </c>
-      <c r="K14" s="49" t="n">
-        <v>5416.525</v>
-      </c>
-      <c r="L14" s="49" t="n">
-        <v>5416.525</v>
-      </c>
-      <c r="M14" s="49" t="n">
-        <v>5416.525</v>
-      </c>
-      <c r="N14" s="49" t="n">
-        <v>5416.525</v>
-      </c>
-      <c r="O14" s="49" t="n">
-        <v>5416.525</v>
-      </c>
-      <c r="P14" s="49" t="n">
-        <v>5416.525</v>
-      </c>
-      <c r="Q14" s="49" t="n">
-        <v>5416.525</v>
-      </c>
-      <c r="R14" s="49" t="n">
-        <v>5416.525</v>
-      </c>
-      <c r="S14" s="49" t="n">
-        <v>5416.525</v>
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>JUR-D06</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>Jurídico</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D14" s="41" t="inlineStr">
+        <is>
+          <t>Bonificações trimestrais/semestrais do time</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="inlineStr">
+        <is>
+          <t>Participação em projetos e atingimento de resultados — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr"/>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>Prêmios</t>
+        </is>
+      </c>
+      <c r="H14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="42" t="n">
+        <v>10293.6</v>
+      </c>
+      <c r="P14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="42" t="n">
+        <v>12867</v>
       </c>
       <c r="T14" s="54">
         <f>SUM(H14:S14)</f>
@@ -21923,7 +22001,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="47" t="inlineStr">
         <is>
-          <t>TI-E02</t>
+          <t>TI-E01</t>
         </is>
       </c>
       <c r="B15" s="47" t="inlineStr">
@@ -21938,59 +22016,59 @@
       </c>
       <c r="D15" s="48" t="inlineStr">
         <is>
-          <t>Elias Benedito</t>
+          <t>Vinicius Di Franco</t>
         </is>
       </c>
       <c r="E15" s="48" t="inlineStr">
         <is>
-          <t>Suporte Técnico Terceirizado</t>
+          <t>Analista Administrativo — orçado pelo custo total (encargos de folha + benefícios). Salário bruto: R$ 2.570,52/mês até jul/26 e R$ 3.070,52 a partir de 05/08/26, aumento absorvido pela folga do envelope</t>
         </is>
       </c>
       <c r="F15" s="47" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>CLT</t>
         </is>
       </c>
       <c r="G15" s="47" t="inlineStr">
         <is>
-          <t>Pessoal - PJ</t>
+          <t>Pessoal - CLT</t>
         </is>
       </c>
       <c r="H15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="I15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="J15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="K15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="L15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="M15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="N15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="O15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="P15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="Q15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="R15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="S15" s="49" t="n">
-        <v>1065</v>
+        <v>5416.525</v>
       </c>
       <c r="T15" s="54">
         <f>SUM(H15:S15)</f>
@@ -22000,7 +22078,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="47" t="inlineStr">
         <is>
-          <t>TI-E03</t>
+          <t>TI-E02</t>
         </is>
       </c>
       <c r="B16" s="47" t="inlineStr">
@@ -22015,12 +22093,12 @@
       </c>
       <c r="D16" s="48" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Elias Benedito</t>
         </is>
       </c>
       <c r="E16" s="48" t="inlineStr">
         <is>
-          <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
+          <t>Suporte Técnico Terceirizado</t>
         </is>
       </c>
       <c r="F16" s="47" t="inlineStr">
@@ -22034,40 +22112,40 @@
         </is>
       </c>
       <c r="H16" s="49" t="n">
-        <v>0</v>
+        <v>1065</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>0</v>
+        <v>1065</v>
       </c>
       <c r="J16" s="49" t="n">
-        <v>0</v>
+        <v>1065</v>
       </c>
       <c r="K16" s="49" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="L16" s="49" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="M16" s="49" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="N16" s="49" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="O16" s="49" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="P16" s="49" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="Q16" s="49" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="R16" s="49" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="S16" s="49" t="n">
-        <v>10000</v>
+        <v>1065</v>
       </c>
       <c r="T16" s="54">
         <f>SUM(H16:S16)</f>
@@ -22077,7 +22155,7 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="47" t="inlineStr">
         <is>
-          <t>TI-D01</t>
+          <t>TI-E03</t>
         </is>
       </c>
       <c r="B17" s="47" t="inlineStr">
@@ -22087,60 +22165,64 @@
       </c>
       <c r="C17" s="47" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="D17" s="48" t="inlineStr">
         <is>
-          <t>Peças de Manutenção</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="E17" s="48" t="inlineStr">
         <is>
-          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
-        </is>
-      </c>
-      <c r="F17" s="47" t="inlineStr"/>
+          <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
+        </is>
+      </c>
+      <c r="F17" s="47" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
       <c r="G17" s="47" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos Diversos</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="H17" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="J17" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="K17" s="49" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="L17" s="49" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="M17" s="49" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="N17" s="49" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="O17" s="49" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="P17" s="49" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="Q17" s="49" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="R17" s="49" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="S17" s="49" t="n">
-        <v>810</v>
+        <v>10000</v>
       </c>
       <c r="T17" s="54">
         <f>SUM(H17:S17)</f>
@@ -22150,7 +22232,7 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="47" t="inlineStr">
         <is>
-          <t>TI-D02</t>
+          <t>TI-D01</t>
         </is>
       </c>
       <c r="B18" s="47" t="inlineStr">
@@ -22165,55 +22247,55 @@
       </c>
       <c r="D18" s="48" t="inlineStr">
         <is>
-          <t>Backup em Nuvem</t>
+          <t>Peças de Manutenção</t>
         </is>
       </c>
       <c r="E18" s="48" t="inlineStr">
         <is>
-          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
+          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
         </is>
       </c>
       <c r="F18" s="47" t="inlineStr"/>
       <c r="G18" s="47" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
       <c r="H18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="J18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="K18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="L18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="M18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="N18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="O18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="P18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="Q18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="R18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="S18" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="T18" s="54">
         <f>SUM(H18:S18)</f>
@@ -22223,7 +22305,7 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="47" t="inlineStr">
         <is>
-          <t>TI-D03</t>
+          <t>TI-D02</t>
         </is>
       </c>
       <c r="B19" s="47" t="inlineStr">
@@ -22238,12 +22320,12 @@
       </c>
       <c r="D19" s="48" t="inlineStr">
         <is>
-          <t>Inteligência Artificial (Adapta)</t>
+          <t>Backup em Nuvem</t>
         </is>
       </c>
       <c r="E19" s="48" t="inlineStr">
         <is>
-          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
+          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F19" s="47" t="inlineStr"/>
@@ -22253,40 +22335,40 @@
         </is>
       </c>
       <c r="H19" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="J19" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="K19" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="L19" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="M19" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="N19" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="O19" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="P19" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="Q19" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="R19" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="S19" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="T19" s="54">
         <f>SUM(H19:S19)</f>
@@ -22296,7 +22378,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="47" t="inlineStr">
         <is>
-          <t>TI-D04</t>
+          <t>TI-D03</t>
         </is>
       </c>
       <c r="B20" s="47" t="inlineStr">
@@ -22311,12 +22393,12 @@
       </c>
       <c r="D20" s="48" t="inlineStr">
         <is>
-          <t>Antivírus</t>
+          <t>Inteligência Artificial (Adapta)</t>
         </is>
       </c>
       <c r="E20" s="48" t="inlineStr">
         <is>
-          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
+          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F20" s="47" t="inlineStr"/>
@@ -22326,40 +22408,40 @@
         </is>
       </c>
       <c r="H20" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="J20" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="K20" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="L20" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="M20" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="N20" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="O20" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="P20" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="Q20" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="R20" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="S20" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="T20" s="54">
         <f>SUM(H20:S20)</f>
@@ -22369,7 +22451,7 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="47" t="inlineStr">
         <is>
-          <t>TI-D05</t>
+          <t>TI-D04</t>
         </is>
       </c>
       <c r="B21" s="47" t="inlineStr">
@@ -22384,12 +22466,12 @@
       </c>
       <c r="D21" s="48" t="inlineStr">
         <is>
-          <t>Pacote Office 365</t>
+          <t>Antivírus</t>
         </is>
       </c>
       <c r="E21" s="48" t="inlineStr">
         <is>
-          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
+          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F21" s="47" t="inlineStr"/>
@@ -22399,40 +22481,40 @@
         </is>
       </c>
       <c r="H21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="J21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="K21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="L21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="M21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="N21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="O21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="P21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="Q21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="R21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="S21" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="T21" s="54">
         <f>SUM(H21:S21)</f>
@@ -22442,7 +22524,7 @@
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="47" t="inlineStr">
         <is>
-          <t>TI-D06</t>
+          <t>TI-D05</t>
         </is>
       </c>
       <c r="B22" s="47" t="inlineStr">
@@ -22457,55 +22539,55 @@
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
-          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
+          <t>Pacote Office 365</t>
         </is>
       </c>
       <c r="E22" s="48" t="inlineStr">
         <is>
-          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
+          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F22" s="47" t="inlineStr"/>
       <c r="G22" s="47" t="inlineStr">
         <is>
-          <t>Móveis e Utensílios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="J22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="K22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="L22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="M22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="N22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="O22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="P22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="Q22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="R22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="S22" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="T22" s="54">
         <f>SUM(H22:S22)</f>
@@ -22515,7 +22597,7 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="47" t="inlineStr">
         <is>
-          <t>TI-D07</t>
+          <t>TI-D06</t>
         </is>
       </c>
       <c r="B23" s="47" t="inlineStr">
@@ -22530,51 +22612,55 @@
       </c>
       <c r="D23" s="48" t="inlineStr">
         <is>
-          <t>Cursos e Treinamentos</t>
-        </is>
-      </c>
-      <c r="E23" s="48" t="inlineStr"/>
+          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
+        </is>
+      </c>
+      <c r="E23" s="48" t="inlineStr">
+        <is>
+          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
+        </is>
+      </c>
       <c r="F23" s="47" t="inlineStr"/>
       <c r="G23" s="47" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Móveis e Utensílios</t>
         </is>
       </c>
       <c r="H23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="J23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="K23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="L23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="M23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="N23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="O23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="P23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="Q23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="R23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="S23" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="T23" s="54">
         <f>SUM(H23:S23)</f>
@@ -22584,7 +22670,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="47" t="inlineStr">
         <is>
-          <t>TI-D08</t>
+          <t>TI-D07</t>
         </is>
       </c>
       <c r="B24" s="47" t="inlineStr">
@@ -22599,51 +22685,51 @@
       </c>
       <c r="D24" s="48" t="inlineStr">
         <is>
-          <t>Aplicativo de Gravação de Reunião</t>
+          <t>Cursos e Treinamentos</t>
         </is>
       </c>
       <c r="E24" s="48" t="inlineStr"/>
       <c r="F24" s="47" t="inlineStr"/>
       <c r="G24" s="47" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="H24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="J24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="K24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="M24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="N24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="O24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="P24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="Q24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="R24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="S24" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="T24" s="54">
         <f>SUM(H24:S24)</f>
@@ -22653,7 +22739,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="47" t="inlineStr">
         <is>
-          <t>TI-D10</t>
+          <t>TI-D08</t>
         </is>
       </c>
       <c r="B25" s="47" t="inlineStr">
@@ -22668,14 +22754,10 @@
       </c>
       <c r="D25" s="48" t="inlineStr">
         <is>
-          <t>Claude</t>
-        </is>
-      </c>
-      <c r="E25" s="48" t="inlineStr">
-        <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria</t>
-        </is>
-      </c>
+          <t>Aplicativo de Gravação de Reunião</t>
+        </is>
+      </c>
+      <c r="E25" s="48" t="inlineStr"/>
       <c r="F25" s="47" t="inlineStr"/>
       <c r="G25" s="47" t="inlineStr">
         <is>
@@ -22683,40 +22765,40 @@
         </is>
       </c>
       <c r="H25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="J25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="K25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="L25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="M25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="N25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="O25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="P25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="Q25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="R25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="S25" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="T25" s="54">
         <f>SUM(H25:S25)</f>
@@ -22726,7 +22808,7 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="47" t="inlineStr">
         <is>
-          <t>TI-D11</t>
+          <t>TI-D10</t>
         </is>
       </c>
       <c r="B26" s="47" t="inlineStr">
@@ -22741,7 +22823,7 @@
       </c>
       <c r="D26" s="48" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="E26" s="48" t="inlineStr">
@@ -22799,7 +22881,7 @@
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="47" t="inlineStr">
         <is>
-          <t>TI-D12</t>
+          <t>TI-D11</t>
         </is>
       </c>
       <c r="B27" s="47" t="inlineStr">
@@ -22814,12 +22896,12 @@
       </c>
       <c r="D27" s="48" t="inlineStr">
         <is>
-          <t>Adapta One</t>
+          <t>GPT</t>
         </is>
       </c>
       <c r="E27" s="48" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria</t>
         </is>
       </c>
       <c r="F27" s="47" t="inlineStr"/>
@@ -22872,7 +22954,7 @@
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="47" t="inlineStr">
         <is>
-          <t>TI-D13</t>
+          <t>TI-D12</t>
         </is>
       </c>
       <c r="B28" s="47" t="inlineStr">
@@ -22887,12 +22969,12 @@
       </c>
       <c r="D28" s="48" t="inlineStr">
         <is>
-          <t>Adapta Skip</t>
+          <t>Adapta One</t>
         </is>
       </c>
       <c r="E28" s="48" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
         </is>
       </c>
       <c r="F28" s="47" t="inlineStr"/>
@@ -22945,7 +23027,7 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="47" t="inlineStr">
         <is>
-          <t>TI-D09</t>
+          <t>TI-D13</t>
         </is>
       </c>
       <c r="B29" s="47" t="inlineStr">
@@ -22960,18 +23042,18 @@
       </c>
       <c r="D29" s="48" t="inlineStr">
         <is>
-          <t>Bonificação do time</t>
+          <t>Adapta Skip</t>
         </is>
       </c>
       <c r="E29" s="48" t="inlineStr">
         <is>
-          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
         </is>
       </c>
       <c r="F29" s="47" t="inlineStr"/>
       <c r="G29" s="47" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H29" s="49" t="n">
@@ -22996,7 +23078,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="49" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="P29" s="49" t="n">
         <v>0</v>
@@ -23008,80 +23090,153 @@
         <v>0</v>
       </c>
       <c r="S29" s="49" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="T29" s="54">
         <f>SUM(H29:S29)</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="47" t="inlineStr">
+        <is>
+          <t>TI-D09</t>
+        </is>
+      </c>
+      <c r="B30" s="47" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C30" s="47" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D30" s="48" t="inlineStr">
+        <is>
+          <t>Bonificação do time</t>
+        </is>
+      </c>
+      <c r="E30" s="48" t="inlineStr">
+        <is>
+          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
+      <c r="F30" s="47" t="inlineStr"/>
+      <c r="G30" s="47" t="inlineStr">
+        <is>
+          <t>Prêmios</t>
+        </is>
+      </c>
+      <c r="H30" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="49" t="n">
+        <v>2400</v>
+      </c>
+      <c r="P30" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="49" t="n">
+        <v>3600</v>
+      </c>
+      <c r="T30" s="54">
+        <f>SUM(H30:S30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="17">
-        <f>SUM(H5:H29)</f>
-        <v/>
-      </c>
-      <c r="I30" s="17">
-        <f>SUM(I5:I29)</f>
-        <v/>
-      </c>
-      <c r="J30" s="17">
-        <f>SUM(J5:J29)</f>
-        <v/>
-      </c>
-      <c r="K30" s="17">
-        <f>SUM(K5:K29)</f>
-        <v/>
-      </c>
-      <c r="L30" s="17">
-        <f>SUM(L5:L29)</f>
-        <v/>
-      </c>
-      <c r="M30" s="17">
-        <f>SUM(M5:M29)</f>
-        <v/>
-      </c>
-      <c r="N30" s="17">
-        <f>SUM(N5:N29)</f>
-        <v/>
-      </c>
-      <c r="O30" s="17">
-        <f>SUM(O5:O29)</f>
-        <v/>
-      </c>
-      <c r="P30" s="17">
-        <f>SUM(P5:P29)</f>
-        <v/>
-      </c>
-      <c r="Q30" s="17">
-        <f>SUM(Q5:Q29)</f>
-        <v/>
-      </c>
-      <c r="R30" s="17">
-        <f>SUM(R5:R29)</f>
-        <v/>
-      </c>
-      <c r="S30" s="17">
-        <f>SUM(S5:S29)</f>
-        <v/>
-      </c>
-      <c r="T30" s="17">
-        <f>SUM(T5:T29)</f>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="16" t="n"/>
+      <c r="H31" s="17">
+        <f>SUM(H5:H30)</f>
+        <v/>
+      </c>
+      <c r="I31" s="17">
+        <f>SUM(I5:I30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="17">
+        <f>SUM(J5:J30)</f>
+        <v/>
+      </c>
+      <c r="K31" s="17">
+        <f>SUM(K5:K30)</f>
+        <v/>
+      </c>
+      <c r="L31" s="17">
+        <f>SUM(L5:L30)</f>
+        <v/>
+      </c>
+      <c r="M31" s="17">
+        <f>SUM(M5:M30)</f>
+        <v/>
+      </c>
+      <c r="N31" s="17">
+        <f>SUM(N5:N30)</f>
+        <v/>
+      </c>
+      <c r="O31" s="17">
+        <f>SUM(O5:O30)</f>
+        <v/>
+      </c>
+      <c r="P31" s="17">
+        <f>SUM(P5:P30)</f>
+        <v/>
+      </c>
+      <c r="Q31" s="17">
+        <f>SUM(Q5:Q30)</f>
+        <v/>
+      </c>
+      <c r="R31" s="17">
+        <f>SUM(R5:R30)</f>
+        <v/>
+      </c>
+      <c r="S31" s="17">
+        <f>SUM(S5:S30)</f>
+        <v/>
+      </c>
+      <c r="T31" s="17">
+        <f>SUM(T5:T30)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T29"/>
+  <autoFilter ref="A4:T30"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
@@ -23096,7 +23251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23509,35 +23664,25 @@
         <v>0</v>
       </c>
       <c r="N8" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="58" t="n">
-        <v>0</v>
-      </c>
+        <v>2750</v>
+      </c>
+      <c r="O8" s="58" t="n"/>
+      <c r="P8" s="58" t="n"/>
+      <c r="Q8" s="58" t="n"/>
+      <c r="R8" s="58" t="n"/>
+      <c r="S8" s="58" t="n"/>
       <c r="T8" s="54">
         <f>SUM(H8:S8)</f>
         <v/>
       </c>
       <c r="U8" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Extrato do financeiro</t>
         </is>
       </c>
       <c r="V8" s="59" t="inlineStr">
         <is>
-          <t>Nunca iniciado. Cancelado em jan/26 na fase de experimento e não será contratado: zero o ano todo</t>
+          <t>R$ 2.750/mês fixos a partir de jul/26. Os demais lançamentos em nome dela no extrato são REPASSE de honorários pagos pelo cliente — não são custo do departamento</t>
         </is>
       </c>
     </row>
@@ -23571,31 +23716,41 @@
         <v/>
       </c>
       <c r="H9" s="58" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="I9" s="58" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="J9" s="58" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="K9" s="58" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="L9" s="58" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M9" s="58" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N9" s="58" t="n">
-        <v>136</v>
-      </c>
-      <c r="O9" s="58" t="n"/>
-      <c r="P9" s="58" t="n"/>
-      <c r="Q9" s="58" t="n"/>
-      <c r="R9" s="58" t="n"/>
-      <c r="S9" s="58" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="58" t="n">
+        <v>0</v>
+      </c>
       <c r="T9" s="54">
         <f>SUM(H9:S9)</f>
         <v/>
@@ -23607,7 +23762,7 @@
       </c>
       <c r="V9" s="59" t="inlineStr">
         <is>
-          <t>R$ 136,00/mês contra R$ 104,90 orçados. Erro no orçamento original</t>
+          <t>Nunca iniciado. Cancelado em jan/26 na fase de experimento e não será contratado: zero o ano todo</t>
         </is>
       </c>
     </row>
@@ -23641,53 +23796,43 @@
         <v/>
       </c>
       <c r="H10" s="58" t="n">
-        <v>1346.28</v>
+        <v>136</v>
       </c>
       <c r="I10" s="58" t="n">
-        <v>5385.12</v>
+        <v>136</v>
       </c>
       <c r="J10" s="58" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="K10" s="58" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="L10" s="58" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M10" s="58" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N10" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="58" t="n">
-        <v>0</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O10" s="58" t="n"/>
+      <c r="P10" s="58" t="n"/>
+      <c r="Q10" s="58" t="n"/>
+      <c r="R10" s="58" t="n"/>
+      <c r="S10" s="58" t="n"/>
       <c r="T10" s="54">
         <f>SUM(H10:S10)</f>
         <v/>
       </c>
       <c r="U10" s="59" t="inlineStr">
         <is>
-          <t>Extrato do financeiro + portal Astrea</t>
+          <t>Gestora, 05/08/26</t>
         </is>
       </c>
       <c r="V10" s="59" t="inlineStr">
         <is>
-          <t>Anuidade 2025/26 = R$ 6.731,40 em 5x de R$ 1.346,28 (venc. 01/11/25 a 01/03/26), quitada em 10/02/26. Cancelamento em ago/26, sem renovação e sem substituto: zero de mar a dez</t>
+          <t>R$ 136,00/mês contra R$ 104,90 orçados. Erro no orçamento original</t>
         </is>
       </c>
     </row>
@@ -23721,41 +23866,55 @@
         <v/>
       </c>
       <c r="H11" s="58" t="n">
-        <v>970</v>
+        <v>1346.28</v>
       </c>
       <c r="I11" s="58" t="n">
-        <v>970</v>
+        <v>5385.12</v>
       </c>
       <c r="J11" s="58" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="K11" s="58" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="L11" s="58" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="M11" s="58" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="N11" s="58" t="n">
-        <v>970</v>
-      </c>
-      <c r="O11" s="58" t="n"/>
-      <c r="P11" s="58" t="n"/>
-      <c r="Q11" s="58" t="n"/>
-      <c r="R11" s="58" t="n"/>
-      <c r="S11" s="58" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="58" t="n">
+        <v>0</v>
+      </c>
       <c r="T11" s="54">
         <f>SUM(H11:S11)</f>
         <v/>
       </c>
       <c r="U11" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
-        </is>
-      </c>
-      <c r="V11" s="59" t="n"/>
+          <t>Extrato do financeiro + portal Astrea</t>
+        </is>
+      </c>
+      <c r="V11" s="59" t="inlineStr">
+        <is>
+          <t>Anuidade 2025/26 = R$ 6.731,40 em 5x de R$ 1.346,28 (venc. 01/11/25 a 01/03/26), quitada em 10/02/26. Cancelamento em ago/26, sem renovação e sem substituto: zero de mar a dez</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="56">
@@ -23787,25 +23946,25 @@
         <v/>
       </c>
       <c r="H12" s="58" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="I12" s="58" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="J12" s="58" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="K12" s="58" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="L12" s="58" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="M12" s="58" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="N12" s="58" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="O12" s="58" t="n"/>
       <c r="P12" s="58" t="n"/>
@@ -23821,11 +23980,7 @@
           <t>Gestora, 05/08/26</t>
         </is>
       </c>
-      <c r="V12" s="59" t="inlineStr">
-        <is>
-          <t>Sem gasto no período</t>
-        </is>
-      </c>
+      <c r="V12" s="59" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="56">
@@ -23893,7 +24048,7 @@
       </c>
       <c r="V13" s="59" t="inlineStr">
         <is>
-          <t>Sem parcela no 1º semestre; bonificação de ago/26 a confirmar</t>
+          <t>Sem gasto no período</t>
         </is>
       </c>
     </row>
@@ -23926,13 +24081,27 @@
         <f>Planejado!G14</f>
         <v/>
       </c>
-      <c r="H14" s="58" t="n"/>
-      <c r="I14" s="58" t="n"/>
-      <c r="J14" s="58" t="n"/>
-      <c r="K14" s="58" t="n"/>
-      <c r="L14" s="58" t="n"/>
-      <c r="M14" s="58" t="n"/>
-      <c r="N14" s="58" t="n"/>
+      <c r="H14" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="58" t="n">
+        <v>0</v>
+      </c>
       <c r="O14" s="58" t="n"/>
       <c r="P14" s="58" t="n"/>
       <c r="Q14" s="58" t="n"/>
@@ -23942,10 +24111,14 @@
         <f>SUM(H14:S14)</f>
         <v/>
       </c>
-      <c r="U14" s="59" t="n"/>
+      <c r="U14" s="59" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
       <c r="V14" s="59" t="inlineStr">
         <is>
-          <t>PREENCHER com o CUSTO TOTAL. Bruto: R$ 2.570,52/mês até jul e R$ 3.070,52 de ago — faltam encargos e benefícios</t>
+          <t>Sem parcela no 1º semestre; bonificação de ago/26 a confirmar</t>
         </is>
       </c>
     </row>
@@ -23978,27 +24151,13 @@
         <f>Planejado!G15</f>
         <v/>
       </c>
-      <c r="H15" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="58" t="n">
-        <v>0</v>
-      </c>
+      <c r="H15" s="58" t="n"/>
+      <c r="I15" s="58" t="n"/>
+      <c r="J15" s="58" t="n"/>
+      <c r="K15" s="58" t="n"/>
+      <c r="L15" s="58" t="n"/>
+      <c r="M15" s="58" t="n"/>
+      <c r="N15" s="58" t="n"/>
       <c r="O15" s="58" t="n"/>
       <c r="P15" s="58" t="n"/>
       <c r="Q15" s="58" t="n"/>
@@ -24008,14 +24167,10 @@
         <f>SUM(H15:S15)</f>
         <v/>
       </c>
-      <c r="U15" s="59" t="inlineStr">
-        <is>
-          <t>Gestora, 05/08/26</t>
-        </is>
-      </c>
+      <c r="U15" s="59" t="n"/>
       <c r="V15" s="59" t="inlineStr">
         <is>
-          <t>Sem acionamento no período — confirmar se o contrato segue ativo</t>
+          <t>PREENCHER com o CUSTO TOTAL. Bruto: R$ 2.570,52/mês até jul e R$ 3.070,52 de ago — faltam encargos e benefícios</t>
         </is>
       </c>
     </row>
@@ -24058,16 +24213,16 @@
         <v>0</v>
       </c>
       <c r="K16" s="58" t="n">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="L16" s="58" t="n">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="M16" s="58" t="n">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="N16" s="58" t="n">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="O16" s="58" t="n"/>
       <c r="P16" s="58" t="n"/>
@@ -24085,7 +24240,7 @@
       </c>
       <c r="V16" s="59" t="inlineStr">
         <is>
-          <t>Entrada em abr/26. R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
+          <t>Sem acionamento no período — confirmar se o contrato segue ativo</t>
         </is>
       </c>
     </row>
@@ -24118,13 +24273,27 @@
         <f>Planejado!G17</f>
         <v/>
       </c>
-      <c r="H17" s="58" t="n"/>
-      <c r="I17" s="58" t="n"/>
-      <c r="J17" s="58" t="n"/>
-      <c r="K17" s="58" t="n"/>
-      <c r="L17" s="58" t="n"/>
-      <c r="M17" s="58" t="n"/>
-      <c r="N17" s="58" t="n"/>
+      <c r="H17" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="58" t="n">
+        <v>6300</v>
+      </c>
+      <c r="L17" s="58" t="n">
+        <v>6300</v>
+      </c>
+      <c r="M17" s="58" t="n">
+        <v>6300</v>
+      </c>
+      <c r="N17" s="58" t="n">
+        <v>6300</v>
+      </c>
       <c r="O17" s="58" t="n"/>
       <c r="P17" s="58" t="n"/>
       <c r="Q17" s="58" t="n"/>
@@ -24134,8 +24303,16 @@
         <f>SUM(H17:S17)</f>
         <v/>
       </c>
-      <c r="U17" s="59" t="n"/>
-      <c r="V17" s="59" t="n"/>
+      <c r="U17" s="59" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="V17" s="59" t="inlineStr">
+        <is>
+          <t>Entrada em abr/26. R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="56">
@@ -24713,72 +24890,120 @@
       <c r="U29" s="59" t="n"/>
       <c r="V29" s="59" t="n"/>
     </row>
-    <row r="30">
-      <c r="A30" s="60" t="inlineStr">
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="56">
+        <f>Planejado!A30</f>
+        <v/>
+      </c>
+      <c r="B30" s="56">
+        <f>Planejado!B30</f>
+        <v/>
+      </c>
+      <c r="C30" s="56">
+        <f>Planejado!C30</f>
+        <v/>
+      </c>
+      <c r="D30" s="57">
+        <f>Planejado!D30</f>
+        <v/>
+      </c>
+      <c r="E30" s="57">
+        <f>Planejado!E30</f>
+        <v/>
+      </c>
+      <c r="F30" s="56">
+        <f>Planejado!F30</f>
+        <v/>
+      </c>
+      <c r="G30" s="56">
+        <f>Planejado!G30</f>
+        <v/>
+      </c>
+      <c r="H30" s="58" t="n"/>
+      <c r="I30" s="58" t="n"/>
+      <c r="J30" s="58" t="n"/>
+      <c r="K30" s="58" t="n"/>
+      <c r="L30" s="58" t="n"/>
+      <c r="M30" s="58" t="n"/>
+      <c r="N30" s="58" t="n"/>
+      <c r="O30" s="58" t="n"/>
+      <c r="P30" s="58" t="n"/>
+      <c r="Q30" s="58" t="n"/>
+      <c r="R30" s="58" t="n"/>
+      <c r="S30" s="58" t="n"/>
+      <c r="T30" s="54">
+        <f>SUM(H30:S30)</f>
+        <v/>
+      </c>
+      <c r="U30" s="59" t="n"/>
+      <c r="V30" s="59" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B30" s="60" t="n"/>
-      <c r="C30" s="60" t="n"/>
-      <c r="D30" s="60" t="n"/>
-      <c r="E30" s="60" t="n"/>
-      <c r="F30" s="60" t="n"/>
-      <c r="G30" s="60" t="n"/>
-      <c r="H30" s="61">
-        <f>SUM(H5:H29)</f>
-        <v/>
-      </c>
-      <c r="I30" s="61">
-        <f>SUM(I5:I29)</f>
-        <v/>
-      </c>
-      <c r="J30" s="61">
-        <f>SUM(J5:J29)</f>
-        <v/>
-      </c>
-      <c r="K30" s="61">
-        <f>SUM(K5:K29)</f>
-        <v/>
-      </c>
-      <c r="L30" s="61">
-        <f>SUM(L5:L29)</f>
-        <v/>
-      </c>
-      <c r="M30" s="61">
-        <f>SUM(M5:M29)</f>
-        <v/>
-      </c>
-      <c r="N30" s="61">
-        <f>SUM(N5:N29)</f>
-        <v/>
-      </c>
-      <c r="O30" s="61">
-        <f>SUM(O5:O29)</f>
-        <v/>
-      </c>
-      <c r="P30" s="61">
-        <f>SUM(P5:P29)</f>
-        <v/>
-      </c>
-      <c r="Q30" s="61">
-        <f>SUM(Q5:Q29)</f>
-        <v/>
-      </c>
-      <c r="R30" s="61">
-        <f>SUM(R5:R29)</f>
-        <v/>
-      </c>
-      <c r="S30" s="61">
-        <f>SUM(S5:S29)</f>
-        <v/>
-      </c>
-      <c r="T30" s="61">
-        <f>SUM(T5:T29)</f>
-        <v/>
-      </c>
-      <c r="U30" s="60" t="n"/>
-      <c r="V30" s="60" t="n"/>
+      <c r="B31" s="60" t="n"/>
+      <c r="C31" s="60" t="n"/>
+      <c r="D31" s="60" t="n"/>
+      <c r="E31" s="60" t="n"/>
+      <c r="F31" s="60" t="n"/>
+      <c r="G31" s="60" t="n"/>
+      <c r="H31" s="61">
+        <f>SUM(H5:H30)</f>
+        <v/>
+      </c>
+      <c r="I31" s="61">
+        <f>SUM(I5:I30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="61">
+        <f>SUM(J5:J30)</f>
+        <v/>
+      </c>
+      <c r="K31" s="61">
+        <f>SUM(K5:K30)</f>
+        <v/>
+      </c>
+      <c r="L31" s="61">
+        <f>SUM(L5:L30)</f>
+        <v/>
+      </c>
+      <c r="M31" s="61">
+        <f>SUM(M5:M30)</f>
+        <v/>
+      </c>
+      <c r="N31" s="61">
+        <f>SUM(N5:N30)</f>
+        <v/>
+      </c>
+      <c r="O31" s="61">
+        <f>SUM(O5:O30)</f>
+        <v/>
+      </c>
+      <c r="P31" s="61">
+        <f>SUM(P5:P30)</f>
+        <v/>
+      </c>
+      <c r="Q31" s="61">
+        <f>SUM(Q5:Q30)</f>
+        <v/>
+      </c>
+      <c r="R31" s="61">
+        <f>SUM(R5:R30)</f>
+        <v/>
+      </c>
+      <c r="S31" s="61">
+        <f>SUM(S5:S30)</f>
+        <v/>
+      </c>
+      <c r="T31" s="61">
+        <f>SUM(T5:T30)</f>
+        <v/>
+      </c>
+      <c r="U31" s="60" t="n"/>
+      <c r="V31" s="60" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -24883,19 +25108,19 @@
         </is>
       </c>
       <c r="B5" s="42">
-        <f>SUMIFS(Planejado!$H$5:$H$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="42">
-        <f>SUMIFS(Realizado!$H$5:$H$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="42">
-        <f>SUMIFS(Planejado!$H$5:$H$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="42">
-        <f>SUMIFS(Realizado!$H$5:$H$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="42">
@@ -24926,19 +25151,19 @@
         </is>
       </c>
       <c r="B6" s="49">
-        <f>SUMIFS(Planejado!$I$5:$I$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="49">
-        <f>SUMIFS(Realizado!$I$5:$I$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="49">
-        <f>SUMIFS(Planejado!$I$5:$I$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="49">
-        <f>SUMIFS(Realizado!$I$5:$I$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="49">
@@ -24969,19 +25194,19 @@
         </is>
       </c>
       <c r="B7" s="42">
-        <f>SUMIFS(Planejado!$J$5:$J$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="42">
-        <f>SUMIFS(Realizado!$J$5:$J$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="42">
-        <f>SUMIFS(Planejado!$J$5:$J$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="42">
-        <f>SUMIFS(Realizado!$J$5:$J$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="42">
@@ -25012,19 +25237,19 @@
         </is>
       </c>
       <c r="B8" s="49">
-        <f>SUMIFS(Planejado!$K$5:$K$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="49">
-        <f>SUMIFS(Realizado!$K$5:$K$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="49">
-        <f>SUMIFS(Planejado!$K$5:$K$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="49">
-        <f>SUMIFS(Realizado!$K$5:$K$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="49">
@@ -25055,19 +25280,19 @@
         </is>
       </c>
       <c r="B9" s="42">
-        <f>SUMIFS(Planejado!$L$5:$L$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="42">
-        <f>SUMIFS(Realizado!$L$5:$L$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="42">
-        <f>SUMIFS(Planejado!$L$5:$L$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="42">
-        <f>SUMIFS(Realizado!$L$5:$L$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="42">
@@ -25098,19 +25323,19 @@
         </is>
       </c>
       <c r="B10" s="49">
-        <f>SUMIFS(Planejado!$M$5:$M$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="49">
-        <f>SUMIFS(Realizado!$M$5:$M$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="49">
-        <f>SUMIFS(Planejado!$M$5:$M$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="49">
-        <f>SUMIFS(Realizado!$M$5:$M$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="49">
@@ -25141,19 +25366,19 @@
         </is>
       </c>
       <c r="B11" s="42">
-        <f>SUMIFS(Planejado!$N$5:$N$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="42">
-        <f>SUMIFS(Realizado!$N$5:$N$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="42">
-        <f>SUMIFS(Planejado!$N$5:$N$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="42">
-        <f>SUMIFS(Realizado!$N$5:$N$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="42">
@@ -25184,19 +25409,19 @@
         </is>
       </c>
       <c r="B12" s="49">
-        <f>SUMIFS(Planejado!$O$5:$O$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C12" s="49">
-        <f>SUMIFS(Realizado!$O$5:$O$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D12" s="49">
-        <f>SUMIFS(Planejado!$O$5:$O$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E12" s="49">
-        <f>SUMIFS(Realizado!$O$5:$O$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F12" s="49">
@@ -25227,19 +25452,19 @@
         </is>
       </c>
       <c r="B13" s="42">
-        <f>SUMIFS(Planejado!$P$5:$P$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C13" s="42">
-        <f>SUMIFS(Realizado!$P$5:$P$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D13" s="42">
-        <f>SUMIFS(Planejado!$P$5:$P$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E13" s="42">
-        <f>SUMIFS(Realizado!$P$5:$P$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F13" s="42">
@@ -25270,19 +25495,19 @@
         </is>
       </c>
       <c r="B14" s="49">
-        <f>SUMIFS(Planejado!$Q$5:$Q$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C14" s="49">
-        <f>SUMIFS(Realizado!$Q$5:$Q$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D14" s="49">
-        <f>SUMIFS(Planejado!$Q$5:$Q$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E14" s="49">
-        <f>SUMIFS(Realizado!$Q$5:$Q$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F14" s="49">
@@ -25313,19 +25538,19 @@
         </is>
       </c>
       <c r="B15" s="42">
-        <f>SUMIFS(Planejado!$R$5:$R$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C15" s="42">
-        <f>SUMIFS(Realizado!$R$5:$R$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D15" s="42">
-        <f>SUMIFS(Planejado!$R$5:$R$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E15" s="42">
-        <f>SUMIFS(Realizado!$R$5:$R$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F15" s="42">
@@ -25356,19 +25581,19 @@
         </is>
       </c>
       <c r="B16" s="49">
-        <f>SUMIFS(Planejado!$S$5:$S$29,Planejado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$30,Planejado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="C16" s="49">
-        <f>SUMIFS(Realizado!$S$5:$S$29,Realizado!$B$5:$B$29,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$30,Realizado!$B$5:$B$30,"Jurídico")</f>
         <v/>
       </c>
       <c r="D16" s="49">
-        <f>SUMIFS(Planejado!$S$5:$S$29,Planejado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$30,Planejado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="E16" s="49">
-        <f>SUMIFS(Realizado!$S$5:$S$29,Realizado!$B$5:$B$29,"TI")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$30,Realizado!$B$5:$B$30,"TI")</f>
         <v/>
       </c>
       <c r="F16" s="49">
@@ -25541,19 +25766,19 @@
         </is>
       </c>
       <c r="B5" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A5,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A5,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A5,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A5,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A5,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A5,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A5,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A5,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="42">
@@ -25573,7 +25798,7 @@
         <v/>
       </c>
       <c r="J5" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A5)</f>
         <v/>
       </c>
     </row>
@@ -25584,19 +25809,19 @@
         </is>
       </c>
       <c r="B6" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A6,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A6,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A6,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A6,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A6,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A6,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A6,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A6,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="49">
@@ -25616,7 +25841,7 @@
         <v/>
       </c>
       <c r="J6" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A6)</f>
         <v/>
       </c>
     </row>
@@ -25627,19 +25852,19 @@
         </is>
       </c>
       <c r="B7" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A7,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A7,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A7,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A7,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A7,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A7,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A7,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A7,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="42">
@@ -25659,7 +25884,7 @@
         <v/>
       </c>
       <c r="J7" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A7)</f>
         <v/>
       </c>
     </row>
@@ -25670,19 +25895,19 @@
         </is>
       </c>
       <c r="B8" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A8,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A8,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A8,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A8,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A8,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A8,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A8,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A8,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="49">
@@ -25702,7 +25927,7 @@
         <v/>
       </c>
       <c r="J8" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A8)</f>
         <v/>
       </c>
     </row>
@@ -25713,19 +25938,19 @@
         </is>
       </c>
       <c r="B9" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A9,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A9,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A9,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A9,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A9,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A9,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A9,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A9,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="42">
@@ -25745,7 +25970,7 @@
         <v/>
       </c>
       <c r="J9" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A9)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A9)</f>
         <v/>
       </c>
     </row>
@@ -25756,19 +25981,19 @@
         </is>
       </c>
       <c r="B10" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A10,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A10,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A10,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A10,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A10,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A10,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A10,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A10,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="49">
@@ -25788,7 +26013,7 @@
         <v/>
       </c>
       <c r="J10" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A10)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A10)</f>
         <v/>
       </c>
     </row>
@@ -25799,19 +26024,19 @@
         </is>
       </c>
       <c r="B11" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A11,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A11,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A11,Comparativo!$B$6:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A11,Comparativo!$B$6:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$30,Comparativo!$E$6:$E$30,$A11,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A11,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$30,Comparativo!$E$6:$E$30,$A11,Comparativo!$B$6:$B$30,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A11,Comparativo!$B$6:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="42">
@@ -25831,7 +26056,7 @@
         <v/>
       </c>
       <c r="J11" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$29,Planejado!$G$5:$G$29,$A11)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A11)</f>
         <v/>
       </c>
     </row>
@@ -25901,7 +26126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -26264,7 +26489,7 @@
       </c>
       <c r="D14" s="72" t="inlineStr">
         <is>
-          <t>Só os dois primeiros credores do Jurídico superam o orçamento anual inteiro do departamento. Decidir na reunião quais entram no centro de custo da área — e, para os que entrarem, criar linha no orçamento, senão aparecerão como 'Não orçado' e distorcerão o comparativo.</t>
+          <t>Só os dois primeiros credores do Jurídico superam o orçamento anual inteiro do departamento. ATENÇÃO: parte desses valores pode ser repasse ou custa reembolsável pelo cliente, e não custo da área — foi o caso da Dra. Michele (ver item P). Separar o que é custo antes de decidir. Para os que entrarem no centro de custo, criar linha no orçamento, senão aparecerão como 'Não orçado' e distorcerão o comparativo.</t>
         </is>
       </c>
       <c r="E14" s="72" t="inlineStr">
@@ -26441,22 +26666,22 @@
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="71" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B20" s="72" t="inlineStr">
         <is>
-          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
+          <t>Dra. Michele fora do orçamento — INCLUIR</t>
         </is>
       </c>
       <c r="C20" s="72" t="inlineStr">
         <is>
-          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
+          <t>Advogada que presta serviço ao departamento e não foi incluída na ficha. Recebe R$ 2.750/mês fixos desde jul/26. A linha foi criada com planejado zerado, à espera da definição.</t>
         </is>
       </c>
       <c r="D20" s="72" t="inlineStr">
         <is>
-          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
+          <t>A R$ 2.750/mês são R$ 33.000/ano, que hoje não têm previsão. Enquanto o planejado for zero, a linha aparece como 'Não orçado' e o valor entra inteiro como estouro. Definir o valor a orçar e a partir de quando.</t>
         </is>
       </c>
       <c r="E20" s="72" t="inlineStr">
@@ -26473,123 +26698,123 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="68" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B21" s="69" t="inlineStr">
         <is>
-          <t>Ferramentas de IA sem orçamento — DEFINIR META</t>
+          <t>Extrato contém REPASSES, não só custo</t>
         </is>
       </c>
       <c r="C21" s="69" t="inlineStr">
         <is>
-          <t>Claude, GPT, Adapta One e Adapta Skip são gastos que existem hoje e não constavam na ficha. Foram criadas quatro linhas separadas, com planejado zerado, para a meta ser definida junto com a diretoria.</t>
+          <t>Os lançamentos em nome da Dra. Michele até jun/26 (R$ 20.821,53) são repasse: o cliente paga à empresa e a empresa repassa a ela. Não são custo do departamento e por isso não foram lançados no realizado.</t>
         </is>
       </c>
       <c r="D21" s="69" t="inlineStr">
         <is>
-          <t>Enquanto o planejado for zero, qualquer lançamento nessas linhas aparece como 'Não orçado'. Conferir também se há sobreposição com a linha 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano — pode ser que ela já cubra o Adapta One e o Adapta Skip. E confirmar o nome exato do 'Adapta Skip'.</t>
+          <t>Vale a mesma checagem nos outros credores das abas 'Contas Pagas' antes de usá-los como custo — em especial custas processuais e honorários de terceiros, que podem ser reembolsados pelo cliente. O total de R$ 446.577,92 do centro de custo Jurídico no extrato NÃO é despesa líquida do departamento.</t>
         </is>
       </c>
       <c r="E21" s="69" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F21" s="75" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F21" s="76" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B22" s="72" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos de TI</t>
+          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
         </is>
       </c>
       <c r="C22" s="72" t="inlineStr">
         <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
+          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
         </is>
       </c>
       <c r="D22" s="72" t="inlineStr">
         <is>
-          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
+          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
         </is>
       </c>
       <c r="E22" s="72" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
-        </is>
-      </c>
-      <c r="F22" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F22" s="75" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B23" s="69" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Ferramentas de IA sem orçamento — DEFINIR META</t>
         </is>
       </c>
       <c r="C23" s="69" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>Claude, GPT, Adapta One e Adapta Skip são gastos que existem hoje e não constavam na ficha. Foram criadas quatro linhas separadas, com planejado zerado, para a meta ser definida junto com a diretoria.</t>
         </is>
       </c>
       <c r="D23" s="69" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>Enquanto o planejado for zero, qualquer lançamento nessas linhas aparece como 'Não orçado'. Conferir também se há sobreposição com a linha 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano — pode ser que ela já cubra o Adapta One e o Adapta Skip. E confirmar o nome exato do 'Adapta Skip'.</t>
         </is>
       </c>
       <c r="E23" s="69" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F23" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F23" s="75" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B24" s="72" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Rateio dos softwares corporativos de TI</t>
         </is>
       </c>
       <c r="C24" s="72" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
         </is>
       </c>
       <c r="D24" s="72" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
         </is>
       </c>
       <c r="E24" s="72" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Controladoria</t>
         </is>
       </c>
       <c r="F24" s="74" t="inlineStr">
@@ -26601,30 +26826,94 @@
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="68" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="69" t="inlineStr">
+        <is>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
+        </is>
+      </c>
+      <c r="C25" s="69" t="inlineStr">
+        <is>
+          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+        </is>
+      </c>
+      <c r="D25" s="69" t="inlineStr">
+        <is>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+        </is>
+      </c>
+      <c r="E25" s="69" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F25" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="72" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C26" s="72" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D26" s="72" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E26" s="72" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F26" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="68" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B25" s="69" t="inlineStr">
+      <c r="B27" s="69" t="inlineStr">
         <is>
           <t>Competência x caixa — DEFASAGEM CONFIRMADA</t>
         </is>
       </c>
-      <c r="C25" s="69" t="inlineStr">
+      <c r="C27" s="69" t="inlineStr">
         <is>
           <t>O pagamento do Miguel de 01/08/26 refere-se a julho, então há pelo menos um prestador cujo pagamento cai no mês seguinte ao da prestação. Todo o realizado está lançado por CAIXA (mês em que o pagamento saiu), que é como os valores foram informados.</t>
         </is>
       </c>
-      <c r="D25" s="69" t="inlineStr">
+      <c r="D27" s="69" t="inlineStr">
         <is>
           <t>Consequência: o valor lançado em jan/26 pode ser referente a dez/2025, e o serviço de dez/26 só aparecerá em jan/2027 — o ano fecha com 12 pagamentos, mas defasados em relação ao orçamento, que é de competência. Com a extração vindo do SIENGE, basta escolher o regime na hora de gerar o relatório: definir isso UMA vez e manter, para o histórico não misturar critérios.</t>
         </is>
       </c>
-      <c r="E25" s="69" t="inlineStr">
+      <c r="E27" s="69" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F25" s="76" t="inlineStr">
+      <c r="F27" s="76" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -21514,7 +21514,7 @@
       </c>
       <c r="E8" s="41" t="inlineStr">
         <is>
-          <t>Advogada — NÃO CONSTAVA NA FICHA. R$ 2.750/mês fixos desde jul/26. Planejado a definir com a diretoria</t>
+          <t>Advogada — R$ 2.750/mês fixos desde jan/26. Não constava na ficha por esquecimento na montagem do orçamento; incluída na revisão</t>
         </is>
       </c>
       <c r="F8" s="40" t="inlineStr">
@@ -21528,40 +21528,40 @@
         </is>
       </c>
       <c r="H8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="I8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="J8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="K8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="L8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="M8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="N8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="O8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="P8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="Q8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="R8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="S8" s="42" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="T8" s="54">
         <f>SUM(H8:S8)</f>
@@ -23646,22 +23646,22 @@
         <v/>
       </c>
       <c r="H8" s="58" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="I8" s="58" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="J8" s="58" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="K8" s="58" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="L8" s="58" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="M8" s="58" t="n">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="N8" s="58" t="n">
         <v>2750</v>
@@ -23677,12 +23677,12 @@
       </c>
       <c r="U8" s="59" t="inlineStr">
         <is>
-          <t>Extrato do financeiro</t>
+          <t>Gestora, 05/08/26</t>
         </is>
       </c>
       <c r="V8" s="59" t="inlineStr">
         <is>
-          <t>R$ 2.750/mês fixos a partir de jul/26. Os demais lançamentos em nome dela no extrato são REPASSE de honorários pagos pelo cliente — não são custo do departamento</t>
+          <t>R$ 2.750/mês fixos desde jan/26. Os demais lançamentos em nome dela no extrato são REPASSE de honorários pagos pelo cliente — não são custo do departamento</t>
         </is>
       </c>
     </row>
@@ -26671,27 +26671,27 @@
       </c>
       <c r="B20" s="72" t="inlineStr">
         <is>
-          <t>Dra. Michele fora do orçamento — INCLUIR</t>
+          <t>Dra. Michele incluída no orçamento</t>
         </is>
       </c>
       <c r="C20" s="72" t="inlineStr">
         <is>
-          <t>Advogada que presta serviço ao departamento e não foi incluída na ficha. Recebe R$ 2.750/mês fixos desde jul/26. A linha foi criada com planejado zerado, à espera da definição.</t>
+          <t>Mão de obra que ficou de fora da ficha por esquecimento na montagem do orçamento. Orçada em R$ 2.750/mês pelo ano inteiro, valor fixo em vigor desde jan/26.</t>
         </is>
       </c>
       <c r="D20" s="72" t="inlineStr">
         <is>
-          <t>A R$ 2.750/mês são R$ 33.000/ano, que hoje não têm previsão. Enquanto o planejado for zero, a linha aparece como 'Não orçado' e o valor entra inteiro como estouro. Definir o valor a orçar e a partir de quando.</t>
+          <t>Acréscimo de R$ 33.000 ao orçamento do Jurídico, que passa a R$ 324.730,42. CONFERIR NO SIENGE: no extrato de contas pagas, o único lançamento isolado de R$ 2.750 é o de jul/26 — de jan a jun aparecem apenas honorários por processo, que são repasse (item P). Ou os pagamentos do fixo de jan a jun saíram por outro centro de custo, ou estão embutidos naqueles lançamentos. Vale localizar antes da reunião. A justificativa da inclusão é pauta.</t>
         </is>
       </c>
       <c r="E20" s="72" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F20" s="75" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F20" s="76" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -26681,17 +26681,17 @@
       </c>
       <c r="D20" s="72" t="inlineStr">
         <is>
-          <t>Acréscimo de R$ 33.000 ao orçamento do Jurídico, que passa a R$ 324.730,42. CONFERIR NO SIENGE: no extrato de contas pagas, o único lançamento isolado de R$ 2.750 é o de jul/26 — de jan a jun aparecem apenas honorários por processo, que são repasse (item P). Ou os pagamentos do fixo de jan a jun saíram por outro centro de custo, ou estão embutidos naqueles lançamentos. Vale localizar antes da reunião. A justificativa da inclusão é pauta.</t>
+          <t>Acréscimo de R$ 33.000 ao orçamento do Jurídico, que passa a R$ 324.730,42. No extrato, o fixo de jan a jun vem somado aos honorários de repasse no mesmo credor: o total mensal (R$ 3.739 a R$ 4.326) é o fixo de R$ 2.750 mais o repasse, que o cliente paga e a empresa apenas transfere. Só jun/26 fica abaixo do fixo (R$ 1.036,92), provavelmente porque o pagamento daquele mês caiu em jul — é o lançamento isolado de R$ 2.750 que aparece lá. A justificativa da inclusão é pauta da reunião.</t>
         </is>
       </c>
       <c r="E20" s="72" t="inlineStr">
         <is>
-          <t>Cristiane + Financeiro</t>
-        </is>
-      </c>
-      <c r="F20" s="76" t="inlineStr">
-        <is>
-          <t>CONFERIR</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F20" s="73" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -28719,12 +28719,12 @@
       </c>
       <c r="C27" s="69" t="inlineStr">
         <is>
-          <t>Confirmado pela gestora: TODOS os PJs prestam o serviço e recebem no mês seguinte. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
+          <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
       <c r="D27" s="69" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios.</t>
+          <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
       <c r="E27" s="69" t="inlineStr">

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -23994,7 +23994,7 @@
       </c>
       <c r="E17" s="48" t="inlineStr">
         <is>
-          <t>Consultor — entrada em abr/26 (9 meses), conforme o total da ficha original</t>
+          <t>Consultor — orçado desde jan/26. As atividades só começaram em abr/26: a contratação foi segurada por três meses</t>
         </is>
       </c>
       <c r="F17" s="47" t="inlineStr">
@@ -24008,13 +24008,13 @@
         </is>
       </c>
       <c r="H17" s="49" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="J17" s="49" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="K17" s="49" t="n">
         <v>10000</v>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="V17" s="59" t="inlineStr">
         <is>
-          <t>Entrada em abr/26. R$ 3.700/mês abaixo do contratado — confirmar escopo</t>
+          <t>Sem custo em jan–mar (contratação segurada). R$ 6.300/mês a partir de abr, contra R$ 10.000 orçados</t>
         </is>
       </c>
     </row>
@@ -28170,17 +28170,17 @@
       </c>
       <c r="B10" s="72" t="inlineStr">
         <is>
-          <t>Jonathan R$ 3.700/mês abaixo do contratado</t>
+          <t>Jonathan — economia de R$ 44.800 até julho</t>
         </is>
       </c>
       <c r="C10" s="72" t="inlineStr">
         <is>
-          <t>Orçado R$ 10.000/mês, realizado R$ 6.300/mês em mai, jun e jul.</t>
+          <t>Orçado R$ 10.000/mês desde jan/26. A contratação foi segurada e as atividades só começaram em abr/26, a R$ 6.300/mês. Resultado: três meses sem custo (R$ 30.000) e quatro meses a R$ 3.700 abaixo do orçado (R$ 14.800).</t>
         </is>
       </c>
       <c r="D10" s="72" t="inlineStr">
         <is>
-          <t>Maior desvio em reais de todo o orçamento: R$ 11.100 em três meses. Se o valor menor for o novo padrão, o planejado de ago a dez deve ser revisado para baixo — sobrariam R$ 18.500 no orçamento do TI.</t>
+          <t>É de longe a maior economia das duas áreas: R$ 44.800 em sete meses, e decorre de decisão de gestão, não de erro de orçamento. Se o valor de R$ 6.300 se mantiver até dez, somam-se outros R$ 18.500 — total de R$ 63.300 no ano. Vale destacar na apresentação à diretoria.</t>
         </is>
       </c>
       <c r="E10" s="72" t="inlineStr">
@@ -28188,9 +28188,9 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F10" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F10" s="73" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
@@ -28362,17 +28362,17 @@
       </c>
       <c r="B16" s="72" t="inlineStr">
         <is>
-          <t>Base de meses — reconciliada com a ficha original</t>
+          <t>Base de meses do TI — Jonathan corrigido para 12 meses</t>
         </is>
       </c>
       <c r="C16" s="72" t="inlineStr">
         <is>
-          <t>A ficha trazia a coluna TOTAL do TI digitada à mão em bases diferentes por pessoa (Vinicius e Elias em 12 meses, Jonathan em 9) enquanto o grid mensal tinha só 8 colunas. Com o período em jan–dez os três totais batem exatamente: R$ 64.998,30 + R$ 12.780,00 + R$ 90.000,00 = R$ 167.778,30, o valor da ficha. Não era erro de digitação — era o grid que estava incompleto.</t>
+          <t>A ficha trazia os totais do TI digitados à mão: Vinicius e Elias em 12 meses (R$ 64.998,30 e R$ 12.780,00, ambos confirmados) e Jonathan em 9 meses (R$ 90.000). A gestora confirmou que o orçamento dele valia desde jan/26, ou seja, 12 meses — os R$ 90.000 da ficha não refletiam o orçamento aprovado.</t>
         </is>
       </c>
       <c r="D16" s="72" t="inlineStr">
         <is>
-          <t>Equipe de TI no valor original de R$ 167.778,30. Jonathan lançado com entrada em abr/26 (9 meses), que é o que explica os R$ 90.000.</t>
+          <t>Equipe de TI passa de R$ 167.778,30 para R$ 197.778,30 (+R$ 30.000). Os R$ 167.778,30 da ficha continuam batendo com Vinicius e Elias, mas a linha do Jonathan estava subdimensionada em 3 meses.</t>
         </is>
       </c>
       <c r="E16" s="72" t="inlineStr">

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -24647,7 +24647,7 @@
       </c>
       <c r="E26" s="48" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas</t>
         </is>
       </c>
       <c r="F26" s="47" t="inlineStr"/>
@@ -24720,7 +24720,7 @@
       </c>
       <c r="E27" s="48" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas</t>
         </is>
       </c>
       <c r="F27" s="47" t="inlineStr"/>
@@ -24793,7 +24793,7 @@
       </c>
       <c r="E28" s="48" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
         </is>
       </c>
       <c r="F28" s="47" t="inlineStr"/>
@@ -24866,7 +24866,7 @@
       </c>
       <c r="E29" s="48" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
         </is>
       </c>
       <c r="F29" s="47" t="inlineStr"/>
@@ -28586,17 +28586,17 @@
       </c>
       <c r="B23" s="69" t="inlineStr">
         <is>
-          <t>Ferramentas de IA sem orçamento — DEFINIR META</t>
+          <t>Ferramentas de IA — DEFINIR META E RATEIO</t>
         </is>
       </c>
       <c r="C23" s="69" t="inlineStr">
         <is>
-          <t>Claude, GPT, Adapta One e Adapta Skip são gastos que existem hoje e não constavam na ficha. Foram criadas quatro linhas separadas, com planejado zerado, para a meta ser definida junto com a diretoria.</t>
+          <t>Claude, GPT, Adapta One e Adapta Skip existem hoje e não constavam na ficha. Quatro linhas criadas com planejado zerado, à espera da meta. Todas marcadas com RATEIO A DEFINIR: são de uso transversal, não exclusivo do TI.</t>
         </is>
       </c>
       <c r="D23" s="69" t="inlineStr">
         <is>
-          <t>Enquanto o planejado for zero, qualquer lançamento nessas linhas aparece como 'Não orçado'. Conferir também se há sobreposição com a linha 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano — pode ser que ela já cubra o Adapta One e o Adapta Skip. E confirmar o nome exato do 'Adapta Skip'.</t>
+          <t>O rateio já acontece de fato, mas sem regra: no extrato, a OpenAI (R$ 5.950,10) caiu no centro de custo do TI e o Adapta (R$ 3.351) caiu no Jurídico — mesma natureza de gasto, centros diferentes por acaso. Sem critério definido, o TI absorve custo de ferramenta que a empresa inteira usa e aparece caro na comparação, enquanto as áreas usuárias não enxergam o que consomem. Sugestão: manter o contrato centralizado no TI (facilita negociação e controle de licenças) e ratear o custo por usuário ativo, que é métrica que as próprias plataformas fornecem. Conferir também a sobreposição com 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano, e o nome exato do 'Adapta Skip'.</t>
         </is>
       </c>
       <c r="E23" s="69" t="inlineStr">
@@ -28618,17 +28618,17 @@
       </c>
       <c r="B24" s="72" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos de TI</t>
+          <t>Rateio dos softwares corporativos e das IAs</t>
         </is>
       </c>
       <c r="C24" s="72" t="inlineStr">
         <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo'. Total no ano: R$ 34.680.</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo' — R$ 34.680 no ano. Somam-se a eles as quatro ferramentas de IA do item L, também de uso transversal.</t>
         </is>
       </c>
       <c r="D24" s="72" t="inlineStr">
         <is>
-          <t>São 39% das despesas do TI. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro.</t>
+          <t>São 39% das despesas orçadas do TI, mais o que vier das IAs. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro. Tratar os dois blocos com o mesmo critério de rateio, para não criar duas regras diferentes.</t>
         </is>
       </c>
       <c r="E24" s="72" t="inlineStr">

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -24217,7 +24217,7 @@
       </c>
       <c r="E20" s="48" t="inlineStr">
         <is>
-          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR</t>
+          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR. Pagamentos reais de R$ 575/mês estão lançados no centro de custo Jurídico por engano (ver pendência Q)</t>
         </is>
       </c>
       <c r="F20" s="47" t="inlineStr"/>
@@ -27945,7 +27945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -28517,22 +28517,22 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="68" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B21" s="69" t="inlineStr">
         <is>
-          <t>Extrato contém REPASSES, não só custo</t>
+          <t>Adapta lançado no centro de custo errado — RECLASSIFICAR</t>
         </is>
       </c>
       <c r="C21" s="69" t="inlineStr">
         <is>
-          <t>Os lançamentos em nome da Dra. Michele até jun/26 (R$ 20.821,53) são repasse: o cliente paga à empresa e a empresa repassa a ela. Não são custo do departamento e por isso não foram lançados no realizado.</t>
+          <t>Os pagamentos do Adapta (ADAPTA EDUCACAO LTDA, contrato 4134643529) estão no centro de custo Jurídico no SIENGE: R$ 575,00/mês de jan a mai e R$ 476,00 em jun, todos com vencimento dia 15. Total de R$ 3.351,00 em seis meses. Não é despesa do Jurídico — é ferramenta de IA, de uso transversal.</t>
         </is>
       </c>
       <c r="D21" s="69" t="inlineStr">
         <is>
-          <t>Vale a mesma checagem nos outros credores das abas 'Contas Pagas' antes de usá-los como custo — em especial custas processuais e honorários de terceiros, que podem ser reembolsados pelo cliente. O total de R$ 446.577,92 do centro de custo Jurídico no extrato NÃO é despesa líquida do departamento.</t>
+          <t>Reclassificar no SIENGE para o centro de custo correto e aplicar o rateio do item L. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado. Aproveitar a abertura do novo centro de custo para acertar a classificação desde a origem.</t>
         </is>
       </c>
       <c r="E21" s="69" t="inlineStr">
@@ -28540,63 +28540,63 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F21" s="76" t="inlineStr">
-        <is>
-          <t>CONFERIR</t>
+      <c r="F21" s="70" t="inlineStr">
+        <is>
+          <t>RECLASSIFICAR</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="71" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B22" s="72" t="inlineStr">
         <is>
-          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
+          <t>Extrato contém REPASSES, não só custo</t>
         </is>
       </c>
       <c r="C22" s="72" t="inlineStr">
         <is>
-          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
+          <t>Os lançamentos em nome da Dra. Michele até jun/26 (R$ 20.821,53) são repasse: o cliente paga à empresa e a empresa repassa a ela. Não são custo do departamento e por isso não foram lançados no realizado.</t>
         </is>
       </c>
       <c r="D22" s="72" t="inlineStr">
         <is>
-          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
+          <t>Vale a mesma checagem nos outros credores das abas 'Contas Pagas' antes de usá-los como custo — em especial custas processuais e honorários de terceiros, que podem ser reembolsados pelo cliente. O total de R$ 446.577,92 do centro de custo Jurídico no extrato NÃO é despesa líquida do departamento.</t>
         </is>
       </c>
       <c r="E22" s="72" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F22" s="75" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F22" s="76" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="68" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B23" s="69" t="inlineStr">
         <is>
-          <t>Ferramentas de IA — DEFINIR META E RATEIO</t>
+          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
         </is>
       </c>
       <c r="C23" s="69" t="inlineStr">
         <is>
-          <t>Claude, GPT, Adapta One e Adapta Skip existem hoje e não constavam na ficha. Quatro linhas criadas com planejado zerado, à espera da meta. Todas marcadas com RATEIO A DEFINIR: são de uso transversal, não exclusivo do TI.</t>
+          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
         </is>
       </c>
       <c r="D23" s="69" t="inlineStr">
         <is>
-          <t>O rateio já acontece de fato, mas sem regra: no extrato, a OpenAI (R$ 5.950,10) caiu no centro de custo do TI e o Adapta (R$ 3.351) caiu no Jurídico — mesma natureza de gasto, centros diferentes por acaso. Sem critério definido, o TI absorve custo de ferramenta que a empresa inteira usa e aparece caro na comparação, enquanto as áreas usuárias não enxergam o que consomem. Sugestão: manter o contrato centralizado no TI (facilita negociação e controle de licenças) e ratear o custo por usuário ativo, que é métrica que as próprias plataformas fornecem. Conferir também a sobreposição com 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano, e o nome exato do 'Adapta Skip'.</t>
+          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
         </is>
       </c>
       <c r="E23" s="69" t="inlineStr">
@@ -28613,59 +28613,59 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B24" s="72" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos e das IAs</t>
+          <t>Ferramentas de IA — DEFINIR META E RATEIO</t>
         </is>
       </c>
       <c r="C24" s="72" t="inlineStr">
         <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo' — R$ 34.680 no ano. Somam-se a eles as quatro ferramentas de IA do item L, também de uso transversal.</t>
+          <t>Claude, GPT, Adapta One e Adapta Skip existem hoje e não constavam na ficha. Quatro linhas criadas com planejado zerado, à espera da meta. Todas marcadas com RATEIO A DEFINIR: são de uso transversal, não exclusivo do TI.</t>
         </is>
       </c>
       <c r="D24" s="72" t="inlineStr">
         <is>
-          <t>São 39% das despesas orçadas do TI, mais o que vier das IAs. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro. Tratar os dois blocos com o mesmo critério de rateio, para não criar duas regras diferentes.</t>
+          <t>O rateio já acontece de fato, mas sem regra: no extrato, a OpenAI (R$ 5.950,10) caiu no centro de custo do TI e o Adapta (R$ 3.351) caiu no Jurídico — mesma natureza de gasto, centros diferentes por acaso. Sem critério definido, o TI absorve custo de ferramenta que a empresa inteira usa e aparece caro na comparação, enquanto as áreas usuárias não enxergam o que consomem. Sugestão: manter o contrato centralizado no TI (facilita negociação e controle de licenças) e ratear o custo por usuário ativo, que é métrica que as próprias plataformas fornecem. Conferir também a sobreposição com 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano, e o nome exato do 'Adapta Skip'.</t>
         </is>
       </c>
       <c r="E24" s="72" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
-        </is>
-      </c>
-      <c r="F24" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F24" s="75" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B25" s="69" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Rateio dos softwares corporativos e das IAs</t>
         </is>
       </c>
       <c r="C25" s="69" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo' — R$ 34.680 no ano. Somam-se a eles as quatro ferramentas de IA do item L, também de uso transversal.</t>
         </is>
       </c>
       <c r="D25" s="69" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>São 39% das despesas orçadas do TI, mais o que vier das IAs. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro. Tratar os dois blocos com o mesmo critério de rateio, para não criar duas regras diferentes.</t>
         </is>
       </c>
       <c r="E25" s="69" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Controladoria</t>
         </is>
       </c>
       <c r="F25" s="74" t="inlineStr">
@@ -28677,22 +28677,22 @@
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B26" s="72" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Sala de Reunião — recorrente ou pontual?</t>
         </is>
       </c>
       <c r="C26" s="72" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
         </is>
       </c>
       <c r="D26" s="72" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
         </is>
       </c>
       <c r="E26" s="72" t="inlineStr">
@@ -28709,30 +28709,62 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="68" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="69" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C27" s="69" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D27" s="69" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E27" s="69" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F27" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="71" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B27" s="69" t="inlineStr">
+      <c r="B28" s="72" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C27" s="69" t="inlineStr">
+      <c r="C28" s="72" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D27" s="69" t="inlineStr">
+      <c r="D28" s="72" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E27" s="69" t="inlineStr">
+      <c r="E28" s="72" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F27" s="76" t="inlineStr">
+      <c r="F28" s="76" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -28682,27 +28682,27 @@
       </c>
       <c r="B26" s="72" t="inlineStr">
         <is>
-          <t>Sala de Reunião — recorrente ou pontual?</t>
+          <t>Sala de Reunião — EXECUTAR, PAUSAR OU REPENSAR?</t>
         </is>
       </c>
       <c r="C26" s="72" t="inlineStr">
         <is>
-          <t>R$ 2.800/mês × 12 = R$ 33.600 diluídos linearmente, classificados em Móveis e Utensílios.</t>
+          <t>Projeto orçado em R$ 2.800/mês × 12 = R$ 33.600, classificado em Móveis e Utensílios, sem nenhum lançamento até jul/26. A gestora levanta que a sala já não comporta todas as pessoas, então investir na configuração atual pode não resolver o problema real. Três caminhos: executar como está, pausar, ou repensar a solução (outro espaço, formato híbrido, mais de uma sala).</t>
         </is>
       </c>
       <c r="D26" s="72" t="inlineStr">
         <is>
-          <t>Se for compra pontual (CAPEX), o desvio mensal vai acusar alarme falso todo mês até a compra acontecer, e um pico no mês da compra.</t>
+          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer.</t>
         </is>
       </c>
       <c r="E26" s="72" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F26" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F26" s="75" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -27945,7 +27945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -28709,62 +28709,94 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B27" s="69" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Notebooks — TI compra, mas não enxerga o saldo das áreas</t>
         </is>
       </c>
       <c r="C27" s="69" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Cada área tem a própria linha de orçamento para notebooks, mas é o TI que recebe a solicitação e executa a compra quando surge a necessidade. Hoje o TI não tem acompanhamento do orçamento das outras áreas, então aprova pedidos sem saber quanto resta em cada uma.</t>
         </is>
       </c>
       <c r="D27" s="69" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>O TI vira o executor de um estouro que não é dele e que ninguém percebe antes de acontecer — a área descobre no fechamento, quando já comprou. Proposta: o TI passa a acompanhar o saldo da rubrica de notebooks de cada área e avisa quando a solicitação for levar ao estouro, antes de comprar. Com o centro de custo no SIENGE, esse acompanhamento sai do mesmo relatório. Definir com a diretoria quem dá o aval quando o saldo acabar: a área solicitante, o TI ou a controladoria.</t>
         </is>
       </c>
       <c r="E27" s="69" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F27" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F27" s="75" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="71" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="72" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C28" s="72" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D28" s="72" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E28" s="72" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F28" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="68" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B28" s="72" t="inlineStr">
+      <c r="B29" s="69" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C28" s="72" t="inlineStr">
+      <c r="C29" s="69" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D28" s="72" t="inlineStr">
+      <c r="D29" s="69" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E28" s="72" t="inlineStr">
+      <c r="E29" s="69" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F28" s="76" t="inlineStr">
+      <c r="F29" s="76" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -27945,7 +27945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -28741,22 +28741,22 @@
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B28" s="72" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Rubricas genéricas — detalhar no lançamento, não no orçamento</t>
         </is>
       </c>
       <c r="C28" s="72" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Rubricas como 'Peças de Manutenção' (R$ 9.720/ano) agrupam itens de naturezas diferentes: mouse, teclado, carregador, tela, carcaça. Sem detalhe, não dá para saber o que puxa o gasto. A alternativa de criar uma linha por item foi avaliada e descartada por ora.</t>
         </is>
       </c>
       <c r="D28" s="72" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>DECIDIDO: manter uma linha de orçamento e detalhar na DESCRIÇÃO do lançamento no SIENGE, com padrão fixo ('Peças – mouse', 'Peças – tela'). Motivos: (1) não há histórico — as despesas do TI ainda não têm lançamento, então orçar item a item seria estimativa sem base, e cada linha acusaria desvio pela divisão errada, não pelo gasto; (2) cinco linhas viram cinco lançamentos mensais para uma rubrica que é 11% das despesas da área; (3) o plano de contas é definido pela controladoria, então subitens no orçamento não mudariam a classificação contábil. Em jan/27, com seis meses de dados reais, reavaliar. Se separar, separar por NATUREZA (reposição x reparo), que é o que dá leitura gerencial, e não item a item. Mesmo critério vale para 'Equipamentos Eletrônicos Diversos' e demais rubricas genéricas.</t>
         </is>
       </c>
       <c r="E28" s="72" t="inlineStr">
@@ -28764,39 +28764,71 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F28" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F28" s="73" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="68" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="69" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C29" s="69" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D29" s="69" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E29" s="69" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F29" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="71" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B29" s="69" t="inlineStr">
+      <c r="B30" s="72" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C29" s="69" t="inlineStr">
+      <c r="C30" s="72" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D29" s="69" t="inlineStr">
+      <c r="D30" s="72" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E29" s="69" t="inlineStr">
+      <c r="E30" s="72" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F29" s="76" t="inlineStr">
+      <c r="F30" s="76" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>
@@ -28817,7 +28849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -28910,134 +28942,156 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>COMO LER OS NÚMEROS</t>
+          <t>PADRÃO DE DESCRIÇÃO</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="77" t="inlineStr">
         <is>
-          <t>Desvio positivo (vermelho)</t>
+          <t>Rubricas genéricas</t>
         </is>
       </c>
       <c r="B12" s="78" t="inlineStr">
         <is>
-          <t>Gastou ACIMA do orçado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="77" t="inlineStr">
-        <is>
-          <t>Desvio negativo (verde)</t>
-        </is>
-      </c>
-      <c r="B13" s="78" t="inlineStr">
-        <is>
-          <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="77" t="inlineStr">
-        <is>
-          <t>Planejado acum.</t>
-        </is>
-      </c>
-      <c r="B14" s="78" t="inlineStr">
-        <is>
-          <t>Soma de maio até o mês selecionado.</t>
+          <t>Em linhas que agrupam itens variados (peças de manutenção, equipamentos diversos), detalhe o item na descrição do lançamento no SIENGE, sempre no mesmo padrão: 'Peças – mouse', 'Peças – tela'. O orçamento fica numa linha só e o detalhe sai por filtro quando precisar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>COMO LER OS NÚMEROS</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="77" t="inlineStr">
         <is>
-          <t>% Executado</t>
+          <t>Desvio positivo (vermelho)</t>
         </is>
       </c>
       <c r="B15" s="78" t="inlineStr">
         <is>
-          <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
+          <t>Gastou ACIMA do orçado.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="77" t="inlineStr">
         <is>
-          <t>Sem lançamento</t>
+          <t>Desvio negativo (verde)</t>
         </is>
       </c>
       <c r="B16" s="78" t="inlineStr">
         <is>
-          <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="8" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>REGRAS DA PLANILHA</t>
+          <t>Gastou ABAIXO do orçado — economia ou despesa ainda não realizada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="77" t="inlineStr">
+        <is>
+          <t>Planejado acum.</t>
+        </is>
+      </c>
+      <c r="B17" s="78" t="inlineStr">
+        <is>
+          <t>Soma de maio até o mês selecionado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="77" t="inlineStr">
+        <is>
+          <t>% Executado</t>
+        </is>
+      </c>
+      <c r="B18" s="78" t="inlineStr">
+        <is>
+          <t>Realizado acumulado ÷ Planejado acumulado. Perto de 100% = no ritmo.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="77" t="inlineStr">
         <is>
+          <t>Sem lançamento</t>
+        </is>
+      </c>
+      <c r="B19" s="78" t="inlineStr">
+        <is>
+          <t>Nada foi lançado no realizado ainda — não confunda com economia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>REGRAS DA PLANILHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="77" t="inlineStr">
+        <is>
           <t>Não altere</t>
         </is>
       </c>
-      <c r="B19" s="78" t="inlineStr">
+      <c r="B22" s="78" t="inlineStr">
         <is>
           <t>As colunas de identificação da aba Realizado (A a G) são fórmulas que espelham a aba Planejado. Alterar quebra o comparativo.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="77" t="inlineStr">
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="77" t="inlineStr">
         <is>
           <t>Nova linha de orçamento</t>
         </is>
       </c>
-      <c r="B20" s="78" t="inlineStr">
+      <c r="B23" s="78" t="inlineStr">
         <is>
           <t>Insira na aba Planejado e replique a mesma linha na aba Realizado e na aba Comparativo, mantendo o mesmo ID.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="77" t="inlineStr">
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="77" t="inlineStr">
         <is>
           <t>Revisão de orçamento</t>
         </is>
       </c>
-      <c r="B21" s="78" t="inlineStr">
+      <c r="B24" s="78" t="inlineStr">
         <is>
           <t>Se a diretoria aprovar um valor novo, altere na aba Planejado e registre o motivo na aba Pendências.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B13:C13"/>
+  <mergeCells count="20">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -28287,7 +28287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -29034,7 +29034,7 @@
       </c>
       <c r="D26" s="72" t="inlineStr">
         <is>
-          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer.</t>
+          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. SEPARAR OS ITENS: a descrição na ficha mistura infraestrutura de reunião (câmeras, microfones, cadeiras) com material de consumo e brindes (canetas, blocos personalizados, copos, cafeteira). O segundo grupo é papelaria e deveria estar no Administrativo, não no TI (item U).</t>
         </is>
       </c>
       <c r="E26" s="72" t="inlineStr">
@@ -29147,62 +29147,94 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B30" s="72" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Papelaria não é TI — manter no Administrativo</t>
         </is>
       </c>
       <c r="C30" s="72" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Recomendação registrada: o controle de papelaria (canetas, blocos, papel, copos) deve ficar no Administrativo/Facilities, não no TI. O TI controla equipamento porque há decisão TÉCNICA envolvida — se o notebook precisa de troca ou só de formatação, se a tela quebrou por defeito ou por queda. Não existe decisão técnica em caneta e bloco.</t>
         </is>
       </c>
       <c r="D30" s="72" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Três diferenças separam as duas coisas: (1) papelaria acaba, não quebra, então a regra de troca 1x1 não se aplica — o controle é de estoque por ponto de pedido, outra lógica; (2) não há patrimônio nem número de série para rastrear item a item; (3) o custo de controlar uma caneta é maior que a caneta. Se papelaria estiver caindo no orçamento do TI por motivo histórico, é o mesmo caso do Adapta (item Q): classificação errada, corrigir na origem quando o centro de custo novo for aberto.</t>
         </is>
       </c>
       <c r="E30" s="72" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Administrativo</t>
         </is>
       </c>
       <c r="F30" s="74" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>RECOMENDAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="68" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B31" s="69" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C31" s="69" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D31" s="69" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E31" s="69" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F31" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="71" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B31" s="69" t="inlineStr">
+      <c r="B32" s="72" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C31" s="69" t="inlineStr">
+      <c r="C32" s="72" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D31" s="69" t="inlineStr">
+      <c r="D32" s="72" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E31" s="69" t="inlineStr">
+      <c r="E32" s="72" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F31" s="76" t="inlineStr">
+      <c r="F32" s="76" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -21,8 +21,8 @@
     <sheet name="Contas Pagas (detalhe)" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Controle de Equipamentos'!$A$11:$J$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$423</definedName>
@@ -1280,15 +1280,15 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"Jurídico",Planejado!$C$5:$C$30,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"Jurídico",Planejado!$C$5:$C$31,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -1304,7 +1304,7 @@
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1320,15 +1320,15 @@
         </is>
       </c>
       <c r="C7" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"Jurídico",Planejado!$C$5:$C$30,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"Jurídico",Planejado!$C$5:$C$31,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="9">
@@ -1344,7 +1344,7 @@
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"Jurídico",Comparativo!$C$6:$C$31,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1360,15 +1360,15 @@
         </is>
       </c>
       <c r="C8" s="13">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="F8" s="13">
@@ -1384,7 +1384,7 @@
         <v/>
       </c>
       <c r="I8" s="15">
-        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
     </row>
@@ -1400,15 +1400,15 @@
         </is>
       </c>
       <c r="C9" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"TI",Planejado!$C$5:$C$30,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"TI",Planejado!$C$5:$C$31,"Equipe")</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Equipe")</f>
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Equipe")</f>
         <v/>
       </c>
       <c r="F9" s="9">
@@ -1424,7 +1424,7 @@
         <v/>
       </c>
       <c r="I9" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1440,15 +1440,15 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"TI",Planejado!$C$5:$C$30,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"TI",Planejado!$C$5:$C$31,"Despesas")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Despesas")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Despesas")</f>
         <v/>
       </c>
       <c r="F10" s="9">
@@ -1464,7 +1464,7 @@
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"TI",Comparativo!$C$6:$C$31,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1480,15 +1480,15 @@
         </is>
       </c>
       <c r="C11" s="13">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="13">
@@ -1504,7 +1504,7 @@
         <v/>
       </c>
       <c r="I11" s="15">
-        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0",Comparativo!$B$6:$B$31,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$31,"?*",Comparativo!$B$6:$B$31,"TI")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
     </row>
@@ -1516,15 +1516,15 @@
       </c>
       <c r="B12" s="16" t="inlineStr"/>
       <c r="C12" s="17">
-        <f>SUM(Planejado!$T$5:$T$30)</f>
+        <f>SUM(Planejado!$T$5:$T$31)</f>
         <v/>
       </c>
       <c r="D12" s="17">
-        <f>SUM(Comparativo!$I$6:$I$31)</f>
+        <f>SUM(Comparativo!$I$6:$I$32)</f>
         <v/>
       </c>
       <c r="E12" s="17">
-        <f>SUM(Comparativo!$J$6:$J$31)</f>
+        <f>SUM(Comparativo!$J$6:$J$32)</f>
         <v/>
       </c>
       <c r="F12" s="17">
@@ -1540,7 +1540,7 @@
         <v/>
       </c>
       <c r="I12" s="19">
-        <f>COUNTIFS(Comparativo!$P$6:$P$31,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$31)</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$32)</f>
         <v/>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B16" s="21" t="n"/>
       <c r="C16" s="22">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$31,"&lt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$32,"&lt;0")</f>
         <v/>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B17" s="21" t="n"/>
       <c r="C17" s="22">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$31,"&gt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$32,"&gt;0")</f>
         <v/>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B18" s="24" t="n"/>
       <c r="C18" s="25">
-        <f>-SUM(Comparativo!$Q$6:$Q$31)</f>
+        <f>-SUM(Comparativo!$Q$6:$Q$32)</f>
         <v/>
       </c>
       <c r="D18" s="26" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B19" s="21" t="n"/>
       <c r="C19" s="22">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$31)/Comparativo!$D$3*12,"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$32)/Comparativo!$D$3*12,"")</f>
         <v/>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" s="21" t="n"/>
       <c r="C20" s="27">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$31)/SUM(Comparativo!$S$6:$S$31),"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$32)/SUM(Comparativo!$S$6:$S$32),"")</f>
         <v/>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -1718,23 +1718,23 @@
         <v>1</v>
       </c>
       <c r="B25" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A25),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A25),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="C25" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A25),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A25),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A25),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A25),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A25),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A25),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A25),Comparativo!$R$6:$R$31,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A25),Comparativo!$R$6:$R$32,0)),""),"")</f>
         <v/>
       </c>
       <c r="G25" s="34">
@@ -1747,23 +1747,23 @@
         <v>2</v>
       </c>
       <c r="B26" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A26),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A26),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="C26" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A26),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A26),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A26),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A26),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A26),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A26),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="F26" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A26),Comparativo!$R$6:$R$31,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A26),Comparativo!$R$6:$R$32,0)),""),"")</f>
         <v/>
       </c>
       <c r="G26" s="34">
@@ -1776,23 +1776,23 @@
         <v>3</v>
       </c>
       <c r="B27" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A27),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A27),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="C27" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A27),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A27),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A27),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A27),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A27),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A27),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="F27" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A27),Comparativo!$R$6:$R$31,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A27),Comparativo!$R$6:$R$32,0)),""),"")</f>
         <v/>
       </c>
       <c r="G27" s="34">
@@ -1805,23 +1805,23 @@
         <v>4</v>
       </c>
       <c r="B28" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A28),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A28),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="C28" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A28),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A28),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A28),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A28),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A28),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A28),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="F28" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A28),Comparativo!$R$6:$R$31,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A28),Comparativo!$R$6:$R$32,0)),""),"")</f>
         <v/>
       </c>
       <c r="G28" s="34">
@@ -1834,23 +1834,23 @@
         <v>5</v>
       </c>
       <c r="B29" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A29),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A29),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="C29" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A29),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A29),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A29),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A29),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A29),Comparativo!$R$6:$R$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A29),Comparativo!$R$6:$R$32,0)),"")</f>
         <v/>
       </c>
       <c r="F29" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$R$6:$R$31,A29),Comparativo!$R$6:$R$31,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A29),Comparativo!$R$6:$R$32,0)),""),"")</f>
         <v/>
       </c>
       <c r="G29" s="34">
@@ -1908,23 +1908,23 @@
         <v>1</v>
       </c>
       <c r="B34" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A34),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A34),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="C34" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A34),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A34),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A34),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A34),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A34),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A34),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="F34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A34),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A34),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="G34" s="34">
@@ -1937,23 +1937,23 @@
         <v>2</v>
       </c>
       <c r="B35" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A35),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A35),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="C35" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A35),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A35),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A35),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A35),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A35),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A35),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="F35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A35),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A35),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="G35" s="34">
@@ -1966,23 +1966,23 @@
         <v>3</v>
       </c>
       <c r="B36" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A36),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A36),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="C36" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A36),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A36),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A36),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A36),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A36),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A36),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="F36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A36),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A36),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="G36" s="34">
@@ -1995,23 +1995,23 @@
         <v>4</v>
       </c>
       <c r="B37" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A37),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A37),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="C37" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A37),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A37),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A37),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A37),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A37),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A37),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="F37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A37),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A37),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="G37" s="34">
@@ -2024,23 +2024,23 @@
         <v>5</v>
       </c>
       <c r="B38" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A38),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A38),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="C38" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A38),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A38),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A38),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A38),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A38),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A38),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="F38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$31,MATCH(LARGE(Comparativo!$O$6:$O$31,A38),Comparativo!$O$6:$O$31,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A38),Comparativo!$O$6:$O$32,0)),"")</f>
         <v/>
       </c>
       <c r="G38" s="34">
@@ -21017,7 +21017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23199,57 +23199,135 @@
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="47">
+        <f>Planejado!A31</f>
+        <v/>
+      </c>
+      <c r="B32" s="47">
+        <f>Planejado!B31</f>
+        <v/>
+      </c>
+      <c r="C32" s="47">
+        <f>Planejado!C31</f>
+        <v/>
+      </c>
+      <c r="D32" s="48">
+        <f>Planejado!D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="47">
+        <f>Planejado!G31</f>
+        <v/>
+      </c>
+      <c r="F32" s="49">
+        <f>INDEX(Planejado!$H31:$S31,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G32" s="49">
+        <f>INDEX(Realizado!$H31:$S31,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H32" s="49">
+        <f>G32-F32</f>
+        <v/>
+      </c>
+      <c r="I32" s="49">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H31:$S31)</f>
+        <v/>
+      </c>
+      <c r="J32" s="49">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H31:$S31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="49">
+        <f>J32-I32</f>
+        <v/>
+      </c>
+      <c r="L32" s="50">
+        <f>IFERROR(K32/I32,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="50">
+        <f>IFERROR(J32/I32,"")</f>
+        <v/>
+      </c>
+      <c r="N32" s="51">
+        <f>IF(P32=0,"Sem lançamento",IF(AND(I32=0,J32=0),"—",IF(I32=0,"Não orçado",IF(K32&gt;0.05*I32,"Acima do orçado",IF(K32&lt;-0.05*I32,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O32" s="39">
+        <f>IF(K32&gt;1,K32+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P32" s="52">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H31:$S31&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q32" s="46">
+        <f>IF(P32=0,"",K32)</f>
+        <v/>
+      </c>
+      <c r="R32" s="46">
+        <f>IF(AND(Q32&lt;&gt;"",Q32&lt;-1),-Q32+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S32" s="46">
+        <f>IF(Q32="","",I32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="17">
-        <f>SUM(F6:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="17">
-        <f>SUM(G6:G31)</f>
-        <v/>
-      </c>
-      <c r="H32" s="17">
-        <f>SUM(H6:H31)</f>
-        <v/>
-      </c>
-      <c r="I32" s="17">
-        <f>SUM(I6:I31)</f>
-        <v/>
-      </c>
-      <c r="J32" s="17">
-        <f>SUM(J6:J31)</f>
-        <v/>
-      </c>
-      <c r="K32" s="17">
-        <f>SUM(K6:K31)</f>
-        <v/>
-      </c>
-      <c r="L32" s="53">
-        <f>IFERROR(K32/I32,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="53">
-        <f>IFERROR(J32/I32,"")</f>
-        <v/>
-      </c>
-      <c r="N32" s="16" t="n"/>
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="17">
+        <f>SUM(F6:F32)</f>
+        <v/>
+      </c>
+      <c r="G33" s="17">
+        <f>SUM(G6:G32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="17">
+        <f>SUM(H6:H32)</f>
+        <v/>
+      </c>
+      <c r="I33" s="17">
+        <f>SUM(I6:I32)</f>
+        <v/>
+      </c>
+      <c r="J33" s="17">
+        <f>SUM(J6:J32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="17">
+        <f>SUM(K6:K32)</f>
+        <v/>
+      </c>
+      <c r="L33" s="53">
+        <f>IFERROR(K33/I33,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="53">
+        <f>IFERROR(J33/I33,"")</f>
+        <v/>
+      </c>
+      <c r="N33" s="16" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N31"/>
+  <autoFilter ref="A5:N32"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H31">
+  <conditionalFormatting sqref="H6:H32">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -23257,7 +23335,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K31">
+  <conditionalFormatting sqref="K6:K32">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -23280,7 +23358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T31"/>
+  <dimension ref="A1:T32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24259,7 +24337,7 @@
       </c>
       <c r="E16" s="48" t="inlineStr">
         <is>
-          <t>Suporte Técnico Terceirizado</t>
+          <t>Suporte Técnico Terceirizado — R$ 1.065/mês até ago/26; R$ 603,30 a partir de set/26 (renegociação)</t>
         </is>
       </c>
       <c r="F16" s="47" t="inlineStr">
@@ -24297,16 +24375,16 @@
         <v>1065</v>
       </c>
       <c r="P16" s="49" t="n">
-        <v>1065</v>
+        <v>603.3</v>
       </c>
       <c r="Q16" s="49" t="n">
-        <v>1065</v>
+        <v>603.3</v>
       </c>
       <c r="R16" s="49" t="n">
-        <v>1065</v>
+        <v>603.3</v>
       </c>
       <c r="S16" s="49" t="n">
-        <v>1065</v>
+        <v>603.3</v>
       </c>
       <c r="T16" s="54">
         <f>SUM(H16:S16)</f>
@@ -25261,7 +25339,7 @@
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="47" t="inlineStr">
         <is>
-          <t>TI-D09</t>
+          <t>TI-D14</t>
         </is>
       </c>
       <c r="B30" s="47" t="inlineStr">
@@ -25276,18 +25354,18 @@
       </c>
       <c r="D30" s="48" t="inlineStr">
         <is>
-          <t>Bonificação do time</t>
+          <t>AnyDesk</t>
         </is>
       </c>
       <c r="E30" s="48" t="inlineStr">
         <is>
-          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+          <t>Licença de acesso remoto — contratação prevista, não constava na ficha. Valor e mês de início a definir. CONFERIR sobreposição com o serviço de monitoramento remoto já contratado (J H Alves)</t>
         </is>
       </c>
       <c r="F30" s="47" t="inlineStr"/>
       <c r="G30" s="47" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H30" s="49" t="n">
@@ -25312,7 +25390,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="49" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="P30" s="49" t="n">
         <v>0</v>
@@ -25324,80 +25402,153 @@
         <v>0</v>
       </c>
       <c r="S30" s="49" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="T30" s="54">
         <f>SUM(H30:S30)</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="47" t="inlineStr">
+        <is>
+          <t>TI-D09</t>
+        </is>
+      </c>
+      <c r="B31" s="47" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C31" s="47" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D31" s="48" t="inlineStr">
+        <is>
+          <t>Bonificação do time</t>
+        </is>
+      </c>
+      <c r="E31" s="48" t="inlineStr">
+        <is>
+          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
+      <c r="F31" s="47" t="inlineStr"/>
+      <c r="G31" s="47" t="inlineStr">
+        <is>
+          <t>Prêmios</t>
+        </is>
+      </c>
+      <c r="H31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="49" t="n">
+        <v>2400</v>
+      </c>
+      <c r="P31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="49" t="n">
+        <v>3600</v>
+      </c>
+      <c r="T31" s="54">
+        <f>SUM(H31:S31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="17">
-        <f>SUM(H5:H30)</f>
-        <v/>
-      </c>
-      <c r="I31" s="17">
-        <f>SUM(I5:I30)</f>
-        <v/>
-      </c>
-      <c r="J31" s="17">
-        <f>SUM(J5:J30)</f>
-        <v/>
-      </c>
-      <c r="K31" s="17">
-        <f>SUM(K5:K30)</f>
-        <v/>
-      </c>
-      <c r="L31" s="17">
-        <f>SUM(L5:L30)</f>
-        <v/>
-      </c>
-      <c r="M31" s="17">
-        <f>SUM(M5:M30)</f>
-        <v/>
-      </c>
-      <c r="N31" s="17">
-        <f>SUM(N5:N30)</f>
-        <v/>
-      </c>
-      <c r="O31" s="17">
-        <f>SUM(O5:O30)</f>
-        <v/>
-      </c>
-      <c r="P31" s="17">
-        <f>SUM(P5:P30)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="17">
-        <f>SUM(Q5:Q30)</f>
-        <v/>
-      </c>
-      <c r="R31" s="17">
-        <f>SUM(R5:R30)</f>
-        <v/>
-      </c>
-      <c r="S31" s="17">
-        <f>SUM(S5:S30)</f>
-        <v/>
-      </c>
-      <c r="T31" s="17">
-        <f>SUM(T5:T30)</f>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="17">
+        <f>SUM(H5:H31)</f>
+        <v/>
+      </c>
+      <c r="I32" s="17">
+        <f>SUM(I5:I31)</f>
+        <v/>
+      </c>
+      <c r="J32" s="17">
+        <f>SUM(J5:J31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="17">
+        <f>SUM(K5:K31)</f>
+        <v/>
+      </c>
+      <c r="L32" s="17">
+        <f>SUM(L5:L31)</f>
+        <v/>
+      </c>
+      <c r="M32" s="17">
+        <f>SUM(M5:M31)</f>
+        <v/>
+      </c>
+      <c r="N32" s="17">
+        <f>SUM(N5:N31)</f>
+        <v/>
+      </c>
+      <c r="O32" s="17">
+        <f>SUM(O5:O31)</f>
+        <v/>
+      </c>
+      <c r="P32" s="17">
+        <f>SUM(P5:P31)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="17">
+        <f>SUM(Q5:Q31)</f>
+        <v/>
+      </c>
+      <c r="R32" s="17">
+        <f>SUM(R5:R31)</f>
+        <v/>
+      </c>
+      <c r="S32" s="17">
+        <f>SUM(S5:S31)</f>
+        <v/>
+      </c>
+      <c r="T32" s="17">
+        <f>SUM(T5:T31)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T30"/>
+  <autoFilter ref="A4:T31"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
@@ -25412,7 +25563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -27099,72 +27250,120 @@
       <c r="U30" s="59" t="n"/>
       <c r="V30" s="59" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="60" t="inlineStr">
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="56">
+        <f>Planejado!A31</f>
+        <v/>
+      </c>
+      <c r="B31" s="56">
+        <f>Planejado!B31</f>
+        <v/>
+      </c>
+      <c r="C31" s="56">
+        <f>Planejado!C31</f>
+        <v/>
+      </c>
+      <c r="D31" s="57">
+        <f>Planejado!D31</f>
+        <v/>
+      </c>
+      <c r="E31" s="57">
+        <f>Planejado!E31</f>
+        <v/>
+      </c>
+      <c r="F31" s="56">
+        <f>Planejado!F31</f>
+        <v/>
+      </c>
+      <c r="G31" s="56">
+        <f>Planejado!G31</f>
+        <v/>
+      </c>
+      <c r="H31" s="58" t="n"/>
+      <c r="I31" s="58" t="n"/>
+      <c r="J31" s="58" t="n"/>
+      <c r="K31" s="58" t="n"/>
+      <c r="L31" s="58" t="n"/>
+      <c r="M31" s="58" t="n"/>
+      <c r="N31" s="58" t="n"/>
+      <c r="O31" s="58" t="n"/>
+      <c r="P31" s="58" t="n"/>
+      <c r="Q31" s="58" t="n"/>
+      <c r="R31" s="58" t="n"/>
+      <c r="S31" s="58" t="n"/>
+      <c r="T31" s="54">
+        <f>SUM(H31:S31)</f>
+        <v/>
+      </c>
+      <c r="U31" s="59" t="n"/>
+      <c r="V31" s="59" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="60" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B31" s="60" t="n"/>
-      <c r="C31" s="60" t="n"/>
-      <c r="D31" s="60" t="n"/>
-      <c r="E31" s="60" t="n"/>
-      <c r="F31" s="60" t="n"/>
-      <c r="G31" s="60" t="n"/>
-      <c r="H31" s="61">
-        <f>SUM(H5:H30)</f>
-        <v/>
-      </c>
-      <c r="I31" s="61">
-        <f>SUM(I5:I30)</f>
-        <v/>
-      </c>
-      <c r="J31" s="61">
-        <f>SUM(J5:J30)</f>
-        <v/>
-      </c>
-      <c r="K31" s="61">
-        <f>SUM(K5:K30)</f>
-        <v/>
-      </c>
-      <c r="L31" s="61">
-        <f>SUM(L5:L30)</f>
-        <v/>
-      </c>
-      <c r="M31" s="61">
-        <f>SUM(M5:M30)</f>
-        <v/>
-      </c>
-      <c r="N31" s="61">
-        <f>SUM(N5:N30)</f>
-        <v/>
-      </c>
-      <c r="O31" s="61">
-        <f>SUM(O5:O30)</f>
-        <v/>
-      </c>
-      <c r="P31" s="61">
-        <f>SUM(P5:P30)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="61">
-        <f>SUM(Q5:Q30)</f>
-        <v/>
-      </c>
-      <c r="R31" s="61">
-        <f>SUM(R5:R30)</f>
-        <v/>
-      </c>
-      <c r="S31" s="61">
-        <f>SUM(S5:S30)</f>
-        <v/>
-      </c>
-      <c r="T31" s="61">
-        <f>SUM(T5:T30)</f>
-        <v/>
-      </c>
-      <c r="U31" s="60" t="n"/>
-      <c r="V31" s="60" t="n"/>
+      <c r="B32" s="60" t="n"/>
+      <c r="C32" s="60" t="n"/>
+      <c r="D32" s="60" t="n"/>
+      <c r="E32" s="60" t="n"/>
+      <c r="F32" s="60" t="n"/>
+      <c r="G32" s="60" t="n"/>
+      <c r="H32" s="61">
+        <f>SUM(H5:H31)</f>
+        <v/>
+      </c>
+      <c r="I32" s="61">
+        <f>SUM(I5:I31)</f>
+        <v/>
+      </c>
+      <c r="J32" s="61">
+        <f>SUM(J5:J31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="61">
+        <f>SUM(K5:K31)</f>
+        <v/>
+      </c>
+      <c r="L32" s="61">
+        <f>SUM(L5:L31)</f>
+        <v/>
+      </c>
+      <c r="M32" s="61">
+        <f>SUM(M5:M31)</f>
+        <v/>
+      </c>
+      <c r="N32" s="61">
+        <f>SUM(N5:N31)</f>
+        <v/>
+      </c>
+      <c r="O32" s="61">
+        <f>SUM(O5:O31)</f>
+        <v/>
+      </c>
+      <c r="P32" s="61">
+        <f>SUM(P5:P31)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="61">
+        <f>SUM(Q5:Q31)</f>
+        <v/>
+      </c>
+      <c r="R32" s="61">
+        <f>SUM(R5:R31)</f>
+        <v/>
+      </c>
+      <c r="S32" s="61">
+        <f>SUM(S5:S31)</f>
+        <v/>
+      </c>
+      <c r="T32" s="61">
+        <f>SUM(T5:T31)</f>
+        <v/>
+      </c>
+      <c r="U32" s="60" t="n"/>
+      <c r="V32" s="60" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -27269,19 +27468,19 @@
         </is>
       </c>
       <c r="B5" s="42">
-        <f>SUMIFS(Planejado!$H$5:$H$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="42">
-        <f>SUMIFS(Realizado!$H$5:$H$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="42">
-        <f>SUMIFS(Planejado!$H$5:$H$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="42">
-        <f>SUMIFS(Realizado!$H$5:$H$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="42">
@@ -27312,19 +27511,19 @@
         </is>
       </c>
       <c r="B6" s="49">
-        <f>SUMIFS(Planejado!$I$5:$I$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="49">
-        <f>SUMIFS(Realizado!$I$5:$I$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="49">
-        <f>SUMIFS(Planejado!$I$5:$I$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="49">
-        <f>SUMIFS(Realizado!$I$5:$I$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="49">
@@ -27355,19 +27554,19 @@
         </is>
       </c>
       <c r="B7" s="42">
-        <f>SUMIFS(Planejado!$J$5:$J$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="42">
-        <f>SUMIFS(Realizado!$J$5:$J$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="42">
-        <f>SUMIFS(Planejado!$J$5:$J$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="42">
-        <f>SUMIFS(Realizado!$J$5:$J$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="42">
@@ -27398,19 +27597,19 @@
         </is>
       </c>
       <c r="B8" s="49">
-        <f>SUMIFS(Planejado!$K$5:$K$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="49">
-        <f>SUMIFS(Realizado!$K$5:$K$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="49">
-        <f>SUMIFS(Planejado!$K$5:$K$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="49">
-        <f>SUMIFS(Realizado!$K$5:$K$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="49">
@@ -27441,19 +27640,19 @@
         </is>
       </c>
       <c r="B9" s="42">
-        <f>SUMIFS(Planejado!$L$5:$L$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="42">
-        <f>SUMIFS(Realizado!$L$5:$L$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="42">
-        <f>SUMIFS(Planejado!$L$5:$L$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="42">
-        <f>SUMIFS(Realizado!$L$5:$L$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="42">
@@ -27484,19 +27683,19 @@
         </is>
       </c>
       <c r="B10" s="49">
-        <f>SUMIFS(Planejado!$M$5:$M$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="49">
-        <f>SUMIFS(Realizado!$M$5:$M$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="49">
-        <f>SUMIFS(Planejado!$M$5:$M$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="49">
-        <f>SUMIFS(Realizado!$M$5:$M$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="49">
@@ -27527,19 +27726,19 @@
         </is>
       </c>
       <c r="B11" s="42">
-        <f>SUMIFS(Planejado!$N$5:$N$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="42">
-        <f>SUMIFS(Realizado!$N$5:$N$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="42">
-        <f>SUMIFS(Planejado!$N$5:$N$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="42">
-        <f>SUMIFS(Realizado!$N$5:$N$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="42">
@@ -27570,19 +27769,19 @@
         </is>
       </c>
       <c r="B12" s="49">
-        <f>SUMIFS(Planejado!$O$5:$O$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C12" s="49">
-        <f>SUMIFS(Realizado!$O$5:$O$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D12" s="49">
-        <f>SUMIFS(Planejado!$O$5:$O$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E12" s="49">
-        <f>SUMIFS(Realizado!$O$5:$O$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F12" s="49">
@@ -27613,19 +27812,19 @@
         </is>
       </c>
       <c r="B13" s="42">
-        <f>SUMIFS(Planejado!$P$5:$P$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C13" s="42">
-        <f>SUMIFS(Realizado!$P$5:$P$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D13" s="42">
-        <f>SUMIFS(Planejado!$P$5:$P$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E13" s="42">
-        <f>SUMIFS(Realizado!$P$5:$P$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F13" s="42">
@@ -27656,19 +27855,19 @@
         </is>
       </c>
       <c r="B14" s="49">
-        <f>SUMIFS(Planejado!$Q$5:$Q$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C14" s="49">
-        <f>SUMIFS(Realizado!$Q$5:$Q$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D14" s="49">
-        <f>SUMIFS(Planejado!$Q$5:$Q$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E14" s="49">
-        <f>SUMIFS(Realizado!$Q$5:$Q$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F14" s="49">
@@ -27699,19 +27898,19 @@
         </is>
       </c>
       <c r="B15" s="42">
-        <f>SUMIFS(Planejado!$R$5:$R$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C15" s="42">
-        <f>SUMIFS(Realizado!$R$5:$R$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D15" s="42">
-        <f>SUMIFS(Planejado!$R$5:$R$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E15" s="42">
-        <f>SUMIFS(Realizado!$R$5:$R$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F15" s="42">
@@ -27742,19 +27941,19 @@
         </is>
       </c>
       <c r="B16" s="49">
-        <f>SUMIFS(Planejado!$S$5:$S$30,Planejado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$31,Planejado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="C16" s="49">
-        <f>SUMIFS(Realizado!$S$5:$S$30,Realizado!$B$5:$B$30,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$31,Realizado!$B$5:$B$31,"Jurídico")</f>
         <v/>
       </c>
       <c r="D16" s="49">
-        <f>SUMIFS(Planejado!$S$5:$S$30,Planejado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$31,Planejado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="E16" s="49">
-        <f>SUMIFS(Realizado!$S$5:$S$30,Realizado!$B$5:$B$30,"TI")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$31,Realizado!$B$5:$B$31,"TI")</f>
         <v/>
       </c>
       <c r="F16" s="49">
@@ -27927,19 +28126,19 @@
         </is>
       </c>
       <c r="B5" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A5,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A5,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A5,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A5,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A5,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A5,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A5,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A5,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="42">
@@ -27959,7 +28158,7 @@
         <v/>
       </c>
       <c r="J5" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A5)</f>
         <v/>
       </c>
     </row>
@@ -27970,19 +28169,19 @@
         </is>
       </c>
       <c r="B6" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A6,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A6,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A6,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A6,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A6,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A6,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A6,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A6,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="49">
@@ -28002,7 +28201,7 @@
         <v/>
       </c>
       <c r="J6" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A6)</f>
         <v/>
       </c>
     </row>
@@ -28013,19 +28212,19 @@
         </is>
       </c>
       <c r="B7" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A7,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A7,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A7,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A7,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A7,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A7,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A7,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A7,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="42">
@@ -28045,7 +28244,7 @@
         <v/>
       </c>
       <c r="J7" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A7)</f>
         <v/>
       </c>
     </row>
@@ -28056,19 +28255,19 @@
         </is>
       </c>
       <c r="B8" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A8,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A8,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A8,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A8,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A8,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A8,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A8,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A8,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="49">
@@ -28088,7 +28287,7 @@
         <v/>
       </c>
       <c r="J8" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A8)</f>
         <v/>
       </c>
     </row>
@@ -28099,19 +28298,19 @@
         </is>
       </c>
       <c r="B9" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A9,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A9,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A9,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A9,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A9,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A9,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A9,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A9,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="42">
@@ -28131,7 +28330,7 @@
         <v/>
       </c>
       <c r="J9" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A9)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A9)</f>
         <v/>
       </c>
     </row>
@@ -28142,19 +28341,19 @@
         </is>
       </c>
       <c r="B10" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A10,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A10,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A10,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A10,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A10,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A10,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A10,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A10,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="49">
@@ -28174,7 +28373,7 @@
         <v/>
       </c>
       <c r="J10" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A10)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A10)</f>
         <v/>
       </c>
     </row>
@@ -28185,19 +28384,19 @@
         </is>
       </c>
       <c r="B11" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A11,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A11,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A11,Comparativo!$B$6:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A11,Comparativo!$B$6:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$31,Comparativo!$E$6:$E$31,$A11,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A11,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$31,Comparativo!$E$6:$E$31,$A11,Comparativo!$B$6:$B$31,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A11,Comparativo!$B$6:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="42">
@@ -28217,7 +28416,7 @@
         <v/>
       </c>
       <c r="J11" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$30,Planejado!$G$5:$G$30,$A11)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A11)</f>
         <v/>
       </c>
     </row>
@@ -28287,7 +28486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -28544,17 +28743,17 @@
       </c>
       <c r="B11" s="69" t="inlineStr">
         <is>
-          <t>Elias Benedito zerado nos três meses</t>
+          <t>Elias Benedito — sem custo até jul, renegociado para set</t>
         </is>
       </c>
       <c r="C11" s="69" t="inlineStr">
         <is>
-          <t>Orçado R$ 1.065/mês como suporte técnico terceirizado, realizado R$ 0 em mai, jun e jul.</t>
+          <t>Orçado R$ 1.065/mês, realizado R$ 0 de jan a jul — contrato ativo, mas sem acionamento no período (confirmado pela gestora). O pagamento passa a ocorrer agora, e a partir de set/26 o valor foi renegociado de R$ 1.065 para R$ 603,30.</t>
         </is>
       </c>
       <c r="D11" s="69" t="inlineStr">
         <is>
-          <t>Confirmar se o contrato segue ativo (acionamento sob demanda) ou se foi encerrado. Se encerrado, são R$ 12.780 a liberar no orçamento do ano.</t>
+          <t>Duas economias na mesma linha: R$ 7.455 pelos sete meses sem acionamento, e R$ 461,70/mês (43%) a partir de set pela renegociação — R$ 1.846,80 no ano. O planejado já reflete o valor novo de set a dez.</t>
         </is>
       </c>
       <c r="E11" s="69" t="inlineStr">
@@ -28562,9 +28761,9 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F11" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+      <c r="F11" s="73" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
@@ -29179,22 +29378,22 @@
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B31" s="69" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>AnyDesk — contratação prevista, definir valor</t>
         </is>
       </c>
       <c r="C31" s="69" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Licença de acesso remoto que será contratada e não constava na ficha. Linha criada com planejado zerado, à espera do valor e do mês de início.</t>
         </is>
       </c>
       <c r="D31" s="69" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>ATENÇÃO À SOBREPOSIÇÃO: o extrato mostra R$ 20.508,55 pagos a J H ALVES — MONITOR REMOTO de jan a jul, o maior fornecedor de despesa do TI e também fora do orçamento (item M). Se o AnyDesk cobre a mesma necessidade, é substituição e pode gerar economia; se é complementar, é custo novo somado a um custo que já não estava previsto. Esclarecer antes de contratar — é o mesmo padrão do Jusfy x Astrea, em que dois softwares de função parecida quase rodaram em paralelo.</t>
         </is>
       </c>
       <c r="E31" s="69" t="inlineStr">
@@ -29204,37 +29403,69 @@
       </c>
       <c r="F31" s="74" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>DEFINIR VALOR</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="71" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B32" s="72" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C32" s="72" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D32" s="72" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E32" s="72" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F32" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="68" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B32" s="72" t="inlineStr">
+      <c r="B33" s="69" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C32" s="72" t="inlineStr">
+      <c r="C33" s="69" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D32" s="72" t="inlineStr">
+      <c r="D33" s="69" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E32" s="72" t="inlineStr">
+      <c r="E33" s="69" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F32" s="76" t="inlineStr">
+      <c r="F33" s="76" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -28486,7 +28486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -29410,62 +29410,94 @@
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B32" s="72" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Vitor (diretoria) — Claude ou GPT? PERGUNTAR</t>
         </is>
       </c>
       <c r="C32" s="72" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Confirmar com o Vitor se ele seguirá usando o Claude, o GPT, ou os dois. Hoje as duas ferramentas estão contratadas e são de mesma finalidade — IA generalista —, então manter as duas para o mesmo usuário é redundância paga.</t>
         </is>
       </c>
       <c r="D32" s="72" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>É pré-requisito para fechar a meta do item L: não dá para dimensionar o orçamento de IA sem saber quantas licenças de cada ferramenta ficam de pé. Referência de custo: a OpenAI aparece no extrato com R$ 5.950,10 em sete meses, sendo R$ 5.394 só em abr/26. Levantar a mesma informação para os demais usuários, não só a diretoria — a decisão vale para todo mundo.</t>
         </is>
       </c>
       <c r="E32" s="72" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Vitor</t>
         </is>
       </c>
       <c r="F32" s="74" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>PERGUNTAR</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="68" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="69" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C33" s="69" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D33" s="69" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E33" s="69" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F33" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="71" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B33" s="69" t="inlineStr">
+      <c r="B34" s="72" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C33" s="69" t="inlineStr">
+      <c r="C34" s="72" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D33" s="69" t="inlineStr">
+      <c r="D34" s="72" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E33" s="69" t="inlineStr">
+      <c r="E34" s="72" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F33" s="76" t="inlineStr">
+      <c r="F34" s="76" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -28486,7 +28486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -29442,62 +29442,94 @@
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B33" s="69" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Mapa de licenças de IA — quem usa o quê</t>
         </is>
       </c>
       <c r="C33" s="69" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>Situação atual conhecida: a licença do GPT era da Thamar e hoje é usada em conjunto por Gil, Miguel e Thamar. Uma licença também foi cedida ao Financeiro. Falta o mapa completo — quem usa cada ferramenta, em qual área e sob qual login.</t>
         </is>
       </c>
       <c r="D33" s="69" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>Duas consequências. ORÇAMENTO: uma licença usada pelo Financeiro é custo de outra área lançado no TI/Jurídico — é exatamente o caso que o rateio do item L precisa resolver, e sem o mapa não há como ratear. RISCO: contas de IA generalista são individuais, e o compartilhamento entre pessoas costuma contrariar os termos de uso do fornecedor, com risco de suspensão. Mais grave num escritório de advocacia: o histórico de conversas fica visível para todos que usam o mesmo login, então dados de um cliente podem ser vistos por quem não atua no caso — questão de sigilo profissional, não só de custo. Avaliar licenças individuais ou plano de equipe, que costuma sair mais barato por usuário e separa os históricos.</t>
         </is>
       </c>
       <c r="E33" s="69" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Vitor</t>
         </is>
       </c>
       <c r="F33" s="74" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>LEVANTAR</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="71" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="72" t="inlineStr">
+        <is>
+          <t>Office 365 — nº de licenças</t>
+        </is>
+      </c>
+      <c r="C34" s="72" t="inlineStr">
+        <is>
+          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+        </is>
+      </c>
+      <c r="D34" s="72" t="inlineStr">
+        <is>
+          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+        </is>
+      </c>
+      <c r="E34" s="72" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F34" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="68" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B34" s="72" t="inlineStr">
+      <c r="B35" s="69" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C34" s="72" t="inlineStr">
+      <c r="C35" s="69" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D34" s="72" t="inlineStr">
+      <c r="D35" s="69" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E34" s="72" t="inlineStr">
+      <c r="E35" s="69" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F34" s="76" t="inlineStr">
+      <c r="F35" s="76" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -29479,17 +29479,17 @@
       </c>
       <c r="B34" s="72" t="inlineStr">
         <is>
-          <t>Office 365 — nº de licenças</t>
+          <t>Office 365 — CONFIRMAR se R$ 440 é por licença ou o total</t>
         </is>
       </c>
       <c r="C34" s="72" t="inlineStr">
         <is>
-          <t>A observação diz '10 licenças de software – 60 usuários'. Os dois números não fecham entre si.</t>
+          <t>A gestora esclareceu a estrutura: cada licença atende 6 funcionários e custa R$ 440. Com 10 licenças, fecham os 60 usuários da ficha. Falta confirmar UMA coisa: os R$ 440 são o valor de CADA licença ou o total pago por mês? Não há lançamento de Microsoft/Office no extrato de jan a jul, o que também precisa ser explicado — é custo mensal e deveria aparecer.</t>
         </is>
       </c>
       <c r="D34" s="72" t="inlineStr">
         <is>
-          <t>Afeta o valor orçado da linha e a projeção de crescimento.</t>
+          <t>A diferença entre as duas leituras é enorme. Se R$ 440 for o total: R$ 5.280/ano, R$ 780 acima dos R$ 4.500 orçados — ajuste pequeno. Se for por licença: 10 x R$ 440 = R$ 4.400/mês, R$ 52.800/ano, R$ 48.300 acima do orçado — sozinho maior que todas as despesas orçadas do TI, e o orçamento da área estaria comprometido. Confirmar antes da reunião.</t>
         </is>
       </c>
       <c r="E34" s="72" t="inlineStr">
@@ -29499,7 +29499,7 @@
       </c>
       <c r="F34" s="74" t="inlineStr">
         <is>
-          <t>EM ABERTO</t>
+          <t>CONFIRMAR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -28486,7 +28486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -29474,22 +29474,22 @@
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B34" s="72" t="inlineStr">
         <is>
-          <t>Office 365 — CONFIRMAR se R$ 440 é por licença ou o total</t>
+          <t>Divisão de responsabilidades no acompanhamento</t>
         </is>
       </c>
       <c r="C34" s="72" t="inlineStr">
         <is>
-          <t>A gestora esclareceu a estrutura: cada licença atende 6 funcionários e custa R$ 440. Com 10 licenças, fecham os 60 usuários da ficha. Falta confirmar UMA coisa: os R$ 440 são o valor de CADA licença ou o total pago por mês? Não há lançamento de Microsoft/Office no extrato de jan a jul, o que também precisa ser explicado — é custo mensal e deveria aparecer.</t>
+          <t>Definição de quem faz o quê no controle orçamentário do TI. Capacidades: Vinicius, analista, 173 h/mês a R$ 31,25/h de custo total; Jonathan, consultor/desenvolvedor, 3 dias por semana, 104 h/mês a R$ 60,58/h — o dobro. Cristiane na gestão.</t>
         </is>
       </c>
       <c r="D34" s="72" t="inlineStr">
         <is>
-          <t>A diferença entre as duas leituras é enorme. Se R$ 440 for o total: R$ 5.280/ano, R$ 780 acima dos R$ 4.500 orçados — ajuste pequeno. Se for por licença: 10 x R$ 440 = R$ 4.400/mês, R$ 52.800/ano, R$ 48.300 acima do orçado — sozinho maior que todas as despesas orçadas do TI, e o orçamento da área estaria comprometido. Confirmar antes da reunião.</t>
+          <t>VINICIUS (todo o recorrente): extração mensal do SIENGE e lançamento do realizado, controle de equipamentos (solicitações, empréstimos, troca 1x1), acompanhamento do saldo por área para avisar antes do estouro, conferência de faturas contra contrato. JONATHAN (pontual e técnico, nunca rotina): avaliar AnyDesk x Monitor Remoto, avaliar Claude x GPT e planos de equipe, e automatizar a extração do SIENGE — esta última é a que paga o custo dele, porque devolve tempo do analista todos os meses. CRISTIANE: negociação de contratos, rateio, o que entra e sai do orçamento, apresentação à diretoria. Critério: 104 h/mês é capacidade limitada, e cada hora do consultor em tarefa administrativa custa o dobro da mesma hora do analista. Se o Jonathan aparecer na rotina mensal, é sinal de que algo deveria ter sido automatizado.</t>
         </is>
       </c>
       <c r="E34" s="72" t="inlineStr">
@@ -29497,39 +29497,71 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F34" s="74" t="inlineStr">
-        <is>
-          <t>CONFIRMAR</t>
+      <c r="F34" s="73" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="68" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B35" s="69" t="inlineStr">
+        <is>
+          <t>Office 365 — CONFIRMAR se R$ 440 é por licença ou o total</t>
+        </is>
+      </c>
+      <c r="C35" s="69" t="inlineStr">
+        <is>
+          <t>A gestora esclareceu a estrutura: cada licença atende 6 funcionários e custa R$ 440. Com 10 licenças, fecham os 60 usuários da ficha. Falta confirmar UMA coisa: os R$ 440 são o valor de CADA licença ou o total pago por mês? Não há lançamento de Microsoft/Office no extrato de jan a jul, o que também precisa ser explicado — é custo mensal e deveria aparecer.</t>
+        </is>
+      </c>
+      <c r="D35" s="69" t="inlineStr">
+        <is>
+          <t>A diferença entre as duas leituras é enorme. Se R$ 440 for o total: R$ 5.280/ano, R$ 780 acima dos R$ 4.500 orçados — ajuste pequeno. Se for por licença: 10 x R$ 440 = R$ 4.400/mês, R$ 52.800/ano, R$ 48.300 acima do orçado — sozinho maior que todas as despesas orçadas do TI, e o orçamento da área estaria comprometido. Confirmar antes da reunião.</t>
+        </is>
+      </c>
+      <c r="E35" s="69" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F35" s="74" t="inlineStr">
+        <is>
+          <t>CONFIRMAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="71" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B35" s="69" t="inlineStr">
+      <c r="B36" s="72" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C35" s="69" t="inlineStr">
+      <c r="C36" s="72" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D35" s="69" t="inlineStr">
+      <c r="D36" s="72" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E35" s="69" t="inlineStr">
+      <c r="E36" s="72" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F35" s="76" t="inlineStr">
+      <c r="F36" s="76" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -227,12 +227,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
     <fill>
@@ -2816,38 +2816,42 @@
       <c r="L12" s="91" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="64" t="inlineStr">
+      <c r="A13" s="92" t="inlineStr">
         <is>
           <t>J H ALVES - MONITOR REMOTO</t>
         </is>
       </c>
-      <c r="B13" s="64" t="inlineStr">
+      <c r="B13" s="92" t="inlineStr">
         <is>
           <t>T.I</t>
         </is>
       </c>
-      <c r="C13" s="62" t="n">
+      <c r="C13" s="93" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="42" t="n">
+      <c r="D13" s="94" t="n">
         <v>4311.56</v>
       </c>
-      <c r="E13" s="42" t="n"/>
-      <c r="F13" s="42" t="n"/>
-      <c r="G13" s="42" t="n"/>
-      <c r="H13" s="42" t="n">
+      <c r="E13" s="94" t="n"/>
+      <c r="F13" s="94" t="n"/>
+      <c r="G13" s="94" t="n"/>
+      <c r="H13" s="94" t="n">
         <v>3723.62</v>
       </c>
-      <c r="I13" s="42" t="n">
+      <c r="I13" s="94" t="n">
         <v>6173.37</v>
       </c>
-      <c r="J13" s="42" t="n">
+      <c r="J13" s="94" t="n">
         <v>6300</v>
       </c>
-      <c r="K13" s="90" t="n">
+      <c r="K13" s="95" t="n">
         <v>20508.55</v>
       </c>
-      <c r="L13" s="91" t="n"/>
+      <c r="L13" s="96" t="inlineStr">
+        <is>
+          <t>TI-E03 Jonathan (Monitor Remoto)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="92" t="inlineStr">
@@ -26586,7 +26590,7 @@
         <v/>
       </c>
       <c r="H17" s="58" t="n">
-        <v>0</v>
+        <v>4311.56</v>
       </c>
       <c r="I17" s="58" t="n">
         <v>0</v>
@@ -26595,13 +26599,13 @@
         <v>0</v>
       </c>
       <c r="K17" s="58" t="n">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="L17" s="58" t="n">
-        <v>6300</v>
+        <v>3723.62</v>
       </c>
       <c r="M17" s="58" t="n">
-        <v>6300</v>
+        <v>6173.37</v>
       </c>
       <c r="N17" s="58" t="n">
         <v>6300</v>
@@ -26617,12 +26621,12 @@
       </c>
       <c r="U17" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Extrato do financeiro</t>
         </is>
       </c>
       <c r="V17" s="59" t="inlineStr">
         <is>
-          <t>Sem custo em jan–mar (contratação segurada). R$ 6.300/mês a partir de abr, contra R$ 10.000 orçados</t>
+          <t>Credor 'J H ALVES - MONITOR REMOTO'. Pagamentos: 19/01 NFS.70 R$ 4.311,56; 01/05 NFS.76 R$ 3.723,62; 01/06 NFS.78 R$ 6.173,37; 01/07 NFS.3 R$ 6.300,00. Sem pagamento em fev, mar e abr</t>
         </is>
       </c>
     </row>
@@ -28711,17 +28715,17 @@
       </c>
       <c r="B10" s="72" t="inlineStr">
         <is>
-          <t>Jonathan — economia de R$ 44.800 até julho</t>
+          <t>Jonathan — economia de R$ 49.491 até julho</t>
         </is>
       </c>
       <c r="C10" s="72" t="inlineStr">
         <is>
-          <t>Orçado R$ 10.000/mês desde jan/26. A contratação foi segurada e as atividades só começaram em abr/26, a R$ 6.300/mês. Resultado: três meses sem custo (R$ 30.000) e quatro meses a R$ 3.700 abaixo do orçado (R$ 14.800).</t>
+          <t>Orçado R$ 10.000/mês desde jan/26. A contratação foi segurada e o serviço só começou depois, chegando a R$ 6.300/mês. Realizado pelo extrato, no credor 'J H ALVES — MONITOR REMOTO': R$ 4.311,56 em jan, nada em fev, mar e abr, e R$ 3.723,62, R$ 6.173,37 e R$ 6.300,00 em mai, jun e jul. Total de R$ 20.508,55 contra R$ 70.000 orçados.</t>
         </is>
       </c>
       <c r="D10" s="72" t="inlineStr">
         <is>
-          <t>É de longe a maior economia das duas áreas: R$ 44.800 em sete meses, e decorre de decisão de gestão, não de erro de orçamento. Se o valor de R$ 6.300 se mantiver até dez, somam-se outros R$ 18.500 — total de R$ 63.300 no ano. Vale destacar na apresentação à diretoria.</t>
+          <t>É de longe a maior economia das duas áreas: R$ 49.491,45 em sete meses, e decorre de decisão de gestão, não de erro de orçamento. Vale destacar na apresentação. DOIS PONTOS A ESCLARECER: (1) o pagamento de R$ 4.311,56 em 19/01 é anterior ao início das atividades — provavelmente serviço de dez/2025 recebido no mês seguinte, confirmar; (2) mai e jun saíram abaixo de R$ 6.300 (R$ 3.723,62 e R$ 6.173,37), verificar se foi proporcional por dias trabalhados.</t>
         </is>
       </c>
       <c r="E10" s="72" t="inlineStr">
@@ -28729,9 +28733,9 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F10" s="73" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
+      <c r="F10" s="75" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>
@@ -28844,7 +28848,7 @@
       </c>
       <c r="C14" s="72" t="inlineStr">
         <is>
-          <t>O extrato do financeiro traz gastos relevantes sem linha na ficha. Jurídico: Carneiro Rabelo (R$ 107.742) e Cristiane Carneiro Rabelo (R$ 94.825), somando R$ 202.567 em sete meses; mais Tribunal de Justiça (R$ 49.244), Michele de Oliveira (R$ 23.572) e ONR (R$ 22.576). TI: J H Alves / Monitor Remoto (R$ 20.509) e um bloco de telefonia e infraestrutura de cerca de R$ 15.700 (Claro, TIM, Telefônica, Locaweb, Web Mobile, Sabha, Intelbras, VC1, Alfama).</t>
+          <t>O extrato do financeiro traz gastos relevantes sem linha na ficha. Jurídico: Carneiro Rabelo (R$ 107.742) e Cristiane Carneiro Rabelo (R$ 94.825), somando R$ 202.567 em sete meses; mais Tribunal de Justiça (R$ 49.244), Michele de Oliveira (R$ 23.572) e ONR (R$ 22.576). TI: um bloco de telefonia e infraestrutura de cerca de R$ 15.700 (Claro, TIM, Telefônica, Locaweb, Web Mobile, Sabha, Intelbras, VC1, Alfama). O 'J H Alves — Monitor Remoto' NÃO entra nesta lista: é o Jonathan, que já tem linha no orçamento (TI-E03).</t>
         </is>
       </c>
       <c r="D14" s="72" t="inlineStr">
@@ -28857,7 +28861,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F14" s="75" t="inlineStr">
+      <c r="F14" s="76" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -29113,7 +29117,7 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F22" s="76" t="inlineStr">
+      <c r="F22" s="75" t="inlineStr">
         <is>
           <t>CONFERIR</t>
         </is>
@@ -29145,7 +29149,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F23" s="75" t="inlineStr">
+      <c r="F23" s="76" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -29177,7 +29181,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="F24" s="76" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -29241,7 +29245,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F26" s="75" t="inlineStr">
+      <c r="F26" s="76" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -29273,7 +29277,7 @@
           <t>Cristiane + Diretoria</t>
         </is>
       </c>
-      <c r="F27" s="75" t="inlineStr">
+      <c r="F27" s="76" t="inlineStr">
         <is>
           <t>PAUTA REUNIÃO</t>
         </is>
@@ -29393,7 +29397,7 @@
       </c>
       <c r="D31" s="69" t="inlineStr">
         <is>
-          <t>ATENÇÃO À SOBREPOSIÇÃO: o extrato mostra R$ 20.508,55 pagos a J H ALVES — MONITOR REMOTO de jan a jul, o maior fornecedor de despesa do TI e também fora do orçamento (item M). Se o AnyDesk cobre a mesma necessidade, é substituição e pode gerar economia; se é complementar, é custo novo somado a um custo que já não estava previsto. Esclarecer antes de contratar — é o mesmo padrão do Jusfy x Astrea, em que dois softwares de função parecida quase rodaram em paralelo.</t>
+          <t>Não há sobreposição com o 'Monitor Remoto' do extrato: aquele credor é o Jonathan (J H Alves), consultor, não um software de acesso remoto. O AnyDesk é contratação nova e sem substituto atual. Definir valor e mês para a linha entrar no orçamento — enquanto o planejado for zero, qualquer lançamento aparece como 'Não orçado'.</t>
         </is>
       </c>
       <c r="E31" s="69" t="inlineStr">
@@ -29561,7 +29565,7 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F36" s="76" t="inlineStr">
+      <c r="F36" s="75" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -21,8 +21,8 @@
     <sheet name="Contas Pagas (detalhe)" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Controle de Equipamentos'!$A$11:$J$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$423</definedName>
@@ -1280,15 +1280,15 @@
         </is>
       </c>
       <c r="C6" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"Jurídico",Planejado!$C$5:$C$31,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$B$5:$B$32,"Jurídico",Planejado!$C$5:$C$32,"Equipe")</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$B$6:$B$33,"Jurídico",Comparativo!$C$6:$C$33,"Equipe")</f>
         <v/>
       </c>
       <c r="E6" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$B$6:$B$33,"Jurídico",Comparativo!$C$6:$C$33,"Equipe")</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -1304,7 +1304,7 @@
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$33,"&gt;0",Comparativo!$B$6:$B$33,"Jurídico",Comparativo!$C$6:$C$33,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$33,"?*",Comparativo!$B$6:$B$33,"Jurídico",Comparativo!$C$6:$C$33,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1320,15 +1320,15 @@
         </is>
       </c>
       <c r="C7" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"Jurídico",Planejado!$C$5:$C$31,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$B$5:$B$32,"Jurídico",Planejado!$C$5:$C$32,"Despesas")</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$B$6:$B$33,"Jurídico",Comparativo!$C$6:$C$33,"Despesas")</f>
         <v/>
       </c>
       <c r="E7" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$B$6:$B$33,"Jurídico",Comparativo!$C$6:$C$33,"Despesas")</f>
         <v/>
       </c>
       <c r="F7" s="9">
@@ -1344,7 +1344,7 @@
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"Jurídico",Comparativo!$C$6:$C$32,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$33,"&gt;0",Comparativo!$B$6:$B$33,"Jurídico",Comparativo!$C$6:$C$33,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$33,"?*",Comparativo!$B$6:$B$33,"Jurídico",Comparativo!$C$6:$C$33,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1360,15 +1360,15 @@
         </is>
       </c>
       <c r="C8" s="13">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="F8" s="13">
@@ -1384,7 +1384,7 @@
         <v/>
       </c>
       <c r="I8" s="15">
-        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$33,"&gt;0",Comparativo!$B$6:$B$33,"Jurídico")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$33,"?*",Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
     </row>
@@ -1400,15 +1400,15 @@
         </is>
       </c>
       <c r="C9" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"TI",Planejado!$C$5:$C$31,"Equipe")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$B$5:$B$32,"TI",Planejado!$C$5:$C$32,"Equipe")</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$B$6:$B$33,"TI",Comparativo!$C$6:$C$33,"Equipe")</f>
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Equipe")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$B$6:$B$33,"TI",Comparativo!$C$6:$C$33,"Equipe")</f>
         <v/>
       </c>
       <c r="F9" s="9">
@@ -1424,7 +1424,7 @@
         <v/>
       </c>
       <c r="I9" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Equipe")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$33,"&gt;0",Comparativo!$B$6:$B$33,"TI",Comparativo!$C$6:$C$33,"Equipe")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$33,"?*",Comparativo!$B$6:$B$33,"TI",Comparativo!$C$6:$C$33,"Equipe")</f>
         <v/>
       </c>
     </row>
@@ -1440,15 +1440,15 @@
         </is>
       </c>
       <c r="C10" s="9">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"TI",Planejado!$C$5:$C$31,"Despesas")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$B$5:$B$32,"TI",Planejado!$C$5:$C$32,"Despesas")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$B$6:$B$33,"TI",Comparativo!$C$6:$C$33,"Despesas")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Despesas")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$B$6:$B$33,"TI",Comparativo!$C$6:$C$33,"Despesas")</f>
         <v/>
       </c>
       <c r="F10" s="9">
@@ -1464,7 +1464,7 @@
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"TI",Comparativo!$C$6:$C$32,"Despesas")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$33,"&gt;0",Comparativo!$B$6:$B$33,"TI",Comparativo!$C$6:$C$33,"Despesas")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$33,"?*",Comparativo!$B$6:$B$33,"TI",Comparativo!$C$6:$C$33,"Despesas")</f>
         <v/>
       </c>
     </row>
@@ -1480,15 +1480,15 @@
         </is>
       </c>
       <c r="C11" s="13">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="13">
@@ -1504,7 +1504,7 @@
         <v/>
       </c>
       <c r="I11" s="15">
-        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0",Comparativo!$B$6:$B$32,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$32,"?*",Comparativo!$B$6:$B$32,"TI")</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$33,"&gt;0",Comparativo!$B$6:$B$33,"TI")&amp;" de "&amp;COUNTIFS(Comparativo!$A$6:$A$33,"?*",Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
     </row>
@@ -1516,15 +1516,15 @@
       </c>
       <c r="B12" s="16" t="inlineStr"/>
       <c r="C12" s="17">
-        <f>SUM(Planejado!$T$5:$T$31)</f>
+        <f>SUM(Planejado!$T$5:$T$32)</f>
         <v/>
       </c>
       <c r="D12" s="17">
-        <f>SUM(Comparativo!$I$6:$I$32)</f>
+        <f>SUM(Comparativo!$I$6:$I$33)</f>
         <v/>
       </c>
       <c r="E12" s="17">
-        <f>SUM(Comparativo!$J$6:$J$32)</f>
+        <f>SUM(Comparativo!$J$6:$J$33)</f>
         <v/>
       </c>
       <c r="F12" s="17">
@@ -1540,7 +1540,7 @@
         <v/>
       </c>
       <c r="I12" s="19">
-        <f>COUNTIFS(Comparativo!$P$6:$P$32,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$32)</f>
+        <f>COUNTIFS(Comparativo!$P$6:$P$33,"&gt;0")&amp;" de "&amp;COUNTA(Comparativo!$A$6:$A$33)</f>
         <v/>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B16" s="21" t="n"/>
       <c r="C16" s="22">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$32,"&lt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$33,"&lt;0")</f>
         <v/>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B17" s="21" t="n"/>
       <c r="C17" s="22">
-        <f>-SUMIF(Comparativo!$Q$6:$Q$32,"&gt;0")</f>
+        <f>-SUMIF(Comparativo!$Q$6:$Q$33,"&gt;0")</f>
         <v/>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B18" s="24" t="n"/>
       <c r="C18" s="25">
-        <f>-SUM(Comparativo!$Q$6:$Q$32)</f>
+        <f>-SUM(Comparativo!$Q$6:$Q$33)</f>
         <v/>
       </c>
       <c r="D18" s="26" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B19" s="21" t="n"/>
       <c r="C19" s="22">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$32)/Comparativo!$D$3*12,"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$33)/Comparativo!$D$3*12,"")</f>
         <v/>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" s="21" t="n"/>
       <c r="C20" s="27">
-        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$32)/SUM(Comparativo!$S$6:$S$32),"")</f>
+        <f>IFERROR(-SUM(Comparativo!$Q$6:$Q$33)/SUM(Comparativo!$S$6:$S$33),"")</f>
         <v/>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -1718,23 +1718,23 @@
         <v>1</v>
       </c>
       <c r="B25" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A25),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A25),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="C25" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A25),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A25),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A25),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A25),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A25),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A25),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="F25" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A25),Comparativo!$R$6:$R$32,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A25),Comparativo!$R$6:$R$33,0)),""),"")</f>
         <v/>
       </c>
       <c r="G25" s="34">
@@ -1747,23 +1747,23 @@
         <v>2</v>
       </c>
       <c r="B26" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A26),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A26),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="C26" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A26),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A26),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A26),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A26),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A26),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A26),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="F26" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A26),Comparativo!$R$6:$R$32,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A26),Comparativo!$R$6:$R$33,0)),""),"")</f>
         <v/>
       </c>
       <c r="G26" s="34">
@@ -1776,23 +1776,23 @@
         <v>3</v>
       </c>
       <c r="B27" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A27),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A27),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="C27" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A27),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A27),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A27),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A27),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A27),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A27),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="F27" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A27),Comparativo!$R$6:$R$32,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A27),Comparativo!$R$6:$R$33,0)),""),"")</f>
         <v/>
       </c>
       <c r="G27" s="34">
@@ -1805,23 +1805,23 @@
         <v>4</v>
       </c>
       <c r="B28" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A28),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A28),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="C28" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A28),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A28),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A28),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A28),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A28),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A28),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="F28" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A28),Comparativo!$R$6:$R$32,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A28),Comparativo!$R$6:$R$33,0)),""),"")</f>
         <v/>
       </c>
       <c r="G28" s="34">
@@ -1834,23 +1834,23 @@
         <v>5</v>
       </c>
       <c r="B29" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A29),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A29),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="C29" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A29),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A29),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A29),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A29),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A29),Comparativo!$R$6:$R$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A29),Comparativo!$R$6:$R$33,0)),"")</f>
         <v/>
       </c>
       <c r="F29" s="33">
-        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$R$6:$R$32,A29),Comparativo!$R$6:$R$32,0)),""),"")</f>
+        <f>IFERROR(-IFERROR(INDEX(Comparativo!$K$6:$K$33,MATCH(LARGE(Comparativo!$R$6:$R$33,A29),Comparativo!$R$6:$R$33,0)),""),"")</f>
         <v/>
       </c>
       <c r="G29" s="34">
@@ -1908,23 +1908,23 @@
         <v>1</v>
       </c>
       <c r="B34" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A34),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A34),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="C34" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A34),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A34),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A34),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A34),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A34),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A34),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="F34" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A34),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A34),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="G34" s="34">
@@ -1937,23 +1937,23 @@
         <v>2</v>
       </c>
       <c r="B35" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A35),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A35),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="C35" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A35),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A35),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A35),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A35),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A35),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A35),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="F35" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A35),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A35),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="G35" s="34">
@@ -1966,23 +1966,23 @@
         <v>3</v>
       </c>
       <c r="B36" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A36),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A36),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="C36" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A36),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A36),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A36),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A36),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A36),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A36),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="F36" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A36),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A36),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="G36" s="34">
@@ -1995,23 +1995,23 @@
         <v>4</v>
       </c>
       <c r="B37" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A37),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A37),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="C37" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A37),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A37),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A37),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A37),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A37),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A37),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="F37" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A37),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A37),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="G37" s="34">
@@ -2024,23 +2024,23 @@
         <v>5</v>
       </c>
       <c r="B38" s="31">
-        <f>IFERROR(INDEX(Comparativo!$D$6:$D$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A38),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$D$6:$D$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A38),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="C38" s="31">
-        <f>IFERROR(INDEX(Comparativo!$B$6:$B$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A38),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$B$6:$B$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A38),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$I$6:$I$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A38),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$I$6:$I$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A38),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$J$6:$J$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A38),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$J$6:$J$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A38),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="F38" s="32">
-        <f>IFERROR(INDEX(Comparativo!$K$6:$K$32,MATCH(LARGE(Comparativo!$O$6:$O$32,A38),Comparativo!$O$6:$O$32,0)),"")</f>
+        <f>IFERROR(INDEX(Comparativo!$K$6:$K$33,MATCH(LARGE(Comparativo!$O$6:$O$33,A38),Comparativo!$O$6:$O$33,0)),"")</f>
         <v/>
       </c>
       <c r="G38" s="34">
@@ -21021,7 +21021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23281,57 +23281,135 @@
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="47">
+        <f>Planejado!A32</f>
+        <v/>
+      </c>
+      <c r="B33" s="47">
+        <f>Planejado!B32</f>
+        <v/>
+      </c>
+      <c r="C33" s="47">
+        <f>Planejado!C32</f>
+        <v/>
+      </c>
+      <c r="D33" s="48">
+        <f>Planejado!D32</f>
+        <v/>
+      </c>
+      <c r="E33" s="47">
+        <f>Planejado!G32</f>
+        <v/>
+      </c>
+      <c r="F33" s="49">
+        <f>INDEX(Planejado!$H32:$S32,$D$3)</f>
+        <v/>
+      </c>
+      <c r="G33" s="49">
+        <f>INDEX(Realizado!$H32:$S32,$D$3)</f>
+        <v/>
+      </c>
+      <c r="H33" s="49">
+        <f>G33-F33</f>
+        <v/>
+      </c>
+      <c r="I33" s="49">
+        <f>SUMPRODUCT((COLUMN(Planejado!$H$4:$S$4)-COLUMN(Planejado!$H$4)+1&lt;=$D$3)*Planejado!$H32:$S32)</f>
+        <v/>
+      </c>
+      <c r="J33" s="49">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*Realizado!$H32:$S32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="49">
+        <f>J33-I33</f>
+        <v/>
+      </c>
+      <c r="L33" s="50">
+        <f>IFERROR(K33/I33,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="50">
+        <f>IFERROR(J33/I33,"")</f>
+        <v/>
+      </c>
+      <c r="N33" s="51">
+        <f>IF(P33=0,"Sem lançamento",IF(AND(I33=0,J33=0),"—",IF(I33=0,"Não orçado",IF(K33&gt;0.05*I33,"Acima do orçado",IF(K33&lt;-0.05*I33,"Abaixo do orçado","Dentro do orçado")))))</f>
+        <v/>
+      </c>
+      <c r="O33" s="39">
+        <f>IF(K33&gt;1,K33+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="P33" s="52">
+        <f>SUMPRODUCT((COLUMN(Realizado!$H$4:$S$4)-COLUMN(Realizado!$H$4)+1&lt;=$D$3)*(Realizado!$H32:$S32&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="Q33" s="46">
+        <f>IF(P33=0,"",K33)</f>
+        <v/>
+      </c>
+      <c r="R33" s="46">
+        <f>IF(AND(Q33&lt;&gt;"",Q33&lt;-1),-Q33+ROW()/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="S33" s="46">
+        <f>IF(Q33="","",I33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="17">
-        <f>SUM(F6:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="17">
-        <f>SUM(G6:G32)</f>
-        <v/>
-      </c>
-      <c r="H33" s="17">
-        <f>SUM(H6:H32)</f>
-        <v/>
-      </c>
-      <c r="I33" s="17">
-        <f>SUM(I6:I32)</f>
-        <v/>
-      </c>
-      <c r="J33" s="17">
-        <f>SUM(J6:J32)</f>
-        <v/>
-      </c>
-      <c r="K33" s="17">
-        <f>SUM(K6:K32)</f>
-        <v/>
-      </c>
-      <c r="L33" s="53">
-        <f>IFERROR(K33/I33,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="53">
-        <f>IFERROR(J33/I33,"")</f>
-        <v/>
-      </c>
-      <c r="N33" s="16" t="n"/>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
+      <c r="F34" s="17">
+        <f>SUM(F6:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="17">
+        <f>SUM(G6:G33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="17">
+        <f>SUM(H6:H33)</f>
+        <v/>
+      </c>
+      <c r="I34" s="17">
+        <f>SUM(I6:I33)</f>
+        <v/>
+      </c>
+      <c r="J34" s="17">
+        <f>SUM(J6:J33)</f>
+        <v/>
+      </c>
+      <c r="K34" s="17">
+        <f>SUM(K6:K33)</f>
+        <v/>
+      </c>
+      <c r="L34" s="53">
+        <f>IFERROR(K34/I34,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="53">
+        <f>IFERROR(J34/I34,"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="16" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N32"/>
+  <autoFilter ref="A5:N33"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H32">
+  <conditionalFormatting sqref="H6:H33">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -23339,7 +23417,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K32">
+  <conditionalFormatting sqref="K6:K33">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -23362,7 +23440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:T33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24264,7 +24342,7 @@
       </c>
       <c r="E15" s="48" t="inlineStr">
         <is>
-          <t>Analista Administrativo — orçado pelo custo total (encargos de folha + benefícios). Salário bruto: R$ 2.570,52/mês até jul/26 e R$ 3.070,52 a partir de 05/08/26, aumento absorvido pela folga do envelope</t>
+          <t>Analista Administrativo — suporte ao usuário, rotina administrativa do orçamento e apoio operacional ao desenvolvimento conduzido pelo consultor. Orçado pelo custo total (encargos de folha + benefícios). Salário bruto: R$ 2.570,52/mês até jul/26 e R$ 3.070,52 a partir de 05/08/26, aumento absorvido pela folga do envelope</t>
         </is>
       </c>
       <c r="F15" s="47" t="inlineStr">
@@ -24413,12 +24491,12 @@
       </c>
       <c r="D17" s="48" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Jonathan — consultor (desde abr/26)</t>
         </is>
       </c>
       <c r="E17" s="48" t="inlineStr">
         <is>
-          <t>Consultor — orçado desde jan/26. As atividades só começaram em abr/26: a contratação foi segurada por três meses</t>
+          <t>Consultor/desenvolvedor, 3 dias por semana (104 h/mês) desde abr/26. Orçado em R$ 10.000/mês desde jan/26; a contratação foi segurada por três meses. Credor no SIENGE: J H ALVES — MONITOR REMOTO</t>
         </is>
       </c>
       <c r="F17" s="47" t="inlineStr">
@@ -24475,7 +24553,7 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="47" t="inlineStr">
         <is>
-          <t>TI-D01</t>
+          <t>TI-E04</t>
         </is>
       </c>
       <c r="B18" s="47" t="inlineStr">
@@ -24485,60 +24563,64 @@
       </c>
       <c r="C18" s="47" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>Equipe</t>
         </is>
       </c>
       <c r="D18" s="48" t="inlineStr">
         <is>
-          <t>Peças de Manutenção</t>
+          <t>Monitor Remoto — serviços esporádicos (até mar/26)</t>
         </is>
       </c>
       <c r="E18" s="48" t="inlineStr">
         <is>
-          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
-        </is>
-      </c>
-      <c r="F18" s="47" t="inlineStr"/>
+          <t>Mesmo prestador do TI-E03, em vínculo anterior: serviços esporádicos prestados de fora, encerrados quando ele passou a atuar como consultor fixo em abr/26. Não constava na ficha de orçamento</t>
+        </is>
+      </c>
+      <c r="F18" s="47" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
       <c r="G18" s="47" t="inlineStr">
         <is>
-          <t>Equipamentos Eletrônicos Diversos</t>
+          <t>Pessoal - PJ</t>
         </is>
       </c>
       <c r="H18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="J18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="K18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="L18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="M18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="N18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="O18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="P18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="R18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="S18" s="49" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="T18" s="54">
         <f>SUM(H18:S18)</f>
@@ -24548,7 +24630,7 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="47" t="inlineStr">
         <is>
-          <t>TI-D02</t>
+          <t>TI-D01</t>
         </is>
       </c>
       <c r="B19" s="47" t="inlineStr">
@@ -24563,55 +24645,55 @@
       </c>
       <c r="D19" s="48" t="inlineStr">
         <is>
-          <t>Backup em Nuvem</t>
+          <t>Peças de Manutenção</t>
         </is>
       </c>
       <c r="E19" s="48" t="inlineStr">
         <is>
-          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
+          <t>Tela, teclado, carcaça, mouses de reposição, carregadores etc.</t>
         </is>
       </c>
       <c r="F19" s="47" t="inlineStr"/>
       <c r="G19" s="47" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Equipamentos Eletrônicos Diversos</t>
         </is>
       </c>
       <c r="H19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="J19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="K19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="L19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="M19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="N19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="O19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="P19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="Q19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="R19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="S19" s="49" t="n">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="T19" s="54">
         <f>SUM(H19:S19)</f>
@@ -24621,7 +24703,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="47" t="inlineStr">
         <is>
-          <t>TI-D03</t>
+          <t>TI-D02</t>
         </is>
       </c>
       <c r="B20" s="47" t="inlineStr">
@@ -24636,12 +24718,12 @@
       </c>
       <c r="D20" s="48" t="inlineStr">
         <is>
-          <t>Inteligência Artificial (Adapta)</t>
+          <t>Backup em Nuvem</t>
         </is>
       </c>
       <c r="E20" s="48" t="inlineStr">
         <is>
-          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR. Pagamentos reais de R$ 575/mês estão lançados no centro de custo Jurídico por engano (ver pendência Q)</t>
+          <t>Serviço de backup em nuvem para servidor — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F20" s="47" t="inlineStr"/>
@@ -24651,40 +24733,40 @@
         </is>
       </c>
       <c r="H20" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="J20" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="K20" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="L20" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="M20" s="49" t="n">
-        <v>1300</v>
+        <v>825</v>
       </c>
       <c r="N20" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="O20" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="P20" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="Q20" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="R20" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="S20" s="49" t="n">
-        <v>1600</v>
+        <v>825</v>
       </c>
       <c r="T20" s="54">
         <f>SUM(H20:S20)</f>
@@ -24694,7 +24776,7 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="47" t="inlineStr">
         <is>
-          <t>TI-D04</t>
+          <t>TI-D03</t>
         </is>
       </c>
       <c r="B21" s="47" t="inlineStr">
@@ -24709,12 +24791,12 @@
       </c>
       <c r="D21" s="48" t="inlineStr">
         <is>
-          <t>Antivírus</t>
+          <t>Inteligência Artificial (Adapta)</t>
         </is>
       </c>
       <c r="E21" s="48" t="inlineStr">
         <is>
-          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
+          <t>Plataforma de IA para utilização de agentes — RATEIO A DEFINIR. Pagamentos reais de R$ 575/mês estão lançados no centro de custo Jurídico por engano (ver pendência Q)</t>
         </is>
       </c>
       <c r="F21" s="47" t="inlineStr"/>
@@ -24724,40 +24806,40 @@
         </is>
       </c>
       <c r="H21" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="J21" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="K21" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="L21" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="M21" s="49" t="n">
-        <v>240</v>
+        <v>1300</v>
       </c>
       <c r="N21" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="O21" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="P21" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="Q21" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="R21" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="S21" s="49" t="n">
-        <v>240</v>
+        <v>1600</v>
       </c>
       <c r="T21" s="54">
         <f>SUM(H21:S21)</f>
@@ -24767,7 +24849,7 @@
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="47" t="inlineStr">
         <is>
-          <t>TI-D05</t>
+          <t>TI-D04</t>
         </is>
       </c>
       <c r="B22" s="47" t="inlineStr">
@@ -24782,12 +24864,12 @@
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
-          <t>Pacote Office 365</t>
+          <t>Antivírus</t>
         </is>
       </c>
       <c r="E22" s="48" t="inlineStr">
         <is>
-          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
+          <t>Proteção para equipamentos — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F22" s="47" t="inlineStr"/>
@@ -24797,40 +24879,40 @@
         </is>
       </c>
       <c r="H22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="J22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="K22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="L22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="M22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="N22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="O22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="P22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="Q22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="R22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="S22" s="49" t="n">
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="T22" s="54">
         <f>SUM(H22:S22)</f>
@@ -24840,7 +24922,7 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="47" t="inlineStr">
         <is>
-          <t>TI-D06</t>
+          <t>TI-D05</t>
         </is>
       </c>
       <c r="B23" s="47" t="inlineStr">
@@ -24855,55 +24937,55 @@
       </c>
       <c r="D23" s="48" t="inlineStr">
         <is>
-          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
+          <t>Pacote Office 365</t>
         </is>
       </c>
       <c r="E23" s="48" t="inlineStr">
         <is>
-          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
+          <t>Licenças de software (conferir nº de licenças x usuários) — RATEIO A DEFINIR</t>
         </is>
       </c>
       <c r="F23" s="47" t="inlineStr"/>
       <c r="G23" s="47" t="inlineStr">
         <is>
-          <t>Móveis e Utensílios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="J23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="K23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="L23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="M23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="N23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="O23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="P23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="Q23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="R23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="S23" s="49" t="n">
-        <v>2800</v>
+        <v>375</v>
       </c>
       <c r="T23" s="54">
         <f>SUM(H23:S23)</f>
@@ -24913,7 +24995,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="47" t="inlineStr">
         <is>
-          <t>TI-D07</t>
+          <t>TI-D06</t>
         </is>
       </c>
       <c r="B24" s="47" t="inlineStr">
@@ -24928,51 +25010,55 @@
       </c>
       <c r="D24" s="48" t="inlineStr">
         <is>
-          <t>Cursos e Treinamentos</t>
-        </is>
-      </c>
-      <c r="E24" s="48" t="inlineStr"/>
+          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
+        </is>
+      </c>
+      <c r="E24" s="48" t="inlineStr">
+        <is>
+          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
+        </is>
+      </c>
       <c r="F24" s="47" t="inlineStr"/>
       <c r="G24" s="47" t="inlineStr">
         <is>
-          <t>Custeio de Treinamento</t>
+          <t>Móveis e Utensílios</t>
         </is>
       </c>
       <c r="H24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="J24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="K24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="L24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="M24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="N24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="O24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="P24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="Q24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="R24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="S24" s="49" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="T24" s="54">
         <f>SUM(H24:S24)</f>
@@ -24982,7 +25068,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="47" t="inlineStr">
         <is>
-          <t>TI-D08</t>
+          <t>TI-D07</t>
         </is>
       </c>
       <c r="B25" s="47" t="inlineStr">
@@ -24997,51 +25083,51 @@
       </c>
       <c r="D25" s="48" t="inlineStr">
         <is>
-          <t>Aplicativo de Gravação de Reunião</t>
+          <t>Cursos e Treinamentos</t>
         </is>
       </c>
       <c r="E25" s="48" t="inlineStr"/>
       <c r="F25" s="47" t="inlineStr"/>
       <c r="G25" s="47" t="inlineStr">
         <is>
-          <t>Licenças de Softwares</t>
+          <t>Custeio de Treinamento</t>
         </is>
       </c>
       <c r="H25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="J25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="K25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="M25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="N25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="O25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="P25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="Q25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="R25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="S25" s="49" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="T25" s="54">
         <f>SUM(H25:S25)</f>
@@ -25051,7 +25137,7 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="47" t="inlineStr">
         <is>
-          <t>TI-D10</t>
+          <t>TI-D08</t>
         </is>
       </c>
       <c r="B26" s="47" t="inlineStr">
@@ -25066,14 +25152,10 @@
       </c>
       <c r="D26" s="48" t="inlineStr">
         <is>
-          <t>Claude</t>
-        </is>
-      </c>
-      <c r="E26" s="48" t="inlineStr">
-        <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas</t>
-        </is>
-      </c>
+          <t>Aplicativo de Gravação de Reunião</t>
+        </is>
+      </c>
+      <c r="E26" s="48" t="inlineStr"/>
       <c r="F26" s="47" t="inlineStr"/>
       <c r="G26" s="47" t="inlineStr">
         <is>
@@ -25081,40 +25163,40 @@
         </is>
       </c>
       <c r="H26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="J26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="K26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="L26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="M26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="N26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="O26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="P26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="Q26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="R26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="S26" s="49" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="T26" s="54">
         <f>SUM(H26:S26)</f>
@@ -25124,7 +25206,7 @@
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="47" t="inlineStr">
         <is>
-          <t>TI-D11</t>
+          <t>TI-D10</t>
         </is>
       </c>
       <c r="B27" s="47" t="inlineStr">
@@ -25139,7 +25221,7 @@
       </c>
       <c r="D27" s="48" t="inlineStr">
         <is>
-          <t>GPT</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="E27" s="48" t="inlineStr">
@@ -25197,7 +25279,7 @@
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="47" t="inlineStr">
         <is>
-          <t>TI-D12</t>
+          <t>TI-D11</t>
         </is>
       </c>
       <c r="B28" s="47" t="inlineStr">
@@ -25212,12 +25294,12 @@
       </c>
       <c r="D28" s="48" t="inlineStr">
         <is>
-          <t>Adapta One</t>
+          <t>GPT</t>
         </is>
       </c>
       <c r="E28" s="48" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas</t>
         </is>
       </c>
       <c r="F28" s="47" t="inlineStr"/>
@@ -25270,7 +25352,7 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="47" t="inlineStr">
         <is>
-          <t>TI-D13</t>
+          <t>TI-D12</t>
         </is>
       </c>
       <c r="B29" s="47" t="inlineStr">
@@ -25285,12 +25367,12 @@
       </c>
       <c r="D29" s="48" t="inlineStr">
         <is>
-          <t>Adapta Skip</t>
+          <t>Adapta One</t>
         </is>
       </c>
       <c r="E29" s="48" t="inlineStr">
         <is>
-          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR sobreposição com a linha 'Inteligência Artificial (Adapta)'</t>
         </is>
       </c>
       <c r="F29" s="47" t="inlineStr"/>
@@ -25343,7 +25425,7 @@
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="47" t="inlineStr">
         <is>
-          <t>TI-D14</t>
+          <t>TI-D13</t>
         </is>
       </c>
       <c r="B30" s="47" t="inlineStr">
@@ -25358,12 +25440,12 @@
       </c>
       <c r="D30" s="48" t="inlineStr">
         <is>
-          <t>AnyDesk</t>
+          <t>Adapta Skip</t>
         </is>
       </c>
       <c r="E30" s="48" t="inlineStr">
         <is>
-          <t>Licença de acesso remoto — contratação prevista, não constava na ficha. Valor e mês de início a definir. CONFERIR sobreposição com o serviço de monitoramento remoto já contratado (J H Alves)</t>
+          <t>Ferramenta de IA — não constava na ficha. Planejado a definir com a diretoria. RATEIO A DEFINIR: uso transversal entre as áreas. CONFERIR o nome exato do produto e a sobreposição com 'Inteligência Artificial (Adapta)'</t>
         </is>
       </c>
       <c r="F30" s="47" t="inlineStr"/>
@@ -25416,7 +25498,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="47" t="inlineStr">
         <is>
-          <t>TI-D09</t>
+          <t>TI-D14</t>
         </is>
       </c>
       <c r="B31" s="47" t="inlineStr">
@@ -25431,18 +25513,18 @@
       </c>
       <c r="D31" s="48" t="inlineStr">
         <is>
-          <t>Bonificação do time</t>
+          <t>AnyDesk</t>
         </is>
       </c>
       <c r="E31" s="48" t="inlineStr">
         <is>
-          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+          <t>Licença de acesso remoto — contratação prevista, não constava na ficha. Valor e mês de início a definir. CONFERIR sobreposição com o serviço de monitoramento remoto já contratado (J H Alves)</t>
         </is>
       </c>
       <c r="F31" s="47" t="inlineStr"/>
       <c r="G31" s="47" t="inlineStr">
         <is>
-          <t>Prêmios</t>
+          <t>Licenças de Softwares</t>
         </is>
       </c>
       <c r="H31" s="49" t="n">
@@ -25467,7 +25549,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="49" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="P31" s="49" t="n">
         <v>0</v>
@@ -25479,80 +25561,153 @@
         <v>0</v>
       </c>
       <c r="S31" s="49" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="T31" s="54">
         <f>SUM(H31:S31)</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="47" t="inlineStr">
+        <is>
+          <t>TI-D09</t>
+        </is>
+      </c>
+      <c r="B32" s="47" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C32" s="47" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="D32" s="48" t="inlineStr">
+        <is>
+          <t>Bonificação do time</t>
+        </is>
+      </c>
+      <c r="E32" s="48" t="inlineStr">
+        <is>
+          <t>Cumprimento de prazos e participação em projetos — CONFIRMAR se houve parcela no 1º quadrimestre</t>
+        </is>
+      </c>
+      <c r="F32" s="47" t="inlineStr"/>
+      <c r="G32" s="47" t="inlineStr">
+        <is>
+          <t>Prêmios</t>
+        </is>
+      </c>
+      <c r="H32" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="49" t="n">
+        <v>2400</v>
+      </c>
+      <c r="P32" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="49" t="n">
+        <v>3600</v>
+      </c>
+      <c r="T32" s="54">
+        <f>SUM(H32:S32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="17">
-        <f>SUM(H5:H31)</f>
-        <v/>
-      </c>
-      <c r="I32" s="17">
-        <f>SUM(I5:I31)</f>
-        <v/>
-      </c>
-      <c r="J32" s="17">
-        <f>SUM(J5:J31)</f>
-        <v/>
-      </c>
-      <c r="K32" s="17">
-        <f>SUM(K5:K31)</f>
-        <v/>
-      </c>
-      <c r="L32" s="17">
-        <f>SUM(L5:L31)</f>
-        <v/>
-      </c>
-      <c r="M32" s="17">
-        <f>SUM(M5:M31)</f>
-        <v/>
-      </c>
-      <c r="N32" s="17">
-        <f>SUM(N5:N31)</f>
-        <v/>
-      </c>
-      <c r="O32" s="17">
-        <f>SUM(O5:O31)</f>
-        <v/>
-      </c>
-      <c r="P32" s="17">
-        <f>SUM(P5:P31)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="17">
-        <f>SUM(Q5:Q31)</f>
-        <v/>
-      </c>
-      <c r="R32" s="17">
-        <f>SUM(R5:R31)</f>
-        <v/>
-      </c>
-      <c r="S32" s="17">
-        <f>SUM(S5:S31)</f>
-        <v/>
-      </c>
-      <c r="T32" s="17">
-        <f>SUM(T5:T31)</f>
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="16" t="n"/>
+      <c r="H33" s="17">
+        <f>SUM(H5:H32)</f>
+        <v/>
+      </c>
+      <c r="I33" s="17">
+        <f>SUM(I5:I32)</f>
+        <v/>
+      </c>
+      <c r="J33" s="17">
+        <f>SUM(J5:J32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="17">
+        <f>SUM(K5:K32)</f>
+        <v/>
+      </c>
+      <c r="L33" s="17">
+        <f>SUM(L5:L32)</f>
+        <v/>
+      </c>
+      <c r="M33" s="17">
+        <f>SUM(M5:M32)</f>
+        <v/>
+      </c>
+      <c r="N33" s="17">
+        <f>SUM(N5:N32)</f>
+        <v/>
+      </c>
+      <c r="O33" s="17">
+        <f>SUM(O5:O32)</f>
+        <v/>
+      </c>
+      <c r="P33" s="17">
+        <f>SUM(P5:P32)</f>
+        <v/>
+      </c>
+      <c r="Q33" s="17">
+        <f>SUM(Q5:Q32)</f>
+        <v/>
+      </c>
+      <c r="R33" s="17">
+        <f>SUM(R5:R32)</f>
+        <v/>
+      </c>
+      <c r="S33" s="17">
+        <f>SUM(S5:S32)</f>
+        <v/>
+      </c>
+      <c r="T33" s="17">
+        <f>SUM(T5:T32)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:T31"/>
+  <autoFilter ref="A4:T32"/>
   <mergeCells count="2">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="A2:T2"/>
@@ -25567,7 +25722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26590,7 +26745,7 @@
         <v/>
       </c>
       <c r="H17" s="58" t="n">
-        <v>4311.56</v>
+        <v>0</v>
       </c>
       <c r="I17" s="58" t="n">
         <v>0</v>
@@ -26626,7 +26781,7 @@
       </c>
       <c r="V17" s="59" t="inlineStr">
         <is>
-          <t>Credor 'J H ALVES - MONITOR REMOTO'. Pagamentos: 19/01 NFS.70 R$ 4.311,56; 01/05 NFS.76 R$ 3.723,62; 01/06 NFS.78 R$ 6.173,37; 01/07 NFS.3 R$ 6.300,00. Sem pagamento em fev, mar e abr</t>
+          <t>01/05 NFS.76 R$ 3.723,62; 01/06 NFS.78 R$ 6.173,37; 01/07 NFS.3 R$ 6.300,00. Sem pagamento em jan–abr: contratação segurada</t>
         </is>
       </c>
     </row>
@@ -26659,24 +26814,56 @@
         <f>Planejado!G18</f>
         <v/>
       </c>
-      <c r="H18" s="58" t="n"/>
-      <c r="I18" s="58" t="n"/>
-      <c r="J18" s="58" t="n"/>
-      <c r="K18" s="58" t="n"/>
-      <c r="L18" s="58" t="n"/>
-      <c r="M18" s="58" t="n"/>
-      <c r="N18" s="58" t="n"/>
-      <c r="O18" s="58" t="n"/>
-      <c r="P18" s="58" t="n"/>
-      <c r="Q18" s="58" t="n"/>
-      <c r="R18" s="58" t="n"/>
-      <c r="S18" s="58" t="n"/>
+      <c r="H18" s="58" t="n">
+        <v>4311.56</v>
+      </c>
+      <c r="I18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="58" t="n">
+        <v>0</v>
+      </c>
       <c r="T18" s="54">
         <f>SUM(H18:S18)</f>
         <v/>
       </c>
-      <c r="U18" s="59" t="n"/>
-      <c r="V18" s="59" t="n"/>
+      <c r="U18" s="59" t="inlineStr">
+        <is>
+          <t>Extrato do financeiro</t>
+        </is>
+      </c>
+      <c r="V18" s="59" t="inlineStr">
+        <is>
+          <t>19/01 NFS.70 R$ 4.311,56 — serviço esporádico, provavelmente referente a dez/25. Vínculo encerrado com a entrada como consultor fixo</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="56">
@@ -27302,72 +27489,120 @@
       <c r="U31" s="59" t="n"/>
       <c r="V31" s="59" t="n"/>
     </row>
-    <row r="32">
-      <c r="A32" s="60" t="inlineStr">
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="56">
+        <f>Planejado!A32</f>
+        <v/>
+      </c>
+      <c r="B32" s="56">
+        <f>Planejado!B32</f>
+        <v/>
+      </c>
+      <c r="C32" s="56">
+        <f>Planejado!C32</f>
+        <v/>
+      </c>
+      <c r="D32" s="57">
+        <f>Planejado!D32</f>
+        <v/>
+      </c>
+      <c r="E32" s="57">
+        <f>Planejado!E32</f>
+        <v/>
+      </c>
+      <c r="F32" s="56">
+        <f>Planejado!F32</f>
+        <v/>
+      </c>
+      <c r="G32" s="56">
+        <f>Planejado!G32</f>
+        <v/>
+      </c>
+      <c r="H32" s="58" t="n"/>
+      <c r="I32" s="58" t="n"/>
+      <c r="J32" s="58" t="n"/>
+      <c r="K32" s="58" t="n"/>
+      <c r="L32" s="58" t="n"/>
+      <c r="M32" s="58" t="n"/>
+      <c r="N32" s="58" t="n"/>
+      <c r="O32" s="58" t="n"/>
+      <c r="P32" s="58" t="n"/>
+      <c r="Q32" s="58" t="n"/>
+      <c r="R32" s="58" t="n"/>
+      <c r="S32" s="58" t="n"/>
+      <c r="T32" s="54">
+        <f>SUM(H32:S32)</f>
+        <v/>
+      </c>
+      <c r="U32" s="59" t="n"/>
+      <c r="V32" s="59" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="60" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B32" s="60" t="n"/>
-      <c r="C32" s="60" t="n"/>
-      <c r="D32" s="60" t="n"/>
-      <c r="E32" s="60" t="n"/>
-      <c r="F32" s="60" t="n"/>
-      <c r="G32" s="60" t="n"/>
-      <c r="H32" s="61">
-        <f>SUM(H5:H31)</f>
-        <v/>
-      </c>
-      <c r="I32" s="61">
-        <f>SUM(I5:I31)</f>
-        <v/>
-      </c>
-      <c r="J32" s="61">
-        <f>SUM(J5:J31)</f>
-        <v/>
-      </c>
-      <c r="K32" s="61">
-        <f>SUM(K5:K31)</f>
-        <v/>
-      </c>
-      <c r="L32" s="61">
-        <f>SUM(L5:L31)</f>
-        <v/>
-      </c>
-      <c r="M32" s="61">
-        <f>SUM(M5:M31)</f>
-        <v/>
-      </c>
-      <c r="N32" s="61">
-        <f>SUM(N5:N31)</f>
-        <v/>
-      </c>
-      <c r="O32" s="61">
-        <f>SUM(O5:O31)</f>
-        <v/>
-      </c>
-      <c r="P32" s="61">
-        <f>SUM(P5:P31)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="61">
-        <f>SUM(Q5:Q31)</f>
-        <v/>
-      </c>
-      <c r="R32" s="61">
-        <f>SUM(R5:R31)</f>
-        <v/>
-      </c>
-      <c r="S32" s="61">
-        <f>SUM(S5:S31)</f>
-        <v/>
-      </c>
-      <c r="T32" s="61">
-        <f>SUM(T5:T31)</f>
-        <v/>
-      </c>
-      <c r="U32" s="60" t="n"/>
-      <c r="V32" s="60" t="n"/>
+      <c r="B33" s="60" t="n"/>
+      <c r="C33" s="60" t="n"/>
+      <c r="D33" s="60" t="n"/>
+      <c r="E33" s="60" t="n"/>
+      <c r="F33" s="60" t="n"/>
+      <c r="G33" s="60" t="n"/>
+      <c r="H33" s="61">
+        <f>SUM(H5:H32)</f>
+        <v/>
+      </c>
+      <c r="I33" s="61">
+        <f>SUM(I5:I32)</f>
+        <v/>
+      </c>
+      <c r="J33" s="61">
+        <f>SUM(J5:J32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="61">
+        <f>SUM(K5:K32)</f>
+        <v/>
+      </c>
+      <c r="L33" s="61">
+        <f>SUM(L5:L32)</f>
+        <v/>
+      </c>
+      <c r="M33" s="61">
+        <f>SUM(M5:M32)</f>
+        <v/>
+      </c>
+      <c r="N33" s="61">
+        <f>SUM(N5:N32)</f>
+        <v/>
+      </c>
+      <c r="O33" s="61">
+        <f>SUM(O5:O32)</f>
+        <v/>
+      </c>
+      <c r="P33" s="61">
+        <f>SUM(P5:P32)</f>
+        <v/>
+      </c>
+      <c r="Q33" s="61">
+        <f>SUM(Q5:Q32)</f>
+        <v/>
+      </c>
+      <c r="R33" s="61">
+        <f>SUM(R5:R32)</f>
+        <v/>
+      </c>
+      <c r="S33" s="61">
+        <f>SUM(S5:S32)</f>
+        <v/>
+      </c>
+      <c r="T33" s="61">
+        <f>SUM(T5:T32)</f>
+        <v/>
+      </c>
+      <c r="U33" s="60" t="n"/>
+      <c r="V33" s="60" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -27472,19 +27707,19 @@
         </is>
       </c>
       <c r="B5" s="42">
-        <f>SUMIFS(Planejado!$H$5:$H$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="42">
-        <f>SUMIFS(Realizado!$H$5:$H$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="42">
-        <f>SUMIFS(Planejado!$H$5:$H$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$H$5:$H$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="42">
-        <f>SUMIFS(Realizado!$H$5:$H$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$H$5:$H$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="42">
@@ -27515,19 +27750,19 @@
         </is>
       </c>
       <c r="B6" s="49">
-        <f>SUMIFS(Planejado!$I$5:$I$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="49">
-        <f>SUMIFS(Realizado!$I$5:$I$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="49">
-        <f>SUMIFS(Planejado!$I$5:$I$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$I$5:$I$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="49">
-        <f>SUMIFS(Realizado!$I$5:$I$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$I$5:$I$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="49">
@@ -27558,19 +27793,19 @@
         </is>
       </c>
       <c r="B7" s="42">
-        <f>SUMIFS(Planejado!$J$5:$J$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="42">
-        <f>SUMIFS(Realizado!$J$5:$J$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="42">
-        <f>SUMIFS(Planejado!$J$5:$J$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$J$5:$J$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="42">
-        <f>SUMIFS(Realizado!$J$5:$J$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$J$5:$J$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="42">
@@ -27601,19 +27836,19 @@
         </is>
       </c>
       <c r="B8" s="49">
-        <f>SUMIFS(Planejado!$K$5:$K$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="49">
-        <f>SUMIFS(Realizado!$K$5:$K$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="49">
-        <f>SUMIFS(Planejado!$K$5:$K$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$K$5:$K$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="49">
-        <f>SUMIFS(Realizado!$K$5:$K$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$K$5:$K$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="49">
@@ -27644,19 +27879,19 @@
         </is>
       </c>
       <c r="B9" s="42">
-        <f>SUMIFS(Planejado!$L$5:$L$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="42">
-        <f>SUMIFS(Realizado!$L$5:$L$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="42">
-        <f>SUMIFS(Planejado!$L$5:$L$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$L$5:$L$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="42">
-        <f>SUMIFS(Realizado!$L$5:$L$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$L$5:$L$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="42">
@@ -27687,19 +27922,19 @@
         </is>
       </c>
       <c r="B10" s="49">
-        <f>SUMIFS(Planejado!$M$5:$M$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="49">
-        <f>SUMIFS(Realizado!$M$5:$M$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="49">
-        <f>SUMIFS(Planejado!$M$5:$M$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$M$5:$M$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="49">
-        <f>SUMIFS(Realizado!$M$5:$M$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$M$5:$M$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="49">
@@ -27730,19 +27965,19 @@
         </is>
       </c>
       <c r="B11" s="42">
-        <f>SUMIFS(Planejado!$N$5:$N$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="42">
-        <f>SUMIFS(Realizado!$N$5:$N$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="42">
-        <f>SUMIFS(Planejado!$N$5:$N$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$N$5:$N$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="42">
-        <f>SUMIFS(Realizado!$N$5:$N$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$N$5:$N$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="42">
@@ -27773,19 +28008,19 @@
         </is>
       </c>
       <c r="B12" s="49">
-        <f>SUMIFS(Planejado!$O$5:$O$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C12" s="49">
-        <f>SUMIFS(Realizado!$O$5:$O$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D12" s="49">
-        <f>SUMIFS(Planejado!$O$5:$O$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$O$5:$O$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E12" s="49">
-        <f>SUMIFS(Realizado!$O$5:$O$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$O$5:$O$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F12" s="49">
@@ -27816,19 +28051,19 @@
         </is>
       </c>
       <c r="B13" s="42">
-        <f>SUMIFS(Planejado!$P$5:$P$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C13" s="42">
-        <f>SUMIFS(Realizado!$P$5:$P$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D13" s="42">
-        <f>SUMIFS(Planejado!$P$5:$P$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$P$5:$P$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E13" s="42">
-        <f>SUMIFS(Realizado!$P$5:$P$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$P$5:$P$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F13" s="42">
@@ -27859,19 +28094,19 @@
         </is>
       </c>
       <c r="B14" s="49">
-        <f>SUMIFS(Planejado!$Q$5:$Q$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C14" s="49">
-        <f>SUMIFS(Realizado!$Q$5:$Q$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D14" s="49">
-        <f>SUMIFS(Planejado!$Q$5:$Q$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$Q$5:$Q$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E14" s="49">
-        <f>SUMIFS(Realizado!$Q$5:$Q$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$Q$5:$Q$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F14" s="49">
@@ -27902,19 +28137,19 @@
         </is>
       </c>
       <c r="B15" s="42">
-        <f>SUMIFS(Planejado!$R$5:$R$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C15" s="42">
-        <f>SUMIFS(Realizado!$R$5:$R$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D15" s="42">
-        <f>SUMIFS(Planejado!$R$5:$R$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$R$5:$R$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E15" s="42">
-        <f>SUMIFS(Realizado!$R$5:$R$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$R$5:$R$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F15" s="42">
@@ -27945,19 +28180,19 @@
         </is>
       </c>
       <c r="B16" s="49">
-        <f>SUMIFS(Planejado!$S$5:$S$31,Planejado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$32,Planejado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="C16" s="49">
-        <f>SUMIFS(Realizado!$S$5:$S$31,Realizado!$B$5:$B$31,"Jurídico")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$32,Realizado!$B$5:$B$32,"Jurídico")</f>
         <v/>
       </c>
       <c r="D16" s="49">
-        <f>SUMIFS(Planejado!$S$5:$S$31,Planejado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Planejado!$S$5:$S$32,Planejado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="E16" s="49">
-        <f>SUMIFS(Realizado!$S$5:$S$31,Realizado!$B$5:$B$31,"TI")</f>
+        <f>SUMIFS(Realizado!$S$5:$S$32,Realizado!$B$5:$B$32,"TI")</f>
         <v/>
       </c>
       <c r="F16" s="49">
@@ -28130,19 +28365,19 @@
         </is>
       </c>
       <c r="B5" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A5,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A5,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="C5" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A5,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A5,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="D5" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A5,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A5,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="E5" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A5,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A5,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="F5" s="42">
@@ -28162,7 +28397,7 @@
         <v/>
       </c>
       <c r="J5" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A5)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$G$5:$G$32,$A5)</f>
         <v/>
       </c>
     </row>
@@ -28173,19 +28408,19 @@
         </is>
       </c>
       <c r="B6" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A6,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A6,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="C6" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A6,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A6,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="D6" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A6,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A6,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="E6" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A6,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A6,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="F6" s="49">
@@ -28205,7 +28440,7 @@
         <v/>
       </c>
       <c r="J6" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A6)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$G$5:$G$32,$A6)</f>
         <v/>
       </c>
     </row>
@@ -28216,19 +28451,19 @@
         </is>
       </c>
       <c r="B7" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A7,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A7,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="C7" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A7,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A7,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="D7" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A7,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A7,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="E7" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A7,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A7,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="F7" s="42">
@@ -28248,7 +28483,7 @@
         <v/>
       </c>
       <c r="J7" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A7)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$G$5:$G$32,$A7)</f>
         <v/>
       </c>
     </row>
@@ -28259,19 +28494,19 @@
         </is>
       </c>
       <c r="B8" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A8,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A8,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="C8" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A8,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A8,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="D8" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A8,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A8,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="E8" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A8,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A8,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="F8" s="49">
@@ -28291,7 +28526,7 @@
         <v/>
       </c>
       <c r="J8" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A8)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$G$5:$G$32,$A8)</f>
         <v/>
       </c>
     </row>
@@ -28302,19 +28537,19 @@
         </is>
       </c>
       <c r="B9" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A9,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A9,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="C9" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A9,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A9,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="D9" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A9,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A9,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="E9" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A9,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A9,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="F9" s="42">
@@ -28334,7 +28569,7 @@
         <v/>
       </c>
       <c r="J9" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A9)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$G$5:$G$32,$A9)</f>
         <v/>
       </c>
     </row>
@@ -28345,19 +28580,19 @@
         </is>
       </c>
       <c r="B10" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A10,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A10,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="C10" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A10,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A10,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="D10" s="49">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A10,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A10,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="E10" s="49">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A10,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A10,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="F10" s="49">
@@ -28377,7 +28612,7 @@
         <v/>
       </c>
       <c r="J10" s="49">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A10)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$G$5:$G$32,$A10)</f>
         <v/>
       </c>
     </row>
@@ -28388,19 +28623,19 @@
         </is>
       </c>
       <c r="B11" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A11,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A11,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="C11" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A11,Comparativo!$B$6:$B$32,"Jurídico")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A11,Comparativo!$B$6:$B$33,"Jurídico")</f>
         <v/>
       </c>
       <c r="D11" s="42">
-        <f>SUMIFS(Comparativo!$I$6:$I$32,Comparativo!$E$6:$E$32,$A11,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$I$6:$I$33,Comparativo!$E$6:$E$33,$A11,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="E11" s="42">
-        <f>SUMIFS(Comparativo!$J$6:$J$32,Comparativo!$E$6:$E$32,$A11,Comparativo!$B$6:$B$32,"TI")</f>
+        <f>SUMIFS(Comparativo!$J$6:$J$33,Comparativo!$E$6:$E$33,$A11,Comparativo!$B$6:$B$33,"TI")</f>
         <v/>
       </c>
       <c r="F11" s="42">
@@ -28420,7 +28655,7 @@
         <v/>
       </c>
       <c r="J11" s="42">
-        <f>SUMIFS(Planejado!$T$5:$T$31,Planejado!$G$5:$G$31,$A11)</f>
+        <f>SUMIFS(Planejado!$T$5:$T$32,Planejado!$G$5:$G$32,$A11)</f>
         <v/>
       </c>
     </row>
@@ -28490,7 +28725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -28715,17 +28950,17 @@
       </c>
       <c r="B10" s="72" t="inlineStr">
         <is>
-          <t>Jonathan — economia de R$ 49.491 até julho</t>
+          <t>Jonathan — economia de R$ 53.803 até julho</t>
         </is>
       </c>
       <c r="C10" s="72" t="inlineStr">
         <is>
-          <t>Orçado R$ 10.000/mês desde jan/26. A contratação foi segurada e o serviço só começou depois, chegando a R$ 6.300/mês. Realizado pelo extrato, no credor 'J H ALVES — MONITOR REMOTO': R$ 4.311,56 em jan, nada em fev, mar e abr, e R$ 3.723,62, R$ 6.173,37 e R$ 6.300,00 em mai, jun e jul. Total de R$ 20.508,55 contra R$ 70.000 orçados.</t>
+          <t>Orçado R$ 10.000/mês desde jan/26, com a contratação segurada até abr/26, quando ele passou a atuar como consultor fixo, 3 dias por semana. Realizado de R$ 16.196,99 em jan–jul (pagamentos de mai, jun e jul) contra R$ 70.000 orçados. O vínculo anterior, de serviços esporádicos prestados de fora, foi separado na linha TI-E04.</t>
         </is>
       </c>
       <c r="D10" s="72" t="inlineStr">
         <is>
-          <t>É de longe a maior economia das duas áreas: R$ 49.491,45 em sete meses, e decorre de decisão de gestão, não de erro de orçamento. Vale destacar na apresentação. DOIS PONTOS A ESCLARECER: (1) o pagamento de R$ 4.311,56 em 19/01 é anterior ao início das atividades — provavelmente serviço de dez/2025 recebido no mês seguinte, confirmar; (2) mai e jun saíram abaixo de R$ 6.300 (R$ 3.723,62 e R$ 6.173,37), verificar se foi proporcional por dias trabalhados.</t>
+          <t>É de longe a maior economia das duas áreas: R$ 53.803,01 em sete meses, e decorre de decisão de gestão, não de erro de orçamento. Vale destacar na apresentação. A CONFERIR: mai e jun saíram abaixo de R$ 6.300 (R$ 3.723,62 e R$ 6.173,37) — verificar se foi proporcional aos dias trabalhados no início do contrato.</t>
         </is>
       </c>
       <c r="E10" s="72" t="inlineStr">
@@ -28742,22 +28977,22 @@
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="68" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B11" s="69" t="inlineStr">
         <is>
-          <t>Elias Benedito — sem custo até jul, renegociado para set</t>
+          <t>Serviços esporádicos do Monitor Remoto — fora do orçamento</t>
         </is>
       </c>
       <c r="C11" s="69" t="inlineStr">
         <is>
-          <t>Orçado R$ 1.065/mês, realizado R$ 0 de jan a jul — contrato ativo, mas sem acionamento no período (confirmado pela gestora). O pagamento passa a ocorrer agora, e a partir de set/26 o valor foi renegociado de R$ 1.065 para R$ 603,30.</t>
+          <t>Antes de entrar como consultor fixo, o mesmo prestador atendia de fora, em serviços esporádicos. Consta um pagamento de R$ 4.311,56 em 19/01/26 (NFS.70), provavelmente referente a dez/25 pelo regime de caixa. Esse vínculo não estava na ficha de orçamento e foi encerrado em abr/26.</t>
         </is>
       </c>
       <c r="D11" s="69" t="inlineStr">
         <is>
-          <t>Duas economias na mesma linha: R$ 7.455 pelos sete meses sem acionamento, e R$ 461,70/mês (43%) a partir de set pela renegociação — R$ 1.846,80 no ano. O planejado já reflete o valor novo de set a dez.</t>
+          <t>Linha TI-E04 criada com planejado zero, então o valor aparece como 'Não orçado'. Como o vínculo acabou, não haverá novos lançamentos — a linha existe para o histórico não se misturar com a consultoria fixa. Confirmar se houve pagamento esporádico em fev e mar que não caiu no centro de custo do TI.</t>
         </is>
       </c>
       <c r="E11" s="69" t="inlineStr">
@@ -28765,31 +29000,31 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F11" s="73" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
+      <c r="F11" s="75" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="71" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B12" s="72" t="inlineStr">
         <is>
-          <t>Planejado de jan a abr — conferido</t>
+          <t>Elias Benedito — sem custo até jul, renegociado para set</t>
         </is>
       </c>
       <c r="C12" s="72" t="inlineStr">
         <is>
-          <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
+          <t>Orçado R$ 1.065/mês, realizado R$ 0 de jan a jul — contrato ativo, mas sem acionamento no período (confirmado pela gestora). O pagamento passa a ocorrer agora, e a partir de set/26 o valor foi renegociado de R$ 1.065 para R$ 603,30.</t>
         </is>
       </c>
       <c r="D12" s="72" t="inlineStr">
         <is>
-          <t>Conferido e validado pela gestora: os valores replicados estão corretos, nenhum ajuste necessário.</t>
+          <t>Duas economias na mesma linha: R$ 7.455 pelos sete meses sem acionamento, e R$ 461,70/mês (43%) a partir de set pela renegociação — R$ 1.846,80 no ano. O planejado já reflete o valor novo de set a dez.</t>
         </is>
       </c>
       <c r="E12" s="72" t="inlineStr">
@@ -28799,29 +29034,29 @@
       </c>
       <c r="F12" s="73" t="inlineStr">
         <is>
-          <t>APLICADO</t>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="68" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B13" s="69" t="inlineStr">
         <is>
-          <t>Realizado de ago a dez — a lançar no decorrer do ano</t>
+          <t>Planejado de jan a abr — conferido</t>
         </is>
       </c>
       <c r="C13" s="69" t="inlineStr">
         <is>
-          <t>Jan a jul estão lançados. Ago a dez ficam em branco e serão preenchidos conforme os meses fecharem, com a extração do SIENGE.</t>
+          <t>O 1º quadrimestre foi preenchido replicando os valores mensais conhecidos, porque a ficha original só trazia o grid de mai a dez. Exceções tratadas: Jonathan começa em abr, Thamar a R$ 5.000 (pré-reajuste), Vinicius com bruto de R$ 2.570,52 e Adapta a R$ 1.300 (valor até jun).</t>
         </is>
       </c>
       <c r="D13" s="69" t="inlineStr">
         <is>
-          <t>Enquanto isso, o mês de referência do Comparativo deve ficar no último mês fechado (hoje Jul/26) — assim o acumulado compara períodos iguais dos dois lados.</t>
+          <t>Conferido e validado pela gestora: os valores replicados estão corretos, nenhum ajuste necessário.</t>
         </is>
       </c>
       <c r="E13" s="69" t="inlineStr">
@@ -28838,86 +29073,86 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B14" s="72" t="inlineStr">
         <is>
-          <t>Despesas fora do orçamento identificadas no extrato</t>
+          <t>Realizado de ago a dez — a lançar no decorrer do ano</t>
         </is>
       </c>
       <c r="C14" s="72" t="inlineStr">
         <is>
-          <t>O extrato do financeiro traz gastos relevantes sem linha na ficha. Jurídico: Carneiro Rabelo (R$ 107.742) e Cristiane Carneiro Rabelo (R$ 94.825), somando R$ 202.567 em sete meses; mais Tribunal de Justiça (R$ 49.244), Michele de Oliveira (R$ 23.572) e ONR (R$ 22.576). TI: um bloco de telefonia e infraestrutura de cerca de R$ 15.700 (Claro, TIM, Telefônica, Locaweb, Web Mobile, Sabha, Intelbras, VC1, Alfama). O 'J H Alves — Monitor Remoto' NÃO entra nesta lista: é o Jonathan, que já tem linha no orçamento (TI-E03).</t>
+          <t>Jan a jul estão lançados. Ago a dez ficam em branco e serão preenchidos conforme os meses fecharem, com a extração do SIENGE.</t>
         </is>
       </c>
       <c r="D14" s="72" t="inlineStr">
         <is>
-          <t>Só os dois primeiros credores do Jurídico superam o orçamento anual inteiro do departamento. ATENÇÃO: parte desses valores pode ser repasse ou custa reembolsável pelo cliente, e não custo da área — foi o caso da Dra. Michele (ver item P). Separar o que é custo antes de decidir. Para os que entrarem no centro de custo, criar linha no orçamento, senão aparecerão como 'Não orçado' e distorcerão o comparativo.</t>
+          <t>Enquanto isso, o mês de referência do Comparativo deve ficar no último mês fechado (hoje Jul/26) — assim o acumulado compara períodos iguais dos dois lados.</t>
         </is>
       </c>
       <c r="E14" s="72" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F14" s="76" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F14" s="73" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="68" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B15" s="69" t="inlineStr">
         <is>
-          <t>Despesas do TI — A LANÇAR</t>
+          <t>Despesas fora do orçamento identificadas no extrato</t>
         </is>
       </c>
       <c r="C15" s="69" t="inlineStr">
         <is>
-          <t>As 9 linhas de despesas do TI (peças, backup, Adapta, antivírus, Office, sala de reunião, cursos, app de gravação e bonificação) não têm lançamento em nenhum mês.</t>
+          <t>O extrato do financeiro traz gastos relevantes sem linha na ficha. Jurídico: Carneiro Rabelo (R$ 107.742) e Cristiane Carneiro Rabelo (R$ 94.825), somando R$ 202.567 em sete meses; mais Tribunal de Justiça (R$ 49.244), Michele de Oliveira (R$ 23.572) e ONR (R$ 22.576). TI: um bloco de telefonia e infraestrutura de cerca de R$ 15.700 (Claro, TIM, Telefônica, Locaweb, Web Mobile, Sabha, Intelbras, VC1, Alfama). O 'J H Alves — Monitor Remoto' NÃO entra nesta lista: é o Jonathan, que já tem linha no orçamento (TI-E03).</t>
         </is>
       </c>
       <c r="D15" s="69" t="inlineStr">
         <is>
-          <t>São R$ 89.040 orçados no ano, 35% do orçamento do TI. Sem lançamento, o departamento aparece com desvio negativo que é ausência de dado.</t>
+          <t>Só os dois primeiros credores do Jurídico superam o orçamento anual inteiro do departamento. ATENÇÃO: parte desses valores pode ser repasse ou custa reembolsável pelo cliente, e não custo da área — foi o caso da Dra. Michele (ver item P). Separar o que é custo antes de decidir. Para os que entrarem no centro de custo, criar linha no orçamento, senão aparecerão como 'Não orçado' e distorcerão o comparativo.</t>
         </is>
       </c>
       <c r="E15" s="69" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F15" s="70" t="inlineStr">
-        <is>
-          <t>A LANÇAR</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F15" s="76" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B16" s="72" t="inlineStr">
         <is>
-          <t>Base de meses do TI — Jonathan corrigido para 12 meses</t>
+          <t>Despesas do TI — A LANÇAR</t>
         </is>
       </c>
       <c r="C16" s="72" t="inlineStr">
         <is>
-          <t>A ficha trazia os totais do TI digitados à mão: Vinicius e Elias em 12 meses (R$ 64.998,30 e R$ 12.780,00, ambos confirmados) e Jonathan em 9 meses (R$ 90.000). A gestora confirmou que o orçamento dele valia desde jan/26, ou seja, 12 meses — os R$ 90.000 da ficha não refletiam o orçamento aprovado.</t>
+          <t>As 9 linhas de despesas do TI (peças, backup, Adapta, antivírus, Office, sala de reunião, cursos, app de gravação e bonificação) não têm lançamento em nenhum mês.</t>
         </is>
       </c>
       <c r="D16" s="72" t="inlineStr">
         <is>
-          <t>Equipe de TI passa de R$ 167.778,30 para R$ 197.778,30 (+R$ 30.000). Os R$ 167.778,30 da ficha continuam batendo com Vinicius e Elias, mas a linha do Jonathan estava subdimensionada em 3 meses.</t>
+          <t>São R$ 89.040 orçados no ano, 35% do orçamento do TI. Sem lançamento, o departamento aparece com desvio negativo que é ausência de dado.</t>
         </is>
       </c>
       <c r="E16" s="72" t="inlineStr">
@@ -28925,36 +29160,36 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F16" s="73" t="inlineStr">
-        <is>
-          <t>RESOLVIDO</t>
+      <c r="F16" s="70" t="inlineStr">
+        <is>
+          <t>A LANÇAR</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" s="69" t="inlineStr">
         <is>
-          <t>Origem do valor realizado — DEFINIDA: SIENGE</t>
+          <t>Base de meses do TI — Jonathan corrigido para 12 meses</t>
         </is>
       </c>
       <c r="C17" s="69" t="inlineStr">
         <is>
-          <t>Será aberto um centro de custo próprio no SIENGE e todos os valores do realizado serão extraídos de lá. Nada será lançado manualmente. O extrato das abas 'Contas Pagas' já vem nesse formato.</t>
+          <t>A ficha trazia os totais do TI digitados à mão: Vinicius e Elias em 12 meses (R$ 64.998,30 e R$ 12.780,00, ambos confirmados) e Jonathan em 9 meses (R$ 90.000). A gestora confirmou que o orçamento dele valia desde jan/26, ou seja, 12 meses — os R$ 90.000 da ficha não refletiam o orçamento aprovado.</t>
         </is>
       </c>
       <c r="D17" s="69" t="inlineStr">
         <is>
-          <t>O realizado passa a bater com a contabilidade por construção, que era o risco principal. Duas coisas a encaminhar: (1) o de-para entre credor do SIENGE e linha do orçamento — a coluna 'Já está no orçamento?' da aba de resumo é o rascunho dele; (2) definir se a extração sai por regime de caixa ou de competência, ver item 7.</t>
+          <t>Equipe de TI passa de R$ 167.778,30 para R$ 197.778,30 (+R$ 30.000). Os R$ 167.778,30 da ficha continuam batendo com Vinicius e Elias, mas a linha do Jonathan estava subdimensionada em 3 meses.</t>
         </is>
       </c>
       <c r="E17" s="69" t="inlineStr">
         <is>
-          <t>Cristiane + Financeiro</t>
+          <t>Cristiane</t>
         </is>
       </c>
       <c r="F17" s="73" t="inlineStr">
@@ -28966,27 +29201,27 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" s="72" t="inlineStr">
         <is>
-          <t>Jusfy — nunca iniciado</t>
+          <t>Origem do valor realizado — DEFINIDA: SIENGE</t>
         </is>
       </c>
       <c r="C18" s="72" t="inlineStr">
         <is>
-          <t>O Jusfy entrou na ficha porque o orçamento foi montado em nov/dez de 2025, durante a fase de experimento. Em janeiro a decisão foi cancelar, e o serviço nunca chegou a ser iniciado. Custo zero o ano todo.</t>
+          <t>Será aberto um centro de custo próprio no SIENGE e todos os valores do realizado serão extraídos de lá. Nada será lançado manualmente. O extrato das abas 'Contas Pagas' já vem nesse formato.</t>
         </is>
       </c>
       <c r="D18" s="72" t="inlineStr">
         <is>
-          <t>Os R$ 1.200 orçados no ano nunca serão usados, e a gestora confirmou que não haverá substituto para o Astrea. Não é economia de gestão: é item que já nasceu fora do escopo e deve sair na revisão do orçamento.</t>
+          <t>O realizado passa a bater com a contabilidade por construção, que era o risco principal. Duas coisas a encaminhar: (1) o de-para entre credor do SIENGE e linha do orçamento — a coluna 'Já está no orçamento?' da aba de resumo é o rascunho dele; (2) definir se a extração sai por regime de caixa ou de competência, ver item 7.</t>
         </is>
       </c>
       <c r="E18" s="72" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Financeiro</t>
         </is>
       </c>
       <c r="F18" s="73" t="inlineStr">
@@ -28998,118 +29233,118 @@
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="68" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B19" s="69" t="inlineStr">
         <is>
-          <t>Astrea — cancelar antes de 01/11/26 (renovação automática)</t>
+          <t>Jusfy — nunca iniciado</t>
         </is>
       </c>
       <c r="C19" s="69" t="inlineStr">
         <is>
-          <t>Anuidade 2025/26 de R$ 6.731,40 em 5x de R$ 1.346,28, com vencimentos de 01/11/25 a 01/03/26 e quitação em 10/02/26 — conferido contra o portal do fornecedor. Cancelamento solicitado em ago/26, sem substituto. Realizado zerado de mar a dez.</t>
+          <t>O Jusfy entrou na ficha porque o orçamento foi montado em nov/dez de 2025, durante a fase de experimento. Em janeiro a decisão foi cancelar, e o serviço nunca chegou a ser iniciado. Custo zero o ano todo.</t>
         </is>
       </c>
       <c r="D19" s="69" t="inlineStr">
         <is>
-          <t>ATENÇÃO AO PRAZO: o ciclo do Astrea começa sempre em 1º de novembro e a cobrança é automática em cartão (Visa final 4957) — não passa por aprovação de boleto. Se o cancelamento não estiver confirmado até 01/11/26, entra a anuidade 2026/27, que pelo histórico de reajuste (+83% e depois +10,1%) sairia por volta de R$ 7.400. O responsável financeiro cadastrado no fornecedor é a Thamar. Guardar a confirmação por escrito.</t>
+          <t>Os R$ 1.200 orçados no ano nunca serão usados, e a gestora confirmou que não haverá substituto para o Astrea. Não é economia de gestão: é item que já nasceu fora do escopo e deve sair na revisão do orçamento.</t>
         </is>
       </c>
       <c r="E19" s="69" t="inlineStr">
         <is>
-          <t>Cristiane + Thamar</t>
-        </is>
-      </c>
-      <c r="F19" s="70" t="inlineStr">
-        <is>
-          <t>PRAZO 01/11</t>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F19" s="73" t="inlineStr">
+        <is>
+          <t>RESOLVIDO</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B20" s="72" t="inlineStr">
         <is>
-          <t>Dra. Michele incluída no orçamento</t>
+          <t>Astrea — cancelar antes de 01/11/26 (renovação automática)</t>
         </is>
       </c>
       <c r="C20" s="72" t="inlineStr">
         <is>
-          <t>Mão de obra que ficou de fora da ficha por esquecimento na montagem do orçamento. Orçada em R$ 2.750/mês pelo ano inteiro, valor fixo em vigor desde jan/26.</t>
+          <t>Anuidade 2025/26 de R$ 6.731,40 em 5x de R$ 1.346,28, com vencimentos de 01/11/25 a 01/03/26 e quitação em 10/02/26 — conferido contra o portal do fornecedor. Cancelamento solicitado em ago/26, sem substituto. Realizado zerado de mar a dez.</t>
         </is>
       </c>
       <c r="D20" s="72" t="inlineStr">
         <is>
-          <t>Acréscimo de R$ 33.000 ao orçamento do Jurídico, que passa a R$ 324.730,42. No extrato, o fixo de jan a jun vem somado aos honorários de repasse no mesmo credor: o total mensal (R$ 3.739 a R$ 4.326) é o fixo de R$ 2.750 mais o repasse, que o cliente paga e a empresa apenas transfere. Só jun/26 fica abaixo do fixo (R$ 1.036,92), provavelmente porque o pagamento daquele mês caiu em jul — é o lançamento isolado de R$ 2.750 que aparece lá. A justificativa da inclusão é pauta da reunião.</t>
+          <t>ATENÇÃO AO PRAZO: o ciclo do Astrea começa sempre em 1º de novembro e a cobrança é automática em cartão (Visa final 4957) — não passa por aprovação de boleto. Se o cancelamento não estiver confirmado até 01/11/26, entra a anuidade 2026/27, que pelo histórico de reajuste (+83% e depois +10,1%) sairia por volta de R$ 7.400. O responsável financeiro cadastrado no fornecedor é a Thamar. Guardar a confirmação por escrito.</t>
         </is>
       </c>
       <c r="E20" s="72" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F20" s="73" t="inlineStr">
-        <is>
-          <t>APLICADO</t>
+          <t>Cristiane + Thamar</t>
+        </is>
+      </c>
+      <c r="F20" s="70" t="inlineStr">
+        <is>
+          <t>PRAZO 01/11</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="68" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B21" s="69" t="inlineStr">
         <is>
-          <t>Adapta lançado no centro de custo errado — RECLASSIFICAR</t>
+          <t>Dra. Michele incluída no orçamento</t>
         </is>
       </c>
       <c r="C21" s="69" t="inlineStr">
         <is>
-          <t>Os pagamentos do Adapta (ADAPTA EDUCACAO LTDA, contrato 4134643529) estão no centro de custo Jurídico no SIENGE: R$ 575,00/mês de jan a mai e R$ 476,00 em jun, todos com vencimento dia 15. Total de R$ 3.351,00 em seis meses. Não é despesa do Jurídico — é ferramenta de IA, de uso transversal.</t>
+          <t>Mão de obra que ficou de fora da ficha por esquecimento na montagem do orçamento. Orçada em R$ 2.750/mês pelo ano inteiro, valor fixo em vigor desde jan/26.</t>
         </is>
       </c>
       <c r="D21" s="69" t="inlineStr">
         <is>
-          <t>Reclassificar no SIENGE para o centro de custo correto e aplicar o rateio do item L. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado. Aproveitar a abertura do novo centro de custo para acertar a classificação desde a origem.</t>
+          <t>Acréscimo de R$ 33.000 ao orçamento do Jurídico, que passa a R$ 324.730,42. No extrato, o fixo de jan a jun vem somado aos honorários de repasse no mesmo credor: o total mensal (R$ 3.739 a R$ 4.326) é o fixo de R$ 2.750 mais o repasse, que o cliente paga e a empresa apenas transfere. Só jun/26 fica abaixo do fixo (R$ 1.036,92), provavelmente porque o pagamento daquele mês caiu em jul — é o lançamento isolado de R$ 2.750 que aparece lá. A justificativa da inclusão é pauta da reunião.</t>
         </is>
       </c>
       <c r="E21" s="69" t="inlineStr">
         <is>
-          <t>Cristiane + Financeiro</t>
-        </is>
-      </c>
-      <c r="F21" s="70" t="inlineStr">
-        <is>
-          <t>RECLASSIFICAR</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F21" s="73" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="71" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B22" s="72" t="inlineStr">
         <is>
-          <t>Extrato contém REPASSES, não só custo</t>
+          <t>Adapta lançado no centro de custo errado — RECLASSIFICAR</t>
         </is>
       </c>
       <c r="C22" s="72" t="inlineStr">
         <is>
-          <t>Os lançamentos em nome da Dra. Michele até jun/26 (R$ 20.821,53) são repasse: o cliente paga à empresa e a empresa repassa a ela. Não são custo do departamento e por isso não foram lançados no realizado.</t>
+          <t>Os pagamentos do Adapta (ADAPTA EDUCACAO LTDA, contrato 4134643529) estão no centro de custo Jurídico no SIENGE: R$ 575,00/mês de jan a mai e R$ 476,00 em jun, todos com vencimento dia 15. Total de R$ 3.351,00 em seis meses. Não é despesa do Jurídico — é ferramenta de IA, de uso transversal.</t>
         </is>
       </c>
       <c r="D22" s="72" t="inlineStr">
         <is>
-          <t>Vale a mesma checagem nos outros credores das abas 'Contas Pagas' antes de usá-los como custo — em especial custas processuais e honorários de terceiros, que podem ser reembolsados pelo cliente. O total de R$ 446.577,92 do centro de custo Jurídico no extrato NÃO é despesa líquida do departamento.</t>
+          <t>Reclassificar no SIENGE para o centro de custo correto e aplicar o rateio do item L. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado. Aproveitar a abertura do novo centro de custo para acertar a classificação desde a origem.</t>
         </is>
       </c>
       <c r="E22" s="72" t="inlineStr">
@@ -29117,63 +29352,63 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F22" s="75" t="inlineStr">
-        <is>
-          <t>CONFERIR</t>
+      <c r="F22" s="70" t="inlineStr">
+        <is>
+          <t>RECLASSIFICAR</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="68" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B23" s="69" t="inlineStr">
         <is>
-          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
+          <t>Extrato contém REPASSES, não só custo</t>
         </is>
       </c>
       <c r="C23" s="69" t="inlineStr">
         <is>
-          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
+          <t>Os lançamentos em nome da Dra. Michele até jun/26 (R$ 20.821,53) são repasse: o cliente paga à empresa e a empresa repassa a ela. Não são custo do departamento e por isso não foram lançados no realizado.</t>
         </is>
       </c>
       <c r="D23" s="69" t="inlineStr">
         <is>
-          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
+          <t>Vale a mesma checagem nos outros credores das abas 'Contas Pagas' antes de usá-los como custo — em especial custas processuais e honorários de terceiros, que podem ser reembolsados pelo cliente. O total de R$ 446.577,92 do centro de custo Jurídico no extrato NÃO é despesa líquida do departamento.</t>
         </is>
       </c>
       <c r="E23" s="69" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F23" s="76" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane + Financeiro</t>
+        </is>
+      </c>
+      <c r="F23" s="75" t="inlineStr">
+        <is>
+          <t>CONFERIR</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="71" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B24" s="72" t="inlineStr">
         <is>
-          <t>Ferramentas de IA — DEFINIR META E RATEIO</t>
+          <t>ORÇAMENTO VEIO ERRADO — Astrea e Jusbrasil</t>
         </is>
       </c>
       <c r="C24" s="72" t="inlineStr">
         <is>
-          <t>Claude, GPT, Adapta One e Adapta Skip existem hoje e não constavam na ficha. Quatro linhas criadas com planejado zerado, à espera da meta. Todas marcadas com RATEIO A DEFINIR: são de uso transversal, não exclusivo do TI.</t>
+          <t>ASTREA: orçado R$ 112,07/mês, o que dá R$ 1.344,84 no ano — praticamente o valor de UMA das cinco parcelas (R$ 1.346,28). Quem montou a ficha tomou uma parcela pelo custo total do ano. O custo real da anuidade foi R$ 6.731,40, 5x o orçado. JUSBRASIL: orçado R$ 104,90/mês contra R$ 136,00 reais (1,3x), R$ 373,20 no ano. PAUTA PARA A REUNIÃO COM A DIRETORIA.</t>
         </is>
       </c>
       <c r="D24" s="72" t="inlineStr">
         <is>
-          <t>O rateio já acontece de fato, mas sem regra: no extrato, a OpenAI (R$ 5.950,10) caiu no centro de custo do TI e o Adapta (R$ 3.351) caiu no Jurídico — mesma natureza de gasto, centros diferentes por acaso. Sem critério definido, o TI absorve custo de ferramenta que a empresa inteira usa e aparece caro na comparação, enquanto as áreas usuárias não enxergam o que consomem. Sugestão: manter o contrato centralizado no TI (facilita negociação e controle de licenças) e ratear o custo por usuário ativo, que é métrica que as próprias plataformas fornecem. Conferir também a sobreposição com 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano, e o nome exato do 'Adapta Skip'.</t>
+          <t>Subdimensionamento de R$ 5.759,76 no ano (R$ 5.386,56 do Astrea + R$ 373,20 do Jusbrasil). O planejado das duas linhas foi mantido como veio na ficha, de propósito, para o erro aparecer no comparativo em vez de ser corrigido em silêncio. Não é estouro de gestão: é erro na origem. Como o Astrea será cancelado, o efeito prático é só de 2026 — mas o método de orçar serviços parcelados precisa ser revisto para o ano que vem.</t>
         </is>
       </c>
       <c r="E24" s="72" t="inlineStr">
@@ -29190,86 +29425,86 @@
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B25" s="69" t="inlineStr">
         <is>
-          <t>Rateio dos softwares corporativos e das IAs</t>
+          <t>Ferramentas de IA — DEFINIR META E RATEIO</t>
         </is>
       </c>
       <c r="C25" s="69" t="inlineStr">
         <is>
-          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo' — R$ 34.680 no ano. Somam-se a eles as quatro ferramentas de IA do item L, também de uso transversal.</t>
+          <t>Claude, GPT, Adapta One e Adapta Skip existem hoje e não constavam na ficha. Quatro linhas criadas com planejado zerado, à espera da meta. Todas marcadas com RATEIO A DEFINIR: são de uso transversal, não exclusivo do TI.</t>
         </is>
       </c>
       <c r="D25" s="69" t="inlineStr">
         <is>
-          <t>São 39% das despesas orçadas do TI, mais o que vier das IAs. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro. Tratar os dois blocos com o mesmo critério de rateio, para não criar duas regras diferentes.</t>
+          <t>O rateio já acontece de fato, mas sem regra: no extrato, a OpenAI (R$ 5.950,10) caiu no centro de custo do TI e o Adapta (R$ 3.351) caiu no Jurídico — mesma natureza de gasto, centros diferentes por acaso. Sem critério definido, o TI absorve custo de ferramenta que a empresa inteira usa e aparece caro na comparação, enquanto as áreas usuárias não enxergam o que consomem. Sugestão: manter o contrato centralizado no TI (facilita negociação e controle de licenças) e ratear o custo por usuário ativo, que é métrica que as próprias plataformas fornecem. Conferir também a sobreposição com 'Inteligência Artificial (Adapta)', já orçada em R$ 17.400/ano, e o nome exato do 'Adapta Skip'.</t>
         </is>
       </c>
       <c r="E25" s="69" t="inlineStr">
         <is>
-          <t>Cristiane + Controladoria</t>
-        </is>
-      </c>
-      <c r="F25" s="74" t="inlineStr">
-        <is>
-          <t>EM ABERTO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F25" s="76" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B26" s="72" t="inlineStr">
         <is>
-          <t>Sala de Reunião — EXECUTAR, PAUSAR OU REPENSAR?</t>
+          <t>Rateio dos softwares corporativos e das IAs</t>
         </is>
       </c>
       <c r="C26" s="72" t="inlineStr">
         <is>
-          <t>Projeto orçado em R$ 2.800/mês × 12 = R$ 33.600, classificado em Móveis e Utensílios, sem nenhum lançamento até jul/26. A gestora levanta que a sala já não comporta todas as pessoas, então investir na configuração atual pode não resolver o problema real. Três caminhos: executar como está, pausar, ou repensar a solução (outro espaço, formato híbrido, mais de uma sala).</t>
+          <t>Backup (R$ 9.900), Adapta/IA (R$ 17.400), Antivírus (R$ 2.880) e Office 365 (R$ 4.500) estão marcados na ficha como 'não sei se seria administrativo' — R$ 34.680 no ano. Somam-se a eles as quatro ferramentas de IA do item L, também de uso transversal.</t>
         </is>
       </c>
       <c r="D26" s="72" t="inlineStr">
         <is>
-          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. SEPARAR OS ITENS: a descrição na ficha mistura infraestrutura de reunião (câmeras, microfones, cadeiras) com material de consumo e brindes (canetas, blocos personalizados, copos, cafeteira). O segundo grupo é papelaria e deveria estar no Administrativo, não no TI (item U).</t>
+          <t>São 39% das despesas orçadas do TI, mais o que vier das IAs. Se são da empresa toda e ficam no centro de custo de TI, o departamento carrega despesa que não é dele e aparece caro. Tratar os dois blocos com o mesmo critério de rateio, para não criar duas regras diferentes.</t>
         </is>
       </c>
       <c r="E26" s="72" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F26" s="76" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane + Controladoria</t>
+        </is>
+      </c>
+      <c r="F26" s="74" t="inlineStr">
+        <is>
+          <t>EM ABERTO</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="68" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B27" s="69" t="inlineStr">
         <is>
-          <t>Notebooks — TI compra, mas não enxerga o saldo das áreas</t>
+          <t>Sala de Reunião — EXECUTAR, PAUSAR OU REPENSAR?</t>
         </is>
       </c>
       <c r="C27" s="69" t="inlineStr">
         <is>
-          <t>Cada área tem a própria linha de orçamento para notebooks, mas é o TI que recebe a solicitação e executa a compra quando surge a necessidade. Hoje o TI não tem acompanhamento do orçamento das outras áreas, então aprova pedidos sem saber quanto resta em cada uma.</t>
+          <t>Projeto orçado em R$ 2.800/mês × 12 = R$ 33.600, classificado em Móveis e Utensílios, sem nenhum lançamento até jul/26. A gestora levanta que a sala já não comporta todas as pessoas, então investir na configuração atual pode não resolver o problema real. Três caminhos: executar como está, pausar, ou repensar a solução (outro espaço, formato híbrido, mais de uma sala).</t>
         </is>
       </c>
       <c r="D27" s="69" t="inlineStr">
         <is>
-          <t>O TI vira o executor de um estouro que não é dele e que ninguém percebe antes de acontecer — a área descobre no fechamento, quando já comprou. Proposta: o TI passa a acompanhar o saldo da rubrica de notebooks de cada área e avisa quando a solicitação for levar ao estouro, antes de comprar. Com o centro de custo no SIENGE, esse acompanhamento sai do mesmo relatório. Definir com a diretoria quem dá o aval quando o saldo acabar: a área solicitante, o TI ou a controladoria.</t>
+          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. SEPARAR OS ITENS: a descrição na ficha mistura infraestrutura de reunião (câmeras, microfones, cadeiras) com material de consumo e brindes (canetas, blocos personalizados, copos, cafeteira). O segundo grupo é papelaria e deveria estar no Administrativo, não no TI (item U).</t>
         </is>
       </c>
       <c r="E27" s="69" t="inlineStr">
@@ -29286,54 +29521,54 @@
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="71" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B28" s="72" t="inlineStr">
         <is>
-          <t>Rubricas genéricas — detalhar no lançamento, não no orçamento</t>
+          <t>Notebooks — TI compra, mas não enxerga o saldo das áreas</t>
         </is>
       </c>
       <c r="C28" s="72" t="inlineStr">
         <is>
-          <t>Rubricas como 'Peças de Manutenção' (R$ 9.720/ano) agrupam itens de naturezas diferentes: mouse, teclado, carregador, tela, carcaça. Sem detalhe, não dá para saber o que puxa o gasto. A alternativa de criar uma linha por item foi avaliada e descartada por ora.</t>
+          <t>Cada área tem a própria linha de orçamento para notebooks, mas é o TI que recebe a solicitação e executa a compra quando surge a necessidade. Hoje o TI não tem acompanhamento do orçamento das outras áreas, então aprova pedidos sem saber quanto resta em cada uma.</t>
         </is>
       </c>
       <c r="D28" s="72" t="inlineStr">
         <is>
-          <t>DECIDIDO: manter uma linha de orçamento e detalhar na DESCRIÇÃO do lançamento no SIENGE, com padrão fixo ('Peças – mouse', 'Peças – tela'). Motivos: (1) não há histórico — as despesas do TI ainda não têm lançamento, então orçar item a item seria estimativa sem base, e cada linha acusaria desvio pela divisão errada, não pelo gasto; (2) cinco linhas viram cinco lançamentos mensais para uma rubrica que é 11% das despesas da área; (3) o plano de contas é definido pela controladoria, então subitens no orçamento não mudariam a classificação contábil. Em jan/27, com seis meses de dados reais, reavaliar. Se separar, separar por NATUREZA (reposição x reparo), que é o que dá leitura gerencial, e não item a item. Mesmo critério vale para 'Equipamentos Eletrônicos Diversos' e demais rubricas genéricas.</t>
+          <t>O TI vira o executor de um estouro que não é dele e que ninguém percebe antes de acontecer — a área descobre no fechamento, quando já comprou. Proposta: o TI passa a acompanhar o saldo da rubrica de notebooks de cada área e avisa quando a solicitação for levar ao estouro, antes de comprar. Com o centro de custo no SIENGE, esse acompanhamento sai do mesmo relatório. Definir com a diretoria quem dá o aval quando o saldo acabar: a área solicitante, o TI ou a controladoria.</t>
         </is>
       </c>
       <c r="E28" s="72" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F28" s="73" t="inlineStr">
-        <is>
-          <t>APLICADO</t>
+          <t>Cristiane + Diretoria</t>
+        </is>
+      </c>
+      <c r="F28" s="76" t="inlineStr">
+        <is>
+          <t>PAUTA REUNIÃO</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="68" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B29" s="69" t="inlineStr">
         <is>
-          <t>Política de troca 1x1 e empréstimo — IMPLANTAR</t>
+          <t>Rubricas genéricas — detalhar no lançamento, não no orçamento</t>
         </is>
       </c>
       <c r="C29" s="69" t="inlineStr">
         <is>
-          <t>Hoje não existe regra: o pedido chega e a compra é feita. A proposta é que para receber um item novo a pessoa entregue o que quebrou (troca 1x1), e que exista um equipamento reserva para empréstimo imediato, para ninguém ficar parado esperando. O reserva é COM FIO de propósito: mais barato e menos confortável que o definitivo, o que cria o incentivo natural para devolver e fechar a troca. A aba 'Controle de Equipamentos' já está pronta para o registro.</t>
+          <t>Rubricas como 'Peças de Manutenção' (R$ 9.720/ano) agrupam itens de naturezas diferentes: mouse, teclado, carregador, tela, carcaça. Sem detalhe, não dá para saber o que puxa o gasto. A alternativa de criar uma linha por item foi avaliada e descartada por ora.</t>
         </is>
       </c>
       <c r="D29" s="69" t="inlineStr">
         <is>
-          <t>Além de controlar estoque, a troca 1x1 gera dado de durabilidade e padrão de uso — se uma área quebra três vezes mais que as outras, isso aparece. Encaminhar: (1) comunicar a regra às áreas; (2) montar o pequeno estoque de reserva; (3) definir quantos dias o empréstimo pode durar antes de virar 'Atrasado'; (4) verificar com o financeiro se o lançamento pode nascer no centro de custo da área solicitante — se puder, o controle de custo por área sai do próprio SIENGE e esta aba fica só para o que ainda não virou pagamento.</t>
+          <t>DECIDIDO: manter uma linha de orçamento e detalhar na DESCRIÇÃO do lançamento no SIENGE, com padrão fixo ('Peças – mouse', 'Peças – tela'). Motivos: (1) não há histórico — as despesas do TI ainda não têm lançamento, então orçar item a item seria estimativa sem base, e cada linha acusaria desvio pela divisão errada, não pelo gasto; (2) cinco linhas viram cinco lançamentos mensais para uma rubrica que é 11% das despesas da área; (3) o plano de contas é definido pela controladoria, então subitens no orçamento não mudariam a classificação contábil. Em jan/27, com seis meses de dados reais, reavaliar. Se separar, separar por NATUREZA (reposição x reparo), que é o que dá leitura gerencial, e não item a item. Mesmo critério vale para 'Equipamentos Eletrônicos Diversos' e demais rubricas genéricas.</t>
         </is>
       </c>
       <c r="E29" s="69" t="inlineStr">
@@ -29341,127 +29576,127 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F29" s="74" t="inlineStr">
-        <is>
-          <t>IMPLANTAR</t>
+      <c r="F29" s="73" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="71" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B30" s="72" t="inlineStr">
         <is>
-          <t>Papelaria não é TI — manter no Administrativo</t>
+          <t>Política de troca 1x1 e empréstimo — IMPLANTAR</t>
         </is>
       </c>
       <c r="C30" s="72" t="inlineStr">
         <is>
-          <t>Recomendação registrada: o controle de papelaria (canetas, blocos, papel, copos) deve ficar no Administrativo/Facilities, não no TI. O TI controla equipamento porque há decisão TÉCNICA envolvida — se o notebook precisa de troca ou só de formatação, se a tela quebrou por defeito ou por queda. Não existe decisão técnica em caneta e bloco.</t>
+          <t>Hoje não existe regra: o pedido chega e a compra é feita. A proposta é que para receber um item novo a pessoa entregue o que quebrou (troca 1x1), e que exista um equipamento reserva para empréstimo imediato, para ninguém ficar parado esperando. O reserva é COM FIO de propósito: mais barato e menos confortável que o definitivo, o que cria o incentivo natural para devolver e fechar a troca. A aba 'Controle de Equipamentos' já está pronta para o registro.</t>
         </is>
       </c>
       <c r="D30" s="72" t="inlineStr">
         <is>
-          <t>Três diferenças separam as duas coisas: (1) papelaria acaba, não quebra, então a regra de troca 1x1 não se aplica — o controle é de estoque por ponto de pedido, outra lógica; (2) não há patrimônio nem número de série para rastrear item a item; (3) o custo de controlar uma caneta é maior que a caneta. Se papelaria estiver caindo no orçamento do TI por motivo histórico, é o mesmo caso do Adapta (item Q): classificação errada, corrigir na origem quando o centro de custo novo for aberto.</t>
+          <t>Além de controlar estoque, a troca 1x1 gera dado de durabilidade e padrão de uso — se uma área quebra três vezes mais que as outras, isso aparece. Encaminhar: (1) comunicar a regra às áreas; (2) montar o pequeno estoque de reserva; (3) definir quantos dias o empréstimo pode durar antes de virar 'Atrasado'; (4) verificar com o financeiro se o lançamento pode nascer no centro de custo da área solicitante — se puder, o controle de custo por área sai do próprio SIENGE e esta aba fica só para o que ainda não virou pagamento.</t>
         </is>
       </c>
       <c r="E30" s="72" t="inlineStr">
         <is>
-          <t>Cristiane + Administrativo</t>
+          <t>Cristiane</t>
         </is>
       </c>
       <c r="F30" s="74" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO</t>
+          <t>IMPLANTAR</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="68" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>U</t>
         </is>
       </c>
       <c r="B31" s="69" t="inlineStr">
         <is>
-          <t>AnyDesk — contratação prevista, definir valor</t>
+          <t>Papelaria não é TI — manter no Administrativo</t>
         </is>
       </c>
       <c r="C31" s="69" t="inlineStr">
         <is>
-          <t>Licença de acesso remoto que será contratada e não constava na ficha. Linha criada com planejado zerado, à espera do valor e do mês de início.</t>
+          <t>Recomendação registrada: o controle de papelaria (canetas, blocos, papel, copos) deve ficar no Administrativo/Facilities, não no TI. O TI controla equipamento porque há decisão TÉCNICA envolvida — se o notebook precisa de troca ou só de formatação, se a tela quebrou por defeito ou por queda. Não existe decisão técnica em caneta e bloco.</t>
         </is>
       </c>
       <c r="D31" s="69" t="inlineStr">
         <is>
-          <t>Não há sobreposição com o 'Monitor Remoto' do extrato: aquele credor é o Jonathan (J H Alves), consultor, não um software de acesso remoto. O AnyDesk é contratação nova e sem substituto atual. Definir valor e mês para a linha entrar no orçamento — enquanto o planejado for zero, qualquer lançamento aparece como 'Não orçado'.</t>
+          <t>Três diferenças separam as duas coisas: (1) papelaria acaba, não quebra, então a regra de troca 1x1 não se aplica — o controle é de estoque por ponto de pedido, outra lógica; (2) não há patrimônio nem número de série para rastrear item a item; (3) o custo de controlar uma caneta é maior que a caneta. Se papelaria estiver caindo no orçamento do TI por motivo histórico, é o mesmo caso do Adapta (item Q): classificação errada, corrigir na origem quando o centro de custo novo for aberto.</t>
         </is>
       </c>
       <c r="E31" s="69" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Administrativo</t>
         </is>
       </c>
       <c r="F31" s="74" t="inlineStr">
         <is>
-          <t>DEFINIR VALOR</t>
+          <t>RECOMENDAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="71" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B32" s="72" t="inlineStr">
         <is>
-          <t>Vitor (diretoria) — Claude ou GPT? PERGUNTAR</t>
+          <t>AnyDesk — contratação prevista, definir valor</t>
         </is>
       </c>
       <c r="C32" s="72" t="inlineStr">
         <is>
-          <t>Confirmar com o Vitor se ele seguirá usando o Claude, o GPT, ou os dois. Hoje as duas ferramentas estão contratadas e são de mesma finalidade — IA generalista —, então manter as duas para o mesmo usuário é redundância paga.</t>
+          <t>Licença de acesso remoto que será contratada e não constava na ficha. Linha criada com planejado zerado, à espera do valor e do mês de início.</t>
         </is>
       </c>
       <c r="D32" s="72" t="inlineStr">
         <is>
-          <t>É pré-requisito para fechar a meta do item L: não dá para dimensionar o orçamento de IA sem saber quantas licenças de cada ferramenta ficam de pé. Referência de custo: a OpenAI aparece no extrato com R$ 5.950,10 em sete meses, sendo R$ 5.394 só em abr/26. Levantar a mesma informação para os demais usuários, não só a diretoria — a decisão vale para todo mundo.</t>
+          <t>Não há sobreposição com o 'Monitor Remoto' do extrato: aquele credor é o Jonathan (J H Alves), consultor, não um software de acesso remoto. O AnyDesk é contratação nova e sem substituto atual. Definir valor e mês para a linha entrar no orçamento — enquanto o planejado for zero, qualquer lançamento aparece como 'Não orçado'.</t>
         </is>
       </c>
       <c r="E32" s="72" t="inlineStr">
         <is>
-          <t>Cristiane + Vitor</t>
+          <t>Cristiane</t>
         </is>
       </c>
       <c r="F32" s="74" t="inlineStr">
         <is>
-          <t>PERGUNTAR</t>
+          <t>DEFINIR VALOR</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B33" s="69" t="inlineStr">
         <is>
-          <t>Mapa de licenças de IA — quem usa o quê</t>
+          <t>Vitor (diretoria) — Claude ou GPT? PERGUNTAR</t>
         </is>
       </c>
       <c r="C33" s="69" t="inlineStr">
         <is>
-          <t>Situação atual conhecida: a licença do GPT era da Thamar e hoje é usada em conjunto por Gil, Miguel e Thamar. Uma licença também foi cedida ao Financeiro. Falta o mapa completo — quem usa cada ferramenta, em qual área e sob qual login.</t>
+          <t>Confirmar com o Vitor se ele seguirá usando o Claude, o GPT, ou os dois. Hoje as duas ferramentas estão contratadas e são de mesma finalidade — IA generalista —, então manter as duas para o mesmo usuário é redundância paga.</t>
         </is>
       </c>
       <c r="D33" s="69" t="inlineStr">
         <is>
-          <t>Duas consequências. ORÇAMENTO: uma licença usada pelo Financeiro é custo de outra área lançado no TI/Jurídico — é exatamente o caso que o rateio do item L precisa resolver, e sem o mapa não há como ratear. RISCO: contas de IA generalista são individuais, e o compartilhamento entre pessoas costuma contrariar os termos de uso do fornecedor, com risco de suspensão. Mais grave num escritório de advocacia: o histórico de conversas fica visível para todos que usam o mesmo login, então dados de um cliente podem ser vistos por quem não atua no caso — questão de sigilo profissional, não só de custo. Avaliar licenças individuais ou plano de equipe, que costuma sair mais barato por usuário e separa os históricos.</t>
+          <t>É pré-requisito para fechar a meta do item L: não dá para dimensionar o orçamento de IA sem saber quantas licenças de cada ferramenta ficam de pé. Referência de custo: a OpenAI aparece no extrato com R$ 5.950,10 em sete meses, sendo R$ 5.394 só em abr/26. Levantar a mesma informação para os demais usuários, não só a diretoria — a decisão vale para todo mundo.</t>
         </is>
       </c>
       <c r="E33" s="69" t="inlineStr">
@@ -29471,61 +29706,61 @@
       </c>
       <c r="F33" s="74" t="inlineStr">
         <is>
-          <t>LEVANTAR</t>
+          <t>PERGUNTAR</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="71" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B34" s="72" t="inlineStr">
         <is>
-          <t>Divisão de responsabilidades no acompanhamento</t>
+          <t>Mapa de licenças de IA — quem usa o quê</t>
         </is>
       </c>
       <c r="C34" s="72" t="inlineStr">
         <is>
-          <t>Definição de quem faz o quê no controle orçamentário do TI. Capacidades: Vinicius, analista, 173 h/mês a R$ 31,25/h de custo total; Jonathan, consultor/desenvolvedor, 3 dias por semana, 104 h/mês a R$ 60,58/h — o dobro. Cristiane na gestão.</t>
+          <t>Situação atual conhecida: a licença do GPT era da Thamar e hoje é usada em conjunto por Gil, Miguel e Thamar. Uma licença também foi cedida ao Financeiro. Falta o mapa completo — quem usa cada ferramenta, em qual área e sob qual login.</t>
         </is>
       </c>
       <c r="D34" s="72" t="inlineStr">
         <is>
-          <t>VINICIUS (todo o recorrente): extração mensal do SIENGE e lançamento do realizado, controle de equipamentos (solicitações, empréstimos, troca 1x1), acompanhamento do saldo por área para avisar antes do estouro, conferência de faturas contra contrato. JONATHAN (pontual e técnico, nunca rotina): avaliar AnyDesk x Monitor Remoto, avaliar Claude x GPT e planos de equipe, e automatizar a extração do SIENGE — esta última é a que paga o custo dele, porque devolve tempo do analista todos os meses. CRISTIANE: negociação de contratos, rateio, o que entra e sai do orçamento, apresentação à diretoria. Critério: 104 h/mês é capacidade limitada, e cada hora do consultor em tarefa administrativa custa o dobro da mesma hora do analista. Se o Jonathan aparecer na rotina mensal, é sinal de que algo deveria ter sido automatizado.</t>
+          <t>Duas consequências. ORÇAMENTO: uma licença usada pelo Financeiro é custo de outra área lançado no TI/Jurídico — é exatamente o caso que o rateio do item L precisa resolver, e sem o mapa não há como ratear. RISCO: contas de IA generalista são individuais, e o compartilhamento entre pessoas costuma contrariar os termos de uso do fornecedor, com risco de suspensão. Mais grave num escritório de advocacia: o histórico de conversas fica visível para todos que usam o mesmo login, então dados de um cliente podem ser vistos por quem não atua no caso — questão de sigilo profissional, não só de custo. Avaliar licenças individuais ou plano de equipe, que costuma sair mais barato por usuário e separa os históricos.</t>
         </is>
       </c>
       <c r="E34" s="72" t="inlineStr">
         <is>
-          <t>Cristiane</t>
-        </is>
-      </c>
-      <c r="F34" s="73" t="inlineStr">
-        <is>
-          <t>APLICADO</t>
+          <t>Cristiane + Vitor</t>
+        </is>
+      </c>
+      <c r="F34" s="74" t="inlineStr">
+        <is>
+          <t>LEVANTAR</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B35" s="69" t="inlineStr">
         <is>
-          <t>Office 365 — CONFIRMAR se R$ 440 é por licença ou o total</t>
+          <t>Divisão de responsabilidades no acompanhamento</t>
         </is>
       </c>
       <c r="C35" s="69" t="inlineStr">
         <is>
-          <t>A gestora esclareceu a estrutura: cada licença atende 6 funcionários e custa R$ 440. Com 10 licenças, fecham os 60 usuários da ficha. Falta confirmar UMA coisa: os R$ 440 são o valor de CADA licença ou o total pago por mês? Não há lançamento de Microsoft/Office no extrato de jan a jul, o que também precisa ser explicado — é custo mensal e deveria aparecer.</t>
+          <t>Definição de quem faz o quê no controle orçamentário do TI. Capacidades: Vinicius, analista, 173 h/mês a R$ 31,25/h de custo total; Jonathan, consultor/desenvolvedor, 3 dias por semana, 104 h/mês a R$ 60,58/h — o dobro. Cristiane na gestão.</t>
         </is>
       </c>
       <c r="D35" s="69" t="inlineStr">
         <is>
-          <t>A diferença entre as duas leituras é enorme. Se R$ 440 for o total: R$ 5.280/ano, R$ 780 acima dos R$ 4.500 orçados — ajuste pequeno. Se for por licença: 10 x R$ 440 = R$ 4.400/mês, R$ 52.800/ano, R$ 48.300 acima do orçado — sozinho maior que todas as despesas orçadas do TI, e o orçamento da área estaria comprometido. Confirmar antes da reunião.</t>
+          <t>VINICIUS (suporte + recorrente + apoio ao desenvolvimento): suporte ao usuário; extração mensal do SIENGE e lançamento do realizado; controle de equipamentos (solicitações, empréstimos, troca 1x1); acompanhamento do saldo por área para avisar antes do estouro; conferência de faturas contra contrato; e apoio operacional ao Jonathan no que o desenvolvimento exigir. Esse apoio é o que multiplica as 104 h/mês do consultor: cada tarefa operacional que sai das mãos dele por R$ 31,25/h é uma hora de R$ 60,58 liberada para o que só ele faz. JONATHAN (pontual e técnico, nunca rotina): avaliar AnyDesk x Monitor Remoto, avaliar Claude x GPT e planos de equipe, e automatizar a extração do SIENGE — esta última é a que paga o custo dele, porque devolve tempo do analista todos os meses. CRISTIANE: negociação de contratos, rateio, o que entra e sai do orçamento, apresentação à diretoria. Critério: 104 h/mês é capacidade limitada, e cada hora do consultor em tarefa administrativa custa o dobro da mesma hora do analista. Se o Jonathan aparecer na rotina mensal, é sinal de que algo deveria ter sido automatizado.</t>
         </is>
       </c>
       <c r="E35" s="69" t="inlineStr">
@@ -29533,39 +29768,71 @@
           <t>Cristiane</t>
         </is>
       </c>
-      <c r="F35" s="74" t="inlineStr">
-        <is>
-          <t>CONFIRMAR</t>
+      <c r="F35" s="73" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="71" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B36" s="72" t="inlineStr">
+        <is>
+          <t>Office 365 — CONFIRMAR se R$ 440 é por licença ou o total</t>
+        </is>
+      </c>
+      <c r="C36" s="72" t="inlineStr">
+        <is>
+          <t>A gestora esclareceu a estrutura: cada licença atende 6 funcionários e custa R$ 440. Com 10 licenças, fecham os 60 usuários da ficha. Falta confirmar UMA coisa: os R$ 440 são o valor de CADA licença ou o total pago por mês? Não há lançamento de Microsoft/Office no extrato de jan a jul, o que também precisa ser explicado — é custo mensal e deveria aparecer.</t>
+        </is>
+      </c>
+      <c r="D36" s="72" t="inlineStr">
+        <is>
+          <t>A diferença entre as duas leituras é enorme. Se R$ 440 for o total: R$ 5.280/ano, R$ 780 acima dos R$ 4.500 orçados — ajuste pequeno. Se for por licença: 10 x R$ 440 = R$ 4.400/mês, R$ 52.800/ano, R$ 48.300 acima do orçado — sozinho maior que todas as despesas orçadas do TI, e o orçamento da área estaria comprometido. Confirmar antes da reunião.</t>
+        </is>
+      </c>
+      <c r="E36" s="72" t="inlineStr">
+        <is>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F36" s="74" t="inlineStr">
+        <is>
+          <t>CONFIRMAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="68" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="72" t="inlineStr">
+      <c r="B37" s="69" t="inlineStr">
         <is>
           <t>Competência x caixa — DECIDIR O REGIME</t>
         </is>
       </c>
-      <c r="C36" s="72" t="inlineStr">
+      <c r="C37" s="69" t="inlineStr">
         <is>
           <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
         </is>
       </c>
-      <c r="D36" s="72" t="inlineStr">
+      <c r="D37" s="69" t="inlineStr">
         <is>
           <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
         </is>
       </c>
-      <c r="E36" s="72" t="inlineStr">
+      <c r="E37" s="69" t="inlineStr">
         <is>
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F36" s="75" t="inlineStr">
+      <c r="F37" s="75" t="inlineStr">
         <is>
           <t>DECIDIR</t>
         </is>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -28623,13 +28623,27 @@
         <f>Planejado!G31</f>
         <v/>
       </c>
-      <c r="H31" s="58" t="n"/>
-      <c r="I31" s="58" t="n"/>
-      <c r="J31" s="58" t="n"/>
-      <c r="K31" s="58" t="n"/>
-      <c r="L31" s="58" t="n"/>
-      <c r="M31" s="58" t="n"/>
-      <c r="N31" s="58" t="n"/>
+      <c r="H31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="58" t="n">
+        <v>0</v>
+      </c>
       <c r="O31" s="58" t="n"/>
       <c r="P31" s="58" t="n"/>
       <c r="Q31" s="58" t="n"/>
@@ -28639,8 +28653,16 @@
         <f>SUM(H31:S31)</f>
         <v/>
       </c>
-      <c r="U31" s="59" t="n"/>
-      <c r="V31" s="59" t="n"/>
+      <c r="U31" s="59" t="inlineStr">
+        <is>
+          <t>Gestora, 05/08/26</t>
+        </is>
+      </c>
+      <c r="V31" s="59" t="inlineStr">
+        <is>
+          <t>Ainda não contratado — sem custo até jul/26</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="56">
@@ -30817,7 +30839,7 @@
       </c>
       <c r="D32" s="72" t="inlineStr">
         <is>
-          <t>Não há sobreposição com o 'Monitor Remoto' do extrato: aquele credor é o Jonathan (J H Alves), consultor, não um software de acesso remoto. O AnyDesk é contratação nova e sem substituto atual. Definir valor e mês para a linha entrar no orçamento — enquanto o planejado for zero, qualquer lançamento aparece como 'Não orçado'.</t>
+          <t>Ainda não contratado — realizado zerado até jul/26, e não falta de lançamento. Não há sobreposição com o 'Monitor Remoto' do extrato: aquele credor é o Jonathan (J H Alves), consultor, não um software de acesso remoto. É contratação nova, sem substituto atual. Definir valor e mês antes de assinar — enquanto o planejado for zero, qualquer lançamento aparece como 'Não orçado'.</t>
         </is>
       </c>
       <c r="E32" s="72" t="inlineStr">

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -26163,12 +26163,12 @@
       </c>
       <c r="D24" s="48" t="inlineStr">
         <is>
-          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
+          <t>Projeto Sala de Reunião — itens funcionais</t>
         </is>
       </c>
       <c r="E24" s="48" t="inlineStr">
         <is>
-          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc.</t>
+          <t>Câmeras, microfones e cadeiras. DECIDIDO executar só o funcional; cafeteira, copos, canetas e blocos personalizados saem para o Administrativo. Valor a rever quando vier a quebra entre funcional e consumo</t>
         </is>
       </c>
       <c r="F24" s="47" t="inlineStr"/>
@@ -30669,27 +30669,27 @@
       </c>
       <c r="B27" s="69" t="inlineStr">
         <is>
-          <t>Sala de Reunião — EXECUTAR, PAUSAR OU REPENSAR?</t>
+          <t>Sala de Reunião — DECIDIDO: executar só o funcional</t>
         </is>
       </c>
       <c r="C27" s="69" t="inlineStr">
         <is>
-          <t>Projeto orçado em R$ 2.800/mês × 12 = R$ 33.600, classificado em Móveis e Utensílios, sem nenhum lançamento até jul/26. A gestora levanta que a sala já não comporta todas as pessoas, então investir na configuração atual pode não resolver o problema real. Três caminhos: executar como está, pausar, ou repensar a solução (outro espaço, formato híbrido, mais de uma sala).</t>
+          <t>DECISÃO DA GESTORA: mexer somente no que for funcional. Entram os itens de infraestrutura de reunião — câmeras, microfones e cadeiras. Ficam de fora cafeteira, copos, canetas e blocos personalizados, que são consumo e brinde, pertencem ao Administrativo (item U) e não resolvem o problema da sala. O orçamento atual é de R$ 2.800/mês, R$ 33.600 no ano, sem nenhum lançamento até jul/26.</t>
         </is>
       </c>
       <c r="D27" s="69" t="inlineStr">
         <is>
-          <t>É a maior despesa isolada do TI e 38% de tudo que a área tem orçado em despesas. Se pausar, são R$ 33.600 liberados — mais que a economia atual do departamento. Decidir antes de comprometer o valor. Se a decisão for executar, definir também se é compra pontual ou parcelada: hoje está diluída linearmente, e se for compra única o desvio mensal vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. SEPARAR OS ITENS: a descrição na ficha mistura infraestrutura de reunião (câmeras, microfones, cadeiras) com material de consumo e brindes (canetas, blocos personalizados, copos, cafeteira). O segundo grupo é papelaria e deveria estar no Administrativo, não no TI (item U).</t>
+          <t>FALTA A QUEBRA DO VALOR: quanto dos R$ 33.600 é funcional e quanto é consumo. Só com isso dá para ajustar a linha e liberar a diferença. Levantar orçamento dos itens funcionais antes de comprar. Definir também se é compra pontual ou parcelada — hoje está diluída linearmente em 12 meses, e se for compra única o desvio vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. Segue de pé a observação da gestora de que a sala já não comporta todas as pessoas: o funcional melhora a qualidade da reunião, não a capacidade — se o problema de espaço precisar de solução, é projeto à parte.</t>
         </is>
       </c>
       <c r="E27" s="69" t="inlineStr">
         <is>
-          <t>Cristiane + Diretoria</t>
-        </is>
-      </c>
-      <c r="F27" s="76" t="inlineStr">
-        <is>
-          <t>PAUTA REUNIÃO</t>
+          <t>Cristiane</t>
+        </is>
+      </c>
+      <c r="F27" s="74" t="inlineStr">
+        <is>
+          <t>QUEBRAR VALOR</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comparativo'!$A$5:$N$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Planejado'!$A$4:$T$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Controle de Equipamentos'!$A$11:$J$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Controle de Equipamentos'!$A$12:$J$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Contas Pagas (resumo)'!$A$4:$L$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Contas Pagas (detalhe)'!$A$4:$H$423</definedName>
   </definedNames>
@@ -2108,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2187,12 +2187,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="90" t="inlineStr">
         <is>
-          <t>Sem devolução</t>
+          <t>Prazo: 7 dias</t>
         </is>
       </c>
       <c r="B7" s="85" t="inlineStr">
         <is>
-          <t>Se a pessoa não entrega o item antigo, a solicitação fica 'Pendente devolução' e não vira compra até ser resolvida.</t>
+          <t>O empréstimo vale por 7 dias corridos. Passou disso, o status vira 'Atrasado' e o TI cobra a devolução. A coluna 'Dias em posse' calcula sozinha a partir da data de saída.</t>
         </is>
       </c>
       <c r="C7" s="86" t="n"/>
@@ -2207,12 +2207,12 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="90" t="inlineStr">
         <is>
-          <t>Aviso de saldo</t>
+          <t>Sem devolução</t>
         </is>
       </c>
       <c r="B8" s="85" t="inlineStr">
         <is>
-          <t>Antes de aprovar, conferir o saldo da rubrica da área solicitante. Se a compra for levar ao estouro, avisar a área ANTES de comprar (pendência R).</t>
+          <t>Se a pessoa não entrega o item antigo, a solicitação fica 'Pendente devolução' e não vira compra até ser resolvida.</t>
         </is>
       </c>
       <c r="C8" s="86" t="n"/>
@@ -2224,76 +2224,84 @@
       <c r="I8" s="86" t="n"/>
       <c r="J8" s="86" t="n"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="83" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="90" t="inlineStr">
+        <is>
+          <t>Aviso de saldo</t>
+        </is>
+      </c>
+      <c r="B9" s="85" t="inlineStr">
+        <is>
+          <t>Antes de aprovar, conferir o saldo da rubrica da área solicitante. Se a compra for levar ao estouro, avisar a área ANTES de comprar (pendência R).</t>
+        </is>
+      </c>
+      <c r="C9" s="86" t="n"/>
+      <c r="D9" s="86" t="n"/>
+      <c r="E9" s="86" t="n"/>
+      <c r="F9" s="86" t="n"/>
+      <c r="G9" s="86" t="n"/>
+      <c r="H9" s="86" t="n"/>
+      <c r="I9" s="86" t="n"/>
+      <c r="J9" s="86" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="83" t="inlineStr">
         <is>
           <t>SOLICITAÇÕES</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Área solicitante</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Solicitante</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Motivo</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Devolveu o antigo?</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Patrimônio devolvido</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Valor estimado</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="91" t="n"/>
-      <c r="B12" s="91" t="n"/>
-      <c r="C12" s="91" t="n"/>
-      <c r="D12" s="91" t="n"/>
-      <c r="E12" s="91" t="n"/>
-      <c r="F12" s="91" t="n"/>
-      <c r="G12" s="91" t="n"/>
-      <c r="H12" s="58" t="n"/>
-      <c r="I12" s="91" t="n"/>
-      <c r="J12" s="91" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="91" t="n"/>
@@ -2763,79 +2771,76 @@
       <c r="I51" s="91" t="n"/>
       <c r="J51" s="91" t="n"/>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="29" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="91" t="n"/>
+      <c r="B52" s="91" t="n"/>
+      <c r="C52" s="91" t="n"/>
+      <c r="D52" s="91" t="n"/>
+      <c r="E52" s="91" t="n"/>
+      <c r="F52" s="91" t="n"/>
+      <c r="G52" s="91" t="n"/>
+      <c r="H52" s="58" t="n"/>
+      <c r="I52" s="91" t="n"/>
+      <c r="J52" s="91" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t>EMPRÉSTIMOS (equipamento reserva)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="92" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="92" t="inlineStr">
         <is>
           <t>Item emprestado</t>
         </is>
       </c>
-      <c r="B54" s="92" t="inlineStr">
+      <c r="B55" s="92" t="inlineStr">
         <is>
           <t>Patrimônio</t>
         </is>
       </c>
-      <c r="C54" s="92" t="inlineStr">
+      <c r="C55" s="92" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="D54" s="92" t="inlineStr">
+      <c r="D55" s="92" t="inlineStr">
         <is>
           <t>Pessoa</t>
         </is>
       </c>
-      <c r="E54" s="92" t="inlineStr">
+      <c r="E55" s="92" t="inlineStr">
         <is>
           <t>Saída em</t>
         </is>
       </c>
-      <c r="F54" s="92" t="inlineStr">
+      <c r="F55" s="92" t="inlineStr">
         <is>
           <t>Previsão de devolução</t>
         </is>
       </c>
-      <c r="G54" s="92" t="inlineStr">
+      <c r="G55" s="92" t="inlineStr">
         <is>
           <t>Devolvido em</t>
         </is>
       </c>
-      <c r="H54" s="92" t="inlineStr">
+      <c r="H55" s="92" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I54" s="92" t="inlineStr">
-        <is>
-          <t>Dias em posse</t>
-        </is>
-      </c>
-      <c r="J54" s="92" t="inlineStr">
+      <c r="I55" s="92" t="inlineStr">
+        <is>
+          <t>Dias em posse (limite: 7)</t>
+        </is>
+      </c>
+      <c r="J55" s="92" t="inlineStr">
         <is>
           <t>Observações</t>
         </is>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="91" t="n"/>
-      <c r="B55" s="91" t="n"/>
-      <c r="C55" s="91" t="n"/>
-      <c r="D55" s="91" t="n"/>
-      <c r="E55" s="91" t="n"/>
-      <c r="F55" s="91" t="n"/>
-      <c r="G55" s="91" t="n"/>
-      <c r="H55" s="91" t="n"/>
-      <c r="I55" s="93">
-        <f>IF(E55="","",IF(G55="",TODAY()-E55,G55-E55))</f>
-        <v/>
-      </c>
-      <c r="J55" s="91" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="91" t="n"/>
@@ -3197,27 +3202,48 @@
       </c>
       <c r="J79" s="91" t="n"/>
     </row>
+    <row r="80">
+      <c r="A80" s="91" t="n"/>
+      <c r="B80" s="91" t="n"/>
+      <c r="C80" s="91" t="n"/>
+      <c r="D80" s="91" t="n"/>
+      <c r="E80" s="91" t="n"/>
+      <c r="F80" s="91" t="n"/>
+      <c r="G80" s="91" t="n"/>
+      <c r="H80" s="91" t="n"/>
+      <c r="I80" s="93">
+        <f>IF(E80="","",IF(G80="",TODAY()-E80,G80-E80))</f>
+        <v/>
+      </c>
+      <c r="J80" s="91" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A11:J51"/>
-  <mergeCells count="9">
+  <autoFilter ref="A12:J52"/>
+  <mergeCells count="10">
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B5:J5"/>
-    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="B9:J9"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A10:J10"/>
     <mergeCell ref="B6:J6"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
+  <conditionalFormatting sqref="I56:I80">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>7</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="I12:I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I13:I52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aberta,Aguardando devolução,Aprovada,Comprada,Entregue,Negada"</formula1>
     </dataValidation>
-    <dataValidation sqref="F12:F51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F13:F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sim,Não,Não se aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="H55:H79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H56:H80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Emprestado,Devolvido,Atrasado,Baixado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -30775,17 +30801,17 @@
       </c>
       <c r="D30" s="72" t="inlineStr">
         <is>
-          <t>Além de controlar estoque, a troca 1x1 gera dado de durabilidade e padrão de uso — se uma área quebra três vezes mais que as outras, isso aparece. Encaminhar: (1) comunicar a regra às áreas; (2) montar o pequeno estoque de reserva; (3) definir quantos dias o empréstimo pode durar antes de virar 'Atrasado'; (4) verificar com o financeiro se o lançamento pode nascer no centro de custo da área solicitante — se puder, o controle de custo por área sai do próprio SIENGE e esta aba fica só para o que ainda não virou pagamento.</t>
+          <t>APROVADA pela gestora, com prazo de empréstimo de 7 DIAS CORRIDOS — passou disso, vira 'Atrasado' e o TI cobra a devolução. A aba de controle já destaca em vermelho quem passar do prazo. Além de controlar estoque, a troca 1x1 gera dado de durabilidade e padrão de uso: se uma área quebra três vezes mais que as outras, isso aparece. Falta encaminhar: (1) comunicar a regra e o prazo às áreas; (2) montar o estoque de reserva com fio; (3) verificar com o financeiro se o lançamento pode nascer no centro de custo da área solicitante — se puder, o controle de custo por área sai do próprio SIENGE e esta aba fica só para o que ainda não virou pagamento.</t>
         </is>
       </c>
       <c r="E30" s="72" t="inlineStr">
         <is>
-          <t>Cristiane</t>
+          <t>Cristiane + Vinicius</t>
         </is>
       </c>
       <c r="F30" s="74" t="inlineStr">
         <is>
-          <t>IMPLANTAR</t>
+          <t>APROVADA</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -30545,7 +30545,7 @@
       </c>
       <c r="D22" s="72" t="inlineStr">
         <is>
-          <t>Reclassificar no SIENGE para o centro de custo correto e aplicar o rateio do item L. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado. Aproveitar a abertura do novo centro de custo para acertar a classificação desde a origem.</t>
+          <t>DECIDIDO: solicitar a reclassificação contábil ao financeiro agora, sem esperar a abertura do centro de custo novo. Enquanto não for corrigido, o Jurídico carrega R$ 3.351 que não são dele e o TI aparece sem um gasto que é seu — as duas áreas ficam com o comparativo errado ao mesmo tempo. O que pedir ao financeiro: reclassificar os seis lançamentos do contrato 4134643529 (jan a jun/26) do centro de custo Jurídico para o de TI, e ajustar a classificação dos próximos para não repetir. Depois de reclassificado, aplicar o rateio do item L, já que é ferramenta de uso transversal. Quando o centro de custo novo abrir, conferir se a classificação nasceu certa.</t>
         </is>
       </c>
       <c r="E22" s="72" t="inlineStr">
@@ -30553,9 +30553,9 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F22" s="70" t="inlineStr">
-        <is>
-          <t>RECLASSIFICAR</t>
+      <c r="F22" s="74" t="inlineStr">
+        <is>
+          <t>SOLICITADA</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -30833,7 +30833,7 @@
       </c>
       <c r="D31" s="69" t="inlineStr">
         <is>
-          <t>Três diferenças separam as duas coisas: (1) papelaria acaba, não quebra, então a regra de troca 1x1 não se aplica — o controle é de estoque por ponto de pedido, outra lógica; (2) não há patrimônio nem número de série para rastrear item a item; (3) o custo de controlar uma caneta é maior que a caneta. Se papelaria estiver caindo no orçamento do TI por motivo histórico, é o mesmo caso do Adapta (item Q): classificação errada, corrigir na origem quando o centro de custo novo for aberto.</t>
+          <t>CONFIRMADO pela gestora: papelaria fica no Administrativo. Três diferenças sustentam a separação: (1) papelaria acaba, não quebra, então a regra de troca 1x1 não se aplica — o controle é de estoque por ponto de pedido, outra lógica; (2) não há patrimônio nem número de série para rastrear item a item; (3) o custo de controlar uma caneta é maior que a caneta. A VERIFICAR: se hoje há papelaria caindo no orçamento ou no centro de custo do TI por motivo histórico. Se houver, entra no mesmo pedido de reclassificação do Adapta (item Q). Vale conferir também os itens de consumo que estavam no projeto da sala de reunião — cafeteira, copos, canetas e blocos personalizados —, que por esta decisão saem do TI.</t>
         </is>
       </c>
       <c r="E31" s="69" t="inlineStr">
@@ -30843,7 +30843,7 @@
       </c>
       <c r="F31" s="74" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO</t>
+          <t>CONFIRMADA</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -22246,7 +22246,7 @@
       </c>
       <c r="B3" s="36" t="inlineStr">
         <is>
-          <t>Jul/26</t>
+          <t>Jun/26</t>
         </is>
       </c>
       <c r="C3" s="37" t="inlineStr">
@@ -27102,11 +27102,9 @@
         <v>6750</v>
       </c>
       <c r="N5" s="58" t="n">
-        <v>6750</v>
-      </c>
-      <c r="O5" s="58" t="n">
         <v>8818</v>
       </c>
+      <c r="O5" s="58" t="n"/>
       <c r="P5" s="58" t="n"/>
       <c r="Q5" s="58" t="n"/>
       <c r="R5" s="58" t="n"/>
@@ -27117,12 +27115,12 @@
       </c>
       <c r="U5" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V5" s="59" t="inlineStr">
         <is>
-          <t>R$ 6.750/mês de jan a jul; R$ 8.818 pagos em 01/08 (ref. julho). Lançado por caixa</t>
+          <t>R$ 6.750/mês de jan a jun e R$ 8.818 em jul (pago em 01/08). O pagamento de jan/26 era serviço de dez/25 e saiu do exercício</t>
         </is>
       </c>
     </row>
@@ -27187,7 +27185,7 @@
       </c>
       <c r="U6" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V6" s="59" t="inlineStr">
@@ -27232,7 +27230,7 @@
         <v>4500</v>
       </c>
       <c r="J7" s="58" t="n">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="K7" s="58" t="n">
         <v>5500</v>
@@ -27243,9 +27241,7 @@
       <c r="M7" s="58" t="n">
         <v>5500</v>
       </c>
-      <c r="N7" s="58" t="n">
-        <v>5500</v>
-      </c>
+      <c r="N7" s="58" t="n"/>
       <c r="O7" s="58" t="n"/>
       <c r="P7" s="58" t="n"/>
       <c r="Q7" s="58" t="n"/>
@@ -27257,12 +27253,12 @@
       </c>
       <c r="U7" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V7" s="59" t="inlineStr">
         <is>
-          <t>R$ 4.500/mês em jan–mar; aumento de R$ 1.000 a partir de abr/26</t>
+          <t>R$ 4.500 em jan–fev e R$ 5.500 de mar a jun, por competência. CONFERIR: o aumento foi no serviço de mar ou de abr?</t>
         </is>
       </c>
     </row>
@@ -27313,9 +27309,7 @@
       <c r="M8" s="58" t="n">
         <v>2750</v>
       </c>
-      <c r="N8" s="58" t="n">
-        <v>2750</v>
-      </c>
+      <c r="N8" s="58" t="n"/>
       <c r="O8" s="58" t="n"/>
       <c r="P8" s="58" t="n"/>
       <c r="Q8" s="58" t="n"/>
@@ -27327,7 +27321,7 @@
       </c>
       <c r="U8" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V8" s="59" t="inlineStr">
@@ -27407,7 +27401,7 @@
       </c>
       <c r="U9" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V9" s="59" t="inlineStr">
@@ -27477,7 +27471,7 @@
       </c>
       <c r="U10" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V10" s="59" t="inlineStr">
@@ -27627,7 +27621,7 @@
       </c>
       <c r="U12" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V12" s="59" t="n"/>
@@ -27693,7 +27687,7 @@
       </c>
       <c r="U13" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V13" s="59" t="inlineStr">
@@ -27763,7 +27757,7 @@
       </c>
       <c r="U14" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V14" s="59" t="inlineStr">
@@ -27871,9 +27865,7 @@
       <c r="M16" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="58" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" s="58" t="n"/>
       <c r="O16" s="58" t="n"/>
       <c r="P16" s="58" t="n"/>
       <c r="Q16" s="58" t="n"/>
@@ -27885,7 +27877,7 @@
       </c>
       <c r="U16" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V16" s="59" t="inlineStr">
@@ -27933,17 +27925,15 @@
         <v>0</v>
       </c>
       <c r="K17" s="58" t="n">
-        <v>0</v>
+        <v>3723.62</v>
       </c>
       <c r="L17" s="58" t="n">
-        <v>3723.62</v>
+        <v>6173.37</v>
       </c>
       <c r="M17" s="58" t="n">
-        <v>6173.37</v>
-      </c>
-      <c r="N17" s="58" t="n">
         <v>6300</v>
       </c>
+      <c r="N17" s="58" t="n"/>
       <c r="O17" s="58" t="n"/>
       <c r="P17" s="58" t="n"/>
       <c r="Q17" s="58" t="n"/>
@@ -27960,7 +27950,7 @@
       </c>
       <c r="V17" s="59" t="inlineStr">
         <is>
-          <t>01/05 NFS.76 R$ 3.723,62; 01/06 NFS.78 R$ 6.173,37; 01/07 NFS.3 R$ 6.300,00. Sem pagamento em jan–abr: contratação segurada</t>
+          <t>Serviço de abr, mai e jun (pagos em 01/05, 01/06 e 01/07). Zero em jan–mar: contratação segurada — bate com a entrada em abr</t>
         </is>
       </c>
     </row>
@@ -27994,7 +27984,7 @@
         <v/>
       </c>
       <c r="H18" s="58" t="n">
-        <v>4311.56</v>
+        <v>0</v>
       </c>
       <c r="I18" s="58" t="n">
         <v>0</v>
@@ -28040,7 +28030,7 @@
       </c>
       <c r="V18" s="59" t="inlineStr">
         <is>
-          <t>19/01 NFS.70 R$ 4.311,56 — serviço esporádico, provavelmente referente a dez/25. Vínculo encerrado com a entrada como consultor fixo</t>
+          <t>Zero no exercício: o pagamento de R$ 4.311,56 em 19/01 (NFS.70) era serviço de dez/25 e, por competência, não pertence a 2026. Vínculo encerrado com a entrada como consultor fixo</t>
         </is>
       </c>
     </row>
@@ -28681,7 +28671,7 @@
       </c>
       <c r="U31" s="59" t="inlineStr">
         <is>
-          <t>Gestora, 05/08/26</t>
+          <t>Gestora, 05/08/26 — competência</t>
         </is>
       </c>
       <c r="V31" s="59" t="inlineStr">
@@ -31015,17 +31005,17 @@
       </c>
       <c r="B37" s="69" t="inlineStr">
         <is>
-          <t>Competência x caixa — DECIDIR O REGIME</t>
+          <t>Competência x caixa — DECIDIDO: COMPETÊNCIA</t>
         </is>
       </c>
       <c r="C37" s="69" t="inlineStr">
         <is>
-          <t>Confirmado pela gestora: TODOS os PJs das duas áreas prestam o serviço e recebem no mês seguinte — no Jurídico, Miguel, Thamar e Dra. Michele; no TI, Elias e Jonathan. O que foi pago em jan/26 é serviço de dez/2025, e o serviço de dez/26 só será pago em jan/2027. Hoje o realizado está lançado por CAIXA (mês do pagamento), que é como os valores foram informados, enquanto o orçamento foi montado por COMPETÊNCIA (mês do serviço). São bases diferentes no mesmo comparativo.</t>
+          <t>Todos os PJs prestam no mês e recebem no seguinte — Miguel, Thamar e Dra. Michele no Jurídico; Elias e Jonathan no TI. O realizado foi convertido para COMPETÊNCIA: os valores dos PJs foram deslocados um mês para trás em relação à data de pagamento. O que foi pago em jan/26 era serviço de dez/25 e saiu do exercício.</t>
         </is>
       </c>
       <c r="D37" s="69" t="inlineStr">
         <is>
-          <t>RECOMENDAÇÃO: migrar para competência, deslocando os PJs um mês para trás. Motivos: (1) o orçamento já é de competência, então acaba a comparação de bases diferentes; (2) por caixa, o ano de 2026 carrega um mês de 2025 e perde dez/26, o que distorce sempre que o valor muda no meio do ano — no Miguel, R$ 47.250 por caixa contra R$ 49.318 por competência em jan–jul, R$ 2.068 de diferença; (3) o SIENGE gera os dois regimes, então é escolha de configuração. Contra: caixa é mais fácil de bater com o extrato bancário. Decidir UMA vez e manter, senão o histórico mistura critérios. ATENÇÃO NO JONATHAN: o planejado dele começa em abr/26 (competência) e o realizado também foi lançado a partir de abr (caixa) — se ele recebe no mês seguinte, o pagamento de abril é serviço de março, e ou a entrada dele foi em março, ou o realizado de abril deveria ser zero. Conferir junto com a decisão do regime.</t>
+          <t>Três efeitos. (1) O último mês completo passa a ser JUNHO, não julho: o serviço de jul só fecha quando sair o pagamento de ago — o mês de referência do Comparativo foi ajustado. (2) A conversão validou a entrada do Jonathan: por competência, o primeiro mês de serviço dele cai em abr, exatamente como informado. (3) O Monitor Remoto zerou no exercício — aquele pagamento de jan era serviço de dez/25. A CONFERIR: os CLT (Geovanna e Vinicius) NÃO foram deslocados. Se a folha for paga no mês seguinte, como é usual, eles também precisam deslocar. E na Thamar, confirmar se o aumento valeu para o serviço de mar ou de abr. Ao configurar a extração no SIENGE, travar o regime de competência e manter — trocar no meio do ano mistura critérios no histórico.</t>
         </is>
       </c>
       <c r="E37" s="69" t="inlineStr">
@@ -31033,9 +31023,9 @@
           <t>Cristiane + Financeiro</t>
         </is>
       </c>
-      <c r="F37" s="75" t="inlineStr">
-        <is>
-          <t>DECIDIR</t>
+      <c r="F37" s="73" t="inlineStr">
+        <is>
+          <t>APLICADO</t>
         </is>
       </c>
     </row>

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -27171,9 +27171,7 @@
       <c r="M6" s="58" t="n">
         <v>2886.91</v>
       </c>
-      <c r="N6" s="58" t="n">
-        <v>2886.91</v>
-      </c>
+      <c r="N6" s="58" t="n"/>
       <c r="O6" s="58" t="n"/>
       <c r="P6" s="58" t="n"/>
       <c r="Q6" s="58" t="n"/>
@@ -27457,9 +27455,7 @@
       <c r="M10" s="58" t="n">
         <v>136</v>
       </c>
-      <c r="N10" s="58" t="n">
-        <v>136</v>
-      </c>
+      <c r="N10" s="58" t="n"/>
       <c r="O10" s="58" t="n"/>
       <c r="P10" s="58" t="n"/>
       <c r="Q10" s="58" t="n"/>
@@ -27607,9 +27603,7 @@
       <c r="M12" s="58" t="n">
         <v>970</v>
       </c>
-      <c r="N12" s="58" t="n">
-        <v>970</v>
-      </c>
+      <c r="N12" s="58" t="n"/>
       <c r="O12" s="58" t="n"/>
       <c r="P12" s="58" t="n"/>
       <c r="Q12" s="58" t="n"/>
@@ -27673,9 +27667,7 @@
       <c r="M13" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="58" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" s="58" t="n"/>
       <c r="O13" s="58" t="n"/>
       <c r="P13" s="58" t="n"/>
       <c r="Q13" s="58" t="n"/>
@@ -27743,9 +27735,7 @@
       <c r="M14" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="58" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" s="58" t="n"/>
       <c r="O14" s="58" t="n"/>
       <c r="P14" s="58" t="n"/>
       <c r="Q14" s="58" t="n"/>
@@ -28657,9 +28647,7 @@
       <c r="M31" s="58" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="58" t="n">
-        <v>0</v>
-      </c>
+      <c r="N31" s="58" t="n"/>
       <c r="O31" s="58" t="n"/>
       <c r="P31" s="58" t="n"/>
       <c r="Q31" s="58" t="n"/>
@@ -31015,7 +31003,7 @@
       </c>
       <c r="D37" s="69" t="inlineStr">
         <is>
-          <t>Três efeitos. (1) O último mês completo passa a ser JUNHO, não julho: o serviço de jul só fecha quando sair o pagamento de ago — o mês de referência do Comparativo foi ajustado. (2) A conversão validou a entrada do Jonathan: por competência, o primeiro mês de serviço dele cai em abr, exatamente como informado. (3) O Monitor Remoto zerou no exercício — aquele pagamento de jan era serviço de dez/25. A CONFERIR: os CLT (Geovanna e Vinicius) NÃO foram deslocados. Se a folha for paga no mês seguinte, como é usual, eles também precisam deslocar. E na Thamar, confirmar se o aumento valeu para o serviço de mar ou de abr. Ao configurar a extração no SIENGE, travar o regime de competência e manter — trocar no meio do ano mistura critérios no histórico.</t>
+          <t>Três efeitos. (1) O último mês completo passa a ser JUNHO, não julho: o serviço de jul só fecha quando sair o pagamento de ago — o mês de referência do Comparativo foi ajustado. (2) A conversão validou a entrada do Jonathan: por competência, o primeiro mês de serviço dele cai em abr, exatamente como informado. (3) O Monitor Remoto zerou no exercício — aquele pagamento de jan era serviço de dez/25. Os CLT (Geovanna e Vinicius) seguem a mesma regra, confirmado pela gestora: folha paga no mês seguinte, também deslocados. A CONFERIR apenas na Thamar: se o aumento valeu para o serviço de mar ou de abr. Ao configurar a extração no SIENGE, travar o regime de competência e manter — trocar no meio do ano mistura critérios no histórico.</t>
         </is>
       </c>
       <c r="E37" s="69" t="inlineStr">

--- a/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
+++ b/orcamento/Orcamento_Planejado_x_Realizado_2026.xlsx
@@ -26189,12 +26189,12 @@
       </c>
       <c r="D24" s="48" t="inlineStr">
         <is>
-          <t>Projeto Sala de Reunião — itens funcionais</t>
+          <t>Projeto Melhoria de Infraestrutura - Sala de Reunião</t>
         </is>
       </c>
       <c r="E24" s="48" t="inlineStr">
         <is>
-          <t>Câmeras, microfones e cadeiras. DECIDIDO executar só o funcional; cafeteira, copos, canetas e blocos personalizados saem para o Administrativo. Valor a rever quando vier a quebra entre funcional e consumo</t>
+          <t>Cadeiras, cafeteira, copos, canetas, blocos personalizados, câmeras, microfones etc. APROVADO no escopo completo. Definir se é compra pontual ou parcelada — hoje está diluída linearmente em 12 meses</t>
         </is>
       </c>
       <c r="F24" s="47" t="inlineStr"/>
@@ -30673,17 +30673,17 @@
       </c>
       <c r="B27" s="69" t="inlineStr">
         <is>
-          <t>Sala de Reunião — DECIDIDO: executar só o funcional</t>
+          <t>Sala de Reunião — DECIDIDO: executar o projeto completo</t>
         </is>
       </c>
       <c r="C27" s="69" t="inlineStr">
         <is>
-          <t>DECISÃO DA GESTORA: mexer somente no que for funcional. Entram os itens de infraestrutura de reunião — câmeras, microfones e cadeiras. Ficam de fora cafeteira, copos, canetas e blocos personalizados, que são consumo e brinde, pertencem ao Administrativo (item U) e não resolvem o problema da sala. O orçamento atual é de R$ 2.800/mês, R$ 33.600 no ano, sem nenhum lançamento até jul/26.</t>
+          <t>DECISÃO DA GESTORA: executar como está, no escopo original. Entram tanto os itens de infraestrutura (câmeras, microfones, cadeiras) quanto os de consumo e ambientação (cafeteira, copos, canetas e blocos personalizados). Orçamento mantido em R$ 2.800/mês, R$ 33.600 no ano, sem nenhum lançamento até jun/26. Revoga a decisão anterior de executar só o funcional.</t>
         </is>
       </c>
       <c r="D27" s="69" t="inlineStr">
         <is>
-          <t>FALTA A QUEBRA DO VALOR: quanto dos R$ 33.600 é funcional e quanto é consumo. Só com isso dá para ajustar a linha e liberar a diferença. Levantar orçamento dos itens funcionais antes de comprar. Definir também se é compra pontual ou parcelada — hoje está diluída linearmente em 12 meses, e se for compra única o desvio vai acusar economia falsa todo mês até a compra e um pico no mês em que ocorrer. Segue de pé a observação da gestora de que a sala já não comporta todas as pessoas: o funcional melhora a qualidade da reunião, não a capacidade — se o problema de espaço precisar de solução, é projeto à parte.</t>
+          <t>É a maior despesa isolada do TI e 38% do que a área tem orçado em despesas, então o mês em que a compra ocorrer vai dominar o comparativo. DEFINIR: se é compra pontual ou parcelada. Hoje está diluída linearmente em 12 meses — se for compra única, o desvio vai acusar economia falsa todo mês até a compra e um pico no mês em que ela acontecer; nesse caso vale concentrar o planejado no mês previsto. OBSERVAR: os itens de consumo e brinde deste projeto são a exceção à decisão do item U, que tirou papelaria do TI — aqui ficam por serem parte de um projeto de ambientação, não reposição de material de escritório. E a ressalva da própria gestora continua de pé: o projeto melhora a qualidade da reunião, não a capacidade da sala. Se o espaço não comporta todas as pessoas, isso segue verdade depois da compra.</t>
         </is>
       </c>
       <c r="E27" s="69" t="inlineStr">
@@ -30693,7 +30693,7 @@
       </c>
       <c r="F27" s="74" t="inlineStr">
         <is>
-          <t>QUEBRAR VALOR</t>
+          <t>APROVADO</t>
         </is>
       </c>
     </row>
